--- a/trend/stock_trend_history.xlsx
+++ b/trend/stock_trend_history.xlsx
@@ -694,7 +694,7 @@
     <row r="1" ht="36" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>📊 주식 트렌드 조기 감지 대시보드   |   최종 업데이트: 2026-06-13 06:55</t>
+          <t>📊 주식 트렌드 조기 감지 대시보드   |   최종 업데이트: 2026-06-14 06:55</t>
         </is>
       </c>
     </row>
@@ -708,7 +708,7 @@
       </c>
       <c r="E3" s="3" t="n"/>
       <c r="G3" s="5" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="H3" s="3" t="n"/>
       <c r="J3" s="6" t="n">
@@ -787,21 +787,21 @@
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="11" t="inlineStr">
         <is>
-          <t>⚡ 최신(2026-06-13) 상위: 반도체  점수 69.0점</t>
+          <t>⚡ 최신(2026-06-14) 상위: 반도체  점수 74.0점</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1">
       <c r="A11" s="12" t="inlineStr">
         <is>
-          <t>⚡ 최신(2026-06-13) 상위: 로봇  점수 27.0점</t>
+          <t>⚡ 최신(2026-06-14) 상위: 바이오  점수 23.0점</t>
         </is>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1">
       <c r="A12" s="11" t="inlineStr">
         <is>
-          <t>⚡ 최신(2026-06-13) 상위: 인공지능  점수 23.0점</t>
+          <t>⚡ 최신(2026-06-14) 상위: 로봇  점수 22.0점</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="B14" s="15" t="n">
@@ -928,10 +928,10 @@
         </is>
       </c>
       <c r="D14" s="15" t="n">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="E14" s="15" t="n">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="F14" s="15" t="n">
         <v>0</v>
@@ -947,7 +947,7 @@
       </c>
       <c r="J14" s="17" t="inlineStr">
         <is>
-          <t>매일경제 헤드라인 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 기사 언급 / 매일경제 기사 언급 / 네이버뉴스 헤드라인 언급</t>
+          <t>매일경제 헤드라인 언급 / 매일경제 기사 언급 / 네이버뉴스 기사 언급 / 매일경제 기사 언급 / 네이버뉴스 헤드라인 언급</t>
         </is>
       </c>
       <c r="K14" s="17" t="inlineStr">
@@ -959,7 +959,7 @@
     <row r="15" ht="18" customHeight="1">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="B15" s="15" t="n">
@@ -967,14 +967,14 @@
       </c>
       <c r="C15" s="16" t="inlineStr">
         <is>
-          <t>로봇</t>
+          <t>바이오</t>
         </is>
       </c>
       <c r="D15" s="15" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="E15" s="15" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="F15" s="15" t="n">
         <v>0</v>
@@ -990,17 +990,19 @@
       </c>
       <c r="J15" s="17" t="inlineStr">
         <is>
-          <t>매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 한국경제 헤드라인 언급 / 한국경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K15" s="17" t="n">
-        <v/>
+          <t>네이버뉴스 헤드라인 언급 / 네이버뉴스 헤드라인 언급 / 매일경제 헤드라인 언급 / 네이버뉴스 헤드라인 언급 / 매일경제 기사 언급</t>
+        </is>
+      </c>
+      <c r="K15" s="17" t="inlineStr">
+        <is>
+          <t>네이버</t>
+        </is>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
       <c r="A16" s="15" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="B16" s="15" t="n">
@@ -1008,14 +1010,14 @@
       </c>
       <c r="C16" s="16" t="inlineStr">
         <is>
-          <t>인공지능</t>
+          <t>로봇</t>
         </is>
       </c>
       <c r="D16" s="15" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E16" s="15" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F16" s="15" t="n">
         <v>0</v>
@@ -1031,7 +1033,7 @@
       </c>
       <c r="J16" s="17" t="inlineStr">
         <is>
-          <t>매일경제 기사 언급 / 매일경제 기사 언급 / 네이버뉴스 기사 언급 / 매일경제 기사 언급 / 매일경제 기사 언급</t>
+          <t>매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 네이버뉴스 기사 언급 / 한국경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
         </is>
       </c>
       <c r="K16" s="17" t="inlineStr">
@@ -1043,7 +1045,7 @@
     <row r="17" ht="18" customHeight="1">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="B17" s="15" t="n">
@@ -1051,14 +1053,14 @@
       </c>
       <c r="C17" s="16" t="inlineStr">
         <is>
-          <t>바이오</t>
+          <t>인공지능</t>
         </is>
       </c>
       <c r="D17" s="15" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E17" s="15" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F17" s="15" t="n">
         <v>0</v>
@@ -1074,7 +1076,7 @@
       </c>
       <c r="J17" s="17" t="inlineStr">
         <is>
-          <t>네이버뉴스 헤드라인 언급 / 네이버뉴스 헤드라인 언급 / 네이버뉴스 기사 언급 / 매일경제 헤드라인 언급 / 매일경제 기사 언급</t>
+          <t>매일경제 기사 언급 / 매일경제 기사 언급 / 매일경제 기사 언급 / 매일경제 기사 언급 / 매일경제 기사 언급</t>
         </is>
       </c>
       <c r="K17" s="17" t="inlineStr">
@@ -1086,7 +1088,7 @@
     <row r="18" ht="18" customHeight="1">
       <c r="A18" s="15" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="B18" s="15" t="n">
@@ -1094,14 +1096,14 @@
       </c>
       <c r="C18" s="16" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>현대차</t>
         </is>
       </c>
       <c r="D18" s="15" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E18" s="15" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F18" s="15" t="n">
         <v>0</v>
@@ -1110,14 +1112,14 @@
         <v>0</v>
       </c>
       <c r="H18" s="18" t="n">
-        <v>7.86</v>
+        <v>1.68</v>
       </c>
       <c r="I18" s="19" t="n">
-        <v>-1.98</v>
+        <v>-13.29</v>
       </c>
       <c r="J18" s="17" t="inlineStr">
         <is>
-          <t>매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 네이버뉴스 기사 언급 / 매일경제 기사 언급</t>
+          <t>네이버뉴스 헤드라인 언급 / 한국경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
         </is>
       </c>
       <c r="K18" s="17" t="inlineStr">
@@ -1129,7 +1131,7 @@
     <row r="19" ht="18" customHeight="1">
       <c r="A19" s="15" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="B19" s="15" t="n">
@@ -1137,14 +1139,14 @@
       </c>
       <c r="C19" s="16" t="inlineStr">
         <is>
-          <t>현대차</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="D19" s="15" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E19" s="15" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F19" s="15" t="n">
         <v>0</v>
@@ -1153,14 +1155,14 @@
         <v>0</v>
       </c>
       <c r="H19" s="18" t="n">
-        <v>1.68</v>
+        <v>7.86</v>
       </c>
       <c r="I19" s="19" t="n">
-        <v>-13.29</v>
+        <v>-1.98</v>
       </c>
       <c r="J19" s="17" t="inlineStr">
         <is>
-          <t>매일경제 헤드라인 언급 / 한국경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
+          <t>매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 기사 언급 / 매일경제 기사 언급 / 매일경제 기사 언급</t>
         </is>
       </c>
       <c r="K19" s="17" t="n">
@@ -1170,7 +1172,7 @@
     <row r="20" ht="18" customHeight="1">
       <c r="A20" s="15" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="B20" s="15" t="n">
@@ -1178,7 +1180,7 @@
       </c>
       <c r="C20" s="16" t="inlineStr">
         <is>
-          <t>제약</t>
+          <t>LG</t>
         </is>
       </c>
       <c r="D20" s="15" t="n">
@@ -1193,15 +1195,15 @@
       <c r="G20" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="H20" s="15" t="n">
-        <v/>
-      </c>
-      <c r="I20" s="15" t="n">
-        <v/>
+      <c r="H20" s="19" t="n">
+        <v>-0.93</v>
+      </c>
+      <c r="I20" s="19" t="n">
+        <v>-13.34</v>
       </c>
       <c r="J20" s="17" t="inlineStr">
         <is>
-          <t>네이버뉴스 헤드라인 언급 / 네이버뉴스 헤드라인 언급 / 네이버뉴스 기사 언급 / 매일경제 기사 언급 / 매일경제 헤드라인 언급</t>
+          <t>매일경제 헤드라인 언급 / 네이버뉴스 기사 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급</t>
         </is>
       </c>
       <c r="K20" s="17" t="inlineStr">
@@ -1213,7 +1215,7 @@
     <row r="21" ht="18" customHeight="1">
       <c r="A21" s="15" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="B21" s="15" t="n">
@@ -1221,14 +1223,14 @@
       </c>
       <c r="C21" s="16" t="inlineStr">
         <is>
-          <t>KB금융</t>
+          <t>삼성전기</t>
         </is>
       </c>
       <c r="D21" s="15" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E21" s="15" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F21" s="15" t="n">
         <v>0</v>
@@ -1236,27 +1238,27 @@
       <c r="G21" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="H21" s="18" t="n">
-        <v>6.4</v>
+      <c r="H21" s="19" t="n">
+        <v>-5.04</v>
       </c>
       <c r="I21" s="19" t="n">
-        <v>-6.06</v>
+        <v>-2.45</v>
       </c>
       <c r="J21" s="17" t="inlineStr">
         <is>
-          <t>Google 급상승 검색어 등장 (KR) / 매일경제 헤드라인 언급 / 한국경제 헤드라인 언급 / 매일경제 기사 언급</t>
+          <t>네이버뉴스 기사 언급 / 한국경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 네이버뉴스 헤드라인 언급 / 매일경제 헤드라인 언급</t>
         </is>
       </c>
       <c r="K21" s="17" t="inlineStr">
         <is>
-          <t>Google</t>
+          <t>네이버</t>
         </is>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
       <c r="A22" s="15" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="B22" s="15" t="n">
@@ -1264,14 +1266,14 @@
       </c>
       <c r="C22" s="16" t="inlineStr">
         <is>
-          <t>LG</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="D22" s="15" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E22" s="15" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F22" s="15" t="n">
         <v>0</v>
@@ -1279,15 +1281,15 @@
       <c r="G22" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="H22" s="19" t="n">
-        <v>-0.93</v>
-      </c>
-      <c r="I22" s="19" t="n">
-        <v>-13.34</v>
+      <c r="H22" s="18" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="I22" s="18" t="n">
+        <v>3.86</v>
       </c>
       <c r="J22" s="17" t="inlineStr">
         <is>
-          <t>매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
+          <t>한국경제 헤드라인 언급 / 매일경제 기사 언급 / 매일경제 기사 언급 / 매일경제 기사 언급 / 한국경제 헤드라인 언급</t>
         </is>
       </c>
       <c r="K22" s="17" t="n">
@@ -1297,7 +1299,7 @@
     <row r="23" ht="18" customHeight="1">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="B23" s="15" t="n">
@@ -1309,13 +1311,13 @@
         </is>
       </c>
       <c r="D23" s="15" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E23" s="15" t="n">
         <v>10</v>
       </c>
       <c r="F23" s="15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G23" s="15" t="n">
         <v>0</v>
@@ -1328,7 +1330,7 @@
       </c>
       <c r="J23" s="17" t="inlineStr">
         <is>
-          <t>중요공시 2건 / 한국경제 헤드라인 언급 / 한국경제 헤드라인 언급 / 매일경제 헤드라인 언급</t>
+          <t>중요공시 2건 / 중요공시 3일 +100% / 한국경제 헤드라인 언급 / 한국경제 헤드라인 언급 / 매일경제 헤드라인 언급</t>
         </is>
       </c>
       <c r="K23" s="17" t="inlineStr">
@@ -1340,7 +1342,7 @@
     <row r="24" ht="18" customHeight="1">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="B24" s="15" t="n">
@@ -1348,14 +1350,14 @@
       </c>
       <c r="C24" s="16" t="inlineStr">
         <is>
-          <t>CSA 코스믹</t>
+          <t>제약</t>
         </is>
       </c>
       <c r="D24" s="15" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E24" s="15" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F24" s="15" t="n">
         <v>0</v>
@@ -1363,27 +1365,27 @@
       <c r="G24" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="H24" s="18" t="n">
-        <v>29.93</v>
-      </c>
-      <c r="I24" s="18" t="n">
-        <v>69.53</v>
+      <c r="H24" s="15" t="n">
+        <v/>
+      </c>
+      <c r="I24" s="15" t="n">
+        <v/>
       </c>
       <c r="J24" s="17" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +158% / 중요공시 5건 / 매일경제 헤드라인 언급</t>
+          <t>네이버뉴스 기사 언급 / 네이버뉴스 기사 언급 / 매일경제 기사 언급 / 네이버뉴스 헤드라인 언급 / 매일경제 헤드라인 언급</t>
         </is>
       </c>
       <c r="K24" s="17" t="inlineStr">
         <is>
-          <t>네이버, 공시</t>
+          <t>네이버</t>
         </is>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
       <c r="A25" s="15" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="B25" s="15" t="n">
@@ -1391,42 +1393,42 @@
       </c>
       <c r="C25" s="16" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>CSA 코스믹</t>
         </is>
       </c>
       <c r="D25" s="15" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E25" s="15" t="n">
         <v>9</v>
       </c>
       <c r="F25" s="15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G25" s="15" t="n">
         <v>0</v>
       </c>
       <c r="H25" s="18" t="n">
-        <v>2.33</v>
+        <v>29.93</v>
       </c>
       <c r="I25" s="18" t="n">
-        <v>3.86</v>
+        <v>69.53</v>
       </c>
       <c r="J25" s="17" t="inlineStr">
         <is>
-          <t>한국경제 헤드라인 언급 / 네이버뉴스 기사 언급 / 매일경제 기사 언급 / 매일경제 기사 언급 / 한국경제 헤드라인 언급</t>
+          <t>네이버 검색 당일 +244% / 중요공시 5건 / 중요공시 3일 +150% / 매일경제 헤드라인 언급</t>
         </is>
       </c>
       <c r="K25" s="17" t="inlineStr">
         <is>
-          <t>네이버</t>
+          <t>공시, 네이버</t>
         </is>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
       <c r="A26" s="15" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="B26" s="15" t="n">
@@ -1467,7 +1469,7 @@
     <row r="27" ht="18" customHeight="1">
       <c r="A27" s="15" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="B27" s="15" t="n">
@@ -1508,7 +1510,7 @@
     <row r="28" ht="18" customHeight="1">
       <c r="A28" s="15" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="B28" s="15" t="n">
@@ -1516,169 +1518,169 @@
       </c>
       <c r="C28" s="16" t="inlineStr">
         <is>
-          <t>NH투자증권</t>
+          <t>성호전자</t>
         </is>
       </c>
       <c r="D28" s="15" t="n">
         <v>8</v>
       </c>
       <c r="E28" s="15" t="n">
+        <v>6</v>
+      </c>
+      <c r="F28" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="G28" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" s="18" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="I28" s="19" t="n">
+        <v>-4.41</v>
+      </c>
+      <c r="J28" s="17" t="inlineStr">
+        <is>
+          <t>중요공시 3건 / 중요공시 3일 +200% / 한국경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K28" s="17" t="inlineStr">
+        <is>
+          <t>공시</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="18" customHeight="1">
+      <c r="A29" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B29" s="15" t="n">
+        <v>16</v>
+      </c>
+      <c r="C29" s="16" t="inlineStr">
+        <is>
+          <t>모바일어플라이언스</t>
+        </is>
+      </c>
+      <c r="D29" s="15" t="n">
         <v>8</v>
       </c>
-      <c r="F28" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G28" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H28" s="18" t="n">
+      <c r="E29" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="F29" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="G29" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="H29" s="19" t="n">
+        <v>-2.09</v>
+      </c>
+      <c r="I29" s="19" t="n">
+        <v>-27.06</v>
+      </c>
+      <c r="J29" s="17" t="inlineStr">
+        <is>
+          <t>중요공시 3건 / 중요공시 3일 +200% / 중요공시 7일 +50%</t>
+        </is>
+      </c>
+      <c r="K29" s="17" t="inlineStr">
+        <is>
+          <t>공시</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="18" customHeight="1">
+      <c r="A30" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B30" s="15" t="n">
+        <v>17</v>
+      </c>
+      <c r="C30" s="16" t="inlineStr">
+        <is>
+          <t>NH투자증권</t>
+        </is>
+      </c>
+      <c r="D30" s="15" t="n">
+        <v>8</v>
+      </c>
+      <c r="E30" s="15" t="n">
+        <v>8</v>
+      </c>
+      <c r="F30" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" s="18" t="n">
         <v>1.76</v>
       </c>
-      <c r="I28" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J28" s="17" t="inlineStr">
+      <c r="I30" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" s="17" t="inlineStr">
         <is>
           <t>매일경제 기사 언급 / 한국경제 헤드라인 언급 / 한국경제 헤드라인 언급 / 매일경제 기사 언급 / 매일경제 기사 언급</t>
         </is>
       </c>
-      <c r="K28" s="17" t="n">
+      <c r="K30" s="17" t="n">
         <v/>
       </c>
     </row>
-    <row r="29" ht="18" customHeight="1">
-      <c r="A29" s="20" t="inlineStr">
-        <is>
-          <t>2026-06-13</t>
-        </is>
-      </c>
-      <c r="B29" s="20" t="n">
-        <v>16</v>
-      </c>
-      <c r="C29" s="21" t="inlineStr">
+    <row r="31" ht="18" customHeight="1">
+      <c r="A31" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B31" s="15" t="n">
+        <v>18</v>
+      </c>
+      <c r="C31" s="16" t="inlineStr">
         <is>
           <t>에이팩트</t>
         </is>
       </c>
-      <c r="D29" s="20" t="n">
-        <v>6</v>
-      </c>
-      <c r="E29" s="20" t="n">
-        <v>3</v>
-      </c>
-      <c r="F29" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G29" s="20" t="n">
-        <v>3</v>
-      </c>
-      <c r="H29" s="22" t="n">
+      <c r="D31" s="15" t="n">
+        <v>7</v>
+      </c>
+      <c r="E31" s="15" t="n">
+        <v>4</v>
+      </c>
+      <c r="F31" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="H31" s="18" t="n">
         <v>13.08</v>
       </c>
-      <c r="I29" s="22" t="n">
+      <c r="I31" s="18" t="n">
         <v>45.57</v>
       </c>
-      <c r="J29" s="23" t="inlineStr">
-        <is>
-          <t>네이버 검색 당일 +81% / 중요공시 2건 / 중요공시 7일 +100%</t>
-        </is>
-      </c>
-      <c r="K29" s="23" t="inlineStr">
-        <is>
-          <t>네이버, 공시</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="18" customHeight="1">
-      <c r="A30" s="20" t="inlineStr">
-        <is>
-          <t>2026-06-13</t>
-        </is>
-      </c>
-      <c r="B30" s="20" t="n">
-        <v>17</v>
-      </c>
-      <c r="C30" s="21" t="inlineStr">
-        <is>
-          <t>우리금융지주</t>
-        </is>
-      </c>
-      <c r="D30" s="20" t="n">
-        <v>6</v>
-      </c>
-      <c r="E30" s="20" t="n">
-        <v>6</v>
-      </c>
-      <c r="F30" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G30" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H30" s="22" t="n">
-        <v>3.32</v>
-      </c>
-      <c r="I30" s="24" t="n">
-        <v>-0.16</v>
-      </c>
-      <c r="J30" s="23" t="inlineStr">
-        <is>
-          <t>중요공시 1건 / Google 급상승 검색어 등장 (KR)</t>
-        </is>
-      </c>
-      <c r="K30" s="23" t="inlineStr">
-        <is>
-          <t>공시, Google</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="18" customHeight="1">
-      <c r="A31" s="20" t="inlineStr">
-        <is>
-          <t>2026-06-13</t>
-        </is>
-      </c>
-      <c r="B31" s="20" t="n">
-        <v>18</v>
-      </c>
-      <c r="C31" s="21" t="inlineStr">
-        <is>
-          <t>성호전자</t>
-        </is>
-      </c>
-      <c r="D31" s="20" t="n">
-        <v>6</v>
-      </c>
-      <c r="E31" s="20" t="n">
-        <v>6</v>
-      </c>
-      <c r="F31" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G31" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H31" s="22" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="I31" s="24" t="n">
-        <v>-4.41</v>
-      </c>
-      <c r="J31" s="23" t="inlineStr">
-        <is>
-          <t>중요공시 3건 / 한국경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K31" s="23" t="inlineStr">
-        <is>
-          <t>공시</t>
+      <c r="J31" s="17" t="inlineStr">
+        <is>
+          <t>네이버 검색 당일 +137% / 중요공시 2건 / 중요공시 7일 +100%</t>
+        </is>
+      </c>
+      <c r="K31" s="17" t="inlineStr">
+        <is>
+          <t>공시, 네이버</t>
         </is>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
       <c r="A32" s="20" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="B32" s="20" t="n">
@@ -1686,7 +1688,7 @@
       </c>
       <c r="C32" s="21" t="inlineStr">
         <is>
-          <t>엑시온그룹</t>
+          <t>후성</t>
         </is>
       </c>
       <c r="D32" s="20" t="n">
@@ -1702,26 +1704,26 @@
         <v>0</v>
       </c>
       <c r="H32" s="22" t="n">
-        <v>5.63</v>
+        <v>20.55</v>
       </c>
       <c r="I32" s="22" t="n">
-        <v>4.85</v>
+        <v>63.46</v>
       </c>
       <c r="J32" s="23" t="inlineStr">
         <is>
-          <t>중요공시 3건 / 매일경제 헤드라인 언급</t>
+          <t>네이버 검색 당일 +322% / 매일경제 헤드라인 언급</t>
         </is>
       </c>
       <c r="K32" s="23" t="inlineStr">
         <is>
-          <t>공시</t>
+          <t>네이버</t>
         </is>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
       <c r="A33" s="20" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="B33" s="20" t="n">
@@ -1729,30 +1731,30 @@
       </c>
       <c r="C33" s="21" t="inlineStr">
         <is>
-          <t>모바일어플라이언스</t>
+          <t>스피어</t>
         </is>
       </c>
       <c r="D33" s="20" t="n">
         <v>6</v>
       </c>
       <c r="E33" s="20" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F33" s="20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G33" s="20" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H33" s="24" t="n">
-        <v>-2.09</v>
-      </c>
-      <c r="I33" s="24" t="n">
-        <v>-27.06</v>
+        <v>-4.68</v>
+      </c>
+      <c r="I33" s="22" t="n">
+        <v>19.54</v>
       </c>
       <c r="J33" s="23" t="inlineStr">
         <is>
-          <t>중요공시 3건 / 중요공시 7일 +50%</t>
+          <t>중요공시 4건 / 중요공시 3일 +100%</t>
         </is>
       </c>
       <c r="K33" s="23" t="inlineStr">
@@ -1764,7 +1766,7 @@
     <row r="34" ht="18" customHeight="1">
       <c r="A34" s="20" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="B34" s="20" t="n">
@@ -1772,7 +1774,7 @@
       </c>
       <c r="C34" s="21" t="inlineStr">
         <is>
-          <t>대양금속</t>
+          <t>미래에셋증권</t>
         </is>
       </c>
       <c r="D34" s="20" t="n">
@@ -1788,26 +1790,24 @@
         <v>0</v>
       </c>
       <c r="H34" s="22" t="n">
-        <v>1.55</v>
+        <v>2.35</v>
       </c>
       <c r="I34" s="24" t="n">
-        <v>-13.65</v>
+        <v>-7.27</v>
       </c>
       <c r="J34" s="23" t="inlineStr">
         <is>
-          <t>중요공시 1건 / Google 급상승 검색어 등장 (KR)</t>
-        </is>
-      </c>
-      <c r="K34" s="23" t="inlineStr">
-        <is>
-          <t>공시, Google</t>
-        </is>
+          <t>매일경제 헤드라인 언급 / 매일경제 기사 언급 / 한국경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K34" s="23" t="n">
+        <v/>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
       <c r="A35" s="20" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="B35" s="20" t="n">
@@ -1815,40 +1815,42 @@
       </c>
       <c r="C35" s="21" t="inlineStr">
         <is>
-          <t>삼성전기</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="D35" s="20" t="n">
         <v>6</v>
       </c>
       <c r="E35" s="20" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F35" s="20" t="n">
         <v>0</v>
       </c>
       <c r="G35" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H35" s="24" t="n">
-        <v>-5.04</v>
+        <v>3</v>
+      </c>
+      <c r="H35" s="22" t="n">
+        <v>6.32</v>
       </c>
       <c r="I35" s="24" t="n">
-        <v>-2.45</v>
+        <v>-3.06</v>
       </c>
       <c r="J35" s="23" t="inlineStr">
         <is>
-          <t>한국경제 헤드라인 언급 / 매일경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K35" s="23" t="n">
-        <v/>
+          <t>중요공시 3건 / 중요공시 7일 +200%</t>
+        </is>
+      </c>
+      <c r="K35" s="23" t="inlineStr">
+        <is>
+          <t>공시</t>
+        </is>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
       <c r="A36" s="20" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="B36" s="20" t="n">
@@ -1856,42 +1858,42 @@
       </c>
       <c r="C36" s="21" t="inlineStr">
         <is>
-          <t>네이버</t>
+          <t>에스아이리소스</t>
         </is>
       </c>
       <c r="D36" s="20" t="n">
         <v>6</v>
       </c>
       <c r="E36" s="20" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F36" s="20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G36" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H36" s="20" t="n">
-        <v/>
-      </c>
-      <c r="I36" s="20" t="n">
-        <v/>
+        <v>3</v>
+      </c>
+      <c r="H36" s="24" t="n">
+        <v>-6.32</v>
+      </c>
+      <c r="I36" s="24" t="n">
+        <v>-9.18</v>
       </c>
       <c r="J36" s="23" t="inlineStr">
         <is>
-          <t>네이버뉴스 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 기사 언급</t>
+          <t>중요공시 2건 / 중요공시 3일 +100% / 중요공시 7일 +100%</t>
         </is>
       </c>
       <c r="K36" s="23" t="inlineStr">
         <is>
-          <t>네이버</t>
+          <t>공시</t>
         </is>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
       <c r="A37" s="20" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="B37" s="20" t="n">
@@ -1899,7 +1901,7 @@
       </c>
       <c r="C37" s="21" t="inlineStr">
         <is>
-          <t>수소</t>
+          <t>엑시온그룹</t>
         </is>
       </c>
       <c r="D37" s="20" t="n">
@@ -1914,25 +1916,27 @@
       <c r="G37" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H37" s="20" t="n">
-        <v/>
-      </c>
-      <c r="I37" s="20" t="n">
-        <v/>
+      <c r="H37" s="22" t="n">
+        <v>5.63</v>
+      </c>
+      <c r="I37" s="22" t="n">
+        <v>4.85</v>
       </c>
       <c r="J37" s="23" t="inlineStr">
         <is>
-          <t>한국경제 헤드라인 언급 / 매일경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K37" s="23" t="n">
-        <v/>
+          <t>중요공시 3건 / 매일경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K37" s="23" t="inlineStr">
+        <is>
+          <t>공시</t>
+        </is>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
       <c r="A38" s="20" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="B38" s="20" t="n">
@@ -1973,7 +1977,7 @@
     <row r="39" ht="18" customHeight="1">
       <c r="A39" s="20" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="B39" s="20" t="n">
@@ -1981,7 +1985,7 @@
       </c>
       <c r="C39" s="21" t="inlineStr">
         <is>
-          <t>태양금속</t>
+          <t>한화오션</t>
         </is>
       </c>
       <c r="D39" s="20" t="n">
@@ -1997,26 +2001,26 @@
         <v>0</v>
       </c>
       <c r="H39" s="22" t="n">
-        <v>3.3</v>
+        <v>7.85</v>
       </c>
       <c r="I39" s="22" t="n">
-        <v>29.88</v>
+        <v>0.45</v>
       </c>
       <c r="J39" s="23" t="inlineStr">
         <is>
-          <t>Google 급상승 검색어 등장 (KR)</t>
+          <t>중요공시 1건 / 한국경제 헤드라인 언급</t>
         </is>
       </c>
       <c r="K39" s="23" t="inlineStr">
         <is>
-          <t>Google</t>
+          <t>공시</t>
         </is>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
       <c r="A40" s="20" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="B40" s="20" t="n">
@@ -2024,42 +2028,42 @@
       </c>
       <c r="C40" s="21" t="inlineStr">
         <is>
-          <t>BNK금융지주</t>
+          <t>알엔티엑스</t>
         </is>
       </c>
       <c r="D40" s="20" t="n">
         <v>5</v>
       </c>
       <c r="E40" s="20" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F40" s="20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G40" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H40" s="22" t="n">
-        <v>5.05</v>
-      </c>
-      <c r="I40" s="22" t="n">
-        <v>2.49</v>
+      <c r="H40" s="24" t="n">
+        <v>-0.44</v>
+      </c>
+      <c r="I40" s="24" t="n">
+        <v>-17.65</v>
       </c>
       <c r="J40" s="23" t="inlineStr">
         <is>
-          <t>Google 급상승 검색어 등장 (KR)</t>
+          <t>중요공시 5건 / 중요공시 3일 +150%</t>
         </is>
       </c>
       <c r="K40" s="23" t="inlineStr">
         <is>
-          <t>Google</t>
+          <t>공시</t>
         </is>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
       <c r="A41" s="20" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="B41" s="20" t="n">
@@ -2067,14 +2071,14 @@
       </c>
       <c r="C41" s="21" t="inlineStr">
         <is>
-          <t>하나금융지주</t>
+          <t>라이콤</t>
         </is>
       </c>
       <c r="D41" s="20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E41" s="20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F41" s="20" t="n">
         <v>0</v>
@@ -2082,27 +2086,27 @@
       <c r="G41" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H41" s="22" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="I41" s="24" t="n">
-        <v>-2.1</v>
+      <c r="H41" s="24" t="n">
+        <v>-12.4</v>
+      </c>
+      <c r="I41" s="22" t="n">
+        <v>30.29</v>
       </c>
       <c r="J41" s="23" t="inlineStr">
         <is>
-          <t>Google 급상승 검색어 등장 (KR)</t>
+          <t>네이버 검색 당일 +214% / 중요공시 1건</t>
         </is>
       </c>
       <c r="K41" s="23" t="inlineStr">
         <is>
-          <t>Google</t>
+          <t>공시, 네이버</t>
         </is>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
       <c r="A42" s="20" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="B42" s="20" t="n">
@@ -2110,14 +2114,14 @@
       </c>
       <c r="C42" s="21" t="inlineStr">
         <is>
-          <t>JB금융지주</t>
+          <t>원익IPS</t>
         </is>
       </c>
       <c r="D42" s="20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E42" s="20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F42" s="20" t="n">
         <v>0</v>
@@ -2126,26 +2130,26 @@
         <v>0</v>
       </c>
       <c r="H42" s="22" t="n">
-        <v>2.69</v>
+        <v>30</v>
       </c>
       <c r="I42" s="22" t="n">
-        <v>3.69</v>
+        <v>38.13</v>
       </c>
       <c r="J42" s="23" t="inlineStr">
         <is>
-          <t>Google 급상승 검색어 등장 (KR)</t>
+          <t>네이버뉴스 헤드라인 언급</t>
         </is>
       </c>
       <c r="K42" s="23" t="inlineStr">
         <is>
-          <t>Google</t>
+          <t>네이버</t>
         </is>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1">
       <c r="A43" s="20" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="B43" s="20" t="n">
@@ -2153,14 +2157,14 @@
       </c>
       <c r="C43" s="21" t="inlineStr">
         <is>
-          <t>iM금융지주</t>
+          <t>하림</t>
         </is>
       </c>
       <c r="D43" s="20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E43" s="20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F43" s="20" t="n">
         <v>0</v>
@@ -2169,26 +2173,24 @@
         <v>0</v>
       </c>
       <c r="H43" s="24" t="n">
-        <v>-3.38</v>
-      </c>
-      <c r="I43" s="20" t="n">
-        <v>0</v>
+        <v>-0.87</v>
+      </c>
+      <c r="I43" s="22" t="n">
+        <v>0.71</v>
       </c>
       <c r="J43" s="23" t="inlineStr">
         <is>
-          <t>Google 급상승 검색어 등장 (KR)</t>
-        </is>
-      </c>
-      <c r="K43" s="23" t="inlineStr">
-        <is>
-          <t>Google</t>
-        </is>
+          <t>한국경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K43" s="23" t="n">
+        <v/>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
       <c r="A44" s="20" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="B44" s="20" t="n">
@@ -2196,14 +2198,14 @@
       </c>
       <c r="C44" s="21" t="inlineStr">
         <is>
-          <t>금호타이어</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="D44" s="20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E44" s="20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F44" s="20" t="n">
         <v>0</v>
@@ -2212,26 +2214,26 @@
         <v>0</v>
       </c>
       <c r="H44" s="22" t="n">
-        <v>5.97</v>
+        <v>11.54</v>
       </c>
       <c r="I44" s="22" t="n">
-        <v>3.01</v>
+        <v>5.31</v>
       </c>
       <c r="J44" s="23" t="inlineStr">
         <is>
-          <t>Google 급상승 검색어 등장 (KR)</t>
+          <t>중요공시 1건 / 네이버뉴스 헤드라인 언급</t>
         </is>
       </c>
       <c r="K44" s="23" t="inlineStr">
         <is>
-          <t>Google</t>
+          <t>공시, 네이버</t>
         </is>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
       <c r="A45" s="20" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="B45" s="20" t="n">
@@ -2239,42 +2241,42 @@
       </c>
       <c r="C45" s="21" t="inlineStr">
         <is>
-          <t>금호전기</t>
+          <t>현대건설</t>
         </is>
       </c>
       <c r="D45" s="20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E45" s="20" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F45" s="20" t="n">
         <v>0</v>
       </c>
       <c r="G45" s="20" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H45" s="22" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="I45" s="24" t="n">
-        <v>-6.17</v>
+        <v>28.36</v>
+      </c>
+      <c r="I45" s="22" t="n">
+        <v>19.41</v>
       </c>
       <c r="J45" s="23" t="inlineStr">
         <is>
-          <t>Google 급상승 검색어 등장 (KR)</t>
+          <t>중요공시 2건 / 중요공시 7일 +100%</t>
         </is>
       </c>
       <c r="K45" s="23" t="inlineStr">
         <is>
-          <t>Google</t>
+          <t>공시</t>
         </is>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
       <c r="A46" s="20" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="B46" s="20" t="n">
@@ -2282,14 +2284,14 @@
       </c>
       <c r="C46" s="21" t="inlineStr">
         <is>
-          <t>한국금융지주</t>
+          <t>삼성바이오로직스</t>
         </is>
       </c>
       <c r="D46" s="20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E46" s="20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F46" s="20" t="n">
         <v>0</v>
@@ -2298,26 +2300,26 @@
         <v>0</v>
       </c>
       <c r="H46" s="22" t="n">
-        <v>4.57</v>
+        <v>0.7</v>
       </c>
       <c r="I46" s="24" t="n">
-        <v>-2.43</v>
+        <v>-3.36</v>
       </c>
       <c r="J46" s="23" t="inlineStr">
         <is>
-          <t>Google 급상승 검색어 등장 (KR)</t>
+          <t>중요공시 1건 / 네이버뉴스 헤드라인 언급</t>
         </is>
       </c>
       <c r="K46" s="23" t="inlineStr">
         <is>
-          <t>Google</t>
+          <t>공시, 네이버</t>
         </is>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
       <c r="A47" s="20" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="B47" s="20" t="n">
@@ -2325,14 +2327,14 @@
       </c>
       <c r="C47" s="21" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>전기차</t>
         </is>
       </c>
       <c r="D47" s="20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E47" s="20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F47" s="20" t="n">
         <v>0</v>
@@ -2348,19 +2350,17 @@
       </c>
       <c r="J47" s="23" t="inlineStr">
         <is>
-          <t>네이버뉴스 기사 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K47" s="23" t="inlineStr">
-        <is>
-          <t>네이버</t>
-        </is>
+          <t>매일경제 기사 언급 / 매일경제 기사 언급 / 매일경제 기사 언급 / 매일경제 기사 언급</t>
+        </is>
+      </c>
+      <c r="K47" s="23" t="n">
+        <v/>
       </c>
     </row>
     <row r="48" ht="18" customHeight="1">
       <c r="A48" s="20" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="B48" s="20" t="n">
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C48" s="21" t="inlineStr">
         <is>
-          <t>라이콤</t>
+          <t>KB금융</t>
         </is>
       </c>
       <c r="D48" s="20" t="n">
@@ -2383,27 +2383,25 @@
       <c r="G48" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H48" s="24" t="n">
-        <v>-12.4</v>
-      </c>
-      <c r="I48" s="22" t="n">
-        <v>30.29</v>
+      <c r="H48" s="22" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="I48" s="24" t="n">
+        <v>-6.06</v>
       </c>
       <c r="J48" s="23" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +160% / 중요공시 1건</t>
-        </is>
-      </c>
-      <c r="K48" s="23" t="inlineStr">
-        <is>
-          <t>네이버, 공시</t>
-        </is>
+          <t>매일경제 헤드라인 언급 / 매일경제 기사 언급</t>
+        </is>
+      </c>
+      <c r="K48" s="23" t="n">
+        <v/>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1">
       <c r="A49" s="20" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="B49" s="20" t="n">
@@ -2411,7 +2409,7 @@
       </c>
       <c r="C49" s="21" t="inlineStr">
         <is>
-          <t>한화오션</t>
+          <t>철강</t>
         </is>
       </c>
       <c r="D49" s="20" t="n">
@@ -2426,197 +2424,199 @@
       <c r="G49" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H49" s="22" t="n">
-        <v>7.85</v>
-      </c>
-      <c r="I49" s="22" t="n">
-        <v>0.45</v>
+      <c r="H49" s="20" t="n">
+        <v/>
+      </c>
+      <c r="I49" s="20" t="n">
+        <v/>
       </c>
       <c r="J49" s="23" t="inlineStr">
         <is>
-          <t>중요공시 1건 / 한국경제 헤드라인 언급</t>
+          <t>네이버뉴스 헤드라인 언급 / 매일경제 기사 언급</t>
         </is>
       </c>
       <c r="K49" s="23" t="inlineStr">
         <is>
-          <t>공시</t>
+          <t>네이버</t>
         </is>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
-      <c r="A50" s="20" t="inlineStr">
-        <is>
-          <t>2026-06-13</t>
-        </is>
-      </c>
-      <c r="B50" s="20" t="n">
+      <c r="A50" s="25" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B50" s="25" t="n">
         <v>37</v>
       </c>
-      <c r="C50" s="21" t="inlineStr">
-        <is>
-          <t>대한광통신</t>
-        </is>
-      </c>
-      <c r="D50" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="E50" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="F50" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G50" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H50" s="22" t="n">
-        <v>11.54</v>
-      </c>
-      <c r="I50" s="22" t="n">
-        <v>5.31</v>
-      </c>
-      <c r="J50" s="23" t="inlineStr">
-        <is>
-          <t>중요공시 1건 / 네이버뉴스 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K50" s="23" t="inlineStr">
-        <is>
-          <t>네이버, 공시</t>
+      <c r="C50" s="26" t="inlineStr">
+        <is>
+          <t>세미티에스</t>
+        </is>
+      </c>
+      <c r="D50" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="E50" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="F50" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G50" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H50" s="27" t="n">
+        <v>29.97</v>
+      </c>
+      <c r="I50" s="28" t="n">
+        <v>-7.54</v>
+      </c>
+      <c r="J50" s="29" t="inlineStr">
+        <is>
+          <t>네이버 검색 당일 +4221%</t>
+        </is>
+      </c>
+      <c r="K50" s="29" t="inlineStr">
+        <is>
+          <t>네이버</t>
         </is>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
-      <c r="A51" s="20" t="inlineStr">
-        <is>
-          <t>2026-06-13</t>
-        </is>
-      </c>
-      <c r="B51" s="20" t="n">
+      <c r="A51" s="25" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B51" s="25" t="n">
         <v>38</v>
       </c>
-      <c r="C51" s="21" t="inlineStr">
-        <is>
-          <t>에스아이리소스</t>
-        </is>
-      </c>
-      <c r="D51" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="E51" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="F51" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G51" s="20" t="n">
-        <v>3</v>
-      </c>
-      <c r="H51" s="24" t="n">
-        <v>-6.32</v>
-      </c>
-      <c r="I51" s="24" t="n">
-        <v>-9.18</v>
-      </c>
-      <c r="J51" s="23" t="inlineStr">
-        <is>
-          <t>중요공시 2건 / 중요공시 7일 +100%</t>
-        </is>
-      </c>
-      <c r="K51" s="23" t="inlineStr">
-        <is>
-          <t>공시</t>
+      <c r="C51" s="26" t="inlineStr">
+        <is>
+          <t>화신정공</t>
+        </is>
+      </c>
+      <c r="D51" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="E51" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="F51" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G51" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H51" s="27" t="n">
+        <v>6.18</v>
+      </c>
+      <c r="I51" s="27" t="n">
+        <v>142.33</v>
+      </c>
+      <c r="J51" s="29" t="inlineStr">
+        <is>
+          <t>네이버 검색 당일 +2072%</t>
+        </is>
+      </c>
+      <c r="K51" s="29" t="inlineStr">
+        <is>
+          <t>네이버</t>
         </is>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1">
-      <c r="A52" s="20" t="inlineStr">
-        <is>
-          <t>2026-06-13</t>
-        </is>
-      </c>
-      <c r="B52" s="20" t="n">
+      <c r="A52" s="25" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B52" s="25" t="n">
         <v>39</v>
       </c>
-      <c r="C52" s="21" t="inlineStr">
-        <is>
-          <t>현대건설</t>
-        </is>
-      </c>
-      <c r="D52" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="E52" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="F52" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G52" s="20" t="n">
-        <v>3</v>
-      </c>
-      <c r="H52" s="22" t="n">
-        <v>28.36</v>
-      </c>
-      <c r="I52" s="22" t="n">
-        <v>19.41</v>
-      </c>
-      <c r="J52" s="23" t="inlineStr">
-        <is>
-          <t>중요공시 2건 / 중요공시 7일 +100%</t>
-        </is>
-      </c>
-      <c r="K52" s="23" t="inlineStr">
-        <is>
-          <t>공시</t>
+      <c r="C52" s="26" t="inlineStr">
+        <is>
+          <t>마니커</t>
+        </is>
+      </c>
+      <c r="D52" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="E52" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="F52" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G52" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H52" s="28" t="n">
+        <v>-5.97</v>
+      </c>
+      <c r="I52" s="27" t="n">
+        <v>24.75</v>
+      </c>
+      <c r="J52" s="29" t="inlineStr">
+        <is>
+          <t>네이버 검색 당일 +495%</t>
+        </is>
+      </c>
+      <c r="K52" s="29" t="inlineStr">
+        <is>
+          <t>네이버</t>
         </is>
       </c>
     </row>
     <row r="53" ht="18" customHeight="1">
-      <c r="A53" s="20" t="inlineStr">
-        <is>
-          <t>2026-06-13</t>
-        </is>
-      </c>
-      <c r="B53" s="20" t="n">
+      <c r="A53" s="25" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B53" s="25" t="n">
         <v>40</v>
       </c>
-      <c r="C53" s="21" t="inlineStr">
-        <is>
-          <t>DB</t>
-        </is>
-      </c>
-      <c r="D53" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="E53" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="F53" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G53" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H53" s="22" t="n">
-        <v>3.09</v>
-      </c>
-      <c r="I53" s="22" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="J53" s="23" t="inlineStr">
-        <is>
-          <t>매일경제 헤드라인 언급 / 매일경제 기사 언급</t>
-        </is>
-      </c>
-      <c r="K53" s="23" t="n">
-        <v/>
+      <c r="C53" s="26" t="inlineStr">
+        <is>
+          <t>SK이터닉스</t>
+        </is>
+      </c>
+      <c r="D53" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="E53" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="F53" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G53" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H53" s="27" t="n">
+        <v>6.04</v>
+      </c>
+      <c r="I53" s="27" t="n">
+        <v>21.64</v>
+      </c>
+      <c r="J53" s="29" t="inlineStr">
+        <is>
+          <t>네이버 검색 당일 +264%</t>
+        </is>
+      </c>
+      <c r="K53" s="29" t="inlineStr">
+        <is>
+          <t>네이버</t>
+        </is>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
       <c r="A54" s="25" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="B54" s="25" t="n">
@@ -2624,7 +2624,7 @@
       </c>
       <c r="C54" s="26" t="inlineStr">
         <is>
-          <t>세미티에스</t>
+          <t>마니커에프앤지</t>
         </is>
       </c>
       <c r="D54" s="25" t="n">
@@ -2639,15 +2639,15 @@
       <c r="G54" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H54" s="27" t="n">
-        <v>29.97</v>
-      </c>
-      <c r="I54" s="28" t="n">
-        <v>-7.54</v>
+      <c r="H54" s="28" t="n">
+        <v>-15.17</v>
+      </c>
+      <c r="I54" s="27" t="n">
+        <v>3.85</v>
       </c>
       <c r="J54" s="29" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +3403%</t>
+          <t>네이버 검색 당일 +190%</t>
         </is>
       </c>
       <c r="K54" s="29" t="inlineStr">
@@ -2659,7 +2659,7 @@
     <row r="55" ht="18" customHeight="1">
       <c r="A55" s="25" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="B55" s="25" t="n">
@@ -2667,7 +2667,7 @@
       </c>
       <c r="C55" s="26" t="inlineStr">
         <is>
-          <t>화신정공</t>
+          <t>랩지노믹스</t>
         </is>
       </c>
       <c r="D55" s="25" t="n">
@@ -2682,15 +2682,15 @@
       <c r="G55" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H55" s="27" t="n">
-        <v>6.18</v>
+      <c r="H55" s="28" t="n">
+        <v>-3.41</v>
       </c>
       <c r="I55" s="27" t="n">
-        <v>142.33</v>
+        <v>24.65</v>
       </c>
       <c r="J55" s="29" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +1692%</t>
+          <t>네이버 검색 당일 +138%</t>
         </is>
       </c>
       <c r="K55" s="29" t="inlineStr">
@@ -2702,7 +2702,7 @@
     <row r="56" ht="18" customHeight="1">
       <c r="A56" s="25" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="B56" s="25" t="n">
@@ -2710,7 +2710,7 @@
       </c>
       <c r="C56" s="26" t="inlineStr">
         <is>
-          <t>마니커</t>
+          <t>아이로보틱스</t>
         </is>
       </c>
       <c r="D56" s="25" t="n">
@@ -2725,15 +2725,15 @@
       <c r="G56" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H56" s="28" t="n">
-        <v>-5.97</v>
+      <c r="H56" s="27" t="n">
+        <v>22.3</v>
       </c>
       <c r="I56" s="27" t="n">
-        <v>24.75</v>
+        <v>27.7</v>
       </c>
       <c r="J56" s="29" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +267%</t>
+          <t>네이버 검색 당일 +137%</t>
         </is>
       </c>
       <c r="K56" s="29" t="inlineStr">
@@ -2745,7 +2745,7 @@
     <row r="57" ht="18" customHeight="1">
       <c r="A57" s="25" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="B57" s="25" t="n">
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C57" s="26" t="inlineStr">
         <is>
-          <t>후성</t>
+          <t>테크윙</t>
         </is>
       </c>
       <c r="D57" s="25" t="n">
@@ -2769,14 +2769,14 @@
         <v>0</v>
       </c>
       <c r="H57" s="27" t="n">
-        <v>20.55</v>
+        <v>6.87</v>
       </c>
       <c r="I57" s="27" t="n">
-        <v>63.46</v>
+        <v>19.38</v>
       </c>
       <c r="J57" s="29" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +216%</t>
+          <t>네이버 검색 당일 +128%</t>
         </is>
       </c>
       <c r="K57" s="29" t="inlineStr">
@@ -2788,7 +2788,7 @@
     <row r="58" ht="18" customHeight="1">
       <c r="A58" s="25" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="B58" s="25" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="C58" s="26" t="inlineStr">
         <is>
-          <t>SK이터닉스</t>
+          <t>제주은행</t>
         </is>
       </c>
       <c r="D58" s="25" t="n">
@@ -2812,14 +2812,14 @@
         <v>0</v>
       </c>
       <c r="H58" s="27" t="n">
-        <v>6.04</v>
+        <v>0.16</v>
       </c>
       <c r="I58" s="27" t="n">
-        <v>21.64</v>
+        <v>15.07</v>
       </c>
       <c r="J58" s="29" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +211%</t>
+          <t>네이버 검색 당일 +100%</t>
         </is>
       </c>
       <c r="K58" s="29" t="inlineStr">
@@ -2831,7 +2831,7 @@
     <row r="59" ht="18" customHeight="1">
       <c r="A59" s="25" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="B59" s="25" t="n">
@@ -2839,7 +2839,7 @@
       </c>
       <c r="C59" s="26" t="inlineStr">
         <is>
-          <t>랩지노믹스</t>
+          <t>SK네트웍스</t>
         </is>
       </c>
       <c r="D59" s="25" t="n">
@@ -2854,15 +2854,15 @@
       <c r="G59" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H59" s="28" t="n">
-        <v>-3.41</v>
+      <c r="H59" s="27" t="n">
+        <v>11.4</v>
       </c>
       <c r="I59" s="27" t="n">
-        <v>24.65</v>
+        <v>19.27</v>
       </c>
       <c r="J59" s="29" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +115%</t>
+          <t>네이버 검색 당일 +73% / 매일경제 기사 언급</t>
         </is>
       </c>
       <c r="K59" s="29" t="inlineStr">
@@ -2874,7 +2874,7 @@
     <row r="60" ht="18" customHeight="1">
       <c r="A60" s="25" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="B60" s="25" t="n">
@@ -2882,7 +2882,7 @@
       </c>
       <c r="C60" s="26" t="inlineStr">
         <is>
-          <t>스피어</t>
+          <t>하나마이크론</t>
         </is>
       </c>
       <c r="D60" s="25" t="n">
@@ -2897,27 +2897,27 @@
       <c r="G60" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H60" s="28" t="n">
-        <v>-4.68</v>
+      <c r="H60" s="27" t="n">
+        <v>2.09</v>
       </c>
       <c r="I60" s="27" t="n">
-        <v>19.54</v>
+        <v>16.97</v>
       </c>
       <c r="J60" s="29" t="inlineStr">
         <is>
-          <t>중요공시 4건</t>
+          <t>네이버뉴스 헤드라인 언급</t>
         </is>
       </c>
       <c r="K60" s="29" t="inlineStr">
         <is>
-          <t>공시</t>
+          <t>네이버</t>
         </is>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
       <c r="A61" s="25" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="B61" s="25" t="n">
@@ -2925,7 +2925,7 @@
       </c>
       <c r="C61" s="26" t="inlineStr">
         <is>
-          <t>하림</t>
+          <t>저스템</t>
         </is>
       </c>
       <c r="D61" s="25" t="n">
@@ -2940,15 +2940,15 @@
       <c r="G61" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H61" s="28" t="n">
-        <v>-0.87</v>
+      <c r="H61" s="27" t="n">
+        <v>15.21</v>
       </c>
       <c r="I61" s="27" t="n">
-        <v>0.71</v>
+        <v>19.29</v>
       </c>
       <c r="J61" s="29" t="inlineStr">
         <is>
-          <t>한국경제 헤드라인 언급</t>
+          <t>매일경제 헤드라인 언급</t>
         </is>
       </c>
       <c r="K61" s="29" t="n">
@@ -2958,7 +2958,7 @@
     <row r="62" ht="18" customHeight="1">
       <c r="A62" s="25" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="B62" s="25" t="n">
@@ -2966,7 +2966,7 @@
       </c>
       <c r="C62" s="26" t="inlineStr">
         <is>
-          <t>NAVER</t>
+          <t>리노공업</t>
         </is>
       </c>
       <c r="D62" s="25" t="n">
@@ -2982,26 +2982,24 @@
         <v>0</v>
       </c>
       <c r="H62" s="27" t="n">
-        <v>10.27</v>
-      </c>
-      <c r="I62" s="28" t="n">
-        <v>-3.33</v>
+        <v>4.71</v>
+      </c>
+      <c r="I62" s="27" t="n">
+        <v>11.05</v>
       </c>
       <c r="J62" s="29" t="inlineStr">
         <is>
-          <t>네이버뉴스 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K62" s="29" t="inlineStr">
-        <is>
-          <t>네이버</t>
-        </is>
+          <t>매일경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K62" s="29" t="n">
+        <v/>
       </c>
     </row>
     <row r="63" ht="18" customHeight="1">
       <c r="A63" s="25" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="B63" s="25" t="n">
@@ -3009,7 +3007,7 @@
       </c>
       <c r="C63" s="26" t="inlineStr">
         <is>
-          <t>저스템</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="D63" s="25" t="n">
@@ -3025,14 +3023,14 @@
         <v>0</v>
       </c>
       <c r="H63" s="27" t="n">
-        <v>15.21</v>
-      </c>
-      <c r="I63" s="27" t="n">
-        <v>19.29</v>
+        <v>5.08</v>
+      </c>
+      <c r="I63" s="28" t="n">
+        <v>-2.62</v>
       </c>
       <c r="J63" s="29" t="inlineStr">
         <is>
-          <t>매일경제 헤드라인 언급</t>
+          <t>한국경제 헤드라인 언급</t>
         </is>
       </c>
       <c r="K63" s="29" t="n">
@@ -3132,22 +3130,22 @@
         <v>1</v>
       </c>
       <c r="C3" s="25" t="n">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="D3" s="25" t="n">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="E3" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F3" s="25" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="G3" s="25" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="H3" s="25" t="n"/>
@@ -3156,29 +3154,29 @@
     <row r="4" ht="18" customHeight="1">
       <c r="A4" s="26" t="inlineStr">
         <is>
-          <t>로봇</t>
+          <t>바이오</t>
         </is>
       </c>
       <c r="B4" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C4" s="25" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="D4" s="25" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="E4" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F4" s="25" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="G4" s="25" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="H4" s="25" t="n"/>
@@ -3187,29 +3185,29 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="26" t="inlineStr">
         <is>
-          <t>인공지능</t>
+          <t>로봇</t>
         </is>
       </c>
       <c r="B5" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C5" s="25" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D5" s="25" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E5" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F5" s="25" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="G5" s="25" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="H5" s="25" t="n"/>
@@ -3218,29 +3216,29 @@
     <row r="6" ht="18" customHeight="1">
       <c r="A6" s="26" t="inlineStr">
         <is>
-          <t>바이오</t>
+          <t>인공지능</t>
         </is>
       </c>
       <c r="B6" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C6" s="25" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D6" s="25" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E6" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F6" s="25" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="G6" s="25" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="H6" s="25" t="n"/>
@@ -3249,77 +3247,77 @@
     <row r="7" ht="18" customHeight="1">
       <c r="A7" s="26" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>현대차</t>
         </is>
       </c>
       <c r="B7" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C7" s="25" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D7" s="25" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E7" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F7" s="25" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="G7" s="25" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="H7" s="27" t="n">
-        <v>7.86</v>
+        <v>1.68</v>
       </c>
       <c r="I7" s="28" t="n">
-        <v>-1.98</v>
+        <v>-13.29</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="26" t="inlineStr">
         <is>
-          <t>현대차</t>
+          <t>LG</t>
         </is>
       </c>
       <c r="B8" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C8" s="25" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D8" s="25" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E8" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F8" s="25" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="G8" s="25" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
-        </is>
-      </c>
-      <c r="H8" s="27" t="n">
-        <v>1.68</v>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="H8" s="28" t="n">
+        <v>-0.93</v>
       </c>
       <c r="I8" s="28" t="n">
-        <v>-13.29</v>
+        <v>-13.34</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
       <c r="A9" s="26" t="inlineStr">
         <is>
-          <t>제약</t>
+          <t>삼성전기</t>
         </is>
       </c>
       <c r="B9" s="25" t="n">
@@ -3336,190 +3334,190 @@
       </c>
       <c r="F9" s="25" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="G9" s="25" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
-        </is>
-      </c>
-      <c r="H9" s="25" t="n"/>
-      <c r="I9" s="25" t="n"/>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="H9" s="28" t="n">
+        <v>-5.04</v>
+      </c>
+      <c r="I9" s="28" t="n">
+        <v>-2.45</v>
+      </c>
     </row>
     <row r="10" ht="18" customHeight="1">
       <c r="A10" s="26" t="inlineStr">
         <is>
-          <t>KB금융</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B10" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C10" s="25" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D10" s="25" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E10" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F10" s="25" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="G10" s="25" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="H10" s="27" t="n">
-        <v>6.4</v>
+        <v>7.86</v>
       </c>
       <c r="I10" s="28" t="n">
-        <v>-6.06</v>
+        <v>-1.98</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
       <c r="A11" s="26" t="inlineStr">
         <is>
-          <t>LG</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B11" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C11" s="25" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D11" s="25" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E11" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F11" s="25" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="G11" s="25" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
-        </is>
-      </c>
-      <c r="H11" s="28" t="n">
-        <v>-0.93</v>
-      </c>
-      <c r="I11" s="28" t="n">
-        <v>-13.34</v>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="H11" s="27" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="I11" s="27" t="n">
+        <v>3.86</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
       <c r="A12" s="26" t="inlineStr">
         <is>
-          <t>한미반도체</t>
+          <t>제약</t>
         </is>
       </c>
       <c r="B12" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C12" s="25" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D12" s="25" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E12" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F12" s="25" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="G12" s="25" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
-        </is>
-      </c>
-      <c r="H12" s="27" t="n">
-        <v>24.05</v>
-      </c>
-      <c r="I12" s="27" t="n">
-        <v>27.56</v>
-      </c>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="H12" s="25" t="n"/>
+      <c r="I12" s="25" t="n"/>
     </row>
     <row r="13" ht="18" customHeight="1">
       <c r="A13" s="26" t="inlineStr">
         <is>
-          <t>CSA 코스믹</t>
+          <t>한미반도체</t>
         </is>
       </c>
       <c r="B13" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C13" s="25" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D13" s="25" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E13" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F13" s="25" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="G13" s="25" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="H13" s="27" t="n">
-        <v>29.93</v>
+        <v>24.05</v>
       </c>
       <c r="I13" s="27" t="n">
-        <v>69.53</v>
+        <v>27.56</v>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="26" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>CSA 코스믹</t>
         </is>
       </c>
       <c r="B14" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C14" s="25" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D14" s="25" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E14" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F14" s="25" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="G14" s="25" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="H14" s="27" t="n">
-        <v>2.33</v>
+        <v>29.93</v>
       </c>
       <c r="I14" s="27" t="n">
-        <v>3.86</v>
+        <v>69.53</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
@@ -3542,12 +3540,12 @@
       </c>
       <c r="F15" s="25" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="G15" s="25" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="H15" s="25" t="n"/>
@@ -3573,12 +3571,12 @@
       </c>
       <c r="F16" s="25" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="G16" s="25" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="H16" s="27" t="n">
@@ -3608,12 +3606,12 @@
       </c>
       <c r="F17" s="25" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="G17" s="25" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="H17" s="27" t="n">
@@ -3626,108 +3624,112 @@
     <row r="18" ht="18" customHeight="1">
       <c r="A18" s="26" t="inlineStr">
         <is>
-          <t>네이버</t>
+          <t>모바일어플라이언스</t>
         </is>
       </c>
       <c r="B18" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C18" s="25" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D18" s="25" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E18" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F18" s="25" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="G18" s="25" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
-        </is>
-      </c>
-      <c r="H18" s="25" t="n"/>
-      <c r="I18" s="25" t="n"/>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="H18" s="28" t="n">
+        <v>-2.09</v>
+      </c>
+      <c r="I18" s="28" t="n">
+        <v>-27.06</v>
+      </c>
     </row>
     <row r="19" ht="18" customHeight="1">
       <c r="A19" s="26" t="inlineStr">
         <is>
-          <t>대양금속</t>
+          <t>성호전자</t>
         </is>
       </c>
       <c r="B19" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C19" s="25" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D19" s="25" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E19" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F19" s="25" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="G19" s="25" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="H19" s="27" t="n">
-        <v>1.55</v>
+        <v>2.41</v>
       </c>
       <c r="I19" s="28" t="n">
-        <v>-13.65</v>
+        <v>-4.41</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
       <c r="A20" s="26" t="inlineStr">
         <is>
-          <t>모바일어플라이언스</t>
+          <t>에이팩트</t>
         </is>
       </c>
       <c r="B20" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C20" s="25" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D20" s="25" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E20" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F20" s="25" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="G20" s="25" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
-        </is>
-      </c>
-      <c r="H20" s="28" t="n">
-        <v>-2.09</v>
-      </c>
-      <c r="I20" s="28" t="n">
-        <v>-27.06</v>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="H20" s="27" t="n">
+        <v>13.08</v>
+      </c>
+      <c r="I20" s="27" t="n">
+        <v>45.57</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
       <c r="A21" s="26" t="inlineStr">
         <is>
-          <t>삼성전기</t>
+          <t>미래에셋증권</t>
         </is>
       </c>
       <c r="B21" s="25" t="n">
@@ -3744,25 +3746,25 @@
       </c>
       <c r="F21" s="25" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="G21" s="25" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
-        </is>
-      </c>
-      <c r="H21" s="28" t="n">
-        <v>-5.04</v>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="H21" s="27" t="n">
+        <v>2.35</v>
       </c>
       <c r="I21" s="28" t="n">
-        <v>-2.45</v>
+        <v>-7.27</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
       <c r="A22" s="26" t="inlineStr">
         <is>
-          <t>성호전자</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="B22" s="25" t="n">
@@ -3779,25 +3781,25 @@
       </c>
       <c r="F22" s="25" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="G22" s="25" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="H22" s="27" t="n">
-        <v>2.41</v>
+        <v>6.32</v>
       </c>
       <c r="I22" s="28" t="n">
-        <v>-4.41</v>
+        <v>-3.06</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
       <c r="A23" s="26" t="inlineStr">
         <is>
-          <t>수소</t>
+          <t>스피어</t>
         </is>
       </c>
       <c r="B23" s="25" t="n">
@@ -3814,21 +3816,25 @@
       </c>
       <c r="F23" s="25" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="G23" s="25" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
-        </is>
-      </c>
-      <c r="H23" s="25" t="n"/>
-      <c r="I23" s="25" t="n"/>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="H23" s="28" t="n">
+        <v>-4.68</v>
+      </c>
+      <c r="I23" s="27" t="n">
+        <v>19.54</v>
+      </c>
     </row>
     <row r="24" ht="18" customHeight="1">
       <c r="A24" s="26" t="inlineStr">
         <is>
-          <t>에이팩트</t>
+          <t>에스아이리소스</t>
         </is>
       </c>
       <c r="B24" s="25" t="n">
@@ -3845,19 +3851,19 @@
       </c>
       <c r="F24" s="25" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="G24" s="25" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
-        </is>
-      </c>
-      <c r="H24" s="27" t="n">
-        <v>13.08</v>
-      </c>
-      <c r="I24" s="27" t="n">
-        <v>45.57</v>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="H24" s="28" t="n">
+        <v>-6.32</v>
+      </c>
+      <c r="I24" s="28" t="n">
+        <v>-9.18</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
@@ -3880,12 +3886,12 @@
       </c>
       <c r="F25" s="25" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="G25" s="25" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="H25" s="27" t="n">
@@ -3898,7 +3904,7 @@
     <row r="26" ht="18" customHeight="1">
       <c r="A26" s="26" t="inlineStr">
         <is>
-          <t>우리금융지주</t>
+          <t>현대로템</t>
         </is>
       </c>
       <c r="B26" s="25" t="n">
@@ -3915,25 +3921,25 @@
       </c>
       <c r="F26" s="25" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="G26" s="25" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="H26" s="27" t="n">
-        <v>3.32</v>
-      </c>
-      <c r="I26" s="28" t="n">
-        <v>-0.16</v>
+        <v>10.67</v>
+      </c>
+      <c r="I26" s="27" t="n">
+        <v>8.93</v>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
       <c r="A27" s="26" t="inlineStr">
         <is>
-          <t>현대로템</t>
+          <t>후성</t>
         </is>
       </c>
       <c r="B27" s="25" t="n">
@@ -3950,25 +3956,25 @@
       </c>
       <c r="F27" s="25" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="G27" s="25" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="H27" s="27" t="n">
-        <v>10.67</v>
+        <v>20.55</v>
       </c>
       <c r="I27" s="27" t="n">
-        <v>8.93</v>
+        <v>63.46</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
       <c r="A28" s="26" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>알엔티엑스</t>
         </is>
       </c>
       <c r="B28" s="25" t="n">
@@ -3985,21 +3991,25 @@
       </c>
       <c r="F28" s="25" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="G28" s="25" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
-        </is>
-      </c>
-      <c r="H28" s="25" t="n"/>
-      <c r="I28" s="25" t="n"/>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="H28" s="28" t="n">
+        <v>-0.44</v>
+      </c>
+      <c r="I28" s="28" t="n">
+        <v>-17.65</v>
+      </c>
     </row>
     <row r="29" ht="18" customHeight="1">
       <c r="A29" s="26" t="inlineStr">
         <is>
-          <t>BNK금융지주</t>
+          <t>한화오션</t>
         </is>
       </c>
       <c r="B29" s="25" t="n">
@@ -4016,270 +4026,262 @@
       </c>
       <c r="F29" s="25" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="G29" s="25" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="H29" s="27" t="n">
-        <v>5.05</v>
+        <v>7.85</v>
       </c>
       <c r="I29" s="27" t="n">
-        <v>2.49</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
       <c r="A30" s="26" t="inlineStr">
         <is>
-          <t>JB금융지주</t>
+          <t>KB금융</t>
         </is>
       </c>
       <c r="B30" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C30" s="25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D30" s="25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E30" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F30" s="25" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="G30" s="25" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="H30" s="27" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="I30" s="27" t="n">
-        <v>3.69</v>
+        <v>6.4</v>
+      </c>
+      <c r="I30" s="28" t="n">
+        <v>-6.06</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
       <c r="A31" s="26" t="inlineStr">
         <is>
-          <t>iM금융지주</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B31" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C31" s="25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D31" s="25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E31" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F31" s="25" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="G31" s="25" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
-        </is>
-      </c>
-      <c r="H31" s="28" t="n">
-        <v>-3.38</v>
-      </c>
-      <c r="I31" s="25" t="n">
-        <v>0</v>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="H31" s="27" t="n">
+        <v>11.54</v>
+      </c>
+      <c r="I31" s="27" t="n">
+        <v>5.31</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
       <c r="A32" s="26" t="inlineStr">
         <is>
-          <t>금호전기</t>
+          <t>라이콤</t>
         </is>
       </c>
       <c r="B32" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C32" s="25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D32" s="25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E32" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F32" s="25" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="G32" s="25" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
-        </is>
-      </c>
-      <c r="H32" s="27" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="I32" s="28" t="n">
-        <v>-6.17</v>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="H32" s="28" t="n">
+        <v>-12.4</v>
+      </c>
+      <c r="I32" s="27" t="n">
+        <v>30.29</v>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
       <c r="A33" s="26" t="inlineStr">
         <is>
-          <t>금호타이어</t>
+          <t>삼성바이오로직스</t>
         </is>
       </c>
       <c r="B33" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C33" s="25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D33" s="25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E33" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F33" s="25" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="G33" s="25" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="H33" s="27" t="n">
-        <v>5.97</v>
-      </c>
-      <c r="I33" s="27" t="n">
-        <v>3.01</v>
+        <v>0.7</v>
+      </c>
+      <c r="I33" s="28" t="n">
+        <v>-3.36</v>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
       <c r="A34" s="26" t="inlineStr">
         <is>
-          <t>태양금속</t>
+          <t>원익IPS</t>
         </is>
       </c>
       <c r="B34" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C34" s="25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D34" s="25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E34" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F34" s="25" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="G34" s="25" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="H34" s="27" t="n">
-        <v>3.3</v>
+        <v>30</v>
       </c>
       <c r="I34" s="27" t="n">
-        <v>29.88</v>
+        <v>38.13</v>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
       <c r="A35" s="26" t="inlineStr">
         <is>
-          <t>하나금융지주</t>
+          <t>전기차</t>
         </is>
       </c>
       <c r="B35" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C35" s="25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D35" s="25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E35" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F35" s="25" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="G35" s="25" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
-        </is>
-      </c>
-      <c r="H35" s="27" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="I35" s="28" t="n">
-        <v>-2.1</v>
-      </c>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="H35" s="25" t="n"/>
+      <c r="I35" s="25" t="n"/>
     </row>
     <row r="36" ht="18" customHeight="1">
       <c r="A36" s="26" t="inlineStr">
         <is>
-          <t>한국금융지주</t>
+          <t>철강</t>
         </is>
       </c>
       <c r="B36" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C36" s="25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D36" s="25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E36" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F36" s="25" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="G36" s="25" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
-        </is>
-      </c>
-      <c r="H36" s="27" t="n">
-        <v>4.57</v>
-      </c>
-      <c r="I36" s="28" t="n">
-        <v>-2.43</v>
-      </c>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="H36" s="25" t="n"/>
+      <c r="I36" s="25" t="n"/>
     </row>
     <row r="37" ht="18" customHeight="1">
       <c r="A37" s="26" t="inlineStr">
         <is>
-          <t>DB</t>
+          <t>하림</t>
         </is>
       </c>
       <c r="B37" s="25" t="n">
@@ -4296,25 +4298,25 @@
       </c>
       <c r="F37" s="25" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="G37" s="25" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
-        </is>
-      </c>
-      <c r="H37" s="27" t="n">
-        <v>3.09</v>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="H37" s="28" t="n">
+        <v>-0.87</v>
       </c>
       <c r="I37" s="27" t="n">
-        <v>4.4</v>
+        <v>0.71</v>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
       <c r="A38" s="26" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>현대건설</t>
         </is>
       </c>
       <c r="B38" s="25" t="n">
@@ -4331,165 +4333,165 @@
       </c>
       <c r="F38" s="25" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="G38" s="25" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="H38" s="27" t="n">
-        <v>11.54</v>
+        <v>28.36</v>
       </c>
       <c r="I38" s="27" t="n">
-        <v>5.31</v>
+        <v>19.41</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
       <c r="A39" s="26" t="inlineStr">
         <is>
-          <t>라이콤</t>
+          <t>SK네트웍스</t>
         </is>
       </c>
       <c r="B39" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C39" s="25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D39" s="25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E39" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F39" s="25" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="G39" s="25" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
-        </is>
-      </c>
-      <c r="H39" s="28" t="n">
-        <v>-12.4</v>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="H39" s="27" t="n">
+        <v>11.4</v>
       </c>
       <c r="I39" s="27" t="n">
-        <v>30.29</v>
+        <v>19.27</v>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
       <c r="A40" s="26" t="inlineStr">
         <is>
-          <t>에스아이리소스</t>
+          <t>SK이터닉스</t>
         </is>
       </c>
       <c r="B40" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C40" s="25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D40" s="25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E40" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F40" s="25" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="G40" s="25" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
-        </is>
-      </c>
-      <c r="H40" s="28" t="n">
-        <v>-6.32</v>
-      </c>
-      <c r="I40" s="28" t="n">
-        <v>-9.18</v>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="H40" s="27" t="n">
+        <v>6.04</v>
+      </c>
+      <c r="I40" s="27" t="n">
+        <v>21.64</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
       <c r="A41" s="26" t="inlineStr">
         <is>
-          <t>한화오션</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B41" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C41" s="25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D41" s="25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E41" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F41" s="25" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="G41" s="25" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="H41" s="27" t="n">
-        <v>7.85</v>
-      </c>
-      <c r="I41" s="27" t="n">
-        <v>0.45</v>
+        <v>5.08</v>
+      </c>
+      <c r="I41" s="28" t="n">
+        <v>-2.62</v>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
       <c r="A42" s="26" t="inlineStr">
         <is>
-          <t>현대건설</t>
+          <t>랩지노믹스</t>
         </is>
       </c>
       <c r="B42" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C42" s="25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D42" s="25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E42" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F42" s="25" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="G42" s="25" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
-        </is>
-      </c>
-      <c r="H42" s="27" t="n">
-        <v>28.36</v>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="H42" s="28" t="n">
+        <v>-3.41</v>
       </c>
       <c r="I42" s="27" t="n">
-        <v>19.41</v>
+        <v>24.65</v>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1">
       <c r="A43" s="26" t="inlineStr">
         <is>
-          <t>NAVER</t>
+          <t>리노공업</t>
         </is>
       </c>
       <c r="B43" s="25" t="n">
@@ -4506,25 +4508,25 @@
       </c>
       <c r="F43" s="25" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="G43" s="25" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="H43" s="27" t="n">
-        <v>10.27</v>
-      </c>
-      <c r="I43" s="28" t="n">
-        <v>-3.33</v>
+        <v>4.71</v>
+      </c>
+      <c r="I43" s="27" t="n">
+        <v>11.05</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
       <c r="A44" s="26" t="inlineStr">
         <is>
-          <t>SK이터닉스</t>
+          <t>마니커</t>
         </is>
       </c>
       <c r="B44" s="25" t="n">
@@ -4541,25 +4543,25 @@
       </c>
       <c r="F44" s="25" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="G44" s="25" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
-        </is>
-      </c>
-      <c r="H44" s="27" t="n">
-        <v>6.04</v>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="H44" s="28" t="n">
+        <v>-5.97</v>
       </c>
       <c r="I44" s="27" t="n">
-        <v>21.64</v>
+        <v>24.75</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
       <c r="A45" s="26" t="inlineStr">
         <is>
-          <t>랩지노믹스</t>
+          <t>마니커에프앤지</t>
         </is>
       </c>
       <c r="B45" s="25" t="n">
@@ -4576,25 +4578,25 @@
       </c>
       <c r="F45" s="25" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="G45" s="25" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="H45" s="28" t="n">
-        <v>-3.41</v>
+        <v>-15.17</v>
       </c>
       <c r="I45" s="27" t="n">
-        <v>24.65</v>
+        <v>3.85</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
       <c r="A46" s="26" t="inlineStr">
         <is>
-          <t>마니커</t>
+          <t>세미티에스</t>
         </is>
       </c>
       <c r="B46" s="25" t="n">
@@ -4611,25 +4613,25 @@
       </c>
       <c r="F46" s="25" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="G46" s="25" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
-        </is>
-      </c>
-      <c r="H46" s="28" t="n">
-        <v>-5.97</v>
-      </c>
-      <c r="I46" s="27" t="n">
-        <v>24.75</v>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="H46" s="27" t="n">
+        <v>29.97</v>
+      </c>
+      <c r="I46" s="28" t="n">
+        <v>-7.54</v>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
       <c r="A47" s="26" t="inlineStr">
         <is>
-          <t>세미티에스</t>
+          <t>아이로보틱스</t>
         </is>
       </c>
       <c r="B47" s="25" t="n">
@@ -4646,25 +4648,25 @@
       </c>
       <c r="F47" s="25" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="G47" s="25" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="H47" s="27" t="n">
-        <v>29.97</v>
-      </c>
-      <c r="I47" s="28" t="n">
-        <v>-7.54</v>
+        <v>22.3</v>
+      </c>
+      <c r="I47" s="27" t="n">
+        <v>27.7</v>
       </c>
     </row>
     <row r="48" ht="18" customHeight="1">
       <c r="A48" s="26" t="inlineStr">
         <is>
-          <t>스피어</t>
+          <t>저스템</t>
         </is>
       </c>
       <c r="B48" s="25" t="n">
@@ -4681,25 +4683,25 @@
       </c>
       <c r="F48" s="25" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="G48" s="25" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
-        </is>
-      </c>
-      <c r="H48" s="28" t="n">
-        <v>-4.68</v>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="H48" s="27" t="n">
+        <v>15.21</v>
       </c>
       <c r="I48" s="27" t="n">
-        <v>19.54</v>
+        <v>19.29</v>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1">
       <c r="A49" s="26" t="inlineStr">
         <is>
-          <t>저스템</t>
+          <t>제주은행</t>
         </is>
       </c>
       <c r="B49" s="25" t="n">
@@ -4716,25 +4718,25 @@
       </c>
       <c r="F49" s="25" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="G49" s="25" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="H49" s="27" t="n">
-        <v>15.21</v>
+        <v>0.16</v>
       </c>
       <c r="I49" s="27" t="n">
-        <v>19.29</v>
+        <v>15.07</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
       <c r="A50" s="26" t="inlineStr">
         <is>
-          <t>하림</t>
+          <t>테크윙</t>
         </is>
       </c>
       <c r="B50" s="25" t="n">
@@ -4751,25 +4753,25 @@
       </c>
       <c r="F50" s="25" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="G50" s="25" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
-        </is>
-      </c>
-      <c r="H50" s="28" t="n">
-        <v>-0.87</v>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="H50" s="27" t="n">
+        <v>6.87</v>
       </c>
       <c r="I50" s="27" t="n">
-        <v>0.71</v>
+        <v>19.38</v>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
       <c r="A51" s="26" t="inlineStr">
         <is>
-          <t>화신정공</t>
+          <t>하나마이크론</t>
         </is>
       </c>
       <c r="B51" s="25" t="n">
@@ -4786,25 +4788,25 @@
       </c>
       <c r="F51" s="25" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="G51" s="25" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="H51" s="27" t="n">
-        <v>6.18</v>
+        <v>2.09</v>
       </c>
       <c r="I51" s="27" t="n">
-        <v>142.33</v>
+        <v>16.97</v>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1">
       <c r="A52" s="26" t="inlineStr">
         <is>
-          <t>후성</t>
+          <t>화신정공</t>
         </is>
       </c>
       <c r="B52" s="25" t="n">
@@ -4821,19 +4823,19 @@
       </c>
       <c r="F52" s="25" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="G52" s="25" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="H52" s="27" t="n">
-        <v>20.55</v>
+        <v>6.18</v>
       </c>
       <c r="I52" s="27" t="n">
-        <v>63.46</v>
+        <v>142.33</v>
       </c>
     </row>
   </sheetData>
@@ -4917,19 +4919,19 @@
         <v>1</v>
       </c>
       <c r="C3" s="36" t="n">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="D3" s="36" t="n">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="E3" s="36" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="F3" s="37" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="G3" s="37" t="inlineStr">
@@ -4948,19 +4950,19 @@
         <v>1</v>
       </c>
       <c r="C4" s="36" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D4" s="36" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E4" s="36" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="F4" s="37" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="G4" s="37" t="inlineStr">
@@ -4972,26 +4974,26 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="35" t="inlineStr">
         <is>
-          <t>원전</t>
+          <t>전기차</t>
         </is>
       </c>
       <c r="B5" s="36" t="n">
         <v>1</v>
       </c>
       <c r="C5" s="36" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D5" s="36" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E5" s="36" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="F5" s="37" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="G5" s="37" t="inlineStr">
@@ -5003,26 +5005,26 @@
     <row r="6" ht="18" customHeight="1">
       <c r="A6" s="35" t="inlineStr">
         <is>
-          <t>로봇</t>
+          <t>원전</t>
         </is>
       </c>
       <c r="B6" s="36" t="n">
         <v>1</v>
       </c>
       <c r="C6" s="36" t="n">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="D6" s="36" t="n">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="E6" s="36" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="F6" s="37" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="G6" s="37" t="inlineStr">
@@ -5034,26 +5036,26 @@
     <row r="7" ht="18" customHeight="1">
       <c r="A7" s="35" t="inlineStr">
         <is>
-          <t>수소</t>
+          <t>로봇</t>
         </is>
       </c>
       <c r="B7" s="36" t="n">
         <v>1</v>
       </c>
       <c r="C7" s="36" t="n">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="D7" s="36" t="n">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="E7" s="36" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="F7" s="37" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="G7" s="37" t="inlineStr">
@@ -5065,26 +5067,26 @@
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="35" t="inlineStr">
         <is>
-          <t>제약</t>
+          <t>철강</t>
         </is>
       </c>
       <c r="B8" s="36" t="n">
         <v>1</v>
       </c>
       <c r="C8" s="36" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="D8" s="36" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="E8" s="36" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="F8" s="37" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="G8" s="37" t="inlineStr">
@@ -5096,26 +5098,26 @@
     <row r="9" ht="18" customHeight="1">
       <c r="A9" s="35" t="inlineStr">
         <is>
-          <t>인공지능</t>
+          <t>제약</t>
         </is>
       </c>
       <c r="B9" s="36" t="n">
         <v>1</v>
       </c>
       <c r="C9" s="36" t="n">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="D9" s="36" t="n">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="E9" s="36" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="F9" s="37" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="G9" s="37" t="inlineStr">
@@ -5127,26 +5129,26 @@
     <row r="10" ht="18" customHeight="1">
       <c r="A10" s="35" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>인공지능</t>
         </is>
       </c>
       <c r="B10" s="36" t="n">
         <v>1</v>
       </c>
       <c r="C10" s="36" t="n">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="D10" s="36" t="n">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="E10" s="36" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="F10" s="37" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="G10" s="37" t="inlineStr">
@@ -5212,7 +5214,7 @@
     <row r="13" ht="18" customHeight="1">
       <c r="A13" s="26" t="inlineStr">
         <is>
-          <t>전기차</t>
+          <t>방산</t>
         </is>
       </c>
       <c r="B13" s="25" t="n">
@@ -5239,7 +5241,7 @@
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="26" t="inlineStr">
         <is>
-          <t>방산</t>
+          <t>수소</t>
         </is>
       </c>
       <c r="B14" s="25" t="n">
@@ -5428,7 +5430,7 @@
     <row r="21" ht="18" customHeight="1">
       <c r="A21" s="26" t="inlineStr">
         <is>
-          <t>철강</t>
+          <t>의료기기</t>
         </is>
       </c>
       <c r="B21" s="25" t="n">
@@ -5455,7 +5457,7 @@
     <row r="22" ht="18" customHeight="1">
       <c r="A22" s="26" t="inlineStr">
         <is>
-          <t>의료기기</t>
+          <t>NVIDIA</t>
         </is>
       </c>
       <c r="B22" s="25" t="n">
@@ -5482,7 +5484,7 @@
     <row r="23" ht="18" customHeight="1">
       <c r="A23" s="26" t="inlineStr">
         <is>
-          <t>NVIDIA</t>
+          <t>Tesla</t>
         </is>
       </c>
       <c r="B23" s="25" t="n">
@@ -5509,7 +5511,7 @@
     <row r="24" ht="18" customHeight="1">
       <c r="A24" s="26" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="B24" s="25" t="n">

--- a/trend/stock_trend_history.xlsx
+++ b/trend/stock_trend_history.xlsx
@@ -694,7 +694,7 @@
     <row r="1" ht="36" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>📊 주식 트렌드 조기 감지 대시보드   |   최종 업데이트: 2026-06-14 06:55</t>
+          <t>📊 주식 트렌드 조기 감지 대시보드   |   최종 업데이트: 2026-06-15 06:54</t>
         </is>
       </c>
     </row>
@@ -787,21 +787,21 @@
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="11" t="inlineStr">
         <is>
-          <t>⚡ 최신(2026-06-14) 상위: 반도체  점수 74.0점</t>
+          <t>⚡ 최신(2026-06-15) 상위: 반도체  점수 68.0점</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1">
       <c r="A11" s="12" t="inlineStr">
         <is>
-          <t>⚡ 최신(2026-06-14) 상위: 바이오  점수 23.0점</t>
+          <t>⚡ 최신(2026-06-15) 상위: 인공지능  점수 17.0점</t>
         </is>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1">
       <c r="A12" s="11" t="inlineStr">
         <is>
-          <t>⚡ 최신(2026-06-14) 상위: 로봇  점수 22.0점</t>
+          <t>⚡ 최신(2026-06-15) 상위: 삼성전자  점수 15.0점</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B14" s="15" t="n">
@@ -928,10 +928,10 @@
         </is>
       </c>
       <c r="D14" s="15" t="n">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="E14" s="15" t="n">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="F14" s="15" t="n">
         <v>0</v>
@@ -947,7 +947,7 @@
       </c>
       <c r="J14" s="17" t="inlineStr">
         <is>
-          <t>매일경제 헤드라인 언급 / 매일경제 기사 언급 / 네이버뉴스 기사 언급 / 매일경제 기사 언급 / 네이버뉴스 헤드라인 언급</t>
+          <t>매일경제 기사 언급 / 매일경제 헤드라인 언급 / 매일경제 기사 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급</t>
         </is>
       </c>
       <c r="K14" s="17" t="inlineStr">
@@ -959,7 +959,7 @@
     <row r="15" ht="18" customHeight="1">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B15" s="15" t="n">
@@ -967,14 +967,14 @@
       </c>
       <c r="C15" s="16" t="inlineStr">
         <is>
-          <t>바이오</t>
+          <t>인공지능</t>
         </is>
       </c>
       <c r="D15" s="15" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="E15" s="15" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="F15" s="15" t="n">
         <v>0</v>
@@ -990,7 +990,7 @@
       </c>
       <c r="J15" s="17" t="inlineStr">
         <is>
-          <t>네이버뉴스 헤드라인 언급 / 네이버뉴스 헤드라인 언급 / 매일경제 헤드라인 언급 / 네이버뉴스 헤드라인 언급 / 매일경제 기사 언급</t>
+          <t>매일경제 기사 언급 / 매일경제 기사 언급 / 매일경제 기사 언급 / 매일경제 기사 언급 / 매일경제 기사 언급</t>
         </is>
       </c>
       <c r="K15" s="17" t="inlineStr">
@@ -1002,7 +1002,7 @@
     <row r="16" ht="18" customHeight="1">
       <c r="A16" s="15" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B16" s="15" t="n">
@@ -1010,14 +1010,14 @@
       </c>
       <c r="C16" s="16" t="inlineStr">
         <is>
-          <t>로봇</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="D16" s="15" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="E16" s="15" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="F16" s="15" t="n">
         <v>0</v>
@@ -1025,15 +1025,15 @@
       <c r="G16" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="H16" s="15" t="n">
-        <v/>
-      </c>
-      <c r="I16" s="15" t="n">
-        <v/>
+      <c r="H16" s="18" t="n">
+        <v>7.86</v>
+      </c>
+      <c r="I16" s="19" t="n">
+        <v>-1.98</v>
       </c>
       <c r="J16" s="17" t="inlineStr">
         <is>
-          <t>매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 네이버뉴스 기사 언급 / 한국경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
+          <t>매일경제 헤드라인 언급 / 네이버뉴스 기사 언급 / 매일경제 기사 언급 / 매일경제 기사 언급 / 한국경제 헤드라인 언급</t>
         </is>
       </c>
       <c r="K16" s="17" t="inlineStr">
@@ -1045,7 +1045,7 @@
     <row r="17" ht="18" customHeight="1">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B17" s="15" t="n">
@@ -1053,14 +1053,14 @@
       </c>
       <c r="C17" s="16" t="inlineStr">
         <is>
-          <t>인공지능</t>
+          <t>삼성전기</t>
         </is>
       </c>
       <c r="D17" s="15" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="E17" s="15" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="F17" s="15" t="n">
         <v>0</v>
@@ -1068,27 +1068,25 @@
       <c r="G17" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="H17" s="15" t="n">
+      <c r="H17" s="19" t="n">
+        <v>-5.04</v>
+      </c>
+      <c r="I17" s="19" t="n">
+        <v>-2.45</v>
+      </c>
+      <c r="J17" s="17" t="inlineStr">
+        <is>
+          <t>매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K17" s="17" t="n">
         <v/>
-      </c>
-      <c r="I17" s="15" t="n">
-        <v/>
-      </c>
-      <c r="J17" s="17" t="inlineStr">
-        <is>
-          <t>매일경제 기사 언급 / 매일경제 기사 언급 / 매일경제 기사 언급 / 매일경제 기사 언급 / 매일경제 기사 언급</t>
-        </is>
-      </c>
-      <c r="K17" s="17" t="inlineStr">
-        <is>
-          <t>네이버</t>
-        </is>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
       <c r="A18" s="15" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B18" s="15" t="n">
@@ -1096,14 +1094,14 @@
       </c>
       <c r="C18" s="16" t="inlineStr">
         <is>
-          <t>현대차</t>
+          <t>바이오</t>
         </is>
       </c>
       <c r="D18" s="15" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E18" s="15" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F18" s="15" t="n">
         <v>0</v>
@@ -1111,15 +1109,15 @@
       <c r="G18" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="H18" s="18" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="I18" s="19" t="n">
-        <v>-13.29</v>
+      <c r="H18" s="15" t="n">
+        <v/>
+      </c>
+      <c r="I18" s="15" t="n">
+        <v/>
       </c>
       <c r="J18" s="17" t="inlineStr">
         <is>
-          <t>네이버뉴스 헤드라인 언급 / 한국경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
+          <t>네이버뉴스 헤드라인 언급 / 네이버뉴스 헤드라인 언급 / 매일경제 기사 언급 / 네이버뉴스 헤드라인 언급 / 네이버뉴스 기사 언급</t>
         </is>
       </c>
       <c r="K18" s="17" t="inlineStr">
@@ -1131,7 +1129,7 @@
     <row r="19" ht="18" customHeight="1">
       <c r="A19" s="15" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B19" s="15" t="n">
@@ -1139,7 +1137,7 @@
       </c>
       <c r="C19" s="16" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>로봇</t>
         </is>
       </c>
       <c r="D19" s="15" t="n">
@@ -1154,25 +1152,27 @@
       <c r="G19" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="H19" s="18" t="n">
-        <v>7.86</v>
-      </c>
-      <c r="I19" s="19" t="n">
-        <v>-1.98</v>
+      <c r="H19" s="15" t="n">
+        <v/>
+      </c>
+      <c r="I19" s="15" t="n">
+        <v/>
       </c>
       <c r="J19" s="17" t="inlineStr">
         <is>
-          <t>매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 기사 언급 / 매일경제 기사 언급 / 매일경제 기사 언급</t>
-        </is>
-      </c>
-      <c r="K19" s="17" t="n">
-        <v/>
+          <t>매일경제 헤드라인 언급 / 네이버뉴스 기사 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K19" s="17" t="inlineStr">
+        <is>
+          <t>네이버</t>
+        </is>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
       <c r="A20" s="15" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B20" s="15" t="n">
@@ -1203,7 +1203,7 @@
       </c>
       <c r="J20" s="17" t="inlineStr">
         <is>
-          <t>매일경제 헤드라인 언급 / 네이버뉴스 기사 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급</t>
+          <t>매일경제 헤드라인 언급 / 네이버뉴스 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 기사 언급</t>
         </is>
       </c>
       <c r="K20" s="17" t="inlineStr">
@@ -1215,7 +1215,7 @@
     <row r="21" ht="18" customHeight="1">
       <c r="A21" s="15" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B21" s="15" t="n">
@@ -1223,14 +1223,14 @@
       </c>
       <c r="C21" s="16" t="inlineStr">
         <is>
-          <t>삼성전기</t>
+          <t>미래에셋증권</t>
         </is>
       </c>
       <c r="D21" s="15" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E21" s="15" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F21" s="15" t="n">
         <v>0</v>
@@ -1238,15 +1238,15 @@
       <c r="G21" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="H21" s="19" t="n">
-        <v>-5.04</v>
+      <c r="H21" s="18" t="n">
+        <v>2.35</v>
       </c>
       <c r="I21" s="19" t="n">
-        <v>-2.45</v>
+        <v>-7.27</v>
       </c>
       <c r="J21" s="17" t="inlineStr">
         <is>
-          <t>네이버뉴스 기사 언급 / 한국경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 네이버뉴스 헤드라인 언급 / 매일경제 헤드라인 언급</t>
+          <t>네이버뉴스 헤드라인 언급 / 매일경제 헤드라인 언급 / 네이버뉴스 기사 언급 / 매일경제 기사 언급 / 한국경제 헤드라인 언급</t>
         </is>
       </c>
       <c r="K21" s="17" t="inlineStr">
@@ -1258,7 +1258,7 @@
     <row r="22" ht="18" customHeight="1">
       <c r="A22" s="15" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B22" s="15" t="n">
@@ -1270,10 +1270,10 @@
         </is>
       </c>
       <c r="D22" s="15" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E22" s="15" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F22" s="15" t="n">
         <v>0</v>
@@ -1289,7 +1289,7 @@
       </c>
       <c r="J22" s="17" t="inlineStr">
         <is>
-          <t>한국경제 헤드라인 언급 / 매일경제 기사 언급 / 매일경제 기사 언급 / 매일경제 기사 언급 / 한국경제 헤드라인 언급</t>
+          <t>매일경제 기사 언급 / 매일경제 기사 언급 / 한국경제 헤드라인 언급 / 매일경제 기사 언급 / 매일경제 기사 언급</t>
         </is>
       </c>
       <c r="K22" s="17" t="n">
@@ -1299,7 +1299,7 @@
     <row r="23" ht="18" customHeight="1">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B23" s="15" t="n">
@@ -1307,42 +1307,42 @@
       </c>
       <c r="C23" s="16" t="inlineStr">
         <is>
-          <t>한미반도체</t>
+          <t>제약</t>
         </is>
       </c>
       <c r="D23" s="15" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E23" s="15" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F23" s="15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G23" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="H23" s="18" t="n">
-        <v>24.05</v>
-      </c>
-      <c r="I23" s="18" t="n">
-        <v>27.56</v>
+      <c r="H23" s="15" t="n">
+        <v/>
+      </c>
+      <c r="I23" s="15" t="n">
+        <v/>
       </c>
       <c r="J23" s="17" t="inlineStr">
         <is>
-          <t>중요공시 2건 / 중요공시 3일 +100% / 한국경제 헤드라인 언급 / 한국경제 헤드라인 언급 / 매일경제 헤드라인 언급</t>
+          <t>네이버뉴스 헤드라인 언급 / 네이버뉴스 헤드라인 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 기사 언급</t>
         </is>
       </c>
       <c r="K23" s="17" t="inlineStr">
         <is>
-          <t>공시</t>
+          <t>네이버</t>
         </is>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B24" s="15" t="n">
@@ -1350,42 +1350,42 @@
       </c>
       <c r="C24" s="16" t="inlineStr">
         <is>
-          <t>제약</t>
+          <t>CSA 코스믹</t>
         </is>
       </c>
       <c r="D24" s="15" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E24" s="15" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="F24" s="15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G24" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="H24" s="15" t="n">
-        <v/>
-      </c>
-      <c r="I24" s="15" t="n">
-        <v/>
+      <c r="H24" s="18" t="n">
+        <v>29.93</v>
+      </c>
+      <c r="I24" s="18" t="n">
+        <v>69.53</v>
       </c>
       <c r="J24" s="17" t="inlineStr">
         <is>
-          <t>네이버뉴스 기사 언급 / 네이버뉴스 기사 언급 / 매일경제 기사 언급 / 네이버뉴스 헤드라인 언급 / 매일경제 헤드라인 언급</t>
+          <t>네이버 검색 당일 +262% / 중요공시 5건 / 중요공시 3일 +67%</t>
         </is>
       </c>
       <c r="K24" s="17" t="inlineStr">
         <is>
-          <t>네이버</t>
+          <t>네이버, 공시</t>
         </is>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
       <c r="A25" s="15" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B25" s="15" t="n">
@@ -1393,14 +1393,14 @@
       </c>
       <c r="C25" s="16" t="inlineStr">
         <is>
-          <t>CSA 코스믹</t>
+          <t>성호전자</t>
         </is>
       </c>
       <c r="D25" s="15" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E25" s="15" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F25" s="15" t="n">
         <v>2</v>
@@ -1409,26 +1409,26 @@
         <v>0</v>
       </c>
       <c r="H25" s="18" t="n">
-        <v>29.93</v>
-      </c>
-      <c r="I25" s="18" t="n">
-        <v>69.53</v>
+        <v>2.41</v>
+      </c>
+      <c r="I25" s="19" t="n">
+        <v>-4.41</v>
       </c>
       <c r="J25" s="17" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +244% / 중요공시 5건 / 중요공시 3일 +150% / 매일경제 헤드라인 언급</t>
+          <t>중요공시 3건 / 중요공시 3일 +200% / 한국경제 헤드라인 언급</t>
         </is>
       </c>
       <c r="K25" s="17" t="inlineStr">
         <is>
-          <t>공시, 네이버</t>
+          <t>공시</t>
         </is>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
       <c r="A26" s="15" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B26" s="15" t="n">
@@ -1436,40 +1436,42 @@
       </c>
       <c r="C26" s="16" t="inlineStr">
         <is>
-          <t>원전</t>
+          <t>알엔티엑스</t>
         </is>
       </c>
       <c r="D26" s="15" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E26" s="15" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="F26" s="15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G26" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H26" s="15" t="n">
-        <v/>
-      </c>
-      <c r="I26" s="15" t="n">
-        <v/>
+        <v>3</v>
+      </c>
+      <c r="H26" s="19" t="n">
+        <v>-0.44</v>
+      </c>
+      <c r="I26" s="19" t="n">
+        <v>-17.65</v>
       </c>
       <c r="J26" s="17" t="inlineStr">
         <is>
-          <t>한국경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 한국경제 헤드라인 언급 / 매일경제 기사 언급</t>
-        </is>
-      </c>
-      <c r="K26" s="17" t="n">
-        <v/>
+          <t>중요공시 5건 / 중요공시 3일 +150% / 중요공시 7일 +67%</t>
+        </is>
+      </c>
+      <c r="K26" s="17" t="inlineStr">
+        <is>
+          <t>공시</t>
+        </is>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
       <c r="A27" s="15" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B27" s="15" t="n">
@@ -1477,40 +1479,42 @@
       </c>
       <c r="C27" s="16" t="inlineStr">
         <is>
-          <t>대한항공</t>
+          <t>모바일어플라이언스</t>
         </is>
       </c>
       <c r="D27" s="15" t="n">
         <v>8</v>
       </c>
       <c r="E27" s="15" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="F27" s="15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G27" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H27" s="18" t="n">
-        <v>7.26</v>
-      </c>
-      <c r="I27" s="18" t="n">
-        <v>6.83</v>
+        <v>3</v>
+      </c>
+      <c r="H27" s="19" t="n">
+        <v>-2.09</v>
+      </c>
+      <c r="I27" s="19" t="n">
+        <v>-27.06</v>
       </c>
       <c r="J27" s="17" t="inlineStr">
         <is>
-          <t>매일경제 헤드라인 언급 / 한국경제 헤드라인 언급 / 매일경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K27" s="17" t="n">
-        <v/>
+          <t>중요공시 3건 / 중요공시 3일 +200% / 중요공시 7일 +200%</t>
+        </is>
+      </c>
+      <c r="K27" s="17" t="inlineStr">
+        <is>
+          <t>공시</t>
+        </is>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
       <c r="A28" s="15" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B28" s="15" t="n">
@@ -1518,42 +1522,42 @@
       </c>
       <c r="C28" s="16" t="inlineStr">
         <is>
-          <t>성호전자</t>
+          <t>에이팩트</t>
         </is>
       </c>
       <c r="D28" s="15" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E28" s="15" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F28" s="15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G28" s="15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H28" s="18" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="I28" s="19" t="n">
-        <v>-4.41</v>
+        <v>13.08</v>
+      </c>
+      <c r="I28" s="18" t="n">
+        <v>45.57</v>
       </c>
       <c r="J28" s="17" t="inlineStr">
         <is>
-          <t>중요공시 3건 / 중요공시 3일 +200% / 한국경제 헤드라인 언급</t>
+          <t>네이버 검색 당일 +148% / 중요공시 2건 / 중요공시 7일 +100%</t>
         </is>
       </c>
       <c r="K28" s="17" t="inlineStr">
         <is>
-          <t>공시</t>
+          <t>네이버, 공시</t>
         </is>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
       <c r="A29" s="15" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B29" s="15" t="n">
@@ -1561,30 +1565,30 @@
       </c>
       <c r="C29" s="16" t="inlineStr">
         <is>
-          <t>모바일어플라이언스</t>
+          <t>한미반도체</t>
         </is>
       </c>
       <c r="D29" s="15" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E29" s="15" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F29" s="15" t="n">
         <v>2</v>
       </c>
       <c r="G29" s="15" t="n">
-        <v>3</v>
-      </c>
-      <c r="H29" s="19" t="n">
-        <v>-2.09</v>
-      </c>
-      <c r="I29" s="19" t="n">
-        <v>-27.06</v>
+        <v>0</v>
+      </c>
+      <c r="H29" s="18" t="n">
+        <v>24.05</v>
+      </c>
+      <c r="I29" s="18" t="n">
+        <v>27.56</v>
       </c>
       <c r="J29" s="17" t="inlineStr">
         <is>
-          <t>중요공시 3건 / 중요공시 3일 +200% / 중요공시 7일 +50%</t>
+          <t>중요공시 2건 / 중요공시 3일 +100% / 매일경제 헤드라인 언급</t>
         </is>
       </c>
       <c r="K29" s="17" t="inlineStr">
@@ -1596,7 +1600,7 @@
     <row r="30" ht="18" customHeight="1">
       <c r="A30" s="15" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B30" s="15" t="n">
@@ -1604,14 +1608,14 @@
       </c>
       <c r="C30" s="16" t="inlineStr">
         <is>
-          <t>NH투자증권</t>
+          <t>원전</t>
         </is>
       </c>
       <c r="D30" s="15" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E30" s="15" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F30" s="15" t="n">
         <v>0</v>
@@ -1619,15 +1623,15 @@
       <c r="G30" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="H30" s="18" t="n">
-        <v>1.76</v>
+      <c r="H30" s="15" t="n">
+        <v/>
       </c>
       <c r="I30" s="15" t="n">
-        <v>0</v>
+        <v/>
       </c>
       <c r="J30" s="17" t="inlineStr">
         <is>
-          <t>매일경제 기사 언급 / 한국경제 헤드라인 언급 / 한국경제 헤드라인 언급 / 매일경제 기사 언급 / 매일경제 기사 언급</t>
+          <t>매일경제 기사 언급 / 매일경제 헤드라인 언급 / 한국경제 헤드라인 언급 / 매일경제 기사 언급</t>
         </is>
       </c>
       <c r="K30" s="17" t="n">
@@ -1637,7 +1641,7 @@
     <row r="31" ht="18" customHeight="1">
       <c r="A31" s="15" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B31" s="15" t="n">
@@ -1645,42 +1649,42 @@
       </c>
       <c r="C31" s="16" t="inlineStr">
         <is>
-          <t>에이팩트</t>
+          <t>현대차</t>
         </is>
       </c>
       <c r="D31" s="15" t="n">
         <v>7</v>
       </c>
       <c r="E31" s="15" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F31" s="15" t="n">
         <v>0</v>
       </c>
       <c r="G31" s="15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H31" s="18" t="n">
-        <v>13.08</v>
-      </c>
-      <c r="I31" s="18" t="n">
-        <v>45.57</v>
+        <v>1.68</v>
+      </c>
+      <c r="I31" s="19" t="n">
+        <v>-13.29</v>
       </c>
       <c r="J31" s="17" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +137% / 중요공시 2건 / 중요공시 7일 +100%</t>
+          <t>매일경제 헤드라인 언급 / 네이버뉴스 기사 언급 / 한국경제 헤드라인 언급 / 매일경제 기사 언급</t>
         </is>
       </c>
       <c r="K31" s="17" t="inlineStr">
         <is>
-          <t>공시, 네이버</t>
+          <t>네이버</t>
         </is>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
       <c r="A32" s="20" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B32" s="20" t="n">
@@ -1711,7 +1715,7 @@
       </c>
       <c r="J32" s="23" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +322% / 매일경제 헤드라인 언급</t>
+          <t>네이버 검색 당일 +343% / 매일경제 헤드라인 언급</t>
         </is>
       </c>
       <c r="K32" s="23" t="inlineStr">
@@ -1723,7 +1727,7 @@
     <row r="33" ht="18" customHeight="1">
       <c r="A33" s="20" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B33" s="20" t="n">
@@ -1731,30 +1735,30 @@
       </c>
       <c r="C33" s="21" t="inlineStr">
         <is>
-          <t>스피어</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="D33" s="20" t="n">
         <v>6</v>
       </c>
       <c r="E33" s="20" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F33" s="20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G33" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H33" s="24" t="n">
-        <v>-4.68</v>
-      </c>
-      <c r="I33" s="22" t="n">
-        <v>19.54</v>
+        <v>3</v>
+      </c>
+      <c r="H33" s="22" t="n">
+        <v>6.32</v>
+      </c>
+      <c r="I33" s="24" t="n">
+        <v>-3.06</v>
       </c>
       <c r="J33" s="23" t="inlineStr">
         <is>
-          <t>중요공시 4건 / 중요공시 3일 +100%</t>
+          <t>중요공시 3건 / 중요공시 7일 +50%</t>
         </is>
       </c>
       <c r="K33" s="23" t="inlineStr">
@@ -1766,7 +1770,7 @@
     <row r="34" ht="18" customHeight="1">
       <c r="A34" s="20" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B34" s="20" t="n">
@@ -1774,7 +1778,7 @@
       </c>
       <c r="C34" s="21" t="inlineStr">
         <is>
-          <t>미래에셋증권</t>
+          <t>방산</t>
         </is>
       </c>
       <c r="D34" s="20" t="n">
@@ -1789,15 +1793,15 @@
       <c r="G34" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H34" s="22" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="I34" s="24" t="n">
-        <v>-7.27</v>
+      <c r="H34" s="20" t="n">
+        <v/>
+      </c>
+      <c r="I34" s="20" t="n">
+        <v/>
       </c>
       <c r="J34" s="23" t="inlineStr">
         <is>
-          <t>매일경제 헤드라인 언급 / 매일경제 기사 언급 / 한국경제 헤드라인 언급</t>
+          <t>매일경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
         </is>
       </c>
       <c r="K34" s="23" t="n">
@@ -1807,7 +1811,7 @@
     <row r="35" ht="18" customHeight="1">
       <c r="A35" s="20" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B35" s="20" t="n">
@@ -1815,42 +1819,42 @@
       </c>
       <c r="C35" s="21" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>전기차</t>
         </is>
       </c>
       <c r="D35" s="20" t="n">
         <v>6</v>
       </c>
       <c r="E35" s="20" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F35" s="20" t="n">
         <v>0</v>
       </c>
       <c r="G35" s="20" t="n">
-        <v>3</v>
-      </c>
-      <c r="H35" s="22" t="n">
-        <v>6.32</v>
-      </c>
-      <c r="I35" s="24" t="n">
-        <v>-3.06</v>
+        <v>0</v>
+      </c>
+      <c r="H35" s="20" t="n">
+        <v/>
+      </c>
+      <c r="I35" s="20" t="n">
+        <v/>
       </c>
       <c r="J35" s="23" t="inlineStr">
         <is>
-          <t>중요공시 3건 / 중요공시 7일 +200%</t>
+          <t>매일경제 기사 언급 / 매일경제 기사 언급 / 네이버뉴스 헤드라인 언급 / 매일경제 기사 언급</t>
         </is>
       </c>
       <c r="K35" s="23" t="inlineStr">
         <is>
-          <t>공시</t>
+          <t>네이버</t>
         </is>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
       <c r="A36" s="20" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B36" s="20" t="n">
@@ -1858,42 +1862,40 @@
       </c>
       <c r="C36" s="21" t="inlineStr">
         <is>
-          <t>에스아이리소스</t>
+          <t>현대로템</t>
         </is>
       </c>
       <c r="D36" s="20" t="n">
         <v>6</v>
       </c>
       <c r="E36" s="20" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F36" s="20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G36" s="20" t="n">
-        <v>3</v>
-      </c>
-      <c r="H36" s="24" t="n">
-        <v>-6.32</v>
-      </c>
-      <c r="I36" s="24" t="n">
-        <v>-9.18</v>
+        <v>0</v>
+      </c>
+      <c r="H36" s="22" t="n">
+        <v>10.67</v>
+      </c>
+      <c r="I36" s="22" t="n">
+        <v>8.93</v>
       </c>
       <c r="J36" s="23" t="inlineStr">
         <is>
-          <t>중요공시 2건 / 중요공시 3일 +100% / 중요공시 7일 +100%</t>
-        </is>
-      </c>
-      <c r="K36" s="23" t="inlineStr">
-        <is>
-          <t>공시</t>
-        </is>
+          <t>매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K36" s="23" t="n">
+        <v/>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
       <c r="A37" s="20" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B37" s="20" t="n">
@@ -1901,30 +1903,30 @@
       </c>
       <c r="C37" s="21" t="inlineStr">
         <is>
-          <t>엑시온그룹</t>
+          <t>피노</t>
         </is>
       </c>
       <c r="D37" s="20" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E37" s="20" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F37" s="20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G37" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H37" s="22" t="n">
-        <v>5.63</v>
-      </c>
-      <c r="I37" s="22" t="n">
-        <v>4.85</v>
+      <c r="H37" s="24" t="n">
+        <v>-3.76</v>
+      </c>
+      <c r="I37" s="24" t="n">
+        <v>-13.44</v>
       </c>
       <c r="J37" s="23" t="inlineStr">
         <is>
-          <t>중요공시 3건 / 매일경제 헤드라인 언급</t>
+          <t>중요공시 3건 / 중요공시 3일 +200%</t>
         </is>
       </c>
       <c r="K37" s="23" t="inlineStr">
@@ -1936,7 +1938,7 @@
     <row r="38" ht="18" customHeight="1">
       <c r="A38" s="20" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B38" s="20" t="n">
@@ -1944,14 +1946,14 @@
       </c>
       <c r="C38" s="21" t="inlineStr">
         <is>
-          <t>현대로템</t>
+          <t>네이버</t>
         </is>
       </c>
       <c r="D38" s="20" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E38" s="20" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F38" s="20" t="n">
         <v>0</v>
@@ -1959,15 +1961,15 @@
       <c r="G38" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H38" s="22" t="n">
-        <v>10.67</v>
-      </c>
-      <c r="I38" s="22" t="n">
-        <v>8.93</v>
+      <c r="H38" s="20" t="n">
+        <v/>
+      </c>
+      <c r="I38" s="20" t="n">
+        <v/>
       </c>
       <c r="J38" s="23" t="inlineStr">
         <is>
-          <t>매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급</t>
+          <t>한국경제 헤드라인 언급 / 매일경제 헤드라인 언급</t>
         </is>
       </c>
       <c r="K38" s="23" t="n">
@@ -1977,7 +1979,7 @@
     <row r="39" ht="18" customHeight="1">
       <c r="A39" s="20" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B39" s="20" t="n">
@@ -1985,7 +1987,7 @@
       </c>
       <c r="C39" s="21" t="inlineStr">
         <is>
-          <t>한화오션</t>
+          <t>NH투자증권</t>
         </is>
       </c>
       <c r="D39" s="20" t="n">
@@ -2001,26 +2003,24 @@
         <v>0</v>
       </c>
       <c r="H39" s="22" t="n">
-        <v>7.85</v>
-      </c>
-      <c r="I39" s="22" t="n">
-        <v>0.45</v>
+        <v>1.76</v>
+      </c>
+      <c r="I39" s="20" t="n">
+        <v>0</v>
       </c>
       <c r="J39" s="23" t="inlineStr">
         <is>
-          <t>중요공시 1건 / 한국경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K39" s="23" t="inlineStr">
-        <is>
-          <t>공시</t>
-        </is>
+          <t>매일경제 기사 언급 / 한국경제 헤드라인 언급 / 매일경제 기사 언급 / 매일경제 기사 언급</t>
+        </is>
+      </c>
+      <c r="K39" s="23" t="n">
+        <v/>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
       <c r="A40" s="20" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B40" s="20" t="n">
@@ -2028,42 +2028,42 @@
       </c>
       <c r="C40" s="21" t="inlineStr">
         <is>
-          <t>알엔티엑스</t>
+          <t>라이콤</t>
         </is>
       </c>
       <c r="D40" s="20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E40" s="20" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F40" s="20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G40" s="20" t="n">
         <v>0</v>
       </c>
       <c r="H40" s="24" t="n">
-        <v>-0.44</v>
-      </c>
-      <c r="I40" s="24" t="n">
-        <v>-17.65</v>
+        <v>-12.4</v>
+      </c>
+      <c r="I40" s="22" t="n">
+        <v>30.29</v>
       </c>
       <c r="J40" s="23" t="inlineStr">
         <is>
-          <t>중요공시 5건 / 중요공시 3일 +150%</t>
+          <t>네이버 검색 당일 +229% / 중요공시 1건</t>
         </is>
       </c>
       <c r="K40" s="23" t="inlineStr">
         <is>
-          <t>공시</t>
+          <t>네이버, 공시</t>
         </is>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
       <c r="A41" s="20" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B41" s="20" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="C41" s="21" t="inlineStr">
         <is>
-          <t>라이콤</t>
+          <t>스피어</t>
         </is>
       </c>
       <c r="D41" s="20" t="n">
@@ -2087,26 +2087,26 @@
         <v>0</v>
       </c>
       <c r="H41" s="24" t="n">
-        <v>-12.4</v>
+        <v>-4.68</v>
       </c>
       <c r="I41" s="22" t="n">
-        <v>30.29</v>
+        <v>19.54</v>
       </c>
       <c r="J41" s="23" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +214% / 중요공시 1건</t>
+          <t>중요공시 4건</t>
         </is>
       </c>
       <c r="K41" s="23" t="inlineStr">
         <is>
-          <t>공시, 네이버</t>
+          <t>공시</t>
         </is>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
       <c r="A42" s="20" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B42" s="20" t="n">
@@ -2114,42 +2114,42 @@
       </c>
       <c r="C42" s="21" t="inlineStr">
         <is>
-          <t>원익IPS</t>
+          <t>현대건설</t>
         </is>
       </c>
       <c r="D42" s="20" t="n">
         <v>4</v>
       </c>
       <c r="E42" s="20" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F42" s="20" t="n">
         <v>0</v>
       </c>
       <c r="G42" s="20" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H42" s="22" t="n">
-        <v>30</v>
+        <v>28.36</v>
       </c>
       <c r="I42" s="22" t="n">
-        <v>38.13</v>
+        <v>19.41</v>
       </c>
       <c r="J42" s="23" t="inlineStr">
         <is>
-          <t>네이버뉴스 헤드라인 언급</t>
+          <t>중요공시 2건 / 중요공시 7일 +100%</t>
         </is>
       </c>
       <c r="K42" s="23" t="inlineStr">
         <is>
-          <t>네이버</t>
+          <t>공시</t>
         </is>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1">
       <c r="A43" s="20" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B43" s="20" t="n">
@@ -2157,7 +2157,7 @@
       </c>
       <c r="C43" s="21" t="inlineStr">
         <is>
-          <t>하림</t>
+          <t>삼성바이오로직스</t>
         </is>
       </c>
       <c r="D43" s="20" t="n">
@@ -2172,25 +2172,27 @@
       <c r="G43" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H43" s="24" t="n">
-        <v>-0.87</v>
-      </c>
-      <c r="I43" s="22" t="n">
-        <v>0.71</v>
+      <c r="H43" s="22" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="I43" s="24" t="n">
+        <v>-3.36</v>
       </c>
       <c r="J43" s="23" t="inlineStr">
         <is>
-          <t>한국경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K43" s="23" t="n">
-        <v/>
+          <t>중요공시 1건 / 네이버뉴스 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K43" s="23" t="inlineStr">
+        <is>
+          <t>네이버, 공시</t>
+        </is>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
       <c r="A44" s="20" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B44" s="20" t="n">
@@ -2198,7 +2200,7 @@
       </c>
       <c r="C44" s="21" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>철강</t>
         </is>
       </c>
       <c r="D44" s="20" t="n">
@@ -2213,27 +2215,27 @@
       <c r="G44" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H44" s="22" t="n">
-        <v>11.54</v>
-      </c>
-      <c r="I44" s="22" t="n">
-        <v>5.31</v>
+      <c r="H44" s="20" t="n">
+        <v/>
+      </c>
+      <c r="I44" s="20" t="n">
+        <v/>
       </c>
       <c r="J44" s="23" t="inlineStr">
         <is>
-          <t>중요공시 1건 / 네이버뉴스 헤드라인 언급</t>
+          <t>네이버뉴스 기사 언급 / 네이버뉴스 기사 언급 / 매일경제 기사 언급 / 매일경제 기사 언급</t>
         </is>
       </c>
       <c r="K44" s="23" t="inlineStr">
         <is>
-          <t>공시, 네이버</t>
+          <t>네이버</t>
         </is>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
       <c r="A45" s="20" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B45" s="20" t="n">
@@ -2241,42 +2243,42 @@
       </c>
       <c r="C45" s="21" t="inlineStr">
         <is>
-          <t>현대건설</t>
+          <t>현대제철</t>
         </is>
       </c>
       <c r="D45" s="20" t="n">
         <v>4</v>
       </c>
       <c r="E45" s="20" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F45" s="20" t="n">
         <v>0</v>
       </c>
       <c r="G45" s="20" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H45" s="22" t="n">
-        <v>28.36</v>
-      </c>
-      <c r="I45" s="22" t="n">
-        <v>19.41</v>
+        <v>8.710000000000001</v>
+      </c>
+      <c r="I45" s="24" t="n">
+        <v>-2.65</v>
       </c>
       <c r="J45" s="23" t="inlineStr">
         <is>
-          <t>중요공시 2건 / 중요공시 7일 +100%</t>
+          <t>네이버뉴스 헤드라인 언급 / 매일경제 기사 언급</t>
         </is>
       </c>
       <c r="K45" s="23" t="inlineStr">
         <is>
-          <t>공시</t>
+          <t>네이버</t>
         </is>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
       <c r="A46" s="20" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B46" s="20" t="n">
@@ -2284,7 +2286,7 @@
       </c>
       <c r="C46" s="21" t="inlineStr">
         <is>
-          <t>삼성바이오로직스</t>
+          <t>클라우드</t>
         </is>
       </c>
       <c r="D46" s="20" t="n">
@@ -2299,143 +2301,147 @@
       <c r="G46" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H46" s="22" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="I46" s="24" t="n">
-        <v>-3.36</v>
+      <c r="H46" s="20" t="n">
+        <v/>
+      </c>
+      <c r="I46" s="20" t="n">
+        <v/>
       </c>
       <c r="J46" s="23" t="inlineStr">
         <is>
-          <t>중요공시 1건 / 네이버뉴스 헤드라인 언급</t>
+          <t>네이버뉴스 기사 언급 / 네이버뉴스 헤드라인 언급</t>
         </is>
       </c>
       <c r="K46" s="23" t="inlineStr">
         <is>
-          <t>공시, 네이버</t>
+          <t>네이버</t>
         </is>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
-      <c r="A47" s="20" t="inlineStr">
-        <is>
-          <t>2026-06-14</t>
-        </is>
-      </c>
-      <c r="B47" s="20" t="n">
+      <c r="A47" s="25" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B47" s="25" t="n">
         <v>34</v>
       </c>
-      <c r="C47" s="21" t="inlineStr">
-        <is>
-          <t>전기차</t>
-        </is>
-      </c>
-      <c r="D47" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="E47" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="F47" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G47" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H47" s="20" t="n">
-        <v/>
-      </c>
-      <c r="I47" s="20" t="n">
-        <v/>
-      </c>
-      <c r="J47" s="23" t="inlineStr">
-        <is>
-          <t>매일경제 기사 언급 / 매일경제 기사 언급 / 매일경제 기사 언급 / 매일경제 기사 언급</t>
-        </is>
-      </c>
-      <c r="K47" s="23" t="n">
-        <v/>
+      <c r="C47" s="26" t="inlineStr">
+        <is>
+          <t>세미티에스</t>
+        </is>
+      </c>
+      <c r="D47" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="E47" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="F47" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G47" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H47" s="27" t="n">
+        <v>29.97</v>
+      </c>
+      <c r="I47" s="28" t="n">
+        <v>-7.54</v>
+      </c>
+      <c r="J47" s="29" t="inlineStr">
+        <is>
+          <t>네이버 검색 당일 +4464%</t>
+        </is>
+      </c>
+      <c r="K47" s="29" t="inlineStr">
+        <is>
+          <t>네이버</t>
+        </is>
       </c>
     </row>
     <row r="48" ht="18" customHeight="1">
-      <c r="A48" s="20" t="inlineStr">
-        <is>
-          <t>2026-06-14</t>
-        </is>
-      </c>
-      <c r="B48" s="20" t="n">
+      <c r="A48" s="25" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B48" s="25" t="n">
         <v>35</v>
       </c>
-      <c r="C48" s="21" t="inlineStr">
-        <is>
-          <t>KB금융</t>
-        </is>
-      </c>
-      <c r="D48" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="E48" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="F48" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G48" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H48" s="22" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="I48" s="24" t="n">
-        <v>-6.06</v>
-      </c>
-      <c r="J48" s="23" t="inlineStr">
-        <is>
-          <t>매일경제 헤드라인 언급 / 매일경제 기사 언급</t>
-        </is>
-      </c>
-      <c r="K48" s="23" t="n">
-        <v/>
+      <c r="C48" s="26" t="inlineStr">
+        <is>
+          <t>화신정공</t>
+        </is>
+      </c>
+      <c r="D48" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="E48" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="F48" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G48" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H48" s="27" t="n">
+        <v>6.18</v>
+      </c>
+      <c r="I48" s="27" t="n">
+        <v>142.33</v>
+      </c>
+      <c r="J48" s="29" t="inlineStr">
+        <is>
+          <t>네이버 검색 당일 +2148%</t>
+        </is>
+      </c>
+      <c r="K48" s="29" t="inlineStr">
+        <is>
+          <t>네이버</t>
+        </is>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1">
-      <c r="A49" s="20" t="inlineStr">
-        <is>
-          <t>2026-06-14</t>
-        </is>
-      </c>
-      <c r="B49" s="20" t="n">
+      <c r="A49" s="25" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B49" s="25" t="n">
         <v>36</v>
       </c>
-      <c r="C49" s="21" t="inlineStr">
-        <is>
-          <t>철강</t>
-        </is>
-      </c>
-      <c r="D49" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="E49" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="F49" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G49" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H49" s="20" t="n">
-        <v/>
-      </c>
-      <c r="I49" s="20" t="n">
-        <v/>
-      </c>
-      <c r="J49" s="23" t="inlineStr">
-        <is>
-          <t>네이버뉴스 헤드라인 언급 / 매일경제 기사 언급</t>
-        </is>
-      </c>
-      <c r="K49" s="23" t="inlineStr">
+      <c r="C49" s="26" t="inlineStr">
+        <is>
+          <t>마니커</t>
+        </is>
+      </c>
+      <c r="D49" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="E49" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="F49" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G49" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H49" s="28" t="n">
+        <v>-5.97</v>
+      </c>
+      <c r="I49" s="27" t="n">
+        <v>24.75</v>
+      </c>
+      <c r="J49" s="29" t="inlineStr">
+        <is>
+          <t>네이버 검색 당일 +519%</t>
+        </is>
+      </c>
+      <c r="K49" s="29" t="inlineStr">
         <is>
           <t>네이버</t>
         </is>
@@ -2444,7 +2450,7 @@
     <row r="50" ht="18" customHeight="1">
       <c r="A50" s="25" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B50" s="25" t="n">
@@ -2452,7 +2458,7 @@
       </c>
       <c r="C50" s="26" t="inlineStr">
         <is>
-          <t>세미티에스</t>
+          <t>SK이터닉스</t>
         </is>
       </c>
       <c r="D50" s="25" t="n">
@@ -2468,14 +2474,14 @@
         <v>0</v>
       </c>
       <c r="H50" s="27" t="n">
-        <v>29.97</v>
-      </c>
-      <c r="I50" s="28" t="n">
-        <v>-7.54</v>
+        <v>6.04</v>
+      </c>
+      <c r="I50" s="27" t="n">
+        <v>21.64</v>
       </c>
       <c r="J50" s="29" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +4221%</t>
+          <t>네이버 검색 당일 +274%</t>
         </is>
       </c>
       <c r="K50" s="29" t="inlineStr">
@@ -2487,7 +2493,7 @@
     <row r="51" ht="18" customHeight="1">
       <c r="A51" s="25" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B51" s="25" t="n">
@@ -2495,7 +2501,7 @@
       </c>
       <c r="C51" s="26" t="inlineStr">
         <is>
-          <t>화신정공</t>
+          <t>마니커에프앤지</t>
         </is>
       </c>
       <c r="D51" s="25" t="n">
@@ -2510,15 +2516,15 @@
       <c r="G51" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H51" s="27" t="n">
-        <v>6.18</v>
+      <c r="H51" s="28" t="n">
+        <v>-15.17</v>
       </c>
       <c r="I51" s="27" t="n">
-        <v>142.33</v>
+        <v>3.85</v>
       </c>
       <c r="J51" s="29" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +2072%</t>
+          <t>네이버 검색 당일 +203%</t>
         </is>
       </c>
       <c r="K51" s="29" t="inlineStr">
@@ -2530,7 +2536,7 @@
     <row r="52" ht="18" customHeight="1">
       <c r="A52" s="25" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B52" s="25" t="n">
@@ -2538,7 +2544,7 @@
       </c>
       <c r="C52" s="26" t="inlineStr">
         <is>
-          <t>마니커</t>
+          <t>아이로보틱스</t>
         </is>
       </c>
       <c r="D52" s="25" t="n">
@@ -2553,15 +2559,15 @@
       <c r="G52" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H52" s="28" t="n">
-        <v>-5.97</v>
+      <c r="H52" s="27" t="n">
+        <v>22.3</v>
       </c>
       <c r="I52" s="27" t="n">
-        <v>24.75</v>
+        <v>27.7</v>
       </c>
       <c r="J52" s="29" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +495%</t>
+          <t>네이버 검색 당일 +146%</t>
         </is>
       </c>
       <c r="K52" s="29" t="inlineStr">
@@ -2573,7 +2579,7 @@
     <row r="53" ht="18" customHeight="1">
       <c r="A53" s="25" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B53" s="25" t="n">
@@ -2581,7 +2587,7 @@
       </c>
       <c r="C53" s="26" t="inlineStr">
         <is>
-          <t>SK이터닉스</t>
+          <t>랩지노믹스</t>
         </is>
       </c>
       <c r="D53" s="25" t="n">
@@ -2596,15 +2602,15 @@
       <c r="G53" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H53" s="27" t="n">
-        <v>6.04</v>
+      <c r="H53" s="28" t="n">
+        <v>-3.41</v>
       </c>
       <c r="I53" s="27" t="n">
-        <v>21.64</v>
+        <v>24.65</v>
       </c>
       <c r="J53" s="29" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +264%</t>
+          <t>네이버 검색 당일 +144%</t>
         </is>
       </c>
       <c r="K53" s="29" t="inlineStr">
@@ -2616,7 +2622,7 @@
     <row r="54" ht="18" customHeight="1">
       <c r="A54" s="25" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B54" s="25" t="n">
@@ -2624,7 +2630,7 @@
       </c>
       <c r="C54" s="26" t="inlineStr">
         <is>
-          <t>마니커에프앤지</t>
+          <t>테크윙</t>
         </is>
       </c>
       <c r="D54" s="25" t="n">
@@ -2639,15 +2645,15 @@
       <c r="G54" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H54" s="28" t="n">
-        <v>-15.17</v>
+      <c r="H54" s="27" t="n">
+        <v>6.87</v>
       </c>
       <c r="I54" s="27" t="n">
-        <v>3.85</v>
+        <v>19.38</v>
       </c>
       <c r="J54" s="29" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +190%</t>
+          <t>네이버 검색 당일 +141%</t>
         </is>
       </c>
       <c r="K54" s="29" t="inlineStr">
@@ -2659,7 +2665,7 @@
     <row r="55" ht="18" customHeight="1">
       <c r="A55" s="25" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B55" s="25" t="n">
@@ -2667,7 +2673,7 @@
       </c>
       <c r="C55" s="26" t="inlineStr">
         <is>
-          <t>랩지노믹스</t>
+          <t>제주은행</t>
         </is>
       </c>
       <c r="D55" s="25" t="n">
@@ -2682,15 +2688,15 @@
       <c r="G55" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H55" s="28" t="n">
-        <v>-3.41</v>
+      <c r="H55" s="27" t="n">
+        <v>0.16</v>
       </c>
       <c r="I55" s="27" t="n">
-        <v>24.65</v>
+        <v>15.07</v>
       </c>
       <c r="J55" s="29" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +138%</t>
+          <t>네이버 검색 당일 +106%</t>
         </is>
       </c>
       <c r="K55" s="29" t="inlineStr">
@@ -2702,7 +2708,7 @@
     <row r="56" ht="18" customHeight="1">
       <c r="A56" s="25" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B56" s="25" t="n">
@@ -2710,7 +2716,7 @@
       </c>
       <c r="C56" s="26" t="inlineStr">
         <is>
-          <t>아이로보틱스</t>
+          <t>윈팩</t>
         </is>
       </c>
       <c r="D56" s="25" t="n">
@@ -2725,15 +2731,15 @@
       <c r="G56" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H56" s="27" t="n">
-        <v>22.3</v>
+      <c r="H56" s="28" t="n">
+        <v>-4.93</v>
       </c>
       <c r="I56" s="27" t="n">
-        <v>27.7</v>
+        <v>20.38</v>
       </c>
       <c r="J56" s="29" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +137%</t>
+          <t>네이버 검색 당일 +102%</t>
         </is>
       </c>
       <c r="K56" s="29" t="inlineStr">
@@ -2745,7 +2751,7 @@
     <row r="57" ht="18" customHeight="1">
       <c r="A57" s="25" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B57" s="25" t="n">
@@ -2753,7 +2759,7 @@
       </c>
       <c r="C57" s="26" t="inlineStr">
         <is>
-          <t>테크윙</t>
+          <t>SK네트웍스</t>
         </is>
       </c>
       <c r="D57" s="25" t="n">
@@ -2769,14 +2775,14 @@
         <v>0</v>
       </c>
       <c r="H57" s="27" t="n">
-        <v>6.87</v>
+        <v>11.4</v>
       </c>
       <c r="I57" s="27" t="n">
-        <v>19.38</v>
+        <v>19.27</v>
       </c>
       <c r="J57" s="29" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +128%</t>
+          <t>네이버 검색 당일 +78% / 매일경제 기사 언급</t>
         </is>
       </c>
       <c r="K57" s="29" t="inlineStr">
@@ -2788,7 +2794,7 @@
     <row r="58" ht="18" customHeight="1">
       <c r="A58" s="25" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B58" s="25" t="n">
@@ -2796,7 +2802,7 @@
       </c>
       <c r="C58" s="26" t="inlineStr">
         <is>
-          <t>제주은행</t>
+          <t>기아</t>
         </is>
       </c>
       <c r="D58" s="25" t="n">
@@ -2812,26 +2818,24 @@
         <v>0</v>
       </c>
       <c r="H58" s="27" t="n">
-        <v>0.16</v>
+        <v>6.92</v>
       </c>
       <c r="I58" s="27" t="n">
-        <v>15.07</v>
+        <v>3.54</v>
       </c>
       <c r="J58" s="29" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +100%</t>
-        </is>
-      </c>
-      <c r="K58" s="29" t="inlineStr">
-        <is>
-          <t>네이버</t>
-        </is>
+          <t>매일경제 헤드라인 언급 / 매일경제 기사 언급</t>
+        </is>
+      </c>
+      <c r="K58" s="29" t="n">
+        <v/>
       </c>
     </row>
     <row r="59" ht="18" customHeight="1">
       <c r="A59" s="25" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B59" s="25" t="n">
@@ -2839,7 +2843,7 @@
       </c>
       <c r="C59" s="26" t="inlineStr">
         <is>
-          <t>SK네트웍스</t>
+          <t>LG전자</t>
         </is>
       </c>
       <c r="D59" s="25" t="n">
@@ -2854,27 +2858,25 @@
       <c r="G59" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H59" s="27" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="I59" s="27" t="n">
-        <v>19.27</v>
+      <c r="H59" s="28" t="n">
+        <v>-0.22</v>
+      </c>
+      <c r="I59" s="28" t="n">
+        <v>-25.58</v>
       </c>
       <c r="J59" s="29" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +73% / 매일경제 기사 언급</t>
-        </is>
-      </c>
-      <c r="K59" s="29" t="inlineStr">
-        <is>
-          <t>네이버</t>
-        </is>
+          <t>매일경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K59" s="29" t="n">
+        <v/>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1">
       <c r="A60" s="25" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B60" s="25" t="n">
@@ -2882,7 +2884,7 @@
       </c>
       <c r="C60" s="26" t="inlineStr">
         <is>
-          <t>하나마이크론</t>
+          <t>한화솔루션</t>
         </is>
       </c>
       <c r="D60" s="25" t="n">
@@ -2898,26 +2900,26 @@
         <v>0</v>
       </c>
       <c r="H60" s="27" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="I60" s="27" t="n">
-        <v>16.97</v>
+        <v>0.14</v>
+      </c>
+      <c r="I60" s="28" t="n">
+        <v>-3.65</v>
       </c>
       <c r="J60" s="29" t="inlineStr">
         <is>
-          <t>네이버뉴스 헤드라인 언급</t>
+          <t>중요공시 3건</t>
         </is>
       </c>
       <c r="K60" s="29" t="inlineStr">
         <is>
-          <t>네이버</t>
+          <t>공시</t>
         </is>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
       <c r="A61" s="25" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B61" s="25" t="n">
@@ -2925,7 +2927,7 @@
       </c>
       <c r="C61" s="26" t="inlineStr">
         <is>
-          <t>저스템</t>
+          <t>엑시온그룹</t>
         </is>
       </c>
       <c r="D61" s="25" t="n">
@@ -2941,24 +2943,26 @@
         <v>0</v>
       </c>
       <c r="H61" s="27" t="n">
-        <v>15.21</v>
+        <v>5.63</v>
       </c>
       <c r="I61" s="27" t="n">
-        <v>19.29</v>
+        <v>4.85</v>
       </c>
       <c r="J61" s="29" t="inlineStr">
         <is>
-          <t>매일경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K61" s="29" t="n">
-        <v/>
+          <t>중요공시 3건</t>
+        </is>
+      </c>
+      <c r="K61" s="29" t="inlineStr">
+        <is>
+          <t>공시</t>
+        </is>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1">
       <c r="A62" s="25" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B62" s="25" t="n">
@@ -2966,40 +2970,42 @@
       </c>
       <c r="C62" s="26" t="inlineStr">
         <is>
-          <t>리노공업</t>
+          <t>한성크린텍</t>
         </is>
       </c>
       <c r="D62" s="25" t="n">
         <v>3</v>
       </c>
       <c r="E62" s="25" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F62" s="25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G62" s="25" t="n">
         <v>0</v>
       </c>
       <c r="H62" s="27" t="n">
-        <v>4.71</v>
+        <v>2.75</v>
       </c>
       <c r="I62" s="27" t="n">
-        <v>11.05</v>
+        <v>0.79</v>
       </c>
       <c r="J62" s="29" t="inlineStr">
         <is>
-          <t>매일경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K62" s="29" t="n">
-        <v/>
+          <t>중요공시 2건 / 중요공시 3일 +100%</t>
+        </is>
+      </c>
+      <c r="K62" s="29" t="inlineStr">
+        <is>
+          <t>공시</t>
+        </is>
       </c>
     </row>
     <row r="63" ht="18" customHeight="1">
       <c r="A63" s="25" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B63" s="25" t="n">
@@ -3007,7 +3013,7 @@
       </c>
       <c r="C63" s="26" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>셀트리온</t>
         </is>
       </c>
       <c r="D63" s="25" t="n">
@@ -3023,18 +3029,20 @@
         <v>0</v>
       </c>
       <c r="H63" s="27" t="n">
-        <v>5.08</v>
-      </c>
-      <c r="I63" s="28" t="n">
-        <v>-2.62</v>
+        <v>4.09</v>
+      </c>
+      <c r="I63" s="27" t="n">
+        <v>0.93</v>
       </c>
       <c r="J63" s="29" t="inlineStr">
         <is>
-          <t>한국경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K63" s="29" t="n">
-        <v/>
+          <t>네이버뉴스 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K63" s="29" t="inlineStr">
+        <is>
+          <t>네이버</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -3130,22 +3138,22 @@
         <v>1</v>
       </c>
       <c r="C3" s="25" t="n">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="D3" s="25" t="n">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="E3" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F3" s="25" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="G3" s="25" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="H3" s="25" t="n"/>
@@ -3154,29 +3162,29 @@
     <row r="4" ht="18" customHeight="1">
       <c r="A4" s="26" t="inlineStr">
         <is>
-          <t>바이오</t>
+          <t>인공지능</t>
         </is>
       </c>
       <c r="B4" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C4" s="25" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="D4" s="25" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="E4" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F4" s="25" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="G4" s="25" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="H4" s="25" t="n"/>
@@ -3185,99 +3193,103 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="26" t="inlineStr">
         <is>
-          <t>로봇</t>
+          <t>삼성전기</t>
         </is>
       </c>
       <c r="B5" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C5" s="25" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="D5" s="25" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="E5" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F5" s="25" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="G5" s="25" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
-        </is>
-      </c>
-      <c r="H5" s="25" t="n"/>
-      <c r="I5" s="25" t="n"/>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="H5" s="28" t="n">
+        <v>-5.04</v>
+      </c>
+      <c r="I5" s="28" t="n">
+        <v>-2.45</v>
+      </c>
     </row>
     <row r="6" ht="18" customHeight="1">
       <c r="A6" s="26" t="inlineStr">
         <is>
-          <t>인공지능</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B6" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C6" s="25" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="D6" s="25" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="E6" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F6" s="25" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="G6" s="25" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
-        </is>
-      </c>
-      <c r="H6" s="25" t="n"/>
-      <c r="I6" s="25" t="n"/>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="H6" s="27" t="n">
+        <v>7.86</v>
+      </c>
+      <c r="I6" s="28" t="n">
+        <v>-1.98</v>
+      </c>
     </row>
     <row r="7" ht="18" customHeight="1">
       <c r="A7" s="26" t="inlineStr">
         <is>
-          <t>현대차</t>
+          <t>바이오</t>
         </is>
       </c>
       <c r="B7" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C7" s="25" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D7" s="25" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E7" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F7" s="25" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="G7" s="25" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
-        </is>
-      </c>
-      <c r="H7" s="27" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="I7" s="28" t="n">
-        <v>-13.29</v>
-      </c>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="H7" s="25" t="n"/>
+      <c r="I7" s="25" t="n"/>
     </row>
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="26" t="inlineStr">
@@ -3299,12 +3311,12 @@
       </c>
       <c r="F8" s="25" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="G8" s="25" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="H8" s="28" t="n">
@@ -3317,7 +3329,7 @@
     <row r="9" ht="18" customHeight="1">
       <c r="A9" s="26" t="inlineStr">
         <is>
-          <t>삼성전기</t>
+          <t>로봇</t>
         </is>
       </c>
       <c r="B9" s="25" t="n">
@@ -3334,54 +3346,50 @@
       </c>
       <c r="F9" s="25" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="G9" s="25" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
-        </is>
-      </c>
-      <c r="H9" s="28" t="n">
-        <v>-5.04</v>
-      </c>
-      <c r="I9" s="28" t="n">
-        <v>-2.45</v>
-      </c>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="H9" s="25" t="n"/>
+      <c r="I9" s="25" t="n"/>
     </row>
     <row r="10" ht="18" customHeight="1">
       <c r="A10" s="26" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>미래에셋증권</t>
         </is>
       </c>
       <c r="B10" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C10" s="25" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D10" s="25" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E10" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F10" s="25" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="G10" s="25" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="H10" s="27" t="n">
-        <v>7.86</v>
+        <v>2.35</v>
       </c>
       <c r="I10" s="28" t="n">
-        <v>-1.98</v>
+        <v>-7.27</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
@@ -3394,22 +3402,22 @@
         <v>1</v>
       </c>
       <c r="C11" s="25" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D11" s="25" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E11" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F11" s="25" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="G11" s="25" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="H11" s="27" t="n">
@@ -3429,22 +3437,22 @@
         <v>1</v>
       </c>
       <c r="C12" s="25" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D12" s="25" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E12" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F12" s="25" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="G12" s="25" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="H12" s="25" t="n"/>
@@ -3453,108 +3461,112 @@
     <row r="13" ht="18" customHeight="1">
       <c r="A13" s="26" t="inlineStr">
         <is>
-          <t>한미반도체</t>
+          <t>CSA 코스믹</t>
         </is>
       </c>
       <c r="B13" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C13" s="25" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D13" s="25" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E13" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F13" s="25" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="G13" s="25" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="H13" s="27" t="n">
-        <v>24.05</v>
+        <v>29.93</v>
       </c>
       <c r="I13" s="27" t="n">
-        <v>27.56</v>
+        <v>69.53</v>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="26" t="inlineStr">
         <is>
-          <t>CSA 코스믹</t>
+          <t>모바일어플라이언스</t>
         </is>
       </c>
       <c r="B14" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C14" s="25" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D14" s="25" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E14" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F14" s="25" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="G14" s="25" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
-        </is>
-      </c>
-      <c r="H14" s="27" t="n">
-        <v>29.93</v>
-      </c>
-      <c r="I14" s="27" t="n">
-        <v>69.53</v>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="H14" s="28" t="n">
+        <v>-2.09</v>
+      </c>
+      <c r="I14" s="28" t="n">
+        <v>-27.06</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
       <c r="A15" s="26" t="inlineStr">
         <is>
-          <t>원전</t>
+          <t>성호전자</t>
         </is>
       </c>
       <c r="B15" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C15" s="25" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D15" s="25" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E15" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F15" s="25" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="G15" s="25" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
-        </is>
-      </c>
-      <c r="H15" s="25" t="n"/>
-      <c r="I15" s="25" t="n"/>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="H15" s="27" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="I15" s="28" t="n">
+        <v>-4.41</v>
+      </c>
     </row>
     <row r="16" ht="18" customHeight="1">
       <c r="A16" s="26" t="inlineStr">
         <is>
-          <t>NH투자증권</t>
+          <t>알엔티엑스</t>
         </is>
       </c>
       <c r="B16" s="25" t="n">
@@ -3571,130 +3583,126 @@
       </c>
       <c r="F16" s="25" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="G16" s="25" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
-        </is>
-      </c>
-      <c r="H16" s="27" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="I16" s="25" t="n">
-        <v>0</v>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="H16" s="28" t="n">
+        <v>-0.44</v>
+      </c>
+      <c r="I16" s="28" t="n">
+        <v>-17.65</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
       <c r="A17" s="26" t="inlineStr">
         <is>
-          <t>대한항공</t>
+          <t>에이팩트</t>
         </is>
       </c>
       <c r="B17" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C17" s="25" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D17" s="25" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E17" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F17" s="25" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="G17" s="25" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="H17" s="27" t="n">
-        <v>7.26</v>
+        <v>13.08</v>
       </c>
       <c r="I17" s="27" t="n">
-        <v>6.83</v>
+        <v>45.57</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
       <c r="A18" s="26" t="inlineStr">
         <is>
-          <t>모바일어플라이언스</t>
+          <t>원전</t>
         </is>
       </c>
       <c r="B18" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C18" s="25" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D18" s="25" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E18" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F18" s="25" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="G18" s="25" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
-        </is>
-      </c>
-      <c r="H18" s="28" t="n">
-        <v>-2.09</v>
-      </c>
-      <c r="I18" s="28" t="n">
-        <v>-27.06</v>
-      </c>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="H18" s="25" t="n"/>
+      <c r="I18" s="25" t="n"/>
     </row>
     <row r="19" ht="18" customHeight="1">
       <c r="A19" s="26" t="inlineStr">
         <is>
-          <t>성호전자</t>
+          <t>한미반도체</t>
         </is>
       </c>
       <c r="B19" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C19" s="25" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D19" s="25" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E19" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F19" s="25" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="G19" s="25" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="H19" s="27" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="I19" s="28" t="n">
-        <v>-4.41</v>
+        <v>24.05</v>
+      </c>
+      <c r="I19" s="27" t="n">
+        <v>27.56</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
       <c r="A20" s="26" t="inlineStr">
         <is>
-          <t>에이팩트</t>
+          <t>현대차</t>
         </is>
       </c>
       <c r="B20" s="25" t="n">
@@ -3711,25 +3719,25 @@
       </c>
       <c r="F20" s="25" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="G20" s="25" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="H20" s="27" t="n">
-        <v>13.08</v>
-      </c>
-      <c r="I20" s="27" t="n">
-        <v>45.57</v>
+        <v>1.68</v>
+      </c>
+      <c r="I20" s="28" t="n">
+        <v>-13.29</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
       <c r="A21" s="26" t="inlineStr">
         <is>
-          <t>미래에셋증권</t>
+          <t>방산</t>
         </is>
       </c>
       <c r="B21" s="25" t="n">
@@ -3746,20 +3754,16 @@
       </c>
       <c r="F21" s="25" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="G21" s="25" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
-        </is>
-      </c>
-      <c r="H21" s="27" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="I21" s="28" t="n">
-        <v>-7.27</v>
-      </c>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="H21" s="25" t="n"/>
+      <c r="I21" s="25" t="n"/>
     </row>
     <row r="22" ht="18" customHeight="1">
       <c r="A22" s="26" t="inlineStr">
@@ -3781,12 +3785,12 @@
       </c>
       <c r="F22" s="25" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="G22" s="25" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="H22" s="27" t="n">
@@ -3799,7 +3803,7 @@
     <row r="23" ht="18" customHeight="1">
       <c r="A23" s="26" t="inlineStr">
         <is>
-          <t>스피어</t>
+          <t>전기차</t>
         </is>
       </c>
       <c r="B23" s="25" t="n">
@@ -3816,25 +3820,21 @@
       </c>
       <c r="F23" s="25" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="G23" s="25" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
-        </is>
-      </c>
-      <c r="H23" s="28" t="n">
-        <v>-4.68</v>
-      </c>
-      <c r="I23" s="27" t="n">
-        <v>19.54</v>
-      </c>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="H23" s="25" t="n"/>
+      <c r="I23" s="25" t="n"/>
     </row>
     <row r="24" ht="18" customHeight="1">
       <c r="A24" s="26" t="inlineStr">
         <is>
-          <t>에스아이리소스</t>
+          <t>현대로템</t>
         </is>
       </c>
       <c r="B24" s="25" t="n">
@@ -3851,25 +3851,25 @@
       </c>
       <c r="F24" s="25" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="G24" s="25" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
-        </is>
-      </c>
-      <c r="H24" s="28" t="n">
-        <v>-6.32</v>
-      </c>
-      <c r="I24" s="28" t="n">
-        <v>-9.18</v>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="H24" s="27" t="n">
+        <v>10.67</v>
+      </c>
+      <c r="I24" s="27" t="n">
+        <v>8.93</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
       <c r="A25" s="26" t="inlineStr">
         <is>
-          <t>엑시온그룹</t>
+          <t>후성</t>
         </is>
       </c>
       <c r="B25" s="25" t="n">
@@ -3886,95 +3886,91 @@
       </c>
       <c r="F25" s="25" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="G25" s="25" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="H25" s="27" t="n">
-        <v>5.63</v>
+        <v>20.55</v>
       </c>
       <c r="I25" s="27" t="n">
-        <v>4.85</v>
+        <v>63.46</v>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
       <c r="A26" s="26" t="inlineStr">
         <is>
-          <t>현대로템</t>
+          <t>NH투자증권</t>
         </is>
       </c>
       <c r="B26" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C26" s="25" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D26" s="25" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E26" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F26" s="25" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="G26" s="25" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="H26" s="27" t="n">
-        <v>10.67</v>
-      </c>
-      <c r="I26" s="27" t="n">
-        <v>8.93</v>
+        <v>1.76</v>
+      </c>
+      <c r="I26" s="25" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
       <c r="A27" s="26" t="inlineStr">
         <is>
-          <t>후성</t>
+          <t>네이버</t>
         </is>
       </c>
       <c r="B27" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C27" s="25" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D27" s="25" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E27" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F27" s="25" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="G27" s="25" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
-        </is>
-      </c>
-      <c r="H27" s="27" t="n">
-        <v>20.55</v>
-      </c>
-      <c r="I27" s="27" t="n">
-        <v>63.46</v>
-      </c>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="H27" s="25" t="n"/>
+      <c r="I27" s="25" t="n"/>
     </row>
     <row r="28" ht="18" customHeight="1">
       <c r="A28" s="26" t="inlineStr">
         <is>
-          <t>알엔티엑스</t>
+          <t>피노</t>
         </is>
       </c>
       <c r="B28" s="25" t="n">
@@ -3991,60 +3987,60 @@
       </c>
       <c r="F28" s="25" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="G28" s="25" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="H28" s="28" t="n">
-        <v>-0.44</v>
+        <v>-3.76</v>
       </c>
       <c r="I28" s="28" t="n">
-        <v>-17.65</v>
+        <v>-13.44</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
       <c r="A29" s="26" t="inlineStr">
         <is>
-          <t>한화오션</t>
+          <t>라이콤</t>
         </is>
       </c>
       <c r="B29" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C29" s="25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D29" s="25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E29" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F29" s="25" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="G29" s="25" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
-        </is>
-      </c>
-      <c r="H29" s="27" t="n">
-        <v>7.85</v>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="H29" s="28" t="n">
+        <v>-12.4</v>
       </c>
       <c r="I29" s="27" t="n">
-        <v>0.45</v>
+        <v>30.29</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
       <c r="A30" s="26" t="inlineStr">
         <is>
-          <t>KB금융</t>
+          <t>삼성바이오로직스</t>
         </is>
       </c>
       <c r="B30" s="25" t="n">
@@ -4061,25 +4057,25 @@
       </c>
       <c r="F30" s="25" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="G30" s="25" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="H30" s="27" t="n">
-        <v>6.4</v>
+        <v>0.7</v>
       </c>
       <c r="I30" s="28" t="n">
-        <v>-6.06</v>
+        <v>-3.36</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
       <c r="A31" s="26" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>스피어</t>
         </is>
       </c>
       <c r="B31" s="25" t="n">
@@ -4096,25 +4092,25 @@
       </c>
       <c r="F31" s="25" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="G31" s="25" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
-        </is>
-      </c>
-      <c r="H31" s="27" t="n">
-        <v>11.54</v>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="H31" s="28" t="n">
+        <v>-4.68</v>
       </c>
       <c r="I31" s="27" t="n">
-        <v>5.31</v>
+        <v>19.54</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
       <c r="A32" s="26" t="inlineStr">
         <is>
-          <t>라이콤</t>
+          <t>철강</t>
         </is>
       </c>
       <c r="B32" s="25" t="n">
@@ -4131,25 +4127,21 @@
       </c>
       <c r="F32" s="25" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="G32" s="25" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
-        </is>
-      </c>
-      <c r="H32" s="28" t="n">
-        <v>-12.4</v>
-      </c>
-      <c r="I32" s="27" t="n">
-        <v>30.29</v>
-      </c>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="H32" s="25" t="n"/>
+      <c r="I32" s="25" t="n"/>
     </row>
     <row r="33" ht="18" customHeight="1">
       <c r="A33" s="26" t="inlineStr">
         <is>
-          <t>삼성바이오로직스</t>
+          <t>클라우드</t>
         </is>
       </c>
       <c r="B33" s="25" t="n">
@@ -4166,25 +4158,21 @@
       </c>
       <c r="F33" s="25" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="G33" s="25" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
-        </is>
-      </c>
-      <c r="H33" s="27" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="I33" s="28" t="n">
-        <v>-3.36</v>
-      </c>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="H33" s="25" t="n"/>
+      <c r="I33" s="25" t="n"/>
     </row>
     <row r="34" ht="18" customHeight="1">
       <c r="A34" s="26" t="inlineStr">
         <is>
-          <t>원익IPS</t>
+          <t>현대건설</t>
         </is>
       </c>
       <c r="B34" s="25" t="n">
@@ -4201,25 +4189,25 @@
       </c>
       <c r="F34" s="25" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="G34" s="25" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="H34" s="27" t="n">
-        <v>30</v>
+        <v>28.36</v>
       </c>
       <c r="I34" s="27" t="n">
-        <v>38.13</v>
+        <v>19.41</v>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
       <c r="A35" s="26" t="inlineStr">
         <is>
-          <t>전기차</t>
+          <t>현대제철</t>
         </is>
       </c>
       <c r="B35" s="25" t="n">
@@ -4236,122 +4224,130 @@
       </c>
       <c r="F35" s="25" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="G35" s="25" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
-        </is>
-      </c>
-      <c r="H35" s="25" t="n"/>
-      <c r="I35" s="25" t="n"/>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="H35" s="27" t="n">
+        <v>8.710000000000001</v>
+      </c>
+      <c r="I35" s="28" t="n">
+        <v>-2.65</v>
+      </c>
     </row>
     <row r="36" ht="18" customHeight="1">
       <c r="A36" s="26" t="inlineStr">
         <is>
-          <t>철강</t>
+          <t>LG전자</t>
         </is>
       </c>
       <c r="B36" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C36" s="25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D36" s="25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E36" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F36" s="25" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="G36" s="25" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
-        </is>
-      </c>
-      <c r="H36" s="25" t="n"/>
-      <c r="I36" s="25" t="n"/>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="H36" s="28" t="n">
+        <v>-0.22</v>
+      </c>
+      <c r="I36" s="28" t="n">
+        <v>-25.58</v>
+      </c>
     </row>
     <row r="37" ht="18" customHeight="1">
       <c r="A37" s="26" t="inlineStr">
         <is>
-          <t>하림</t>
+          <t>SK네트웍스</t>
         </is>
       </c>
       <c r="B37" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C37" s="25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D37" s="25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E37" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F37" s="25" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="G37" s="25" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
-        </is>
-      </c>
-      <c r="H37" s="28" t="n">
-        <v>-0.87</v>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="H37" s="27" t="n">
+        <v>11.4</v>
       </c>
       <c r="I37" s="27" t="n">
-        <v>0.71</v>
+        <v>19.27</v>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
       <c r="A38" s="26" t="inlineStr">
         <is>
-          <t>현대건설</t>
+          <t>SK이터닉스</t>
         </is>
       </c>
       <c r="B38" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C38" s="25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D38" s="25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E38" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F38" s="25" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="G38" s="25" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="H38" s="27" t="n">
-        <v>28.36</v>
+        <v>6.04</v>
       </c>
       <c r="I38" s="27" t="n">
-        <v>19.41</v>
+        <v>21.64</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
       <c r="A39" s="26" t="inlineStr">
         <is>
-          <t>SK네트웍스</t>
+          <t>기아</t>
         </is>
       </c>
       <c r="B39" s="25" t="n">
@@ -4368,25 +4364,25 @@
       </c>
       <c r="F39" s="25" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="G39" s="25" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="H39" s="27" t="n">
-        <v>11.4</v>
+        <v>6.92</v>
       </c>
       <c r="I39" s="27" t="n">
-        <v>19.27</v>
+        <v>3.54</v>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
       <c r="A40" s="26" t="inlineStr">
         <is>
-          <t>SK이터닉스</t>
+          <t>랩지노믹스</t>
         </is>
       </c>
       <c r="B40" s="25" t="n">
@@ -4403,25 +4399,25 @@
       </c>
       <c r="F40" s="25" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="G40" s="25" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
-        </is>
-      </c>
-      <c r="H40" s="27" t="n">
-        <v>6.04</v>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="H40" s="28" t="n">
+        <v>-3.41</v>
       </c>
       <c r="I40" s="27" t="n">
-        <v>21.64</v>
+        <v>24.65</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
       <c r="A41" s="26" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>마니커</t>
         </is>
       </c>
       <c r="B41" s="25" t="n">
@@ -4438,25 +4434,25 @@
       </c>
       <c r="F41" s="25" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="G41" s="25" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
-        </is>
-      </c>
-      <c r="H41" s="27" t="n">
-        <v>5.08</v>
-      </c>
-      <c r="I41" s="28" t="n">
-        <v>-2.62</v>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="H41" s="28" t="n">
+        <v>-5.97</v>
+      </c>
+      <c r="I41" s="27" t="n">
+        <v>24.75</v>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
       <c r="A42" s="26" t="inlineStr">
         <is>
-          <t>랩지노믹스</t>
+          <t>마니커에프앤지</t>
         </is>
       </c>
       <c r="B42" s="25" t="n">
@@ -4473,25 +4469,25 @@
       </c>
       <c r="F42" s="25" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="G42" s="25" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="H42" s="28" t="n">
-        <v>-3.41</v>
+        <v>-15.17</v>
       </c>
       <c r="I42" s="27" t="n">
-        <v>24.65</v>
+        <v>3.85</v>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1">
       <c r="A43" s="26" t="inlineStr">
         <is>
-          <t>리노공업</t>
+          <t>세미티에스</t>
         </is>
       </c>
       <c r="B43" s="25" t="n">
@@ -4508,25 +4504,25 @@
       </c>
       <c r="F43" s="25" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="G43" s="25" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="H43" s="27" t="n">
-        <v>4.71</v>
-      </c>
-      <c r="I43" s="27" t="n">
-        <v>11.05</v>
+        <v>29.97</v>
+      </c>
+      <c r="I43" s="28" t="n">
+        <v>-7.54</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
       <c r="A44" s="26" t="inlineStr">
         <is>
-          <t>마니커</t>
+          <t>셀트리온</t>
         </is>
       </c>
       <c r="B44" s="25" t="n">
@@ -4543,25 +4539,25 @@
       </c>
       <c r="F44" s="25" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="G44" s="25" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
-        </is>
-      </c>
-      <c r="H44" s="28" t="n">
-        <v>-5.97</v>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="H44" s="27" t="n">
+        <v>4.09</v>
       </c>
       <c r="I44" s="27" t="n">
-        <v>24.75</v>
+        <v>0.93</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
       <c r="A45" s="26" t="inlineStr">
         <is>
-          <t>마니커에프앤지</t>
+          <t>아이로보틱스</t>
         </is>
       </c>
       <c r="B45" s="25" t="n">
@@ -4578,25 +4574,25 @@
       </c>
       <c r="F45" s="25" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="G45" s="25" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
-        </is>
-      </c>
-      <c r="H45" s="28" t="n">
-        <v>-15.17</v>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="H45" s="27" t="n">
+        <v>22.3</v>
       </c>
       <c r="I45" s="27" t="n">
-        <v>3.85</v>
+        <v>27.7</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
       <c r="A46" s="26" t="inlineStr">
         <is>
-          <t>세미티에스</t>
+          <t>엑시온그룹</t>
         </is>
       </c>
       <c r="B46" s="25" t="n">
@@ -4613,25 +4609,25 @@
       </c>
       <c r="F46" s="25" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="G46" s="25" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="H46" s="27" t="n">
-        <v>29.97</v>
-      </c>
-      <c r="I46" s="28" t="n">
-        <v>-7.54</v>
+        <v>5.63</v>
+      </c>
+      <c r="I46" s="27" t="n">
+        <v>4.85</v>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
       <c r="A47" s="26" t="inlineStr">
         <is>
-          <t>아이로보틱스</t>
+          <t>윈팩</t>
         </is>
       </c>
       <c r="B47" s="25" t="n">
@@ -4648,25 +4644,25 @@
       </c>
       <c r="F47" s="25" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="G47" s="25" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
-        </is>
-      </c>
-      <c r="H47" s="27" t="n">
-        <v>22.3</v>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="H47" s="28" t="n">
+        <v>-4.93</v>
       </c>
       <c r="I47" s="27" t="n">
-        <v>27.7</v>
+        <v>20.38</v>
       </c>
     </row>
     <row r="48" ht="18" customHeight="1">
       <c r="A48" s="26" t="inlineStr">
         <is>
-          <t>저스템</t>
+          <t>제주은행</t>
         </is>
       </c>
       <c r="B48" s="25" t="n">
@@ -4683,25 +4679,25 @@
       </c>
       <c r="F48" s="25" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="G48" s="25" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="H48" s="27" t="n">
-        <v>15.21</v>
+        <v>0.16</v>
       </c>
       <c r="I48" s="27" t="n">
-        <v>19.29</v>
+        <v>15.07</v>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1">
       <c r="A49" s="26" t="inlineStr">
         <is>
-          <t>제주은행</t>
+          <t>테크윙</t>
         </is>
       </c>
       <c r="B49" s="25" t="n">
@@ -4718,25 +4714,25 @@
       </c>
       <c r="F49" s="25" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="G49" s="25" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="H49" s="27" t="n">
-        <v>0.16</v>
+        <v>6.87</v>
       </c>
       <c r="I49" s="27" t="n">
-        <v>15.07</v>
+        <v>19.38</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
       <c r="A50" s="26" t="inlineStr">
         <is>
-          <t>테크윙</t>
+          <t>한성크린텍</t>
         </is>
       </c>
       <c r="B50" s="25" t="n">
@@ -4753,25 +4749,25 @@
       </c>
       <c r="F50" s="25" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="G50" s="25" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="H50" s="27" t="n">
-        <v>6.87</v>
+        <v>2.75</v>
       </c>
       <c r="I50" s="27" t="n">
-        <v>19.38</v>
+        <v>0.79</v>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
       <c r="A51" s="26" t="inlineStr">
         <is>
-          <t>하나마이크론</t>
+          <t>한화솔루션</t>
         </is>
       </c>
       <c r="B51" s="25" t="n">
@@ -4788,19 +4784,19 @@
       </c>
       <c r="F51" s="25" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="G51" s="25" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="H51" s="27" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="I51" s="27" t="n">
-        <v>16.97</v>
+        <v>0.14</v>
+      </c>
+      <c r="I51" s="28" t="n">
+        <v>-3.65</v>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1">
@@ -4823,12 +4819,12 @@
       </c>
       <c r="F52" s="25" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="G52" s="25" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="H52" s="27" t="n">
@@ -4919,19 +4915,19 @@
         <v>1</v>
       </c>
       <c r="C3" s="36" t="n">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="D3" s="36" t="n">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="E3" s="36" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="F3" s="37" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="G3" s="37" t="inlineStr">
@@ -4950,19 +4946,19 @@
         <v>1</v>
       </c>
       <c r="C4" s="36" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="D4" s="36" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="E4" s="36" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="F4" s="37" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="G4" s="37" t="inlineStr">
@@ -4981,19 +4977,19 @@
         <v>1</v>
       </c>
       <c r="C5" s="36" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D5" s="36" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E5" s="36" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="F5" s="37" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="G5" s="37" t="inlineStr">
@@ -5005,26 +5001,26 @@
     <row r="6" ht="18" customHeight="1">
       <c r="A6" s="35" t="inlineStr">
         <is>
-          <t>원전</t>
+          <t>방산</t>
         </is>
       </c>
       <c r="B6" s="36" t="n">
         <v>1</v>
       </c>
       <c r="C6" s="36" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D6" s="36" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E6" s="36" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="F6" s="37" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="G6" s="37" t="inlineStr">
@@ -5036,26 +5032,26 @@
     <row r="7" ht="18" customHeight="1">
       <c r="A7" s="35" t="inlineStr">
         <is>
-          <t>로봇</t>
+          <t>원전</t>
         </is>
       </c>
       <c r="B7" s="36" t="n">
         <v>1</v>
       </c>
       <c r="C7" s="36" t="n">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="D7" s="36" t="n">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="E7" s="36" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="F7" s="37" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="G7" s="37" t="inlineStr">
@@ -5067,26 +5063,26 @@
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="35" t="inlineStr">
         <is>
-          <t>철강</t>
+          <t>로봇</t>
         </is>
       </c>
       <c r="B8" s="36" t="n">
         <v>1</v>
       </c>
       <c r="C8" s="36" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="D8" s="36" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="E8" s="36" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="F8" s="37" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="G8" s="37" t="inlineStr">
@@ -5098,26 +5094,26 @@
     <row r="9" ht="18" customHeight="1">
       <c r="A9" s="35" t="inlineStr">
         <is>
-          <t>제약</t>
+          <t>클라우드</t>
         </is>
       </c>
       <c r="B9" s="36" t="n">
         <v>1</v>
       </c>
       <c r="C9" s="36" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="D9" s="36" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="E9" s="36" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="F9" s="37" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="G9" s="37" t="inlineStr">
@@ -5129,92 +5125,100 @@
     <row r="10" ht="18" customHeight="1">
       <c r="A10" s="35" t="inlineStr">
         <is>
+          <t>철강</t>
+        </is>
+      </c>
+      <c r="B10" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" s="36" t="n">
+        <v>4</v>
+      </c>
+      <c r="D10" s="36" t="n">
+        <v>4</v>
+      </c>
+      <c r="E10" s="36" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="F10" s="37" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="G10" s="37" t="inlineStr">
+        <is>
+          <t>⚡ 관심</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="18" customHeight="1">
+      <c r="A11" s="35" t="inlineStr">
+        <is>
+          <t>제약</t>
+        </is>
+      </c>
+      <c r="B11" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" s="36" t="n">
+        <v>9</v>
+      </c>
+      <c r="D11" s="36" t="n">
+        <v>9</v>
+      </c>
+      <c r="E11" s="36" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="F11" s="37" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="G11" s="37" t="inlineStr">
+        <is>
+          <t>⚡ 관심</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="18" customHeight="1">
+      <c r="A12" s="35" t="inlineStr">
+        <is>
           <t>인공지능</t>
         </is>
       </c>
-      <c r="B10" s="36" t="n">
-        <v>1</v>
-      </c>
-      <c r="C10" s="36" t="n">
-        <v>21</v>
-      </c>
-      <c r="D10" s="36" t="n">
-        <v>21</v>
-      </c>
-      <c r="E10" s="36" t="inlineStr">
-        <is>
-          <t>2026-06-14</t>
-        </is>
-      </c>
-      <c r="F10" s="37" t="inlineStr">
-        <is>
-          <t>2026-06-14</t>
-        </is>
-      </c>
-      <c r="G10" s="37" t="inlineStr">
+      <c r="B12" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" s="36" t="n">
+        <v>17</v>
+      </c>
+      <c r="D12" s="36" t="n">
+        <v>17</v>
+      </c>
+      <c r="E12" s="36" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="F12" s="37" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="G12" s="37" t="inlineStr">
         <is>
           <t>⚡ 관심</t>
         </is>
       </c>
-    </row>
-    <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="26" t="inlineStr">
-        <is>
-          <t>이차전지</t>
-        </is>
-      </c>
-      <c r="B11" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="C11" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" s="25" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F11" s="29" t="inlineStr">
-        <is>
-          <t>감지 없음</t>
-        </is>
-      </c>
-      <c r="G11" s="29" t="inlineStr"/>
-    </row>
-    <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="26" t="inlineStr">
-        <is>
-          <t>AI반도체</t>
-        </is>
-      </c>
-      <c r="B12" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="C12" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" s="25" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F12" s="29" t="inlineStr">
-        <is>
-          <t>감지 없음</t>
-        </is>
-      </c>
-      <c r="G12" s="29" t="inlineStr"/>
     </row>
     <row r="13" ht="18" customHeight="1">
       <c r="A13" s="26" t="inlineStr">
         <is>
-          <t>방산</t>
+          <t>이차전지</t>
         </is>
       </c>
       <c r="B13" s="25" t="n">
@@ -5241,7 +5245,7 @@
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="26" t="inlineStr">
         <is>
-          <t>수소</t>
+          <t>AI반도체</t>
         </is>
       </c>
       <c r="B14" s="25" t="n">
@@ -5268,7 +5272,7 @@
     <row r="15" ht="18" customHeight="1">
       <c r="A15" s="26" t="inlineStr">
         <is>
-          <t>태양광</t>
+          <t>수소</t>
         </is>
       </c>
       <c r="B15" s="25" t="n">
@@ -5295,7 +5299,7 @@
     <row r="16" ht="18" customHeight="1">
       <c r="A16" s="26" t="inlineStr">
         <is>
-          <t>게임</t>
+          <t>태양광</t>
         </is>
       </c>
       <c r="B16" s="25" t="n">
@@ -5322,7 +5326,7 @@
     <row r="17" ht="18" customHeight="1">
       <c r="A17" s="26" t="inlineStr">
         <is>
-          <t>엔터</t>
+          <t>게임</t>
         </is>
       </c>
       <c r="B17" s="25" t="n">
@@ -5349,7 +5353,7 @@
     <row r="18" ht="18" customHeight="1">
       <c r="A18" s="26" t="inlineStr">
         <is>
-          <t>핀테크</t>
+          <t>엔터</t>
         </is>
       </c>
       <c r="B18" s="25" t="n">
@@ -5376,7 +5380,7 @@
     <row r="19" ht="18" customHeight="1">
       <c r="A19" s="26" t="inlineStr">
         <is>
-          <t>클라우드</t>
+          <t>핀테크</t>
         </is>
       </c>
       <c r="B19" s="25" t="n">

--- a/trend/stock_trend_history.xlsx
+++ b/trend/stock_trend_history.xlsx
@@ -57,13 +57,13 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="00E53935"/>
+      <color rgb="002563EB"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="002563EB"/>
+      <color rgb="00E53935"/>
       <sz val="10"/>
     </font>
     <font>
@@ -258,13 +258,13 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -276,11 +276,11 @@
     <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -694,7 +694,7 @@
     <row r="1" ht="36" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>📊 주식 트렌드 조기 감지 대시보드   |   최종 업데이트: 2026-06-17 06:55</t>
+          <t>📊 주식 트렌드 조기 감지 대시보드   |   최종 업데이트: 2026-06-18 06:55</t>
         </is>
       </c>
     </row>
@@ -708,7 +708,7 @@
       </c>
       <c r="E3" s="3" t="n"/>
       <c r="G3" s="5" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="H3" s="3" t="n"/>
       <c r="J3" s="6" t="n">
@@ -787,21 +787,21 @@
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="11" t="inlineStr">
         <is>
-          <t>⚡ 최신(2026-06-17) 상위: 반도체  점수 54.0점</t>
+          <t>⚡ 최신(2026-06-18) 상위: 반도체  점수 57.0점</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1">
       <c r="A11" s="12" t="inlineStr">
         <is>
-          <t>⚡ 최신(2026-06-17) 상위: 삼성전자  점수 17.0점</t>
+          <t>⚡ 최신(2026-06-18) 상위: LG  점수 31.0점</t>
         </is>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1">
       <c r="A12" s="11" t="inlineStr">
         <is>
-          <t>⚡ 최신(2026-06-17) 상위: 인공지능  점수 17.0점</t>
+          <t>⚡ 최신(2026-06-18) 상위: 삼성전자  점수 28.0점</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B14" s="15" t="n">
@@ -928,10 +928,10 @@
         </is>
       </c>
       <c r="D14" s="15" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="E14" s="15" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="F14" s="15" t="n">
         <v>0</v>
@@ -947,7 +947,7 @@
       </c>
       <c r="J14" s="17" t="inlineStr">
         <is>
-          <t>네이버뉴스 기사 언급 / 한국경제 헤드라인 언급 / 한국경제 헤드라인 언급 / 매일경제 기사 언급 / 매일경제 기사 언급</t>
+          <t>매일경제 헤드라인 언급 / 네이버뉴스 헤드라인 언급 / 네이버뉴스 기사 언급 / 한국경제 헤드라인 언급 / 매일경제 기사 언급</t>
         </is>
       </c>
       <c r="K14" s="17" t="inlineStr">
@@ -959,7 +959,7 @@
     <row r="15" ht="18" customHeight="1">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B15" s="15" t="n">
@@ -967,14 +967,14 @@
       </c>
       <c r="C15" s="16" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>LG</t>
         </is>
       </c>
       <c r="D15" s="15" t="n">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="E15" s="15" t="n">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="F15" s="15" t="n">
         <v>0</v>
@@ -983,14 +983,14 @@
         <v>0</v>
       </c>
       <c r="H15" s="18" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="I15" s="18" t="n">
-        <v>6.52</v>
+        <v>-1.4</v>
+      </c>
+      <c r="I15" s="19" t="n">
+        <v>3.5</v>
       </c>
       <c r="J15" s="17" t="inlineStr">
         <is>
-          <t>매일경제 기사 언급 / 네이버뉴스 기사 언급 / 매일경제 기사 언급 / 매일경제 기사 언급 / 매일경제 기사 언급</t>
+          <t>매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 기사 언급 / 매일경제 헤드라인 언급 / 네이버뉴스 기사 언급</t>
         </is>
       </c>
       <c r="K15" s="17" t="inlineStr">
@@ -1002,7 +1002,7 @@
     <row r="16" ht="18" customHeight="1">
       <c r="A16" s="15" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B16" s="15" t="n">
@@ -1010,14 +1010,14 @@
       </c>
       <c r="C16" s="16" t="inlineStr">
         <is>
-          <t>인공지능</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="D16" s="15" t="n">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="E16" s="15" t="n">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="F16" s="15" t="n">
         <v>0</v>
@@ -1025,15 +1025,15 @@
       <c r="G16" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="H16" s="15" t="n">
-        <v/>
-      </c>
-      <c r="I16" s="15" t="n">
-        <v/>
+      <c r="H16" s="19" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="I16" s="19" t="n">
+        <v>14.55</v>
       </c>
       <c r="J16" s="17" t="inlineStr">
         <is>
-          <t>네이버뉴스 기사 언급 / 매일경제 기사 언급 / 네이버뉴스 기사 언급 / 매일경제 기사 언급 / 매일경제 기사 언급</t>
+          <t>네이버뉴스 기사 언급 / 네이버뉴스 헤드라인 언급 / 네이버뉴스 기사 언급 / 매일경제 기사 언급 / 매일경제 헤드라인 언급</t>
         </is>
       </c>
       <c r="K16" s="17" t="inlineStr">
@@ -1045,7 +1045,7 @@
     <row r="17" ht="18" customHeight="1">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B17" s="15" t="n">
@@ -1053,14 +1053,14 @@
       </c>
       <c r="C17" s="16" t="inlineStr">
         <is>
-          <t>방산</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="D17" s="15" t="n">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="E17" s="15" t="n">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="F17" s="15" t="n">
         <v>0</v>
@@ -1068,15 +1068,15 @@
       <c r="G17" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="H17" s="15" t="n">
-        <v/>
-      </c>
-      <c r="I17" s="15" t="n">
-        <v/>
+      <c r="H17" s="19" t="n">
+        <v>5.84</v>
+      </c>
+      <c r="I17" s="19" t="n">
+        <v>23.1</v>
       </c>
       <c r="J17" s="17" t="inlineStr">
         <is>
-          <t>한국경제 헤드라인 언급 / 네이버뉴스 기사 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
+          <t>매일경제 헤드라인 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 헤드라인 언급 / 매일경제 헤드라인 언급 / 네이버뉴스 기사 언급</t>
         </is>
       </c>
       <c r="K17" s="17" t="inlineStr">
@@ -1088,7 +1088,7 @@
     <row r="18" ht="18" customHeight="1">
       <c r="A18" s="15" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B18" s="15" t="n">
@@ -1096,14 +1096,14 @@
       </c>
       <c r="C18" s="16" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>원전</t>
         </is>
       </c>
       <c r="D18" s="15" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="E18" s="15" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="F18" s="15" t="n">
         <v>0</v>
@@ -1111,27 +1111,25 @@
       <c r="G18" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="H18" s="18" t="n">
-        <v>4.11</v>
-      </c>
-      <c r="I18" s="18" t="n">
-        <v>7.54</v>
+      <c r="H18" s="15" t="n">
+        <v/>
+      </c>
+      <c r="I18" s="15" t="n">
+        <v/>
       </c>
       <c r="J18" s="17" t="inlineStr">
         <is>
-          <t>한국경제 헤드라인 언급 / 매일경제 기사 언급 / 네이버뉴스 기사 언급 / 한국경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K18" s="17" t="inlineStr">
-        <is>
-          <t>네이버</t>
-        </is>
+          <t>한국경제 헤드라인 언급 / 매일경제 기사 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K18" s="17" t="n">
+        <v/>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
       <c r="A19" s="15" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B19" s="15" t="n">
@@ -1139,14 +1137,14 @@
       </c>
       <c r="C19" s="16" t="inlineStr">
         <is>
-          <t>로봇</t>
+          <t>미래에셋증권</t>
         </is>
       </c>
       <c r="D19" s="15" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E19" s="15" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F19" s="15" t="n">
         <v>0</v>
@@ -1154,25 +1152,27 @@
       <c r="G19" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="H19" s="15" t="n">
-        <v/>
-      </c>
-      <c r="I19" s="15" t="n">
-        <v/>
+      <c r="H19" s="18" t="n">
+        <v>-1.75</v>
+      </c>
+      <c r="I19" s="18" t="n">
+        <v>-1.56</v>
       </c>
       <c r="J19" s="17" t="inlineStr">
         <is>
-          <t>매일경제 기사 언급 / 매일경제 헤드라인 언급 / 한국경제 헤드라인 언급 / 한국경제 헤드라인 언급 / 매일경제 기사 언급</t>
-        </is>
-      </c>
-      <c r="K19" s="17" t="n">
-        <v/>
+          <t>중요공시 2건 / Google 급상승 검색어 등장 (KR) / 매일경제 기사 언급 / 한국경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K19" s="17" t="inlineStr">
+        <is>
+          <t>Google, 공시</t>
+        </is>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
       <c r="A20" s="15" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B20" s="15" t="n">
@@ -1184,10 +1184,10 @@
         </is>
       </c>
       <c r="D20" s="15" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E20" s="15" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="F20" s="15" t="n">
         <v>0</v>
@@ -1203,7 +1203,7 @@
       </c>
       <c r="J20" s="17" t="inlineStr">
         <is>
-          <t>네이버뉴스 헤드라인 언급 / 네이버뉴스 헤드라인 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 기사 언급</t>
+          <t>매일경제 헤드라인 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 기사 언급</t>
         </is>
       </c>
       <c r="K20" s="17" t="inlineStr">
@@ -1215,7 +1215,7 @@
     <row r="21" ht="18" customHeight="1">
       <c r="A21" s="15" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B21" s="15" t="n">
@@ -1223,14 +1223,14 @@
       </c>
       <c r="C21" s="16" t="inlineStr">
         <is>
-          <t>현대차</t>
+          <t>인공지능</t>
         </is>
       </c>
       <c r="D21" s="15" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E21" s="15" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F21" s="15" t="n">
         <v>0</v>
@@ -1238,15 +1238,15 @@
       <c r="G21" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="H21" s="19" t="n">
-        <v>-1.08</v>
-      </c>
-      <c r="I21" s="18" t="n">
-        <v>0.16</v>
+      <c r="H21" s="15" t="n">
+        <v/>
+      </c>
+      <c r="I21" s="15" t="n">
+        <v/>
       </c>
       <c r="J21" s="17" t="inlineStr">
         <is>
-          <t>한국경제 헤드라인 언급 / 매일경제 기사 언급 / 매일경제 기사 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급</t>
+          <t>매일경제 기사 언급 / 매일경제 기사 언급 / 매일경제 기사 언급 / 매일경제 기사 언급 / 매일경제 기사 언급</t>
         </is>
       </c>
       <c r="K21" s="17" t="n">
@@ -1256,7 +1256,7 @@
     <row r="22" ht="18" customHeight="1">
       <c r="A22" s="15" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B22" s="15" t="n">
@@ -1264,298 +1264,294 @@
       </c>
       <c r="C22" s="16" t="inlineStr">
         <is>
-          <t>카카오</t>
+          <t>SK스퀘어</t>
         </is>
       </c>
       <c r="D22" s="15" t="n">
+        <v>10</v>
+      </c>
+      <c r="E22" s="15" t="n">
+        <v>10</v>
+      </c>
+      <c r="F22" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" s="19" t="n">
+        <v>6.33</v>
+      </c>
+      <c r="I22" s="19" t="n">
+        <v>34.91</v>
+      </c>
+      <c r="J22" s="17" t="inlineStr">
+        <is>
+          <t>매일경제 헤드라인 언급 / 한국경제 헤드라인 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 기사 언급 / 매일경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K22" s="17" t="inlineStr">
+        <is>
+          <t>네이버</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="18" customHeight="1">
+      <c r="A23" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="B23" s="15" t="n">
+        <v>10</v>
+      </c>
+      <c r="C23" s="16" t="inlineStr">
+        <is>
+          <t>조선</t>
+        </is>
+      </c>
+      <c r="D23" s="15" t="n">
+        <v>10</v>
+      </c>
+      <c r="E23" s="15" t="n">
+        <v>10</v>
+      </c>
+      <c r="F23" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" s="15" t="n">
+        <v/>
+      </c>
+      <c r="I23" s="15" t="n">
+        <v/>
+      </c>
+      <c r="J23" s="17" t="inlineStr">
+        <is>
+          <t>네이버뉴스 기사 언급 / 한국경제 헤드라인 언급 / 한국경제 헤드라인 언급 / 매일경제 기사 언급 / 한국경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K23" s="17" t="inlineStr">
+        <is>
+          <t>네이버</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="18" customHeight="1">
+      <c r="A24" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="B24" s="15" t="n">
+        <v>11</v>
+      </c>
+      <c r="C24" s="16" t="inlineStr">
+        <is>
+          <t>한솔테크닉스</t>
+        </is>
+      </c>
+      <c r="D24" s="15" t="n">
+        <v>9</v>
+      </c>
+      <c r="E24" s="15" t="n">
+        <v>4</v>
+      </c>
+      <c r="F24" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="G24" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="H24" s="19" t="n">
+        <v>30</v>
+      </c>
+      <c r="I24" s="19" t="n">
+        <v>41.51</v>
+      </c>
+      <c r="J24" s="17" t="inlineStr">
+        <is>
+          <t>중요공시 3건 / 중요공시 3일 +200% / 중요공시 7일 +50% / 네이버뉴스 기사 언급</t>
+        </is>
+      </c>
+      <c r="K24" s="17" t="inlineStr">
+        <is>
+          <t>네이버, 공시</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="18" customHeight="1">
+      <c r="A25" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="B25" s="15" t="n">
+        <v>12</v>
+      </c>
+      <c r="C25" s="16" t="inlineStr">
+        <is>
+          <t>제약</t>
+        </is>
+      </c>
+      <c r="D25" s="15" t="n">
+        <v>8</v>
+      </c>
+      <c r="E25" s="15" t="n">
+        <v>8</v>
+      </c>
+      <c r="F25" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" s="15" t="n">
+        <v/>
+      </c>
+      <c r="I25" s="15" t="n">
+        <v/>
+      </c>
+      <c r="J25" s="17" t="inlineStr">
+        <is>
+          <t>네이버뉴스 기사 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K25" s="17" t="inlineStr">
+        <is>
+          <t>네이버</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="18" customHeight="1">
+      <c r="A26" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="B26" s="15" t="n">
+        <v>13</v>
+      </c>
+      <c r="C26" s="16" t="inlineStr">
+        <is>
+          <t>LG이노텍</t>
+        </is>
+      </c>
+      <c r="D26" s="15" t="n">
         <v>7</v>
       </c>
-      <c r="E22" s="15" t="n">
+      <c r="E26" s="15" t="n">
         <v>7</v>
       </c>
-      <c r="F22" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" s="19" t="n">
-        <v>-0.74</v>
-      </c>
-      <c r="I22" s="18" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="J22" s="17" t="inlineStr">
-        <is>
-          <t>한국경제 헤드라인 언급 / 매일경제 기사 언급 / 매일경제 헤드라인 언급 / 매일경제 기사 언급</t>
-        </is>
-      </c>
-      <c r="K22" s="17" t="n">
+      <c r="F26" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" s="19" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="I26" s="19" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="J26" s="17" t="inlineStr">
+        <is>
+          <t>매일경제 헤드라인 언급 / 매일경제 기사 언급 / 한국경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K26" s="17" t="n">
         <v/>
       </c>
     </row>
-    <row r="23" ht="18" customHeight="1">
-      <c r="A23" s="20" t="inlineStr">
-        <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="B23" s="20" t="n">
-        <v>10</v>
-      </c>
-      <c r="C23" s="21" t="inlineStr">
-        <is>
-          <t>모바일어플라이언스</t>
-        </is>
-      </c>
-      <c r="D23" s="20" t="n">
-        <v>6</v>
-      </c>
-      <c r="E23" s="20" t="n">
-        <v>3</v>
-      </c>
-      <c r="F23" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" s="20" t="n">
-        <v>3</v>
-      </c>
-      <c r="H23" s="22" t="n">
-        <v>-24.14</v>
-      </c>
-      <c r="I23" s="22" t="n">
-        <v>-7.04</v>
-      </c>
-      <c r="J23" s="23" t="inlineStr">
-        <is>
-          <t>중요공시 3건 / 중요공시 7일 +200%</t>
-        </is>
-      </c>
-      <c r="K23" s="23" t="inlineStr">
-        <is>
-          <t>공시</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="18" customHeight="1">
-      <c r="A24" s="20" t="inlineStr">
-        <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="B24" s="20" t="n">
-        <v>11</v>
-      </c>
-      <c r="C24" s="21" t="inlineStr">
-        <is>
-          <t>한화솔루션</t>
-        </is>
-      </c>
-      <c r="D24" s="20" t="n">
-        <v>6</v>
-      </c>
-      <c r="E24" s="20" t="n">
-        <v>6</v>
-      </c>
-      <c r="F24" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" s="24" t="n">
-        <v>9.039999999999999</v>
-      </c>
-      <c r="I24" s="24" t="n">
-        <v>25.85</v>
-      </c>
-      <c r="J24" s="23" t="inlineStr">
-        <is>
-          <t>중요공시 3건 / 한국경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K24" s="23" t="inlineStr">
-        <is>
-          <t>공시</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="18" customHeight="1">
-      <c r="A25" s="20" t="inlineStr">
-        <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="B25" s="20" t="n">
-        <v>12</v>
-      </c>
-      <c r="C25" s="21" t="inlineStr">
-        <is>
-          <t>동양</t>
-        </is>
-      </c>
-      <c r="D25" s="20" t="n">
-        <v>6</v>
-      </c>
-      <c r="E25" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="F25" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="G25" s="20" t="n">
-        <v>3</v>
-      </c>
-      <c r="H25" s="24" t="n">
-        <v>11.83</v>
-      </c>
-      <c r="I25" s="24" t="n">
-        <v>13.66</v>
-      </c>
-      <c r="J25" s="23" t="inlineStr">
-        <is>
-          <t>중요공시 2건 / 중요공시 3일 +100% / 중요공시 7일 +100%</t>
-        </is>
-      </c>
-      <c r="K25" s="23" t="inlineStr">
-        <is>
-          <t>공시</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="18" customHeight="1">
-      <c r="A26" s="20" t="inlineStr">
-        <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="B26" s="20" t="n">
-        <v>13</v>
-      </c>
-      <c r="C26" s="21" t="inlineStr">
-        <is>
-          <t>알엔티엑스</t>
-        </is>
-      </c>
-      <c r="D26" s="20" t="n">
-        <v>6</v>
-      </c>
-      <c r="E26" s="20" t="n">
-        <v>3</v>
-      </c>
-      <c r="F26" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G26" s="20" t="n">
-        <v>3</v>
-      </c>
-      <c r="H26" s="22" t="n">
-        <v>-1.61</v>
-      </c>
-      <c r="I26" s="22" t="n">
-        <v>-19.43</v>
-      </c>
-      <c r="J26" s="23" t="inlineStr">
-        <is>
-          <t>중요공시 5건 / 중요공시 7일 +67%</t>
-        </is>
-      </c>
-      <c r="K26" s="23" t="inlineStr">
-        <is>
-          <t>공시</t>
-        </is>
-      </c>
-    </row>
     <row r="27" ht="18" customHeight="1">
-      <c r="A27" s="20" t="inlineStr">
-        <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="B27" s="20" t="n">
+      <c r="A27" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="B27" s="15" t="n">
         <v>14</v>
       </c>
-      <c r="C27" s="21" t="inlineStr">
-        <is>
-          <t>두산에너빌리티</t>
-        </is>
-      </c>
-      <c r="D27" s="20" t="n">
-        <v>5</v>
-      </c>
-      <c r="E27" s="20" t="n">
-        <v>5</v>
-      </c>
-      <c r="F27" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G27" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H27" s="24" t="n">
-        <v>3.51</v>
-      </c>
-      <c r="I27" s="24" t="n">
-        <v>11.92</v>
-      </c>
-      <c r="J27" s="23" t="inlineStr">
-        <is>
-          <t>중요공시 1건 / 네이버뉴스 헤드라인 언급 / 매일경제 기사 언급</t>
-        </is>
-      </c>
-      <c r="K27" s="23" t="inlineStr">
-        <is>
-          <t>공시, 네이버</t>
-        </is>
+      <c r="C27" s="16" t="inlineStr">
+        <is>
+          <t>로봇</t>
+        </is>
+      </c>
+      <c r="D27" s="15" t="n">
+        <v>7</v>
+      </c>
+      <c r="E27" s="15" t="n">
+        <v>7</v>
+      </c>
+      <c r="F27" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" s="15" t="n">
+        <v/>
+      </c>
+      <c r="I27" s="15" t="n">
+        <v/>
+      </c>
+      <c r="J27" s="17" t="inlineStr">
+        <is>
+          <t>매일경제 기사 언급 / 매일경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K27" s="17" t="n">
+        <v/>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
-      <c r="A28" s="20" t="inlineStr">
-        <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="B28" s="20" t="n">
+      <c r="A28" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="B28" s="15" t="n">
         <v>15</v>
       </c>
-      <c r="C28" s="21" t="inlineStr">
-        <is>
-          <t>에코프로</t>
-        </is>
-      </c>
-      <c r="D28" s="20" t="n">
-        <v>5</v>
-      </c>
-      <c r="E28" s="20" t="n">
-        <v>5</v>
-      </c>
-      <c r="F28" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G28" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H28" s="22" t="n">
-        <v>-1.13</v>
-      </c>
-      <c r="I28" s="24" t="n">
-        <v>14.15</v>
-      </c>
-      <c r="J28" s="23" t="inlineStr">
-        <is>
-          <t>Google 급상승 검색어 등장 (KR)</t>
-        </is>
-      </c>
-      <c r="K28" s="23" t="inlineStr">
-        <is>
-          <t>Google</t>
-        </is>
+      <c r="C28" s="16" t="inlineStr">
+        <is>
+          <t>기아</t>
+        </is>
+      </c>
+      <c r="D28" s="15" t="n">
+        <v>7</v>
+      </c>
+      <c r="E28" s="15" t="n">
+        <v>7</v>
+      </c>
+      <c r="F28" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" s="18" t="n">
+        <v>-2.29</v>
+      </c>
+      <c r="I28" s="19" t="n">
+        <v>4.13</v>
+      </c>
+      <c r="J28" s="17" t="inlineStr">
+        <is>
+          <t>매일경제 기사 언급 / 한국경제 헤드라인 언급 / 한국경제 헤드라인 언급 / 매일경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K28" s="17" t="n">
+        <v/>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
       <c r="A29" s="20" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B29" s="20" t="n">
@@ -1563,42 +1559,42 @@
       </c>
       <c r="C29" s="21" t="inlineStr">
         <is>
-          <t>에코프로에이치엔</t>
+          <t>모바일어플라이언스</t>
         </is>
       </c>
       <c r="D29" s="20" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E29" s="20" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F29" s="20" t="n">
         <v>0</v>
       </c>
       <c r="G29" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H29" s="24" t="n">
-        <v>5.02</v>
-      </c>
-      <c r="I29" s="24" t="n">
-        <v>9.029999999999999</v>
+        <v>3</v>
+      </c>
+      <c r="H29" s="22" t="n">
+        <v>-6.28</v>
+      </c>
+      <c r="I29" s="22" t="n">
+        <v>-15.26</v>
       </c>
       <c r="J29" s="23" t="inlineStr">
         <is>
-          <t>Google 급상승 검색어 등장 (KR)</t>
+          <t>중요공시 3건 / 중요공시 7일 +200%</t>
         </is>
       </c>
       <c r="K29" s="23" t="inlineStr">
         <is>
-          <t>Google</t>
+          <t>공시</t>
         </is>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
       <c r="A30" s="20" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B30" s="20" t="n">
@@ -1606,42 +1602,42 @@
       </c>
       <c r="C30" s="21" t="inlineStr">
         <is>
-          <t>에코프로비엠</t>
+          <t>알엔티엑스</t>
         </is>
       </c>
       <c r="D30" s="20" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E30" s="20" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F30" s="20" t="n">
         <v>0</v>
       </c>
       <c r="G30" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H30" s="22" t="n">
-        <v>-3.75</v>
-      </c>
-      <c r="I30" s="24" t="n">
-        <v>7.1</v>
+        <v>3</v>
+      </c>
+      <c r="H30" s="24" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="I30" s="22" t="n">
+        <v>-10</v>
       </c>
       <c r="J30" s="23" t="inlineStr">
         <is>
-          <t>Google 급상승 검색어 등장 (KR)</t>
+          <t>중요공시 5건 / 중요공시 7일 +67%</t>
         </is>
       </c>
       <c r="K30" s="23" t="inlineStr">
         <is>
-          <t>Google</t>
+          <t>공시</t>
         </is>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
       <c r="A31" s="20" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B31" s="20" t="n">
@@ -1649,40 +1645,42 @@
       </c>
       <c r="C31" s="21" t="inlineStr">
         <is>
-          <t>태양광</t>
+          <t>한솔홀딩스</t>
         </is>
       </c>
       <c r="D31" s="20" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E31" s="20" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F31" s="20" t="n">
         <v>0</v>
       </c>
       <c r="G31" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H31" s="20" t="n">
-        <v/>
-      </c>
-      <c r="I31" s="20" t="n">
-        <v/>
+        <v>3</v>
+      </c>
+      <c r="H31" s="24" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="I31" s="24" t="n">
+        <v>6.46</v>
       </c>
       <c r="J31" s="23" t="inlineStr">
         <is>
-          <t>매일경제 헤드라인 언급 / 매일경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K31" s="23" t="n">
-        <v/>
+          <t>중요공시 3건 / 중요공시 7일 +200%</t>
+        </is>
+      </c>
+      <c r="K31" s="23" t="inlineStr">
+        <is>
+          <t>공시</t>
+        </is>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
       <c r="A32" s="20" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B32" s="20" t="n">
@@ -1690,14 +1688,14 @@
       </c>
       <c r="C32" s="21" t="inlineStr">
         <is>
-          <t>후성</t>
+          <t>게임</t>
         </is>
       </c>
       <c r="D32" s="20" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E32" s="20" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F32" s="20" t="n">
         <v>0</v>
@@ -1705,25 +1703,27 @@
       <c r="G32" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H32" s="22" t="n">
-        <v>-14.29</v>
-      </c>
-      <c r="I32" s="24" t="n">
-        <v>42.01</v>
+      <c r="H32" s="20" t="n">
+        <v/>
+      </c>
+      <c r="I32" s="20" t="n">
+        <v/>
       </c>
       <c r="J32" s="23" t="inlineStr">
         <is>
-          <t>매일경제 기사 언급 / 매일경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K32" s="23" t="n">
-        <v/>
+          <t>매일경제 헤드라인 언급 / 네이버뉴스 기사 언급 / 매일경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K32" s="23" t="inlineStr">
+        <is>
+          <t>네이버</t>
+        </is>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
       <c r="A33" s="20" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B33" s="20" t="n">
@@ -1731,14 +1731,14 @@
       </c>
       <c r="C33" s="21" t="inlineStr">
         <is>
-          <t>한국전력</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="D33" s="20" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E33" s="20" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F33" s="20" t="n">
         <v>0</v>
@@ -1746,15 +1746,15 @@
       <c r="G33" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H33" s="22" t="n">
-        <v>-3.86</v>
-      </c>
-      <c r="I33" s="24" t="n">
-        <v>10.25</v>
+      <c r="H33" s="20" t="n">
+        <v/>
+      </c>
+      <c r="I33" s="20" t="n">
+        <v/>
       </c>
       <c r="J33" s="23" t="inlineStr">
         <is>
-          <t>네이버뉴스 헤드라인 언급 / 매일경제 기사 언급</t>
+          <t>네이버뉴스 헤드라인 언급 / 한국경제 헤드라인 언급</t>
         </is>
       </c>
       <c r="K33" s="23" t="inlineStr">
@@ -1766,7 +1766,7 @@
     <row r="34" ht="18" customHeight="1">
       <c r="A34" s="20" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B34" s="20" t="n">
@@ -1774,14 +1774,14 @@
       </c>
       <c r="C34" s="21" t="inlineStr">
         <is>
-          <t>제너셈</t>
+          <t>하이브</t>
         </is>
       </c>
       <c r="D34" s="20" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E34" s="20" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F34" s="20" t="n">
         <v>0</v>
@@ -1790,26 +1790,24 @@
         <v>0</v>
       </c>
       <c r="H34" s="24" t="n">
-        <v>4.59</v>
+        <v>5.61</v>
       </c>
       <c r="I34" s="24" t="n">
-        <v>12.02</v>
+        <v>14.88</v>
       </c>
       <c r="J34" s="23" t="inlineStr">
         <is>
-          <t>중요공시 1건 / 한국경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K34" s="23" t="inlineStr">
-        <is>
-          <t>공시</t>
-        </is>
+          <t>매일경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K34" s="23" t="n">
+        <v/>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
       <c r="A35" s="20" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B35" s="20" t="n">
@@ -1817,14 +1815,14 @@
       </c>
       <c r="C35" s="21" t="inlineStr">
         <is>
-          <t>제약</t>
+          <t>철강</t>
         </is>
       </c>
       <c r="D35" s="20" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E35" s="20" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F35" s="20" t="n">
         <v>0</v>
@@ -1840,7 +1838,7 @@
       </c>
       <c r="J35" s="23" t="inlineStr">
         <is>
-          <t>네이버뉴스 기사 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 기사 언급</t>
+          <t>네이버뉴스 기사 언급 / 한국경제 헤드라인 언급 / 네이버뉴스 기사 언급 / 매일경제 기사 언급</t>
         </is>
       </c>
       <c r="K35" s="23" t="inlineStr">
@@ -1852,7 +1850,7 @@
     <row r="36" ht="18" customHeight="1">
       <c r="A36" s="20" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B36" s="20" t="n">
@@ -1860,14 +1858,14 @@
       </c>
       <c r="C36" s="21" t="inlineStr">
         <is>
-          <t>셀트리온</t>
+          <t>미래에셋벤처투자</t>
         </is>
       </c>
       <c r="D36" s="20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E36" s="20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F36" s="20" t="n">
         <v>0</v>
@@ -1876,26 +1874,26 @@
         <v>0</v>
       </c>
       <c r="H36" s="22" t="n">
-        <v>-0.29</v>
-      </c>
-      <c r="I36" s="24" t="n">
-        <v>2.65</v>
+        <v>-8.720000000000001</v>
+      </c>
+      <c r="I36" s="22" t="n">
+        <v>-31.05</v>
       </c>
       <c r="J36" s="23" t="inlineStr">
         <is>
-          <t>네이버뉴스 기사 언급 / 네이버뉴스 헤드라인 언급</t>
+          <t>Google 급상승 검색어 등장 (KR)</t>
         </is>
       </c>
       <c r="K36" s="23" t="inlineStr">
         <is>
-          <t>네이버</t>
+          <t>Google</t>
         </is>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
       <c r="A37" s="20" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B37" s="20" t="n">
@@ -1903,14 +1901,14 @@
       </c>
       <c r="C37" s="21" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>미래에셋생명</t>
         </is>
       </c>
       <c r="D37" s="20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E37" s="20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F37" s="20" t="n">
         <v>0</v>
@@ -1918,25 +1916,27 @@
       <c r="G37" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H37" s="24" t="n">
-        <v>4.76</v>
+      <c r="H37" s="22" t="n">
+        <v>-5.12</v>
       </c>
       <c r="I37" s="24" t="n">
-        <v>7.32</v>
+        <v>35.4</v>
       </c>
       <c r="J37" s="23" t="inlineStr">
         <is>
-          <t>매일경제 헤드라인 언급 / 매일경제 기사 언급</t>
-        </is>
-      </c>
-      <c r="K37" s="23" t="n">
-        <v/>
+          <t>Google 급상승 검색어 등장 (KR)</t>
+        </is>
+      </c>
+      <c r="K37" s="23" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
       <c r="A38" s="20" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B38" s="20" t="n">
@@ -1944,14 +1944,14 @@
       </c>
       <c r="C38" s="21" t="inlineStr">
         <is>
-          <t>철강</t>
+          <t>미래에셋증권2우B</t>
         </is>
       </c>
       <c r="D38" s="20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E38" s="20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F38" s="20" t="n">
         <v>0</v>
@@ -1959,27 +1959,27 @@
       <c r="G38" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H38" s="20" t="n">
-        <v/>
-      </c>
-      <c r="I38" s="20" t="n">
-        <v/>
+      <c r="H38" s="22" t="n">
+        <v>-2.58</v>
+      </c>
+      <c r="I38" s="22" t="n">
+        <v>-0.87</v>
       </c>
       <c r="J38" s="23" t="inlineStr">
         <is>
-          <t>네이버뉴스 기사 언급 / 네이버뉴스 헤드라인 언급</t>
+          <t>Google 급상승 검색어 등장 (KR)</t>
         </is>
       </c>
       <c r="K38" s="23" t="inlineStr">
         <is>
-          <t>네이버</t>
+          <t>Google</t>
         </is>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
       <c r="A39" s="20" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B39" s="20" t="n">
@@ -1987,419 +1987,425 @@
       </c>
       <c r="C39" s="21" t="inlineStr">
         <is>
-          <t>기아</t>
+          <t>방산</t>
         </is>
       </c>
       <c r="D39" s="20" t="n">
+        <v>5</v>
+      </c>
+      <c r="E39" s="20" t="n">
+        <v>5</v>
+      </c>
+      <c r="F39" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G39" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" s="20" t="n">
+        <v/>
+      </c>
+      <c r="I39" s="20" t="n">
+        <v/>
+      </c>
+      <c r="J39" s="23" t="inlineStr">
+        <is>
+          <t>네이버뉴스 기사 언급 / 한국경제 헤드라인 언급 / 네이버뉴스 기사 언급</t>
+        </is>
+      </c>
+      <c r="K39" s="23" t="inlineStr">
+        <is>
+          <t>네이버</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="18" customHeight="1">
+      <c r="A40" s="20" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="B40" s="20" t="n">
+        <v>27</v>
+      </c>
+      <c r="C40" s="21" t="inlineStr">
+        <is>
+          <t>LG전자</t>
+        </is>
+      </c>
+      <c r="D40" s="20" t="n">
+        <v>5</v>
+      </c>
+      <c r="E40" s="20" t="n">
+        <v>5</v>
+      </c>
+      <c r="F40" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G40" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" s="24" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="I40" s="24" t="n">
+        <v>4.69</v>
+      </c>
+      <c r="J40" s="23" t="inlineStr">
+        <is>
+          <t>네이버뉴스 기사 언급 / 매일경제 헤드라인 언급 / 매일경제 기사 언급</t>
+        </is>
+      </c>
+      <c r="K40" s="23" t="inlineStr">
+        <is>
+          <t>네이버</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="18" customHeight="1">
+      <c r="A41" s="20" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="B41" s="20" t="n">
+        <v>28</v>
+      </c>
+      <c r="C41" s="21" t="inlineStr">
+        <is>
+          <t>현대약품</t>
+        </is>
+      </c>
+      <c r="D41" s="20" t="n">
         <v>4</v>
       </c>
-      <c r="E39" s="20" t="n">
+      <c r="E41" s="20" t="n">
         <v>4</v>
       </c>
-      <c r="F39" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G39" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H39" s="24" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="I39" s="24" t="n">
-        <v>3.59</v>
-      </c>
-      <c r="J39" s="23" t="inlineStr">
-        <is>
-          <t>매일경제 헤드라인 언급 / 매일경제 기사 언급</t>
-        </is>
-      </c>
-      <c r="K39" s="23" t="n">
+      <c r="F41" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G41" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" s="24" t="n">
+        <v>6.71</v>
+      </c>
+      <c r="I41" s="24" t="n">
+        <v>45.08</v>
+      </c>
+      <c r="J41" s="23" t="inlineStr">
+        <is>
+          <t>네이버 검색 당일 +121% / 네이버뉴스 기사 언급</t>
+        </is>
+      </c>
+      <c r="K41" s="23" t="inlineStr">
+        <is>
+          <t>네이버</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="18" customHeight="1">
+      <c r="A42" s="20" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="B42" s="20" t="n">
+        <v>29</v>
+      </c>
+      <c r="C42" s="21" t="inlineStr">
+        <is>
+          <t>대우건설</t>
+        </is>
+      </c>
+      <c r="D42" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="E42" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="F42" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G42" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" s="22" t="n">
+        <v>-9.65</v>
+      </c>
+      <c r="I42" s="24" t="n">
+        <v>19.52</v>
+      </c>
+      <c r="J42" s="23" t="inlineStr">
+        <is>
+          <t>중요공시 1건 / 매일경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K42" s="23" t="inlineStr">
+        <is>
+          <t>공시</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="18" customHeight="1">
+      <c r="A43" s="20" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="B43" s="20" t="n">
+        <v>30</v>
+      </c>
+      <c r="C43" s="21" t="inlineStr">
+        <is>
+          <t>디앤디파마텍</t>
+        </is>
+      </c>
+      <c r="D43" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="E43" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="F43" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G43" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" s="24" t="n">
+        <v>18.01</v>
+      </c>
+      <c r="I43" s="24" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="J43" s="23" t="inlineStr">
+        <is>
+          <t>중요공시 1건 / 매일경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K43" s="23" t="inlineStr">
+        <is>
+          <t>공시</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="18" customHeight="1">
+      <c r="A44" s="20" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="B44" s="20" t="n">
+        <v>31</v>
+      </c>
+      <c r="C44" s="21" t="inlineStr">
+        <is>
+          <t>KBI메탈</t>
+        </is>
+      </c>
+      <c r="D44" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="E44" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="F44" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G44" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" s="24" t="n">
+        <v>16.42</v>
+      </c>
+      <c r="I44" s="24" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="J44" s="23" t="inlineStr">
+        <is>
+          <t>중요공시 1건 / 매일경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K44" s="23" t="inlineStr">
+        <is>
+          <t>공시</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="18" customHeight="1">
+      <c r="A45" s="20" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="B45" s="20" t="n">
+        <v>32</v>
+      </c>
+      <c r="C45" s="21" t="inlineStr">
+        <is>
+          <t>한미반도체</t>
+        </is>
+      </c>
+      <c r="D45" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="E45" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="F45" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G45" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" s="22" t="n">
+        <v>-2.74</v>
+      </c>
+      <c r="I45" s="24" t="n">
+        <v>18.33</v>
+      </c>
+      <c r="J45" s="23" t="inlineStr">
+        <is>
+          <t>중요공시 2건 / 한국경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K45" s="23" t="inlineStr">
+        <is>
+          <t>공시</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="18" customHeight="1">
+      <c r="A46" s="20" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="B46" s="20" t="n">
+        <v>33</v>
+      </c>
+      <c r="C46" s="21" t="inlineStr">
+        <is>
+          <t>가온전선</t>
+        </is>
+      </c>
+      <c r="D46" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="E46" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="F46" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G46" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" s="24" t="n">
+        <v>29.9</v>
+      </c>
+      <c r="I46" s="24" t="n">
+        <v>8.949999999999999</v>
+      </c>
+      <c r="J46" s="23" t="inlineStr">
+        <is>
+          <t>중요공시 2건 / 매일경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K46" s="23" t="inlineStr">
+        <is>
+          <t>공시</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="18" customHeight="1">
+      <c r="A47" s="20" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="B47" s="20" t="n">
+        <v>34</v>
+      </c>
+      <c r="C47" s="21" t="inlineStr">
+        <is>
+          <t>현대차</t>
+        </is>
+      </c>
+      <c r="D47" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="E47" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="F47" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G47" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H47" s="22" t="n">
+        <v>-3.44</v>
+      </c>
+      <c r="I47" s="24" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="J47" s="23" t="inlineStr">
+        <is>
+          <t>매일경제 기사 언급 / 매일경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K47" s="23" t="n">
         <v/>
       </c>
     </row>
-    <row r="40" ht="18" customHeight="1">
-      <c r="A40" s="25" t="inlineStr">
-        <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="B40" s="25" t="n">
-        <v>27</v>
-      </c>
-      <c r="C40" s="26" t="inlineStr">
-        <is>
-          <t>TS트릴리온</t>
-        </is>
-      </c>
-      <c r="D40" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="E40" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="F40" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="G40" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="H40" s="27" t="n">
-        <v>-8.710000000000001</v>
-      </c>
-      <c r="I40" s="28" t="n">
-        <v>23.57</v>
-      </c>
-      <c r="J40" s="29" t="inlineStr">
-        <is>
-          <t>네이버 검색 당일 +109%</t>
-        </is>
-      </c>
-      <c r="K40" s="29" t="inlineStr">
-        <is>
-          <t>네이버</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="18" customHeight="1">
-      <c r="A41" s="25" t="inlineStr">
-        <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="B41" s="25" t="n">
-        <v>28</v>
-      </c>
-      <c r="C41" s="26" t="inlineStr">
-        <is>
-          <t>GS건설</t>
-        </is>
-      </c>
-      <c r="D41" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="E41" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="F41" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="G41" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="H41" s="28" t="n">
-        <v>5.29</v>
-      </c>
-      <c r="I41" s="28" t="n">
-        <v>20.42</v>
-      </c>
-      <c r="J41" s="29" t="inlineStr">
-        <is>
-          <t>매일경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K41" s="29" t="n">
+    <row r="48" ht="18" customHeight="1">
+      <c r="A48" s="20" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="B48" s="20" t="n">
+        <v>35</v>
+      </c>
+      <c r="C48" s="21" t="inlineStr">
+        <is>
+          <t>삼성전기</t>
+        </is>
+      </c>
+      <c r="D48" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="E48" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="F48" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G48" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H48" s="22" t="n">
+        <v>-0.78</v>
+      </c>
+      <c r="I48" s="24" t="n">
+        <v>12.58</v>
+      </c>
+      <c r="J48" s="23" t="inlineStr">
+        <is>
+          <t>매일경제 기사 언급 / 매일경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K48" s="23" t="n">
         <v/>
-      </c>
-    </row>
-    <row r="42" ht="18" customHeight="1">
-      <c r="A42" s="25" t="inlineStr">
-        <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="B42" s="25" t="n">
-        <v>29</v>
-      </c>
-      <c r="C42" s="26" t="inlineStr">
-        <is>
-          <t>CSA 코스믹</t>
-        </is>
-      </c>
-      <c r="D42" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="E42" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="F42" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="G42" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="H42" s="27" t="n">
-        <v>-5.28</v>
-      </c>
-      <c r="I42" s="28" t="n">
-        <v>69.44</v>
-      </c>
-      <c r="J42" s="29" t="inlineStr">
-        <is>
-          <t>중요공시 3건</t>
-        </is>
-      </c>
-      <c r="K42" s="29" t="inlineStr">
-        <is>
-          <t>공시</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="18" customHeight="1">
-      <c r="A43" s="25" t="inlineStr">
-        <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="B43" s="25" t="n">
-        <v>30</v>
-      </c>
-      <c r="C43" s="26" t="inlineStr">
-        <is>
-          <t>SM C&amp;C</t>
-        </is>
-      </c>
-      <c r="D43" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="E43" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="F43" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="G43" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="H43" s="28" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="I43" s="28" t="n">
-        <v>39.65</v>
-      </c>
-      <c r="J43" s="29" t="inlineStr">
-        <is>
-          <t>매일경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K43" s="29" t="n">
-        <v/>
-      </c>
-    </row>
-    <row r="44" ht="18" customHeight="1">
-      <c r="A44" s="25" t="inlineStr">
-        <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="B44" s="25" t="n">
-        <v>31</v>
-      </c>
-      <c r="C44" s="26" t="inlineStr">
-        <is>
-          <t>기업은행</t>
-        </is>
-      </c>
-      <c r="D44" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="E44" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="F44" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="G44" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="H44" s="28" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="I44" s="28" t="n">
-        <v>12.41</v>
-      </c>
-      <c r="J44" s="29" t="inlineStr">
-        <is>
-          <t>한국경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K44" s="29" t="n">
-        <v/>
-      </c>
-    </row>
-    <row r="45" ht="18" customHeight="1">
-      <c r="A45" s="25" t="inlineStr">
-        <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="B45" s="25" t="n">
-        <v>32</v>
-      </c>
-      <c r="C45" s="26" t="inlineStr">
-        <is>
-          <t>씨에스윈드</t>
-        </is>
-      </c>
-      <c r="D45" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="E45" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="F45" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="G45" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="H45" s="28" t="n">
-        <v>29.83</v>
-      </c>
-      <c r="I45" s="28" t="n">
-        <v>40.77</v>
-      </c>
-      <c r="J45" s="29" t="inlineStr">
-        <is>
-          <t>매일경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K45" s="29" t="n">
-        <v/>
-      </c>
-    </row>
-    <row r="46" ht="18" customHeight="1">
-      <c r="A46" s="25" t="inlineStr">
-        <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="B46" s="25" t="n">
-        <v>33</v>
-      </c>
-      <c r="C46" s="26" t="inlineStr">
-        <is>
-          <t>피노</t>
-        </is>
-      </c>
-      <c r="D46" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="E46" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="F46" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="G46" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="H46" s="27" t="n">
-        <v>-5.66</v>
-      </c>
-      <c r="I46" s="27" t="n">
-        <v>-4.84</v>
-      </c>
-      <c r="J46" s="29" t="inlineStr">
-        <is>
-          <t>중요공시 4건</t>
-        </is>
-      </c>
-      <c r="K46" s="29" t="inlineStr">
-        <is>
-          <t>공시</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="18" customHeight="1">
-      <c r="A47" s="25" t="inlineStr">
-        <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="B47" s="25" t="n">
-        <v>34</v>
-      </c>
-      <c r="C47" s="26" t="inlineStr">
-        <is>
-          <t>스피어</t>
-        </is>
-      </c>
-      <c r="D47" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="E47" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="F47" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="G47" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="H47" s="27" t="n">
-        <v>-6.53</v>
-      </c>
-      <c r="I47" s="28" t="n">
-        <v>17.08</v>
-      </c>
-      <c r="J47" s="29" t="inlineStr">
-        <is>
-          <t>중요공시 3건</t>
-        </is>
-      </c>
-      <c r="K47" s="29" t="inlineStr">
-        <is>
-          <t>공시</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="18" customHeight="1">
-      <c r="A48" s="25" t="inlineStr">
-        <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="B48" s="25" t="n">
-        <v>35</v>
-      </c>
-      <c r="C48" s="26" t="inlineStr">
-        <is>
-          <t>한솔테크닉스</t>
-        </is>
-      </c>
-      <c r="D48" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="E48" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="F48" s="25" t="n">
-        <v>2</v>
-      </c>
-      <c r="G48" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="H48" s="27" t="n">
-        <v>-8.24</v>
-      </c>
-      <c r="I48" s="28" t="n">
-        <v>11.11</v>
-      </c>
-      <c r="J48" s="29" t="inlineStr">
-        <is>
-          <t>중요공시 2건 / 중요공시 3일 +100%</t>
-        </is>
-      </c>
-      <c r="K48" s="29" t="inlineStr">
-        <is>
-          <t>공시</t>
-        </is>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1">
       <c r="A49" s="25" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B49" s="25" t="n">
@@ -2407,42 +2413,42 @@
       </c>
       <c r="C49" s="26" t="inlineStr">
         <is>
-          <t>파두</t>
+          <t>JW신약</t>
         </is>
       </c>
       <c r="D49" s="25" t="n">
         <v>3</v>
       </c>
       <c r="E49" s="25" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F49" s="25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G49" s="25" t="n">
         <v>0</v>
       </c>
       <c r="H49" s="27" t="n">
-        <v>-2.04</v>
+        <v>29.87</v>
       </c>
       <c r="I49" s="27" t="n">
-        <v>-2.23</v>
-      </c>
-      <c r="J49" s="29" t="inlineStr">
-        <is>
-          <t>중요공시 2건 / 중요공시 3일 +100%</t>
-        </is>
-      </c>
-      <c r="K49" s="29" t="inlineStr">
-        <is>
-          <t>공시</t>
+        <v>77.56999999999999</v>
+      </c>
+      <c r="J49" s="28" t="inlineStr">
+        <is>
+          <t>네이버 검색 당일 +306%</t>
+        </is>
+      </c>
+      <c r="K49" s="28" t="inlineStr">
+        <is>
+          <t>네이버</t>
         </is>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
       <c r="A50" s="25" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B50" s="25" t="n">
@@ -2450,42 +2456,42 @@
       </c>
       <c r="C50" s="26" t="inlineStr">
         <is>
-          <t>삼보산업</t>
+          <t>TS트릴리온</t>
         </is>
       </c>
       <c r="D50" s="25" t="n">
         <v>3</v>
       </c>
       <c r="E50" s="25" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F50" s="25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G50" s="25" t="n">
         <v>0</v>
       </c>
       <c r="H50" s="27" t="n">
-        <v>-2.34</v>
-      </c>
-      <c r="I50" s="28" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="J50" s="29" t="inlineStr">
-        <is>
-          <t>중요공시 2건 / 중요공시 3일 +100%</t>
-        </is>
-      </c>
-      <c r="K50" s="29" t="inlineStr">
-        <is>
-          <t>공시</t>
+        <v>6.9</v>
+      </c>
+      <c r="I50" s="27" t="n">
+        <v>33.45</v>
+      </c>
+      <c r="J50" s="28" t="inlineStr">
+        <is>
+          <t>네이버 검색 당일 +286%</t>
+        </is>
+      </c>
+      <c r="K50" s="28" t="inlineStr">
+        <is>
+          <t>네이버</t>
         </is>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
       <c r="A51" s="25" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B51" s="25" t="n">
@@ -2493,7 +2499,7 @@
       </c>
       <c r="C51" s="26" t="inlineStr">
         <is>
-          <t>대신증권</t>
+          <t>삼익제약</t>
         </is>
       </c>
       <c r="D51" s="25" t="n">
@@ -2508,25 +2514,27 @@
       <c r="G51" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H51" s="28" t="n">
-        <v>4.87</v>
-      </c>
-      <c r="I51" s="28" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="J51" s="29" t="inlineStr">
-        <is>
-          <t>매일경제 기사 언급 / 매일경제 기사 언급 / 매일경제 기사 언급</t>
-        </is>
-      </c>
-      <c r="K51" s="29" t="n">
-        <v/>
+      <c r="H51" s="27" t="n">
+        <v>6.02</v>
+      </c>
+      <c r="I51" s="27" t="n">
+        <v>21.38</v>
+      </c>
+      <c r="J51" s="28" t="inlineStr">
+        <is>
+          <t>네이버 검색 당일 +208%</t>
+        </is>
+      </c>
+      <c r="K51" s="28" t="inlineStr">
+        <is>
+          <t>네이버</t>
+        </is>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1">
       <c r="A52" s="25" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B52" s="25" t="n">
@@ -2534,7 +2542,7 @@
       </c>
       <c r="C52" s="26" t="inlineStr">
         <is>
-          <t>저스템</t>
+          <t>한국전력</t>
         </is>
       </c>
       <c r="D52" s="25" t="n">
@@ -2550,24 +2558,24 @@
         <v>0</v>
       </c>
       <c r="H52" s="27" t="n">
-        <v>-5.89</v>
-      </c>
-      <c r="I52" s="28" t="n">
-        <v>7.24</v>
-      </c>
-      <c r="J52" s="29" t="inlineStr">
-        <is>
-          <t>매일경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K52" s="29" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="I52" s="27" t="n">
+        <v>11.26</v>
+      </c>
+      <c r="J52" s="28" t="inlineStr">
+        <is>
+          <t>한국경제 헤드라인 언급 / 매일경제 기사 언급</t>
+        </is>
+      </c>
+      <c r="K52" s="28" t="n">
         <v/>
       </c>
     </row>
     <row r="53" ht="18" customHeight="1">
       <c r="A53" s="25" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B53" s="25" t="n">
@@ -2575,7 +2583,7 @@
       </c>
       <c r="C53" s="26" t="inlineStr">
         <is>
-          <t>삼성전기</t>
+          <t>후성</t>
         </is>
       </c>
       <c r="D53" s="25" t="n">
@@ -2590,25 +2598,25 @@
       <c r="G53" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H53" s="28" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="I53" s="28" t="n">
-        <v>3.96</v>
-      </c>
-      <c r="J53" s="29" t="inlineStr">
-        <is>
-          <t>매일경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K53" s="29" t="n">
+      <c r="H53" s="29" t="n">
+        <v>-8.44</v>
+      </c>
+      <c r="I53" s="27" t="n">
+        <v>8.25</v>
+      </c>
+      <c r="J53" s="28" t="inlineStr">
+        <is>
+          <t>한국경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K53" s="28" t="n">
         <v/>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
       <c r="A54" s="25" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B54" s="25" t="n">
@@ -2616,7 +2624,7 @@
       </c>
       <c r="C54" s="26" t="inlineStr">
         <is>
-          <t>신원</t>
+          <t>한화솔루션</t>
         </is>
       </c>
       <c r="D54" s="25" t="n">
@@ -2631,25 +2639,27 @@
       <c r="G54" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H54" s="27" t="n">
-        <v>-0.52</v>
-      </c>
-      <c r="I54" s="28" t="n">
-        <v>8.77</v>
-      </c>
-      <c r="J54" s="29" t="inlineStr">
-        <is>
-          <t>매일경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K54" s="29" t="n">
-        <v/>
+      <c r="H54" s="29" t="n">
+        <v>-2.13</v>
+      </c>
+      <c r="I54" s="27" t="n">
+        <v>19.63</v>
+      </c>
+      <c r="J54" s="28" t="inlineStr">
+        <is>
+          <t>중요공시 3건</t>
+        </is>
+      </c>
+      <c r="K54" s="28" t="inlineStr">
+        <is>
+          <t>공시</t>
+        </is>
       </c>
     </row>
     <row r="55" ht="18" customHeight="1">
       <c r="A55" s="25" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B55" s="25" t="n">
@@ -2657,7 +2667,7 @@
       </c>
       <c r="C55" s="26" t="inlineStr">
         <is>
-          <t>네패스</t>
+          <t>LB세미콘</t>
         </is>
       </c>
       <c r="D55" s="25" t="n">
@@ -2672,25 +2682,27 @@
       <c r="G55" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H55" s="28" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="I55" s="28" t="n">
-        <v>17.14</v>
-      </c>
-      <c r="J55" s="29" t="inlineStr">
-        <is>
-          <t>매일경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K55" s="29" t="n">
-        <v/>
+      <c r="H55" s="27" t="n">
+        <v>4.72</v>
+      </c>
+      <c r="I55" s="27" t="n">
+        <v>29.37</v>
+      </c>
+      <c r="J55" s="28" t="inlineStr">
+        <is>
+          <t>중요공시 3건</t>
+        </is>
+      </c>
+      <c r="K55" s="28" t="inlineStr">
+        <is>
+          <t>공시</t>
+        </is>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1">
       <c r="A56" s="25" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B56" s="25" t="n">
@@ -2698,7 +2710,7 @@
       </c>
       <c r="C56" s="26" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>피노</t>
         </is>
       </c>
       <c r="D56" s="25" t="n">
@@ -2713,27 +2725,27 @@
       <c r="G56" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H56" s="25" t="n">
-        <v/>
-      </c>
-      <c r="I56" s="25" t="n">
-        <v/>
-      </c>
-      <c r="J56" s="29" t="inlineStr">
-        <is>
-          <t>네이버뉴스 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K56" s="29" t="inlineStr">
-        <is>
-          <t>네이버</t>
+      <c r="H56" s="27" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="I56" s="29" t="n">
+        <v>-3.06</v>
+      </c>
+      <c r="J56" s="28" t="inlineStr">
+        <is>
+          <t>중요공시 3건</t>
+        </is>
+      </c>
+      <c r="K56" s="28" t="inlineStr">
+        <is>
+          <t>공시</t>
         </is>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1">
       <c r="A57" s="25" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B57" s="25" t="n">
@@ -2741,7 +2753,7 @@
       </c>
       <c r="C57" s="26" t="inlineStr">
         <is>
-          <t>LIG디펜스앤에어로스페이스</t>
+          <t>모아데이타</t>
         </is>
       </c>
       <c r="D57" s="25" t="n">
@@ -2756,25 +2768,27 @@
       <c r="G57" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H57" s="28" t="n">
-        <v>18.58</v>
-      </c>
-      <c r="I57" s="28" t="n">
-        <v>38.21</v>
-      </c>
-      <c r="J57" s="29" t="inlineStr">
-        <is>
-          <t>매일경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K57" s="29" t="n">
-        <v/>
+      <c r="H57" s="27" t="n">
+        <v>5.14</v>
+      </c>
+      <c r="I57" s="27" t="n">
+        <v>5.59</v>
+      </c>
+      <c r="J57" s="28" t="inlineStr">
+        <is>
+          <t>중요공시 3건</t>
+        </is>
+      </c>
+      <c r="K57" s="28" t="inlineStr">
+        <is>
+          <t>공시</t>
+        </is>
       </c>
     </row>
     <row r="58" ht="18" customHeight="1">
       <c r="A58" s="25" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B58" s="25" t="n">
@@ -2782,40 +2796,42 @@
       </c>
       <c r="C58" s="26" t="inlineStr">
         <is>
-          <t>전기차</t>
+          <t>엑셈</t>
         </is>
       </c>
       <c r="D58" s="25" t="n">
         <v>3</v>
       </c>
       <c r="E58" s="25" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F58" s="25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G58" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H58" s="25" t="n">
-        <v/>
-      </c>
-      <c r="I58" s="25" t="n">
-        <v/>
-      </c>
-      <c r="J58" s="29" t="inlineStr">
-        <is>
-          <t>매일경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K58" s="29" t="n">
-        <v/>
+      <c r="H58" s="27" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="I58" s="29" t="n">
+        <v>-9.25</v>
+      </c>
+      <c r="J58" s="28" t="inlineStr">
+        <is>
+          <t>중요공시 2건 / 중요공시 3일 +100%</t>
+        </is>
+      </c>
+      <c r="K58" s="28" t="inlineStr">
+        <is>
+          <t>공시</t>
+        </is>
       </c>
     </row>
     <row r="59" ht="18" customHeight="1">
       <c r="A59" s="25" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B59" s="25" t="n">
@@ -2823,40 +2839,42 @@
       </c>
       <c r="C59" s="26" t="inlineStr">
         <is>
-          <t>현대모비스</t>
+          <t>파두</t>
         </is>
       </c>
       <c r="D59" s="25" t="n">
         <v>3</v>
       </c>
       <c r="E59" s="25" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F59" s="25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G59" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H59" s="28" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="I59" s="28" t="n">
-        <v>10.92</v>
-      </c>
-      <c r="J59" s="29" t="inlineStr">
-        <is>
-          <t>한국경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K59" s="29" t="n">
-        <v/>
+      <c r="H59" s="27" t="n">
+        <v>5.05</v>
+      </c>
+      <c r="I59" s="27" t="n">
+        <v>6.43</v>
+      </c>
+      <c r="J59" s="28" t="inlineStr">
+        <is>
+          <t>중요공시 2건 / 중요공시 3일 +100%</t>
+        </is>
+      </c>
+      <c r="K59" s="28" t="inlineStr">
+        <is>
+          <t>공시</t>
+        </is>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1">
       <c r="A60" s="25" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B60" s="25" t="n">
@@ -2864,40 +2882,42 @@
       </c>
       <c r="C60" s="26" t="inlineStr">
         <is>
-          <t>테스</t>
+          <t>삼보산업</t>
         </is>
       </c>
       <c r="D60" s="25" t="n">
         <v>3</v>
       </c>
       <c r="E60" s="25" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F60" s="25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G60" s="25" t="n">
         <v>0</v>
       </c>
       <c r="H60" s="27" t="n">
-        <v>-4.41</v>
-      </c>
-      <c r="I60" s="28" t="n">
-        <v>4.83</v>
-      </c>
-      <c r="J60" s="29" t="inlineStr">
-        <is>
-          <t>매일경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K60" s="29" t="n">
-        <v/>
+        <v>10.7</v>
+      </c>
+      <c r="I60" s="29" t="n">
+        <v>-3.23</v>
+      </c>
+      <c r="J60" s="28" t="inlineStr">
+        <is>
+          <t>중요공시 2건 / 중요공시 3일 +100%</t>
+        </is>
+      </c>
+      <c r="K60" s="28" t="inlineStr">
+        <is>
+          <t>공시</t>
+        </is>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
       <c r="A61" s="25" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B61" s="25" t="n">
@@ -2905,42 +2925,42 @@
       </c>
       <c r="C61" s="26" t="inlineStr">
         <is>
-          <t>JW신약</t>
+          <t>페니트리움바이오</t>
         </is>
       </c>
       <c r="D61" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="E61" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="F61" s="25" t="n">
         <v>2</v>
       </c>
-      <c r="E61" s="25" t="n">
-        <v>2</v>
-      </c>
-      <c r="F61" s="25" t="n">
-        <v>0</v>
-      </c>
       <c r="G61" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H61" s="28" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="I61" s="28" t="n">
-        <v>33.88</v>
-      </c>
-      <c r="J61" s="29" t="inlineStr">
-        <is>
-          <t>네이버 검색 당일 +63%</t>
-        </is>
-      </c>
-      <c r="K61" s="29" t="inlineStr">
-        <is>
-          <t>네이버</t>
+      <c r="H61" s="29" t="n">
+        <v>-0.45</v>
+      </c>
+      <c r="I61" s="27" t="n">
+        <v>6.06</v>
+      </c>
+      <c r="J61" s="28" t="inlineStr">
+        <is>
+          <t>중요공시 2건 / 중요공시 3일 +100%</t>
+        </is>
+      </c>
+      <c r="K61" s="28" t="inlineStr">
+        <is>
+          <t>공시</t>
         </is>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1">
       <c r="A62" s="25" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B62" s="25" t="n">
@@ -2948,14 +2968,14 @@
       </c>
       <c r="C62" s="26" t="inlineStr">
         <is>
-          <t>미래에셋증권</t>
+          <t>젬백스</t>
         </is>
       </c>
       <c r="D62" s="25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E62" s="25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F62" s="25" t="n">
         <v>0</v>
@@ -2964,26 +2984,26 @@
         <v>0</v>
       </c>
       <c r="H62" s="27" t="n">
-        <v>-0.58</v>
+        <v>4.38</v>
       </c>
       <c r="I62" s="27" t="n">
-        <v>-0.39</v>
-      </c>
-      <c r="J62" s="29" t="inlineStr">
-        <is>
-          <t>네이버뉴스 기사 언급 / 매일경제 기사 언급</t>
-        </is>
-      </c>
-      <c r="K62" s="29" t="inlineStr">
-        <is>
-          <t>네이버</t>
+        <v>10.08</v>
+      </c>
+      <c r="J62" s="28" t="inlineStr">
+        <is>
+          <t>중요공시 1건 / 한국경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K62" s="28" t="inlineStr">
+        <is>
+          <t>공시</t>
         </is>
       </c>
     </row>
     <row r="63" ht="18" customHeight="1">
       <c r="A63" s="25" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B63" s="25" t="n">
@@ -2991,14 +3011,14 @@
       </c>
       <c r="C63" s="26" t="inlineStr">
         <is>
-          <t>한화오션</t>
+          <t>올릭스</t>
         </is>
       </c>
       <c r="D63" s="25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E63" s="25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F63" s="25" t="n">
         <v>0</v>
@@ -3006,20 +3026,20 @@
       <c r="G63" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H63" s="28" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="I63" s="28" t="n">
-        <v>26.42</v>
-      </c>
-      <c r="J63" s="29" t="inlineStr">
-        <is>
-          <t>중요공시 1건 / 매일경제 기사 언급</t>
-        </is>
-      </c>
-      <c r="K63" s="29" t="inlineStr">
-        <is>
-          <t>공시</t>
+      <c r="H63" s="27" t="n">
+        <v>9.82</v>
+      </c>
+      <c r="I63" s="27" t="n">
+        <v>15.26</v>
+      </c>
+      <c r="J63" s="28" t="inlineStr">
+        <is>
+          <t>네이버뉴스 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K63" s="28" t="inlineStr">
+        <is>
+          <t>네이버</t>
         </is>
       </c>
     </row>
@@ -3116,22 +3136,22 @@
         <v>1</v>
       </c>
       <c r="C3" s="25" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="D3" s="25" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="E3" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F3" s="25" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G3" s="25" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="H3" s="25" t="n"/>
@@ -3140,165 +3160,173 @@
     <row r="4" ht="18" customHeight="1">
       <c r="A4" s="26" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>LG</t>
         </is>
       </c>
       <c r="B4" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C4" s="25" t="n">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="D4" s="25" t="n">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="E4" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F4" s="25" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G4" s="25" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="H4" s="28" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="I4" s="28" t="n">
-        <v>6.52</v>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="H4" s="29" t="n">
+        <v>-1.4</v>
+      </c>
+      <c r="I4" s="27" t="n">
+        <v>3.5</v>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="26" t="inlineStr">
         <is>
-          <t>인공지능</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B5" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C5" s="25" t="n">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="D5" s="25" t="n">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="E5" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F5" s="25" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G5" s="25" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="H5" s="25" t="n"/>
-      <c r="I5" s="25" t="n"/>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="H5" s="27" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="I5" s="27" t="n">
+        <v>14.55</v>
+      </c>
     </row>
     <row r="6" ht="18" customHeight="1">
       <c r="A6" s="26" t="inlineStr">
         <is>
-          <t>방산</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B6" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C6" s="25" t="n">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="D6" s="25" t="n">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="E6" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F6" s="25" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G6" s="25" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="H6" s="25" t="n"/>
-      <c r="I6" s="25" t="n"/>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="H6" s="27" t="n">
+        <v>5.84</v>
+      </c>
+      <c r="I6" s="27" t="n">
+        <v>23.1</v>
+      </c>
     </row>
     <row r="7" ht="18" customHeight="1">
       <c r="A7" s="26" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>원전</t>
         </is>
       </c>
       <c r="B7" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C7" s="25" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="D7" s="25" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="E7" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F7" s="25" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G7" s="25" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="H7" s="28" t="n">
-        <v>4.11</v>
-      </c>
-      <c r="I7" s="28" t="n">
-        <v>7.54</v>
-      </c>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="H7" s="25" t="n"/>
+      <c r="I7" s="25" t="n"/>
     </row>
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="26" t="inlineStr">
         <is>
-          <t>로봇</t>
+          <t>미래에셋증권</t>
         </is>
       </c>
       <c r="B8" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C8" s="25" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D8" s="25" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E8" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F8" s="25" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G8" s="25" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="H8" s="25" t="n"/>
-      <c r="I8" s="25" t="n"/>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="H8" s="29" t="n">
+        <v>-1.75</v>
+      </c>
+      <c r="I8" s="29" t="n">
+        <v>-1.56</v>
+      </c>
     </row>
     <row r="9" ht="18" customHeight="1">
       <c r="A9" s="26" t="inlineStr">
@@ -3310,22 +3338,22 @@
         <v>1</v>
       </c>
       <c r="C9" s="25" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D9" s="25" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E9" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F9" s="25" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G9" s="25" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="H9" s="25" t="n"/>
@@ -3334,682 +3362,666 @@
     <row r="10" ht="18" customHeight="1">
       <c r="A10" s="26" t="inlineStr">
         <is>
-          <t>현대차</t>
+          <t>인공지능</t>
         </is>
       </c>
       <c r="B10" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C10" s="25" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D10" s="25" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E10" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F10" s="25" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G10" s="25" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="H10" s="27" t="n">
-        <v>-1.08</v>
-      </c>
-      <c r="I10" s="28" t="n">
-        <v>0.16</v>
-      </c>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="H10" s="25" t="n"/>
+      <c r="I10" s="25" t="n"/>
     </row>
     <row r="11" ht="18" customHeight="1">
       <c r="A11" s="26" t="inlineStr">
         <is>
-          <t>카카오</t>
+          <t>SK스퀘어</t>
         </is>
       </c>
       <c r="B11" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C11" s="25" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D11" s="25" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E11" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F11" s="25" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G11" s="25" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="H11" s="27" t="n">
-        <v>-0.74</v>
-      </c>
-      <c r="I11" s="28" t="n">
-        <v>2.41</v>
+        <v>6.33</v>
+      </c>
+      <c r="I11" s="27" t="n">
+        <v>34.91</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
       <c r="A12" s="26" t="inlineStr">
         <is>
-          <t>동양</t>
+          <t>조선</t>
         </is>
       </c>
       <c r="B12" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C12" s="25" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D12" s="25" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E12" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F12" s="25" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G12" s="25" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="H12" s="28" t="n">
-        <v>11.83</v>
-      </c>
-      <c r="I12" s="28" t="n">
-        <v>13.66</v>
-      </c>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="H12" s="25" t="n"/>
+      <c r="I12" s="25" t="n"/>
     </row>
     <row r="13" ht="18" customHeight="1">
       <c r="A13" s="26" t="inlineStr">
         <is>
-          <t>모바일어플라이언스</t>
+          <t>한솔테크닉스</t>
         </is>
       </c>
       <c r="B13" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C13" s="25" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D13" s="25" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E13" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F13" s="25" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G13" s="25" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="H13" s="27" t="n">
-        <v>-24.14</v>
+        <v>30</v>
       </c>
       <c r="I13" s="27" t="n">
-        <v>-7.04</v>
+        <v>41.51</v>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="26" t="inlineStr">
         <is>
-          <t>알엔티엑스</t>
+          <t>제약</t>
         </is>
       </c>
       <c r="B14" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C14" s="25" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D14" s="25" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E14" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F14" s="25" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G14" s="25" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="H14" s="27" t="n">
-        <v>-1.61</v>
-      </c>
-      <c r="I14" s="27" t="n">
-        <v>-19.43</v>
-      </c>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="H14" s="25" t="n"/>
+      <c r="I14" s="25" t="n"/>
     </row>
     <row r="15" ht="18" customHeight="1">
       <c r="A15" s="26" t="inlineStr">
         <is>
-          <t>한화솔루션</t>
+          <t>LG이노텍</t>
         </is>
       </c>
       <c r="B15" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C15" s="25" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D15" s="25" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E15" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F15" s="25" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G15" s="25" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="H15" s="28" t="n">
-        <v>9.039999999999999</v>
-      </c>
-      <c r="I15" s="28" t="n">
-        <v>25.85</v>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="H15" s="27" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="I15" s="27" t="n">
+        <v>14.5</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
       <c r="A16" s="26" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>기아</t>
         </is>
       </c>
       <c r="B16" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C16" s="25" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D16" s="25" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E16" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F16" s="25" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G16" s="25" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="H16" s="28" t="n">
-        <v>3.51</v>
-      </c>
-      <c r="I16" s="28" t="n">
-        <v>11.92</v>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="H16" s="29" t="n">
+        <v>-2.29</v>
+      </c>
+      <c r="I16" s="27" t="n">
+        <v>4.13</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
       <c r="A17" s="26" t="inlineStr">
         <is>
-          <t>에코프로</t>
+          <t>로봇</t>
         </is>
       </c>
       <c r="B17" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C17" s="25" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D17" s="25" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E17" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F17" s="25" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G17" s="25" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="H17" s="27" t="n">
-        <v>-1.13</v>
-      </c>
-      <c r="I17" s="28" t="n">
-        <v>14.15</v>
-      </c>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="H17" s="25" t="n"/>
+      <c r="I17" s="25" t="n"/>
     </row>
     <row r="18" ht="18" customHeight="1">
       <c r="A18" s="26" t="inlineStr">
         <is>
-          <t>에코프로비엠</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="B18" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C18" s="25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D18" s="25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E18" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F18" s="25" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G18" s="25" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="H18" s="27" t="n">
-        <v>-3.75</v>
-      </c>
-      <c r="I18" s="28" t="n">
-        <v>7.1</v>
-      </c>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="H18" s="25" t="n"/>
+      <c r="I18" s="25" t="n"/>
     </row>
     <row r="19" ht="18" customHeight="1">
       <c r="A19" s="26" t="inlineStr">
         <is>
-          <t>에코프로에이치엔</t>
+          <t>게임</t>
         </is>
       </c>
       <c r="B19" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C19" s="25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D19" s="25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E19" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F19" s="25" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G19" s="25" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="H19" s="28" t="n">
-        <v>5.02</v>
-      </c>
-      <c r="I19" s="28" t="n">
-        <v>9.029999999999999</v>
-      </c>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="H19" s="25" t="n"/>
+      <c r="I19" s="25" t="n"/>
     </row>
     <row r="20" ht="18" customHeight="1">
       <c r="A20" s="26" t="inlineStr">
         <is>
-          <t>태양광</t>
+          <t>모바일어플라이언스</t>
         </is>
       </c>
       <c r="B20" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C20" s="25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D20" s="25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E20" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F20" s="25" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G20" s="25" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="H20" s="25" t="n"/>
-      <c r="I20" s="25" t="n"/>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="H20" s="29" t="n">
+        <v>-6.28</v>
+      </c>
+      <c r="I20" s="29" t="n">
+        <v>-15.26</v>
+      </c>
     </row>
     <row r="21" ht="18" customHeight="1">
       <c r="A21" s="26" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>알엔티엑스</t>
         </is>
       </c>
       <c r="B21" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C21" s="25" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D21" s="25" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E21" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F21" s="25" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G21" s="25" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="H21" s="28" t="n">
-        <v>4.76</v>
-      </c>
-      <c r="I21" s="28" t="n">
-        <v>7.32</v>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="H21" s="27" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="I21" s="29" t="n">
+        <v>-10</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
       <c r="A22" s="26" t="inlineStr">
         <is>
-          <t>기아</t>
+          <t>철강</t>
         </is>
       </c>
       <c r="B22" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C22" s="25" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D22" s="25" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E22" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F22" s="25" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G22" s="25" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="H22" s="28" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="I22" s="28" t="n">
-        <v>3.59</v>
-      </c>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="H22" s="25" t="n"/>
+      <c r="I22" s="25" t="n"/>
     </row>
     <row r="23" ht="18" customHeight="1">
       <c r="A23" s="26" t="inlineStr">
         <is>
-          <t>셀트리온</t>
+          <t>하이브</t>
         </is>
       </c>
       <c r="B23" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C23" s="25" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D23" s="25" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E23" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F23" s="25" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G23" s="25" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="H23" s="27" t="n">
-        <v>-0.29</v>
-      </c>
-      <c r="I23" s="28" t="n">
-        <v>2.65</v>
+        <v>5.61</v>
+      </c>
+      <c r="I23" s="27" t="n">
+        <v>14.88</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
       <c r="A24" s="26" t="inlineStr">
         <is>
-          <t>제너셈</t>
+          <t>한솔홀딩스</t>
         </is>
       </c>
       <c r="B24" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C24" s="25" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D24" s="25" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E24" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F24" s="25" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G24" s="25" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="H24" s="28" t="n">
-        <v>4.59</v>
-      </c>
-      <c r="I24" s="28" t="n">
-        <v>12.02</v>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="H24" s="27" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="I24" s="27" t="n">
+        <v>6.46</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
       <c r="A25" s="26" t="inlineStr">
         <is>
-          <t>제약</t>
+          <t>LG전자</t>
         </is>
       </c>
       <c r="B25" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C25" s="25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D25" s="25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E25" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F25" s="25" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G25" s="25" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="H25" s="25" t="n"/>
-      <c r="I25" s="25" t="n"/>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="H25" s="27" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="I25" s="27" t="n">
+        <v>4.69</v>
+      </c>
     </row>
     <row r="26" ht="18" customHeight="1">
       <c r="A26" s="26" t="inlineStr">
         <is>
-          <t>철강</t>
+          <t>미래에셋벤처투자</t>
         </is>
       </c>
       <c r="B26" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C26" s="25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D26" s="25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E26" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F26" s="25" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G26" s="25" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="H26" s="25" t="n"/>
-      <c r="I26" s="25" t="n"/>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="H26" s="29" t="n">
+        <v>-8.720000000000001</v>
+      </c>
+      <c r="I26" s="29" t="n">
+        <v>-31.05</v>
+      </c>
     </row>
     <row r="27" ht="18" customHeight="1">
       <c r="A27" s="26" t="inlineStr">
         <is>
-          <t>한국전력</t>
+          <t>미래에셋생명</t>
         </is>
       </c>
       <c r="B27" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C27" s="25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D27" s="25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E27" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F27" s="25" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G27" s="25" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="H27" s="27" t="n">
-        <v>-3.86</v>
-      </c>
-      <c r="I27" s="28" t="n">
-        <v>10.25</v>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="H27" s="29" t="n">
+        <v>-5.12</v>
+      </c>
+      <c r="I27" s="27" t="n">
+        <v>35.4</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
       <c r="A28" s="26" t="inlineStr">
         <is>
-          <t>후성</t>
+          <t>미래에셋증권2우B</t>
         </is>
       </c>
       <c r="B28" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C28" s="25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D28" s="25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E28" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F28" s="25" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G28" s="25" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="H28" s="27" t="n">
-        <v>-14.29</v>
-      </c>
-      <c r="I28" s="28" t="n">
-        <v>42.01</v>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="H28" s="29" t="n">
+        <v>-2.58</v>
+      </c>
+      <c r="I28" s="29" t="n">
+        <v>-0.87</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
       <c r="A29" s="26" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>방산</t>
         </is>
       </c>
       <c r="B29" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C29" s="25" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D29" s="25" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E29" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F29" s="25" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G29" s="25" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="H29" s="25" t="n"/>
@@ -4018,287 +4030,287 @@
     <row r="30" ht="18" customHeight="1">
       <c r="A30" s="26" t="inlineStr">
         <is>
-          <t>CSA 코스믹</t>
+          <t>KBI메탈</t>
         </is>
       </c>
       <c r="B30" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C30" s="25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D30" s="25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E30" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F30" s="25" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G30" s="25" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="H30" s="27" t="n">
-        <v>-5.28</v>
-      </c>
-      <c r="I30" s="28" t="n">
-        <v>69.44</v>
+        <v>16.42</v>
+      </c>
+      <c r="I30" s="27" t="n">
+        <v>18.8</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
       <c r="A31" s="26" t="inlineStr">
         <is>
-          <t>GS건설</t>
+          <t>가온전선</t>
         </is>
       </c>
       <c r="B31" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C31" s="25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D31" s="25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E31" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F31" s="25" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G31" s="25" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="H31" s="28" t="n">
-        <v>5.29</v>
-      </c>
-      <c r="I31" s="28" t="n">
-        <v>20.42</v>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="H31" s="27" t="n">
+        <v>29.9</v>
+      </c>
+      <c r="I31" s="27" t="n">
+        <v>8.949999999999999</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
       <c r="A32" s="26" t="inlineStr">
         <is>
-          <t>LIG디펜스앤에어로스페이스</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B32" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C32" s="25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D32" s="25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E32" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F32" s="25" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G32" s="25" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="H32" s="28" t="n">
-        <v>18.58</v>
-      </c>
-      <c r="I32" s="28" t="n">
-        <v>38.21</v>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="H32" s="29" t="n">
+        <v>-9.65</v>
+      </c>
+      <c r="I32" s="27" t="n">
+        <v>19.52</v>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
       <c r="A33" s="26" t="inlineStr">
         <is>
-          <t>SM C&amp;C</t>
+          <t>디앤디파마텍</t>
         </is>
       </c>
       <c r="B33" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C33" s="25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D33" s="25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E33" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F33" s="25" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G33" s="25" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="H33" s="28" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="I33" s="28" t="n">
-        <v>39.65</v>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="H33" s="27" t="n">
+        <v>18.01</v>
+      </c>
+      <c r="I33" s="27" t="n">
+        <v>24.4</v>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
       <c r="A34" s="26" t="inlineStr">
         <is>
-          <t>TS트릴리온</t>
+          <t>삼성전기</t>
         </is>
       </c>
       <c r="B34" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C34" s="25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D34" s="25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E34" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F34" s="25" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G34" s="25" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="H34" s="27" t="n">
-        <v>-8.710000000000001</v>
-      </c>
-      <c r="I34" s="28" t="n">
-        <v>23.57</v>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="H34" s="29" t="n">
+        <v>-0.78</v>
+      </c>
+      <c r="I34" s="27" t="n">
+        <v>12.58</v>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
       <c r="A35" s="26" t="inlineStr">
         <is>
-          <t>기업은행</t>
+          <t>한미반도체</t>
         </is>
       </c>
       <c r="B35" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C35" s="25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D35" s="25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E35" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F35" s="25" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G35" s="25" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="H35" s="28" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="I35" s="28" t="n">
-        <v>12.41</v>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="H35" s="29" t="n">
+        <v>-2.74</v>
+      </c>
+      <c r="I35" s="27" t="n">
+        <v>18.33</v>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
       <c r="A36" s="26" t="inlineStr">
         <is>
-          <t>네패스</t>
+          <t>현대약품</t>
         </is>
       </c>
       <c r="B36" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C36" s="25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D36" s="25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E36" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F36" s="25" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G36" s="25" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="H36" s="28" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="I36" s="28" t="n">
-        <v>17.14</v>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="H36" s="27" t="n">
+        <v>6.71</v>
+      </c>
+      <c r="I36" s="27" t="n">
+        <v>45.08</v>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
       <c r="A37" s="26" t="inlineStr">
         <is>
-          <t>대신증권</t>
+          <t>현대차</t>
         </is>
       </c>
       <c r="B37" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C37" s="25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D37" s="25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E37" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F37" s="25" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G37" s="25" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="H37" s="28" t="n">
-        <v>4.87</v>
-      </c>
-      <c r="I37" s="28" t="n">
-        <v>5.75</v>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="H37" s="29" t="n">
+        <v>-3.44</v>
+      </c>
+      <c r="I37" s="27" t="n">
+        <v>2.66</v>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
       <c r="A38" s="26" t="inlineStr">
         <is>
-          <t>삼보산업</t>
+          <t>JW신약</t>
         </is>
       </c>
       <c r="B38" s="25" t="n">
@@ -4315,25 +4327,25 @@
       </c>
       <c r="F38" s="25" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G38" s="25" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="H38" s="27" t="n">
-        <v>-2.34</v>
-      </c>
-      <c r="I38" s="28" t="n">
-        <v>0.37</v>
+        <v>29.87</v>
+      </c>
+      <c r="I38" s="27" t="n">
+        <v>77.56999999999999</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
       <c r="A39" s="26" t="inlineStr">
         <is>
-          <t>삼성전기</t>
+          <t>LB세미콘</t>
         </is>
       </c>
       <c r="B39" s="25" t="n">
@@ -4350,25 +4362,25 @@
       </c>
       <c r="F39" s="25" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G39" s="25" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="H39" s="28" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="I39" s="28" t="n">
-        <v>3.96</v>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="H39" s="27" t="n">
+        <v>4.72</v>
+      </c>
+      <c r="I39" s="27" t="n">
+        <v>29.37</v>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
       <c r="A40" s="26" t="inlineStr">
         <is>
-          <t>스피어</t>
+          <t>TS트릴리온</t>
         </is>
       </c>
       <c r="B40" s="25" t="n">
@@ -4385,25 +4397,25 @@
       </c>
       <c r="F40" s="25" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G40" s="25" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="H40" s="27" t="n">
-        <v>-6.53</v>
-      </c>
-      <c r="I40" s="28" t="n">
-        <v>17.08</v>
+        <v>6.9</v>
+      </c>
+      <c r="I40" s="27" t="n">
+        <v>33.45</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
       <c r="A41" s="26" t="inlineStr">
         <is>
-          <t>신원</t>
+          <t>모아데이타</t>
         </is>
       </c>
       <c r="B41" s="25" t="n">
@@ -4420,25 +4432,25 @@
       </c>
       <c r="F41" s="25" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G41" s="25" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="H41" s="27" t="n">
-        <v>-0.52</v>
-      </c>
-      <c r="I41" s="28" t="n">
-        <v>8.77</v>
+        <v>5.14</v>
+      </c>
+      <c r="I41" s="27" t="n">
+        <v>5.59</v>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
       <c r="A42" s="26" t="inlineStr">
         <is>
-          <t>씨에스윈드</t>
+          <t>삼보산업</t>
         </is>
       </c>
       <c r="B42" s="25" t="n">
@@ -4455,25 +4467,25 @@
       </c>
       <c r="F42" s="25" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G42" s="25" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="H42" s="28" t="n">
-        <v>29.83</v>
-      </c>
-      <c r="I42" s="28" t="n">
-        <v>40.77</v>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="H42" s="27" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="I42" s="29" t="n">
+        <v>-3.23</v>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1">
       <c r="A43" s="26" t="inlineStr">
         <is>
-          <t>저스템</t>
+          <t>삼익제약</t>
         </is>
       </c>
       <c r="B43" s="25" t="n">
@@ -4490,25 +4502,25 @@
       </c>
       <c r="F43" s="25" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G43" s="25" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="H43" s="27" t="n">
-        <v>-5.89</v>
-      </c>
-      <c r="I43" s="28" t="n">
-        <v>7.24</v>
+        <v>6.02</v>
+      </c>
+      <c r="I43" s="27" t="n">
+        <v>21.38</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
       <c r="A44" s="26" t="inlineStr">
         <is>
-          <t>전기차</t>
+          <t>엑셈</t>
         </is>
       </c>
       <c r="B44" s="25" t="n">
@@ -4525,21 +4537,25 @@
       </c>
       <c r="F44" s="25" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G44" s="25" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="H44" s="25" t="n"/>
-      <c r="I44" s="25" t="n"/>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="H44" s="27" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="I44" s="29" t="n">
+        <v>-9.25</v>
+      </c>
     </row>
     <row r="45" ht="18" customHeight="1">
       <c r="A45" s="26" t="inlineStr">
         <is>
-          <t>테스</t>
+          <t>올릭스</t>
         </is>
       </c>
       <c r="B45" s="25" t="n">
@@ -4556,25 +4572,25 @@
       </c>
       <c r="F45" s="25" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G45" s="25" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="H45" s="27" t="n">
-        <v>-4.41</v>
-      </c>
-      <c r="I45" s="28" t="n">
-        <v>4.83</v>
+        <v>9.82</v>
+      </c>
+      <c r="I45" s="27" t="n">
+        <v>15.26</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
       <c r="A46" s="26" t="inlineStr">
         <is>
-          <t>파두</t>
+          <t>젬백스</t>
         </is>
       </c>
       <c r="B46" s="25" t="n">
@@ -4591,25 +4607,25 @@
       </c>
       <c r="F46" s="25" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G46" s="25" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="H46" s="27" t="n">
-        <v>-2.04</v>
+        <v>4.38</v>
       </c>
       <c r="I46" s="27" t="n">
-        <v>-2.23</v>
+        <v>10.08</v>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
       <c r="A47" s="26" t="inlineStr">
         <is>
-          <t>피노</t>
+          <t>파두</t>
         </is>
       </c>
       <c r="B47" s="25" t="n">
@@ -4626,25 +4642,25 @@
       </c>
       <c r="F47" s="25" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G47" s="25" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="H47" s="27" t="n">
-        <v>-5.66</v>
+        <v>5.05</v>
       </c>
       <c r="I47" s="27" t="n">
-        <v>-4.84</v>
+        <v>6.43</v>
       </c>
     </row>
     <row r="48" ht="18" customHeight="1">
       <c r="A48" s="26" t="inlineStr">
         <is>
-          <t>한솔테크닉스</t>
+          <t>페니트리움바이오</t>
         </is>
       </c>
       <c r="B48" s="25" t="n">
@@ -4661,25 +4677,25 @@
       </c>
       <c r="F48" s="25" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G48" s="25" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="H48" s="27" t="n">
-        <v>-8.24</v>
-      </c>
-      <c r="I48" s="28" t="n">
-        <v>11.11</v>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="H48" s="29" t="n">
+        <v>-0.45</v>
+      </c>
+      <c r="I48" s="27" t="n">
+        <v>6.06</v>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1">
       <c r="A49" s="26" t="inlineStr">
         <is>
-          <t>현대모비스</t>
+          <t>피노</t>
         </is>
       </c>
       <c r="B49" s="25" t="n">
@@ -4696,124 +4712,124 @@
       </c>
       <c r="F49" s="25" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G49" s="25" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="H49" s="28" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="I49" s="28" t="n">
-        <v>10.92</v>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="H49" s="27" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="I49" s="29" t="n">
+        <v>-3.06</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
       <c r="A50" s="26" t="inlineStr">
         <is>
-          <t>JW신약</t>
+          <t>한국전력</t>
         </is>
       </c>
       <c r="B50" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C50" s="25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D50" s="25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E50" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F50" s="25" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G50" s="25" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="H50" s="28" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="I50" s="28" t="n">
-        <v>33.88</v>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="H50" s="27" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="I50" s="27" t="n">
+        <v>11.26</v>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
       <c r="A51" s="26" t="inlineStr">
         <is>
-          <t>미래에셋증권</t>
+          <t>한화솔루션</t>
         </is>
       </c>
       <c r="B51" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C51" s="25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D51" s="25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E51" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F51" s="25" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G51" s="25" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="H51" s="27" t="n">
-        <v>-0.58</v>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="H51" s="29" t="n">
+        <v>-2.13</v>
       </c>
       <c r="I51" s="27" t="n">
-        <v>-0.39</v>
+        <v>19.63</v>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1">
       <c r="A52" s="26" t="inlineStr">
         <is>
-          <t>한화오션</t>
+          <t>후성</t>
         </is>
       </c>
       <c r="B52" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C52" s="25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D52" s="25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E52" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F52" s="25" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G52" s="25" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="H52" s="28" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="I52" s="28" t="n">
-        <v>26.42</v>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="H52" s="29" t="n">
+        <v>-8.44</v>
+      </c>
+      <c r="I52" s="27" t="n">
+        <v>8.25</v>
       </c>
     </row>
   </sheetData>
@@ -4897,19 +4913,19 @@
         <v>1</v>
       </c>
       <c r="C3" s="36" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="D3" s="36" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="E3" s="36" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="F3" s="37" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G3" s="37" t="inlineStr">
@@ -4928,19 +4944,19 @@
         <v>1</v>
       </c>
       <c r="C4" s="36" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D4" s="36" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E4" s="36" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="F4" s="37" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G4" s="37" t="inlineStr">
@@ -4952,26 +4968,26 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="35" t="inlineStr">
         <is>
-          <t>전기차</t>
+          <t>방산</t>
         </is>
       </c>
       <c r="B5" s="36" t="n">
         <v>1</v>
       </c>
       <c r="C5" s="36" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D5" s="36" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E5" s="36" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="F5" s="37" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G5" s="37" t="inlineStr">
@@ -4983,26 +4999,26 @@
     <row r="6" ht="18" customHeight="1">
       <c r="A6" s="35" t="inlineStr">
         <is>
-          <t>방산</t>
+          <t>원전</t>
         </is>
       </c>
       <c r="B6" s="36" t="n">
         <v>1</v>
       </c>
       <c r="C6" s="36" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="D6" s="36" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="E6" s="36" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="F6" s="37" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G6" s="37" t="inlineStr">
@@ -5021,19 +5037,19 @@
         <v>1</v>
       </c>
       <c r="C7" s="36" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D7" s="36" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="E7" s="36" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="F7" s="37" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G7" s="37" t="inlineStr">
@@ -5045,26 +5061,26 @@
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="35" t="inlineStr">
         <is>
-          <t>태양광</t>
+          <t>게임</t>
         </is>
       </c>
       <c r="B8" s="36" t="n">
         <v>1</v>
       </c>
       <c r="C8" s="36" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D8" s="36" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E8" s="36" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="F8" s="37" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G8" s="37" t="inlineStr">
@@ -5076,26 +5092,26 @@
     <row r="9" ht="18" customHeight="1">
       <c r="A9" s="35" t="inlineStr">
         <is>
-          <t>철강</t>
+          <t>조선</t>
         </is>
       </c>
       <c r="B9" s="36" t="n">
         <v>1</v>
       </c>
       <c r="C9" s="36" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D9" s="36" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E9" s="36" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="F9" s="37" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G9" s="37" t="inlineStr">
@@ -5107,26 +5123,26 @@
     <row r="10" ht="18" customHeight="1">
       <c r="A10" s="35" t="inlineStr">
         <is>
-          <t>제약</t>
+          <t>철강</t>
         </is>
       </c>
       <c r="B10" s="36" t="n">
         <v>1</v>
       </c>
       <c r="C10" s="36" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D10" s="36" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E10" s="36" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="F10" s="37" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G10" s="37" t="inlineStr">
@@ -5138,26 +5154,26 @@
     <row r="11" ht="18" customHeight="1">
       <c r="A11" s="35" t="inlineStr">
         <is>
-          <t>인공지능</t>
+          <t>제약</t>
         </is>
       </c>
       <c r="B11" s="36" t="n">
         <v>1</v>
       </c>
       <c r="C11" s="36" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="D11" s="36" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="E11" s="36" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="F11" s="37" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G11" s="37" t="inlineStr">
@@ -5169,65 +5185,69 @@
     <row r="12" ht="18" customHeight="1">
       <c r="A12" s="35" t="inlineStr">
         <is>
+          <t>인공지능</t>
+        </is>
+      </c>
+      <c r="B12" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" s="36" t="n">
+        <v>11</v>
+      </c>
+      <c r="D12" s="36" t="n">
+        <v>11</v>
+      </c>
+      <c r="E12" s="36" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="F12" s="37" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G12" s="37" t="inlineStr">
+        <is>
+          <t>⚡ 관심</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="18" customHeight="1">
+      <c r="A13" s="35" t="inlineStr">
+        <is>
           <t>AMD</t>
         </is>
       </c>
-      <c r="B12" s="36" t="n">
-        <v>1</v>
-      </c>
-      <c r="C12" s="36" t="n">
-        <v>3</v>
-      </c>
-      <c r="D12" s="36" t="n">
-        <v>3</v>
-      </c>
-      <c r="E12" s="36" t="inlineStr">
-        <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="F12" s="37" t="inlineStr">
-        <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="G12" s="37" t="inlineStr">
+      <c r="B13" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" s="36" t="n">
+        <v>6</v>
+      </c>
+      <c r="D13" s="36" t="n">
+        <v>6</v>
+      </c>
+      <c r="E13" s="36" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="F13" s="37" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G13" s="37" t="inlineStr">
         <is>
           <t>⚡ 관심</t>
         </is>
       </c>
-    </row>
-    <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="26" t="inlineStr">
-        <is>
-          <t>이차전지</t>
-        </is>
-      </c>
-      <c r="B13" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="C13" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" s="25" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F13" s="29" t="inlineStr">
-        <is>
-          <t>감지 없음</t>
-        </is>
-      </c>
-      <c r="G13" s="29" t="inlineStr"/>
     </row>
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="26" t="inlineStr">
         <is>
-          <t>AI반도체</t>
+          <t>이차전지</t>
         </is>
       </c>
       <c r="B14" s="25" t="n">
@@ -5244,17 +5264,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F14" s="29" t="inlineStr">
+      <c r="F14" s="28" t="inlineStr">
         <is>
           <t>감지 없음</t>
         </is>
       </c>
-      <c r="G14" s="29" t="inlineStr"/>
+      <c r="G14" s="28" t="inlineStr"/>
     </row>
     <row r="15" ht="18" customHeight="1">
       <c r="A15" s="26" t="inlineStr">
         <is>
-          <t>원전</t>
+          <t>AI반도체</t>
         </is>
       </c>
       <c r="B15" s="25" t="n">
@@ -5271,17 +5291,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F15" s="29" t="inlineStr">
+      <c r="F15" s="28" t="inlineStr">
         <is>
           <t>감지 없음</t>
         </is>
       </c>
-      <c r="G15" s="29" t="inlineStr"/>
+      <c r="G15" s="28" t="inlineStr"/>
     </row>
     <row r="16" ht="18" customHeight="1">
       <c r="A16" s="26" t="inlineStr">
         <is>
-          <t>수소</t>
+          <t>전기차</t>
         </is>
       </c>
       <c r="B16" s="25" t="n">
@@ -5298,17 +5318,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F16" s="29" t="inlineStr">
+      <c r="F16" s="28" t="inlineStr">
         <is>
           <t>감지 없음</t>
         </is>
       </c>
-      <c r="G16" s="29" t="inlineStr"/>
+      <c r="G16" s="28" t="inlineStr"/>
     </row>
     <row r="17" ht="18" customHeight="1">
       <c r="A17" s="26" t="inlineStr">
         <is>
-          <t>게임</t>
+          <t>수소</t>
         </is>
       </c>
       <c r="B17" s="25" t="n">
@@ -5325,17 +5345,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F17" s="29" t="inlineStr">
+      <c r="F17" s="28" t="inlineStr">
         <is>
           <t>감지 없음</t>
         </is>
       </c>
-      <c r="G17" s="29" t="inlineStr"/>
+      <c r="G17" s="28" t="inlineStr"/>
     </row>
     <row r="18" ht="18" customHeight="1">
       <c r="A18" s="26" t="inlineStr">
         <is>
-          <t>엔터</t>
+          <t>태양광</t>
         </is>
       </c>
       <c r="B18" s="25" t="n">
@@ -5352,17 +5372,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F18" s="29" t="inlineStr">
+      <c r="F18" s="28" t="inlineStr">
         <is>
           <t>감지 없음</t>
         </is>
       </c>
-      <c r="G18" s="29" t="inlineStr"/>
+      <c r="G18" s="28" t="inlineStr"/>
     </row>
     <row r="19" ht="18" customHeight="1">
       <c r="A19" s="26" t="inlineStr">
         <is>
-          <t>핀테크</t>
+          <t>엔터</t>
         </is>
       </c>
       <c r="B19" s="25" t="n">
@@ -5379,17 +5399,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F19" s="29" t="inlineStr">
+      <c r="F19" s="28" t="inlineStr">
         <is>
           <t>감지 없음</t>
         </is>
       </c>
-      <c r="G19" s="29" t="inlineStr"/>
+      <c r="G19" s="28" t="inlineStr"/>
     </row>
     <row r="20" ht="18" customHeight="1">
       <c r="A20" s="26" t="inlineStr">
         <is>
-          <t>클라우드</t>
+          <t>핀테크</t>
         </is>
       </c>
       <c r="B20" s="25" t="n">
@@ -5406,17 +5426,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F20" s="29" t="inlineStr">
+      <c r="F20" s="28" t="inlineStr">
         <is>
           <t>감지 없음</t>
         </is>
       </c>
-      <c r="G20" s="29" t="inlineStr"/>
+      <c r="G20" s="28" t="inlineStr"/>
     </row>
     <row r="21" ht="18" customHeight="1">
       <c r="A21" s="26" t="inlineStr">
         <is>
-          <t>조선</t>
+          <t>클라우드</t>
         </is>
       </c>
       <c r="B21" s="25" t="n">
@@ -5433,12 +5453,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F21" s="29" t="inlineStr">
+      <c r="F21" s="28" t="inlineStr">
         <is>
           <t>감지 없음</t>
         </is>
       </c>
-      <c r="G21" s="29" t="inlineStr"/>
+      <c r="G21" s="28" t="inlineStr"/>
     </row>
     <row r="22" ht="18" customHeight="1">
       <c r="A22" s="26" t="inlineStr">
@@ -5460,12 +5480,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F22" s="29" t="inlineStr">
+      <c r="F22" s="28" t="inlineStr">
         <is>
           <t>감지 없음</t>
         </is>
       </c>
-      <c r="G22" s="29" t="inlineStr"/>
+      <c r="G22" s="28" t="inlineStr"/>
     </row>
     <row r="23" ht="18" customHeight="1">
       <c r="A23" s="26" t="inlineStr">
@@ -5487,12 +5507,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F23" s="29" t="inlineStr">
+      <c r="F23" s="28" t="inlineStr">
         <is>
           <t>감지 없음</t>
         </is>
       </c>
-      <c r="G23" s="29" t="inlineStr"/>
+      <c r="G23" s="28" t="inlineStr"/>
     </row>
     <row r="24" ht="18" customHeight="1">
       <c r="A24" s="26" t="inlineStr">
@@ -5514,12 +5534,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F24" s="29" t="inlineStr">
+      <c r="F24" s="28" t="inlineStr">
         <is>
           <t>감지 없음</t>
         </is>
       </c>
-      <c r="G24" s="29" t="inlineStr"/>
+      <c r="G24" s="28" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/trend/stock_trend_history.xlsx
+++ b/trend/stock_trend_history.xlsx
@@ -258,13 +258,13 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -273,14 +273,14 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -694,7 +694,7 @@
     <row r="1" ht="36" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>📊 주식 트렌드 조기 감지 대시보드   |   최종 업데이트: 2026-06-18 06:55</t>
+          <t>📊 주식 트렌드 조기 감지 대시보드   |   최종 업데이트: 2026-06-19 06:55</t>
         </is>
       </c>
     </row>
@@ -708,7 +708,7 @@
       </c>
       <c r="E3" s="3" t="n"/>
       <c r="G3" s="5" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H3" s="3" t="n"/>
       <c r="J3" s="6" t="n">
@@ -787,21 +787,21 @@
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="11" t="inlineStr">
         <is>
-          <t>⚡ 최신(2026-06-18) 상위: 반도체  점수 57.0점</t>
+          <t>⚡ 최신(2026-06-19) 상위: 반도체  점수 85.0점</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1">
       <c r="A11" s="12" t="inlineStr">
         <is>
-          <t>⚡ 최신(2026-06-18) 상위: LG  점수 31.0점</t>
+          <t>⚡ 최신(2026-06-19) 상위: SK  점수 40.0점</t>
         </is>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1">
       <c r="A12" s="11" t="inlineStr">
         <is>
-          <t>⚡ 최신(2026-06-18) 상위: 삼성전자  점수 28.0점</t>
+          <t>⚡ 최신(2026-06-19) 상위: SK하이닉스  점수 33.0점</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B14" s="15" t="n">
@@ -928,10 +928,10 @@
         </is>
       </c>
       <c r="D14" s="15" t="n">
-        <v>57</v>
+        <v>85</v>
       </c>
       <c r="E14" s="15" t="n">
-        <v>57</v>
+        <v>85</v>
       </c>
       <c r="F14" s="15" t="n">
         <v>0</v>
@@ -947,7 +947,7 @@
       </c>
       <c r="J14" s="17" t="inlineStr">
         <is>
-          <t>매일경제 헤드라인 언급 / 네이버뉴스 헤드라인 언급 / 네이버뉴스 기사 언급 / 한국경제 헤드라인 언급 / 매일경제 기사 언급</t>
+          <t>매일경제 기사 언급 / 네이버뉴스 헤드라인 언급 / 네이버뉴스 헤드라인 언급 / 네이버뉴스 헤드라인 언급 / 네이버뉴스 기사 언급</t>
         </is>
       </c>
       <c r="K14" s="17" t="inlineStr">
@@ -959,7 +959,7 @@
     <row r="15" ht="18" customHeight="1">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B15" s="15" t="n">
@@ -967,14 +967,14 @@
       </c>
       <c r="C15" s="16" t="inlineStr">
         <is>
-          <t>LG</t>
+          <t>SK</t>
         </is>
       </c>
       <c r="D15" s="15" t="n">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="E15" s="15" t="n">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="F15" s="15" t="n">
         <v>0</v>
@@ -983,26 +983,24 @@
         <v>0</v>
       </c>
       <c r="H15" s="18" t="n">
-        <v>-1.4</v>
+        <v>-2.97</v>
       </c>
       <c r="I15" s="19" t="n">
-        <v>3.5</v>
+        <v>19.48</v>
       </c>
       <c r="J15" s="17" t="inlineStr">
         <is>
-          <t>매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 기사 언급 / 매일경제 헤드라인 언급 / 네이버뉴스 기사 언급</t>
-        </is>
-      </c>
-      <c r="K15" s="17" t="inlineStr">
-        <is>
-          <t>네이버</t>
-        </is>
+          <t>매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 기사 언급 / 매일경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K15" s="17" t="n">
+        <v/>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
       <c r="A16" s="15" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B16" s="15" t="n">
@@ -1010,14 +1008,14 @@
       </c>
       <c r="C16" s="16" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="D16" s="15" t="n">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="E16" s="15" t="n">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="F16" s="15" t="n">
         <v>0</v>
@@ -1026,26 +1024,24 @@
         <v>0</v>
       </c>
       <c r="H16" s="19" t="n">
-        <v>1.02</v>
+        <v>6.51</v>
       </c>
       <c r="I16" s="19" t="n">
-        <v>14.55</v>
+        <v>27.8</v>
       </c>
       <c r="J16" s="17" t="inlineStr">
         <is>
-          <t>네이버뉴스 기사 언급 / 네이버뉴스 헤드라인 언급 / 네이버뉴스 기사 언급 / 매일경제 기사 언급 / 매일경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K16" s="17" t="inlineStr">
-        <is>
-          <t>네이버</t>
-        </is>
+          <t>매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 기사 언급 / 매일경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K16" s="17" t="n">
+        <v/>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B17" s="15" t="n">
@@ -1053,14 +1049,14 @@
       </c>
       <c r="C17" s="16" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="D17" s="15" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="E17" s="15" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="F17" s="15" t="n">
         <v>0</v>
@@ -1069,14 +1065,14 @@
         <v>0</v>
       </c>
       <c r="H17" s="19" t="n">
-        <v>5.84</v>
+        <v>4.62</v>
       </c>
       <c r="I17" s="19" t="n">
-        <v>23.1</v>
+        <v>21.24</v>
       </c>
       <c r="J17" s="17" t="inlineStr">
         <is>
-          <t>매일경제 헤드라인 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 헤드라인 언급 / 매일경제 헤드라인 언급 / 네이버뉴스 기사 언급</t>
+          <t>매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 기사 언급 / 매일경제 헤드라인 언급</t>
         </is>
       </c>
       <c r="K17" s="17" t="inlineStr">
@@ -1088,7 +1084,7 @@
     <row r="18" ht="18" customHeight="1">
       <c r="A18" s="15" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B18" s="15" t="n">
@@ -1100,10 +1096,10 @@
         </is>
       </c>
       <c r="D18" s="15" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E18" s="15" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F18" s="15" t="n">
         <v>0</v>
@@ -1119,7 +1115,7 @@
       </c>
       <c r="J18" s="17" t="inlineStr">
         <is>
-          <t>한국경제 헤드라인 언급 / 매일경제 기사 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
+          <t>매일경제 헤드라인 언급 / 한국경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급</t>
         </is>
       </c>
       <c r="K18" s="17" t="n">
@@ -1129,7 +1125,7 @@
     <row r="19" ht="18" customHeight="1">
       <c r="A19" s="15" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B19" s="15" t="n">
@@ -1137,14 +1133,14 @@
       </c>
       <c r="C19" s="16" t="inlineStr">
         <is>
-          <t>미래에셋증권</t>
+          <t>바이오</t>
         </is>
       </c>
       <c r="D19" s="15" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E19" s="15" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F19" s="15" t="n">
         <v>0</v>
@@ -1152,27 +1148,27 @@
       <c r="G19" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="H19" s="18" t="n">
-        <v>-1.75</v>
-      </c>
-      <c r="I19" s="18" t="n">
-        <v>-1.56</v>
+      <c r="H19" s="15" t="n">
+        <v/>
+      </c>
+      <c r="I19" s="15" t="n">
+        <v/>
       </c>
       <c r="J19" s="17" t="inlineStr">
         <is>
-          <t>중요공시 2건 / Google 급상승 검색어 등장 (KR) / 매일경제 기사 언급 / 한국경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
+          <t>네이버뉴스 헤드라인 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 헤드라인 언급 / 네이버뉴스 헤드라인 언급 / 네이버뉴스 헤드라인 언급</t>
         </is>
       </c>
       <c r="K19" s="17" t="inlineStr">
         <is>
-          <t>Google, 공시</t>
+          <t>네이버</t>
         </is>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
       <c r="A20" s="15" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B20" s="15" t="n">
@@ -1180,14 +1176,14 @@
       </c>
       <c r="C20" s="16" t="inlineStr">
         <is>
-          <t>바이오</t>
+          <t>제약</t>
         </is>
       </c>
       <c r="D20" s="15" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E20" s="15" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F20" s="15" t="n">
         <v>0</v>
@@ -1203,7 +1199,7 @@
       </c>
       <c r="J20" s="17" t="inlineStr">
         <is>
-          <t>매일경제 헤드라인 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 기사 언급</t>
+          <t>네이버뉴스 헤드라인 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 헤드라인 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 헤드라인 언급</t>
         </is>
       </c>
       <c r="K20" s="17" t="inlineStr">
@@ -1215,7 +1211,7 @@
     <row r="21" ht="18" customHeight="1">
       <c r="A21" s="15" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B21" s="15" t="n">
@@ -1227,10 +1223,10 @@
         </is>
       </c>
       <c r="D21" s="15" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E21" s="15" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F21" s="15" t="n">
         <v>0</v>
@@ -1246,17 +1242,19 @@
       </c>
       <c r="J21" s="17" t="inlineStr">
         <is>
-          <t>매일경제 기사 언급 / 매일경제 기사 언급 / 매일경제 기사 언급 / 매일경제 기사 언급 / 매일경제 기사 언급</t>
-        </is>
-      </c>
-      <c r="K21" s="17" t="n">
-        <v/>
+          <t>네이버뉴스 기사 언급 / 네이버뉴스 기사 언급 / 매일경제 기사 언급 / 매일경제 기사 언급 / 매일경제 기사 언급</t>
+        </is>
+      </c>
+      <c r="K21" s="17" t="inlineStr">
+        <is>
+          <t>네이버</t>
+        </is>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
       <c r="A22" s="15" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B22" s="15" t="n">
@@ -1264,14 +1262,14 @@
       </c>
       <c r="C22" s="16" t="inlineStr">
         <is>
-          <t>SK스퀘어</t>
+          <t>넥써쓰</t>
         </is>
       </c>
       <c r="D22" s="15" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E22" s="15" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F22" s="15" t="n">
         <v>0</v>
@@ -1280,26 +1278,26 @@
         <v>0</v>
       </c>
       <c r="H22" s="19" t="n">
-        <v>6.33</v>
+        <v>2.67</v>
       </c>
       <c r="I22" s="19" t="n">
-        <v>34.91</v>
+        <v>28.71</v>
       </c>
       <c r="J22" s="17" t="inlineStr">
         <is>
-          <t>매일경제 헤드라인 언급 / 한국경제 헤드라인 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 기사 언급 / 매일경제 헤드라인 언급</t>
+          <t>중요공시 3건 / 매일경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
         </is>
       </c>
       <c r="K22" s="17" t="inlineStr">
         <is>
-          <t>네이버</t>
+          <t>공시</t>
         </is>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B23" s="15" t="n">
@@ -1307,14 +1305,14 @@
       </c>
       <c r="C23" s="16" t="inlineStr">
         <is>
-          <t>조선</t>
+          <t>전기차</t>
         </is>
       </c>
       <c r="D23" s="15" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E23" s="15" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F23" s="15" t="n">
         <v>0</v>
@@ -1330,19 +1328,17 @@
       </c>
       <c r="J23" s="17" t="inlineStr">
         <is>
-          <t>네이버뉴스 기사 언급 / 한국경제 헤드라인 언급 / 한국경제 헤드라인 언급 / 매일경제 기사 언급 / 한국경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K23" s="17" t="inlineStr">
-        <is>
-          <t>네이버</t>
-        </is>
+          <t>매일경제 헤드라인 언급 / 한국경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K23" s="17" t="n">
+        <v/>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B24" s="15" t="n">
@@ -1350,42 +1346,42 @@
       </c>
       <c r="C24" s="16" t="inlineStr">
         <is>
-          <t>한솔테크닉스</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="D24" s="15" t="n">
         <v>9</v>
       </c>
       <c r="E24" s="15" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F24" s="15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G24" s="15" t="n">
-        <v>3</v>
-      </c>
-      <c r="H24" s="19" t="n">
-        <v>30</v>
+        <v>0</v>
+      </c>
+      <c r="H24" s="18" t="n">
+        <v>-5.64</v>
       </c>
       <c r="I24" s="19" t="n">
-        <v>41.51</v>
+        <v>18.59</v>
       </c>
       <c r="J24" s="17" t="inlineStr">
         <is>
-          <t>중요공시 3건 / 중요공시 3일 +200% / 중요공시 7일 +50% / 네이버뉴스 기사 언급</t>
+          <t>네이버뉴스 헤드라인 언급 / 매일경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
         </is>
       </c>
       <c r="K24" s="17" t="inlineStr">
         <is>
-          <t>네이버, 공시</t>
+          <t>네이버</t>
         </is>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
       <c r="A25" s="15" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B25" s="15" t="n">
@@ -1393,7 +1389,7 @@
       </c>
       <c r="C25" s="16" t="inlineStr">
         <is>
-          <t>제약</t>
+          <t>미래에셋증권</t>
         </is>
       </c>
       <c r="D25" s="15" t="n">
@@ -1408,27 +1404,27 @@
       <c r="G25" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="H25" s="15" t="n">
-        <v/>
-      </c>
-      <c r="I25" s="15" t="n">
-        <v/>
+      <c r="H25" s="19" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="I25" s="18" t="n">
+        <v>-0.78</v>
       </c>
       <c r="J25" s="17" t="inlineStr">
         <is>
-          <t>네이버뉴스 기사 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 헤드라인 언급</t>
+          <t>중요공시 2건 / 매일경제 헤드라인 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 헤드라인 언급</t>
         </is>
       </c>
       <c r="K25" s="17" t="inlineStr">
         <is>
-          <t>네이버</t>
+          <t>네이버, 공시</t>
         </is>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
       <c r="A26" s="15" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B26" s="15" t="n">
@@ -1436,14 +1432,14 @@
       </c>
       <c r="C26" s="16" t="inlineStr">
         <is>
-          <t>LG이노텍</t>
+          <t>방산</t>
         </is>
       </c>
       <c r="D26" s="15" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E26" s="15" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F26" s="15" t="n">
         <v>0</v>
@@ -1451,15 +1447,15 @@
       <c r="G26" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="H26" s="19" t="n">
-        <v>0.97</v>
-      </c>
-      <c r="I26" s="19" t="n">
-        <v>14.5</v>
+      <c r="H26" s="15" t="n">
+        <v/>
+      </c>
+      <c r="I26" s="15" t="n">
+        <v/>
       </c>
       <c r="J26" s="17" t="inlineStr">
         <is>
-          <t>매일경제 헤드라인 언급 / 매일경제 기사 언급 / 한국경제 헤드라인 언급</t>
+          <t>매일경제 기사 언급 / 매일경제 기사 언급 / 한국경제 헤드라인 언급 / 매일경제 헤드라인 언급</t>
         </is>
       </c>
       <c r="K26" s="17" t="n">
@@ -1469,7 +1465,7 @@
     <row r="27" ht="18" customHeight="1">
       <c r="A27" s="15" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B27" s="15" t="n">
@@ -1477,7 +1473,7 @@
       </c>
       <c r="C27" s="16" t="inlineStr">
         <is>
-          <t>로봇</t>
+          <t>가온전선</t>
         </is>
       </c>
       <c r="D27" s="15" t="n">
@@ -1492,25 +1488,27 @@
       <c r="G27" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="H27" s="15" t="n">
-        <v/>
-      </c>
-      <c r="I27" s="15" t="n">
-        <v/>
+      <c r="H27" s="19" t="n">
+        <v>13.05</v>
+      </c>
+      <c r="I27" s="19" t="n">
+        <v>18.98</v>
       </c>
       <c r="J27" s="17" t="inlineStr">
         <is>
-          <t>매일경제 기사 언급 / 매일경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K27" s="17" t="n">
-        <v/>
+          <t>중요공시 2건 / 매일경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K27" s="17" t="inlineStr">
+        <is>
+          <t>공시</t>
+        </is>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
       <c r="A28" s="15" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B28" s="15" t="n">
@@ -1518,7 +1516,7 @@
       </c>
       <c r="C28" s="16" t="inlineStr">
         <is>
-          <t>기아</t>
+          <t>카카오</t>
         </is>
       </c>
       <c r="D28" s="15" t="n">
@@ -1534,67 +1532,67 @@
         <v>0</v>
       </c>
       <c r="H28" s="18" t="n">
-        <v>-2.29</v>
-      </c>
-      <c r="I28" s="19" t="n">
-        <v>4.13</v>
+        <v>-3.08</v>
+      </c>
+      <c r="I28" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="J28" s="17" t="inlineStr">
         <is>
-          <t>매일경제 기사 언급 / 한국경제 헤드라인 언급 / 한국경제 헤드라인 언급 / 매일경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K28" s="17" t="n">
+          <t>Google 급상승 검색어 등장 (KR) / 매일경제 기사 언급 / 매일경제 기사 언급</t>
+        </is>
+      </c>
+      <c r="K28" s="17" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="18" customHeight="1">
+      <c r="A29" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="B29" s="15" t="n">
+        <v>16</v>
+      </c>
+      <c r="C29" s="16" t="inlineStr">
+        <is>
+          <t>삼성전기</t>
+        </is>
+      </c>
+      <c r="D29" s="15" t="n">
+        <v>7</v>
+      </c>
+      <c r="E29" s="15" t="n">
+        <v>7</v>
+      </c>
+      <c r="F29" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" s="19" t="n">
+        <v>8.27</v>
+      </c>
+      <c r="I29" s="19" t="n">
+        <v>21.88</v>
+      </c>
+      <c r="J29" s="17" t="inlineStr">
+        <is>
+          <t>매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 기사 언급</t>
+        </is>
+      </c>
+      <c r="K29" s="17" t="n">
         <v/>
-      </c>
-    </row>
-    <row r="29" ht="18" customHeight="1">
-      <c r="A29" s="20" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="B29" s="20" t="n">
-        <v>16</v>
-      </c>
-      <c r="C29" s="21" t="inlineStr">
-        <is>
-          <t>모바일어플라이언스</t>
-        </is>
-      </c>
-      <c r="D29" s="20" t="n">
-        <v>6</v>
-      </c>
-      <c r="E29" s="20" t="n">
-        <v>3</v>
-      </c>
-      <c r="F29" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G29" s="20" t="n">
-        <v>3</v>
-      </c>
-      <c r="H29" s="22" t="n">
-        <v>-6.28</v>
-      </c>
-      <c r="I29" s="22" t="n">
-        <v>-15.26</v>
-      </c>
-      <c r="J29" s="23" t="inlineStr">
-        <is>
-          <t>중요공시 3건 / 중요공시 7일 +200%</t>
-        </is>
-      </c>
-      <c r="K29" s="23" t="inlineStr">
-        <is>
-          <t>공시</t>
-        </is>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
       <c r="A30" s="20" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B30" s="20" t="n">
@@ -1602,42 +1600,40 @@
       </c>
       <c r="C30" s="21" t="inlineStr">
         <is>
-          <t>알엔티엑스</t>
+          <t>대한항공</t>
         </is>
       </c>
       <c r="D30" s="20" t="n">
         <v>6</v>
       </c>
       <c r="E30" s="20" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F30" s="20" t="n">
         <v>0</v>
       </c>
       <c r="G30" s="20" t="n">
-        <v>3</v>
-      </c>
-      <c r="H30" s="24" t="n">
-        <v>3.28</v>
+        <v>0</v>
+      </c>
+      <c r="H30" s="22" t="n">
+        <v>0.17</v>
       </c>
       <c r="I30" s="22" t="n">
-        <v>-10</v>
+        <v>16.33</v>
       </c>
       <c r="J30" s="23" t="inlineStr">
         <is>
-          <t>중요공시 5건 / 중요공시 7일 +67%</t>
-        </is>
-      </c>
-      <c r="K30" s="23" t="inlineStr">
-        <is>
-          <t>공시</t>
-        </is>
+          <t>한국경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K30" s="23" t="n">
+        <v/>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
       <c r="A31" s="20" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B31" s="20" t="n">
@@ -1645,42 +1641,42 @@
       </c>
       <c r="C31" s="21" t="inlineStr">
         <is>
-          <t>한솔홀딩스</t>
+          <t>현대차</t>
         </is>
       </c>
       <c r="D31" s="20" t="n">
         <v>6</v>
       </c>
       <c r="E31" s="20" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F31" s="20" t="n">
         <v>0</v>
       </c>
       <c r="G31" s="20" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H31" s="24" t="n">
-        <v>3.57</v>
-      </c>
-      <c r="I31" s="24" t="n">
-        <v>6.46</v>
+        <v>-2.75</v>
+      </c>
+      <c r="I31" s="22" t="n">
+        <v>0.67</v>
       </c>
       <c r="J31" s="23" t="inlineStr">
         <is>
-          <t>중요공시 3건 / 중요공시 7일 +200%</t>
+          <t>매일경제 헤드라인 언급 / 네이버뉴스 기사 언급 / 한국경제 헤드라인 언급</t>
         </is>
       </c>
       <c r="K31" s="23" t="inlineStr">
         <is>
-          <t>공시</t>
+          <t>네이버</t>
         </is>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
       <c r="A32" s="20" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B32" s="20" t="n">
@@ -1688,7 +1684,7 @@
       </c>
       <c r="C32" s="21" t="inlineStr">
         <is>
-          <t>게임</t>
+          <t>LG</t>
         </is>
       </c>
       <c r="D32" s="20" t="n">
@@ -1703,27 +1699,25 @@
       <c r="G32" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H32" s="20" t="n">
+      <c r="H32" s="24" t="n">
+        <v>-2.31</v>
+      </c>
+      <c r="I32" s="22" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="J32" s="23" t="inlineStr">
+        <is>
+          <t>매일경제 기사 언급 / 매일경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K32" s="23" t="n">
         <v/>
-      </c>
-      <c r="I32" s="20" t="n">
-        <v/>
-      </c>
-      <c r="J32" s="23" t="inlineStr">
-        <is>
-          <t>매일경제 헤드라인 언급 / 네이버뉴스 기사 언급 / 매일경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K32" s="23" t="inlineStr">
-        <is>
-          <t>네이버</t>
-        </is>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
       <c r="A33" s="20" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B33" s="20" t="n">
@@ -1731,7 +1725,7 @@
       </c>
       <c r="C33" s="21" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>철강</t>
         </is>
       </c>
       <c r="D33" s="20" t="n">
@@ -1754,19 +1748,17 @@
       </c>
       <c r="J33" s="23" t="inlineStr">
         <is>
-          <t>네이버뉴스 헤드라인 언급 / 한국경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K33" s="23" t="inlineStr">
-        <is>
-          <t>네이버</t>
-        </is>
+          <t>매일경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K33" s="23" t="n">
+        <v/>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
       <c r="A34" s="20" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B34" s="20" t="n">
@@ -1774,40 +1766,42 @@
       </c>
       <c r="C34" s="21" t="inlineStr">
         <is>
-          <t>하이브</t>
+          <t>파두</t>
         </is>
       </c>
       <c r="D34" s="20" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E34" s="20" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F34" s="20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G34" s="20" t="n">
         <v>0</v>
       </c>
       <c r="H34" s="24" t="n">
-        <v>5.61</v>
-      </c>
-      <c r="I34" s="24" t="n">
-        <v>14.88</v>
+        <v>-1.89</v>
+      </c>
+      <c r="I34" s="22" t="n">
+        <v>4.73</v>
       </c>
       <c r="J34" s="23" t="inlineStr">
         <is>
-          <t>매일경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K34" s="23" t="n">
-        <v/>
+          <t>중요공시 3건 / 중요공시 3일 +200%</t>
+        </is>
+      </c>
+      <c r="K34" s="23" t="inlineStr">
+        <is>
+          <t>공시</t>
+        </is>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
       <c r="A35" s="20" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B35" s="20" t="n">
@@ -1815,14 +1809,14 @@
       </c>
       <c r="C35" s="21" t="inlineStr">
         <is>
-          <t>철강</t>
+          <t>로봇</t>
         </is>
       </c>
       <c r="D35" s="20" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E35" s="20" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F35" s="20" t="n">
         <v>0</v>
@@ -1838,7 +1832,7 @@
       </c>
       <c r="J35" s="23" t="inlineStr">
         <is>
-          <t>네이버뉴스 기사 언급 / 한국경제 헤드라인 언급 / 네이버뉴스 기사 언급 / 매일경제 기사 언급</t>
+          <t>매일경제 헤드라인 언급 / 매일경제 기사 언급 / 네이버뉴스 기사 언급</t>
         </is>
       </c>
       <c r="K35" s="23" t="inlineStr">
@@ -1850,7 +1844,7 @@
     <row r="36" ht="18" customHeight="1">
       <c r="A36" s="20" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B36" s="20" t="n">
@@ -1858,7 +1852,7 @@
       </c>
       <c r="C36" s="21" t="inlineStr">
         <is>
-          <t>미래에셋벤처투자</t>
+          <t>기아</t>
         </is>
       </c>
       <c r="D36" s="20" t="n">
@@ -1873,27 +1867,25 @@
       <c r="G36" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H36" s="22" t="n">
-        <v>-8.720000000000001</v>
+      <c r="H36" s="24" t="n">
+        <v>-4.51</v>
       </c>
       <c r="I36" s="22" t="n">
-        <v>-31.05</v>
+        <v>1.79</v>
       </c>
       <c r="J36" s="23" t="inlineStr">
         <is>
-          <t>Google 급상승 검색어 등장 (KR)</t>
-        </is>
-      </c>
-      <c r="K36" s="23" t="inlineStr">
-        <is>
-          <t>Google</t>
-        </is>
+          <t>매일경제 헤드라인 언급 / 매일경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K36" s="23" t="n">
+        <v/>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
       <c r="A37" s="20" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B37" s="20" t="n">
@@ -1901,7 +1893,7 @@
       </c>
       <c r="C37" s="21" t="inlineStr">
         <is>
-          <t>미래에셋생명</t>
+          <t>조선</t>
         </is>
       </c>
       <c r="D37" s="20" t="n">
@@ -1916,27 +1908,25 @@
       <c r="G37" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H37" s="22" t="n">
-        <v>-5.12</v>
-      </c>
-      <c r="I37" s="24" t="n">
-        <v>35.4</v>
+      <c r="H37" s="20" t="n">
+        <v/>
+      </c>
+      <c r="I37" s="20" t="n">
+        <v/>
       </c>
       <c r="J37" s="23" t="inlineStr">
         <is>
-          <t>Google 급상승 검색어 등장 (KR)</t>
-        </is>
-      </c>
-      <c r="K37" s="23" t="inlineStr">
-        <is>
-          <t>Google</t>
-        </is>
+          <t>매일경제 기사 언급 / 매일경제 기사 언급 / 한국경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K37" s="23" t="n">
+        <v/>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
       <c r="A38" s="20" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B38" s="20" t="n">
@@ -1944,14 +1934,14 @@
       </c>
       <c r="C38" s="21" t="inlineStr">
         <is>
-          <t>미래에셋증권2우B</t>
+          <t>일성건설</t>
         </is>
       </c>
       <c r="D38" s="20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E38" s="20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F38" s="20" t="n">
         <v>0</v>
@@ -1960,26 +1950,26 @@
         <v>0</v>
       </c>
       <c r="H38" s="22" t="n">
-        <v>-2.58</v>
+        <v>2.11</v>
       </c>
       <c r="I38" s="22" t="n">
-        <v>-0.87</v>
+        <v>48.92</v>
       </c>
       <c r="J38" s="23" t="inlineStr">
         <is>
-          <t>Google 급상승 검색어 등장 (KR)</t>
+          <t>네이버 검색 당일 +259% / 중요공시 1건</t>
         </is>
       </c>
       <c r="K38" s="23" t="inlineStr">
         <is>
-          <t>Google</t>
+          <t>네이버, 공시</t>
         </is>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
       <c r="A39" s="20" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B39" s="20" t="n">
@@ -1987,14 +1977,14 @@
       </c>
       <c r="C39" s="21" t="inlineStr">
         <is>
-          <t>방산</t>
+          <t>삼성SDI</t>
         </is>
       </c>
       <c r="D39" s="20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E39" s="20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F39" s="20" t="n">
         <v>0</v>
@@ -2002,410 +1992,412 @@
       <c r="G39" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H39" s="20" t="n">
+      <c r="H39" s="24" t="n">
+        <v>-5.09</v>
+      </c>
+      <c r="I39" s="22" t="n">
+        <v>4.71</v>
+      </c>
+      <c r="J39" s="23" t="inlineStr">
+        <is>
+          <t>매일경제 헤드라인 언급 / 매일경제 기사 언급</t>
+        </is>
+      </c>
+      <c r="K39" s="23" t="n">
         <v/>
       </c>
-      <c r="I39" s="20" t="n">
-        <v/>
-      </c>
-      <c r="J39" s="23" t="inlineStr">
-        <is>
-          <t>네이버뉴스 기사 언급 / 한국경제 헤드라인 언급 / 네이버뉴스 기사 언급</t>
-        </is>
-      </c>
-      <c r="K39" s="23" t="inlineStr">
+    </row>
+    <row r="40" ht="18" customHeight="1">
+      <c r="A40" s="25" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="B40" s="25" t="n">
+        <v>27</v>
+      </c>
+      <c r="C40" s="26" t="inlineStr">
+        <is>
+          <t>JW신약</t>
+        </is>
+      </c>
+      <c r="D40" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="E40" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="F40" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G40" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" s="27" t="n">
+        <v>-11.56</v>
+      </c>
+      <c r="I40" s="28" t="n">
+        <v>58.72</v>
+      </c>
+      <c r="J40" s="29" t="inlineStr">
+        <is>
+          <t>네이버 검색 당일 +622%</t>
+        </is>
+      </c>
+      <c r="K40" s="29" t="inlineStr">
         <is>
           <t>네이버</t>
         </is>
       </c>
     </row>
-    <row r="40" ht="18" customHeight="1">
-      <c r="A40" s="20" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="B40" s="20" t="n">
-        <v>27</v>
-      </c>
-      <c r="C40" s="21" t="inlineStr">
-        <is>
-          <t>LG전자</t>
-        </is>
-      </c>
-      <c r="D40" s="20" t="n">
-        <v>5</v>
-      </c>
-      <c r="E40" s="20" t="n">
-        <v>5</v>
-      </c>
-      <c r="F40" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G40" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H40" s="24" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="I40" s="24" t="n">
-        <v>4.69</v>
-      </c>
-      <c r="J40" s="23" t="inlineStr">
-        <is>
-          <t>네이버뉴스 기사 언급 / 매일경제 헤드라인 언급 / 매일경제 기사 언급</t>
-        </is>
-      </c>
-      <c r="K40" s="23" t="inlineStr">
+    <row r="41" ht="18" customHeight="1">
+      <c r="A41" s="25" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="B41" s="25" t="n">
+        <v>28</v>
+      </c>
+      <c r="C41" s="26" t="inlineStr">
+        <is>
+          <t>TS트릴리온</t>
+        </is>
+      </c>
+      <c r="D41" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="E41" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="F41" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G41" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" s="27" t="n">
+        <v>-8.75</v>
+      </c>
+      <c r="I41" s="28" t="n">
+        <v>21.49</v>
+      </c>
+      <c r="J41" s="29" t="inlineStr">
+        <is>
+          <t>네이버 검색 당일 +379%</t>
+        </is>
+      </c>
+      <c r="K41" s="29" t="inlineStr">
         <is>
           <t>네이버</t>
         </is>
       </c>
     </row>
-    <row r="41" ht="18" customHeight="1">
-      <c r="A41" s="20" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="B41" s="20" t="n">
-        <v>28</v>
-      </c>
-      <c r="C41" s="21" t="inlineStr">
+    <row r="42" ht="18" customHeight="1">
+      <c r="A42" s="25" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="B42" s="25" t="n">
+        <v>29</v>
+      </c>
+      <c r="C42" s="26" t="inlineStr">
+        <is>
+          <t>강동씨앤엘</t>
+        </is>
+      </c>
+      <c r="D42" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="E42" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="F42" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G42" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" s="28" t="n">
+        <v>30</v>
+      </c>
+      <c r="I42" s="28" t="n">
+        <v>77.05</v>
+      </c>
+      <c r="J42" s="29" t="inlineStr">
+        <is>
+          <t>네이버 검색 당일 +281%</t>
+        </is>
+      </c>
+      <c r="K42" s="29" t="inlineStr">
+        <is>
+          <t>네이버</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="18" customHeight="1">
+      <c r="A43" s="25" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="B43" s="25" t="n">
+        <v>30</v>
+      </c>
+      <c r="C43" s="26" t="inlineStr">
         <is>
           <t>현대약품</t>
         </is>
       </c>
-      <c r="D41" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="E41" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="F41" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G41" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H41" s="24" t="n">
-        <v>6.71</v>
-      </c>
-      <c r="I41" s="24" t="n">
-        <v>45.08</v>
-      </c>
-      <c r="J41" s="23" t="inlineStr">
-        <is>
-          <t>네이버 검색 당일 +121% / 네이버뉴스 기사 언급</t>
-        </is>
-      </c>
-      <c r="K41" s="23" t="inlineStr">
+      <c r="D43" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="E43" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="F43" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G43" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" s="28" t="n">
+        <v>4.81</v>
+      </c>
+      <c r="I43" s="28" t="n">
+        <v>48.34</v>
+      </c>
+      <c r="J43" s="29" t="inlineStr">
+        <is>
+          <t>네이버 검색 당일 +228%</t>
+        </is>
+      </c>
+      <c r="K43" s="29" t="inlineStr">
         <is>
           <t>네이버</t>
         </is>
       </c>
     </row>
-    <row r="42" ht="18" customHeight="1">
-      <c r="A42" s="20" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="B42" s="20" t="n">
-        <v>29</v>
-      </c>
-      <c r="C42" s="21" t="inlineStr">
-        <is>
-          <t>대우건설</t>
-        </is>
-      </c>
-      <c r="D42" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="E42" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="F42" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G42" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H42" s="22" t="n">
-        <v>-9.65</v>
-      </c>
-      <c r="I42" s="24" t="n">
-        <v>19.52</v>
-      </c>
-      <c r="J42" s="23" t="inlineStr">
-        <is>
-          <t>중요공시 1건 / 매일경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K42" s="23" t="inlineStr">
+    <row r="44" ht="18" customHeight="1">
+      <c r="A44" s="25" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="B44" s="25" t="n">
+        <v>31</v>
+      </c>
+      <c r="C44" s="26" t="inlineStr">
+        <is>
+          <t>위더스제약</t>
+        </is>
+      </c>
+      <c r="D44" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="E44" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="F44" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G44" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" s="27" t="n">
+        <v>-5.11</v>
+      </c>
+      <c r="I44" s="28" t="n">
+        <v>18.36</v>
+      </c>
+      <c r="J44" s="29" t="inlineStr">
+        <is>
+          <t>네이버 검색 당일 +197%</t>
+        </is>
+      </c>
+      <c r="K44" s="29" t="inlineStr">
+        <is>
+          <t>네이버</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="18" customHeight="1">
+      <c r="A45" s="25" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="B45" s="25" t="n">
+        <v>32</v>
+      </c>
+      <c r="C45" s="26" t="inlineStr">
+        <is>
+          <t>하이스틸</t>
+        </is>
+      </c>
+      <c r="D45" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="E45" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="F45" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G45" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" s="27" t="n">
+        <v>-1.7</v>
+      </c>
+      <c r="I45" s="28" t="n">
+        <v>14.95</v>
+      </c>
+      <c r="J45" s="29" t="inlineStr">
+        <is>
+          <t>네이버 검색 당일 +105%</t>
+        </is>
+      </c>
+      <c r="K45" s="29" t="inlineStr">
+        <is>
+          <t>네이버</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="18" customHeight="1">
+      <c r="A46" s="25" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="B46" s="25" t="n">
+        <v>33</v>
+      </c>
+      <c r="C46" s="26" t="inlineStr">
+        <is>
+          <t>한솔테크닉스</t>
+        </is>
+      </c>
+      <c r="D46" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="E46" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="F46" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="G46" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" s="27" t="n">
+        <v>-10.37</v>
+      </c>
+      <c r="I46" s="28" t="n">
+        <v>19.15</v>
+      </c>
+      <c r="J46" s="29" t="inlineStr">
+        <is>
+          <t>중요공시 2건 / 중요공시 3일 +100%</t>
+        </is>
+      </c>
+      <c r="K46" s="29" t="inlineStr">
         <is>
           <t>공시</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="18" customHeight="1">
-      <c r="A43" s="20" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="B43" s="20" t="n">
+    <row r="47" ht="18" customHeight="1">
+      <c r="A47" s="25" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="B47" s="25" t="n">
+        <v>34</v>
+      </c>
+      <c r="C47" s="26" t="inlineStr">
+        <is>
+          <t>삼보산업</t>
+        </is>
+      </c>
+      <c r="D47" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="E47" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="F47" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="G47" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H47" s="28" t="n">
         <v>30</v>
       </c>
-      <c r="C43" s="21" t="inlineStr">
-        <is>
-          <t>디앤디파마텍</t>
-        </is>
-      </c>
-      <c r="D43" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="E43" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="F43" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G43" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H43" s="24" t="n">
-        <v>18.01</v>
-      </c>
-      <c r="I43" s="24" t="n">
-        <v>24.4</v>
-      </c>
-      <c r="J43" s="23" t="inlineStr">
-        <is>
-          <t>중요공시 1건 / 매일경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K43" s="23" t="inlineStr">
+      <c r="I47" s="28" t="n">
+        <v>38.54</v>
+      </c>
+      <c r="J47" s="29" t="inlineStr">
+        <is>
+          <t>중요공시 2건 / 중요공시 3일 +100%</t>
+        </is>
+      </c>
+      <c r="K47" s="29" t="inlineStr">
         <is>
           <t>공시</t>
         </is>
       </c>
     </row>
-    <row r="44" ht="18" customHeight="1">
-      <c r="A44" s="20" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="B44" s="20" t="n">
-        <v>31</v>
-      </c>
-      <c r="C44" s="21" t="inlineStr">
-        <is>
-          <t>KBI메탈</t>
-        </is>
-      </c>
-      <c r="D44" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="E44" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="F44" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G44" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H44" s="24" t="n">
-        <v>16.42</v>
-      </c>
-      <c r="I44" s="24" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="J44" s="23" t="inlineStr">
-        <is>
-          <t>중요공시 1건 / 매일경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K44" s="23" t="inlineStr">
+    <row r="48" ht="18" customHeight="1">
+      <c r="A48" s="25" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="B48" s="25" t="n">
+        <v>35</v>
+      </c>
+      <c r="C48" s="26" t="inlineStr">
+        <is>
+          <t>한화솔루션</t>
+        </is>
+      </c>
+      <c r="D48" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="E48" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="F48" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G48" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H48" s="27" t="n">
+        <v>-7.75</v>
+      </c>
+      <c r="I48" s="28" t="n">
+        <v>9.32</v>
+      </c>
+      <c r="J48" s="29" t="inlineStr">
+        <is>
+          <t>중요공시 3건</t>
+        </is>
+      </c>
+      <c r="K48" s="29" t="inlineStr">
         <is>
           <t>공시</t>
         </is>
-      </c>
-    </row>
-    <row r="45" ht="18" customHeight="1">
-      <c r="A45" s="20" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="B45" s="20" t="n">
-        <v>32</v>
-      </c>
-      <c r="C45" s="21" t="inlineStr">
-        <is>
-          <t>한미반도체</t>
-        </is>
-      </c>
-      <c r="D45" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="E45" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="F45" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G45" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H45" s="22" t="n">
-        <v>-2.74</v>
-      </c>
-      <c r="I45" s="24" t="n">
-        <v>18.33</v>
-      </c>
-      <c r="J45" s="23" t="inlineStr">
-        <is>
-          <t>중요공시 2건 / 한국경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K45" s="23" t="inlineStr">
-        <is>
-          <t>공시</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="18" customHeight="1">
-      <c r="A46" s="20" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="B46" s="20" t="n">
-        <v>33</v>
-      </c>
-      <c r="C46" s="21" t="inlineStr">
-        <is>
-          <t>가온전선</t>
-        </is>
-      </c>
-      <c r="D46" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="E46" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="F46" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G46" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H46" s="24" t="n">
-        <v>29.9</v>
-      </c>
-      <c r="I46" s="24" t="n">
-        <v>8.949999999999999</v>
-      </c>
-      <c r="J46" s="23" t="inlineStr">
-        <is>
-          <t>중요공시 2건 / 매일경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K46" s="23" t="inlineStr">
-        <is>
-          <t>공시</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="18" customHeight="1">
-      <c r="A47" s="20" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="B47" s="20" t="n">
-        <v>34</v>
-      </c>
-      <c r="C47" s="21" t="inlineStr">
-        <is>
-          <t>현대차</t>
-        </is>
-      </c>
-      <c r="D47" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="E47" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="F47" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G47" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H47" s="22" t="n">
-        <v>-3.44</v>
-      </c>
-      <c r="I47" s="24" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="J47" s="23" t="inlineStr">
-        <is>
-          <t>매일경제 기사 언급 / 매일경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K47" s="23" t="n">
-        <v/>
-      </c>
-    </row>
-    <row r="48" ht="18" customHeight="1">
-      <c r="A48" s="20" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="B48" s="20" t="n">
-        <v>35</v>
-      </c>
-      <c r="C48" s="21" t="inlineStr">
-        <is>
-          <t>삼성전기</t>
-        </is>
-      </c>
-      <c r="D48" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="E48" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="F48" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G48" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H48" s="22" t="n">
-        <v>-0.78</v>
-      </c>
-      <c r="I48" s="24" t="n">
-        <v>12.58</v>
-      </c>
-      <c r="J48" s="23" t="inlineStr">
-        <is>
-          <t>매일경제 기사 언급 / 매일경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K48" s="23" t="n">
-        <v/>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1">
       <c r="A49" s="25" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B49" s="25" t="n">
@@ -2413,7 +2405,7 @@
       </c>
       <c r="C49" s="26" t="inlineStr">
         <is>
-          <t>JW신약</t>
+          <t>진원생명과학</t>
         </is>
       </c>
       <c r="D49" s="25" t="n">
@@ -2429,26 +2421,26 @@
         <v>0</v>
       </c>
       <c r="H49" s="27" t="n">
-        <v>29.87</v>
+        <v>-4.75</v>
       </c>
       <c r="I49" s="27" t="n">
-        <v>77.56999999999999</v>
-      </c>
-      <c r="J49" s="28" t="inlineStr">
-        <is>
-          <t>네이버 검색 당일 +306%</t>
-        </is>
-      </c>
-      <c r="K49" s="28" t="inlineStr">
-        <is>
-          <t>네이버</t>
+        <v>-8.17</v>
+      </c>
+      <c r="J49" s="29" t="inlineStr">
+        <is>
+          <t>중요공시 3건</t>
+        </is>
+      </c>
+      <c r="K49" s="29" t="inlineStr">
+        <is>
+          <t>공시</t>
         </is>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
       <c r="A50" s="25" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B50" s="25" t="n">
@@ -2456,7 +2448,7 @@
       </c>
       <c r="C50" s="26" t="inlineStr">
         <is>
-          <t>TS트릴리온</t>
+          <t>넥사다이내믹스</t>
         </is>
       </c>
       <c r="D50" s="25" t="n">
@@ -2471,27 +2463,27 @@
       <c r="G50" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H50" s="27" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="I50" s="27" t="n">
-        <v>33.45</v>
-      </c>
-      <c r="J50" s="28" t="inlineStr">
-        <is>
-          <t>네이버 검색 당일 +286%</t>
-        </is>
-      </c>
-      <c r="K50" s="28" t="inlineStr">
-        <is>
-          <t>네이버</t>
+      <c r="H50" s="28" t="n">
+        <v>16.18</v>
+      </c>
+      <c r="I50" s="28" t="n">
+        <v>14.52</v>
+      </c>
+      <c r="J50" s="29" t="inlineStr">
+        <is>
+          <t>중요공시 3건</t>
+        </is>
+      </c>
+      <c r="K50" s="29" t="inlineStr">
+        <is>
+          <t>공시</t>
         </is>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
       <c r="A51" s="25" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B51" s="25" t="n">
@@ -2499,7 +2491,7 @@
       </c>
       <c r="C51" s="26" t="inlineStr">
         <is>
-          <t>삼익제약</t>
+          <t>스피어</t>
         </is>
       </c>
       <c r="D51" s="25" t="n">
@@ -2515,26 +2507,26 @@
         <v>0</v>
       </c>
       <c r="H51" s="27" t="n">
-        <v>6.02</v>
+        <v>-9.5</v>
       </c>
       <c r="I51" s="27" t="n">
-        <v>21.38</v>
-      </c>
-      <c r="J51" s="28" t="inlineStr">
-        <is>
-          <t>네이버 검색 당일 +208%</t>
-        </is>
-      </c>
-      <c r="K51" s="28" t="inlineStr">
-        <is>
-          <t>네이버</t>
+        <v>-29.48</v>
+      </c>
+      <c r="J51" s="29" t="inlineStr">
+        <is>
+          <t>중요공시 3건</t>
+        </is>
+      </c>
+      <c r="K51" s="29" t="inlineStr">
+        <is>
+          <t>공시</t>
         </is>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1">
       <c r="A52" s="25" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B52" s="25" t="n">
@@ -2542,7 +2534,7 @@
       </c>
       <c r="C52" s="26" t="inlineStr">
         <is>
-          <t>한국전력</t>
+          <t>LB세미콘</t>
         </is>
       </c>
       <c r="D52" s="25" t="n">
@@ -2558,24 +2550,26 @@
         <v>0</v>
       </c>
       <c r="H52" s="27" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="I52" s="27" t="n">
-        <v>11.26</v>
-      </c>
-      <c r="J52" s="28" t="inlineStr">
-        <is>
-          <t>한국경제 헤드라인 언급 / 매일경제 기사 언급</t>
-        </is>
-      </c>
-      <c r="K52" s="28" t="n">
-        <v/>
+        <v>-0.19</v>
+      </c>
+      <c r="I52" s="28" t="n">
+        <v>14.94</v>
+      </c>
+      <c r="J52" s="29" t="inlineStr">
+        <is>
+          <t>중요공시 3건</t>
+        </is>
+      </c>
+      <c r="K52" s="29" t="inlineStr">
+        <is>
+          <t>공시</t>
+        </is>
       </c>
     </row>
     <row r="53" ht="18" customHeight="1">
       <c r="A53" s="25" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B53" s="25" t="n">
@@ -2583,7 +2577,7 @@
       </c>
       <c r="C53" s="26" t="inlineStr">
         <is>
-          <t>후성</t>
+          <t>피노</t>
         </is>
       </c>
       <c r="D53" s="25" t="n">
@@ -2598,25 +2592,27 @@
       <c r="G53" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H53" s="29" t="n">
-        <v>-8.44</v>
+      <c r="H53" s="28" t="n">
+        <v>1.91</v>
       </c>
       <c r="I53" s="27" t="n">
-        <v>8.25</v>
-      </c>
-      <c r="J53" s="28" t="inlineStr">
-        <is>
-          <t>한국경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K53" s="28" t="n">
-        <v/>
+        <v>-5.43</v>
+      </c>
+      <c r="J53" s="29" t="inlineStr">
+        <is>
+          <t>중요공시 3건</t>
+        </is>
+      </c>
+      <c r="K53" s="29" t="inlineStr">
+        <is>
+          <t>공시</t>
+        </is>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
       <c r="A54" s="25" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B54" s="25" t="n">
@@ -2624,33 +2620,33 @@
       </c>
       <c r="C54" s="26" t="inlineStr">
         <is>
-          <t>한화솔루션</t>
+          <t>HJ중공업</t>
         </is>
       </c>
       <c r="D54" s="25" t="n">
         <v>3</v>
       </c>
       <c r="E54" s="25" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F54" s="25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G54" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H54" s="29" t="n">
-        <v>-2.13</v>
-      </c>
-      <c r="I54" s="27" t="n">
-        <v>19.63</v>
-      </c>
-      <c r="J54" s="28" t="inlineStr">
-        <is>
-          <t>중요공시 3건</t>
-        </is>
-      </c>
-      <c r="K54" s="28" t="inlineStr">
+      <c r="H54" s="27" t="n">
+        <v>-3.14</v>
+      </c>
+      <c r="I54" s="28" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="J54" s="29" t="inlineStr">
+        <is>
+          <t>중요공시 2건 / 중요공시 3일 +100%</t>
+        </is>
+      </c>
+      <c r="K54" s="29" t="inlineStr">
         <is>
           <t>공시</t>
         </is>
@@ -2659,7 +2655,7 @@
     <row r="55" ht="18" customHeight="1">
       <c r="A55" s="25" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B55" s="25" t="n">
@@ -2667,7 +2663,7 @@
       </c>
       <c r="C55" s="26" t="inlineStr">
         <is>
-          <t>LB세미콘</t>
+          <t>현대모비스</t>
         </is>
       </c>
       <c r="D55" s="25" t="n">
@@ -2683,26 +2679,24 @@
         <v>0</v>
       </c>
       <c r="H55" s="27" t="n">
-        <v>4.72</v>
-      </c>
-      <c r="I55" s="27" t="n">
-        <v>29.37</v>
-      </c>
-      <c r="J55" s="28" t="inlineStr">
-        <is>
-          <t>중요공시 3건</t>
-        </is>
-      </c>
-      <c r="K55" s="28" t="inlineStr">
-        <is>
-          <t>공시</t>
-        </is>
+        <v>-4.44</v>
+      </c>
+      <c r="I55" s="28" t="n">
+        <v>4.69</v>
+      </c>
+      <c r="J55" s="29" t="inlineStr">
+        <is>
+          <t>매일경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K55" s="29" t="n">
+        <v/>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1">
       <c r="A56" s="25" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B56" s="25" t="n">
@@ -2710,7 +2704,7 @@
       </c>
       <c r="C56" s="26" t="inlineStr">
         <is>
-          <t>피노</t>
+          <t>한전기술</t>
         </is>
       </c>
       <c r="D56" s="25" t="n">
@@ -2725,27 +2719,25 @@
       <c r="G56" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H56" s="27" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="I56" s="29" t="n">
-        <v>-3.06</v>
-      </c>
-      <c r="J56" s="28" t="inlineStr">
-        <is>
-          <t>중요공시 3건</t>
-        </is>
-      </c>
-      <c r="K56" s="28" t="inlineStr">
-        <is>
-          <t>공시</t>
-        </is>
+      <c r="H56" s="28" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="I56" s="28" t="n">
+        <v>17.44</v>
+      </c>
+      <c r="J56" s="29" t="inlineStr">
+        <is>
+          <t>매일경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K56" s="29" t="n">
+        <v/>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1">
       <c r="A57" s="25" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B57" s="25" t="n">
@@ -2753,7 +2745,7 @@
       </c>
       <c r="C57" s="26" t="inlineStr">
         <is>
-          <t>모아데이타</t>
+          <t>현대제철</t>
         </is>
       </c>
       <c r="D57" s="25" t="n">
@@ -2769,26 +2761,24 @@
         <v>0</v>
       </c>
       <c r="H57" s="27" t="n">
-        <v>5.14</v>
-      </c>
-      <c r="I57" s="27" t="n">
-        <v>5.59</v>
-      </c>
-      <c r="J57" s="28" t="inlineStr">
-        <is>
-          <t>중요공시 3건</t>
-        </is>
-      </c>
-      <c r="K57" s="28" t="inlineStr">
-        <is>
-          <t>공시</t>
-        </is>
+        <v>-4.44</v>
+      </c>
+      <c r="I57" s="28" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="J57" s="29" t="inlineStr">
+        <is>
+          <t>매일경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K57" s="29" t="n">
+        <v/>
       </c>
     </row>
     <row r="58" ht="18" customHeight="1">
       <c r="A58" s="25" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B58" s="25" t="n">
@@ -2796,42 +2786,40 @@
       </c>
       <c r="C58" s="26" t="inlineStr">
         <is>
-          <t>엑셈</t>
+          <t>피스피스스튜디오</t>
         </is>
       </c>
       <c r="D58" s="25" t="n">
         <v>3</v>
       </c>
       <c r="E58" s="25" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F58" s="25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G58" s="25" t="n">
         <v>0</v>
       </c>
       <c r="H58" s="27" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="I58" s="29" t="n">
-        <v>-9.25</v>
-      </c>
-      <c r="J58" s="28" t="inlineStr">
-        <is>
-          <t>중요공시 2건 / 중요공시 3일 +100%</t>
-        </is>
-      </c>
-      <c r="K58" s="28" t="inlineStr">
-        <is>
-          <t>공시</t>
-        </is>
+        <v>-7.95</v>
+      </c>
+      <c r="I58" s="27" t="n">
+        <v>-17.94</v>
+      </c>
+      <c r="J58" s="29" t="inlineStr">
+        <is>
+          <t>한국경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K58" s="29" t="n">
+        <v/>
       </c>
     </row>
     <row r="59" ht="18" customHeight="1">
       <c r="A59" s="25" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B59" s="25" t="n">
@@ -2839,42 +2827,40 @@
       </c>
       <c r="C59" s="26" t="inlineStr">
         <is>
-          <t>파두</t>
+          <t>이차전지</t>
         </is>
       </c>
       <c r="D59" s="25" t="n">
         <v>3</v>
       </c>
       <c r="E59" s="25" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F59" s="25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G59" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H59" s="27" t="n">
-        <v>5.05</v>
-      </c>
-      <c r="I59" s="27" t="n">
-        <v>6.43</v>
-      </c>
-      <c r="J59" s="28" t="inlineStr">
-        <is>
-          <t>중요공시 2건 / 중요공시 3일 +100%</t>
-        </is>
-      </c>
-      <c r="K59" s="28" t="inlineStr">
-        <is>
-          <t>공시</t>
-        </is>
+      <c r="H59" s="25" t="n">
+        <v/>
+      </c>
+      <c r="I59" s="25" t="n">
+        <v/>
+      </c>
+      <c r="J59" s="29" t="inlineStr">
+        <is>
+          <t>한국경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K59" s="29" t="n">
+        <v/>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1">
       <c r="A60" s="25" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B60" s="25" t="n">
@@ -2882,42 +2868,40 @@
       </c>
       <c r="C60" s="26" t="inlineStr">
         <is>
-          <t>삼보산업</t>
+          <t>SK스퀘어</t>
         </is>
       </c>
       <c r="D60" s="25" t="n">
         <v>3</v>
       </c>
       <c r="E60" s="25" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F60" s="25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G60" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H60" s="27" t="n">
-        <v>10.7</v>
-      </c>
-      <c r="I60" s="29" t="n">
-        <v>-3.23</v>
-      </c>
-      <c r="J60" s="28" t="inlineStr">
-        <is>
-          <t>중요공시 2건 / 중요공시 3일 +100%</t>
-        </is>
-      </c>
-      <c r="K60" s="28" t="inlineStr">
-        <is>
-          <t>공시</t>
-        </is>
+      <c r="H60" s="28" t="n">
+        <v>6.52</v>
+      </c>
+      <c r="I60" s="28" t="n">
+        <v>38.44</v>
+      </c>
+      <c r="J60" s="29" t="inlineStr">
+        <is>
+          <t>매일경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K60" s="29" t="n">
+        <v/>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
       <c r="A61" s="25" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B61" s="25" t="n">
@@ -2925,42 +2909,40 @@
       </c>
       <c r="C61" s="26" t="inlineStr">
         <is>
-          <t>페니트리움바이오</t>
+          <t>넷마블</t>
         </is>
       </c>
       <c r="D61" s="25" t="n">
         <v>3</v>
       </c>
       <c r="E61" s="25" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F61" s="25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G61" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H61" s="29" t="n">
-        <v>-0.45</v>
+      <c r="H61" s="27" t="n">
+        <v>-3.12</v>
       </c>
       <c r="I61" s="27" t="n">
-        <v>6.06</v>
-      </c>
-      <c r="J61" s="28" t="inlineStr">
-        <is>
-          <t>중요공시 2건 / 중요공시 3일 +100%</t>
-        </is>
-      </c>
-      <c r="K61" s="28" t="inlineStr">
-        <is>
-          <t>공시</t>
-        </is>
+        <v>-6.27</v>
+      </c>
+      <c r="J61" s="29" t="inlineStr">
+        <is>
+          <t>매일경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K61" s="29" t="n">
+        <v/>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1">
       <c r="A62" s="25" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B62" s="25" t="n">
@@ -2968,7 +2950,7 @@
       </c>
       <c r="C62" s="26" t="inlineStr">
         <is>
-          <t>젬백스</t>
+          <t>엔터</t>
         </is>
       </c>
       <c r="D62" s="25" t="n">
@@ -2983,27 +2965,25 @@
       <c r="G62" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H62" s="27" t="n">
-        <v>4.38</v>
-      </c>
-      <c r="I62" s="27" t="n">
-        <v>10.08</v>
-      </c>
-      <c r="J62" s="28" t="inlineStr">
-        <is>
-          <t>중요공시 1건 / 한국경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K62" s="28" t="inlineStr">
-        <is>
-          <t>공시</t>
-        </is>
+      <c r="H62" s="25" t="n">
+        <v/>
+      </c>
+      <c r="I62" s="25" t="n">
+        <v/>
+      </c>
+      <c r="J62" s="29" t="inlineStr">
+        <is>
+          <t>매일경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K62" s="29" t="n">
+        <v/>
       </c>
     </row>
     <row r="63" ht="18" customHeight="1">
       <c r="A63" s="25" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B63" s="25" t="n">
@@ -3011,14 +2991,14 @@
       </c>
       <c r="C63" s="26" t="inlineStr">
         <is>
-          <t>올릭스</t>
+          <t>삼화전자</t>
         </is>
       </c>
       <c r="D63" s="25" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E63" s="25" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F63" s="25" t="n">
         <v>0</v>
@@ -3026,18 +3006,18 @@
       <c r="G63" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H63" s="27" t="n">
-        <v>9.82</v>
-      </c>
-      <c r="I63" s="27" t="n">
-        <v>15.26</v>
-      </c>
-      <c r="J63" s="28" t="inlineStr">
-        <is>
-          <t>네이버뉴스 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K63" s="28" t="inlineStr">
+      <c r="H63" s="28" t="n">
+        <v>29.86</v>
+      </c>
+      <c r="I63" s="28" t="n">
+        <v>70</v>
+      </c>
+      <c r="J63" s="29" t="inlineStr">
+        <is>
+          <t>네이버 검색 당일 +96%</t>
+        </is>
+      </c>
+      <c r="K63" s="29" t="inlineStr">
         <is>
           <t>네이버</t>
         </is>
@@ -3136,22 +3116,22 @@
         <v>1</v>
       </c>
       <c r="C3" s="25" t="n">
-        <v>57</v>
+        <v>85</v>
       </c>
       <c r="D3" s="25" t="n">
-        <v>57</v>
+        <v>85</v>
       </c>
       <c r="E3" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F3" s="25" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G3" s="25" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="H3" s="25" t="n"/>
@@ -3160,106 +3140,106 @@
     <row r="4" ht="18" customHeight="1">
       <c r="A4" s="26" t="inlineStr">
         <is>
-          <t>LG</t>
+          <t>SK</t>
         </is>
       </c>
       <c r="B4" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C4" s="25" t="n">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="D4" s="25" t="n">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="E4" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F4" s="25" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G4" s="25" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="H4" s="29" t="n">
-        <v>-1.4</v>
-      </c>
-      <c r="I4" s="27" t="n">
-        <v>3.5</v>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="H4" s="27" t="n">
+        <v>-2.97</v>
+      </c>
+      <c r="I4" s="28" t="n">
+        <v>19.48</v>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="26" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B5" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C5" s="25" t="n">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D5" s="25" t="n">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="E5" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F5" s="25" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G5" s="25" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="H5" s="27" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="I5" s="27" t="n">
-        <v>14.55</v>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="H5" s="28" t="n">
+        <v>6.51</v>
+      </c>
+      <c r="I5" s="28" t="n">
+        <v>27.8</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
       <c r="A6" s="26" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B6" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C6" s="25" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D6" s="25" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="E6" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F6" s="25" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G6" s="25" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="H6" s="27" t="n">
-        <v>5.84</v>
-      </c>
-      <c r="I6" s="27" t="n">
-        <v>23.1</v>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="H6" s="28" t="n">
+        <v>4.62</v>
+      </c>
+      <c r="I6" s="28" t="n">
+        <v>21.24</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
@@ -3272,22 +3252,22 @@
         <v>1</v>
       </c>
       <c r="C7" s="25" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D7" s="25" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E7" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F7" s="25" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G7" s="25" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="H7" s="25" t="n"/>
@@ -3296,64 +3276,60 @@
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="26" t="inlineStr">
         <is>
-          <t>미래에셋증권</t>
+          <t>바이오</t>
         </is>
       </c>
       <c r="B8" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C8" s="25" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D8" s="25" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E8" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F8" s="25" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G8" s="25" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="H8" s="29" t="n">
-        <v>-1.75</v>
-      </c>
-      <c r="I8" s="29" t="n">
-        <v>-1.56</v>
-      </c>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="H8" s="25" t="n"/>
+      <c r="I8" s="25" t="n"/>
     </row>
     <row r="9" ht="18" customHeight="1">
       <c r="A9" s="26" t="inlineStr">
         <is>
-          <t>바이오</t>
+          <t>인공지능</t>
         </is>
       </c>
       <c r="B9" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C9" s="25" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D9" s="25" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E9" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F9" s="25" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G9" s="25" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="H9" s="25" t="n"/>
@@ -3362,29 +3338,29 @@
     <row r="10" ht="18" customHeight="1">
       <c r="A10" s="26" t="inlineStr">
         <is>
-          <t>인공지능</t>
+          <t>제약</t>
         </is>
       </c>
       <c r="B10" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C10" s="25" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D10" s="25" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E10" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F10" s="25" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G10" s="25" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="H10" s="25" t="n"/>
@@ -3393,73 +3369,77 @@
     <row r="11" ht="18" customHeight="1">
       <c r="A11" s="26" t="inlineStr">
         <is>
-          <t>SK스퀘어</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="B11" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C11" s="25" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D11" s="25" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E11" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F11" s="25" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G11" s="25" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="H11" s="27" t="n">
-        <v>6.33</v>
-      </c>
-      <c r="I11" s="27" t="n">
-        <v>34.91</v>
+        <v>-5.64</v>
+      </c>
+      <c r="I11" s="28" t="n">
+        <v>18.59</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
       <c r="A12" s="26" t="inlineStr">
         <is>
-          <t>조선</t>
+          <t>넥써쓰</t>
         </is>
       </c>
       <c r="B12" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C12" s="25" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D12" s="25" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E12" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F12" s="25" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G12" s="25" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="H12" s="25" t="n"/>
-      <c r="I12" s="25" t="n"/>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="H12" s="28" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="I12" s="28" t="n">
+        <v>28.71</v>
+      </c>
     </row>
     <row r="13" ht="18" customHeight="1">
       <c r="A13" s="26" t="inlineStr">
         <is>
-          <t>한솔테크닉스</t>
+          <t>전기차</t>
         </is>
       </c>
       <c r="B13" s="25" t="n">
@@ -3476,25 +3456,21 @@
       </c>
       <c r="F13" s="25" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G13" s="25" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="H13" s="27" t="n">
-        <v>30</v>
-      </c>
-      <c r="I13" s="27" t="n">
-        <v>41.51</v>
-      </c>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="H13" s="25" t="n"/>
+      <c r="I13" s="25" t="n"/>
     </row>
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="26" t="inlineStr">
         <is>
-          <t>제약</t>
+          <t>미래에셋증권</t>
         </is>
       </c>
       <c r="B14" s="25" t="n">
@@ -3511,56 +3487,56 @@
       </c>
       <c r="F14" s="25" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G14" s="25" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="H14" s="25" t="n"/>
-      <c r="I14" s="25" t="n"/>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="H14" s="28" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="I14" s="27" t="n">
+        <v>-0.78</v>
+      </c>
     </row>
     <row r="15" ht="18" customHeight="1">
       <c r="A15" s="26" t="inlineStr">
         <is>
-          <t>LG이노텍</t>
+          <t>방산</t>
         </is>
       </c>
       <c r="B15" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C15" s="25" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D15" s="25" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E15" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F15" s="25" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G15" s="25" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="H15" s="27" t="n">
-        <v>0.97</v>
-      </c>
-      <c r="I15" s="27" t="n">
-        <v>14.5</v>
-      </c>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="H15" s="25" t="n"/>
+      <c r="I15" s="25" t="n"/>
     </row>
     <row r="16" ht="18" customHeight="1">
       <c r="A16" s="26" t="inlineStr">
         <is>
-          <t>기아</t>
+          <t>가온전선</t>
         </is>
       </c>
       <c r="B16" s="25" t="n">
@@ -3577,25 +3553,25 @@
       </c>
       <c r="F16" s="25" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G16" s="25" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="H16" s="29" t="n">
-        <v>-2.29</v>
-      </c>
-      <c r="I16" s="27" t="n">
-        <v>4.13</v>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="H16" s="28" t="n">
+        <v>13.05</v>
+      </c>
+      <c r="I16" s="28" t="n">
+        <v>18.98</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
       <c r="A17" s="26" t="inlineStr">
         <is>
-          <t>로봇</t>
+          <t>삼성전기</t>
         </is>
       </c>
       <c r="B17" s="25" t="n">
@@ -3612,52 +3588,60 @@
       </c>
       <c r="F17" s="25" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G17" s="25" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="H17" s="25" t="n"/>
-      <c r="I17" s="25" t="n"/>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="H17" s="28" t="n">
+        <v>8.27</v>
+      </c>
+      <c r="I17" s="28" t="n">
+        <v>21.88</v>
+      </c>
     </row>
     <row r="18" ht="18" customHeight="1">
       <c r="A18" s="26" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>카카오</t>
         </is>
       </c>
       <c r="B18" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C18" s="25" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D18" s="25" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E18" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F18" s="25" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G18" s="25" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="H18" s="25" t="n"/>
-      <c r="I18" s="25" t="n"/>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="H18" s="27" t="n">
+        <v>-3.08</v>
+      </c>
+      <c r="I18" s="25" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19" ht="18" customHeight="1">
       <c r="A19" s="26" t="inlineStr">
         <is>
-          <t>게임</t>
+          <t>LG</t>
         </is>
       </c>
       <c r="B19" s="25" t="n">
@@ -3674,21 +3658,25 @@
       </c>
       <c r="F19" s="25" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G19" s="25" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="H19" s="25" t="n"/>
-      <c r="I19" s="25" t="n"/>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="H19" s="27" t="n">
+        <v>-2.31</v>
+      </c>
+      <c r="I19" s="28" t="n">
+        <v>2.23</v>
+      </c>
     </row>
     <row r="20" ht="18" customHeight="1">
       <c r="A20" s="26" t="inlineStr">
         <is>
-          <t>모바일어플라이언스</t>
+          <t>대한항공</t>
         </is>
       </c>
       <c r="B20" s="25" t="n">
@@ -3705,25 +3693,25 @@
       </c>
       <c r="F20" s="25" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G20" s="25" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="H20" s="29" t="n">
-        <v>-6.28</v>
-      </c>
-      <c r="I20" s="29" t="n">
-        <v>-15.26</v>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="H20" s="28" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="I20" s="28" t="n">
+        <v>16.33</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
       <c r="A21" s="26" t="inlineStr">
         <is>
-          <t>알엔티엑스</t>
+          <t>철강</t>
         </is>
       </c>
       <c r="B21" s="25" t="n">
@@ -3740,25 +3728,21 @@
       </c>
       <c r="F21" s="25" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G21" s="25" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="H21" s="27" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="I21" s="29" t="n">
-        <v>-10</v>
-      </c>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="H21" s="25" t="n"/>
+      <c r="I21" s="25" t="n"/>
     </row>
     <row r="22" ht="18" customHeight="1">
       <c r="A22" s="26" t="inlineStr">
         <is>
-          <t>철강</t>
+          <t>현대차</t>
         </is>
       </c>
       <c r="B22" s="25" t="n">
@@ -3775,91 +3759,91 @@
       </c>
       <c r="F22" s="25" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G22" s="25" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="H22" s="25" t="n"/>
-      <c r="I22" s="25" t="n"/>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="H22" s="27" t="n">
+        <v>-2.75</v>
+      </c>
+      <c r="I22" s="28" t="n">
+        <v>0.67</v>
+      </c>
     </row>
     <row r="23" ht="18" customHeight="1">
       <c r="A23" s="26" t="inlineStr">
         <is>
-          <t>하이브</t>
+          <t>기아</t>
         </is>
       </c>
       <c r="B23" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C23" s="25" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D23" s="25" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E23" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F23" s="25" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G23" s="25" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="H23" s="27" t="n">
-        <v>5.61</v>
-      </c>
-      <c r="I23" s="27" t="n">
-        <v>14.88</v>
+        <v>-4.51</v>
+      </c>
+      <c r="I23" s="28" t="n">
+        <v>1.79</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
       <c r="A24" s="26" t="inlineStr">
         <is>
-          <t>한솔홀딩스</t>
+          <t>로봇</t>
         </is>
       </c>
       <c r="B24" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C24" s="25" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D24" s="25" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E24" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F24" s="25" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G24" s="25" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="H24" s="27" t="n">
-        <v>3.57</v>
-      </c>
-      <c r="I24" s="27" t="n">
-        <v>6.46</v>
-      </c>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="H24" s="25" t="n"/>
+      <c r="I24" s="25" t="n"/>
     </row>
     <row r="25" ht="18" customHeight="1">
       <c r="A25" s="26" t="inlineStr">
         <is>
-          <t>LG전자</t>
+          <t>조선</t>
         </is>
       </c>
       <c r="B25" s="25" t="n">
@@ -3876,25 +3860,21 @@
       </c>
       <c r="F25" s="25" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G25" s="25" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="H25" s="27" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="I25" s="27" t="n">
-        <v>4.69</v>
-      </c>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="H25" s="25" t="n"/>
+      <c r="I25" s="25" t="n"/>
     </row>
     <row r="26" ht="18" customHeight="1">
       <c r="A26" s="26" t="inlineStr">
         <is>
-          <t>미래에셋벤처투자</t>
+          <t>파두</t>
         </is>
       </c>
       <c r="B26" s="25" t="n">
@@ -3911,406 +3891,410 @@
       </c>
       <c r="F26" s="25" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G26" s="25" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="H26" s="29" t="n">
-        <v>-8.720000000000001</v>
-      </c>
-      <c r="I26" s="29" t="n">
-        <v>-31.05</v>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="H26" s="27" t="n">
+        <v>-1.89</v>
+      </c>
+      <c r="I26" s="28" t="n">
+        <v>4.73</v>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
       <c r="A27" s="26" t="inlineStr">
         <is>
-          <t>미래에셋생명</t>
+          <t>삼성SDI</t>
         </is>
       </c>
       <c r="B27" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C27" s="25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D27" s="25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E27" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F27" s="25" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G27" s="25" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="H27" s="29" t="n">
-        <v>-5.12</v>
-      </c>
-      <c r="I27" s="27" t="n">
-        <v>35.4</v>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="H27" s="27" t="n">
+        <v>-5.09</v>
+      </c>
+      <c r="I27" s="28" t="n">
+        <v>4.71</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
       <c r="A28" s="26" t="inlineStr">
         <is>
-          <t>미래에셋증권2우B</t>
+          <t>일성건설</t>
         </is>
       </c>
       <c r="B28" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C28" s="25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D28" s="25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E28" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F28" s="25" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G28" s="25" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="H28" s="29" t="n">
-        <v>-2.58</v>
-      </c>
-      <c r="I28" s="29" t="n">
-        <v>-0.87</v>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="H28" s="28" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="I28" s="28" t="n">
+        <v>48.92</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
       <c r="A29" s="26" t="inlineStr">
         <is>
-          <t>방산</t>
+          <t>HJ중공업</t>
         </is>
       </c>
       <c r="B29" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C29" s="25" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D29" s="25" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E29" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F29" s="25" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G29" s="25" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="H29" s="25" t="n"/>
-      <c r="I29" s="25" t="n"/>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="H29" s="27" t="n">
+        <v>-3.14</v>
+      </c>
+      <c r="I29" s="28" t="n">
+        <v>11.3</v>
+      </c>
     </row>
     <row r="30" ht="18" customHeight="1">
       <c r="A30" s="26" t="inlineStr">
         <is>
-          <t>KBI메탈</t>
+          <t>JW신약</t>
         </is>
       </c>
       <c r="B30" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C30" s="25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D30" s="25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E30" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F30" s="25" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G30" s="25" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="H30" s="27" t="n">
-        <v>16.42</v>
-      </c>
-      <c r="I30" s="27" t="n">
-        <v>18.8</v>
+        <v>-11.56</v>
+      </c>
+      <c r="I30" s="28" t="n">
+        <v>58.72</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
       <c r="A31" s="26" t="inlineStr">
         <is>
-          <t>가온전선</t>
+          <t>LB세미콘</t>
         </is>
       </c>
       <c r="B31" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C31" s="25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D31" s="25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E31" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F31" s="25" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G31" s="25" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="H31" s="27" t="n">
-        <v>29.9</v>
-      </c>
-      <c r="I31" s="27" t="n">
-        <v>8.949999999999999</v>
+        <v>-0.19</v>
+      </c>
+      <c r="I31" s="28" t="n">
+        <v>14.94</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
       <c r="A32" s="26" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>SK스퀘어</t>
         </is>
       </c>
       <c r="B32" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C32" s="25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D32" s="25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E32" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F32" s="25" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G32" s="25" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="H32" s="29" t="n">
-        <v>-9.65</v>
-      </c>
-      <c r="I32" s="27" t="n">
-        <v>19.52</v>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="H32" s="28" t="n">
+        <v>6.52</v>
+      </c>
+      <c r="I32" s="28" t="n">
+        <v>38.44</v>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
       <c r="A33" s="26" t="inlineStr">
         <is>
-          <t>디앤디파마텍</t>
+          <t>TS트릴리온</t>
         </is>
       </c>
       <c r="B33" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C33" s="25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D33" s="25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E33" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F33" s="25" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G33" s="25" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="H33" s="27" t="n">
-        <v>18.01</v>
-      </c>
-      <c r="I33" s="27" t="n">
-        <v>24.4</v>
+        <v>-8.75</v>
+      </c>
+      <c r="I33" s="28" t="n">
+        <v>21.49</v>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
       <c r="A34" s="26" t="inlineStr">
         <is>
-          <t>삼성전기</t>
+          <t>강동씨앤엘</t>
         </is>
       </c>
       <c r="B34" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C34" s="25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D34" s="25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E34" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F34" s="25" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G34" s="25" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="H34" s="29" t="n">
-        <v>-0.78</v>
-      </c>
-      <c r="I34" s="27" t="n">
-        <v>12.58</v>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="H34" s="28" t="n">
+        <v>30</v>
+      </c>
+      <c r="I34" s="28" t="n">
+        <v>77.05</v>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
       <c r="A35" s="26" t="inlineStr">
         <is>
-          <t>한미반도체</t>
+          <t>넥사다이내믹스</t>
         </is>
       </c>
       <c r="B35" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C35" s="25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D35" s="25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E35" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F35" s="25" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G35" s="25" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="H35" s="29" t="n">
-        <v>-2.74</v>
-      </c>
-      <c r="I35" s="27" t="n">
-        <v>18.33</v>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="H35" s="28" t="n">
+        <v>16.18</v>
+      </c>
+      <c r="I35" s="28" t="n">
+        <v>14.52</v>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
       <c r="A36" s="26" t="inlineStr">
         <is>
-          <t>현대약품</t>
+          <t>넷마블</t>
         </is>
       </c>
       <c r="B36" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C36" s="25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D36" s="25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E36" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F36" s="25" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G36" s="25" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="H36" s="27" t="n">
-        <v>6.71</v>
+        <v>-3.12</v>
       </c>
       <c r="I36" s="27" t="n">
-        <v>45.08</v>
+        <v>-6.27</v>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
       <c r="A37" s="26" t="inlineStr">
         <is>
-          <t>현대차</t>
+          <t>삼보산업</t>
         </is>
       </c>
       <c r="B37" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C37" s="25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D37" s="25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E37" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F37" s="25" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G37" s="25" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="H37" s="29" t="n">
-        <v>-3.44</v>
-      </c>
-      <c r="I37" s="27" t="n">
-        <v>2.66</v>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="H37" s="28" t="n">
+        <v>30</v>
+      </c>
+      <c r="I37" s="28" t="n">
+        <v>38.54</v>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
       <c r="A38" s="26" t="inlineStr">
         <is>
-          <t>JW신약</t>
+          <t>스피어</t>
         </is>
       </c>
       <c r="B38" s="25" t="n">
@@ -4327,25 +4311,25 @@
       </c>
       <c r="F38" s="25" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G38" s="25" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="H38" s="27" t="n">
-        <v>29.87</v>
+        <v>-9.5</v>
       </c>
       <c r="I38" s="27" t="n">
-        <v>77.56999999999999</v>
+        <v>-29.48</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
       <c r="A39" s="26" t="inlineStr">
         <is>
-          <t>LB세미콘</t>
+          <t>엔터</t>
         </is>
       </c>
       <c r="B39" s="25" t="n">
@@ -4362,25 +4346,21 @@
       </c>
       <c r="F39" s="25" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G39" s="25" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="H39" s="27" t="n">
-        <v>4.72</v>
-      </c>
-      <c r="I39" s="27" t="n">
-        <v>29.37</v>
-      </c>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="H39" s="25" t="n"/>
+      <c r="I39" s="25" t="n"/>
     </row>
     <row r="40" ht="18" customHeight="1">
       <c r="A40" s="26" t="inlineStr">
         <is>
-          <t>TS트릴리온</t>
+          <t>위더스제약</t>
         </is>
       </c>
       <c r="B40" s="25" t="n">
@@ -4397,25 +4377,25 @@
       </c>
       <c r="F40" s="25" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G40" s="25" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="H40" s="27" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="I40" s="27" t="n">
-        <v>33.45</v>
+        <v>-5.11</v>
+      </c>
+      <c r="I40" s="28" t="n">
+        <v>18.36</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
       <c r="A41" s="26" t="inlineStr">
         <is>
-          <t>모아데이타</t>
+          <t>이차전지</t>
         </is>
       </c>
       <c r="B41" s="25" t="n">
@@ -4432,25 +4412,21 @@
       </c>
       <c r="F41" s="25" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G41" s="25" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="H41" s="27" t="n">
-        <v>5.14</v>
-      </c>
-      <c r="I41" s="27" t="n">
-        <v>5.59</v>
-      </c>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="H41" s="25" t="n"/>
+      <c r="I41" s="25" t="n"/>
     </row>
     <row r="42" ht="18" customHeight="1">
       <c r="A42" s="26" t="inlineStr">
         <is>
-          <t>삼보산업</t>
+          <t>진원생명과학</t>
         </is>
       </c>
       <c r="B42" s="25" t="n">
@@ -4467,25 +4443,25 @@
       </c>
       <c r="F42" s="25" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G42" s="25" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="H42" s="27" t="n">
-        <v>10.7</v>
-      </c>
-      <c r="I42" s="29" t="n">
-        <v>-3.23</v>
+        <v>-4.75</v>
+      </c>
+      <c r="I42" s="27" t="n">
+        <v>-8.17</v>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1">
       <c r="A43" s="26" t="inlineStr">
         <is>
-          <t>삼익제약</t>
+          <t>피노</t>
         </is>
       </c>
       <c r="B43" s="25" t="n">
@@ -4502,25 +4478,25 @@
       </c>
       <c r="F43" s="25" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G43" s="25" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="H43" s="27" t="n">
-        <v>6.02</v>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="H43" s="28" t="n">
+        <v>1.91</v>
       </c>
       <c r="I43" s="27" t="n">
-        <v>21.38</v>
+        <v>-5.43</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
       <c r="A44" s="26" t="inlineStr">
         <is>
-          <t>엑셈</t>
+          <t>피스피스스튜디오</t>
         </is>
       </c>
       <c r="B44" s="25" t="n">
@@ -4537,25 +4513,25 @@
       </c>
       <c r="F44" s="25" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G44" s="25" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="H44" s="27" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="I44" s="29" t="n">
-        <v>-9.25</v>
+        <v>-7.95</v>
+      </c>
+      <c r="I44" s="27" t="n">
+        <v>-17.94</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
       <c r="A45" s="26" t="inlineStr">
         <is>
-          <t>올릭스</t>
+          <t>하이스틸</t>
         </is>
       </c>
       <c r="B45" s="25" t="n">
@@ -4572,25 +4548,25 @@
       </c>
       <c r="F45" s="25" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G45" s="25" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="H45" s="27" t="n">
-        <v>9.82</v>
-      </c>
-      <c r="I45" s="27" t="n">
-        <v>15.26</v>
+        <v>-1.7</v>
+      </c>
+      <c r="I45" s="28" t="n">
+        <v>14.95</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
       <c r="A46" s="26" t="inlineStr">
         <is>
-          <t>젬백스</t>
+          <t>한솔테크닉스</t>
         </is>
       </c>
       <c r="B46" s="25" t="n">
@@ -4607,25 +4583,25 @@
       </c>
       <c r="F46" s="25" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G46" s="25" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="H46" s="27" t="n">
-        <v>4.38</v>
-      </c>
-      <c r="I46" s="27" t="n">
-        <v>10.08</v>
+        <v>-10.37</v>
+      </c>
+      <c r="I46" s="28" t="n">
+        <v>19.15</v>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
       <c r="A47" s="26" t="inlineStr">
         <is>
-          <t>파두</t>
+          <t>한전기술</t>
         </is>
       </c>
       <c r="B47" s="25" t="n">
@@ -4642,25 +4618,25 @@
       </c>
       <c r="F47" s="25" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G47" s="25" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="H47" s="27" t="n">
-        <v>5.05</v>
-      </c>
-      <c r="I47" s="27" t="n">
-        <v>6.43</v>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="H47" s="28" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="I47" s="28" t="n">
+        <v>17.44</v>
       </c>
     </row>
     <row r="48" ht="18" customHeight="1">
       <c r="A48" s="26" t="inlineStr">
         <is>
-          <t>페니트리움바이오</t>
+          <t>한화솔루션</t>
         </is>
       </c>
       <c r="B48" s="25" t="n">
@@ -4677,25 +4653,25 @@
       </c>
       <c r="F48" s="25" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G48" s="25" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="H48" s="29" t="n">
-        <v>-0.45</v>
-      </c>
-      <c r="I48" s="27" t="n">
-        <v>6.06</v>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="H48" s="27" t="n">
+        <v>-7.75</v>
+      </c>
+      <c r="I48" s="28" t="n">
+        <v>9.32</v>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1">
       <c r="A49" s="26" t="inlineStr">
         <is>
-          <t>피노</t>
+          <t>현대모비스</t>
         </is>
       </c>
       <c r="B49" s="25" t="n">
@@ -4712,25 +4688,25 @@
       </c>
       <c r="F49" s="25" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G49" s="25" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="H49" s="27" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="I49" s="29" t="n">
-        <v>-3.06</v>
+        <v>-4.44</v>
+      </c>
+      <c r="I49" s="28" t="n">
+        <v>4.69</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
       <c r="A50" s="26" t="inlineStr">
         <is>
-          <t>한국전력</t>
+          <t>현대약품</t>
         </is>
       </c>
       <c r="B50" s="25" t="n">
@@ -4747,25 +4723,25 @@
       </c>
       <c r="F50" s="25" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G50" s="25" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="H50" s="27" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="I50" s="27" t="n">
-        <v>11.26</v>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="H50" s="28" t="n">
+        <v>4.81</v>
+      </c>
+      <c r="I50" s="28" t="n">
+        <v>48.34</v>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
       <c r="A51" s="26" t="inlineStr">
         <is>
-          <t>한화솔루션</t>
+          <t>현대제철</t>
         </is>
       </c>
       <c r="B51" s="25" t="n">
@@ -4782,54 +4758,54 @@
       </c>
       <c r="F51" s="25" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G51" s="25" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="H51" s="29" t="n">
-        <v>-2.13</v>
-      </c>
-      <c r="I51" s="27" t="n">
-        <v>19.63</v>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="H51" s="27" t="n">
+        <v>-4.44</v>
+      </c>
+      <c r="I51" s="28" t="n">
+        <v>3.73</v>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1">
       <c r="A52" s="26" t="inlineStr">
         <is>
-          <t>후성</t>
+          <t>삼화전자</t>
         </is>
       </c>
       <c r="B52" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C52" s="25" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D52" s="25" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E52" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F52" s="25" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G52" s="25" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="H52" s="29" t="n">
-        <v>-8.44</v>
-      </c>
-      <c r="I52" s="27" t="n">
-        <v>8.25</v>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="H52" s="28" t="n">
+        <v>29.86</v>
+      </c>
+      <c r="I52" s="28" t="n">
+        <v>70</v>
       </c>
     </row>
   </sheetData>
@@ -4906,26 +4882,26 @@
     <row r="3" ht="18" customHeight="1">
       <c r="A3" s="35" t="inlineStr">
         <is>
-          <t>반도체</t>
+          <t>이차전지</t>
         </is>
       </c>
       <c r="B3" s="36" t="n">
         <v>1</v>
       </c>
       <c r="C3" s="36" t="n">
-        <v>57</v>
+        <v>3</v>
       </c>
       <c r="D3" s="36" t="n">
-        <v>57</v>
+        <v>3</v>
       </c>
       <c r="E3" s="36" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="F3" s="37" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G3" s="37" t="inlineStr">
@@ -4937,26 +4913,26 @@
     <row r="4" ht="18" customHeight="1">
       <c r="A4" s="35" t="inlineStr">
         <is>
-          <t>바이오</t>
+          <t>반도체</t>
         </is>
       </c>
       <c r="B4" s="36" t="n">
         <v>1</v>
       </c>
       <c r="C4" s="36" t="n">
-        <v>14</v>
+        <v>85</v>
       </c>
       <c r="D4" s="36" t="n">
-        <v>14</v>
+        <v>85</v>
       </c>
       <c r="E4" s="36" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="F4" s="37" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G4" s="37" t="inlineStr">
@@ -4968,26 +4944,26 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="35" t="inlineStr">
         <is>
-          <t>방산</t>
+          <t>바이오</t>
         </is>
       </c>
       <c r="B5" s="36" t="n">
         <v>1</v>
       </c>
       <c r="C5" s="36" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="D5" s="36" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="E5" s="36" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="F5" s="37" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G5" s="37" t="inlineStr">
@@ -4999,26 +4975,26 @@
     <row r="6" ht="18" customHeight="1">
       <c r="A6" s="35" t="inlineStr">
         <is>
-          <t>원전</t>
+          <t>전기차</t>
         </is>
       </c>
       <c r="B6" s="36" t="n">
         <v>1</v>
       </c>
       <c r="C6" s="36" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="D6" s="36" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="E6" s="36" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="F6" s="37" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G6" s="37" t="inlineStr">
@@ -5030,26 +5006,26 @@
     <row r="7" ht="18" customHeight="1">
       <c r="A7" s="35" t="inlineStr">
         <is>
-          <t>로봇</t>
+          <t>방산</t>
         </is>
       </c>
       <c r="B7" s="36" t="n">
         <v>1</v>
       </c>
       <c r="C7" s="36" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D7" s="36" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E7" s="36" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="F7" s="37" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G7" s="37" t="inlineStr">
@@ -5061,26 +5037,26 @@
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="35" t="inlineStr">
         <is>
-          <t>게임</t>
+          <t>원전</t>
         </is>
       </c>
       <c r="B8" s="36" t="n">
         <v>1</v>
       </c>
       <c r="C8" s="36" t="n">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="D8" s="36" t="n">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="E8" s="36" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="F8" s="37" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G8" s="37" t="inlineStr">
@@ -5092,26 +5068,26 @@
     <row r="9" ht="18" customHeight="1">
       <c r="A9" s="35" t="inlineStr">
         <is>
-          <t>조선</t>
+          <t>로봇</t>
         </is>
       </c>
       <c r="B9" s="36" t="n">
         <v>1</v>
       </c>
       <c r="C9" s="36" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D9" s="36" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E9" s="36" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="F9" s="37" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G9" s="37" t="inlineStr">
@@ -5123,26 +5099,26 @@
     <row r="10" ht="18" customHeight="1">
       <c r="A10" s="35" t="inlineStr">
         <is>
-          <t>철강</t>
+          <t>엔터</t>
         </is>
       </c>
       <c r="B10" s="36" t="n">
         <v>1</v>
       </c>
       <c r="C10" s="36" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D10" s="36" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E10" s="36" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="F10" s="37" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G10" s="37" t="inlineStr">
@@ -5154,26 +5130,26 @@
     <row r="11" ht="18" customHeight="1">
       <c r="A11" s="35" t="inlineStr">
         <is>
-          <t>제약</t>
+          <t>조선</t>
         </is>
       </c>
       <c r="B11" s="36" t="n">
         <v>1</v>
       </c>
       <c r="C11" s="36" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D11" s="36" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E11" s="36" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="F11" s="37" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G11" s="37" t="inlineStr">
@@ -5185,26 +5161,26 @@
     <row r="12" ht="18" customHeight="1">
       <c r="A12" s="35" t="inlineStr">
         <is>
-          <t>인공지능</t>
+          <t>철강</t>
         </is>
       </c>
       <c r="B12" s="36" t="n">
         <v>1</v>
       </c>
       <c r="C12" s="36" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D12" s="36" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E12" s="36" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="F12" s="37" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G12" s="37" t="inlineStr">
@@ -5216,26 +5192,26 @@
     <row r="13" ht="18" customHeight="1">
       <c r="A13" s="35" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>제약</t>
         </is>
       </c>
       <c r="B13" s="36" t="n">
         <v>1</v>
       </c>
       <c r="C13" s="36" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D13" s="36" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E13" s="36" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="F13" s="37" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G13" s="37" t="inlineStr">
@@ -5245,31 +5221,35 @@
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="26" t="inlineStr">
-        <is>
-          <t>이차전지</t>
-        </is>
-      </c>
-      <c r="B14" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="C14" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="D14" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" s="25" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F14" s="28" t="inlineStr">
-        <is>
-          <t>감지 없음</t>
-        </is>
-      </c>
-      <c r="G14" s="28" t="inlineStr"/>
+      <c r="A14" s="35" t="inlineStr">
+        <is>
+          <t>인공지능</t>
+        </is>
+      </c>
+      <c r="B14" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" s="36" t="n">
+        <v>12</v>
+      </c>
+      <c r="D14" s="36" t="n">
+        <v>12</v>
+      </c>
+      <c r="E14" s="36" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="F14" s="37" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="G14" s="37" t="inlineStr">
+        <is>
+          <t>⚡ 관심</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="18" customHeight="1">
       <c r="A15" s="26" t="inlineStr">
@@ -5291,17 +5271,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F15" s="28" t="inlineStr">
+      <c r="F15" s="29" t="inlineStr">
         <is>
           <t>감지 없음</t>
         </is>
       </c>
-      <c r="G15" s="28" t="inlineStr"/>
+      <c r="G15" s="29" t="inlineStr"/>
     </row>
     <row r="16" ht="18" customHeight="1">
       <c r="A16" s="26" t="inlineStr">
         <is>
-          <t>전기차</t>
+          <t>수소</t>
         </is>
       </c>
       <c r="B16" s="25" t="n">
@@ -5318,17 +5298,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F16" s="28" t="inlineStr">
+      <c r="F16" s="29" t="inlineStr">
         <is>
           <t>감지 없음</t>
         </is>
       </c>
-      <c r="G16" s="28" t="inlineStr"/>
+      <c r="G16" s="29" t="inlineStr"/>
     </row>
     <row r="17" ht="18" customHeight="1">
       <c r="A17" s="26" t="inlineStr">
         <is>
-          <t>수소</t>
+          <t>태양광</t>
         </is>
       </c>
       <c r="B17" s="25" t="n">
@@ -5345,17 +5325,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F17" s="28" t="inlineStr">
+      <c r="F17" s="29" t="inlineStr">
         <is>
           <t>감지 없음</t>
         </is>
       </c>
-      <c r="G17" s="28" t="inlineStr"/>
+      <c r="G17" s="29" t="inlineStr"/>
     </row>
     <row r="18" ht="18" customHeight="1">
       <c r="A18" s="26" t="inlineStr">
         <is>
-          <t>태양광</t>
+          <t>게임</t>
         </is>
       </c>
       <c r="B18" s="25" t="n">
@@ -5372,17 +5352,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F18" s="28" t="inlineStr">
+      <c r="F18" s="29" t="inlineStr">
         <is>
           <t>감지 없음</t>
         </is>
       </c>
-      <c r="G18" s="28" t="inlineStr"/>
+      <c r="G18" s="29" t="inlineStr"/>
     </row>
     <row r="19" ht="18" customHeight="1">
       <c r="A19" s="26" t="inlineStr">
         <is>
-          <t>엔터</t>
+          <t>핀테크</t>
         </is>
       </c>
       <c r="B19" s="25" t="n">
@@ -5399,17 +5379,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F19" s="28" t="inlineStr">
+      <c r="F19" s="29" t="inlineStr">
         <is>
           <t>감지 없음</t>
         </is>
       </c>
-      <c r="G19" s="28" t="inlineStr"/>
+      <c r="G19" s="29" t="inlineStr"/>
     </row>
     <row r="20" ht="18" customHeight="1">
       <c r="A20" s="26" t="inlineStr">
         <is>
-          <t>핀테크</t>
+          <t>클라우드</t>
         </is>
       </c>
       <c r="B20" s="25" t="n">
@@ -5426,17 +5406,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F20" s="28" t="inlineStr">
+      <c r="F20" s="29" t="inlineStr">
         <is>
           <t>감지 없음</t>
         </is>
       </c>
-      <c r="G20" s="28" t="inlineStr"/>
+      <c r="G20" s="29" t="inlineStr"/>
     </row>
     <row r="21" ht="18" customHeight="1">
       <c r="A21" s="26" t="inlineStr">
         <is>
-          <t>클라우드</t>
+          <t>의료기기</t>
         </is>
       </c>
       <c r="B21" s="25" t="n">
@@ -5453,17 +5433,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F21" s="28" t="inlineStr">
+      <c r="F21" s="29" t="inlineStr">
         <is>
           <t>감지 없음</t>
         </is>
       </c>
-      <c r="G21" s="28" t="inlineStr"/>
+      <c r="G21" s="29" t="inlineStr"/>
     </row>
     <row r="22" ht="18" customHeight="1">
       <c r="A22" s="26" t="inlineStr">
         <is>
-          <t>의료기기</t>
+          <t>NVIDIA</t>
         </is>
       </c>
       <c r="B22" s="25" t="n">
@@ -5480,17 +5460,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F22" s="28" t="inlineStr">
+      <c r="F22" s="29" t="inlineStr">
         <is>
           <t>감지 없음</t>
         </is>
       </c>
-      <c r="G22" s="28" t="inlineStr"/>
+      <c r="G22" s="29" t="inlineStr"/>
     </row>
     <row r="23" ht="18" customHeight="1">
       <c r="A23" s="26" t="inlineStr">
         <is>
-          <t>NVIDIA</t>
+          <t>Tesla</t>
         </is>
       </c>
       <c r="B23" s="25" t="n">
@@ -5507,17 +5487,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F23" s="28" t="inlineStr">
+      <c r="F23" s="29" t="inlineStr">
         <is>
           <t>감지 없음</t>
         </is>
       </c>
-      <c r="G23" s="28" t="inlineStr"/>
+      <c r="G23" s="29" t="inlineStr"/>
     </row>
     <row r="24" ht="18" customHeight="1">
       <c r="A24" s="26" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="B24" s="25" t="n">
@@ -5534,12 +5514,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F24" s="28" t="inlineStr">
+      <c r="F24" s="29" t="inlineStr">
         <is>
           <t>감지 없음</t>
         </is>
       </c>
-      <c r="G24" s="28" t="inlineStr"/>
+      <c r="G24" s="29" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/trend/stock_trend_history.xlsx
+++ b/trend/stock_trend_history.xlsx
@@ -57,13 +57,13 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="002563EB"/>
+      <color rgb="00E53935"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="00E53935"/>
+      <color rgb="002563EB"/>
       <sz val="10"/>
     </font>
     <font>
@@ -276,11 +276,11 @@
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -694,7 +694,7 @@
     <row r="1" ht="36" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>📊 주식 트렌드 조기 감지 대시보드   |   최종 업데이트: 2026-06-19 06:55</t>
+          <t>📊 주식 트렌드 조기 감지 대시보드   |   최종 업데이트: 2026-06-20 06:55</t>
         </is>
       </c>
     </row>
@@ -708,7 +708,7 @@
       </c>
       <c r="E3" s="3" t="n"/>
       <c r="G3" s="5" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H3" s="3" t="n"/>
       <c r="J3" s="6" t="n">
@@ -787,21 +787,21 @@
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="11" t="inlineStr">
         <is>
-          <t>⚡ 최신(2026-06-19) 상위: 반도체  점수 85.0점</t>
+          <t>⚡ 최신(2026-06-20) 상위: 반도체  점수 60.0점</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1">
       <c r="A11" s="12" t="inlineStr">
         <is>
-          <t>⚡ 최신(2026-06-19) 상위: SK  점수 40.0점</t>
+          <t>⚡ 최신(2026-06-20) 상위: SK  점수 47.0점</t>
         </is>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1">
       <c r="A12" s="11" t="inlineStr">
         <is>
-          <t>⚡ 최신(2026-06-19) 상위: SK하이닉스  점수 33.0점</t>
+          <t>⚡ 최신(2026-06-20) 상위: SK하이닉스  점수 31.0점</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="B14" s="15" t="n">
@@ -928,10 +928,10 @@
         </is>
       </c>
       <c r="D14" s="15" t="n">
-        <v>85</v>
+        <v>60</v>
       </c>
       <c r="E14" s="15" t="n">
-        <v>85</v>
+        <v>60</v>
       </c>
       <c r="F14" s="15" t="n">
         <v>0</v>
@@ -947,7 +947,7 @@
       </c>
       <c r="J14" s="17" t="inlineStr">
         <is>
-          <t>매일경제 기사 언급 / 네이버뉴스 헤드라인 언급 / 네이버뉴스 헤드라인 언급 / 네이버뉴스 헤드라인 언급 / 네이버뉴스 기사 언급</t>
+          <t>매일경제 기사 언급 / 매일경제 기사 언급 / 네이버뉴스 기사 언급 / 매일경제 기사 언급 / 매일경제 기사 언급</t>
         </is>
       </c>
       <c r="K14" s="17" t="inlineStr">
@@ -959,7 +959,7 @@
     <row r="15" ht="18" customHeight="1">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="B15" s="15" t="n">
@@ -971,10 +971,10 @@
         </is>
       </c>
       <c r="D15" s="15" t="n">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="E15" s="15" t="n">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="F15" s="15" t="n">
         <v>0</v>
@@ -983,24 +983,26 @@
         <v>0</v>
       </c>
       <c r="H15" s="18" t="n">
-        <v>-2.97</v>
-      </c>
-      <c r="I15" s="19" t="n">
-        <v>19.48</v>
+        <v>5.39</v>
+      </c>
+      <c r="I15" s="18" t="n">
+        <v>22.09</v>
       </c>
       <c r="J15" s="17" t="inlineStr">
         <is>
-          <t>매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 기사 언급 / 매일경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K15" s="17" t="n">
-        <v/>
+          <t>매일경제 헤드라인 언급 / 매일경제 기사 언급 / 한국경제 헤드라인 언급 / 한국경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K15" s="17" t="inlineStr">
+        <is>
+          <t>네이버</t>
+        </is>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
       <c r="A16" s="15" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="B16" s="15" t="n">
@@ -1012,10 +1014,10 @@
         </is>
       </c>
       <c r="D16" s="15" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E16" s="15" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F16" s="15" t="n">
         <v>0</v>
@@ -1023,15 +1025,15 @@
       <c r="G16" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="H16" s="19" t="n">
-        <v>6.51</v>
-      </c>
-      <c r="I16" s="19" t="n">
-        <v>27.8</v>
+      <c r="H16" s="18" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="I16" s="18" t="n">
+        <v>28.56</v>
       </c>
       <c r="J16" s="17" t="inlineStr">
         <is>
-          <t>매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 기사 언급 / 매일경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
+          <t>매일경제 헤드라인 언급 / 매일경제 기사 언급 / 한국경제 헤드라인 언급 / 매일경제 기사 언급 / 매일경제 기사 언급</t>
         </is>
       </c>
       <c r="K16" s="17" t="n">
@@ -1041,7 +1043,7 @@
     <row r="17" ht="18" customHeight="1">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="B17" s="15" t="n">
@@ -1049,14 +1051,14 @@
       </c>
       <c r="C17" s="16" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>삼성전기</t>
         </is>
       </c>
       <c r="D17" s="15" t="n">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="E17" s="15" t="n">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="F17" s="15" t="n">
         <v>0</v>
@@ -1064,27 +1066,27 @@
       <c r="G17" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="H17" s="19" t="n">
-        <v>4.62</v>
-      </c>
-      <c r="I17" s="19" t="n">
-        <v>21.24</v>
+      <c r="H17" s="18" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="I17" s="18" t="n">
+        <v>32.44</v>
       </c>
       <c r="J17" s="17" t="inlineStr">
         <is>
-          <t>매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 기사 언급 / 매일경제 헤드라인 언급</t>
+          <t>Google 급상승 검색어 등장 (KR) / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급</t>
         </is>
       </c>
       <c r="K17" s="17" t="inlineStr">
         <is>
-          <t>네이버</t>
+          <t>Google</t>
         </is>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
       <c r="A18" s="15" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="B18" s="15" t="n">
@@ -1092,14 +1094,14 @@
       </c>
       <c r="C18" s="16" t="inlineStr">
         <is>
-          <t>원전</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="D18" s="15" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="E18" s="15" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="F18" s="15" t="n">
         <v>0</v>
@@ -1107,15 +1109,15 @@
       <c r="G18" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="H18" s="15" t="n">
-        <v/>
-      </c>
-      <c r="I18" s="15" t="n">
-        <v/>
+      <c r="H18" s="19" t="n">
+        <v>-2.34</v>
+      </c>
+      <c r="I18" s="18" t="n">
+        <v>9.77</v>
       </c>
       <c r="J18" s="17" t="inlineStr">
         <is>
-          <t>매일경제 헤드라인 언급 / 한국경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급</t>
+          <t>매일경제 기사 언급 / 한국경제 헤드라인 언급 / 매일경제 기사 언급 / 매일경제 기사 언급 / 매일경제 기사 언급</t>
         </is>
       </c>
       <c r="K18" s="17" t="n">
@@ -1125,7 +1127,7 @@
     <row r="19" ht="18" customHeight="1">
       <c r="A19" s="15" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="B19" s="15" t="n">
@@ -1133,14 +1135,14 @@
       </c>
       <c r="C19" s="16" t="inlineStr">
         <is>
-          <t>바이오</t>
+          <t>현대차</t>
         </is>
       </c>
       <c r="D19" s="15" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E19" s="15" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F19" s="15" t="n">
         <v>0</v>
@@ -1148,27 +1150,25 @@
       <c r="G19" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="H19" s="15" t="n">
+      <c r="H19" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="I19" s="18" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="J19" s="17" t="inlineStr">
+        <is>
+          <t>매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 기사 언급 / 한국경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K19" s="17" t="n">
         <v/>
-      </c>
-      <c r="I19" s="15" t="n">
-        <v/>
-      </c>
-      <c r="J19" s="17" t="inlineStr">
-        <is>
-          <t>네이버뉴스 헤드라인 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 헤드라인 언급 / 네이버뉴스 헤드라인 언급 / 네이버뉴스 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K19" s="17" t="inlineStr">
-        <is>
-          <t>네이버</t>
-        </is>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
       <c r="A20" s="15" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="B20" s="15" t="n">
@@ -1176,14 +1176,14 @@
       </c>
       <c r="C20" s="16" t="inlineStr">
         <is>
-          <t>제약</t>
+          <t>대한항공</t>
         </is>
       </c>
       <c r="D20" s="15" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E20" s="15" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F20" s="15" t="n">
         <v>0</v>
@@ -1191,27 +1191,25 @@
       <c r="G20" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="H20" s="15" t="n">
+      <c r="H20" s="19" t="n">
+        <v>-3.12</v>
+      </c>
+      <c r="I20" s="18" t="n">
+        <v>5.08</v>
+      </c>
+      <c r="J20" s="17" t="inlineStr">
+        <is>
+          <t>매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 한국경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K20" s="17" t="n">
         <v/>
-      </c>
-      <c r="I20" s="15" t="n">
-        <v/>
-      </c>
-      <c r="J20" s="17" t="inlineStr">
-        <is>
-          <t>네이버뉴스 헤드라인 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 헤드라인 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K20" s="17" t="inlineStr">
-        <is>
-          <t>네이버</t>
-        </is>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
       <c r="A21" s="15" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="B21" s="15" t="n">
@@ -1223,10 +1221,10 @@
         </is>
       </c>
       <c r="D21" s="15" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E21" s="15" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F21" s="15" t="n">
         <v>0</v>
@@ -1254,7 +1252,7 @@
     <row r="22" ht="18" customHeight="1">
       <c r="A22" s="15" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="B22" s="15" t="n">
@@ -1262,7 +1260,7 @@
       </c>
       <c r="C22" s="16" t="inlineStr">
         <is>
-          <t>넥써쓰</t>
+          <t>로봇</t>
         </is>
       </c>
       <c r="D22" s="15" t="n">
@@ -1277,27 +1275,27 @@
       <c r="G22" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="H22" s="19" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="I22" s="19" t="n">
-        <v>28.71</v>
+      <c r="H22" s="15" t="n">
+        <v/>
+      </c>
+      <c r="I22" s="15" t="n">
+        <v/>
       </c>
       <c r="J22" s="17" t="inlineStr">
         <is>
-          <t>중요공시 3건 / 매일경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
+          <t>네이버뉴스 헤드라인 언급 / 매일경제 기사 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급</t>
         </is>
       </c>
       <c r="K22" s="17" t="inlineStr">
         <is>
-          <t>공시</t>
+          <t>네이버</t>
         </is>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="B23" s="15" t="n">
@@ -1305,7 +1303,7 @@
       </c>
       <c r="C23" s="16" t="inlineStr">
         <is>
-          <t>전기차</t>
+          <t>제약</t>
         </is>
       </c>
       <c r="D23" s="15" t="n">
@@ -1328,17 +1326,19 @@
       </c>
       <c r="J23" s="17" t="inlineStr">
         <is>
-          <t>매일경제 헤드라인 언급 / 한국경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K23" s="17" t="n">
-        <v/>
+          <t>네이버뉴스 기사 언급 / 네이버뉴스 헤드라인 언급 / 네이버뉴스 헤드라인 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 기사 언급</t>
+        </is>
+      </c>
+      <c r="K23" s="17" t="inlineStr">
+        <is>
+          <t>네이버</t>
+        </is>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="B24" s="15" t="n">
@@ -1346,7 +1346,7 @@
       </c>
       <c r="C24" s="16" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>바이오</t>
         </is>
       </c>
       <c r="D24" s="15" t="n">
@@ -1361,15 +1361,15 @@
       <c r="G24" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="H24" s="18" t="n">
-        <v>-5.64</v>
-      </c>
-      <c r="I24" s="19" t="n">
-        <v>18.59</v>
+      <c r="H24" s="15" t="n">
+        <v/>
+      </c>
+      <c r="I24" s="15" t="n">
+        <v/>
       </c>
       <c r="J24" s="17" t="inlineStr">
         <is>
-          <t>네이버뉴스 헤드라인 언급 / 매일경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
+          <t>네이버뉴스 기사 언급 / 네이버뉴스 헤드라인 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 헤드라인 언급 / 네이버뉴스 기사 언급</t>
         </is>
       </c>
       <c r="K24" s="17" t="inlineStr">
@@ -1381,7 +1381,7 @@
     <row r="25" ht="18" customHeight="1">
       <c r="A25" s="15" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="B25" s="15" t="n">
@@ -1389,14 +1389,14 @@
       </c>
       <c r="C25" s="16" t="inlineStr">
         <is>
-          <t>미래에셋증권</t>
+          <t>넥써쓰</t>
         </is>
       </c>
       <c r="D25" s="15" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E25" s="15" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F25" s="15" t="n">
         <v>0</v>
@@ -1405,26 +1405,26 @@
         <v>0</v>
       </c>
       <c r="H25" s="19" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="I25" s="18" t="n">
-        <v>-0.78</v>
+        <v>-27.47</v>
+      </c>
+      <c r="I25" s="19" t="n">
+        <v>-4.83</v>
       </c>
       <c r="J25" s="17" t="inlineStr">
         <is>
-          <t>중요공시 2건 / 매일경제 헤드라인 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 헤드라인 언급</t>
+          <t>중요공시 3건 / 매일경제 헤드라인 언급</t>
         </is>
       </c>
       <c r="K25" s="17" t="inlineStr">
         <is>
-          <t>네이버, 공시</t>
+          <t>공시</t>
         </is>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
       <c r="A26" s="15" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="B26" s="15" t="n">
@@ -1432,14 +1432,14 @@
       </c>
       <c r="C26" s="16" t="inlineStr">
         <is>
-          <t>방산</t>
+          <t>현대로템</t>
         </is>
       </c>
       <c r="D26" s="15" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E26" s="15" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F26" s="15" t="n">
         <v>0</v>
@@ -1447,25 +1447,27 @@
       <c r="G26" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="H26" s="15" t="n">
-        <v/>
-      </c>
-      <c r="I26" s="15" t="n">
-        <v/>
+      <c r="H26" s="19" t="n">
+        <v>-2.13</v>
+      </c>
+      <c r="I26" s="19" t="n">
+        <v>-0.72</v>
       </c>
       <c r="J26" s="17" t="inlineStr">
         <is>
-          <t>매일경제 기사 언급 / 매일경제 기사 언급 / 한국경제 헤드라인 언급 / 매일경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K26" s="17" t="n">
-        <v/>
+          <t>중요공시 1건 / 매일경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K26" s="17" t="inlineStr">
+        <is>
+          <t>공시</t>
+        </is>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
       <c r="A27" s="15" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="B27" s="15" t="n">
@@ -1473,7 +1475,7 @@
       </c>
       <c r="C27" s="16" t="inlineStr">
         <is>
-          <t>가온전선</t>
+          <t>LG</t>
         </is>
       </c>
       <c r="D27" s="15" t="n">
@@ -1489,110 +1491,108 @@
         <v>0</v>
       </c>
       <c r="H27" s="19" t="n">
-        <v>13.05</v>
-      </c>
-      <c r="I27" s="19" t="n">
-        <v>18.98</v>
+        <v>-0.91</v>
+      </c>
+      <c r="I27" s="18" t="n">
+        <v>2.25</v>
       </c>
       <c r="J27" s="17" t="inlineStr">
         <is>
-          <t>중요공시 2건 / 매일경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K27" s="17" t="inlineStr">
-        <is>
-          <t>공시</t>
-        </is>
+          <t>매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K27" s="17" t="n">
+        <v/>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
-      <c r="A28" s="15" t="inlineStr">
-        <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="B28" s="15" t="n">
+      <c r="A28" s="20" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="B28" s="20" t="n">
         <v>15</v>
       </c>
-      <c r="C28" s="16" t="inlineStr">
-        <is>
-          <t>카카오</t>
-        </is>
-      </c>
-      <c r="D28" s="15" t="n">
-        <v>7</v>
-      </c>
-      <c r="E28" s="15" t="n">
-        <v>7</v>
-      </c>
-      <c r="F28" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G28" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H28" s="18" t="n">
-        <v>-3.08</v>
-      </c>
-      <c r="I28" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J28" s="17" t="inlineStr">
-        <is>
-          <t>Google 급상승 검색어 등장 (KR) / 매일경제 기사 언급 / 매일경제 기사 언급</t>
-        </is>
-      </c>
-      <c r="K28" s="17" t="inlineStr">
-        <is>
-          <t>Google</t>
+      <c r="C28" s="21" t="inlineStr">
+        <is>
+          <t>미래에셋증권</t>
+        </is>
+      </c>
+      <c r="D28" s="20" t="n">
+        <v>6</v>
+      </c>
+      <c r="E28" s="20" t="n">
+        <v>6</v>
+      </c>
+      <c r="F28" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" s="22" t="n">
+        <v>-3.85</v>
+      </c>
+      <c r="I28" s="22" t="n">
+        <v>-6.79</v>
+      </c>
+      <c r="J28" s="23" t="inlineStr">
+        <is>
+          <t>중요공시 2건 / 매일경제 헤드라인 언급 / 네이버뉴스 기사 언급 / 매일경제 기사 언급</t>
+        </is>
+      </c>
+      <c r="K28" s="23" t="inlineStr">
+        <is>
+          <t>공시, 네이버</t>
         </is>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
-      <c r="A29" s="15" t="inlineStr">
-        <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="B29" s="15" t="n">
+      <c r="A29" s="20" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="B29" s="20" t="n">
         <v>16</v>
       </c>
-      <c r="C29" s="16" t="inlineStr">
-        <is>
-          <t>삼성전기</t>
-        </is>
-      </c>
-      <c r="D29" s="15" t="n">
-        <v>7</v>
-      </c>
-      <c r="E29" s="15" t="n">
-        <v>7</v>
-      </c>
-      <c r="F29" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G29" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H29" s="19" t="n">
-        <v>8.27</v>
-      </c>
-      <c r="I29" s="19" t="n">
-        <v>21.88</v>
-      </c>
-      <c r="J29" s="17" t="inlineStr">
-        <is>
-          <t>매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 기사 언급</t>
-        </is>
-      </c>
-      <c r="K29" s="17" t="n">
+      <c r="C29" s="21" t="inlineStr">
+        <is>
+          <t>SK스퀘어</t>
+        </is>
+      </c>
+      <c r="D29" s="20" t="n">
+        <v>6</v>
+      </c>
+      <c r="E29" s="20" t="n">
+        <v>6</v>
+      </c>
+      <c r="F29" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" s="24" t="n">
+        <v>4.71</v>
+      </c>
+      <c r="I29" s="24" t="n">
+        <v>31.08</v>
+      </c>
+      <c r="J29" s="23" t="inlineStr">
+        <is>
+          <t>한국경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K29" s="23" t="n">
         <v/>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
       <c r="A30" s="20" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="B30" s="20" t="n">
@@ -1600,7 +1600,7 @@
       </c>
       <c r="C30" s="21" t="inlineStr">
         <is>
-          <t>대한항공</t>
+          <t>삼성물산</t>
         </is>
       </c>
       <c r="D30" s="20" t="n">
@@ -1615,15 +1615,15 @@
       <c r="G30" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H30" s="22" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="I30" s="22" t="n">
-        <v>16.33</v>
+      <c r="H30" s="24" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="I30" s="24" t="n">
+        <v>13.77</v>
       </c>
       <c r="J30" s="23" t="inlineStr">
         <is>
-          <t>한국경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급</t>
+          <t>한국경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
         </is>
       </c>
       <c r="K30" s="23" t="n">
@@ -1633,7 +1633,7 @@
     <row r="31" ht="18" customHeight="1">
       <c r="A31" s="20" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="B31" s="20" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="C31" s="21" t="inlineStr">
         <is>
-          <t>현대차</t>
+          <t>조선</t>
         </is>
       </c>
       <c r="D31" s="20" t="n">
@@ -1656,15 +1656,15 @@
       <c r="G31" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H31" s="24" t="n">
-        <v>-2.75</v>
-      </c>
-      <c r="I31" s="22" t="n">
-        <v>0.67</v>
+      <c r="H31" s="20" t="n">
+        <v/>
+      </c>
+      <c r="I31" s="20" t="n">
+        <v/>
       </c>
       <c r="J31" s="23" t="inlineStr">
         <is>
-          <t>매일경제 헤드라인 언급 / 네이버뉴스 기사 언급 / 한국경제 헤드라인 언급</t>
+          <t>한국경제 헤드라인 언급 / 네이버뉴스 헤드라인 언급</t>
         </is>
       </c>
       <c r="K31" s="23" t="inlineStr">
@@ -1676,7 +1676,7 @@
     <row r="32" ht="18" customHeight="1">
       <c r="A32" s="20" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="B32" s="20" t="n">
@@ -1684,14 +1684,14 @@
       </c>
       <c r="C32" s="21" t="inlineStr">
         <is>
-          <t>LG</t>
+          <t>씨피시스템</t>
         </is>
       </c>
       <c r="D32" s="20" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E32" s="20" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F32" s="20" t="n">
         <v>0</v>
@@ -1700,24 +1700,26 @@
         <v>0</v>
       </c>
       <c r="H32" s="24" t="n">
-        <v>-2.31</v>
-      </c>
-      <c r="I32" s="22" t="n">
-        <v>2.23</v>
+        <v>29.88</v>
+      </c>
+      <c r="I32" s="24" t="n">
+        <v>20.79</v>
       </c>
       <c r="J32" s="23" t="inlineStr">
         <is>
-          <t>매일경제 기사 언급 / 매일경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K32" s="23" t="n">
-        <v/>
+          <t>네이버뉴스 헤드라인 언급 / 한국경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K32" s="23" t="inlineStr">
+        <is>
+          <t>네이버</t>
+        </is>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
       <c r="A33" s="20" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="B33" s="20" t="n">
@@ -1725,40 +1727,42 @@
       </c>
       <c r="C33" s="21" t="inlineStr">
         <is>
-          <t>철강</t>
+          <t>진원생명과학</t>
         </is>
       </c>
       <c r="D33" s="20" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E33" s="20" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F33" s="20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G33" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H33" s="20" t="n">
-        <v/>
-      </c>
-      <c r="I33" s="20" t="n">
-        <v/>
+      <c r="H33" s="22" t="n">
+        <v>-17.67</v>
+      </c>
+      <c r="I33" s="22" t="n">
+        <v>-24.4</v>
       </c>
       <c r="J33" s="23" t="inlineStr">
         <is>
-          <t>매일경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K33" s="23" t="n">
-        <v/>
+          <t>중요공시 3건 / 중요공시 3일 +50%</t>
+        </is>
+      </c>
+      <c r="K33" s="23" t="inlineStr">
+        <is>
+          <t>공시</t>
+        </is>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
       <c r="A34" s="20" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="B34" s="20" t="n">
@@ -1766,42 +1770,40 @@
       </c>
       <c r="C34" s="21" t="inlineStr">
         <is>
-          <t>파두</t>
+          <t>KT</t>
         </is>
       </c>
       <c r="D34" s="20" t="n">
         <v>5</v>
       </c>
       <c r="E34" s="20" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F34" s="20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G34" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H34" s="24" t="n">
-        <v>-1.89</v>
+      <c r="H34" s="22" t="n">
+        <v>-0.37</v>
       </c>
       <c r="I34" s="22" t="n">
-        <v>4.73</v>
+        <v>-2.74</v>
       </c>
       <c r="J34" s="23" t="inlineStr">
         <is>
-          <t>중요공시 3건 / 중요공시 3일 +200%</t>
-        </is>
-      </c>
-      <c r="K34" s="23" t="inlineStr">
-        <is>
-          <t>공시</t>
-        </is>
+          <t>매일경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K34" s="23" t="n">
+        <v/>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
       <c r="A35" s="20" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="B35" s="20" t="n">
@@ -1809,14 +1811,14 @@
       </c>
       <c r="C35" s="21" t="inlineStr">
         <is>
-          <t>로봇</t>
+          <t>남화토건</t>
         </is>
       </c>
       <c r="D35" s="20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E35" s="20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F35" s="20" t="n">
         <v>0</v>
@@ -1824,27 +1826,27 @@
       <c r="G35" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H35" s="20" t="n">
-        <v/>
-      </c>
-      <c r="I35" s="20" t="n">
-        <v/>
+      <c r="H35" s="24" t="n">
+        <v>12.73</v>
+      </c>
+      <c r="I35" s="24" t="n">
+        <v>45.92</v>
       </c>
       <c r="J35" s="23" t="inlineStr">
         <is>
-          <t>매일경제 헤드라인 언급 / 매일경제 기사 언급 / 네이버뉴스 기사 언급</t>
+          <t>네이버 검색 당일 +314% / 중요공시 1건</t>
         </is>
       </c>
       <c r="K35" s="23" t="inlineStr">
         <is>
-          <t>네이버</t>
+          <t>공시, 네이버</t>
         </is>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
       <c r="A36" s="20" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="B36" s="20" t="n">
@@ -1852,40 +1854,42 @@
       </c>
       <c r="C36" s="21" t="inlineStr">
         <is>
-          <t>기아</t>
+          <t>한솔테크닉스</t>
         </is>
       </c>
       <c r="D36" s="20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E36" s="20" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F36" s="20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G36" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H36" s="24" t="n">
-        <v>-4.51</v>
-      </c>
-      <c r="I36" s="22" t="n">
-        <v>1.79</v>
+      <c r="H36" s="22" t="n">
+        <v>-4.87</v>
+      </c>
+      <c r="I36" s="24" t="n">
+        <v>7.83</v>
       </c>
       <c r="J36" s="23" t="inlineStr">
         <is>
-          <t>매일경제 헤드라인 언급 / 매일경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K36" s="23" t="n">
-        <v/>
+          <t>중요공시 2건 / 중요공시 3일 +100%</t>
+        </is>
+      </c>
+      <c r="K36" s="23" t="inlineStr">
+        <is>
+          <t>공시</t>
+        </is>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
       <c r="A37" s="20" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="B37" s="20" t="n">
@@ -1893,14 +1897,14 @@
       </c>
       <c r="C37" s="21" t="inlineStr">
         <is>
-          <t>조선</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="D37" s="20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E37" s="20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F37" s="20" t="n">
         <v>0</v>
@@ -1908,15 +1912,15 @@
       <c r="G37" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H37" s="20" t="n">
-        <v/>
-      </c>
-      <c r="I37" s="20" t="n">
-        <v/>
+      <c r="H37" s="22" t="n">
+        <v>-26.16</v>
+      </c>
+      <c r="I37" s="22" t="n">
+        <v>-19.9</v>
       </c>
       <c r="J37" s="23" t="inlineStr">
         <is>
-          <t>매일경제 기사 언급 / 매일경제 기사 언급 / 한국경제 헤드라인 언급</t>
+          <t>매일경제 헤드라인 언급</t>
         </is>
       </c>
       <c r="K37" s="23" t="n">
@@ -1926,7 +1930,7 @@
     <row r="38" ht="18" customHeight="1">
       <c r="A38" s="20" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="B38" s="20" t="n">
@@ -1934,7 +1938,7 @@
       </c>
       <c r="C38" s="21" t="inlineStr">
         <is>
-          <t>일성건설</t>
+          <t>보해양조</t>
         </is>
       </c>
       <c r="D38" s="20" t="n">
@@ -1949,27 +1953,25 @@
       <c r="G38" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H38" s="22" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="I38" s="22" t="n">
-        <v>48.92</v>
+      <c r="H38" s="24" t="n">
+        <v>29.88</v>
+      </c>
+      <c r="I38" s="24" t="n">
+        <v>58.36</v>
       </c>
       <c r="J38" s="23" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +259% / 중요공시 1건</t>
-        </is>
-      </c>
-      <c r="K38" s="23" t="inlineStr">
-        <is>
-          <t>네이버, 공시</t>
-        </is>
+          <t>매일경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K38" s="23" t="n">
+        <v/>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
       <c r="A39" s="20" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="B39" s="20" t="n">
@@ -1977,7 +1979,7 @@
       </c>
       <c r="C39" s="21" t="inlineStr">
         <is>
-          <t>삼성SDI</t>
+          <t>LG전자</t>
         </is>
       </c>
       <c r="D39" s="20" t="n">
@@ -1992,11 +1994,11 @@
       <c r="G39" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H39" s="24" t="n">
-        <v>-5.09</v>
+      <c r="H39" s="22" t="n">
+        <v>-7.44</v>
       </c>
       <c r="I39" s="22" t="n">
-        <v>4.71</v>
+        <v>-6.21</v>
       </c>
       <c r="J39" s="23" t="inlineStr">
         <is>
@@ -2008,181 +2010,179 @@
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
-      <c r="A40" s="25" t="inlineStr">
-        <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="B40" s="25" t="n">
+      <c r="A40" s="20" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="B40" s="20" t="n">
         <v>27</v>
       </c>
-      <c r="C40" s="26" t="inlineStr">
-        <is>
-          <t>JW신약</t>
-        </is>
-      </c>
-      <c r="D40" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="E40" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="F40" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="G40" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="H40" s="27" t="n">
-        <v>-11.56</v>
-      </c>
-      <c r="I40" s="28" t="n">
-        <v>58.72</v>
-      </c>
-      <c r="J40" s="29" t="inlineStr">
-        <is>
-          <t>네이버 검색 당일 +622%</t>
-        </is>
-      </c>
-      <c r="K40" s="29" t="inlineStr">
+      <c r="C40" s="21" t="inlineStr">
+        <is>
+          <t>HJ중공업</t>
+        </is>
+      </c>
+      <c r="D40" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="E40" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="F40" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G40" s="20" t="n">
+        <v>3</v>
+      </c>
+      <c r="H40" s="22" t="n">
+        <v>-3.67</v>
+      </c>
+      <c r="I40" s="24" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="J40" s="23" t="inlineStr">
+        <is>
+          <t>중요공시 2건 / 중요공시 7일 +100%</t>
+        </is>
+      </c>
+      <c r="K40" s="23" t="inlineStr">
+        <is>
+          <t>공시</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="18" customHeight="1">
+      <c r="A41" s="20" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="B41" s="20" t="n">
+        <v>28</v>
+      </c>
+      <c r="C41" s="21" t="inlineStr">
+        <is>
+          <t>HD현대중공업</t>
+        </is>
+      </c>
+      <c r="D41" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="E41" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="F41" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G41" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" s="22" t="n">
+        <v>-2.49</v>
+      </c>
+      <c r="I41" s="24" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="J41" s="23" t="inlineStr">
+        <is>
+          <t>중요공시 1건 / 한국경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K41" s="23" t="inlineStr">
+        <is>
+          <t>공시</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="18" customHeight="1">
+      <c r="A42" s="20" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="B42" s="20" t="n">
+        <v>29</v>
+      </c>
+      <c r="C42" s="21" t="inlineStr">
+        <is>
+          <t>전기차</t>
+        </is>
+      </c>
+      <c r="D42" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="E42" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="F42" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G42" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" s="20" t="n">
+        <v/>
+      </c>
+      <c r="I42" s="20" t="n">
+        <v/>
+      </c>
+      <c r="J42" s="23" t="inlineStr">
+        <is>
+          <t>네이버뉴스 기사 언급 / 매일경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K42" s="23" t="inlineStr">
         <is>
           <t>네이버</t>
         </is>
       </c>
     </row>
-    <row r="41" ht="18" customHeight="1">
-      <c r="A41" s="25" t="inlineStr">
-        <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="B41" s="25" t="n">
-        <v>28</v>
-      </c>
-      <c r="C41" s="26" t="inlineStr">
-        <is>
-          <t>TS트릴리온</t>
-        </is>
-      </c>
-      <c r="D41" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="E41" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="F41" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="G41" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="H41" s="27" t="n">
-        <v>-8.75</v>
-      </c>
-      <c r="I41" s="28" t="n">
-        <v>21.49</v>
-      </c>
-      <c r="J41" s="29" t="inlineStr">
-        <is>
-          <t>네이버 검색 당일 +379%</t>
-        </is>
-      </c>
-      <c r="K41" s="29" t="inlineStr">
-        <is>
-          <t>네이버</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="18" customHeight="1">
-      <c r="A42" s="25" t="inlineStr">
-        <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="B42" s="25" t="n">
-        <v>29</v>
-      </c>
-      <c r="C42" s="26" t="inlineStr">
-        <is>
-          <t>강동씨앤엘</t>
-        </is>
-      </c>
-      <c r="D42" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="E42" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="F42" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="G42" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="H42" s="28" t="n">
+    <row r="43" ht="18" customHeight="1">
+      <c r="A43" s="20" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="B43" s="20" t="n">
         <v>30</v>
       </c>
-      <c r="I42" s="28" t="n">
-        <v>77.05</v>
-      </c>
-      <c r="J42" s="29" t="inlineStr">
-        <is>
-          <t>네이버 검색 당일 +281%</t>
-        </is>
-      </c>
-      <c r="K42" s="29" t="inlineStr">
-        <is>
-          <t>네이버</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="18" customHeight="1">
-      <c r="A43" s="25" t="inlineStr">
-        <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="B43" s="25" t="n">
-        <v>30</v>
-      </c>
-      <c r="C43" s="26" t="inlineStr">
-        <is>
-          <t>현대약품</t>
-        </is>
-      </c>
-      <c r="D43" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="E43" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="F43" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="G43" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="H43" s="28" t="n">
-        <v>4.81</v>
-      </c>
-      <c r="I43" s="28" t="n">
-        <v>48.34</v>
-      </c>
-      <c r="J43" s="29" t="inlineStr">
-        <is>
-          <t>네이버 검색 당일 +228%</t>
-        </is>
-      </c>
-      <c r="K43" s="29" t="inlineStr">
-        <is>
-          <t>네이버</t>
-        </is>
+      <c r="C43" s="21" t="inlineStr">
+        <is>
+          <t>HD현대</t>
+        </is>
+      </c>
+      <c r="D43" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="E43" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="F43" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G43" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" s="22" t="n">
+        <v>-3.35</v>
+      </c>
+      <c r="I43" s="22" t="n">
+        <v>-5.53</v>
+      </c>
+      <c r="J43" s="23" t="inlineStr">
+        <is>
+          <t>매일경제 기사 언급 / 한국경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K43" s="23" t="n">
+        <v/>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
       <c r="A44" s="25" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="B44" s="25" t="n">
@@ -2190,7 +2190,7 @@
       </c>
       <c r="C44" s="26" t="inlineStr">
         <is>
-          <t>위더스제약</t>
+          <t>JW신약</t>
         </is>
       </c>
       <c r="D44" s="25" t="n">
@@ -2206,17 +2206,17 @@
         <v>0</v>
       </c>
       <c r="H44" s="27" t="n">
-        <v>-5.11</v>
-      </c>
-      <c r="I44" s="28" t="n">
-        <v>18.36</v>
-      </c>
-      <c r="J44" s="29" t="inlineStr">
-        <is>
-          <t>네이버 검색 당일 +197%</t>
-        </is>
-      </c>
-      <c r="K44" s="29" t="inlineStr">
+        <v>13.08</v>
+      </c>
+      <c r="I44" s="27" t="n">
+        <v>70.94</v>
+      </c>
+      <c r="J44" s="28" t="inlineStr">
+        <is>
+          <t>네이버 검색 당일 +953%</t>
+        </is>
+      </c>
+      <c r="K44" s="28" t="inlineStr">
         <is>
           <t>네이버</t>
         </is>
@@ -2225,7 +2225,7 @@
     <row r="45" ht="18" customHeight="1">
       <c r="A45" s="25" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="B45" s="25" t="n">
@@ -2233,7 +2233,7 @@
       </c>
       <c r="C45" s="26" t="inlineStr">
         <is>
-          <t>하이스틸</t>
+          <t>강동씨앤엘</t>
         </is>
       </c>
       <c r="D45" s="25" t="n">
@@ -2249,17 +2249,17 @@
         <v>0</v>
       </c>
       <c r="H45" s="27" t="n">
-        <v>-1.7</v>
-      </c>
-      <c r="I45" s="28" t="n">
-        <v>14.95</v>
-      </c>
-      <c r="J45" s="29" t="inlineStr">
-        <is>
-          <t>네이버 검색 당일 +105%</t>
-        </is>
-      </c>
-      <c r="K45" s="29" t="inlineStr">
+        <v>29.91</v>
+      </c>
+      <c r="I45" s="27" t="n">
+        <v>121.56</v>
+      </c>
+      <c r="J45" s="28" t="inlineStr">
+        <is>
+          <t>네이버 검색 당일 +830%</t>
+        </is>
+      </c>
+      <c r="K45" s="28" t="inlineStr">
         <is>
           <t>네이버</t>
         </is>
@@ -2268,7 +2268,7 @@
     <row r="46" ht="18" customHeight="1">
       <c r="A46" s="25" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="B46" s="25" t="n">
@@ -2276,42 +2276,42 @@
       </c>
       <c r="C46" s="26" t="inlineStr">
         <is>
-          <t>한솔테크닉스</t>
+          <t>삼익제약</t>
         </is>
       </c>
       <c r="D46" s="25" t="n">
         <v>3</v>
       </c>
       <c r="E46" s="25" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F46" s="25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G46" s="25" t="n">
         <v>0</v>
       </c>
       <c r="H46" s="27" t="n">
-        <v>-10.37</v>
-      </c>
-      <c r="I46" s="28" t="n">
-        <v>19.15</v>
-      </c>
-      <c r="J46" s="29" t="inlineStr">
-        <is>
-          <t>중요공시 2건 / 중요공시 3일 +100%</t>
-        </is>
-      </c>
-      <c r="K46" s="29" t="inlineStr">
-        <is>
-          <t>공시</t>
+        <v>29.98</v>
+      </c>
+      <c r="I46" s="27" t="n">
+        <v>41.82</v>
+      </c>
+      <c r="J46" s="28" t="inlineStr">
+        <is>
+          <t>네이버 검색 당일 +439%</t>
+        </is>
+      </c>
+      <c r="K46" s="28" t="inlineStr">
+        <is>
+          <t>네이버</t>
         </is>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
       <c r="A47" s="25" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="B47" s="25" t="n">
@@ -2319,42 +2319,42 @@
       </c>
       <c r="C47" s="26" t="inlineStr">
         <is>
-          <t>삼보산업</t>
+          <t>현대약품</t>
         </is>
       </c>
       <c r="D47" s="25" t="n">
         <v>3</v>
       </c>
       <c r="E47" s="25" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F47" s="25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G47" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H47" s="28" t="n">
-        <v>30</v>
-      </c>
-      <c r="I47" s="28" t="n">
-        <v>38.54</v>
-      </c>
-      <c r="J47" s="29" t="inlineStr">
-        <is>
-          <t>중요공시 2건 / 중요공시 3일 +100%</t>
-        </is>
-      </c>
-      <c r="K47" s="29" t="inlineStr">
-        <is>
-          <t>공시</t>
+      <c r="H47" s="29" t="n">
+        <v>-4.12</v>
+      </c>
+      <c r="I47" s="27" t="n">
+        <v>42.23</v>
+      </c>
+      <c r="J47" s="28" t="inlineStr">
+        <is>
+          <t>네이버 검색 당일 +339%</t>
+        </is>
+      </c>
+      <c r="K47" s="28" t="inlineStr">
+        <is>
+          <t>네이버</t>
         </is>
       </c>
     </row>
     <row r="48" ht="18" customHeight="1">
       <c r="A48" s="25" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="B48" s="25" t="n">
@@ -2362,7 +2362,7 @@
       </c>
       <c r="C48" s="26" t="inlineStr">
         <is>
-          <t>한화솔루션</t>
+          <t>위더스제약</t>
         </is>
       </c>
       <c r="D48" s="25" t="n">
@@ -2378,26 +2378,26 @@
         <v>0</v>
       </c>
       <c r="H48" s="27" t="n">
-        <v>-7.75</v>
-      </c>
-      <c r="I48" s="28" t="n">
-        <v>9.32</v>
-      </c>
-      <c r="J48" s="29" t="inlineStr">
-        <is>
-          <t>중요공시 3건</t>
-        </is>
-      </c>
-      <c r="K48" s="29" t="inlineStr">
-        <is>
-          <t>공시</t>
+        <v>13.59</v>
+      </c>
+      <c r="I48" s="27" t="n">
+        <v>33.03</v>
+      </c>
+      <c r="J48" s="28" t="inlineStr">
+        <is>
+          <t>네이버 검색 당일 +269%</t>
+        </is>
+      </c>
+      <c r="K48" s="28" t="inlineStr">
+        <is>
+          <t>네이버</t>
         </is>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1">
       <c r="A49" s="25" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="B49" s="25" t="n">
@@ -2405,7 +2405,7 @@
       </c>
       <c r="C49" s="26" t="inlineStr">
         <is>
-          <t>진원생명과학</t>
+          <t>삼화전자</t>
         </is>
       </c>
       <c r="D49" s="25" t="n">
@@ -2421,26 +2421,26 @@
         <v>0</v>
       </c>
       <c r="H49" s="27" t="n">
-        <v>-4.75</v>
+        <v>2.81</v>
       </c>
       <c r="I49" s="27" t="n">
-        <v>-8.17</v>
-      </c>
-      <c r="J49" s="29" t="inlineStr">
-        <is>
-          <t>중요공시 3건</t>
-        </is>
-      </c>
-      <c r="K49" s="29" t="inlineStr">
-        <is>
-          <t>공시</t>
+        <v>73.59</v>
+      </c>
+      <c r="J49" s="28" t="inlineStr">
+        <is>
+          <t>네이버 검색 당일 +230%</t>
+        </is>
+      </c>
+      <c r="K49" s="28" t="inlineStr">
+        <is>
+          <t>네이버</t>
         </is>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
       <c r="A50" s="25" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="B50" s="25" t="n">
@@ -2448,7 +2448,7 @@
       </c>
       <c r="C50" s="26" t="inlineStr">
         <is>
-          <t>넥사다이내믹스</t>
+          <t>율촌</t>
         </is>
       </c>
       <c r="D50" s="25" t="n">
@@ -2463,27 +2463,27 @@
       <c r="G50" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H50" s="28" t="n">
-        <v>16.18</v>
-      </c>
-      <c r="I50" s="28" t="n">
-        <v>14.52</v>
-      </c>
-      <c r="J50" s="29" t="inlineStr">
-        <is>
-          <t>중요공시 3건</t>
-        </is>
-      </c>
-      <c r="K50" s="29" t="inlineStr">
-        <is>
-          <t>공시</t>
+      <c r="H50" s="29" t="n">
+        <v>-13.55</v>
+      </c>
+      <c r="I50" s="27" t="n">
+        <v>30.73</v>
+      </c>
+      <c r="J50" s="28" t="inlineStr">
+        <is>
+          <t>네이버 검색 당일 +153%</t>
+        </is>
+      </c>
+      <c r="K50" s="28" t="inlineStr">
+        <is>
+          <t>네이버</t>
         </is>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
       <c r="A51" s="25" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="B51" s="25" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="C51" s="26" t="inlineStr">
         <is>
-          <t>스피어</t>
+          <t>티웨이홀딩스</t>
         </is>
       </c>
       <c r="D51" s="25" t="n">
@@ -2506,27 +2506,27 @@
       <c r="G51" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H51" s="27" t="n">
-        <v>-9.5</v>
+      <c r="H51" s="29" t="n">
+        <v>-7.09</v>
       </c>
       <c r="I51" s="27" t="n">
-        <v>-29.48</v>
-      </c>
-      <c r="J51" s="29" t="inlineStr">
-        <is>
-          <t>중요공시 3건</t>
-        </is>
-      </c>
-      <c r="K51" s="29" t="inlineStr">
-        <is>
-          <t>공시</t>
+        <v>26.88</v>
+      </c>
+      <c r="J51" s="28" t="inlineStr">
+        <is>
+          <t>네이버 검색 당일 +141%</t>
+        </is>
+      </c>
+      <c r="K51" s="28" t="inlineStr">
+        <is>
+          <t>네이버</t>
         </is>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1">
       <c r="A52" s="25" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="B52" s="25" t="n">
@@ -2534,7 +2534,7 @@
       </c>
       <c r="C52" s="26" t="inlineStr">
         <is>
-          <t>LB세미콘</t>
+          <t>성문전자</t>
         </is>
       </c>
       <c r="D52" s="25" t="n">
@@ -2550,26 +2550,26 @@
         <v>0</v>
       </c>
       <c r="H52" s="27" t="n">
-        <v>-0.19</v>
-      </c>
-      <c r="I52" s="28" t="n">
-        <v>14.94</v>
-      </c>
-      <c r="J52" s="29" t="inlineStr">
-        <is>
-          <t>중요공시 3건</t>
-        </is>
-      </c>
-      <c r="K52" s="29" t="inlineStr">
-        <is>
-          <t>공시</t>
+        <v>4.43</v>
+      </c>
+      <c r="I52" s="27" t="n">
+        <v>40.24</v>
+      </c>
+      <c r="J52" s="28" t="inlineStr">
+        <is>
+          <t>네이버 검색 당일 +111%</t>
+        </is>
+      </c>
+      <c r="K52" s="28" t="inlineStr">
+        <is>
+          <t>네이버</t>
         </is>
       </c>
     </row>
     <row r="53" ht="18" customHeight="1">
       <c r="A53" s="25" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="B53" s="25" t="n">
@@ -2577,7 +2577,7 @@
       </c>
       <c r="C53" s="26" t="inlineStr">
         <is>
-          <t>피노</t>
+          <t>동일스틸럭스</t>
         </is>
       </c>
       <c r="D53" s="25" t="n">
@@ -2592,27 +2592,27 @@
       <c r="G53" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H53" s="28" t="n">
-        <v>1.91</v>
+      <c r="H53" s="29" t="n">
+        <v>-11.15</v>
       </c>
       <c r="I53" s="27" t="n">
-        <v>-5.43</v>
-      </c>
-      <c r="J53" s="29" t="inlineStr">
-        <is>
-          <t>중요공시 3건</t>
-        </is>
-      </c>
-      <c r="K53" s="29" t="inlineStr">
-        <is>
-          <t>공시</t>
+        <v>29.05</v>
+      </c>
+      <c r="J53" s="28" t="inlineStr">
+        <is>
+          <t>네이버 검색 당일 +105%</t>
+        </is>
+      </c>
+      <c r="K53" s="28" t="inlineStr">
+        <is>
+          <t>네이버</t>
         </is>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
       <c r="A54" s="25" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="B54" s="25" t="n">
@@ -2620,42 +2620,42 @@
       </c>
       <c r="C54" s="26" t="inlineStr">
         <is>
-          <t>HJ중공업</t>
+          <t>부국철강</t>
         </is>
       </c>
       <c r="D54" s="25" t="n">
         <v>3</v>
       </c>
       <c r="E54" s="25" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F54" s="25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G54" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H54" s="27" t="n">
-        <v>-3.14</v>
-      </c>
-      <c r="I54" s="28" t="n">
-        <v>11.3</v>
-      </c>
-      <c r="J54" s="29" t="inlineStr">
-        <is>
-          <t>중요공시 2건 / 중요공시 3일 +100%</t>
-        </is>
-      </c>
-      <c r="K54" s="29" t="inlineStr">
-        <is>
-          <t>공시</t>
+      <c r="H54" s="29" t="n">
+        <v>-13.76</v>
+      </c>
+      <c r="I54" s="27" t="n">
+        <v>3.49</v>
+      </c>
+      <c r="J54" s="28" t="inlineStr">
+        <is>
+          <t>네이버 검색 당일 +104%</t>
+        </is>
+      </c>
+      <c r="K54" s="28" t="inlineStr">
+        <is>
+          <t>네이버</t>
         </is>
       </c>
     </row>
     <row r="55" ht="18" customHeight="1">
       <c r="A55" s="25" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="B55" s="25" t="n">
@@ -2663,7 +2663,7 @@
       </c>
       <c r="C55" s="26" t="inlineStr">
         <is>
-          <t>현대모비스</t>
+          <t>대원전선</t>
         </is>
       </c>
       <c r="D55" s="25" t="n">
@@ -2678,25 +2678,27 @@
       <c r="G55" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H55" s="27" t="n">
-        <v>-4.44</v>
-      </c>
-      <c r="I55" s="28" t="n">
-        <v>4.69</v>
-      </c>
-      <c r="J55" s="29" t="inlineStr">
-        <is>
-          <t>매일경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K55" s="29" t="n">
-        <v/>
+      <c r="H55" s="29" t="n">
+        <v>-3.73</v>
+      </c>
+      <c r="I55" s="27" t="n">
+        <v>6.02</v>
+      </c>
+      <c r="J55" s="28" t="inlineStr">
+        <is>
+          <t>네이버 검색 당일 +60% / 중요공시 1건</t>
+        </is>
+      </c>
+      <c r="K55" s="28" t="inlineStr">
+        <is>
+          <t>공시, 네이버</t>
+        </is>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1">
       <c r="A56" s="25" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="B56" s="25" t="n">
@@ -2704,7 +2706,7 @@
       </c>
       <c r="C56" s="26" t="inlineStr">
         <is>
-          <t>한전기술</t>
+          <t>HMM</t>
         </is>
       </c>
       <c r="D56" s="25" t="n">
@@ -2719,25 +2721,25 @@
       <c r="G56" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H56" s="28" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="I56" s="28" t="n">
-        <v>17.44</v>
-      </c>
-      <c r="J56" s="29" t="inlineStr">
+      <c r="H56" s="29" t="n">
+        <v>-1.47</v>
+      </c>
+      <c r="I56" s="27" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J56" s="28" t="inlineStr">
         <is>
           <t>매일경제 헤드라인 언급</t>
         </is>
       </c>
-      <c r="K56" s="29" t="n">
+      <c r="K56" s="28" t="n">
         <v/>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1">
       <c r="A57" s="25" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="B57" s="25" t="n">
@@ -2745,7 +2747,7 @@
       </c>
       <c r="C57" s="26" t="inlineStr">
         <is>
-          <t>현대제철</t>
+          <t>우리기술</t>
         </is>
       </c>
       <c r="D57" s="25" t="n">
@@ -2760,25 +2762,27 @@
       <c r="G57" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H57" s="27" t="n">
-        <v>-4.44</v>
-      </c>
-      <c r="I57" s="28" t="n">
-        <v>3.73</v>
-      </c>
-      <c r="J57" s="29" t="inlineStr">
-        <is>
-          <t>매일경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K57" s="29" t="n">
-        <v/>
+      <c r="H57" s="29" t="n">
+        <v>-1.89</v>
+      </c>
+      <c r="I57" s="29" t="n">
+        <v>-17.47</v>
+      </c>
+      <c r="J57" s="28" t="inlineStr">
+        <is>
+          <t>네이버뉴스 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K57" s="28" t="inlineStr">
+        <is>
+          <t>네이버</t>
+        </is>
       </c>
     </row>
     <row r="58" ht="18" customHeight="1">
       <c r="A58" s="25" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="B58" s="25" t="n">
@@ -2786,7 +2790,7 @@
       </c>
       <c r="C58" s="26" t="inlineStr">
         <is>
-          <t>피스피스스튜디오</t>
+          <t>휴림로봇</t>
         </is>
       </c>
       <c r="D58" s="25" t="n">
@@ -2801,25 +2805,27 @@
       <c r="G58" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H58" s="27" t="n">
-        <v>-7.95</v>
-      </c>
-      <c r="I58" s="27" t="n">
-        <v>-17.94</v>
-      </c>
-      <c r="J58" s="29" t="inlineStr">
-        <is>
-          <t>한국경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K58" s="29" t="n">
-        <v/>
+      <c r="H58" s="29" t="n">
+        <v>-3.34</v>
+      </c>
+      <c r="I58" s="29" t="n">
+        <v>-13.73</v>
+      </c>
+      <c r="J58" s="28" t="inlineStr">
+        <is>
+          <t>네이버뉴스 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K58" s="28" t="inlineStr">
+        <is>
+          <t>네이버</t>
+        </is>
       </c>
     </row>
     <row r="59" ht="18" customHeight="1">
       <c r="A59" s="25" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="B59" s="25" t="n">
@@ -2827,7 +2833,7 @@
       </c>
       <c r="C59" s="26" t="inlineStr">
         <is>
-          <t>이차전지</t>
+          <t>LB세미콘</t>
         </is>
       </c>
       <c r="D59" s="25" t="n">
@@ -2842,25 +2848,27 @@
       <c r="G59" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H59" s="25" t="n">
-        <v/>
-      </c>
-      <c r="I59" s="25" t="n">
-        <v/>
-      </c>
-      <c r="J59" s="29" t="inlineStr">
-        <is>
-          <t>한국경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K59" s="29" t="n">
-        <v/>
+      <c r="H59" s="29" t="n">
+        <v>-3.58</v>
+      </c>
+      <c r="I59" s="27" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="J59" s="28" t="inlineStr">
+        <is>
+          <t>중요공시 3건</t>
+        </is>
+      </c>
+      <c r="K59" s="28" t="inlineStr">
+        <is>
+          <t>공시</t>
+        </is>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1">
       <c r="A60" s="25" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="B60" s="25" t="n">
@@ -2868,7 +2876,7 @@
       </c>
       <c r="C60" s="26" t="inlineStr">
         <is>
-          <t>SK스퀘어</t>
+          <t>모아데이타</t>
         </is>
       </c>
       <c r="D60" s="25" t="n">
@@ -2883,25 +2891,27 @@
       <c r="G60" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H60" s="28" t="n">
-        <v>6.52</v>
-      </c>
-      <c r="I60" s="28" t="n">
-        <v>38.44</v>
-      </c>
-      <c r="J60" s="29" t="inlineStr">
-        <is>
-          <t>매일경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K60" s="29" t="n">
-        <v/>
+      <c r="H60" s="27" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="I60" s="27" t="n">
+        <v>13.39</v>
+      </c>
+      <c r="J60" s="28" t="inlineStr">
+        <is>
+          <t>중요공시 3건</t>
+        </is>
+      </c>
+      <c r="K60" s="28" t="inlineStr">
+        <is>
+          <t>공시</t>
+        </is>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
       <c r="A61" s="25" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="B61" s="25" t="n">
@@ -2909,40 +2919,42 @@
       </c>
       <c r="C61" s="26" t="inlineStr">
         <is>
-          <t>넷마블</t>
+          <t>오르비텍</t>
         </is>
       </c>
       <c r="D61" s="25" t="n">
         <v>3</v>
       </c>
       <c r="E61" s="25" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F61" s="25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G61" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H61" s="27" t="n">
-        <v>-3.12</v>
-      </c>
-      <c r="I61" s="27" t="n">
-        <v>-6.27</v>
-      </c>
-      <c r="J61" s="29" t="inlineStr">
-        <is>
-          <t>매일경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K61" s="29" t="n">
-        <v/>
+      <c r="H61" s="29" t="n">
+        <v>-8.24</v>
+      </c>
+      <c r="I61" s="29" t="n">
+        <v>-10.69</v>
+      </c>
+      <c r="J61" s="28" t="inlineStr">
+        <is>
+          <t>중요공시 2건 / 중요공시 3일 +100%</t>
+        </is>
+      </c>
+      <c r="K61" s="28" t="inlineStr">
+        <is>
+          <t>공시</t>
+        </is>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1">
       <c r="A62" s="25" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="B62" s="25" t="n">
@@ -2950,7 +2962,7 @@
       </c>
       <c r="C62" s="26" t="inlineStr">
         <is>
-          <t>엔터</t>
+          <t>한전기술</t>
         </is>
       </c>
       <c r="D62" s="25" t="n">
@@ -2965,25 +2977,25 @@
       <c r="G62" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H62" s="25" t="n">
-        <v/>
-      </c>
-      <c r="I62" s="25" t="n">
-        <v/>
-      </c>
-      <c r="J62" s="29" t="inlineStr">
+      <c r="H62" s="29" t="n">
+        <v>-9.51</v>
+      </c>
+      <c r="I62" s="29" t="n">
+        <v>-18.24</v>
+      </c>
+      <c r="J62" s="28" t="inlineStr">
         <is>
           <t>매일경제 헤드라인 언급</t>
         </is>
       </c>
-      <c r="K62" s="29" t="n">
+      <c r="K62" s="28" t="n">
         <v/>
       </c>
     </row>
     <row r="63" ht="18" customHeight="1">
       <c r="A63" s="25" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="B63" s="25" t="n">
@@ -2991,14 +3003,14 @@
       </c>
       <c r="C63" s="26" t="inlineStr">
         <is>
-          <t>삼화전자</t>
+          <t>한화</t>
         </is>
       </c>
       <c r="D63" s="25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E63" s="25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F63" s="25" t="n">
         <v>0</v>
@@ -3006,21 +3018,19 @@
       <c r="G63" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H63" s="28" t="n">
-        <v>29.86</v>
-      </c>
-      <c r="I63" s="28" t="n">
-        <v>70</v>
-      </c>
-      <c r="J63" s="29" t="inlineStr">
-        <is>
-          <t>네이버 검색 당일 +96%</t>
-        </is>
-      </c>
-      <c r="K63" s="29" t="inlineStr">
-        <is>
-          <t>네이버</t>
-        </is>
+      <c r="H63" s="29" t="n">
+        <v>-4.71</v>
+      </c>
+      <c r="I63" s="29" t="n">
+        <v>-0.95</v>
+      </c>
+      <c r="J63" s="28" t="inlineStr">
+        <is>
+          <t>매일경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K63" s="28" t="n">
+        <v/>
       </c>
     </row>
   </sheetData>
@@ -3116,22 +3126,22 @@
         <v>1</v>
       </c>
       <c r="C3" s="25" t="n">
-        <v>85</v>
+        <v>60</v>
       </c>
       <c r="D3" s="25" t="n">
-        <v>85</v>
+        <v>60</v>
       </c>
       <c r="E3" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F3" s="25" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="G3" s="25" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="H3" s="25" t="n"/>
@@ -3147,29 +3157,29 @@
         <v>1</v>
       </c>
       <c r="C4" s="25" t="n">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="D4" s="25" t="n">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="E4" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F4" s="25" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="G4" s="25" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="H4" s="27" t="n">
-        <v>-2.97</v>
-      </c>
-      <c r="I4" s="28" t="n">
-        <v>19.48</v>
+        <v>5.39</v>
+      </c>
+      <c r="I4" s="27" t="n">
+        <v>22.09</v>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1">
@@ -3182,185 +3192,197 @@
         <v>1</v>
       </c>
       <c r="C5" s="25" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D5" s="25" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E5" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F5" s="25" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="G5" s="25" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="H5" s="28" t="n">
-        <v>6.51</v>
-      </c>
-      <c r="I5" s="28" t="n">
-        <v>27.8</v>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="H5" s="27" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="I5" s="27" t="n">
+        <v>28.56</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
       <c r="A6" s="26" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>삼성전기</t>
         </is>
       </c>
       <c r="B6" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C6" s="25" t="n">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="D6" s="25" t="n">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="E6" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F6" s="25" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="G6" s="25" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="H6" s="28" t="n">
-        <v>4.62</v>
-      </c>
-      <c r="I6" s="28" t="n">
-        <v>21.24</v>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="H6" s="27" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="I6" s="27" t="n">
+        <v>32.44</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
       <c r="A7" s="26" t="inlineStr">
         <is>
-          <t>원전</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B7" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C7" s="25" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="D7" s="25" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="E7" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F7" s="25" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="G7" s="25" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="H7" s="25" t="n"/>
-      <c r="I7" s="25" t="n"/>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="H7" s="29" t="n">
+        <v>-2.34</v>
+      </c>
+      <c r="I7" s="27" t="n">
+        <v>9.77</v>
+      </c>
     </row>
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="26" t="inlineStr">
         <is>
-          <t>바이오</t>
+          <t>현대차</t>
         </is>
       </c>
       <c r="B8" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C8" s="25" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D8" s="25" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E8" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F8" s="25" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="G8" s="25" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="H8" s="25" t="n"/>
-      <c r="I8" s="25" t="n"/>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="H8" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="I8" s="27" t="n">
+        <v>0.99</v>
+      </c>
     </row>
     <row r="9" ht="18" customHeight="1">
       <c r="A9" s="26" t="inlineStr">
         <is>
-          <t>인공지능</t>
+          <t>대한항공</t>
         </is>
       </c>
       <c r="B9" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C9" s="25" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D9" s="25" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E9" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F9" s="25" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="G9" s="25" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="H9" s="25" t="n"/>
-      <c r="I9" s="25" t="n"/>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="H9" s="29" t="n">
+        <v>-3.12</v>
+      </c>
+      <c r="I9" s="27" t="n">
+        <v>5.08</v>
+      </c>
     </row>
     <row r="10" ht="18" customHeight="1">
       <c r="A10" s="26" t="inlineStr">
         <is>
-          <t>제약</t>
+          <t>로봇</t>
         </is>
       </c>
       <c r="B10" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C10" s="25" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D10" s="25" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E10" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F10" s="25" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="G10" s="25" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="H10" s="25" t="n"/>
@@ -3369,7 +3391,7 @@
     <row r="11" ht="18" customHeight="1">
       <c r="A11" s="26" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>바이오</t>
         </is>
       </c>
       <c r="B11" s="25" t="n">
@@ -3386,25 +3408,21 @@
       </c>
       <c r="F11" s="25" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="G11" s="25" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="H11" s="27" t="n">
-        <v>-5.64</v>
-      </c>
-      <c r="I11" s="28" t="n">
-        <v>18.59</v>
-      </c>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="H11" s="25" t="n"/>
+      <c r="I11" s="25" t="n"/>
     </row>
     <row r="12" ht="18" customHeight="1">
       <c r="A12" s="26" t="inlineStr">
         <is>
-          <t>넥써쓰</t>
+          <t>인공지능</t>
         </is>
       </c>
       <c r="B12" s="25" t="n">
@@ -3421,25 +3439,21 @@
       </c>
       <c r="F12" s="25" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="G12" s="25" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="H12" s="28" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="I12" s="28" t="n">
-        <v>28.71</v>
-      </c>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="H12" s="25" t="n"/>
+      <c r="I12" s="25" t="n"/>
     </row>
     <row r="13" ht="18" customHeight="1">
       <c r="A13" s="26" t="inlineStr">
         <is>
-          <t>전기차</t>
+          <t>제약</t>
         </is>
       </c>
       <c r="B13" s="25" t="n">
@@ -3456,12 +3470,12 @@
       </c>
       <c r="F13" s="25" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="G13" s="25" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="H13" s="25" t="n"/>
@@ -3470,73 +3484,77 @@
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="26" t="inlineStr">
         <is>
-          <t>미래에셋증권</t>
+          <t>LG</t>
         </is>
       </c>
       <c r="B14" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C14" s="25" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D14" s="25" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E14" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F14" s="25" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="G14" s="25" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="H14" s="28" t="n">
-        <v>0.6</v>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="H14" s="29" t="n">
+        <v>-0.91</v>
       </c>
       <c r="I14" s="27" t="n">
-        <v>-0.78</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
       <c r="A15" s="26" t="inlineStr">
         <is>
-          <t>방산</t>
+          <t>넥써쓰</t>
         </is>
       </c>
       <c r="B15" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C15" s="25" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D15" s="25" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E15" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F15" s="25" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="G15" s="25" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="H15" s="25" t="n"/>
-      <c r="I15" s="25" t="n"/>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="H15" s="29" t="n">
+        <v>-27.47</v>
+      </c>
+      <c r="I15" s="29" t="n">
+        <v>-4.83</v>
+      </c>
     </row>
     <row r="16" ht="18" customHeight="1">
       <c r="A16" s="26" t="inlineStr">
         <is>
-          <t>가온전선</t>
+          <t>현대로템</t>
         </is>
       </c>
       <c r="B16" s="25" t="n">
@@ -3553,95 +3571,95 @@
       </c>
       <c r="F16" s="25" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="G16" s="25" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="H16" s="28" t="n">
-        <v>13.05</v>
-      </c>
-      <c r="I16" s="28" t="n">
-        <v>18.98</v>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="H16" s="29" t="n">
+        <v>-2.13</v>
+      </c>
+      <c r="I16" s="29" t="n">
+        <v>-0.72</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
       <c r="A17" s="26" t="inlineStr">
         <is>
-          <t>삼성전기</t>
+          <t>SK스퀘어</t>
         </is>
       </c>
       <c r="B17" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C17" s="25" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D17" s="25" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E17" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F17" s="25" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="G17" s="25" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="H17" s="28" t="n">
-        <v>8.27</v>
-      </c>
-      <c r="I17" s="28" t="n">
-        <v>21.88</v>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="H17" s="27" t="n">
+        <v>4.71</v>
+      </c>
+      <c r="I17" s="27" t="n">
+        <v>31.08</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
       <c r="A18" s="26" t="inlineStr">
         <is>
-          <t>카카오</t>
+          <t>미래에셋증권</t>
         </is>
       </c>
       <c r="B18" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C18" s="25" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D18" s="25" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E18" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F18" s="25" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="G18" s="25" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="H18" s="27" t="n">
-        <v>-3.08</v>
-      </c>
-      <c r="I18" s="25" t="n">
-        <v>0</v>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="H18" s="29" t="n">
+        <v>-3.85</v>
+      </c>
+      <c r="I18" s="29" t="n">
+        <v>-6.79</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
       <c r="A19" s="26" t="inlineStr">
         <is>
-          <t>LG</t>
+          <t>삼성물산</t>
         </is>
       </c>
       <c r="B19" s="25" t="n">
@@ -3658,25 +3676,25 @@
       </c>
       <c r="F19" s="25" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="G19" s="25" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="H19" s="27" t="n">
-        <v>-2.31</v>
-      </c>
-      <c r="I19" s="28" t="n">
-        <v>2.23</v>
+        <v>1.24</v>
+      </c>
+      <c r="I19" s="27" t="n">
+        <v>13.77</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
       <c r="A20" s="26" t="inlineStr">
         <is>
-          <t>대한항공</t>
+          <t>조선</t>
         </is>
       </c>
       <c r="B20" s="25" t="n">
@@ -3693,91 +3711,91 @@
       </c>
       <c r="F20" s="25" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="G20" s="25" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="H20" s="28" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="I20" s="28" t="n">
-        <v>16.33</v>
-      </c>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="H20" s="25" t="n"/>
+      <c r="I20" s="25" t="n"/>
     </row>
     <row r="21" ht="18" customHeight="1">
       <c r="A21" s="26" t="inlineStr">
         <is>
-          <t>철강</t>
+          <t>KT</t>
         </is>
       </c>
       <c r="B21" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C21" s="25" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D21" s="25" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E21" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F21" s="25" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="G21" s="25" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="H21" s="25" t="n"/>
-      <c r="I21" s="25" t="n"/>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="H21" s="29" t="n">
+        <v>-0.37</v>
+      </c>
+      <c r="I21" s="29" t="n">
+        <v>-2.74</v>
+      </c>
     </row>
     <row r="22" ht="18" customHeight="1">
       <c r="A22" s="26" t="inlineStr">
         <is>
-          <t>현대차</t>
+          <t>씨피시스템</t>
         </is>
       </c>
       <c r="B22" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C22" s="25" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D22" s="25" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E22" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F22" s="25" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="G22" s="25" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="H22" s="27" t="n">
-        <v>-2.75</v>
-      </c>
-      <c r="I22" s="28" t="n">
-        <v>0.67</v>
+        <v>29.88</v>
+      </c>
+      <c r="I22" s="27" t="n">
+        <v>20.79</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
       <c r="A23" s="26" t="inlineStr">
         <is>
-          <t>기아</t>
+          <t>진원생명과학</t>
         </is>
       </c>
       <c r="B23" s="25" t="n">
@@ -3794,122 +3812,130 @@
       </c>
       <c r="F23" s="25" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="G23" s="25" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="H23" s="27" t="n">
-        <v>-4.51</v>
-      </c>
-      <c r="I23" s="28" t="n">
-        <v>1.79</v>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="H23" s="29" t="n">
+        <v>-17.67</v>
+      </c>
+      <c r="I23" s="29" t="n">
+        <v>-24.4</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
       <c r="A24" s="26" t="inlineStr">
         <is>
-          <t>로봇</t>
+          <t>HD현대</t>
         </is>
       </c>
       <c r="B24" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C24" s="25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D24" s="25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E24" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F24" s="25" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="G24" s="25" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="H24" s="25" t="n"/>
-      <c r="I24" s="25" t="n"/>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="H24" s="29" t="n">
+        <v>-3.35</v>
+      </c>
+      <c r="I24" s="29" t="n">
+        <v>-5.53</v>
+      </c>
     </row>
     <row r="25" ht="18" customHeight="1">
       <c r="A25" s="26" t="inlineStr">
         <is>
-          <t>조선</t>
+          <t>HD현대중공업</t>
         </is>
       </c>
       <c r="B25" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C25" s="25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D25" s="25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E25" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F25" s="25" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="G25" s="25" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="H25" s="25" t="n"/>
-      <c r="I25" s="25" t="n"/>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="H25" s="29" t="n">
+        <v>-2.49</v>
+      </c>
+      <c r="I25" s="27" t="n">
+        <v>2.62</v>
+      </c>
     </row>
     <row r="26" ht="18" customHeight="1">
       <c r="A26" s="26" t="inlineStr">
         <is>
-          <t>파두</t>
+          <t>HJ중공업</t>
         </is>
       </c>
       <c r="B26" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C26" s="25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D26" s="25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E26" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F26" s="25" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="G26" s="25" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="H26" s="27" t="n">
-        <v>-1.89</v>
-      </c>
-      <c r="I26" s="28" t="n">
-        <v>4.73</v>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="H26" s="29" t="n">
+        <v>-3.67</v>
+      </c>
+      <c r="I26" s="27" t="n">
+        <v>3.24</v>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
       <c r="A27" s="26" t="inlineStr">
         <is>
-          <t>삼성SDI</t>
+          <t>LG전자</t>
         </is>
       </c>
       <c r="B27" s="25" t="n">
@@ -3926,25 +3952,25 @@
       </c>
       <c r="F27" s="25" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="G27" s="25" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="H27" s="27" t="n">
-        <v>-5.09</v>
-      </c>
-      <c r="I27" s="28" t="n">
-        <v>4.71</v>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="H27" s="29" t="n">
+        <v>-7.44</v>
+      </c>
+      <c r="I27" s="29" t="n">
+        <v>-6.21</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
       <c r="A28" s="26" t="inlineStr">
         <is>
-          <t>일성건설</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="B28" s="25" t="n">
@@ -3961,165 +3987,161 @@
       </c>
       <c r="F28" s="25" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="G28" s="25" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="H28" s="28" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="I28" s="28" t="n">
-        <v>48.92</v>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="H28" s="29" t="n">
+        <v>-26.16</v>
+      </c>
+      <c r="I28" s="29" t="n">
+        <v>-19.9</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
       <c r="A29" s="26" t="inlineStr">
         <is>
-          <t>HJ중공업</t>
+          <t>남화토건</t>
         </is>
       </c>
       <c r="B29" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C29" s="25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D29" s="25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E29" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F29" s="25" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="G29" s="25" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="H29" s="27" t="n">
-        <v>-3.14</v>
-      </c>
-      <c r="I29" s="28" t="n">
-        <v>11.3</v>
+        <v>12.73</v>
+      </c>
+      <c r="I29" s="27" t="n">
+        <v>45.92</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
       <c r="A30" s="26" t="inlineStr">
         <is>
-          <t>JW신약</t>
+          <t>보해양조</t>
         </is>
       </c>
       <c r="B30" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C30" s="25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D30" s="25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E30" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F30" s="25" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="G30" s="25" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="H30" s="27" t="n">
-        <v>-11.56</v>
-      </c>
-      <c r="I30" s="28" t="n">
-        <v>58.72</v>
+        <v>29.88</v>
+      </c>
+      <c r="I30" s="27" t="n">
+        <v>58.36</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
       <c r="A31" s="26" t="inlineStr">
         <is>
-          <t>LB세미콘</t>
+          <t>전기차</t>
         </is>
       </c>
       <c r="B31" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C31" s="25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D31" s="25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E31" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F31" s="25" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="G31" s="25" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="H31" s="27" t="n">
-        <v>-0.19</v>
-      </c>
-      <c r="I31" s="28" t="n">
-        <v>14.94</v>
-      </c>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="H31" s="25" t="n"/>
+      <c r="I31" s="25" t="n"/>
     </row>
     <row r="32" ht="18" customHeight="1">
       <c r="A32" s="26" t="inlineStr">
         <is>
-          <t>SK스퀘어</t>
+          <t>한솔테크닉스</t>
         </is>
       </c>
       <c r="B32" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C32" s="25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D32" s="25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E32" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F32" s="25" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="G32" s="25" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="H32" s="28" t="n">
-        <v>6.52</v>
-      </c>
-      <c r="I32" s="28" t="n">
-        <v>38.44</v>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="H32" s="29" t="n">
+        <v>-4.87</v>
+      </c>
+      <c r="I32" s="27" t="n">
+        <v>7.83</v>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
       <c r="A33" s="26" t="inlineStr">
         <is>
-          <t>TS트릴리온</t>
+          <t>HMM</t>
         </is>
       </c>
       <c r="B33" s="25" t="n">
@@ -4136,25 +4158,25 @@
       </c>
       <c r="F33" s="25" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="G33" s="25" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="H33" s="27" t="n">
-        <v>-8.75</v>
-      </c>
-      <c r="I33" s="28" t="n">
-        <v>21.49</v>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="H33" s="29" t="n">
+        <v>-1.47</v>
+      </c>
+      <c r="I33" s="27" t="n">
+        <v>0.5</v>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
       <c r="A34" s="26" t="inlineStr">
         <is>
-          <t>강동씨앤엘</t>
+          <t>JW신약</t>
         </is>
       </c>
       <c r="B34" s="25" t="n">
@@ -4171,25 +4193,25 @@
       </c>
       <c r="F34" s="25" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="G34" s="25" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="H34" s="28" t="n">
-        <v>30</v>
-      </c>
-      <c r="I34" s="28" t="n">
-        <v>77.05</v>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="H34" s="27" t="n">
+        <v>13.08</v>
+      </c>
+      <c r="I34" s="27" t="n">
+        <v>70.94</v>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
       <c r="A35" s="26" t="inlineStr">
         <is>
-          <t>넥사다이내믹스</t>
+          <t>LB세미콘</t>
         </is>
       </c>
       <c r="B35" s="25" t="n">
@@ -4206,25 +4228,25 @@
       </c>
       <c r="F35" s="25" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="G35" s="25" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="H35" s="28" t="n">
-        <v>16.18</v>
-      </c>
-      <c r="I35" s="28" t="n">
-        <v>14.52</v>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="H35" s="29" t="n">
+        <v>-3.58</v>
+      </c>
+      <c r="I35" s="27" t="n">
+        <v>0.97</v>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
       <c r="A36" s="26" t="inlineStr">
         <is>
-          <t>넷마블</t>
+          <t>강동씨앤엘</t>
         </is>
       </c>
       <c r="B36" s="25" t="n">
@@ -4241,25 +4263,25 @@
       </c>
       <c r="F36" s="25" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="G36" s="25" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="H36" s="27" t="n">
-        <v>-3.12</v>
+        <v>29.91</v>
       </c>
       <c r="I36" s="27" t="n">
-        <v>-6.27</v>
+        <v>121.56</v>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
       <c r="A37" s="26" t="inlineStr">
         <is>
-          <t>삼보산업</t>
+          <t>대원전선</t>
         </is>
       </c>
       <c r="B37" s="25" t="n">
@@ -4276,25 +4298,25 @@
       </c>
       <c r="F37" s="25" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="G37" s="25" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="H37" s="28" t="n">
-        <v>30</v>
-      </c>
-      <c r="I37" s="28" t="n">
-        <v>38.54</v>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="H37" s="29" t="n">
+        <v>-3.73</v>
+      </c>
+      <c r="I37" s="27" t="n">
+        <v>6.02</v>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
       <c r="A38" s="26" t="inlineStr">
         <is>
-          <t>스피어</t>
+          <t>동일스틸럭스</t>
         </is>
       </c>
       <c r="B38" s="25" t="n">
@@ -4311,25 +4333,25 @@
       </c>
       <c r="F38" s="25" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="G38" s="25" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="H38" s="27" t="n">
-        <v>-9.5</v>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="H38" s="29" t="n">
+        <v>-11.15</v>
       </c>
       <c r="I38" s="27" t="n">
-        <v>-29.48</v>
+        <v>29.05</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
       <c r="A39" s="26" t="inlineStr">
         <is>
-          <t>엔터</t>
+          <t>모아데이타</t>
         </is>
       </c>
       <c r="B39" s="25" t="n">
@@ -4346,21 +4368,25 @@
       </c>
       <c r="F39" s="25" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="G39" s="25" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="H39" s="25" t="n"/>
-      <c r="I39" s="25" t="n"/>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="H39" s="27" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="I39" s="27" t="n">
+        <v>13.39</v>
+      </c>
     </row>
     <row r="40" ht="18" customHeight="1">
       <c r="A40" s="26" t="inlineStr">
         <is>
-          <t>위더스제약</t>
+          <t>부국철강</t>
         </is>
       </c>
       <c r="B40" s="25" t="n">
@@ -4377,25 +4403,25 @@
       </c>
       <c r="F40" s="25" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="G40" s="25" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="H40" s="27" t="n">
-        <v>-5.11</v>
-      </c>
-      <c r="I40" s="28" t="n">
-        <v>18.36</v>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="H40" s="29" t="n">
+        <v>-13.76</v>
+      </c>
+      <c r="I40" s="27" t="n">
+        <v>3.49</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
       <c r="A41" s="26" t="inlineStr">
         <is>
-          <t>이차전지</t>
+          <t>삼익제약</t>
         </is>
       </c>
       <c r="B41" s="25" t="n">
@@ -4412,21 +4438,25 @@
       </c>
       <c r="F41" s="25" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="G41" s="25" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="H41" s="25" t="n"/>
-      <c r="I41" s="25" t="n"/>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="H41" s="27" t="n">
+        <v>29.98</v>
+      </c>
+      <c r="I41" s="27" t="n">
+        <v>41.82</v>
+      </c>
     </row>
     <row r="42" ht="18" customHeight="1">
       <c r="A42" s="26" t="inlineStr">
         <is>
-          <t>진원생명과학</t>
+          <t>삼화전자</t>
         </is>
       </c>
       <c r="B42" s="25" t="n">
@@ -4443,25 +4473,25 @@
       </c>
       <c r="F42" s="25" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="G42" s="25" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="H42" s="27" t="n">
-        <v>-4.75</v>
+        <v>2.81</v>
       </c>
       <c r="I42" s="27" t="n">
-        <v>-8.17</v>
+        <v>73.59</v>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1">
       <c r="A43" s="26" t="inlineStr">
         <is>
-          <t>피노</t>
+          <t>성문전자</t>
         </is>
       </c>
       <c r="B43" s="25" t="n">
@@ -4478,25 +4508,25 @@
       </c>
       <c r="F43" s="25" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="G43" s="25" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="H43" s="28" t="n">
-        <v>1.91</v>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="H43" s="27" t="n">
+        <v>4.43</v>
       </c>
       <c r="I43" s="27" t="n">
-        <v>-5.43</v>
+        <v>40.24</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
       <c r="A44" s="26" t="inlineStr">
         <is>
-          <t>피스피스스튜디오</t>
+          <t>오르비텍</t>
         </is>
       </c>
       <c r="B44" s="25" t="n">
@@ -4513,25 +4543,25 @@
       </c>
       <c r="F44" s="25" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="G44" s="25" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="H44" s="27" t="n">
-        <v>-7.95</v>
-      </c>
-      <c r="I44" s="27" t="n">
-        <v>-17.94</v>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="H44" s="29" t="n">
+        <v>-8.24</v>
+      </c>
+      <c r="I44" s="29" t="n">
+        <v>-10.69</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
       <c r="A45" s="26" t="inlineStr">
         <is>
-          <t>하이스틸</t>
+          <t>우리기술</t>
         </is>
       </c>
       <c r="B45" s="25" t="n">
@@ -4548,25 +4578,25 @@
       </c>
       <c r="F45" s="25" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="G45" s="25" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="H45" s="27" t="n">
-        <v>-1.7</v>
-      </c>
-      <c r="I45" s="28" t="n">
-        <v>14.95</v>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="H45" s="29" t="n">
+        <v>-1.89</v>
+      </c>
+      <c r="I45" s="29" t="n">
+        <v>-17.47</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
       <c r="A46" s="26" t="inlineStr">
         <is>
-          <t>한솔테크닉스</t>
+          <t>위더스제약</t>
         </is>
       </c>
       <c r="B46" s="25" t="n">
@@ -4583,25 +4613,25 @@
       </c>
       <c r="F46" s="25" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="G46" s="25" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="H46" s="27" t="n">
-        <v>-10.37</v>
-      </c>
-      <c r="I46" s="28" t="n">
-        <v>19.15</v>
+        <v>13.59</v>
+      </c>
+      <c r="I46" s="27" t="n">
+        <v>33.03</v>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
       <c r="A47" s="26" t="inlineStr">
         <is>
-          <t>한전기술</t>
+          <t>율촌</t>
         </is>
       </c>
       <c r="B47" s="25" t="n">
@@ -4618,25 +4648,25 @@
       </c>
       <c r="F47" s="25" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="G47" s="25" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="H47" s="28" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="I47" s="28" t="n">
-        <v>17.44</v>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="H47" s="29" t="n">
+        <v>-13.55</v>
+      </c>
+      <c r="I47" s="27" t="n">
+        <v>30.73</v>
       </c>
     </row>
     <row r="48" ht="18" customHeight="1">
       <c r="A48" s="26" t="inlineStr">
         <is>
-          <t>한화솔루션</t>
+          <t>티웨이홀딩스</t>
         </is>
       </c>
       <c r="B48" s="25" t="n">
@@ -4653,25 +4683,25 @@
       </c>
       <c r="F48" s="25" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="G48" s="25" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="H48" s="27" t="n">
-        <v>-7.75</v>
-      </c>
-      <c r="I48" s="28" t="n">
-        <v>9.32</v>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="H48" s="29" t="n">
+        <v>-7.09</v>
+      </c>
+      <c r="I48" s="27" t="n">
+        <v>26.88</v>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1">
       <c r="A49" s="26" t="inlineStr">
         <is>
-          <t>현대모비스</t>
+          <t>한전기술</t>
         </is>
       </c>
       <c r="B49" s="25" t="n">
@@ -4688,25 +4718,25 @@
       </c>
       <c r="F49" s="25" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="G49" s="25" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="H49" s="27" t="n">
-        <v>-4.44</v>
-      </c>
-      <c r="I49" s="28" t="n">
-        <v>4.69</v>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="H49" s="29" t="n">
+        <v>-9.51</v>
+      </c>
+      <c r="I49" s="29" t="n">
+        <v>-18.24</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
       <c r="A50" s="26" t="inlineStr">
         <is>
-          <t>현대약품</t>
+          <t>한화</t>
         </is>
       </c>
       <c r="B50" s="25" t="n">
@@ -4723,25 +4753,25 @@
       </c>
       <c r="F50" s="25" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="G50" s="25" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="H50" s="28" t="n">
-        <v>4.81</v>
-      </c>
-      <c r="I50" s="28" t="n">
-        <v>48.34</v>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="H50" s="29" t="n">
+        <v>-4.71</v>
+      </c>
+      <c r="I50" s="29" t="n">
+        <v>-0.95</v>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
       <c r="A51" s="26" t="inlineStr">
         <is>
-          <t>현대제철</t>
+          <t>현대약품</t>
         </is>
       </c>
       <c r="B51" s="25" t="n">
@@ -4758,54 +4788,54 @@
       </c>
       <c r="F51" s="25" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="G51" s="25" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="H51" s="27" t="n">
-        <v>-4.44</v>
-      </c>
-      <c r="I51" s="28" t="n">
-        <v>3.73</v>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="H51" s="29" t="n">
+        <v>-4.12</v>
+      </c>
+      <c r="I51" s="27" t="n">
+        <v>42.23</v>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1">
       <c r="A52" s="26" t="inlineStr">
         <is>
-          <t>삼화전자</t>
+          <t>휴림로봇</t>
         </is>
       </c>
       <c r="B52" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C52" s="25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D52" s="25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E52" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F52" s="25" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="G52" s="25" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="H52" s="28" t="n">
-        <v>29.86</v>
-      </c>
-      <c r="I52" s="28" t="n">
-        <v>70</v>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="H52" s="29" t="n">
+        <v>-3.34</v>
+      </c>
+      <c r="I52" s="29" t="n">
+        <v>-13.73</v>
       </c>
     </row>
   </sheetData>
@@ -4882,26 +4912,26 @@
     <row r="3" ht="18" customHeight="1">
       <c r="A3" s="35" t="inlineStr">
         <is>
-          <t>이차전지</t>
+          <t>반도체</t>
         </is>
       </c>
       <c r="B3" s="36" t="n">
         <v>1</v>
       </c>
       <c r="C3" s="36" t="n">
-        <v>3</v>
+        <v>60</v>
       </c>
       <c r="D3" s="36" t="n">
-        <v>3</v>
+        <v>60</v>
       </c>
       <c r="E3" s="36" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="F3" s="37" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="G3" s="37" t="inlineStr">
@@ -4913,26 +4943,26 @@
     <row r="4" ht="18" customHeight="1">
       <c r="A4" s="35" t="inlineStr">
         <is>
-          <t>반도체</t>
+          <t>바이오</t>
         </is>
       </c>
       <c r="B4" s="36" t="n">
         <v>1</v>
       </c>
       <c r="C4" s="36" t="n">
-        <v>85</v>
+        <v>9</v>
       </c>
       <c r="D4" s="36" t="n">
-        <v>85</v>
+        <v>9</v>
       </c>
       <c r="E4" s="36" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="F4" s="37" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="G4" s="37" t="inlineStr">
@@ -4944,26 +4974,26 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="35" t="inlineStr">
         <is>
-          <t>바이오</t>
+          <t>전기차</t>
         </is>
       </c>
       <c r="B5" s="36" t="n">
         <v>1</v>
       </c>
       <c r="C5" s="36" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="D5" s="36" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="E5" s="36" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="F5" s="37" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="G5" s="37" t="inlineStr">
@@ -4975,7 +5005,7 @@
     <row r="6" ht="18" customHeight="1">
       <c r="A6" s="35" t="inlineStr">
         <is>
-          <t>전기차</t>
+          <t>로봇</t>
         </is>
       </c>
       <c r="B6" s="36" t="n">
@@ -4989,12 +5019,12 @@
       </c>
       <c r="E6" s="36" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="F6" s="37" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="G6" s="37" t="inlineStr">
@@ -5006,26 +5036,26 @@
     <row r="7" ht="18" customHeight="1">
       <c r="A7" s="35" t="inlineStr">
         <is>
-          <t>방산</t>
+          <t>조선</t>
         </is>
       </c>
       <c r="B7" s="36" t="n">
         <v>1</v>
       </c>
       <c r="C7" s="36" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D7" s="36" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E7" s="36" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="F7" s="37" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="G7" s="37" t="inlineStr">
@@ -5037,26 +5067,26 @@
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="35" t="inlineStr">
         <is>
-          <t>원전</t>
+          <t>제약</t>
         </is>
       </c>
       <c r="B8" s="36" t="n">
         <v>1</v>
       </c>
       <c r="C8" s="36" t="n">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="D8" s="36" t="n">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="E8" s="36" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="F8" s="37" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="G8" s="37" t="inlineStr">
@@ -5068,26 +5098,26 @@
     <row r="9" ht="18" customHeight="1">
       <c r="A9" s="35" t="inlineStr">
         <is>
-          <t>로봇</t>
+          <t>인공지능</t>
         </is>
       </c>
       <c r="B9" s="36" t="n">
         <v>1</v>
       </c>
       <c r="C9" s="36" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D9" s="36" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E9" s="36" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="F9" s="37" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="G9" s="37" t="inlineStr">
@@ -5097,164 +5127,144 @@
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="35" t="inlineStr">
-        <is>
-          <t>엔터</t>
-        </is>
-      </c>
-      <c r="B10" s="36" t="n">
-        <v>1</v>
-      </c>
-      <c r="C10" s="36" t="n">
-        <v>3</v>
-      </c>
-      <c r="D10" s="36" t="n">
-        <v>3</v>
-      </c>
-      <c r="E10" s="36" t="inlineStr">
-        <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="F10" s="37" t="inlineStr">
-        <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="G10" s="37" t="inlineStr">
-        <is>
-          <t>⚡ 관심</t>
-        </is>
-      </c>
+      <c r="A10" s="26" t="inlineStr">
+        <is>
+          <t>이차전지</t>
+        </is>
+      </c>
+      <c r="B10" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F10" s="28" t="inlineStr">
+        <is>
+          <t>감지 없음</t>
+        </is>
+      </c>
+      <c r="G10" s="28" t="inlineStr"/>
     </row>
     <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="35" t="inlineStr">
-        <is>
-          <t>조선</t>
-        </is>
-      </c>
-      <c r="B11" s="36" t="n">
-        <v>1</v>
-      </c>
-      <c r="C11" s="36" t="n">
-        <v>5</v>
-      </c>
-      <c r="D11" s="36" t="n">
-        <v>5</v>
-      </c>
-      <c r="E11" s="36" t="inlineStr">
-        <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="F11" s="37" t="inlineStr">
-        <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="G11" s="37" t="inlineStr">
-        <is>
-          <t>⚡ 관심</t>
-        </is>
-      </c>
+      <c r="A11" s="26" t="inlineStr">
+        <is>
+          <t>AI반도체</t>
+        </is>
+      </c>
+      <c r="B11" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F11" s="28" t="inlineStr">
+        <is>
+          <t>감지 없음</t>
+        </is>
+      </c>
+      <c r="G11" s="28" t="inlineStr"/>
     </row>
     <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="35" t="inlineStr">
-        <is>
-          <t>철강</t>
-        </is>
-      </c>
-      <c r="B12" s="36" t="n">
-        <v>1</v>
-      </c>
-      <c r="C12" s="36" t="n">
-        <v>6</v>
-      </c>
-      <c r="D12" s="36" t="n">
-        <v>6</v>
-      </c>
-      <c r="E12" s="36" t="inlineStr">
-        <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="F12" s="37" t="inlineStr">
-        <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="G12" s="37" t="inlineStr">
-        <is>
-          <t>⚡ 관심</t>
-        </is>
-      </c>
+      <c r="A12" s="26" t="inlineStr">
+        <is>
+          <t>방산</t>
+        </is>
+      </c>
+      <c r="B12" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F12" s="28" t="inlineStr">
+        <is>
+          <t>감지 없음</t>
+        </is>
+      </c>
+      <c r="G12" s="28" t="inlineStr"/>
     </row>
     <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="35" t="inlineStr">
-        <is>
-          <t>제약</t>
-        </is>
-      </c>
-      <c r="B13" s="36" t="n">
-        <v>1</v>
-      </c>
-      <c r="C13" s="36" t="n">
-        <v>12</v>
-      </c>
-      <c r="D13" s="36" t="n">
-        <v>12</v>
-      </c>
-      <c r="E13" s="36" t="inlineStr">
-        <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="F13" s="37" t="inlineStr">
-        <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="G13" s="37" t="inlineStr">
-        <is>
-          <t>⚡ 관심</t>
-        </is>
-      </c>
+      <c r="A13" s="26" t="inlineStr">
+        <is>
+          <t>원전</t>
+        </is>
+      </c>
+      <c r="B13" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F13" s="28" t="inlineStr">
+        <is>
+          <t>감지 없음</t>
+        </is>
+      </c>
+      <c r="G13" s="28" t="inlineStr"/>
     </row>
     <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="35" t="inlineStr">
-        <is>
-          <t>인공지능</t>
-        </is>
-      </c>
-      <c r="B14" s="36" t="n">
-        <v>1</v>
-      </c>
-      <c r="C14" s="36" t="n">
-        <v>12</v>
-      </c>
-      <c r="D14" s="36" t="n">
-        <v>12</v>
-      </c>
-      <c r="E14" s="36" t="inlineStr">
-        <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="F14" s="37" t="inlineStr">
-        <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="G14" s="37" t="inlineStr">
-        <is>
-          <t>⚡ 관심</t>
-        </is>
-      </c>
+      <c r="A14" s="26" t="inlineStr">
+        <is>
+          <t>수소</t>
+        </is>
+      </c>
+      <c r="B14" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F14" s="28" t="inlineStr">
+        <is>
+          <t>감지 없음</t>
+        </is>
+      </c>
+      <c r="G14" s="28" t="inlineStr"/>
     </row>
     <row r="15" ht="18" customHeight="1">
       <c r="A15" s="26" t="inlineStr">
         <is>
-          <t>AI반도체</t>
+          <t>태양광</t>
         </is>
       </c>
       <c r="B15" s="25" t="n">
@@ -5271,17 +5281,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F15" s="29" t="inlineStr">
+      <c r="F15" s="28" t="inlineStr">
         <is>
           <t>감지 없음</t>
         </is>
       </c>
-      <c r="G15" s="29" t="inlineStr"/>
+      <c r="G15" s="28" t="inlineStr"/>
     </row>
     <row r="16" ht="18" customHeight="1">
       <c r="A16" s="26" t="inlineStr">
         <is>
-          <t>수소</t>
+          <t>게임</t>
         </is>
       </c>
       <c r="B16" s="25" t="n">
@@ -5298,17 +5308,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F16" s="29" t="inlineStr">
+      <c r="F16" s="28" t="inlineStr">
         <is>
           <t>감지 없음</t>
         </is>
       </c>
-      <c r="G16" s="29" t="inlineStr"/>
+      <c r="G16" s="28" t="inlineStr"/>
     </row>
     <row r="17" ht="18" customHeight="1">
       <c r="A17" s="26" t="inlineStr">
         <is>
-          <t>태양광</t>
+          <t>엔터</t>
         </is>
       </c>
       <c r="B17" s="25" t="n">
@@ -5325,17 +5335,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F17" s="29" t="inlineStr">
+      <c r="F17" s="28" t="inlineStr">
         <is>
           <t>감지 없음</t>
         </is>
       </c>
-      <c r="G17" s="29" t="inlineStr"/>
+      <c r="G17" s="28" t="inlineStr"/>
     </row>
     <row r="18" ht="18" customHeight="1">
       <c r="A18" s="26" t="inlineStr">
         <is>
-          <t>게임</t>
+          <t>핀테크</t>
         </is>
       </c>
       <c r="B18" s="25" t="n">
@@ -5352,17 +5362,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F18" s="29" t="inlineStr">
+      <c r="F18" s="28" t="inlineStr">
         <is>
           <t>감지 없음</t>
         </is>
       </c>
-      <c r="G18" s="29" t="inlineStr"/>
+      <c r="G18" s="28" t="inlineStr"/>
     </row>
     <row r="19" ht="18" customHeight="1">
       <c r="A19" s="26" t="inlineStr">
         <is>
-          <t>핀테크</t>
+          <t>클라우드</t>
         </is>
       </c>
       <c r="B19" s="25" t="n">
@@ -5379,17 +5389,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F19" s="29" t="inlineStr">
+      <c r="F19" s="28" t="inlineStr">
         <is>
           <t>감지 없음</t>
         </is>
       </c>
-      <c r="G19" s="29" t="inlineStr"/>
+      <c r="G19" s="28" t="inlineStr"/>
     </row>
     <row r="20" ht="18" customHeight="1">
       <c r="A20" s="26" t="inlineStr">
         <is>
-          <t>클라우드</t>
+          <t>철강</t>
         </is>
       </c>
       <c r="B20" s="25" t="n">
@@ -5406,12 +5416,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F20" s="29" t="inlineStr">
+      <c r="F20" s="28" t="inlineStr">
         <is>
           <t>감지 없음</t>
         </is>
       </c>
-      <c r="G20" s="29" t="inlineStr"/>
+      <c r="G20" s="28" t="inlineStr"/>
     </row>
     <row r="21" ht="18" customHeight="1">
       <c r="A21" s="26" t="inlineStr">
@@ -5433,12 +5443,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F21" s="29" t="inlineStr">
+      <c r="F21" s="28" t="inlineStr">
         <is>
           <t>감지 없음</t>
         </is>
       </c>
-      <c r="G21" s="29" t="inlineStr"/>
+      <c r="G21" s="28" t="inlineStr"/>
     </row>
     <row r="22" ht="18" customHeight="1">
       <c r="A22" s="26" t="inlineStr">
@@ -5460,12 +5470,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F22" s="29" t="inlineStr">
+      <c r="F22" s="28" t="inlineStr">
         <is>
           <t>감지 없음</t>
         </is>
       </c>
-      <c r="G22" s="29" t="inlineStr"/>
+      <c r="G22" s="28" t="inlineStr"/>
     </row>
     <row r="23" ht="18" customHeight="1">
       <c r="A23" s="26" t="inlineStr">
@@ -5487,12 +5497,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F23" s="29" t="inlineStr">
+      <c r="F23" s="28" t="inlineStr">
         <is>
           <t>감지 없음</t>
         </is>
       </c>
-      <c r="G23" s="29" t="inlineStr"/>
+      <c r="G23" s="28" t="inlineStr"/>
     </row>
     <row r="24" ht="18" customHeight="1">
       <c r="A24" s="26" t="inlineStr">
@@ -5514,12 +5524,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F24" s="29" t="inlineStr">
+      <c r="F24" s="28" t="inlineStr">
         <is>
           <t>감지 없음</t>
         </is>
       </c>
-      <c r="G24" s="29" t="inlineStr"/>
+      <c r="G24" s="28" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/trend/stock_trend_history.xlsx
+++ b/trend/stock_trend_history.xlsx
@@ -258,13 +258,13 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -694,7 +694,7 @@
     <row r="1" ht="36" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>📊 주식 트렌드 조기 감지 대시보드   |   최종 업데이트: 2026-06-20 06:55</t>
+          <t>📊 주식 트렌드 조기 감지 대시보드   |   최종 업데이트: 2026-06-21 06:55</t>
         </is>
       </c>
     </row>
@@ -787,21 +787,21 @@
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="11" t="inlineStr">
         <is>
-          <t>⚡ 최신(2026-06-20) 상위: 반도체  점수 60.0점</t>
+          <t>⚡ 최신(2026-06-21) 상위: 반도체  점수 60.0점</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1">
       <c r="A11" s="12" t="inlineStr">
         <is>
-          <t>⚡ 최신(2026-06-20) 상위: SK  점수 47.0점</t>
+          <t>⚡ 최신(2026-06-21) 상위: SK  점수 56.0점</t>
         </is>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1">
       <c r="A12" s="11" t="inlineStr">
         <is>
-          <t>⚡ 최신(2026-06-20) 상위: SK하이닉스  점수 31.0점</t>
+          <t>⚡ 최신(2026-06-21) 상위: SK하이닉스  점수 41.0점</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="B14" s="15" t="n">
@@ -947,7 +947,7 @@
       </c>
       <c r="J14" s="17" t="inlineStr">
         <is>
-          <t>매일경제 기사 언급 / 매일경제 기사 언급 / 네이버뉴스 기사 언급 / 매일경제 기사 언급 / 매일경제 기사 언급</t>
+          <t>네이버뉴스 헤드라인 언급 / 매일경제 기사 언급 / 네이버뉴스 헤드라인 언급 / 네이버뉴스 기사 언급 / 매일경제 기사 언급</t>
         </is>
       </c>
       <c r="K14" s="17" t="inlineStr">
@@ -959,7 +959,7 @@
     <row r="15" ht="18" customHeight="1">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="B15" s="15" t="n">
@@ -971,10 +971,10 @@
         </is>
       </c>
       <c r="D15" s="15" t="n">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="E15" s="15" t="n">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="F15" s="15" t="n">
         <v>0</v>
@@ -990,7 +990,7 @@
       </c>
       <c r="J15" s="17" t="inlineStr">
         <is>
-          <t>매일경제 헤드라인 언급 / 매일경제 기사 언급 / 한국경제 헤드라인 언급 / 한국경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
+          <t>매일경제 헤드라인 언급 / 매일경제 기사 언급 / 네이버뉴스 헤드라인 언급 / 한국경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
         </is>
       </c>
       <c r="K15" s="17" t="inlineStr">
@@ -1002,7 +1002,7 @@
     <row r="16" ht="18" customHeight="1">
       <c r="A16" s="15" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="B16" s="15" t="n">
@@ -1014,10 +1014,10 @@
         </is>
       </c>
       <c r="D16" s="15" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="E16" s="15" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="F16" s="15" t="n">
         <v>0</v>
@@ -1033,17 +1033,19 @@
       </c>
       <c r="J16" s="17" t="inlineStr">
         <is>
-          <t>매일경제 헤드라인 언급 / 매일경제 기사 언급 / 한국경제 헤드라인 언급 / 매일경제 기사 언급 / 매일경제 기사 언급</t>
-        </is>
-      </c>
-      <c r="K16" s="17" t="n">
-        <v/>
+          <t>매일경제 헤드라인 언급 / 매일경제 기사 언급 / 네이버뉴스 기사 언급 / 한국경제 헤드라인 언급 / 매일경제 기사 언급</t>
+        </is>
+      </c>
+      <c r="K16" s="17" t="inlineStr">
+        <is>
+          <t>네이버</t>
+        </is>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="B17" s="15" t="n">
@@ -1051,14 +1053,14 @@
       </c>
       <c r="C17" s="16" t="inlineStr">
         <is>
-          <t>삼성전기</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="D17" s="15" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E17" s="15" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F17" s="15" t="n">
         <v>0</v>
@@ -1066,27 +1068,27 @@
       <c r="G17" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="H17" s="18" t="n">
-        <v>3.18</v>
+      <c r="H17" s="19" t="n">
+        <v>-2.34</v>
       </c>
       <c r="I17" s="18" t="n">
-        <v>32.44</v>
+        <v>9.77</v>
       </c>
       <c r="J17" s="17" t="inlineStr">
         <is>
-          <t>Google 급상승 검색어 등장 (KR) / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급</t>
+          <t>매일경제 기사 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 헤드라인 언급 / 한국경제 헤드라인 언급</t>
         </is>
       </c>
       <c r="K17" s="17" t="inlineStr">
         <is>
-          <t>Google</t>
+          <t>네이버</t>
         </is>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
       <c r="A18" s="15" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="B18" s="15" t="n">
@@ -1094,7 +1096,7 @@
       </c>
       <c r="C18" s="16" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>현대차</t>
         </is>
       </c>
       <c r="D18" s="15" t="n">
@@ -1109,25 +1111,27 @@
       <c r="G18" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="H18" s="19" t="n">
-        <v>-2.34</v>
+      <c r="H18" s="18" t="n">
+        <v>2</v>
       </c>
       <c r="I18" s="18" t="n">
-        <v>9.77</v>
+        <v>0.99</v>
       </c>
       <c r="J18" s="17" t="inlineStr">
         <is>
-          <t>매일경제 기사 언급 / 한국경제 헤드라인 언급 / 매일경제 기사 언급 / 매일경제 기사 언급 / 매일경제 기사 언급</t>
-        </is>
-      </c>
-      <c r="K18" s="17" t="n">
-        <v/>
+          <t>네이버뉴스 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 기사 언급 / 한국경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K18" s="17" t="inlineStr">
+        <is>
+          <t>네이버</t>
+        </is>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
       <c r="A19" s="15" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="B19" s="15" t="n">
@@ -1135,14 +1139,14 @@
       </c>
       <c r="C19" s="16" t="inlineStr">
         <is>
-          <t>현대차</t>
+          <t>대한항공</t>
         </is>
       </c>
       <c r="D19" s="15" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E19" s="15" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F19" s="15" t="n">
         <v>0</v>
@@ -1150,15 +1154,15 @@
       <c r="G19" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="H19" s="18" t="n">
-        <v>2</v>
+      <c r="H19" s="19" t="n">
+        <v>-3.12</v>
       </c>
       <c r="I19" s="18" t="n">
-        <v>0.99</v>
+        <v>5.08</v>
       </c>
       <c r="J19" s="17" t="inlineStr">
         <is>
-          <t>매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 기사 언급 / 한국경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
+          <t>매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 한국경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급</t>
         </is>
       </c>
       <c r="K19" s="17" t="n">
@@ -1168,7 +1172,7 @@
     <row r="20" ht="18" customHeight="1">
       <c r="A20" s="15" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="B20" s="15" t="n">
@@ -1176,14 +1180,14 @@
       </c>
       <c r="C20" s="16" t="inlineStr">
         <is>
-          <t>대한항공</t>
+          <t>삼성전기</t>
         </is>
       </c>
       <c r="D20" s="15" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E20" s="15" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F20" s="15" t="n">
         <v>0</v>
@@ -1191,15 +1195,15 @@
       <c r="G20" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="H20" s="19" t="n">
-        <v>-3.12</v>
+      <c r="H20" s="18" t="n">
+        <v>3.18</v>
       </c>
       <c r="I20" s="18" t="n">
-        <v>5.08</v>
+        <v>32.44</v>
       </c>
       <c r="J20" s="17" t="inlineStr">
         <is>
-          <t>매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 한국경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급</t>
+          <t>매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급</t>
         </is>
       </c>
       <c r="K20" s="17" t="n">
@@ -1209,7 +1213,7 @@
     <row r="21" ht="18" customHeight="1">
       <c r="A21" s="15" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="B21" s="15" t="n">
@@ -1221,10 +1225,10 @@
         </is>
       </c>
       <c r="D21" s="15" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E21" s="15" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F21" s="15" t="n">
         <v>0</v>
@@ -1252,7 +1256,7 @@
     <row r="22" ht="18" customHeight="1">
       <c r="A22" s="15" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="B22" s="15" t="n">
@@ -1260,14 +1264,14 @@
       </c>
       <c r="C22" s="16" t="inlineStr">
         <is>
-          <t>로봇</t>
+          <t>바이오</t>
         </is>
       </c>
       <c r="D22" s="15" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E22" s="15" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F22" s="15" t="n">
         <v>0</v>
@@ -1283,7 +1287,7 @@
       </c>
       <c r="J22" s="17" t="inlineStr">
         <is>
-          <t>네이버뉴스 헤드라인 언급 / 매일경제 기사 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급</t>
+          <t>네이버뉴스 헤드라인 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 헤드라인 언급 / 네이버뉴스 헤드라인 언급 / 네이버뉴스 기사 언급</t>
         </is>
       </c>
       <c r="K22" s="17" t="inlineStr">
@@ -1295,7 +1299,7 @@
     <row r="23" ht="18" customHeight="1">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="B23" s="15" t="n">
@@ -1303,14 +1307,14 @@
       </c>
       <c r="C23" s="16" t="inlineStr">
         <is>
-          <t>제약</t>
+          <t>LG</t>
         </is>
       </c>
       <c r="D23" s="15" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E23" s="15" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F23" s="15" t="n">
         <v>0</v>
@@ -1318,15 +1322,15 @@
       <c r="G23" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="H23" s="15" t="n">
-        <v/>
-      </c>
-      <c r="I23" s="15" t="n">
-        <v/>
+      <c r="H23" s="19" t="n">
+        <v>-0.91</v>
+      </c>
+      <c r="I23" s="18" t="n">
+        <v>2.25</v>
       </c>
       <c r="J23" s="17" t="inlineStr">
         <is>
-          <t>네이버뉴스 기사 언급 / 네이버뉴스 헤드라인 언급 / 네이버뉴스 헤드라인 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 기사 언급</t>
+          <t>네이버뉴스 헤드라인 언급 / 네이버뉴스 기사 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
         </is>
       </c>
       <c r="K23" s="17" t="inlineStr">
@@ -1338,7 +1342,7 @@
     <row r="24" ht="18" customHeight="1">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="B24" s="15" t="n">
@@ -1346,7 +1350,7 @@
       </c>
       <c r="C24" s="16" t="inlineStr">
         <is>
-          <t>바이오</t>
+          <t>넥써쓰</t>
         </is>
       </c>
       <c r="D24" s="15" t="n">
@@ -1361,27 +1365,27 @@
       <c r="G24" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="H24" s="15" t="n">
-        <v/>
-      </c>
-      <c r="I24" s="15" t="n">
-        <v/>
+      <c r="H24" s="19" t="n">
+        <v>-27.47</v>
+      </c>
+      <c r="I24" s="19" t="n">
+        <v>-4.83</v>
       </c>
       <c r="J24" s="17" t="inlineStr">
         <is>
-          <t>네이버뉴스 기사 언급 / 네이버뉴스 헤드라인 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 헤드라인 언급 / 네이버뉴스 기사 언급</t>
+          <t>네이버 검색 당일 +102% / 중요공시 3건 / 매일경제 헤드라인 언급</t>
         </is>
       </c>
       <c r="K24" s="17" t="inlineStr">
         <is>
-          <t>네이버</t>
+          <t>네이버, 공시</t>
         </is>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
       <c r="A25" s="15" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="B25" s="15" t="n">
@@ -1389,14 +1393,14 @@
       </c>
       <c r="C25" s="16" t="inlineStr">
         <is>
-          <t>넥써쓰</t>
+          <t>로봇</t>
         </is>
       </c>
       <c r="D25" s="15" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E25" s="15" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F25" s="15" t="n">
         <v>0</v>
@@ -1404,27 +1408,27 @@
       <c r="G25" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="H25" s="19" t="n">
-        <v>-27.47</v>
-      </c>
-      <c r="I25" s="19" t="n">
-        <v>-4.83</v>
+      <c r="H25" s="15" t="n">
+        <v/>
+      </c>
+      <c r="I25" s="15" t="n">
+        <v/>
       </c>
       <c r="J25" s="17" t="inlineStr">
         <is>
-          <t>중요공시 3건 / 매일경제 헤드라인 언급</t>
+          <t>매일경제 기사 언급 / 매일경제 헤드라인 언급 / 네이버뉴스 헤드라인 언급 / 매일경제 헤드라인 언급</t>
         </is>
       </c>
       <c r="K25" s="17" t="inlineStr">
         <is>
-          <t>공시</t>
+          <t>네이버</t>
         </is>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
       <c r="A26" s="15" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="B26" s="15" t="n">
@@ -1432,7 +1436,7 @@
       </c>
       <c r="C26" s="16" t="inlineStr">
         <is>
-          <t>현대로템</t>
+          <t>셀트리온</t>
         </is>
       </c>
       <c r="D26" s="15" t="n">
@@ -1448,26 +1452,26 @@
         <v>0</v>
       </c>
       <c r="H26" s="19" t="n">
-        <v>-2.13</v>
+        <v>-1.9</v>
       </c>
       <c r="I26" s="19" t="n">
-        <v>-0.72</v>
+        <v>-1.56</v>
       </c>
       <c r="J26" s="17" t="inlineStr">
         <is>
-          <t>중요공시 1건 / 매일경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
+          <t>중요공시 2건 / Google 급상승 검색어 등장 (KR) / 네이버뉴스 기사 언급</t>
         </is>
       </c>
       <c r="K26" s="17" t="inlineStr">
         <is>
-          <t>공시</t>
+          <t>네이버, 공시, Google</t>
         </is>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
       <c r="A27" s="15" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="B27" s="15" t="n">
@@ -1475,7 +1479,7 @@
       </c>
       <c r="C27" s="16" t="inlineStr">
         <is>
-          <t>LG</t>
+          <t>현대로템</t>
         </is>
       </c>
       <c r="D27" s="15" t="n">
@@ -1491,24 +1495,26 @@
         <v>0</v>
       </c>
       <c r="H27" s="19" t="n">
-        <v>-0.91</v>
-      </c>
-      <c r="I27" s="18" t="n">
-        <v>2.25</v>
+        <v>-2.13</v>
+      </c>
+      <c r="I27" s="19" t="n">
+        <v>-0.72</v>
       </c>
       <c r="J27" s="17" t="inlineStr">
         <is>
-          <t>매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K27" s="17" t="n">
-        <v/>
+          <t>중요공시 1건 / 매일경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K27" s="17" t="inlineStr">
+        <is>
+          <t>공시</t>
+        </is>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
       <c r="A28" s="20" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="B28" s="20" t="n">
@@ -1516,7 +1522,7 @@
       </c>
       <c r="C28" s="21" t="inlineStr">
         <is>
-          <t>미래에셋증권</t>
+          <t>보해양조</t>
         </is>
       </c>
       <c r="D28" s="20" t="n">
@@ -1532,26 +1538,26 @@
         <v>0</v>
       </c>
       <c r="H28" s="22" t="n">
-        <v>-3.85</v>
+        <v>29.88</v>
       </c>
       <c r="I28" s="22" t="n">
-        <v>-6.79</v>
+        <v>58.36</v>
       </c>
       <c r="J28" s="23" t="inlineStr">
         <is>
-          <t>중요공시 2건 / 매일경제 헤드라인 언급 / 네이버뉴스 기사 언급 / 매일경제 기사 언급</t>
+          <t>네이버 검색 당일 +186% / 매일경제 헤드라인 언급</t>
         </is>
       </c>
       <c r="K28" s="23" t="inlineStr">
         <is>
-          <t>공시, 네이버</t>
+          <t>네이버</t>
         </is>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
       <c r="A29" s="20" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="B29" s="20" t="n">
@@ -1559,7 +1565,7 @@
       </c>
       <c r="C29" s="21" t="inlineStr">
         <is>
-          <t>SK스퀘어</t>
+          <t>한화</t>
         </is>
       </c>
       <c r="D29" s="20" t="n">
@@ -1575,24 +1581,26 @@
         <v>0</v>
       </c>
       <c r="H29" s="24" t="n">
-        <v>4.71</v>
+        <v>-4.71</v>
       </c>
       <c r="I29" s="24" t="n">
-        <v>31.08</v>
+        <v>-0.95</v>
       </c>
       <c r="J29" s="23" t="inlineStr">
         <is>
-          <t>한국경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K29" s="23" t="n">
-        <v/>
+          <t>네이버뉴스 헤드라인 언급 / 매일경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K29" s="23" t="inlineStr">
+        <is>
+          <t>네이버</t>
+        </is>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
       <c r="A30" s="20" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="B30" s="20" t="n">
@@ -1600,14 +1608,14 @@
       </c>
       <c r="C30" s="21" t="inlineStr">
         <is>
-          <t>삼성물산</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="D30" s="20" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E30" s="20" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F30" s="20" t="n">
         <v>0</v>
@@ -1616,24 +1624,26 @@
         <v>0</v>
       </c>
       <c r="H30" s="24" t="n">
-        <v>1.24</v>
+        <v>-26.16</v>
       </c>
       <c r="I30" s="24" t="n">
-        <v>13.77</v>
+        <v>-19.9</v>
       </c>
       <c r="J30" s="23" t="inlineStr">
         <is>
-          <t>한국경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K30" s="23" t="n">
-        <v/>
+          <t>네이버 검색 당일 +100% / 매일경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K30" s="23" t="inlineStr">
+        <is>
+          <t>네이버</t>
+        </is>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
       <c r="A31" s="20" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="B31" s="20" t="n">
@@ -1641,14 +1651,14 @@
       </c>
       <c r="C31" s="21" t="inlineStr">
         <is>
-          <t>조선</t>
+          <t>한화오션</t>
         </is>
       </c>
       <c r="D31" s="20" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E31" s="20" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F31" s="20" t="n">
         <v>0</v>
@@ -1656,27 +1666,27 @@
       <c r="G31" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H31" s="20" t="n">
-        <v/>
-      </c>
-      <c r="I31" s="20" t="n">
-        <v/>
+      <c r="H31" s="22" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="I31" s="22" t="n">
+        <v>13.93</v>
       </c>
       <c r="J31" s="23" t="inlineStr">
         <is>
-          <t>한국경제 헤드라인 언급 / 네이버뉴스 헤드라인 언급</t>
+          <t>중요공시 1건 / 네이버뉴스 헤드라인 언급</t>
         </is>
       </c>
       <c r="K31" s="23" t="inlineStr">
         <is>
-          <t>네이버</t>
+          <t>네이버, 공시</t>
         </is>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
       <c r="A32" s="20" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="B32" s="20" t="n">
@@ -1684,7 +1694,7 @@
       </c>
       <c r="C32" s="21" t="inlineStr">
         <is>
-          <t>씨피시스템</t>
+          <t>미래에셋증권</t>
         </is>
       </c>
       <c r="D32" s="20" t="n">
@@ -1700,26 +1710,26 @@
         <v>0</v>
       </c>
       <c r="H32" s="24" t="n">
-        <v>29.88</v>
+        <v>-3.85</v>
       </c>
       <c r="I32" s="24" t="n">
-        <v>20.79</v>
+        <v>-6.79</v>
       </c>
       <c r="J32" s="23" t="inlineStr">
         <is>
-          <t>네이버뉴스 헤드라인 언급 / 한국경제 헤드라인 언급</t>
+          <t>중요공시 2건 / 매일경제 헤드라인 언급 / 매일경제 기사 언급</t>
         </is>
       </c>
       <c r="K32" s="23" t="inlineStr">
         <is>
-          <t>네이버</t>
+          <t>공시</t>
         </is>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
       <c r="A33" s="20" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="B33" s="20" t="n">
@@ -1742,10 +1752,10 @@
       <c r="G33" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H33" s="22" t="n">
+      <c r="H33" s="24" t="n">
         <v>-17.67</v>
       </c>
-      <c r="I33" s="22" t="n">
+      <c r="I33" s="24" t="n">
         <v>-24.4</v>
       </c>
       <c r="J33" s="23" t="inlineStr">
@@ -1762,7 +1772,7 @@
     <row r="34" ht="18" customHeight="1">
       <c r="A34" s="20" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="B34" s="20" t="n">
@@ -1770,7 +1780,7 @@
       </c>
       <c r="C34" s="21" t="inlineStr">
         <is>
-          <t>KT</t>
+          <t>제약</t>
         </is>
       </c>
       <c r="D34" s="20" t="n">
@@ -1785,25 +1795,27 @@
       <c r="G34" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H34" s="22" t="n">
-        <v>-0.37</v>
-      </c>
-      <c r="I34" s="22" t="n">
-        <v>-2.74</v>
+      <c r="H34" s="20" t="n">
+        <v/>
+      </c>
+      <c r="I34" s="20" t="n">
+        <v/>
       </c>
       <c r="J34" s="23" t="inlineStr">
         <is>
-          <t>매일경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K34" s="23" t="n">
-        <v/>
+          <t>네이버뉴스 기사 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 기사 언급</t>
+        </is>
+      </c>
+      <c r="K34" s="23" t="inlineStr">
+        <is>
+          <t>네이버</t>
+        </is>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
       <c r="A35" s="20" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="B35" s="20" t="n">
@@ -1811,14 +1823,14 @@
       </c>
       <c r="C35" s="21" t="inlineStr">
         <is>
-          <t>남화토건</t>
+          <t>KT</t>
         </is>
       </c>
       <c r="D35" s="20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E35" s="20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F35" s="20" t="n">
         <v>0</v>
@@ -1827,26 +1839,24 @@
         <v>0</v>
       </c>
       <c r="H35" s="24" t="n">
-        <v>12.73</v>
+        <v>-0.37</v>
       </c>
       <c r="I35" s="24" t="n">
-        <v>45.92</v>
+        <v>-2.74</v>
       </c>
       <c r="J35" s="23" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +314% / 중요공시 1건</t>
-        </is>
-      </c>
-      <c r="K35" s="23" t="inlineStr">
-        <is>
-          <t>공시, 네이버</t>
-        </is>
+          <t>매일경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K35" s="23" t="n">
+        <v/>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
       <c r="A36" s="20" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="B36" s="20" t="n">
@@ -1854,42 +1864,42 @@
       </c>
       <c r="C36" s="21" t="inlineStr">
         <is>
-          <t>한솔테크닉스</t>
+          <t>남화토건</t>
         </is>
       </c>
       <c r="D36" s="20" t="n">
         <v>4</v>
       </c>
       <c r="E36" s="20" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F36" s="20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G36" s="20" t="n">
         <v>0</v>
       </c>
       <c r="H36" s="22" t="n">
-        <v>-4.87</v>
-      </c>
-      <c r="I36" s="24" t="n">
-        <v>7.83</v>
+        <v>12.73</v>
+      </c>
+      <c r="I36" s="22" t="n">
+        <v>45.92</v>
       </c>
       <c r="J36" s="23" t="inlineStr">
         <is>
-          <t>중요공시 2건 / 중요공시 3일 +100%</t>
+          <t>네이버 검색 당일 +819% / 중요공시 1건</t>
         </is>
       </c>
       <c r="K36" s="23" t="inlineStr">
         <is>
-          <t>공시</t>
+          <t>네이버, 공시</t>
         </is>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
       <c r="A37" s="20" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="B37" s="20" t="n">
@@ -1897,7 +1907,7 @@
       </c>
       <c r="C37" s="21" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>씨피시스템</t>
         </is>
       </c>
       <c r="D37" s="20" t="n">
@@ -1913,24 +1923,26 @@
         <v>0</v>
       </c>
       <c r="H37" s="22" t="n">
-        <v>-26.16</v>
+        <v>29.88</v>
       </c>
       <c r="I37" s="22" t="n">
-        <v>-19.9</v>
+        <v>20.79</v>
       </c>
       <c r="J37" s="23" t="inlineStr">
         <is>
-          <t>매일경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K37" s="23" t="n">
-        <v/>
+          <t>네이버 검색 당일 +73% / 한국경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K37" s="23" t="inlineStr">
+        <is>
+          <t>네이버</t>
+        </is>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
       <c r="A38" s="20" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="B38" s="20" t="n">
@@ -1938,7 +1950,7 @@
       </c>
       <c r="C38" s="21" t="inlineStr">
         <is>
-          <t>보해양조</t>
+          <t>LG전자</t>
         </is>
       </c>
       <c r="D38" s="20" t="n">
@@ -1954,14 +1966,14 @@
         <v>0</v>
       </c>
       <c r="H38" s="24" t="n">
-        <v>29.88</v>
+        <v>-7.44</v>
       </c>
       <c r="I38" s="24" t="n">
-        <v>58.36</v>
+        <v>-6.21</v>
       </c>
       <c r="J38" s="23" t="inlineStr">
         <is>
-          <t>매일경제 헤드라인 언급</t>
+          <t>매일경제 헤드라인 언급 / 매일경제 기사 언급</t>
         </is>
       </c>
       <c r="K38" s="23" t="n">
@@ -1971,7 +1983,7 @@
     <row r="39" ht="18" customHeight="1">
       <c r="A39" s="20" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="B39" s="20" t="n">
@@ -1979,40 +1991,42 @@
       </c>
       <c r="C39" s="21" t="inlineStr">
         <is>
-          <t>LG전자</t>
+          <t>HJ중공업</t>
         </is>
       </c>
       <c r="D39" s="20" t="n">
         <v>4</v>
       </c>
       <c r="E39" s="20" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F39" s="20" t="n">
         <v>0</v>
       </c>
       <c r="G39" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H39" s="22" t="n">
-        <v>-7.44</v>
+        <v>3</v>
+      </c>
+      <c r="H39" s="24" t="n">
+        <v>-3.67</v>
       </c>
       <c r="I39" s="22" t="n">
-        <v>-6.21</v>
+        <v>3.24</v>
       </c>
       <c r="J39" s="23" t="inlineStr">
         <is>
-          <t>매일경제 헤드라인 언급 / 매일경제 기사 언급</t>
-        </is>
-      </c>
-      <c r="K39" s="23" t="n">
-        <v/>
+          <t>중요공시 2건 / 중요공시 7일 +100%</t>
+        </is>
+      </c>
+      <c r="K39" s="23" t="inlineStr">
+        <is>
+          <t>공시</t>
+        </is>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
       <c r="A40" s="20" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="B40" s="20" t="n">
@@ -2020,30 +2034,30 @@
       </c>
       <c r="C40" s="21" t="inlineStr">
         <is>
-          <t>HJ중공업</t>
+          <t>HD현대중공업</t>
         </is>
       </c>
       <c r="D40" s="20" t="n">
         <v>4</v>
       </c>
       <c r="E40" s="20" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F40" s="20" t="n">
         <v>0</v>
       </c>
       <c r="G40" s="20" t="n">
-        <v>3</v>
-      </c>
-      <c r="H40" s="22" t="n">
-        <v>-3.67</v>
-      </c>
-      <c r="I40" s="24" t="n">
-        <v>3.24</v>
+        <v>0</v>
+      </c>
+      <c r="H40" s="24" t="n">
+        <v>-2.49</v>
+      </c>
+      <c r="I40" s="22" t="n">
+        <v>2.62</v>
       </c>
       <c r="J40" s="23" t="inlineStr">
         <is>
-          <t>중요공시 2건 / 중요공시 7일 +100%</t>
+          <t>중요공시 1건 / 한국경제 헤드라인 언급</t>
         </is>
       </c>
       <c r="K40" s="23" t="inlineStr">
@@ -2055,7 +2069,7 @@
     <row r="41" ht="18" customHeight="1">
       <c r="A41" s="20" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="B41" s="20" t="n">
@@ -2063,7 +2077,7 @@
       </c>
       <c r="C41" s="21" t="inlineStr">
         <is>
-          <t>HD현대중공업</t>
+          <t>방산</t>
         </is>
       </c>
       <c r="D41" s="20" t="n">
@@ -2078,27 +2092,27 @@
       <c r="G41" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H41" s="22" t="n">
-        <v>-2.49</v>
-      </c>
-      <c r="I41" s="24" t="n">
-        <v>2.62</v>
+      <c r="H41" s="20" t="n">
+        <v/>
+      </c>
+      <c r="I41" s="20" t="n">
+        <v/>
       </c>
       <c r="J41" s="23" t="inlineStr">
         <is>
-          <t>중요공시 1건 / 한국경제 헤드라인 언급</t>
+          <t>네이버뉴스 기사 언급 / 한국경제 헤드라인 언급</t>
         </is>
       </c>
       <c r="K41" s="23" t="inlineStr">
         <is>
-          <t>공시</t>
+          <t>네이버</t>
         </is>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
       <c r="A42" s="20" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="B42" s="20" t="n">
@@ -2141,7 +2155,7 @@
     <row r="43" ht="18" customHeight="1">
       <c r="A43" s="20" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="B43" s="20" t="n">
@@ -2149,7 +2163,7 @@
       </c>
       <c r="C43" s="21" t="inlineStr">
         <is>
-          <t>HD현대</t>
+          <t>태양광</t>
         </is>
       </c>
       <c r="D43" s="20" t="n">
@@ -2164,15 +2178,15 @@
       <c r="G43" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H43" s="22" t="n">
-        <v>-3.35</v>
-      </c>
-      <c r="I43" s="22" t="n">
-        <v>-5.53</v>
+      <c r="H43" s="20" t="n">
+        <v/>
+      </c>
+      <c r="I43" s="20" t="n">
+        <v/>
       </c>
       <c r="J43" s="23" t="inlineStr">
         <is>
-          <t>매일경제 기사 언급 / 한국경제 헤드라인 언급</t>
+          <t>매일경제 헤드라인 언급 / 매일경제 기사 언급</t>
         </is>
       </c>
       <c r="K43" s="23" t="n">
@@ -2180,52 +2194,50 @@
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
-      <c r="A44" s="25" t="inlineStr">
-        <is>
-          <t>2026-06-20</t>
-        </is>
-      </c>
-      <c r="B44" s="25" t="n">
+      <c r="A44" s="20" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="B44" s="20" t="n">
         <v>31</v>
       </c>
-      <c r="C44" s="26" t="inlineStr">
-        <is>
-          <t>JW신약</t>
-        </is>
-      </c>
-      <c r="D44" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="E44" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="F44" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="G44" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="H44" s="27" t="n">
-        <v>13.08</v>
-      </c>
-      <c r="I44" s="27" t="n">
-        <v>70.94</v>
-      </c>
-      <c r="J44" s="28" t="inlineStr">
-        <is>
-          <t>네이버 검색 당일 +953%</t>
-        </is>
-      </c>
-      <c r="K44" s="28" t="inlineStr">
-        <is>
-          <t>네이버</t>
-        </is>
+      <c r="C44" s="21" t="inlineStr">
+        <is>
+          <t>HD현대</t>
+        </is>
+      </c>
+      <c r="D44" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="E44" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="F44" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G44" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" s="24" t="n">
+        <v>-3.35</v>
+      </c>
+      <c r="I44" s="24" t="n">
+        <v>-5.53</v>
+      </c>
+      <c r="J44" s="23" t="inlineStr">
+        <is>
+          <t>매일경제 기사 언급 / 한국경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K44" s="23" t="n">
+        <v/>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
       <c r="A45" s="25" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="B45" s="25" t="n">
@@ -2233,7 +2245,7 @@
       </c>
       <c r="C45" s="26" t="inlineStr">
         <is>
-          <t>강동씨앤엘</t>
+          <t>JW신약</t>
         </is>
       </c>
       <c r="D45" s="25" t="n">
@@ -2249,14 +2261,14 @@
         <v>0</v>
       </c>
       <c r="H45" s="27" t="n">
-        <v>29.91</v>
+        <v>13.08</v>
       </c>
       <c r="I45" s="27" t="n">
-        <v>121.56</v>
+        <v>70.94</v>
       </c>
       <c r="J45" s="28" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +830%</t>
+          <t>네이버 검색 당일 +1348%</t>
         </is>
       </c>
       <c r="K45" s="28" t="inlineStr">
@@ -2268,7 +2280,7 @@
     <row r="46" ht="18" customHeight="1">
       <c r="A46" s="25" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="B46" s="25" t="n">
@@ -2276,7 +2288,7 @@
       </c>
       <c r="C46" s="26" t="inlineStr">
         <is>
-          <t>삼익제약</t>
+          <t>강동씨앤엘</t>
         </is>
       </c>
       <c r="D46" s="25" t="n">
@@ -2292,14 +2304,14 @@
         <v>0</v>
       </c>
       <c r="H46" s="27" t="n">
-        <v>29.98</v>
+        <v>29.91</v>
       </c>
       <c r="I46" s="27" t="n">
-        <v>41.82</v>
+        <v>121.56</v>
       </c>
       <c r="J46" s="28" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +439%</t>
+          <t>네이버 검색 당일 +1305%</t>
         </is>
       </c>
       <c r="K46" s="28" t="inlineStr">
@@ -2311,7 +2323,7 @@
     <row r="47" ht="18" customHeight="1">
       <c r="A47" s="25" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="B47" s="25" t="n">
@@ -2319,7 +2331,7 @@
       </c>
       <c r="C47" s="26" t="inlineStr">
         <is>
-          <t>현대약품</t>
+          <t>삼익제약</t>
         </is>
       </c>
       <c r="D47" s="25" t="n">
@@ -2334,15 +2346,15 @@
       <c r="G47" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H47" s="29" t="n">
-        <v>-4.12</v>
+      <c r="H47" s="27" t="n">
+        <v>29.98</v>
       </c>
       <c r="I47" s="27" t="n">
-        <v>42.23</v>
+        <v>41.82</v>
       </c>
       <c r="J47" s="28" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +339%</t>
+          <t>네이버 검색 당일 +720%</t>
         </is>
       </c>
       <c r="K47" s="28" t="inlineStr">
@@ -2354,7 +2366,7 @@
     <row r="48" ht="18" customHeight="1">
       <c r="A48" s="25" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="B48" s="25" t="n">
@@ -2362,7 +2374,7 @@
       </c>
       <c r="C48" s="26" t="inlineStr">
         <is>
-          <t>위더스제약</t>
+          <t>현대약품</t>
         </is>
       </c>
       <c r="D48" s="25" t="n">
@@ -2377,15 +2389,15 @@
       <c r="G48" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H48" s="27" t="n">
-        <v>13.59</v>
+      <c r="H48" s="29" t="n">
+        <v>-4.12</v>
       </c>
       <c r="I48" s="27" t="n">
-        <v>33.03</v>
+        <v>42.23</v>
       </c>
       <c r="J48" s="28" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +269%</t>
+          <t>네이버 검색 당일 +416%</t>
         </is>
       </c>
       <c r="K48" s="28" t="inlineStr">
@@ -2397,7 +2409,7 @@
     <row r="49" ht="18" customHeight="1">
       <c r="A49" s="25" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="B49" s="25" t="n">
@@ -2405,7 +2417,7 @@
       </c>
       <c r="C49" s="26" t="inlineStr">
         <is>
-          <t>삼화전자</t>
+          <t>위더스제약</t>
         </is>
       </c>
       <c r="D49" s="25" t="n">
@@ -2421,14 +2433,14 @@
         <v>0</v>
       </c>
       <c r="H49" s="27" t="n">
-        <v>2.81</v>
+        <v>13.59</v>
       </c>
       <c r="I49" s="27" t="n">
-        <v>73.59</v>
+        <v>33.03</v>
       </c>
       <c r="J49" s="28" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +230%</t>
+          <t>네이버 검색 당일 +394%</t>
         </is>
       </c>
       <c r="K49" s="28" t="inlineStr">
@@ -2440,7 +2452,7 @@
     <row r="50" ht="18" customHeight="1">
       <c r="A50" s="25" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="B50" s="25" t="n">
@@ -2448,7 +2460,7 @@
       </c>
       <c r="C50" s="26" t="inlineStr">
         <is>
-          <t>율촌</t>
+          <t>삼화전자</t>
         </is>
       </c>
       <c r="D50" s="25" t="n">
@@ -2463,15 +2475,15 @@
       <c r="G50" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H50" s="29" t="n">
-        <v>-13.55</v>
+      <c r="H50" s="27" t="n">
+        <v>2.81</v>
       </c>
       <c r="I50" s="27" t="n">
-        <v>30.73</v>
+        <v>73.59</v>
       </c>
       <c r="J50" s="28" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +153%</t>
+          <t>네이버 검색 당일 +391%</t>
         </is>
       </c>
       <c r="K50" s="28" t="inlineStr">
@@ -2483,7 +2495,7 @@
     <row r="51" ht="18" customHeight="1">
       <c r="A51" s="25" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="B51" s="25" t="n">
@@ -2491,7 +2503,7 @@
       </c>
       <c r="C51" s="26" t="inlineStr">
         <is>
-          <t>티웨이홀딩스</t>
+          <t>율촌</t>
         </is>
       </c>
       <c r="D51" s="25" t="n">
@@ -2507,14 +2519,14 @@
         <v>0</v>
       </c>
       <c r="H51" s="29" t="n">
-        <v>-7.09</v>
+        <v>-13.55</v>
       </c>
       <c r="I51" s="27" t="n">
-        <v>26.88</v>
+        <v>30.73</v>
       </c>
       <c r="J51" s="28" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +141%</t>
+          <t>네이버 검색 당일 +196%</t>
         </is>
       </c>
       <c r="K51" s="28" t="inlineStr">
@@ -2526,7 +2538,7 @@
     <row r="52" ht="18" customHeight="1">
       <c r="A52" s="25" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="B52" s="25" t="n">
@@ -2557,7 +2569,7 @@
       </c>
       <c r="J52" s="28" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +111%</t>
+          <t>네이버 검색 당일 +175%</t>
         </is>
       </c>
       <c r="K52" s="28" t="inlineStr">
@@ -2569,7 +2581,7 @@
     <row r="53" ht="18" customHeight="1">
       <c r="A53" s="25" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="B53" s="25" t="n">
@@ -2577,7 +2589,7 @@
       </c>
       <c r="C53" s="26" t="inlineStr">
         <is>
-          <t>동일스틸럭스</t>
+          <t>티웨이홀딩스</t>
         </is>
       </c>
       <c r="D53" s="25" t="n">
@@ -2593,14 +2605,14 @@
         <v>0</v>
       </c>
       <c r="H53" s="29" t="n">
-        <v>-11.15</v>
+        <v>-7.09</v>
       </c>
       <c r="I53" s="27" t="n">
-        <v>29.05</v>
+        <v>26.88</v>
       </c>
       <c r="J53" s="28" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +105%</t>
+          <t>네이버 검색 당일 +174%</t>
         </is>
       </c>
       <c r="K53" s="28" t="inlineStr">
@@ -2612,7 +2624,7 @@
     <row r="54" ht="18" customHeight="1">
       <c r="A54" s="25" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="B54" s="25" t="n">
@@ -2620,7 +2632,7 @@
       </c>
       <c r="C54" s="26" t="inlineStr">
         <is>
-          <t>부국철강</t>
+          <t>메리츠제2호스팩</t>
         </is>
       </c>
       <c r="D54" s="25" t="n">
@@ -2635,15 +2647,15 @@
       <c r="G54" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H54" s="29" t="n">
-        <v>-13.76</v>
-      </c>
-      <c r="I54" s="27" t="n">
-        <v>3.49</v>
+      <c r="H54" s="25" t="n">
+        <v/>
+      </c>
+      <c r="I54" s="25" t="n">
+        <v/>
       </c>
       <c r="J54" s="28" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +104%</t>
+          <t>네이버 검색 당일 +172%</t>
         </is>
       </c>
       <c r="K54" s="28" t="inlineStr">
@@ -2655,7 +2667,7 @@
     <row r="55" ht="18" customHeight="1">
       <c r="A55" s="25" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="B55" s="25" t="n">
@@ -2663,7 +2675,7 @@
       </c>
       <c r="C55" s="26" t="inlineStr">
         <is>
-          <t>대원전선</t>
+          <t>부국철강</t>
         </is>
       </c>
       <c r="D55" s="25" t="n">
@@ -2679,26 +2691,26 @@
         <v>0</v>
       </c>
       <c r="H55" s="29" t="n">
-        <v>-3.73</v>
+        <v>-13.76</v>
       </c>
       <c r="I55" s="27" t="n">
-        <v>6.02</v>
+        <v>3.49</v>
       </c>
       <c r="J55" s="28" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +60% / 중요공시 1건</t>
+          <t>네이버 검색 당일 +160%</t>
         </is>
       </c>
       <c r="K55" s="28" t="inlineStr">
         <is>
-          <t>공시, 네이버</t>
+          <t>네이버</t>
         </is>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1">
       <c r="A56" s="25" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="B56" s="25" t="n">
@@ -2706,7 +2718,7 @@
       </c>
       <c r="C56" s="26" t="inlineStr">
         <is>
-          <t>HMM</t>
+          <t>피앤에스로보틱스</t>
         </is>
       </c>
       <c r="D56" s="25" t="n">
@@ -2721,25 +2733,27 @@
       <c r="G56" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H56" s="29" t="n">
-        <v>-1.47</v>
+      <c r="H56" s="27" t="n">
+        <v>22.04</v>
       </c>
       <c r="I56" s="27" t="n">
-        <v>0.5</v>
+        <v>20.74</v>
       </c>
       <c r="J56" s="28" t="inlineStr">
         <is>
-          <t>매일경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K56" s="28" t="n">
-        <v/>
+          <t>네이버 검색 당일 +151%</t>
+        </is>
+      </c>
+      <c r="K56" s="28" t="inlineStr">
+        <is>
+          <t>네이버</t>
+        </is>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1">
       <c r="A57" s="25" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="B57" s="25" t="n">
@@ -2747,7 +2761,7 @@
       </c>
       <c r="C57" s="26" t="inlineStr">
         <is>
-          <t>우리기술</t>
+          <t>동일스틸럭스</t>
         </is>
       </c>
       <c r="D57" s="25" t="n">
@@ -2763,14 +2777,14 @@
         <v>0</v>
       </c>
       <c r="H57" s="29" t="n">
-        <v>-1.89</v>
-      </c>
-      <c r="I57" s="29" t="n">
-        <v>-17.47</v>
+        <v>-11.15</v>
+      </c>
+      <c r="I57" s="27" t="n">
+        <v>29.05</v>
       </c>
       <c r="J57" s="28" t="inlineStr">
         <is>
-          <t>네이버뉴스 헤드라인 언급</t>
+          <t>네이버 검색 당일 +147%</t>
         </is>
       </c>
       <c r="K57" s="28" t="inlineStr">
@@ -2782,7 +2796,7 @@
     <row r="58" ht="18" customHeight="1">
       <c r="A58" s="25" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="B58" s="25" t="n">
@@ -2790,7 +2804,7 @@
       </c>
       <c r="C58" s="26" t="inlineStr">
         <is>
-          <t>휴림로봇</t>
+          <t>대원전선</t>
         </is>
       </c>
       <c r="D58" s="25" t="n">
@@ -2806,26 +2820,26 @@
         <v>0</v>
       </c>
       <c r="H58" s="29" t="n">
-        <v>-3.34</v>
-      </c>
-      <c r="I58" s="29" t="n">
-        <v>-13.73</v>
+        <v>-3.73</v>
+      </c>
+      <c r="I58" s="27" t="n">
+        <v>6.02</v>
       </c>
       <c r="J58" s="28" t="inlineStr">
         <is>
-          <t>네이버뉴스 헤드라인 언급</t>
+          <t>네이버 검색 당일 +95% / 중요공시 1건</t>
         </is>
       </c>
       <c r="K58" s="28" t="inlineStr">
         <is>
-          <t>네이버</t>
+          <t>네이버, 공시</t>
         </is>
       </c>
     </row>
     <row r="59" ht="18" customHeight="1">
       <c r="A59" s="25" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="B59" s="25" t="n">
@@ -2833,7 +2847,7 @@
       </c>
       <c r="C59" s="26" t="inlineStr">
         <is>
-          <t>LB세미콘</t>
+          <t>비엘팜텍</t>
         </is>
       </c>
       <c r="D59" s="25" t="n">
@@ -2849,26 +2863,26 @@
         <v>0</v>
       </c>
       <c r="H59" s="29" t="n">
-        <v>-3.58</v>
+        <v>-20.26</v>
       </c>
       <c r="I59" s="27" t="n">
-        <v>0.97</v>
+        <v>4.23</v>
       </c>
       <c r="J59" s="28" t="inlineStr">
         <is>
-          <t>중요공시 3건</t>
+          <t>네이버 검색 당일 +78% / 중요공시 1건</t>
         </is>
       </c>
       <c r="K59" s="28" t="inlineStr">
         <is>
-          <t>공시</t>
+          <t>네이버, 공시</t>
         </is>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1">
       <c r="A60" s="25" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="B60" s="25" t="n">
@@ -2876,7 +2890,7 @@
       </c>
       <c r="C60" s="26" t="inlineStr">
         <is>
-          <t>모아데이타</t>
+          <t>한솔테크닉스</t>
         </is>
       </c>
       <c r="D60" s="25" t="n">
@@ -2891,27 +2905,27 @@
       <c r="G60" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H60" s="27" t="n">
-        <v>2.44</v>
+      <c r="H60" s="29" t="n">
+        <v>-4.87</v>
       </c>
       <c r="I60" s="27" t="n">
-        <v>13.39</v>
+        <v>7.83</v>
       </c>
       <c r="J60" s="28" t="inlineStr">
         <is>
-          <t>중요공시 3건</t>
+          <t>네이버 검색 당일 +76% / 중요공시 2건</t>
         </is>
       </c>
       <c r="K60" s="28" t="inlineStr">
         <is>
-          <t>공시</t>
+          <t>네이버, 공시</t>
         </is>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
       <c r="A61" s="25" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="B61" s="25" t="n">
@@ -2919,42 +2933,42 @@
       </c>
       <c r="C61" s="26" t="inlineStr">
         <is>
-          <t>오르비텍</t>
+          <t>삼보산업</t>
         </is>
       </c>
       <c r="D61" s="25" t="n">
         <v>3</v>
       </c>
       <c r="E61" s="25" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F61" s="25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G61" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H61" s="29" t="n">
-        <v>-8.24</v>
-      </c>
-      <c r="I61" s="29" t="n">
-        <v>-10.69</v>
+      <c r="H61" s="27" t="n">
+        <v>11.54</v>
+      </c>
+      <c r="I61" s="27" t="n">
+        <v>45.97</v>
       </c>
       <c r="J61" s="28" t="inlineStr">
         <is>
-          <t>중요공시 2건 / 중요공시 3일 +100%</t>
+          <t>네이버 검색 당일 +61% / 중요공시 1건</t>
         </is>
       </c>
       <c r="K61" s="28" t="inlineStr">
         <is>
-          <t>공시</t>
+          <t>네이버, 공시</t>
         </is>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1">
       <c r="A62" s="25" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="B62" s="25" t="n">
@@ -2962,7 +2976,7 @@
       </c>
       <c r="C62" s="26" t="inlineStr">
         <is>
-          <t>한전기술</t>
+          <t>다스코</t>
         </is>
       </c>
       <c r="D62" s="25" t="n">
@@ -2977,25 +2991,27 @@
       <c r="G62" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H62" s="29" t="n">
-        <v>-9.51</v>
-      </c>
-      <c r="I62" s="29" t="n">
-        <v>-18.24</v>
+      <c r="H62" s="27" t="n">
+        <v>29.96</v>
+      </c>
+      <c r="I62" s="27" t="n">
+        <v>31.44</v>
       </c>
       <c r="J62" s="28" t="inlineStr">
         <is>
-          <t>매일경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K62" s="28" t="n">
-        <v/>
+          <t>네이버 검색 당일 +59% / 중요공시 1건</t>
+        </is>
+      </c>
+      <c r="K62" s="28" t="inlineStr">
+        <is>
+          <t>네이버, 공시</t>
+        </is>
       </c>
     </row>
     <row r="63" ht="18" customHeight="1">
       <c r="A63" s="25" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="B63" s="25" t="n">
@@ -3003,7 +3019,7 @@
       </c>
       <c r="C63" s="26" t="inlineStr">
         <is>
-          <t>한화</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="D63" s="25" t="n">
@@ -3019,18 +3035,20 @@
         <v>0</v>
       </c>
       <c r="H63" s="29" t="n">
-        <v>-4.71</v>
+        <v>-7.41</v>
       </c>
       <c r="I63" s="29" t="n">
-        <v>-0.95</v>
+        <v>-2.75</v>
       </c>
       <c r="J63" s="28" t="inlineStr">
         <is>
-          <t>매일경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K63" s="28" t="n">
-        <v/>
+          <t>네이버 검색 당일 +58% / 중요공시 1건</t>
+        </is>
+      </c>
+      <c r="K63" s="28" t="inlineStr">
+        <is>
+          <t>네이버, 공시</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -3136,12 +3154,12 @@
       </c>
       <c r="F3" s="25" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="G3" s="25" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="H3" s="25" t="n"/>
@@ -3157,22 +3175,22 @@
         <v>1</v>
       </c>
       <c r="C4" s="25" t="n">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="D4" s="25" t="n">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="E4" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F4" s="25" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="G4" s="25" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="H4" s="27" t="n">
@@ -3192,22 +3210,22 @@
         <v>1</v>
       </c>
       <c r="C5" s="25" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="D5" s="25" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="E5" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F5" s="25" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="G5" s="25" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="H5" s="27" t="n">
@@ -3220,42 +3238,42 @@
     <row r="6" ht="18" customHeight="1">
       <c r="A6" s="26" t="inlineStr">
         <is>
-          <t>삼성전기</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B6" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C6" s="25" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D6" s="25" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E6" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F6" s="25" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="G6" s="25" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
-        </is>
-      </c>
-      <c r="H6" s="27" t="n">
-        <v>3.18</v>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="H6" s="29" t="n">
+        <v>-2.34</v>
       </c>
       <c r="I6" s="27" t="n">
-        <v>32.44</v>
+        <v>9.77</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
       <c r="A7" s="26" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>현대차</t>
         </is>
       </c>
       <c r="B7" s="25" t="n">
@@ -3272,117 +3290,117 @@
       </c>
       <c r="F7" s="25" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="G7" s="25" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
-        </is>
-      </c>
-      <c r="H7" s="29" t="n">
-        <v>-2.34</v>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="H7" s="27" t="n">
+        <v>2</v>
       </c>
       <c r="I7" s="27" t="n">
-        <v>9.77</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="26" t="inlineStr">
         <is>
-          <t>현대차</t>
+          <t>대한항공</t>
         </is>
       </c>
       <c r="B8" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C8" s="25" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D8" s="25" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E8" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F8" s="25" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="G8" s="25" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
-        </is>
-      </c>
-      <c r="H8" s="27" t="n">
-        <v>2</v>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="H8" s="29" t="n">
+        <v>-3.12</v>
       </c>
       <c r="I8" s="27" t="n">
-        <v>0.99</v>
+        <v>5.08</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
       <c r="A9" s="26" t="inlineStr">
         <is>
-          <t>대한항공</t>
+          <t>삼성전기</t>
         </is>
       </c>
       <c r="B9" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C9" s="25" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D9" s="25" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E9" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F9" s="25" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="G9" s="25" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
-        </is>
-      </c>
-      <c r="H9" s="29" t="n">
-        <v>-3.12</v>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="H9" s="27" t="n">
+        <v>3.18</v>
       </c>
       <c r="I9" s="27" t="n">
-        <v>5.08</v>
+        <v>32.44</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
       <c r="A10" s="26" t="inlineStr">
         <is>
-          <t>로봇</t>
+          <t>인공지능</t>
         </is>
       </c>
       <c r="B10" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C10" s="25" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D10" s="25" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E10" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F10" s="25" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="G10" s="25" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="H10" s="25" t="n"/>
@@ -3391,60 +3409,64 @@
     <row r="11" ht="18" customHeight="1">
       <c r="A11" s="26" t="inlineStr">
         <is>
-          <t>바이오</t>
+          <t>LG</t>
         </is>
       </c>
       <c r="B11" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C11" s="25" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D11" s="25" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E11" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F11" s="25" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="G11" s="25" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
-        </is>
-      </c>
-      <c r="H11" s="25" t="n"/>
-      <c r="I11" s="25" t="n"/>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="H11" s="29" t="n">
+        <v>-0.91</v>
+      </c>
+      <c r="I11" s="27" t="n">
+        <v>2.25</v>
+      </c>
     </row>
     <row r="12" ht="18" customHeight="1">
       <c r="A12" s="26" t="inlineStr">
         <is>
-          <t>인공지능</t>
+          <t>바이오</t>
         </is>
       </c>
       <c r="B12" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C12" s="25" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D12" s="25" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E12" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F12" s="25" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="G12" s="25" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="H12" s="25" t="n"/>
@@ -3453,7 +3475,7 @@
     <row r="13" ht="18" customHeight="1">
       <c r="A13" s="26" t="inlineStr">
         <is>
-          <t>제약</t>
+          <t>넥써쓰</t>
         </is>
       </c>
       <c r="B13" s="25" t="n">
@@ -3470,56 +3492,56 @@
       </c>
       <c r="F13" s="25" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="G13" s="25" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
-        </is>
-      </c>
-      <c r="H13" s="25" t="n"/>
-      <c r="I13" s="25" t="n"/>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="H13" s="29" t="n">
+        <v>-27.47</v>
+      </c>
+      <c r="I13" s="29" t="n">
+        <v>-4.83</v>
+      </c>
     </row>
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="26" t="inlineStr">
         <is>
-          <t>LG</t>
+          <t>로봇</t>
         </is>
       </c>
       <c r="B14" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C14" s="25" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D14" s="25" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E14" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F14" s="25" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="G14" s="25" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
-        </is>
-      </c>
-      <c r="H14" s="29" t="n">
-        <v>-0.91</v>
-      </c>
-      <c r="I14" s="27" t="n">
-        <v>2.25</v>
-      </c>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="H14" s="25" t="n"/>
+      <c r="I14" s="25" t="n"/>
     </row>
     <row r="15" ht="18" customHeight="1">
       <c r="A15" s="26" t="inlineStr">
         <is>
-          <t>넥써쓰</t>
+          <t>셀트리온</t>
         </is>
       </c>
       <c r="B15" s="25" t="n">
@@ -3536,19 +3558,19 @@
       </c>
       <c r="F15" s="25" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="G15" s="25" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="H15" s="29" t="n">
-        <v>-27.47</v>
+        <v>-1.9</v>
       </c>
       <c r="I15" s="29" t="n">
-        <v>-4.83</v>
+        <v>-1.56</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
@@ -3571,12 +3593,12 @@
       </c>
       <c r="F16" s="25" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="G16" s="25" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="H16" s="29" t="n">
@@ -3589,7 +3611,7 @@
     <row r="17" ht="18" customHeight="1">
       <c r="A17" s="26" t="inlineStr">
         <is>
-          <t>SK스퀘어</t>
+          <t>보해양조</t>
         </is>
       </c>
       <c r="B17" s="25" t="n">
@@ -3606,25 +3628,25 @@
       </c>
       <c r="F17" s="25" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="G17" s="25" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="H17" s="27" t="n">
-        <v>4.71</v>
+        <v>29.88</v>
       </c>
       <c r="I17" s="27" t="n">
-        <v>31.08</v>
+        <v>58.36</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
       <c r="A18" s="26" t="inlineStr">
         <is>
-          <t>미래에셋증권</t>
+          <t>한화</t>
         </is>
       </c>
       <c r="B18" s="25" t="n">
@@ -3641,91 +3663,95 @@
       </c>
       <c r="F18" s="25" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="G18" s="25" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="H18" s="29" t="n">
-        <v>-3.85</v>
+        <v>-4.71</v>
       </c>
       <c r="I18" s="29" t="n">
-        <v>-6.79</v>
+        <v>-0.95</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
       <c r="A19" s="26" t="inlineStr">
         <is>
-          <t>삼성물산</t>
+          <t>KT</t>
         </is>
       </c>
       <c r="B19" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C19" s="25" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D19" s="25" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E19" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F19" s="25" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="G19" s="25" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
-        </is>
-      </c>
-      <c r="H19" s="27" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="I19" s="27" t="n">
-        <v>13.77</v>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="H19" s="29" t="n">
+        <v>-0.37</v>
+      </c>
+      <c r="I19" s="29" t="n">
+        <v>-2.74</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
       <c r="A20" s="26" t="inlineStr">
         <is>
-          <t>조선</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="B20" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C20" s="25" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D20" s="25" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E20" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F20" s="25" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="G20" s="25" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
-        </is>
-      </c>
-      <c r="H20" s="25" t="n"/>
-      <c r="I20" s="25" t="n"/>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="H20" s="29" t="n">
+        <v>-26.16</v>
+      </c>
+      <c r="I20" s="29" t="n">
+        <v>-19.9</v>
+      </c>
     </row>
     <row r="21" ht="18" customHeight="1">
       <c r="A21" s="26" t="inlineStr">
         <is>
-          <t>KT</t>
+          <t>미래에셋증권</t>
         </is>
       </c>
       <c r="B21" s="25" t="n">
@@ -3742,25 +3768,25 @@
       </c>
       <c r="F21" s="25" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="G21" s="25" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="H21" s="29" t="n">
-        <v>-0.37</v>
+        <v>-3.85</v>
       </c>
       <c r="I21" s="29" t="n">
-        <v>-2.74</v>
+        <v>-6.79</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
       <c r="A22" s="26" t="inlineStr">
         <is>
-          <t>씨피시스템</t>
+          <t>제약</t>
         </is>
       </c>
       <c r="B22" s="25" t="n">
@@ -3777,20 +3803,16 @@
       </c>
       <c r="F22" s="25" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="G22" s="25" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
-        </is>
-      </c>
-      <c r="H22" s="27" t="n">
-        <v>29.88</v>
-      </c>
-      <c r="I22" s="27" t="n">
-        <v>20.79</v>
-      </c>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="H22" s="25" t="n"/>
+      <c r="I22" s="25" t="n"/>
     </row>
     <row r="23" ht="18" customHeight="1">
       <c r="A23" s="26" t="inlineStr">
@@ -3812,12 +3834,12 @@
       </c>
       <c r="F23" s="25" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="G23" s="25" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="H23" s="29" t="n">
@@ -3830,42 +3852,42 @@
     <row r="24" ht="18" customHeight="1">
       <c r="A24" s="26" t="inlineStr">
         <is>
-          <t>HD현대</t>
+          <t>한화오션</t>
         </is>
       </c>
       <c r="B24" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C24" s="25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D24" s="25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E24" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F24" s="25" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="G24" s="25" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
-        </is>
-      </c>
-      <c r="H24" s="29" t="n">
-        <v>-3.35</v>
-      </c>
-      <c r="I24" s="29" t="n">
-        <v>-5.53</v>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="H24" s="27" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="I24" s="27" t="n">
+        <v>13.93</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
       <c r="A25" s="26" t="inlineStr">
         <is>
-          <t>HD현대중공업</t>
+          <t>HD현대</t>
         </is>
       </c>
       <c r="B25" s="25" t="n">
@@ -3882,25 +3904,25 @@
       </c>
       <c r="F25" s="25" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="G25" s="25" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="H25" s="29" t="n">
-        <v>-2.49</v>
-      </c>
-      <c r="I25" s="27" t="n">
-        <v>2.62</v>
+        <v>-3.35</v>
+      </c>
+      <c r="I25" s="29" t="n">
+        <v>-5.53</v>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
       <c r="A26" s="26" t="inlineStr">
         <is>
-          <t>HJ중공업</t>
+          <t>HD현대중공업</t>
         </is>
       </c>
       <c r="B26" s="25" t="n">
@@ -3917,25 +3939,25 @@
       </c>
       <c r="F26" s="25" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="G26" s="25" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="H26" s="29" t="n">
-        <v>-3.67</v>
+        <v>-2.49</v>
       </c>
       <c r="I26" s="27" t="n">
-        <v>3.24</v>
+        <v>2.62</v>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
       <c r="A27" s="26" t="inlineStr">
         <is>
-          <t>LG전자</t>
+          <t>HJ중공업</t>
         </is>
       </c>
       <c r="B27" s="25" t="n">
@@ -3952,25 +3974,25 @@
       </c>
       <c r="F27" s="25" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="G27" s="25" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="H27" s="29" t="n">
-        <v>-7.44</v>
-      </c>
-      <c r="I27" s="29" t="n">
-        <v>-6.21</v>
+        <v>-3.67</v>
+      </c>
+      <c r="I27" s="27" t="n">
+        <v>3.24</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
       <c r="A28" s="26" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>LG전자</t>
         </is>
       </c>
       <c r="B28" s="25" t="n">
@@ -3987,19 +4009,19 @@
       </c>
       <c r="F28" s="25" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="G28" s="25" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="H28" s="29" t="n">
-        <v>-26.16</v>
+        <v>-7.44</v>
       </c>
       <c r="I28" s="29" t="n">
-        <v>-19.9</v>
+        <v>-6.21</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
@@ -4022,12 +4044,12 @@
       </c>
       <c r="F29" s="25" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="G29" s="25" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="H29" s="27" t="n">
@@ -4040,7 +4062,7 @@
     <row r="30" ht="18" customHeight="1">
       <c r="A30" s="26" t="inlineStr">
         <is>
-          <t>보해양조</t>
+          <t>방산</t>
         </is>
       </c>
       <c r="B30" s="25" t="n">
@@ -4057,25 +4079,21 @@
       </c>
       <c r="F30" s="25" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="G30" s="25" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
-        </is>
-      </c>
-      <c r="H30" s="27" t="n">
-        <v>29.88</v>
-      </c>
-      <c r="I30" s="27" t="n">
-        <v>58.36</v>
-      </c>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="H30" s="25" t="n"/>
+      <c r="I30" s="25" t="n"/>
     </row>
     <row r="31" ht="18" customHeight="1">
       <c r="A31" s="26" t="inlineStr">
         <is>
-          <t>전기차</t>
+          <t>씨피시스템</t>
         </is>
       </c>
       <c r="B31" s="25" t="n">
@@ -4092,21 +4110,25 @@
       </c>
       <c r="F31" s="25" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="G31" s="25" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
-        </is>
-      </c>
-      <c r="H31" s="25" t="n"/>
-      <c r="I31" s="25" t="n"/>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="H31" s="27" t="n">
+        <v>29.88</v>
+      </c>
+      <c r="I31" s="27" t="n">
+        <v>20.79</v>
+      </c>
     </row>
     <row r="32" ht="18" customHeight="1">
       <c r="A32" s="26" t="inlineStr">
         <is>
-          <t>한솔테크닉스</t>
+          <t>전기차</t>
         </is>
       </c>
       <c r="B32" s="25" t="n">
@@ -4123,55 +4145,47 @@
       </c>
       <c r="F32" s="25" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="G32" s="25" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
-        </is>
-      </c>
-      <c r="H32" s="29" t="n">
-        <v>-4.87</v>
-      </c>
-      <c r="I32" s="27" t="n">
-        <v>7.83</v>
-      </c>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="H32" s="25" t="n"/>
+      <c r="I32" s="25" t="n"/>
     </row>
     <row r="33" ht="18" customHeight="1">
       <c r="A33" s="26" t="inlineStr">
         <is>
-          <t>HMM</t>
+          <t>태양광</t>
         </is>
       </c>
       <c r="B33" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C33" s="25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D33" s="25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E33" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F33" s="25" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="G33" s="25" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
-        </is>
-      </c>
-      <c r="H33" s="29" t="n">
-        <v>-1.47</v>
-      </c>
-      <c r="I33" s="27" t="n">
-        <v>0.5</v>
-      </c>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="H33" s="25" t="n"/>
+      <c r="I33" s="25" t="n"/>
     </row>
     <row r="34" ht="18" customHeight="1">
       <c r="A34" s="26" t="inlineStr">
@@ -4193,12 +4207,12 @@
       </c>
       <c r="F34" s="25" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="G34" s="25" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="H34" s="27" t="n">
@@ -4211,7 +4225,7 @@
     <row r="35" ht="18" customHeight="1">
       <c r="A35" s="26" t="inlineStr">
         <is>
-          <t>LB세미콘</t>
+          <t>강동씨앤엘</t>
         </is>
       </c>
       <c r="B35" s="25" t="n">
@@ -4228,25 +4242,25 @@
       </c>
       <c r="F35" s="25" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="G35" s="25" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
-        </is>
-      </c>
-      <c r="H35" s="29" t="n">
-        <v>-3.58</v>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="H35" s="27" t="n">
+        <v>29.91</v>
       </c>
       <c r="I35" s="27" t="n">
-        <v>0.97</v>
+        <v>121.56</v>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
       <c r="A36" s="26" t="inlineStr">
         <is>
-          <t>강동씨앤엘</t>
+          <t>다스코</t>
         </is>
       </c>
       <c r="B36" s="25" t="n">
@@ -4263,25 +4277,25 @@
       </c>
       <c r="F36" s="25" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="G36" s="25" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="H36" s="27" t="n">
-        <v>29.91</v>
+        <v>29.96</v>
       </c>
       <c r="I36" s="27" t="n">
-        <v>121.56</v>
+        <v>31.44</v>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
       <c r="A37" s="26" t="inlineStr">
         <is>
-          <t>대원전선</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B37" s="25" t="n">
@@ -4298,25 +4312,25 @@
       </c>
       <c r="F37" s="25" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="G37" s="25" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="H37" s="29" t="n">
-        <v>-3.73</v>
-      </c>
-      <c r="I37" s="27" t="n">
-        <v>6.02</v>
+        <v>-7.41</v>
+      </c>
+      <c r="I37" s="29" t="n">
+        <v>-2.75</v>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
       <c r="A38" s="26" t="inlineStr">
         <is>
-          <t>동일스틸럭스</t>
+          <t>대원전선</t>
         </is>
       </c>
       <c r="B38" s="25" t="n">
@@ -4333,25 +4347,25 @@
       </c>
       <c r="F38" s="25" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="G38" s="25" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="H38" s="29" t="n">
-        <v>-11.15</v>
+        <v>-3.73</v>
       </c>
       <c r="I38" s="27" t="n">
-        <v>29.05</v>
+        <v>6.02</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
       <c r="A39" s="26" t="inlineStr">
         <is>
-          <t>모아데이타</t>
+          <t>동일스틸럭스</t>
         </is>
       </c>
       <c r="B39" s="25" t="n">
@@ -4368,25 +4382,25 @@
       </c>
       <c r="F39" s="25" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="G39" s="25" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
-        </is>
-      </c>
-      <c r="H39" s="27" t="n">
-        <v>2.44</v>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="H39" s="29" t="n">
+        <v>-11.15</v>
       </c>
       <c r="I39" s="27" t="n">
-        <v>13.39</v>
+        <v>29.05</v>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
       <c r="A40" s="26" t="inlineStr">
         <is>
-          <t>부국철강</t>
+          <t>메리츠제2호스팩</t>
         </is>
       </c>
       <c r="B40" s="25" t="n">
@@ -4403,25 +4417,21 @@
       </c>
       <c r="F40" s="25" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="G40" s="25" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
-        </is>
-      </c>
-      <c r="H40" s="29" t="n">
-        <v>-13.76</v>
-      </c>
-      <c r="I40" s="27" t="n">
-        <v>3.49</v>
-      </c>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="H40" s="25" t="n"/>
+      <c r="I40" s="25" t="n"/>
     </row>
     <row r="41" ht="18" customHeight="1">
       <c r="A41" s="26" t="inlineStr">
         <is>
-          <t>삼익제약</t>
+          <t>부국철강</t>
         </is>
       </c>
       <c r="B41" s="25" t="n">
@@ -4438,25 +4448,25 @@
       </c>
       <c r="F41" s="25" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="G41" s="25" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
-        </is>
-      </c>
-      <c r="H41" s="27" t="n">
-        <v>29.98</v>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="H41" s="29" t="n">
+        <v>-13.76</v>
       </c>
       <c r="I41" s="27" t="n">
-        <v>41.82</v>
+        <v>3.49</v>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
       <c r="A42" s="26" t="inlineStr">
         <is>
-          <t>삼화전자</t>
+          <t>비엘팜텍</t>
         </is>
       </c>
       <c r="B42" s="25" t="n">
@@ -4473,25 +4483,25 @@
       </c>
       <c r="F42" s="25" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="G42" s="25" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
-        </is>
-      </c>
-      <c r="H42" s="27" t="n">
-        <v>2.81</v>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="H42" s="29" t="n">
+        <v>-20.26</v>
       </c>
       <c r="I42" s="27" t="n">
-        <v>73.59</v>
+        <v>4.23</v>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1">
       <c r="A43" s="26" t="inlineStr">
         <is>
-          <t>성문전자</t>
+          <t>삼보산업</t>
         </is>
       </c>
       <c r="B43" s="25" t="n">
@@ -4508,25 +4518,25 @@
       </c>
       <c r="F43" s="25" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="G43" s="25" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="H43" s="27" t="n">
-        <v>4.43</v>
+        <v>11.54</v>
       </c>
       <c r="I43" s="27" t="n">
-        <v>40.24</v>
+        <v>45.97</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
       <c r="A44" s="26" t="inlineStr">
         <is>
-          <t>오르비텍</t>
+          <t>삼익제약</t>
         </is>
       </c>
       <c r="B44" s="25" t="n">
@@ -4543,25 +4553,25 @@
       </c>
       <c r="F44" s="25" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="G44" s="25" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
-        </is>
-      </c>
-      <c r="H44" s="29" t="n">
-        <v>-8.24</v>
-      </c>
-      <c r="I44" s="29" t="n">
-        <v>-10.69</v>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="H44" s="27" t="n">
+        <v>29.98</v>
+      </c>
+      <c r="I44" s="27" t="n">
+        <v>41.82</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
       <c r="A45" s="26" t="inlineStr">
         <is>
-          <t>우리기술</t>
+          <t>삼화전자</t>
         </is>
       </c>
       <c r="B45" s="25" t="n">
@@ -4578,25 +4588,25 @@
       </c>
       <c r="F45" s="25" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="G45" s="25" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
-        </is>
-      </c>
-      <c r="H45" s="29" t="n">
-        <v>-1.89</v>
-      </c>
-      <c r="I45" s="29" t="n">
-        <v>-17.47</v>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="H45" s="27" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="I45" s="27" t="n">
+        <v>73.59</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
       <c r="A46" s="26" t="inlineStr">
         <is>
-          <t>위더스제약</t>
+          <t>성문전자</t>
         </is>
       </c>
       <c r="B46" s="25" t="n">
@@ -4613,25 +4623,25 @@
       </c>
       <c r="F46" s="25" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="G46" s="25" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="H46" s="27" t="n">
-        <v>13.59</v>
+        <v>4.43</v>
       </c>
       <c r="I46" s="27" t="n">
-        <v>33.03</v>
+        <v>40.24</v>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
       <c r="A47" s="26" t="inlineStr">
         <is>
-          <t>율촌</t>
+          <t>위더스제약</t>
         </is>
       </c>
       <c r="B47" s="25" t="n">
@@ -4648,25 +4658,25 @@
       </c>
       <c r="F47" s="25" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="G47" s="25" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
-        </is>
-      </c>
-      <c r="H47" s="29" t="n">
-        <v>-13.55</v>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="H47" s="27" t="n">
+        <v>13.59</v>
       </c>
       <c r="I47" s="27" t="n">
-        <v>30.73</v>
+        <v>33.03</v>
       </c>
     </row>
     <row r="48" ht="18" customHeight="1">
       <c r="A48" s="26" t="inlineStr">
         <is>
-          <t>티웨이홀딩스</t>
+          <t>율촌</t>
         </is>
       </c>
       <c r="B48" s="25" t="n">
@@ -4683,25 +4693,25 @@
       </c>
       <c r="F48" s="25" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="G48" s="25" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="H48" s="29" t="n">
-        <v>-7.09</v>
+        <v>-13.55</v>
       </c>
       <c r="I48" s="27" t="n">
-        <v>26.88</v>
+        <v>30.73</v>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1">
       <c r="A49" s="26" t="inlineStr">
         <is>
-          <t>한전기술</t>
+          <t>티웨이홀딩스</t>
         </is>
       </c>
       <c r="B49" s="25" t="n">
@@ -4718,25 +4728,25 @@
       </c>
       <c r="F49" s="25" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="G49" s="25" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="H49" s="29" t="n">
-        <v>-9.51</v>
-      </c>
-      <c r="I49" s="29" t="n">
-        <v>-18.24</v>
+        <v>-7.09</v>
+      </c>
+      <c r="I49" s="27" t="n">
+        <v>26.88</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
       <c r="A50" s="26" t="inlineStr">
         <is>
-          <t>한화</t>
+          <t>피앤에스로보틱스</t>
         </is>
       </c>
       <c r="B50" s="25" t="n">
@@ -4753,25 +4763,25 @@
       </c>
       <c r="F50" s="25" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="G50" s="25" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
-        </is>
-      </c>
-      <c r="H50" s="29" t="n">
-        <v>-4.71</v>
-      </c>
-      <c r="I50" s="29" t="n">
-        <v>-0.95</v>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="H50" s="27" t="n">
+        <v>22.04</v>
+      </c>
+      <c r="I50" s="27" t="n">
+        <v>20.74</v>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
       <c r="A51" s="26" t="inlineStr">
         <is>
-          <t>현대약품</t>
+          <t>한솔테크닉스</t>
         </is>
       </c>
       <c r="B51" s="25" t="n">
@@ -4788,25 +4798,25 @@
       </c>
       <c r="F51" s="25" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="G51" s="25" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="H51" s="29" t="n">
-        <v>-4.12</v>
+        <v>-4.87</v>
       </c>
       <c r="I51" s="27" t="n">
-        <v>42.23</v>
+        <v>7.83</v>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1">
       <c r="A52" s="26" t="inlineStr">
         <is>
-          <t>휴림로봇</t>
+          <t>현대약품</t>
         </is>
       </c>
       <c r="B52" s="25" t="n">
@@ -4823,19 +4833,19 @@
       </c>
       <c r="F52" s="25" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="G52" s="25" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="H52" s="29" t="n">
-        <v>-3.34</v>
-      </c>
-      <c r="I52" s="29" t="n">
-        <v>-13.73</v>
+        <v>-4.12</v>
+      </c>
+      <c r="I52" s="27" t="n">
+        <v>42.23</v>
       </c>
     </row>
   </sheetData>
@@ -4926,12 +4936,12 @@
       </c>
       <c r="E3" s="36" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="F3" s="37" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="G3" s="37" t="inlineStr">
@@ -4950,19 +4960,19 @@
         <v>1</v>
       </c>
       <c r="C4" s="36" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D4" s="36" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E4" s="36" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="F4" s="37" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="G4" s="37" t="inlineStr">
@@ -4988,12 +4998,12 @@
       </c>
       <c r="E5" s="36" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="F5" s="37" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="G5" s="37" t="inlineStr">
@@ -5005,26 +5015,26 @@
     <row r="6" ht="18" customHeight="1">
       <c r="A6" s="35" t="inlineStr">
         <is>
-          <t>로봇</t>
+          <t>방산</t>
         </is>
       </c>
       <c r="B6" s="36" t="n">
         <v>1</v>
       </c>
       <c r="C6" s="36" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D6" s="36" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E6" s="36" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="F6" s="37" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="G6" s="37" t="inlineStr">
@@ -5036,26 +5046,26 @@
     <row r="7" ht="18" customHeight="1">
       <c r="A7" s="35" t="inlineStr">
         <is>
-          <t>조선</t>
+          <t>로봇</t>
         </is>
       </c>
       <c r="B7" s="36" t="n">
         <v>1</v>
       </c>
       <c r="C7" s="36" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D7" s="36" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E7" s="36" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="F7" s="37" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="G7" s="37" t="inlineStr">
@@ -5067,26 +5077,26 @@
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="35" t="inlineStr">
         <is>
-          <t>제약</t>
+          <t>태양광</t>
         </is>
       </c>
       <c r="B8" s="36" t="n">
         <v>1</v>
       </c>
       <c r="C8" s="36" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D8" s="36" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E8" s="36" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="F8" s="37" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="G8" s="37" t="inlineStr">
@@ -5098,65 +5108,69 @@
     <row r="9" ht="18" customHeight="1">
       <c r="A9" s="35" t="inlineStr">
         <is>
+          <t>제약</t>
+        </is>
+      </c>
+      <c r="B9" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" s="36" t="n">
+        <v>5</v>
+      </c>
+      <c r="D9" s="36" t="n">
+        <v>5</v>
+      </c>
+      <c r="E9" s="36" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="F9" s="37" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="G9" s="37" t="inlineStr">
+        <is>
+          <t>⚡ 관심</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="18" customHeight="1">
+      <c r="A10" s="35" t="inlineStr">
+        <is>
           <t>인공지능</t>
         </is>
       </c>
-      <c r="B9" s="36" t="n">
-        <v>1</v>
-      </c>
-      <c r="C9" s="36" t="n">
-        <v>9</v>
-      </c>
-      <c r="D9" s="36" t="n">
-        <v>9</v>
-      </c>
-      <c r="E9" s="36" t="inlineStr">
-        <is>
-          <t>2026-06-20</t>
-        </is>
-      </c>
-      <c r="F9" s="37" t="inlineStr">
-        <is>
-          <t>2026-06-20</t>
-        </is>
-      </c>
-      <c r="G9" s="37" t="inlineStr">
+      <c r="B10" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" s="36" t="n">
+        <v>12</v>
+      </c>
+      <c r="D10" s="36" t="n">
+        <v>12</v>
+      </c>
+      <c r="E10" s="36" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="F10" s="37" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="G10" s="37" t="inlineStr">
         <is>
           <t>⚡ 관심</t>
         </is>
       </c>
-    </row>
-    <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="26" t="inlineStr">
-        <is>
-          <t>이차전지</t>
-        </is>
-      </c>
-      <c r="B10" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="C10" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" s="25" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F10" s="28" t="inlineStr">
-        <is>
-          <t>감지 없음</t>
-        </is>
-      </c>
-      <c r="G10" s="28" t="inlineStr"/>
     </row>
     <row r="11" ht="18" customHeight="1">
       <c r="A11" s="26" t="inlineStr">
         <is>
-          <t>AI반도체</t>
+          <t>이차전지</t>
         </is>
       </c>
       <c r="B11" s="25" t="n">
@@ -5183,7 +5197,7 @@
     <row r="12" ht="18" customHeight="1">
       <c r="A12" s="26" t="inlineStr">
         <is>
-          <t>방산</t>
+          <t>AI반도체</t>
         </is>
       </c>
       <c r="B12" s="25" t="n">
@@ -5264,7 +5278,7 @@
     <row r="15" ht="18" customHeight="1">
       <c r="A15" s="26" t="inlineStr">
         <is>
-          <t>태양광</t>
+          <t>게임</t>
         </is>
       </c>
       <c r="B15" s="25" t="n">
@@ -5291,7 +5305,7 @@
     <row r="16" ht="18" customHeight="1">
       <c r="A16" s="26" t="inlineStr">
         <is>
-          <t>게임</t>
+          <t>엔터</t>
         </is>
       </c>
       <c r="B16" s="25" t="n">
@@ -5318,7 +5332,7 @@
     <row r="17" ht="18" customHeight="1">
       <c r="A17" s="26" t="inlineStr">
         <is>
-          <t>엔터</t>
+          <t>핀테크</t>
         </is>
       </c>
       <c r="B17" s="25" t="n">
@@ -5345,7 +5359,7 @@
     <row r="18" ht="18" customHeight="1">
       <c r="A18" s="26" t="inlineStr">
         <is>
-          <t>핀테크</t>
+          <t>클라우드</t>
         </is>
       </c>
       <c r="B18" s="25" t="n">
@@ -5372,7 +5386,7 @@
     <row r="19" ht="18" customHeight="1">
       <c r="A19" s="26" t="inlineStr">
         <is>
-          <t>클라우드</t>
+          <t>조선</t>
         </is>
       </c>
       <c r="B19" s="25" t="n">

--- a/trend/stock_trend_history.xlsx
+++ b/trend/stock_trend_history.xlsx
@@ -258,13 +258,13 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -694,7 +694,7 @@
     <row r="1" ht="36" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>📊 주식 트렌드 조기 감지 대시보드   |   최종 업데이트: 2026-06-21 06:55</t>
+          <t>📊 주식 트렌드 조기 감지 대시보드   |   최종 업데이트: 2026-06-22 06:55</t>
         </is>
       </c>
     </row>
@@ -787,21 +787,21 @@
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="11" t="inlineStr">
         <is>
-          <t>⚡ 최신(2026-06-21) 상위: 반도체  점수 60.0점</t>
+          <t>⚡ 최신(2026-06-22) 상위: 반도체  점수 82.0점</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1">
       <c r="A11" s="12" t="inlineStr">
         <is>
-          <t>⚡ 최신(2026-06-21) 상위: SK  점수 56.0점</t>
+          <t>⚡ 최신(2026-06-22) 상위: SK  점수 46.0점</t>
         </is>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1">
       <c r="A12" s="11" t="inlineStr">
         <is>
-          <t>⚡ 최신(2026-06-21) 상위: SK하이닉스  점수 41.0점</t>
+          <t>⚡ 최신(2026-06-22) 상위: SK하이닉스  점수 44.0점</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B14" s="15" t="n">
@@ -928,10 +928,10 @@
         </is>
       </c>
       <c r="D14" s="15" t="n">
-        <v>60</v>
+        <v>82</v>
       </c>
       <c r="E14" s="15" t="n">
-        <v>60</v>
+        <v>82</v>
       </c>
       <c r="F14" s="15" t="n">
         <v>0</v>
@@ -947,7 +947,7 @@
       </c>
       <c r="J14" s="17" t="inlineStr">
         <is>
-          <t>네이버뉴스 헤드라인 언급 / 매일경제 기사 언급 / 네이버뉴스 헤드라인 언급 / 네이버뉴스 기사 언급 / 매일경제 기사 언급</t>
+          <t>네이버뉴스 헤드라인 언급 / 매일경제 기사 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 기사 언급</t>
         </is>
       </c>
       <c r="K14" s="17" t="inlineStr">
@@ -959,7 +959,7 @@
     <row r="15" ht="18" customHeight="1">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B15" s="15" t="n">
@@ -971,10 +971,10 @@
         </is>
       </c>
       <c r="D15" s="15" t="n">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="E15" s="15" t="n">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="F15" s="15" t="n">
         <v>0</v>
@@ -990,7 +990,7 @@
       </c>
       <c r="J15" s="17" t="inlineStr">
         <is>
-          <t>매일경제 헤드라인 언급 / 매일경제 기사 언급 / 네이버뉴스 헤드라인 언급 / 한국경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
+          <t>네이버뉴스 헤드라인 언급 / 네이버뉴스 헤드라인 언급 / 네이버뉴스 기사 언급 / 매일경제 기사 언급 / 네이버뉴스 기사 언급</t>
         </is>
       </c>
       <c r="K15" s="17" t="inlineStr">
@@ -1002,7 +1002,7 @@
     <row r="16" ht="18" customHeight="1">
       <c r="A16" s="15" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B16" s="15" t="n">
@@ -1014,10 +1014,10 @@
         </is>
       </c>
       <c r="D16" s="15" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="E16" s="15" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="F16" s="15" t="n">
         <v>0</v>
@@ -1033,7 +1033,7 @@
       </c>
       <c r="J16" s="17" t="inlineStr">
         <is>
-          <t>매일경제 헤드라인 언급 / 매일경제 기사 언급 / 네이버뉴스 기사 언급 / 한국경제 헤드라인 언급 / 매일경제 기사 언급</t>
+          <t>네이버뉴스 헤드라인 언급 / 네이버뉴스 헤드라인 언급 / 네이버뉴스 기사 언급 / 매일경제 기사 언급 / 네이버뉴스 기사 언급</t>
         </is>
       </c>
       <c r="K16" s="17" t="inlineStr">
@@ -1045,7 +1045,7 @@
     <row r="17" ht="18" customHeight="1">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B17" s="15" t="n">
@@ -1053,14 +1053,14 @@
       </c>
       <c r="C17" s="16" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>LG</t>
         </is>
       </c>
       <c r="D17" s="15" t="n">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="E17" s="15" t="n">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="F17" s="15" t="n">
         <v>0</v>
@@ -1069,26 +1069,26 @@
         <v>0</v>
       </c>
       <c r="H17" s="19" t="n">
-        <v>-2.34</v>
+        <v>-0.91</v>
       </c>
       <c r="I17" s="18" t="n">
-        <v>9.77</v>
+        <v>2.25</v>
       </c>
       <c r="J17" s="17" t="inlineStr">
         <is>
-          <t>매일경제 기사 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 헤드라인 언급 / 한국경제 헤드라인 언급</t>
+          <t>Google 급상승 검색어 등장 (KR) / 한국경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
         </is>
       </c>
       <c r="K17" s="17" t="inlineStr">
         <is>
-          <t>네이버</t>
+          <t>Google</t>
         </is>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
       <c r="A18" s="15" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B18" s="15" t="n">
@@ -1096,14 +1096,14 @@
       </c>
       <c r="C18" s="16" t="inlineStr">
         <is>
-          <t>현대차</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="D18" s="15" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="E18" s="15" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="F18" s="15" t="n">
         <v>0</v>
@@ -1111,27 +1111,27 @@
       <c r="G18" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="H18" s="18" t="n">
-        <v>2</v>
+      <c r="H18" s="19" t="n">
+        <v>-2.34</v>
       </c>
       <c r="I18" s="18" t="n">
-        <v>0.99</v>
+        <v>9.77</v>
       </c>
       <c r="J18" s="17" t="inlineStr">
         <is>
-          <t>네이버뉴스 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 기사 언급 / 한국경제 헤드라인 언급</t>
+          <t>Google 급상승 검색어 등장 (KR) / 네이버뉴스 헤드라인 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 헤드라인 언급 / 매일경제 기사 언급</t>
         </is>
       </c>
       <c r="K18" s="17" t="inlineStr">
         <is>
-          <t>네이버</t>
+          <t>Google, 네이버</t>
         </is>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
       <c r="A19" s="15" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B19" s="15" t="n">
@@ -1139,14 +1139,14 @@
       </c>
       <c r="C19" s="16" t="inlineStr">
         <is>
-          <t>대한항공</t>
+          <t>현대차</t>
         </is>
       </c>
       <c r="D19" s="15" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E19" s="15" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F19" s="15" t="n">
         <v>0</v>
@@ -1154,25 +1154,27 @@
       <c r="G19" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="H19" s="19" t="n">
-        <v>-3.12</v>
+      <c r="H19" s="18" t="n">
+        <v>2</v>
       </c>
       <c r="I19" s="18" t="n">
-        <v>5.08</v>
+        <v>0.99</v>
       </c>
       <c r="J19" s="17" t="inlineStr">
         <is>
-          <t>매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 한국경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K19" s="17" t="n">
-        <v/>
+          <t>네이버뉴스 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 기사 언급 / 한국경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K19" s="17" t="inlineStr">
+        <is>
+          <t>네이버</t>
+        </is>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
       <c r="A20" s="15" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B20" s="15" t="n">
@@ -1180,14 +1182,14 @@
       </c>
       <c r="C20" s="16" t="inlineStr">
         <is>
-          <t>삼성전기</t>
+          <t>바이오</t>
         </is>
       </c>
       <c r="D20" s="15" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E20" s="15" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F20" s="15" t="n">
         <v>0</v>
@@ -1195,25 +1197,27 @@
       <c r="G20" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="H20" s="18" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="I20" s="18" t="n">
-        <v>32.44</v>
+      <c r="H20" s="15" t="n">
+        <v/>
+      </c>
+      <c r="I20" s="15" t="n">
+        <v/>
       </c>
       <c r="J20" s="17" t="inlineStr">
         <is>
-          <t>매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K20" s="17" t="n">
-        <v/>
+          <t>매일경제 헤드라인 언급 / 네이버뉴스 헤드라인 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 기사 언급 / 한국경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K20" s="17" t="inlineStr">
+        <is>
+          <t>네이버</t>
+        </is>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
       <c r="A21" s="15" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B21" s="15" t="n">
@@ -1225,10 +1229,10 @@
         </is>
       </c>
       <c r="D21" s="15" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E21" s="15" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F21" s="15" t="n">
         <v>0</v>
@@ -1244,7 +1248,7 @@
       </c>
       <c r="J21" s="17" t="inlineStr">
         <is>
-          <t>네이버뉴스 기사 언급 / 네이버뉴스 기사 언급 / 매일경제 기사 언급 / 매일경제 기사 언급 / 매일경제 기사 언급</t>
+          <t>매일경제 기사 언급 / 네이버뉴스 기사 언급 / 매일경제 기사 언급 / 네이버뉴스 기사 언급 / 매일경제 기사 언급</t>
         </is>
       </c>
       <c r="K21" s="17" t="inlineStr">
@@ -1256,7 +1260,7 @@
     <row r="22" ht="18" customHeight="1">
       <c r="A22" s="15" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B22" s="15" t="n">
@@ -1264,14 +1268,14 @@
       </c>
       <c r="C22" s="16" t="inlineStr">
         <is>
-          <t>바이오</t>
+          <t>로봇</t>
         </is>
       </c>
       <c r="D22" s="15" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E22" s="15" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F22" s="15" t="n">
         <v>0</v>
@@ -1287,19 +1291,17 @@
       </c>
       <c r="J22" s="17" t="inlineStr">
         <is>
-          <t>네이버뉴스 헤드라인 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 헤드라인 언급 / 네이버뉴스 헤드라인 언급 / 네이버뉴스 기사 언급</t>
-        </is>
-      </c>
-      <c r="K22" s="17" t="inlineStr">
-        <is>
-          <t>네이버</t>
-        </is>
+          <t>매일경제 기사 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K22" s="17" t="n">
+        <v/>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B23" s="15" t="n">
@@ -1307,14 +1309,14 @@
       </c>
       <c r="C23" s="16" t="inlineStr">
         <is>
-          <t>LG</t>
+          <t>전기차</t>
         </is>
       </c>
       <c r="D23" s="15" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E23" s="15" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F23" s="15" t="n">
         <v>0</v>
@@ -1322,15 +1324,15 @@
       <c r="G23" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="H23" s="19" t="n">
-        <v>-0.91</v>
-      </c>
-      <c r="I23" s="18" t="n">
-        <v>2.25</v>
+      <c r="H23" s="15" t="n">
+        <v/>
+      </c>
+      <c r="I23" s="15" t="n">
+        <v/>
       </c>
       <c r="J23" s="17" t="inlineStr">
         <is>
-          <t>네이버뉴스 헤드라인 언급 / 네이버뉴스 기사 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
+          <t>네이버뉴스 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급</t>
         </is>
       </c>
       <c r="K23" s="17" t="inlineStr">
@@ -1342,7 +1344,7 @@
     <row r="24" ht="18" customHeight="1">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B24" s="15" t="n">
@@ -1350,14 +1352,14 @@
       </c>
       <c r="C24" s="16" t="inlineStr">
         <is>
-          <t>넥써쓰</t>
+          <t>대한항공</t>
         </is>
       </c>
       <c r="D24" s="15" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E24" s="15" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F24" s="15" t="n">
         <v>0</v>
@@ -1366,26 +1368,24 @@
         <v>0</v>
       </c>
       <c r="H24" s="19" t="n">
-        <v>-27.47</v>
-      </c>
-      <c r="I24" s="19" t="n">
-        <v>-4.83</v>
+        <v>-3.12</v>
+      </c>
+      <c r="I24" s="18" t="n">
+        <v>5.08</v>
       </c>
       <c r="J24" s="17" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +102% / 중요공시 3건 / 매일경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K24" s="17" t="inlineStr">
-        <is>
-          <t>네이버, 공시</t>
-        </is>
+          <t>매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K24" s="17" t="n">
+        <v/>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
       <c r="A25" s="15" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B25" s="15" t="n">
@@ -1393,14 +1393,14 @@
       </c>
       <c r="C25" s="16" t="inlineStr">
         <is>
-          <t>로봇</t>
+          <t>삼성E&amp;A</t>
         </is>
       </c>
       <c r="D25" s="15" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E25" s="15" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F25" s="15" t="n">
         <v>0</v>
@@ -1408,27 +1408,27 @@
       <c r="G25" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="H25" s="15" t="n">
-        <v/>
-      </c>
-      <c r="I25" s="15" t="n">
-        <v/>
+      <c r="H25" s="19" t="n">
+        <v>-2.11</v>
+      </c>
+      <c r="I25" s="18" t="n">
+        <v>2.21</v>
       </c>
       <c r="J25" s="17" t="inlineStr">
         <is>
-          <t>매일경제 기사 언급 / 매일경제 헤드라인 언급 / 네이버뉴스 헤드라인 언급 / 매일경제 헤드라인 언급</t>
+          <t>네이버 검색 당일 +91% / Google 급상승 검색어 등장 (KR)</t>
         </is>
       </c>
       <c r="K25" s="17" t="inlineStr">
         <is>
-          <t>네이버</t>
+          <t>Google, 네이버</t>
         </is>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
       <c r="A26" s="15" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B26" s="15" t="n">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="C26" s="16" t="inlineStr">
         <is>
-          <t>셀트리온</t>
+          <t>LG전자</t>
         </is>
       </c>
       <c r="D26" s="15" t="n">
@@ -1452,26 +1452,24 @@
         <v>0</v>
       </c>
       <c r="H26" s="19" t="n">
-        <v>-1.9</v>
+        <v>-7.44</v>
       </c>
       <c r="I26" s="19" t="n">
-        <v>-1.56</v>
+        <v>-6.21</v>
       </c>
       <c r="J26" s="17" t="inlineStr">
         <is>
-          <t>중요공시 2건 / Google 급상승 검색어 등장 (KR) / 네이버뉴스 기사 언급</t>
-        </is>
-      </c>
-      <c r="K26" s="17" t="inlineStr">
-        <is>
-          <t>네이버, 공시, Google</t>
-        </is>
+          <t>한국경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 기사 언급</t>
+        </is>
+      </c>
+      <c r="K26" s="17" t="n">
+        <v/>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
       <c r="A27" s="15" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B27" s="15" t="n">
@@ -1479,7 +1477,7 @@
       </c>
       <c r="C27" s="16" t="inlineStr">
         <is>
-          <t>현대로템</t>
+          <t>제약</t>
         </is>
       </c>
       <c r="D27" s="15" t="n">
@@ -1494,27 +1492,27 @@
       <c r="G27" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="H27" s="19" t="n">
-        <v>-2.13</v>
-      </c>
-      <c r="I27" s="19" t="n">
-        <v>-0.72</v>
+      <c r="H27" s="15" t="n">
+        <v/>
+      </c>
+      <c r="I27" s="15" t="n">
+        <v/>
       </c>
       <c r="J27" s="17" t="inlineStr">
         <is>
-          <t>중요공시 1건 / 매일경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
+          <t>네이버뉴스 헤드라인 언급 / 네이버뉴스 헤드라인 언급 / 네이버뉴스 기사 언급</t>
         </is>
       </c>
       <c r="K27" s="17" t="inlineStr">
         <is>
-          <t>공시</t>
+          <t>네이버</t>
         </is>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
       <c r="A28" s="20" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B28" s="20" t="n">
@@ -1522,7 +1520,7 @@
       </c>
       <c r="C28" s="21" t="inlineStr">
         <is>
-          <t>보해양조</t>
+          <t>넥써쓰</t>
         </is>
       </c>
       <c r="D28" s="20" t="n">
@@ -1538,26 +1536,26 @@
         <v>0</v>
       </c>
       <c r="H28" s="22" t="n">
-        <v>29.88</v>
+        <v>-27.47</v>
       </c>
       <c r="I28" s="22" t="n">
-        <v>58.36</v>
+        <v>-4.83</v>
       </c>
       <c r="J28" s="23" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +186% / 매일경제 헤드라인 언급</t>
+          <t>네이버 검색 당일 +113% / 중요공시 3건</t>
         </is>
       </c>
       <c r="K28" s="23" t="inlineStr">
         <is>
-          <t>네이버</t>
+          <t>네이버, 공시</t>
         </is>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
       <c r="A29" s="20" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B29" s="20" t="n">
@@ -1565,7 +1563,7 @@
       </c>
       <c r="C29" s="21" t="inlineStr">
         <is>
-          <t>한화</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="D29" s="20" t="n">
@@ -1580,15 +1578,15 @@
       <c r="G29" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H29" s="24" t="n">
-        <v>-4.71</v>
-      </c>
-      <c r="I29" s="24" t="n">
-        <v>-0.95</v>
+      <c r="H29" s="22" t="n">
+        <v>-26.16</v>
+      </c>
+      <c r="I29" s="22" t="n">
+        <v>-19.9</v>
       </c>
       <c r="J29" s="23" t="inlineStr">
         <is>
-          <t>네이버뉴스 헤드라인 언급 / 매일경제 헤드라인 언급</t>
+          <t>네이버 검색 당일 +112% / 한국경제 헤드라인 언급</t>
         </is>
       </c>
       <c r="K29" s="23" t="inlineStr">
@@ -1600,7 +1598,7 @@
     <row r="30" ht="18" customHeight="1">
       <c r="A30" s="20" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B30" s="20" t="n">
@@ -1608,42 +1606,42 @@
       </c>
       <c r="C30" s="21" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>한솔테크닉스</t>
         </is>
       </c>
       <c r="D30" s="20" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E30" s="20" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F30" s="20" t="n">
         <v>0</v>
       </c>
       <c r="G30" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H30" s="24" t="n">
-        <v>-26.16</v>
+        <v>3</v>
+      </c>
+      <c r="H30" s="22" t="n">
+        <v>-4.87</v>
       </c>
       <c r="I30" s="24" t="n">
-        <v>-19.9</v>
+        <v>7.83</v>
       </c>
       <c r="J30" s="23" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +100% / 매일경제 헤드라인 언급</t>
+          <t>네이버 검색 당일 +81% / 중요공시 2건 / 중요공시 7일 +100%</t>
         </is>
       </c>
       <c r="K30" s="23" t="inlineStr">
         <is>
-          <t>네이버</t>
+          <t>네이버, 공시</t>
         </is>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
       <c r="A31" s="20" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B31" s="20" t="n">
@@ -1651,42 +1649,42 @@
       </c>
       <c r="C31" s="21" t="inlineStr">
         <is>
-          <t>한화오션</t>
+          <t>HJ중공업</t>
         </is>
       </c>
       <c r="D31" s="20" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E31" s="20" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F31" s="20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G31" s="20" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H31" s="22" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="I31" s="22" t="n">
-        <v>13.93</v>
+        <v>-3.67</v>
+      </c>
+      <c r="I31" s="24" t="n">
+        <v>3.24</v>
       </c>
       <c r="J31" s="23" t="inlineStr">
         <is>
-          <t>중요공시 1건 / 네이버뉴스 헤드라인 언급</t>
+          <t>중요공시 2건 / 중요공시 3일 +100% / 중요공시 7일 +100%</t>
         </is>
       </c>
       <c r="K31" s="23" t="inlineStr">
         <is>
-          <t>네이버, 공시</t>
+          <t>공시</t>
         </is>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
       <c r="A32" s="20" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B32" s="20" t="n">
@@ -1694,14 +1692,14 @@
       </c>
       <c r="C32" s="21" t="inlineStr">
         <is>
-          <t>미래에셋증권</t>
+          <t>삼성바이오로직스</t>
         </is>
       </c>
       <c r="D32" s="20" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E32" s="20" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F32" s="20" t="n">
         <v>0</v>
@@ -1709,27 +1707,27 @@
       <c r="G32" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H32" s="24" t="n">
-        <v>-3.85</v>
+      <c r="H32" s="22" t="n">
+        <v>-3.92</v>
       </c>
       <c r="I32" s="24" t="n">
-        <v>-6.79</v>
+        <v>6.1</v>
       </c>
       <c r="J32" s="23" t="inlineStr">
         <is>
-          <t>중요공시 2건 / 매일경제 헤드라인 언급 / 매일경제 기사 언급</t>
+          <t>중요공시 1건 / Google 급상승 검색어 등장 (KR)</t>
         </is>
       </c>
       <c r="K32" s="23" t="inlineStr">
         <is>
-          <t>공시</t>
+          <t>Google, 공시</t>
         </is>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
       <c r="A33" s="20" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B33" s="20" t="n">
@@ -1737,42 +1735,42 @@
       </c>
       <c r="C33" s="21" t="inlineStr">
         <is>
-          <t>진원생명과학</t>
+          <t>삼성전자우</t>
         </is>
       </c>
       <c r="D33" s="20" t="n">
         <v>5</v>
       </c>
       <c r="E33" s="20" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F33" s="20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G33" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H33" s="24" t="n">
-        <v>-17.67</v>
+      <c r="H33" s="22" t="n">
+        <v>-2.84</v>
       </c>
       <c r="I33" s="24" t="n">
-        <v>-24.4</v>
+        <v>7.25</v>
       </c>
       <c r="J33" s="23" t="inlineStr">
         <is>
-          <t>중요공시 3건 / 중요공시 3일 +50%</t>
+          <t>Google 급상승 검색어 등장 (KR)</t>
         </is>
       </c>
       <c r="K33" s="23" t="inlineStr">
         <is>
-          <t>공시</t>
+          <t>Google</t>
         </is>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
       <c r="A34" s="20" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B34" s="20" t="n">
@@ -1780,7 +1778,7 @@
       </c>
       <c r="C34" s="21" t="inlineStr">
         <is>
-          <t>제약</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="D34" s="20" t="n">
@@ -1795,27 +1793,27 @@
       <c r="G34" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H34" s="20" t="n">
-        <v/>
-      </c>
-      <c r="I34" s="20" t="n">
-        <v/>
+      <c r="H34" s="22" t="n">
+        <v>-0.54</v>
+      </c>
+      <c r="I34" s="24" t="n">
+        <v>2.42</v>
       </c>
       <c r="J34" s="23" t="inlineStr">
         <is>
-          <t>네이버뉴스 기사 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 기사 언급</t>
+          <t>Google 급상승 검색어 등장 (KR)</t>
         </is>
       </c>
       <c r="K34" s="23" t="inlineStr">
         <is>
-          <t>네이버</t>
+          <t>Google</t>
         </is>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
       <c r="A35" s="20" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B35" s="20" t="n">
@@ -1823,40 +1821,42 @@
       </c>
       <c r="C35" s="21" t="inlineStr">
         <is>
-          <t>KT</t>
+          <t>진원생명과학</t>
         </is>
       </c>
       <c r="D35" s="20" t="n">
         <v>5</v>
       </c>
       <c r="E35" s="20" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F35" s="20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G35" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H35" s="24" t="n">
-        <v>-0.37</v>
-      </c>
-      <c r="I35" s="24" t="n">
-        <v>-2.74</v>
+      <c r="H35" s="22" t="n">
+        <v>-17.67</v>
+      </c>
+      <c r="I35" s="22" t="n">
+        <v>-24.4</v>
       </c>
       <c r="J35" s="23" t="inlineStr">
         <is>
-          <t>매일경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K35" s="23" t="n">
-        <v/>
+          <t>중요공시 3건 / 중요공시 3일 +50%</t>
+        </is>
+      </c>
+      <c r="K35" s="23" t="inlineStr">
+        <is>
+          <t>공시</t>
+        </is>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
       <c r="A36" s="20" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B36" s="20" t="n">
@@ -1864,14 +1864,14 @@
       </c>
       <c r="C36" s="21" t="inlineStr">
         <is>
-          <t>남화토건</t>
+          <t>삼성전기</t>
         </is>
       </c>
       <c r="D36" s="20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E36" s="20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F36" s="20" t="n">
         <v>0</v>
@@ -1879,27 +1879,27 @@
       <c r="G36" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H36" s="22" t="n">
-        <v>12.73</v>
-      </c>
-      <c r="I36" s="22" t="n">
-        <v>45.92</v>
+      <c r="H36" s="24" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="I36" s="24" t="n">
+        <v>32.44</v>
       </c>
       <c r="J36" s="23" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +819% / 중요공시 1건</t>
+          <t>Google 급상승 검색어 등장 (KR)</t>
         </is>
       </c>
       <c r="K36" s="23" t="inlineStr">
         <is>
-          <t>네이버, 공시</t>
+          <t>Google</t>
         </is>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
       <c r="A37" s="20" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B37" s="20" t="n">
@@ -1907,14 +1907,14 @@
       </c>
       <c r="C37" s="21" t="inlineStr">
         <is>
-          <t>씨피시스템</t>
+          <t>삼성물산</t>
         </is>
       </c>
       <c r="D37" s="20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E37" s="20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F37" s="20" t="n">
         <v>0</v>
@@ -1922,27 +1922,27 @@
       <c r="G37" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H37" s="22" t="n">
-        <v>29.88</v>
-      </c>
-      <c r="I37" s="22" t="n">
-        <v>20.79</v>
+      <c r="H37" s="24" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="I37" s="24" t="n">
+        <v>13.77</v>
       </c>
       <c r="J37" s="23" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +73% / 한국경제 헤드라인 언급</t>
+          <t>Google 급상승 검색어 등장 (KR)</t>
         </is>
       </c>
       <c r="K37" s="23" t="inlineStr">
         <is>
-          <t>네이버</t>
+          <t>Google</t>
         </is>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
       <c r="A38" s="20" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B38" s="20" t="n">
@@ -1950,14 +1950,14 @@
       </c>
       <c r="C38" s="21" t="inlineStr">
         <is>
-          <t>LG전자</t>
+          <t>삼성SDI</t>
         </is>
       </c>
       <c r="D38" s="20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E38" s="20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F38" s="20" t="n">
         <v>0</v>
@@ -1966,24 +1966,26 @@
         <v>0</v>
       </c>
       <c r="H38" s="24" t="n">
-        <v>-7.44</v>
+        <v>6.32</v>
       </c>
       <c r="I38" s="24" t="n">
-        <v>-6.21</v>
+        <v>2.97</v>
       </c>
       <c r="J38" s="23" t="inlineStr">
         <is>
-          <t>매일경제 헤드라인 언급 / 매일경제 기사 언급</t>
-        </is>
-      </c>
-      <c r="K38" s="23" t="n">
-        <v/>
+          <t>Google 급상승 검색어 등장 (KR)</t>
+        </is>
+      </c>
+      <c r="K38" s="23" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
       <c r="A39" s="20" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B39" s="20" t="n">
@@ -1991,42 +1993,42 @@
       </c>
       <c r="C39" s="21" t="inlineStr">
         <is>
-          <t>HJ중공업</t>
+          <t>삼성제약</t>
         </is>
       </c>
       <c r="D39" s="20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E39" s="20" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F39" s="20" t="n">
         <v>0</v>
       </c>
       <c r="G39" s="20" t="n">
-        <v>3</v>
-      </c>
-      <c r="H39" s="24" t="n">
-        <v>-3.67</v>
-      </c>
-      <c r="I39" s="22" t="n">
-        <v>3.24</v>
+        <v>0</v>
+      </c>
+      <c r="H39" s="22" t="n">
+        <v>-3.9</v>
+      </c>
+      <c r="I39" s="24" t="n">
+        <v>3.92</v>
       </c>
       <c r="J39" s="23" t="inlineStr">
         <is>
-          <t>중요공시 2건 / 중요공시 7일 +100%</t>
+          <t>Google 급상승 검색어 등장 (KR)</t>
         </is>
       </c>
       <c r="K39" s="23" t="inlineStr">
         <is>
-          <t>공시</t>
+          <t>Google</t>
         </is>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
       <c r="A40" s="20" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B40" s="20" t="n">
@@ -2034,14 +2036,14 @@
       </c>
       <c r="C40" s="21" t="inlineStr">
         <is>
-          <t>HD현대중공업</t>
+          <t>삼성생명</t>
         </is>
       </c>
       <c r="D40" s="20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E40" s="20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F40" s="20" t="n">
         <v>0</v>
@@ -2050,26 +2052,26 @@
         <v>0</v>
       </c>
       <c r="H40" s="24" t="n">
-        <v>-2.49</v>
-      </c>
-      <c r="I40" s="22" t="n">
-        <v>2.62</v>
+        <v>5.97</v>
+      </c>
+      <c r="I40" s="24" t="n">
+        <v>28.92</v>
       </c>
       <c r="J40" s="23" t="inlineStr">
         <is>
-          <t>중요공시 1건 / 한국경제 헤드라인 언급</t>
+          <t>Google 급상승 검색어 등장 (KR)</t>
         </is>
       </c>
       <c r="K40" s="23" t="inlineStr">
         <is>
-          <t>공시</t>
+          <t>Google</t>
         </is>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
       <c r="A41" s="20" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B41" s="20" t="n">
@@ -2077,14 +2079,14 @@
       </c>
       <c r="C41" s="21" t="inlineStr">
         <is>
-          <t>방산</t>
+          <t>삼성증권</t>
         </is>
       </c>
       <c r="D41" s="20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E41" s="20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F41" s="20" t="n">
         <v>0</v>
@@ -2092,27 +2094,27 @@
       <c r="G41" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H41" s="20" t="n">
-        <v/>
-      </c>
-      <c r="I41" s="20" t="n">
-        <v/>
+      <c r="H41" s="22" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="I41" s="24" t="n">
+        <v>0.08</v>
       </c>
       <c r="J41" s="23" t="inlineStr">
         <is>
-          <t>네이버뉴스 기사 언급 / 한국경제 헤드라인 언급</t>
+          <t>Google 급상승 검색어 등장 (KR)</t>
         </is>
       </c>
       <c r="K41" s="23" t="inlineStr">
         <is>
-          <t>네이버</t>
+          <t>Google</t>
         </is>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
       <c r="A42" s="20" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B42" s="20" t="n">
@@ -2120,14 +2122,14 @@
       </c>
       <c r="C42" s="21" t="inlineStr">
         <is>
-          <t>전기차</t>
+          <t>삼성에스디에스</t>
         </is>
       </c>
       <c r="D42" s="20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E42" s="20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F42" s="20" t="n">
         <v>0</v>
@@ -2135,27 +2137,27 @@
       <c r="G42" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H42" s="20" t="n">
-        <v/>
-      </c>
-      <c r="I42" s="20" t="n">
-        <v/>
+      <c r="H42" s="22" t="n">
+        <v>-4.07</v>
+      </c>
+      <c r="I42" s="22" t="n">
+        <v>-10.55</v>
       </c>
       <c r="J42" s="23" t="inlineStr">
         <is>
-          <t>네이버뉴스 기사 언급 / 매일경제 헤드라인 언급</t>
+          <t>Google 급상승 검색어 등장 (KR)</t>
         </is>
       </c>
       <c r="K42" s="23" t="inlineStr">
         <is>
-          <t>네이버</t>
+          <t>Google</t>
         </is>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1">
       <c r="A43" s="20" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B43" s="20" t="n">
@@ -2163,14 +2165,14 @@
       </c>
       <c r="C43" s="21" t="inlineStr">
         <is>
-          <t>태양광</t>
+          <t>한화</t>
         </is>
       </c>
       <c r="D43" s="20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E43" s="20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F43" s="20" t="n">
         <v>0</v>
@@ -2178,15 +2180,15 @@
       <c r="G43" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H43" s="20" t="n">
-        <v/>
-      </c>
-      <c r="I43" s="20" t="n">
-        <v/>
+      <c r="H43" s="22" t="n">
+        <v>-4.71</v>
+      </c>
+      <c r="I43" s="22" t="n">
+        <v>-0.95</v>
       </c>
       <c r="J43" s="23" t="inlineStr">
         <is>
-          <t>매일경제 헤드라인 언급 / 매일경제 기사 언급</t>
+          <t>매일경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
         </is>
       </c>
       <c r="K43" s="23" t="n">
@@ -2196,7 +2198,7 @@
     <row r="44" ht="18" customHeight="1">
       <c r="A44" s="20" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B44" s="20" t="n">
@@ -2204,7 +2206,7 @@
       </c>
       <c r="C44" s="21" t="inlineStr">
         <is>
-          <t>HD현대</t>
+          <t>남화토건</t>
         </is>
       </c>
       <c r="D44" s="20" t="n">
@@ -2220,282 +2222,278 @@
         <v>0</v>
       </c>
       <c r="H44" s="24" t="n">
-        <v>-3.35</v>
+        <v>12.73</v>
       </c>
       <c r="I44" s="24" t="n">
-        <v>-5.53</v>
+        <v>45.92</v>
       </c>
       <c r="J44" s="23" t="inlineStr">
         <is>
-          <t>매일경제 기사 언급 / 한국경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K44" s="23" t="n">
+          <t>네이버 검색 당일 +921% / 중요공시 1건</t>
+        </is>
+      </c>
+      <c r="K44" s="23" t="inlineStr">
+        <is>
+          <t>네이버, 공시</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="18" customHeight="1">
+      <c r="A45" s="20" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="B45" s="20" t="n">
+        <v>32</v>
+      </c>
+      <c r="C45" s="21" t="inlineStr">
+        <is>
+          <t>HMM</t>
+        </is>
+      </c>
+      <c r="D45" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="E45" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="F45" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G45" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" s="22" t="n">
+        <v>-1.47</v>
+      </c>
+      <c r="I45" s="24" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J45" s="23" t="inlineStr">
+        <is>
+          <t>매일경제 기사 언급 / 매일경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K45" s="23" t="n">
         <v/>
       </c>
     </row>
-    <row r="45" ht="18" customHeight="1">
-      <c r="A45" s="25" t="inlineStr">
-        <is>
-          <t>2026-06-21</t>
-        </is>
-      </c>
-      <c r="B45" s="25" t="n">
-        <v>32</v>
-      </c>
-      <c r="C45" s="26" t="inlineStr">
-        <is>
-          <t>JW신약</t>
-        </is>
-      </c>
-      <c r="D45" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="E45" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="F45" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="G45" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="H45" s="27" t="n">
-        <v>13.08</v>
-      </c>
-      <c r="I45" s="27" t="n">
-        <v>70.94</v>
-      </c>
-      <c r="J45" s="28" t="inlineStr">
-        <is>
-          <t>네이버 검색 당일 +1348%</t>
-        </is>
-      </c>
-      <c r="K45" s="28" t="inlineStr">
-        <is>
-          <t>네이버</t>
-        </is>
-      </c>
-    </row>
     <row r="46" ht="18" customHeight="1">
-      <c r="A46" s="25" t="inlineStr">
-        <is>
-          <t>2026-06-21</t>
-        </is>
-      </c>
-      <c r="B46" s="25" t="n">
+      <c r="A46" s="20" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="B46" s="20" t="n">
         <v>33</v>
       </c>
-      <c r="C46" s="26" t="inlineStr">
-        <is>
-          <t>강동씨앤엘</t>
-        </is>
-      </c>
-      <c r="D46" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="E46" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="F46" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="G46" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="H46" s="27" t="n">
-        <v>29.91</v>
-      </c>
-      <c r="I46" s="27" t="n">
-        <v>121.56</v>
-      </c>
-      <c r="J46" s="28" t="inlineStr">
-        <is>
-          <t>네이버 검색 당일 +1305%</t>
-        </is>
-      </c>
-      <c r="K46" s="28" t="inlineStr">
-        <is>
-          <t>네이버</t>
+      <c r="C46" s="21" t="inlineStr">
+        <is>
+          <t>센서뷰</t>
+        </is>
+      </c>
+      <c r="D46" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="E46" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="F46" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G46" s="20" t="n">
+        <v>3</v>
+      </c>
+      <c r="H46" s="22" t="n">
+        <v>-5.11</v>
+      </c>
+      <c r="I46" s="22" t="n">
+        <v>-12.29</v>
+      </c>
+      <c r="J46" s="23" t="inlineStr">
+        <is>
+          <t>중요공시 2건 / 중요공시 7일 +100%</t>
+        </is>
+      </c>
+      <c r="K46" s="23" t="inlineStr">
+        <is>
+          <t>공시</t>
         </is>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
-      <c r="A47" s="25" t="inlineStr">
-        <is>
-          <t>2026-06-21</t>
-        </is>
-      </c>
-      <c r="B47" s="25" t="n">
+      <c r="A47" s="20" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="B47" s="20" t="n">
         <v>34</v>
       </c>
-      <c r="C47" s="26" t="inlineStr">
-        <is>
-          <t>삼익제약</t>
-        </is>
-      </c>
-      <c r="D47" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="E47" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="F47" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="G47" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="H47" s="27" t="n">
-        <v>29.98</v>
-      </c>
-      <c r="I47" s="27" t="n">
-        <v>41.82</v>
-      </c>
-      <c r="J47" s="28" t="inlineStr">
-        <is>
-          <t>네이버 검색 당일 +720%</t>
-        </is>
-      </c>
-      <c r="K47" s="28" t="inlineStr">
-        <is>
-          <t>네이버</t>
+      <c r="C47" s="21" t="inlineStr">
+        <is>
+          <t>파두</t>
+        </is>
+      </c>
+      <c r="D47" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="E47" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="F47" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G47" s="20" t="n">
+        <v>3</v>
+      </c>
+      <c r="H47" s="22" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="I47" s="24" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J47" s="23" t="inlineStr">
+        <is>
+          <t>중요공시 2건 / 중요공시 7일 +100%</t>
+        </is>
+      </c>
+      <c r="K47" s="23" t="inlineStr">
+        <is>
+          <t>공시</t>
         </is>
       </c>
     </row>
     <row r="48" ht="18" customHeight="1">
-      <c r="A48" s="25" t="inlineStr">
-        <is>
-          <t>2026-06-21</t>
-        </is>
-      </c>
-      <c r="B48" s="25" t="n">
+      <c r="A48" s="20" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="B48" s="20" t="n">
         <v>35</v>
       </c>
-      <c r="C48" s="26" t="inlineStr">
-        <is>
-          <t>현대약품</t>
-        </is>
-      </c>
-      <c r="D48" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="E48" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="F48" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="G48" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="H48" s="29" t="n">
-        <v>-4.12</v>
-      </c>
-      <c r="I48" s="27" t="n">
-        <v>42.23</v>
-      </c>
-      <c r="J48" s="28" t="inlineStr">
-        <is>
-          <t>네이버 검색 당일 +416%</t>
-        </is>
-      </c>
-      <c r="K48" s="28" t="inlineStr">
-        <is>
-          <t>네이버</t>
+      <c r="C48" s="21" t="inlineStr">
+        <is>
+          <t>현대로템</t>
+        </is>
+      </c>
+      <c r="D48" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="E48" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="F48" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G48" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H48" s="22" t="n">
+        <v>-2.13</v>
+      </c>
+      <c r="I48" s="22" t="n">
+        <v>-0.72</v>
+      </c>
+      <c r="J48" s="23" t="inlineStr">
+        <is>
+          <t>중요공시 1건 / 매일경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K48" s="23" t="inlineStr">
+        <is>
+          <t>공시</t>
         </is>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1">
-      <c r="A49" s="25" t="inlineStr">
-        <is>
-          <t>2026-06-21</t>
-        </is>
-      </c>
-      <c r="B49" s="25" t="n">
+      <c r="A49" s="20" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="B49" s="20" t="n">
         <v>36</v>
       </c>
-      <c r="C49" s="26" t="inlineStr">
-        <is>
-          <t>위더스제약</t>
-        </is>
-      </c>
-      <c r="D49" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="E49" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="F49" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="G49" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="H49" s="27" t="n">
-        <v>13.59</v>
-      </c>
-      <c r="I49" s="27" t="n">
-        <v>33.03</v>
-      </c>
-      <c r="J49" s="28" t="inlineStr">
-        <is>
-          <t>네이버 검색 당일 +394%</t>
-        </is>
-      </c>
-      <c r="K49" s="28" t="inlineStr">
-        <is>
-          <t>네이버</t>
-        </is>
+      <c r="C49" s="21" t="inlineStr">
+        <is>
+          <t>태양광</t>
+        </is>
+      </c>
+      <c r="D49" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="E49" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="F49" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G49" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H49" s="20" t="n">
+        <v/>
+      </c>
+      <c r="I49" s="20" t="n">
+        <v/>
+      </c>
+      <c r="J49" s="23" t="inlineStr">
+        <is>
+          <t>매일경제 헤드라인 언급 / 매일경제 기사 언급</t>
+        </is>
+      </c>
+      <c r="K49" s="23" t="n">
+        <v/>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
-      <c r="A50" s="25" t="inlineStr">
-        <is>
-          <t>2026-06-21</t>
-        </is>
-      </c>
-      <c r="B50" s="25" t="n">
+      <c r="A50" s="20" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="B50" s="20" t="n">
         <v>37</v>
       </c>
-      <c r="C50" s="26" t="inlineStr">
-        <is>
-          <t>삼화전자</t>
-        </is>
-      </c>
-      <c r="D50" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="E50" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="F50" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="G50" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="H50" s="27" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="I50" s="27" t="n">
-        <v>73.59</v>
-      </c>
-      <c r="J50" s="28" t="inlineStr">
-        <is>
-          <t>네이버 검색 당일 +391%</t>
-        </is>
-      </c>
-      <c r="K50" s="28" t="inlineStr">
-        <is>
-          <t>네이버</t>
-        </is>
+      <c r="C50" s="21" t="inlineStr">
+        <is>
+          <t>DB</t>
+        </is>
+      </c>
+      <c r="D50" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="E50" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="F50" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G50" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H50" s="22" t="n">
+        <v>-2.39</v>
+      </c>
+      <c r="I50" s="22" t="n">
+        <v>-6.55</v>
+      </c>
+      <c r="J50" s="23" t="inlineStr">
+        <is>
+          <t>매일경제 헤드라인 언급 / 매일경제 기사 언급</t>
+        </is>
+      </c>
+      <c r="K50" s="23" t="n">
+        <v/>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
       <c r="A51" s="25" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B51" s="25" t="n">
@@ -2503,7 +2501,7 @@
       </c>
       <c r="C51" s="26" t="inlineStr">
         <is>
-          <t>율촌</t>
+          <t>강동씨앤엘</t>
         </is>
       </c>
       <c r="D51" s="25" t="n">
@@ -2518,15 +2516,15 @@
       <c r="G51" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H51" s="29" t="n">
-        <v>-13.55</v>
+      <c r="H51" s="27" t="n">
+        <v>29.91</v>
       </c>
       <c r="I51" s="27" t="n">
-        <v>30.73</v>
+        <v>121.56</v>
       </c>
       <c r="J51" s="28" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +196%</t>
+          <t>네이버 검색 당일 +1463%</t>
         </is>
       </c>
       <c r="K51" s="28" t="inlineStr">
@@ -2538,7 +2536,7 @@
     <row r="52" ht="18" customHeight="1">
       <c r="A52" s="25" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B52" s="25" t="n">
@@ -2546,7 +2544,7 @@
       </c>
       <c r="C52" s="26" t="inlineStr">
         <is>
-          <t>성문전자</t>
+          <t>JW신약</t>
         </is>
       </c>
       <c r="D52" s="25" t="n">
@@ -2562,14 +2560,14 @@
         <v>0</v>
       </c>
       <c r="H52" s="27" t="n">
-        <v>4.43</v>
+        <v>13.08</v>
       </c>
       <c r="I52" s="27" t="n">
-        <v>40.24</v>
+        <v>70.94</v>
       </c>
       <c r="J52" s="28" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +175%</t>
+          <t>네이버 검색 당일 +1428%</t>
         </is>
       </c>
       <c r="K52" s="28" t="inlineStr">
@@ -2581,7 +2579,7 @@
     <row r="53" ht="18" customHeight="1">
       <c r="A53" s="25" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B53" s="25" t="n">
@@ -2589,7 +2587,7 @@
       </c>
       <c r="C53" s="26" t="inlineStr">
         <is>
-          <t>티웨이홀딩스</t>
+          <t>삼익제약</t>
         </is>
       </c>
       <c r="D53" s="25" t="n">
@@ -2604,15 +2602,15 @@
       <c r="G53" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H53" s="29" t="n">
-        <v>-7.09</v>
+      <c r="H53" s="27" t="n">
+        <v>29.98</v>
       </c>
       <c r="I53" s="27" t="n">
-        <v>26.88</v>
+        <v>41.82</v>
       </c>
       <c r="J53" s="28" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +174%</t>
+          <t>네이버 검색 당일 +800%</t>
         </is>
       </c>
       <c r="K53" s="28" t="inlineStr">
@@ -2624,7 +2622,7 @@
     <row r="54" ht="18" customHeight="1">
       <c r="A54" s="25" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B54" s="25" t="n">
@@ -2632,7 +2630,7 @@
       </c>
       <c r="C54" s="26" t="inlineStr">
         <is>
-          <t>메리츠제2호스팩</t>
+          <t>현대약품</t>
         </is>
       </c>
       <c r="D54" s="25" t="n">
@@ -2647,15 +2645,15 @@
       <c r="G54" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H54" s="25" t="n">
-        <v/>
-      </c>
-      <c r="I54" s="25" t="n">
-        <v/>
+      <c r="H54" s="29" t="n">
+        <v>-4.12</v>
+      </c>
+      <c r="I54" s="27" t="n">
+        <v>42.23</v>
       </c>
       <c r="J54" s="28" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +172%</t>
+          <t>네이버 검색 당일 +429%</t>
         </is>
       </c>
       <c r="K54" s="28" t="inlineStr">
@@ -2667,7 +2665,7 @@
     <row r="55" ht="18" customHeight="1">
       <c r="A55" s="25" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B55" s="25" t="n">
@@ -2675,7 +2673,7 @@
       </c>
       <c r="C55" s="26" t="inlineStr">
         <is>
-          <t>부국철강</t>
+          <t>위더스제약</t>
         </is>
       </c>
       <c r="D55" s="25" t="n">
@@ -2690,15 +2688,15 @@
       <c r="G55" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H55" s="29" t="n">
-        <v>-13.76</v>
+      <c r="H55" s="27" t="n">
+        <v>13.59</v>
       </c>
       <c r="I55" s="27" t="n">
-        <v>3.49</v>
+        <v>33.03</v>
       </c>
       <c r="J55" s="28" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +160%</t>
+          <t>네이버 검색 당일 +422%</t>
         </is>
       </c>
       <c r="K55" s="28" t="inlineStr">
@@ -2710,7 +2708,7 @@
     <row r="56" ht="18" customHeight="1">
       <c r="A56" s="25" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B56" s="25" t="n">
@@ -2718,7 +2716,7 @@
       </c>
       <c r="C56" s="26" t="inlineStr">
         <is>
-          <t>피앤에스로보틱스</t>
+          <t>삼화전자</t>
         </is>
       </c>
       <c r="D56" s="25" t="n">
@@ -2734,14 +2732,14 @@
         <v>0</v>
       </c>
       <c r="H56" s="27" t="n">
-        <v>22.04</v>
+        <v>2.81</v>
       </c>
       <c r="I56" s="27" t="n">
-        <v>20.74</v>
+        <v>73.59</v>
       </c>
       <c r="J56" s="28" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +151%</t>
+          <t>네이버 검색 당일 +412%</t>
         </is>
       </c>
       <c r="K56" s="28" t="inlineStr">
@@ -2753,7 +2751,7 @@
     <row r="57" ht="18" customHeight="1">
       <c r="A57" s="25" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B57" s="25" t="n">
@@ -2761,7 +2759,7 @@
       </c>
       <c r="C57" s="26" t="inlineStr">
         <is>
-          <t>동일스틸럭스</t>
+          <t>보해양조</t>
         </is>
       </c>
       <c r="D57" s="25" t="n">
@@ -2776,15 +2774,15 @@
       <c r="G57" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H57" s="29" t="n">
-        <v>-11.15</v>
+      <c r="H57" s="27" t="n">
+        <v>29.88</v>
       </c>
       <c r="I57" s="27" t="n">
-        <v>29.05</v>
+        <v>58.36</v>
       </c>
       <c r="J57" s="28" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +147%</t>
+          <t>네이버 검색 당일 +237%</t>
         </is>
       </c>
       <c r="K57" s="28" t="inlineStr">
@@ -2796,7 +2794,7 @@
     <row r="58" ht="18" customHeight="1">
       <c r="A58" s="25" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B58" s="25" t="n">
@@ -2804,7 +2802,7 @@
       </c>
       <c r="C58" s="26" t="inlineStr">
         <is>
-          <t>대원전선</t>
+          <t>율촌</t>
         </is>
       </c>
       <c r="D58" s="25" t="n">
@@ -2820,26 +2818,26 @@
         <v>0</v>
       </c>
       <c r="H58" s="29" t="n">
-        <v>-3.73</v>
+        <v>-13.55</v>
       </c>
       <c r="I58" s="27" t="n">
-        <v>6.02</v>
+        <v>30.73</v>
       </c>
       <c r="J58" s="28" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +95% / 중요공시 1건</t>
+          <t>네이버 검색 당일 +208%</t>
         </is>
       </c>
       <c r="K58" s="28" t="inlineStr">
         <is>
-          <t>네이버, 공시</t>
+          <t>네이버</t>
         </is>
       </c>
     </row>
     <row r="59" ht="18" customHeight="1">
       <c r="A59" s="25" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B59" s="25" t="n">
@@ -2847,7 +2845,7 @@
       </c>
       <c r="C59" s="26" t="inlineStr">
         <is>
-          <t>비엘팜텍</t>
+          <t>성문전자</t>
         </is>
       </c>
       <c r="D59" s="25" t="n">
@@ -2862,27 +2860,27 @@
       <c r="G59" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H59" s="29" t="n">
-        <v>-20.26</v>
+      <c r="H59" s="27" t="n">
+        <v>4.43</v>
       </c>
       <c r="I59" s="27" t="n">
-        <v>4.23</v>
+        <v>40.24</v>
       </c>
       <c r="J59" s="28" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +78% / 중요공시 1건</t>
+          <t>네이버 검색 당일 +187%</t>
         </is>
       </c>
       <c r="K59" s="28" t="inlineStr">
         <is>
-          <t>네이버, 공시</t>
+          <t>네이버</t>
         </is>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1">
       <c r="A60" s="25" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B60" s="25" t="n">
@@ -2890,7 +2888,7 @@
       </c>
       <c r="C60" s="26" t="inlineStr">
         <is>
-          <t>한솔테크닉스</t>
+          <t>메리츠제2호스팩</t>
         </is>
       </c>
       <c r="D60" s="25" t="n">
@@ -2905,27 +2903,27 @@
       <c r="G60" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H60" s="29" t="n">
-        <v>-4.87</v>
-      </c>
-      <c r="I60" s="27" t="n">
-        <v>7.83</v>
+      <c r="H60" s="25" t="n">
+        <v/>
+      </c>
+      <c r="I60" s="25" t="n">
+        <v/>
       </c>
       <c r="J60" s="28" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +76% / 중요공시 2건</t>
+          <t>네이버 검색 당일 +186%</t>
         </is>
       </c>
       <c r="K60" s="28" t="inlineStr">
         <is>
-          <t>네이버, 공시</t>
+          <t>네이버</t>
         </is>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
       <c r="A61" s="25" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B61" s="25" t="n">
@@ -2933,7 +2931,7 @@
       </c>
       <c r="C61" s="26" t="inlineStr">
         <is>
-          <t>삼보산업</t>
+          <t>피앤에스로보틱스</t>
         </is>
       </c>
       <c r="D61" s="25" t="n">
@@ -2949,26 +2947,26 @@
         <v>0</v>
       </c>
       <c r="H61" s="27" t="n">
-        <v>11.54</v>
+        <v>22.04</v>
       </c>
       <c r="I61" s="27" t="n">
-        <v>45.97</v>
+        <v>20.74</v>
       </c>
       <c r="J61" s="28" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +61% / 중요공시 1건</t>
+          <t>네이버 검색 당일 +182%</t>
         </is>
       </c>
       <c r="K61" s="28" t="inlineStr">
         <is>
-          <t>네이버, 공시</t>
+          <t>네이버</t>
         </is>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1">
       <c r="A62" s="25" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B62" s="25" t="n">
@@ -2976,7 +2974,7 @@
       </c>
       <c r="C62" s="26" t="inlineStr">
         <is>
-          <t>다스코</t>
+          <t>티웨이홀딩스</t>
         </is>
       </c>
       <c r="D62" s="25" t="n">
@@ -2991,27 +2989,27 @@
       <c r="G62" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H62" s="27" t="n">
-        <v>29.96</v>
+      <c r="H62" s="29" t="n">
+        <v>-7.09</v>
       </c>
       <c r="I62" s="27" t="n">
-        <v>31.44</v>
+        <v>26.88</v>
       </c>
       <c r="J62" s="28" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +59% / 중요공시 1건</t>
+          <t>네이버 검색 당일 +181%</t>
         </is>
       </c>
       <c r="K62" s="28" t="inlineStr">
         <is>
-          <t>네이버, 공시</t>
+          <t>네이버</t>
         </is>
       </c>
     </row>
     <row r="63" ht="18" customHeight="1">
       <c r="A63" s="25" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B63" s="25" t="n">
@@ -3019,7 +3017,7 @@
       </c>
       <c r="C63" s="26" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>부국철강</t>
         </is>
       </c>
       <c r="D63" s="25" t="n">
@@ -3035,19 +3033,19 @@
         <v>0</v>
       </c>
       <c r="H63" s="29" t="n">
-        <v>-7.41</v>
-      </c>
-      <c r="I63" s="29" t="n">
-        <v>-2.75</v>
+        <v>-13.76</v>
+      </c>
+      <c r="I63" s="27" t="n">
+        <v>3.49</v>
       </c>
       <c r="J63" s="28" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +58% / 중요공시 1건</t>
+          <t>네이버 검색 당일 +170%</t>
         </is>
       </c>
       <c r="K63" s="28" t="inlineStr">
         <is>
-          <t>네이버, 공시</t>
+          <t>네이버</t>
         </is>
       </c>
     </row>
@@ -3144,22 +3142,22 @@
         <v>1</v>
       </c>
       <c r="C3" s="25" t="n">
-        <v>60</v>
+        <v>82</v>
       </c>
       <c r="D3" s="25" t="n">
-        <v>60</v>
+        <v>82</v>
       </c>
       <c r="E3" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F3" s="25" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G3" s="25" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="H3" s="25" t="n"/>
@@ -3175,22 +3173,22 @@
         <v>1</v>
       </c>
       <c r="C4" s="25" t="n">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="D4" s="25" t="n">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="E4" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F4" s="25" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G4" s="25" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="H4" s="27" t="n">
@@ -3210,22 +3208,22 @@
         <v>1</v>
       </c>
       <c r="C5" s="25" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="D5" s="25" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="E5" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F5" s="25" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G5" s="25" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="H5" s="27" t="n">
@@ -3238,142 +3236,138 @@
     <row r="6" ht="18" customHeight="1">
       <c r="A6" s="26" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>LG</t>
         </is>
       </c>
       <c r="B6" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C6" s="25" t="n">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="D6" s="25" t="n">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="E6" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F6" s="25" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G6" s="25" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="H6" s="29" t="n">
-        <v>-2.34</v>
+        <v>-0.91</v>
       </c>
       <c r="I6" s="27" t="n">
-        <v>9.77</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
       <c r="A7" s="26" t="inlineStr">
         <is>
-          <t>현대차</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B7" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C7" s="25" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="D7" s="25" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="E7" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F7" s="25" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G7" s="25" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
-        </is>
-      </c>
-      <c r="H7" s="27" t="n">
-        <v>2</v>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="H7" s="29" t="n">
+        <v>-2.34</v>
       </c>
       <c r="I7" s="27" t="n">
-        <v>0.99</v>
+        <v>9.77</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="26" t="inlineStr">
         <is>
-          <t>대한항공</t>
+          <t>현대차</t>
         </is>
       </c>
       <c r="B8" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C8" s="25" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="D8" s="25" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E8" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F8" s="25" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G8" s="25" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
-        </is>
-      </c>
-      <c r="H8" s="29" t="n">
-        <v>-3.12</v>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="H8" s="27" t="n">
+        <v>2</v>
       </c>
       <c r="I8" s="27" t="n">
-        <v>5.08</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
       <c r="A9" s="26" t="inlineStr">
         <is>
-          <t>삼성전기</t>
+          <t>바이오</t>
         </is>
       </c>
       <c r="B9" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C9" s="25" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D9" s="25" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E9" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F9" s="25" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G9" s="25" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
-        </is>
-      </c>
-      <c r="H9" s="27" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="I9" s="27" t="n">
-        <v>32.44</v>
-      </c>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="H9" s="25" t="n"/>
+      <c r="I9" s="25" t="n"/>
     </row>
     <row r="10" ht="18" customHeight="1">
       <c r="A10" s="26" t="inlineStr">
@@ -3385,22 +3379,22 @@
         <v>1</v>
       </c>
       <c r="C10" s="25" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D10" s="25" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E10" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F10" s="25" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G10" s="25" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="H10" s="25" t="n"/>
@@ -3409,64 +3403,60 @@
     <row r="11" ht="18" customHeight="1">
       <c r="A11" s="26" t="inlineStr">
         <is>
-          <t>LG</t>
+          <t>로봇</t>
         </is>
       </c>
       <c r="B11" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C11" s="25" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D11" s="25" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E11" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F11" s="25" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G11" s="25" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
-        </is>
-      </c>
-      <c r="H11" s="29" t="n">
-        <v>-0.91</v>
-      </c>
-      <c r="I11" s="27" t="n">
-        <v>2.25</v>
-      </c>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="H11" s="25" t="n"/>
+      <c r="I11" s="25" t="n"/>
     </row>
     <row r="12" ht="18" customHeight="1">
       <c r="A12" s="26" t="inlineStr">
         <is>
-          <t>바이오</t>
+          <t>전기차</t>
         </is>
       </c>
       <c r="B12" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C12" s="25" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D12" s="25" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E12" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F12" s="25" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G12" s="25" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="H12" s="25" t="n"/>
@@ -3475,73 +3465,77 @@
     <row r="13" ht="18" customHeight="1">
       <c r="A13" s="26" t="inlineStr">
         <is>
-          <t>넥써쓰</t>
+          <t>대한항공</t>
         </is>
       </c>
       <c r="B13" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C13" s="25" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D13" s="25" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E13" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F13" s="25" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G13" s="25" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="H13" s="29" t="n">
-        <v>-27.47</v>
-      </c>
-      <c r="I13" s="29" t="n">
-        <v>-4.83</v>
+        <v>-3.12</v>
+      </c>
+      <c r="I13" s="27" t="n">
+        <v>5.08</v>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="26" t="inlineStr">
         <is>
-          <t>로봇</t>
+          <t>LG전자</t>
         </is>
       </c>
       <c r="B14" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C14" s="25" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D14" s="25" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E14" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F14" s="25" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G14" s="25" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
-        </is>
-      </c>
-      <c r="H14" s="25" t="n"/>
-      <c r="I14" s="25" t="n"/>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="H14" s="29" t="n">
+        <v>-7.44</v>
+      </c>
+      <c r="I14" s="29" t="n">
+        <v>-6.21</v>
+      </c>
     </row>
     <row r="15" ht="18" customHeight="1">
       <c r="A15" s="26" t="inlineStr">
         <is>
-          <t>셀트리온</t>
+          <t>삼성E&amp;A</t>
         </is>
       </c>
       <c r="B15" s="25" t="n">
@@ -3558,25 +3552,25 @@
       </c>
       <c r="F15" s="25" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G15" s="25" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="H15" s="29" t="n">
-        <v>-1.9</v>
-      </c>
-      <c r="I15" s="29" t="n">
-        <v>-1.56</v>
+        <v>-2.11</v>
+      </c>
+      <c r="I15" s="27" t="n">
+        <v>2.21</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
       <c r="A16" s="26" t="inlineStr">
         <is>
-          <t>현대로템</t>
+          <t>제약</t>
         </is>
       </c>
       <c r="B16" s="25" t="n">
@@ -3593,25 +3587,21 @@
       </c>
       <c r="F16" s="25" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G16" s="25" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
-        </is>
-      </c>
-      <c r="H16" s="29" t="n">
-        <v>-2.13</v>
-      </c>
-      <c r="I16" s="29" t="n">
-        <v>-0.72</v>
-      </c>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="H16" s="25" t="n"/>
+      <c r="I16" s="25" t="n"/>
     </row>
     <row r="17" ht="18" customHeight="1">
       <c r="A17" s="26" t="inlineStr">
         <is>
-          <t>보해양조</t>
+          <t>HJ중공업</t>
         </is>
       </c>
       <c r="B17" s="25" t="n">
@@ -3628,25 +3618,25 @@
       </c>
       <c r="F17" s="25" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G17" s="25" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
-        </is>
-      </c>
-      <c r="H17" s="27" t="n">
-        <v>29.88</v>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="H17" s="29" t="n">
+        <v>-3.67</v>
       </c>
       <c r="I17" s="27" t="n">
-        <v>58.36</v>
+        <v>3.24</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
       <c r="A18" s="26" t="inlineStr">
         <is>
-          <t>한화</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="B18" s="25" t="n">
@@ -3663,130 +3653,130 @@
       </c>
       <c r="F18" s="25" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G18" s="25" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="H18" s="29" t="n">
-        <v>-4.71</v>
+        <v>-26.16</v>
       </c>
       <c r="I18" s="29" t="n">
-        <v>-0.95</v>
+        <v>-19.9</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
       <c r="A19" s="26" t="inlineStr">
         <is>
-          <t>KT</t>
+          <t>넥써쓰</t>
         </is>
       </c>
       <c r="B19" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C19" s="25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D19" s="25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E19" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F19" s="25" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G19" s="25" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="H19" s="29" t="n">
-        <v>-0.37</v>
+        <v>-27.47</v>
       </c>
       <c r="I19" s="29" t="n">
-        <v>-2.74</v>
+        <v>-4.83</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
       <c r="A20" s="26" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>삼성바이오로직스</t>
         </is>
       </c>
       <c r="B20" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C20" s="25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D20" s="25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E20" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F20" s="25" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G20" s="25" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="H20" s="29" t="n">
-        <v>-26.16</v>
-      </c>
-      <c r="I20" s="29" t="n">
-        <v>-19.9</v>
+        <v>-3.92</v>
+      </c>
+      <c r="I20" s="27" t="n">
+        <v>6.1</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
       <c r="A21" s="26" t="inlineStr">
         <is>
-          <t>미래에셋증권</t>
+          <t>한솔테크닉스</t>
         </is>
       </c>
       <c r="B21" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C21" s="25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D21" s="25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E21" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F21" s="25" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G21" s="25" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="H21" s="29" t="n">
-        <v>-3.85</v>
-      </c>
-      <c r="I21" s="29" t="n">
-        <v>-6.79</v>
+        <v>-4.87</v>
+      </c>
+      <c r="I21" s="27" t="n">
+        <v>7.83</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
       <c r="A22" s="26" t="inlineStr">
         <is>
-          <t>제약</t>
+          <t>삼성SDI</t>
         </is>
       </c>
       <c r="B22" s="25" t="n">
@@ -3803,21 +3793,25 @@
       </c>
       <c r="F22" s="25" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G22" s="25" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
-        </is>
-      </c>
-      <c r="H22" s="25" t="n"/>
-      <c r="I22" s="25" t="n"/>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="H22" s="27" t="n">
+        <v>6.32</v>
+      </c>
+      <c r="I22" s="27" t="n">
+        <v>2.97</v>
+      </c>
     </row>
     <row r="23" ht="18" customHeight="1">
       <c r="A23" s="26" t="inlineStr">
         <is>
-          <t>진원생명과학</t>
+          <t>삼성물산</t>
         </is>
       </c>
       <c r="B23" s="25" t="n">
@@ -3834,25 +3828,25 @@
       </c>
       <c r="F23" s="25" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G23" s="25" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
-        </is>
-      </c>
-      <c r="H23" s="29" t="n">
-        <v>-17.67</v>
-      </c>
-      <c r="I23" s="29" t="n">
-        <v>-24.4</v>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="H23" s="27" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="I23" s="27" t="n">
+        <v>13.77</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
       <c r="A24" s="26" t="inlineStr">
         <is>
-          <t>한화오션</t>
+          <t>삼성생명</t>
         </is>
       </c>
       <c r="B24" s="25" t="n">
@@ -3869,297 +3863,305 @@
       </c>
       <c r="F24" s="25" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G24" s="25" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="H24" s="27" t="n">
-        <v>2.64</v>
+        <v>5.97</v>
       </c>
       <c r="I24" s="27" t="n">
-        <v>13.93</v>
+        <v>28.92</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
       <c r="A25" s="26" t="inlineStr">
         <is>
-          <t>HD현대</t>
+          <t>삼성에스디에스</t>
         </is>
       </c>
       <c r="B25" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C25" s="25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D25" s="25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E25" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F25" s="25" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G25" s="25" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="H25" s="29" t="n">
-        <v>-3.35</v>
+        <v>-4.07</v>
       </c>
       <c r="I25" s="29" t="n">
-        <v>-5.53</v>
+        <v>-10.55</v>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
       <c r="A26" s="26" t="inlineStr">
         <is>
-          <t>HD현대중공업</t>
+          <t>삼성전기</t>
         </is>
       </c>
       <c r="B26" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C26" s="25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D26" s="25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E26" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F26" s="25" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G26" s="25" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
-        </is>
-      </c>
-      <c r="H26" s="29" t="n">
-        <v>-2.49</v>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="H26" s="27" t="n">
+        <v>3.18</v>
       </c>
       <c r="I26" s="27" t="n">
-        <v>2.62</v>
+        <v>32.44</v>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
       <c r="A27" s="26" t="inlineStr">
         <is>
-          <t>HJ중공업</t>
+          <t>삼성전자우</t>
         </is>
       </c>
       <c r="B27" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C27" s="25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D27" s="25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E27" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F27" s="25" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G27" s="25" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="H27" s="29" t="n">
-        <v>-3.67</v>
+        <v>-2.84</v>
       </c>
       <c r="I27" s="27" t="n">
-        <v>3.24</v>
+        <v>7.25</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
       <c r="A28" s="26" t="inlineStr">
         <is>
-          <t>LG전자</t>
+          <t>삼성제약</t>
         </is>
       </c>
       <c r="B28" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C28" s="25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D28" s="25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E28" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F28" s="25" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G28" s="25" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="H28" s="29" t="n">
-        <v>-7.44</v>
-      </c>
-      <c r="I28" s="29" t="n">
-        <v>-6.21</v>
+        <v>-3.9</v>
+      </c>
+      <c r="I28" s="27" t="n">
+        <v>3.92</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
       <c r="A29" s="26" t="inlineStr">
         <is>
-          <t>남화토건</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="B29" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C29" s="25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D29" s="25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E29" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F29" s="25" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G29" s="25" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
-        </is>
-      </c>
-      <c r="H29" s="27" t="n">
-        <v>12.73</v>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="H29" s="29" t="n">
+        <v>-0.54</v>
       </c>
       <c r="I29" s="27" t="n">
-        <v>45.92</v>
+        <v>2.42</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
       <c r="A30" s="26" t="inlineStr">
         <is>
-          <t>방산</t>
+          <t>삼성증권</t>
         </is>
       </c>
       <c r="B30" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C30" s="25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D30" s="25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E30" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F30" s="25" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G30" s="25" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
-        </is>
-      </c>
-      <c r="H30" s="25" t="n"/>
-      <c r="I30" s="25" t="n"/>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="H30" s="29" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="I30" s="27" t="n">
+        <v>0.08</v>
+      </c>
     </row>
     <row r="31" ht="18" customHeight="1">
       <c r="A31" s="26" t="inlineStr">
         <is>
-          <t>씨피시스템</t>
+          <t>진원생명과학</t>
         </is>
       </c>
       <c r="B31" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C31" s="25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D31" s="25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E31" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F31" s="25" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G31" s="25" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
-        </is>
-      </c>
-      <c r="H31" s="27" t="n">
-        <v>29.88</v>
-      </c>
-      <c r="I31" s="27" t="n">
-        <v>20.79</v>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="H31" s="29" t="n">
+        <v>-17.67</v>
+      </c>
+      <c r="I31" s="29" t="n">
+        <v>-24.4</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
       <c r="A32" s="26" t="inlineStr">
         <is>
-          <t>전기차</t>
+          <t>한화</t>
         </is>
       </c>
       <c r="B32" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C32" s="25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D32" s="25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E32" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F32" s="25" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G32" s="25" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
-        </is>
-      </c>
-      <c r="H32" s="25" t="n"/>
-      <c r="I32" s="25" t="n"/>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="H32" s="29" t="n">
+        <v>-4.71</v>
+      </c>
+      <c r="I32" s="29" t="n">
+        <v>-0.95</v>
+      </c>
     </row>
     <row r="33" ht="18" customHeight="1">
       <c r="A33" s="26" t="inlineStr">
         <is>
-          <t>태양광</t>
+          <t>DB</t>
         </is>
       </c>
       <c r="B33" s="25" t="n">
@@ -4176,231 +4178,231 @@
       </c>
       <c r="F33" s="25" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G33" s="25" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
-        </is>
-      </c>
-      <c r="H33" s="25" t="n"/>
-      <c r="I33" s="25" t="n"/>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="H33" s="29" t="n">
+        <v>-2.39</v>
+      </c>
+      <c r="I33" s="29" t="n">
+        <v>-6.55</v>
+      </c>
     </row>
     <row r="34" ht="18" customHeight="1">
       <c r="A34" s="26" t="inlineStr">
         <is>
-          <t>JW신약</t>
+          <t>HMM</t>
         </is>
       </c>
       <c r="B34" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C34" s="25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D34" s="25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E34" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F34" s="25" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G34" s="25" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
-        </is>
-      </c>
-      <c r="H34" s="27" t="n">
-        <v>13.08</v>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="H34" s="29" t="n">
+        <v>-1.47</v>
       </c>
       <c r="I34" s="27" t="n">
-        <v>70.94</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
       <c r="A35" s="26" t="inlineStr">
         <is>
-          <t>강동씨앤엘</t>
+          <t>남화토건</t>
         </is>
       </c>
       <c r="B35" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C35" s="25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D35" s="25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E35" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F35" s="25" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G35" s="25" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="H35" s="27" t="n">
-        <v>29.91</v>
+        <v>12.73</v>
       </c>
       <c r="I35" s="27" t="n">
-        <v>121.56</v>
+        <v>45.92</v>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
       <c r="A36" s="26" t="inlineStr">
         <is>
-          <t>다스코</t>
+          <t>센서뷰</t>
         </is>
       </c>
       <c r="B36" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C36" s="25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D36" s="25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E36" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F36" s="25" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G36" s="25" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
-        </is>
-      </c>
-      <c r="H36" s="27" t="n">
-        <v>29.96</v>
-      </c>
-      <c r="I36" s="27" t="n">
-        <v>31.44</v>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="H36" s="29" t="n">
+        <v>-5.11</v>
+      </c>
+      <c r="I36" s="29" t="n">
+        <v>-12.29</v>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
       <c r="A37" s="26" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>태양광</t>
         </is>
       </c>
       <c r="B37" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C37" s="25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D37" s="25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E37" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F37" s="25" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G37" s="25" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
-        </is>
-      </c>
-      <c r="H37" s="29" t="n">
-        <v>-7.41</v>
-      </c>
-      <c r="I37" s="29" t="n">
-        <v>-2.75</v>
-      </c>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="H37" s="25" t="n"/>
+      <c r="I37" s="25" t="n"/>
     </row>
     <row r="38" ht="18" customHeight="1">
       <c r="A38" s="26" t="inlineStr">
         <is>
-          <t>대원전선</t>
+          <t>파두</t>
         </is>
       </c>
       <c r="B38" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C38" s="25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D38" s="25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E38" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F38" s="25" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G38" s="25" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="H38" s="29" t="n">
-        <v>-3.73</v>
+        <v>-2.5</v>
       </c>
       <c r="I38" s="27" t="n">
-        <v>6.02</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
       <c r="A39" s="26" t="inlineStr">
         <is>
-          <t>동일스틸럭스</t>
+          <t>현대로템</t>
         </is>
       </c>
       <c r="B39" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C39" s="25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D39" s="25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E39" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F39" s="25" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G39" s="25" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="H39" s="29" t="n">
-        <v>-11.15</v>
-      </c>
-      <c r="I39" s="27" t="n">
-        <v>29.05</v>
+        <v>-2.13</v>
+      </c>
+      <c r="I39" s="29" t="n">
+        <v>-0.72</v>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
       <c r="A40" s="26" t="inlineStr">
         <is>
-          <t>메리츠제2호스팩</t>
+          <t>JW신약</t>
         </is>
       </c>
       <c r="B40" s="25" t="n">
@@ -4417,21 +4419,25 @@
       </c>
       <c r="F40" s="25" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G40" s="25" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
-        </is>
-      </c>
-      <c r="H40" s="25" t="n"/>
-      <c r="I40" s="25" t="n"/>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="H40" s="27" t="n">
+        <v>13.08</v>
+      </c>
+      <c r="I40" s="27" t="n">
+        <v>70.94</v>
+      </c>
     </row>
     <row r="41" ht="18" customHeight="1">
       <c r="A41" s="26" t="inlineStr">
         <is>
-          <t>부국철강</t>
+          <t>강동씨앤엘</t>
         </is>
       </c>
       <c r="B41" s="25" t="n">
@@ -4448,25 +4454,25 @@
       </c>
       <c r="F41" s="25" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G41" s="25" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
-        </is>
-      </c>
-      <c r="H41" s="29" t="n">
-        <v>-13.76</v>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="H41" s="27" t="n">
+        <v>29.91</v>
       </c>
       <c r="I41" s="27" t="n">
-        <v>3.49</v>
+        <v>121.56</v>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
       <c r="A42" s="26" t="inlineStr">
         <is>
-          <t>비엘팜텍</t>
+          <t>메리츠제2호스팩</t>
         </is>
       </c>
       <c r="B42" s="25" t="n">
@@ -4483,25 +4489,21 @@
       </c>
       <c r="F42" s="25" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G42" s="25" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
-        </is>
-      </c>
-      <c r="H42" s="29" t="n">
-        <v>-20.26</v>
-      </c>
-      <c r="I42" s="27" t="n">
-        <v>4.23</v>
-      </c>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="H42" s="25" t="n"/>
+      <c r="I42" s="25" t="n"/>
     </row>
     <row r="43" ht="18" customHeight="1">
       <c r="A43" s="26" t="inlineStr">
         <is>
-          <t>삼보산업</t>
+          <t>보해양조</t>
         </is>
       </c>
       <c r="B43" s="25" t="n">
@@ -4518,25 +4520,25 @@
       </c>
       <c r="F43" s="25" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G43" s="25" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="H43" s="27" t="n">
-        <v>11.54</v>
+        <v>29.88</v>
       </c>
       <c r="I43" s="27" t="n">
-        <v>45.97</v>
+        <v>58.36</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
       <c r="A44" s="26" t="inlineStr">
         <is>
-          <t>삼익제약</t>
+          <t>부국철강</t>
         </is>
       </c>
       <c r="B44" s="25" t="n">
@@ -4553,25 +4555,25 @@
       </c>
       <c r="F44" s="25" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G44" s="25" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
-        </is>
-      </c>
-      <c r="H44" s="27" t="n">
-        <v>29.98</v>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="H44" s="29" t="n">
+        <v>-13.76</v>
       </c>
       <c r="I44" s="27" t="n">
-        <v>41.82</v>
+        <v>3.49</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
       <c r="A45" s="26" t="inlineStr">
         <is>
-          <t>삼화전자</t>
+          <t>삼익제약</t>
         </is>
       </c>
       <c r="B45" s="25" t="n">
@@ -4588,25 +4590,25 @@
       </c>
       <c r="F45" s="25" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G45" s="25" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="H45" s="27" t="n">
-        <v>2.81</v>
+        <v>29.98</v>
       </c>
       <c r="I45" s="27" t="n">
-        <v>73.59</v>
+        <v>41.82</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
       <c r="A46" s="26" t="inlineStr">
         <is>
-          <t>성문전자</t>
+          <t>삼화전자</t>
         </is>
       </c>
       <c r="B46" s="25" t="n">
@@ -4623,25 +4625,25 @@
       </c>
       <c r="F46" s="25" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G46" s="25" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="H46" s="27" t="n">
-        <v>4.43</v>
+        <v>2.81</v>
       </c>
       <c r="I46" s="27" t="n">
-        <v>40.24</v>
+        <v>73.59</v>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
       <c r="A47" s="26" t="inlineStr">
         <is>
-          <t>위더스제약</t>
+          <t>성문전자</t>
         </is>
       </c>
       <c r="B47" s="25" t="n">
@@ -4658,25 +4660,25 @@
       </c>
       <c r="F47" s="25" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G47" s="25" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="H47" s="27" t="n">
-        <v>13.59</v>
+        <v>4.43</v>
       </c>
       <c r="I47" s="27" t="n">
-        <v>33.03</v>
+        <v>40.24</v>
       </c>
     </row>
     <row r="48" ht="18" customHeight="1">
       <c r="A48" s="26" t="inlineStr">
         <is>
-          <t>율촌</t>
+          <t>위더스제약</t>
         </is>
       </c>
       <c r="B48" s="25" t="n">
@@ -4693,25 +4695,25 @@
       </c>
       <c r="F48" s="25" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G48" s="25" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
-        </is>
-      </c>
-      <c r="H48" s="29" t="n">
-        <v>-13.55</v>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="H48" s="27" t="n">
+        <v>13.59</v>
       </c>
       <c r="I48" s="27" t="n">
-        <v>30.73</v>
+        <v>33.03</v>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1">
       <c r="A49" s="26" t="inlineStr">
         <is>
-          <t>티웨이홀딩스</t>
+          <t>율촌</t>
         </is>
       </c>
       <c r="B49" s="25" t="n">
@@ -4728,25 +4730,25 @@
       </c>
       <c r="F49" s="25" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G49" s="25" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="H49" s="29" t="n">
-        <v>-7.09</v>
+        <v>-13.55</v>
       </c>
       <c r="I49" s="27" t="n">
-        <v>26.88</v>
+        <v>30.73</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
       <c r="A50" s="26" t="inlineStr">
         <is>
-          <t>피앤에스로보틱스</t>
+          <t>티웨이홀딩스</t>
         </is>
       </c>
       <c r="B50" s="25" t="n">
@@ -4763,25 +4765,25 @@
       </c>
       <c r="F50" s="25" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G50" s="25" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
-        </is>
-      </c>
-      <c r="H50" s="27" t="n">
-        <v>22.04</v>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="H50" s="29" t="n">
+        <v>-7.09</v>
       </c>
       <c r="I50" s="27" t="n">
-        <v>20.74</v>
+        <v>26.88</v>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
       <c r="A51" s="26" t="inlineStr">
         <is>
-          <t>한솔테크닉스</t>
+          <t>피앤에스로보틱스</t>
         </is>
       </c>
       <c r="B51" s="25" t="n">
@@ -4798,19 +4800,19 @@
       </c>
       <c r="F51" s="25" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G51" s="25" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
-        </is>
-      </c>
-      <c r="H51" s="29" t="n">
-        <v>-4.87</v>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="H51" s="27" t="n">
+        <v>22.04</v>
       </c>
       <c r="I51" s="27" t="n">
-        <v>7.83</v>
+        <v>20.74</v>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1">
@@ -4833,12 +4835,12 @@
       </c>
       <c r="F52" s="25" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G52" s="25" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="H52" s="29" t="n">
@@ -4929,19 +4931,19 @@
         <v>1</v>
       </c>
       <c r="C3" s="36" t="n">
-        <v>60</v>
+        <v>82</v>
       </c>
       <c r="D3" s="36" t="n">
-        <v>60</v>
+        <v>82</v>
       </c>
       <c r="E3" s="36" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="F3" s="37" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G3" s="37" t="inlineStr">
@@ -4960,19 +4962,19 @@
         <v>1</v>
       </c>
       <c r="C4" s="36" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D4" s="36" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E4" s="36" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="F4" s="37" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G4" s="37" t="inlineStr">
@@ -4991,19 +4993,19 @@
         <v>1</v>
       </c>
       <c r="C5" s="36" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D5" s="36" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E5" s="36" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="F5" s="37" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G5" s="37" t="inlineStr">
@@ -5015,26 +5017,26 @@
     <row r="6" ht="18" customHeight="1">
       <c r="A6" s="35" t="inlineStr">
         <is>
-          <t>방산</t>
+          <t>로봇</t>
         </is>
       </c>
       <c r="B6" s="36" t="n">
         <v>1</v>
       </c>
       <c r="C6" s="36" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D6" s="36" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E6" s="36" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="F6" s="37" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G6" s="37" t="inlineStr">
@@ -5046,26 +5048,26 @@
     <row r="7" ht="18" customHeight="1">
       <c r="A7" s="35" t="inlineStr">
         <is>
-          <t>로봇</t>
+          <t>태양광</t>
         </is>
       </c>
       <c r="B7" s="36" t="n">
         <v>1</v>
       </c>
       <c r="C7" s="36" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D7" s="36" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E7" s="36" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="F7" s="37" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G7" s="37" t="inlineStr">
@@ -5077,26 +5079,26 @@
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="35" t="inlineStr">
         <is>
-          <t>태양광</t>
+          <t>제약</t>
         </is>
       </c>
       <c r="B8" s="36" t="n">
         <v>1</v>
       </c>
       <c r="C8" s="36" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D8" s="36" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E8" s="36" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="F8" s="37" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G8" s="37" t="inlineStr">
@@ -5108,26 +5110,26 @@
     <row r="9" ht="18" customHeight="1">
       <c r="A9" s="35" t="inlineStr">
         <is>
-          <t>제약</t>
+          <t>인공지능</t>
         </is>
       </c>
       <c r="B9" s="36" t="n">
         <v>1</v>
       </c>
       <c r="C9" s="36" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D9" s="36" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E9" s="36" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="F9" s="37" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G9" s="37" t="inlineStr">
@@ -5137,40 +5139,36 @@
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="35" t="inlineStr">
-        <is>
-          <t>인공지능</t>
-        </is>
-      </c>
-      <c r="B10" s="36" t="n">
-        <v>1</v>
-      </c>
-      <c r="C10" s="36" t="n">
-        <v>12</v>
-      </c>
-      <c r="D10" s="36" t="n">
-        <v>12</v>
-      </c>
-      <c r="E10" s="36" t="inlineStr">
-        <is>
-          <t>2026-06-21</t>
-        </is>
-      </c>
-      <c r="F10" s="37" t="inlineStr">
-        <is>
-          <t>2026-06-21</t>
-        </is>
-      </c>
-      <c r="G10" s="37" t="inlineStr">
-        <is>
-          <t>⚡ 관심</t>
-        </is>
-      </c>
+      <c r="A10" s="26" t="inlineStr">
+        <is>
+          <t>이차전지</t>
+        </is>
+      </c>
+      <c r="B10" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F10" s="28" t="inlineStr">
+        <is>
+          <t>감지 없음</t>
+        </is>
+      </c>
+      <c r="G10" s="28" t="inlineStr"/>
     </row>
     <row r="11" ht="18" customHeight="1">
       <c r="A11" s="26" t="inlineStr">
         <is>
-          <t>이차전지</t>
+          <t>AI반도체</t>
         </is>
       </c>
       <c r="B11" s="25" t="n">
@@ -5197,7 +5195,7 @@
     <row r="12" ht="18" customHeight="1">
       <c r="A12" s="26" t="inlineStr">
         <is>
-          <t>AI반도체</t>
+          <t>방산</t>
         </is>
       </c>
       <c r="B12" s="25" t="n">

--- a/trend/stock_trend_history.xlsx
+++ b/trend/stock_trend_history.xlsx
@@ -273,14 +273,14 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -694,7 +694,7 @@
     <row r="1" ht="36" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>📊 주식 트렌드 조기 감지 대시보드   |   최종 업데이트: 2026-06-22 06:55</t>
+          <t>📊 주식 트렌드 조기 감지 대시보드   |   최종 업데이트: 2026-06-23 06:54</t>
         </is>
       </c>
     </row>
@@ -708,7 +708,7 @@
       </c>
       <c r="E3" s="3" t="n"/>
       <c r="G3" s="5" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H3" s="3" t="n"/>
       <c r="J3" s="6" t="n">
@@ -787,21 +787,21 @@
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="11" t="inlineStr">
         <is>
-          <t>⚡ 최신(2026-06-22) 상위: 반도체  점수 82.0점</t>
+          <t>⚡ 최신(2026-06-23) 상위: 반도체  점수 62.0점</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1">
       <c r="A11" s="12" t="inlineStr">
         <is>
-          <t>⚡ 최신(2026-06-22) 상위: SK  점수 46.0점</t>
+          <t>⚡ 최신(2026-06-23) 상위: SK하이닉스  점수 47.0점</t>
         </is>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1">
       <c r="A12" s="11" t="inlineStr">
         <is>
-          <t>⚡ 최신(2026-06-22) 상위: SK하이닉스  점수 44.0점</t>
+          <t>⚡ 최신(2026-06-23) 상위: 삼성전자  점수 26.0점</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B14" s="15" t="n">
@@ -928,10 +928,10 @@
         </is>
       </c>
       <c r="D14" s="15" t="n">
-        <v>82</v>
+        <v>62</v>
       </c>
       <c r="E14" s="15" t="n">
-        <v>82</v>
+        <v>62</v>
       </c>
       <c r="F14" s="15" t="n">
         <v>0</v>
@@ -947,7 +947,7 @@
       </c>
       <c r="J14" s="17" t="inlineStr">
         <is>
-          <t>네이버뉴스 헤드라인 언급 / 매일경제 기사 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 기사 언급</t>
+          <t>매일경제 기사 언급 / 네이버뉴스 헤드라인 언급 / 매일경제 기사 언급 / 매일경제 헤드라인 언급 / 매일경제 기사 언급</t>
         </is>
       </c>
       <c r="K14" s="17" t="inlineStr">
@@ -959,7 +959,7 @@
     <row r="15" ht="18" customHeight="1">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B15" s="15" t="n">
@@ -967,14 +967,14 @@
       </c>
       <c r="C15" s="16" t="inlineStr">
         <is>
-          <t>SK</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="D15" s="15" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E15" s="15" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F15" s="15" t="n">
         <v>0</v>
@@ -983,14 +983,14 @@
         <v>0</v>
       </c>
       <c r="H15" s="18" t="n">
-        <v>5.39</v>
+        <v>5.61</v>
       </c>
       <c r="I15" s="18" t="n">
-        <v>22.09</v>
+        <v>27.58</v>
       </c>
       <c r="J15" s="17" t="inlineStr">
         <is>
-          <t>네이버뉴스 헤드라인 언급 / 네이버뉴스 헤드라인 언급 / 네이버뉴스 기사 언급 / 매일경제 기사 언급 / 네이버뉴스 기사 언급</t>
+          <t>매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 기사 언급 / 네이버뉴스 헤드라인 언급</t>
         </is>
       </c>
       <c r="K15" s="17" t="inlineStr">
@@ -1002,7 +1002,7 @@
     <row r="16" ht="18" customHeight="1">
       <c r="A16" s="15" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B16" s="15" t="n">
@@ -1010,14 +1010,14 @@
       </c>
       <c r="C16" s="16" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="D16" s="15" t="n">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="E16" s="15" t="n">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="F16" s="15" t="n">
         <v>0</v>
@@ -1025,15 +1025,15 @@
       <c r="G16" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="H16" s="18" t="n">
-        <v>2.94</v>
+      <c r="H16" s="19" t="n">
+        <v>-0.14</v>
       </c>
       <c r="I16" s="18" t="n">
-        <v>28.56</v>
+        <v>4.9</v>
       </c>
       <c r="J16" s="17" t="inlineStr">
         <is>
-          <t>네이버뉴스 헤드라인 언급 / 네이버뉴스 헤드라인 언급 / 네이버뉴스 기사 언급 / 매일경제 기사 언급 / 네이버뉴스 기사 언급</t>
+          <t>매일경제 헤드라인 언급 / 매일경제 기사 언급 / 매일경제 기사 언급 / 네이버뉴스 헤드라인 언급 / 네이버뉴스 기사 언급</t>
         </is>
       </c>
       <c r="K16" s="17" t="inlineStr">
@@ -1045,7 +1045,7 @@
     <row r="17" ht="18" customHeight="1">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B17" s="15" t="n">
@@ -1057,10 +1057,10 @@
         </is>
       </c>
       <c r="D17" s="15" t="n">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="E17" s="15" t="n">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="F17" s="15" t="n">
         <v>0</v>
@@ -1068,27 +1068,25 @@
       <c r="G17" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="H17" s="19" t="n">
-        <v>-0.91</v>
-      </c>
-      <c r="I17" s="18" t="n">
-        <v>2.25</v>
+      <c r="H17" s="18" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="I17" s="19" t="n">
+        <v>-7.18</v>
       </c>
       <c r="J17" s="17" t="inlineStr">
         <is>
-          <t>Google 급상승 검색어 등장 (KR) / 한국경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K17" s="17" t="inlineStr">
-        <is>
-          <t>Google</t>
-        </is>
+          <t>한국경제 헤드라인 언급 / 매일경제 기사 언급 / 한국경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K17" s="17" t="n">
+        <v/>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
       <c r="A18" s="15" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B18" s="15" t="n">
@@ -1096,14 +1094,14 @@
       </c>
       <c r="C18" s="16" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>바이오</t>
         </is>
       </c>
       <c r="D18" s="15" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="E18" s="15" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="F18" s="15" t="n">
         <v>0</v>
@@ -1111,27 +1109,27 @@
       <c r="G18" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="H18" s="19" t="n">
-        <v>-2.34</v>
-      </c>
-      <c r="I18" s="18" t="n">
-        <v>9.77</v>
+      <c r="H18" s="15" t="n">
+        <v/>
+      </c>
+      <c r="I18" s="15" t="n">
+        <v/>
       </c>
       <c r="J18" s="17" t="inlineStr">
         <is>
-          <t>Google 급상승 검색어 등장 (KR) / 네이버뉴스 헤드라인 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 헤드라인 언급 / 매일경제 기사 언급</t>
+          <t>네이버뉴스 헤드라인 언급 / 네이버뉴스 헤드라인 언급 / 네이버뉴스 헤드라인 언급 / 네이버뉴스 헤드라인 언급 / 네이버뉴스 헤드라인 언급</t>
         </is>
       </c>
       <c r="K18" s="17" t="inlineStr">
         <is>
-          <t>Google, 네이버</t>
+          <t>네이버</t>
         </is>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
       <c r="A19" s="15" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B19" s="15" t="n">
@@ -1139,14 +1137,14 @@
       </c>
       <c r="C19" s="16" t="inlineStr">
         <is>
-          <t>현대차</t>
+          <t>인공지능</t>
         </is>
       </c>
       <c r="D19" s="15" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="E19" s="15" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="F19" s="15" t="n">
         <v>0</v>
@@ -1154,15 +1152,15 @@
       <c r="G19" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="H19" s="18" t="n">
-        <v>2</v>
-      </c>
-      <c r="I19" s="18" t="n">
-        <v>0.99</v>
+      <c r="H19" s="15" t="n">
+        <v/>
+      </c>
+      <c r="I19" s="15" t="n">
+        <v/>
       </c>
       <c r="J19" s="17" t="inlineStr">
         <is>
-          <t>네이버뉴스 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 기사 언급 / 한국경제 헤드라인 언급</t>
+          <t>매일경제 기사 언급 / 네이버뉴스 기사 언급 / 매일경제 기사 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 기사 언급</t>
         </is>
       </c>
       <c r="K19" s="17" t="inlineStr">
@@ -1174,7 +1172,7 @@
     <row r="20" ht="18" customHeight="1">
       <c r="A20" s="15" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B20" s="15" t="n">
@@ -1182,14 +1180,14 @@
       </c>
       <c r="C20" s="16" t="inlineStr">
         <is>
-          <t>바이오</t>
+          <t>SK스퀘어</t>
         </is>
       </c>
       <c r="D20" s="15" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E20" s="15" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F20" s="15" t="n">
         <v>0</v>
@@ -1197,27 +1195,25 @@
       <c r="G20" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="H20" s="15" t="n">
+      <c r="H20" s="18" t="n">
+        <v>10.67</v>
+      </c>
+      <c r="I20" s="18" t="n">
+        <v>39.42</v>
+      </c>
+      <c r="J20" s="17" t="inlineStr">
+        <is>
+          <t>매일경제 헤드라인 언급 / 매일경제 기사 언급 / 매일경제 기사 언급 / 한국경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K20" s="17" t="n">
         <v/>
-      </c>
-      <c r="I20" s="15" t="n">
-        <v/>
-      </c>
-      <c r="J20" s="17" t="inlineStr">
-        <is>
-          <t>매일경제 헤드라인 언급 / 네이버뉴스 헤드라인 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 기사 언급 / 한국경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K20" s="17" t="inlineStr">
-        <is>
-          <t>네이버</t>
-        </is>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
       <c r="A21" s="15" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B21" s="15" t="n">
@@ -1225,14 +1221,14 @@
       </c>
       <c r="C21" s="16" t="inlineStr">
         <is>
-          <t>인공지능</t>
+          <t>제약</t>
         </is>
       </c>
       <c r="D21" s="15" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E21" s="15" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F21" s="15" t="n">
         <v>0</v>
@@ -1248,7 +1244,7 @@
       </c>
       <c r="J21" s="17" t="inlineStr">
         <is>
-          <t>매일경제 기사 언급 / 네이버뉴스 기사 언급 / 매일경제 기사 언급 / 네이버뉴스 기사 언급 / 매일경제 기사 언급</t>
+          <t>네이버뉴스 기사 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 헤드라인 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 헤드라인 언급</t>
         </is>
       </c>
       <c r="K21" s="17" t="inlineStr">
@@ -1260,7 +1256,7 @@
     <row r="22" ht="18" customHeight="1">
       <c r="A22" s="15" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B22" s="15" t="n">
@@ -1268,14 +1264,14 @@
       </c>
       <c r="C22" s="16" t="inlineStr">
         <is>
-          <t>로봇</t>
+          <t>카카오게임즈</t>
         </is>
       </c>
       <c r="D22" s="15" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E22" s="15" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F22" s="15" t="n">
         <v>0</v>
@@ -1283,25 +1279,27 @@
       <c r="G22" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="H22" s="15" t="n">
-        <v/>
-      </c>
-      <c r="I22" s="15" t="n">
-        <v/>
+      <c r="H22" s="18" t="n">
+        <v>13.96</v>
+      </c>
+      <c r="I22" s="18" t="n">
+        <v>9.970000000000001</v>
       </c>
       <c r="J22" s="17" t="inlineStr">
         <is>
-          <t>매일경제 기사 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K22" s="17" t="n">
-        <v/>
+          <t>네이버 검색 당일 +76% / 중요공시 1건 / 한국경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K22" s="17" t="inlineStr">
+        <is>
+          <t>공시, 네이버</t>
+        </is>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B23" s="15" t="n">
@@ -1309,42 +1307,42 @@
       </c>
       <c r="C23" s="16" t="inlineStr">
         <is>
-          <t>전기차</t>
+          <t>삼성바이오로직스</t>
         </is>
       </c>
       <c r="D23" s="15" t="n">
         <v>9</v>
       </c>
       <c r="E23" s="15" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="F23" s="15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G23" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" s="15" t="n">
-        <v/>
-      </c>
-      <c r="I23" s="15" t="n">
-        <v/>
+        <v>3</v>
+      </c>
+      <c r="H23" s="19" t="n">
+        <v>-5.75</v>
+      </c>
+      <c r="I23" s="19" t="n">
+        <v>-2.78</v>
       </c>
       <c r="J23" s="17" t="inlineStr">
         <is>
-          <t>네이버뉴스 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급</t>
+          <t>중요공시 2건 / 중요공시 3일 +100% / 중요공시 7일 +100% / 네이버뉴스 헤드라인 언급</t>
         </is>
       </c>
       <c r="K23" s="17" t="inlineStr">
         <is>
-          <t>네이버</t>
+          <t>공시, 네이버</t>
         </is>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B24" s="15" t="n">
@@ -1352,14 +1350,14 @@
       </c>
       <c r="C24" s="16" t="inlineStr">
         <is>
-          <t>대한항공</t>
+          <t>현대차</t>
         </is>
       </c>
       <c r="D24" s="15" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E24" s="15" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F24" s="15" t="n">
         <v>0</v>
@@ -1368,14 +1366,14 @@
         <v>0</v>
       </c>
       <c r="H24" s="19" t="n">
-        <v>-3.12</v>
-      </c>
-      <c r="I24" s="18" t="n">
-        <v>5.08</v>
+        <v>-5.22</v>
+      </c>
+      <c r="I24" s="19" t="n">
+        <v>-10.2</v>
       </c>
       <c r="J24" s="17" t="inlineStr">
         <is>
-          <t>매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급</t>
+          <t>매일경제 기사 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
         </is>
       </c>
       <c r="K24" s="17" t="n">
@@ -1385,7 +1383,7 @@
     <row r="25" ht="18" customHeight="1">
       <c r="A25" s="15" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B25" s="15" t="n">
@@ -1393,42 +1391,42 @@
       </c>
       <c r="C25" s="16" t="inlineStr">
         <is>
-          <t>삼성E&amp;A</t>
+          <t>에이팩트</t>
         </is>
       </c>
       <c r="D25" s="15" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E25" s="15" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F25" s="15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G25" s="15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H25" s="19" t="n">
-        <v>-2.11</v>
-      </c>
-      <c r="I25" s="18" t="n">
-        <v>2.21</v>
+        <v>-0.72</v>
+      </c>
+      <c r="I25" s="19" t="n">
+        <v>-9.140000000000001</v>
       </c>
       <c r="J25" s="17" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +91% / Google 급상승 검색어 등장 (KR)</t>
+          <t>중요공시 4건 / 중요공시 3일 +300% / 중요공시 7일 +100%</t>
         </is>
       </c>
       <c r="K25" s="17" t="inlineStr">
         <is>
-          <t>Google, 네이버</t>
+          <t>공시</t>
         </is>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
       <c r="A26" s="15" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B26" s="15" t="n">
@@ -1436,14 +1434,14 @@
       </c>
       <c r="C26" s="16" t="inlineStr">
         <is>
-          <t>LG전자</t>
+          <t>로봇</t>
         </is>
       </c>
       <c r="D26" s="15" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E26" s="15" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F26" s="15" t="n">
         <v>0</v>
@@ -1451,15 +1449,15 @@
       <c r="G26" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="H26" s="19" t="n">
-        <v>-7.44</v>
-      </c>
-      <c r="I26" s="19" t="n">
-        <v>-6.21</v>
+      <c r="H26" s="15" t="n">
+        <v/>
+      </c>
+      <c r="I26" s="15" t="n">
+        <v/>
       </c>
       <c r="J26" s="17" t="inlineStr">
         <is>
-          <t>한국경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 기사 언급</t>
+          <t>매일경제 헤드라인 언급 / 한국경제 헤드라인 언급 / 매일경제 헤드라인 언급</t>
         </is>
       </c>
       <c r="K26" s="17" t="n">
@@ -1469,7 +1467,7 @@
     <row r="27" ht="18" customHeight="1">
       <c r="A27" s="15" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B27" s="15" t="n">
@@ -1477,7 +1475,7 @@
       </c>
       <c r="C27" s="16" t="inlineStr">
         <is>
-          <t>제약</t>
+          <t>LG전자</t>
         </is>
       </c>
       <c r="D27" s="15" t="n">
@@ -1492,113 +1490,109 @@
       <c r="G27" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="H27" s="15" t="n">
+      <c r="H27" s="18" t="n">
+        <v>7.57</v>
+      </c>
+      <c r="I27" s="19" t="n">
+        <v>-6.57</v>
+      </c>
+      <c r="J27" s="17" t="inlineStr">
+        <is>
+          <t>한국경제 헤드라인 언급 / 한국경제 헤드라인 언급 / 매일경제 기사 언급</t>
+        </is>
+      </c>
+      <c r="K27" s="17" t="n">
         <v/>
       </c>
-      <c r="I27" s="15" t="n">
+    </row>
+    <row r="28" ht="18" customHeight="1">
+      <c r="A28" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B28" s="15" t="n">
+        <v>15</v>
+      </c>
+      <c r="C28" s="16" t="inlineStr">
+        <is>
+          <t>철강</t>
+        </is>
+      </c>
+      <c r="D28" s="15" t="n">
+        <v>7</v>
+      </c>
+      <c r="E28" s="15" t="n">
+        <v>7</v>
+      </c>
+      <c r="F28" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" s="15" t="n">
         <v/>
       </c>
-      <c r="J27" s="17" t="inlineStr">
-        <is>
-          <t>네이버뉴스 헤드라인 언급 / 네이버뉴스 헤드라인 언급 / 네이버뉴스 기사 언급</t>
-        </is>
-      </c>
-      <c r="K27" s="17" t="inlineStr">
+      <c r="I28" s="15" t="n">
+        <v/>
+      </c>
+      <c r="J28" s="17" t="inlineStr">
+        <is>
+          <t>네이버뉴스 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K28" s="17" t="inlineStr">
         <is>
           <t>네이버</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="18" customHeight="1">
-      <c r="A28" s="20" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
-        </is>
-      </c>
-      <c r="B28" s="20" t="n">
-        <v>15</v>
-      </c>
-      <c r="C28" s="21" t="inlineStr">
-        <is>
-          <t>넥써쓰</t>
-        </is>
-      </c>
-      <c r="D28" s="20" t="n">
-        <v>6</v>
-      </c>
-      <c r="E28" s="20" t="n">
-        <v>6</v>
-      </c>
-      <c r="F28" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G28" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H28" s="22" t="n">
-        <v>-27.47</v>
-      </c>
-      <c r="I28" s="22" t="n">
-        <v>-4.83</v>
-      </c>
-      <c r="J28" s="23" t="inlineStr">
-        <is>
-          <t>네이버 검색 당일 +113% / 중요공시 3건</t>
-        </is>
-      </c>
-      <c r="K28" s="23" t="inlineStr">
-        <is>
-          <t>네이버, 공시</t>
-        </is>
-      </c>
-    </row>
     <row r="29" ht="18" customHeight="1">
-      <c r="A29" s="20" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
-        </is>
-      </c>
-      <c r="B29" s="20" t="n">
+      <c r="A29" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B29" s="15" t="n">
         <v>16</v>
       </c>
-      <c r="C29" s="21" t="inlineStr">
-        <is>
-          <t>SG</t>
-        </is>
-      </c>
-      <c r="D29" s="20" t="n">
-        <v>6</v>
-      </c>
-      <c r="E29" s="20" t="n">
-        <v>6</v>
-      </c>
-      <c r="F29" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G29" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H29" s="22" t="n">
-        <v>-26.16</v>
-      </c>
-      <c r="I29" s="22" t="n">
-        <v>-19.9</v>
-      </c>
-      <c r="J29" s="23" t="inlineStr">
-        <is>
-          <t>네이버 검색 당일 +112% / 한국경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K29" s="23" t="inlineStr">
-        <is>
-          <t>네이버</t>
-        </is>
+      <c r="C29" s="16" t="inlineStr">
+        <is>
+          <t>태양광</t>
+        </is>
+      </c>
+      <c r="D29" s="15" t="n">
+        <v>7</v>
+      </c>
+      <c r="E29" s="15" t="n">
+        <v>7</v>
+      </c>
+      <c r="F29" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" s="15" t="n">
+        <v/>
+      </c>
+      <c r="I29" s="15" t="n">
+        <v/>
+      </c>
+      <c r="J29" s="17" t="inlineStr">
+        <is>
+          <t>매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 기사 언급</t>
+        </is>
+      </c>
+      <c r="K29" s="17" t="n">
+        <v/>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
       <c r="A30" s="20" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B30" s="20" t="n">
@@ -1606,42 +1600,42 @@
       </c>
       <c r="C30" s="21" t="inlineStr">
         <is>
-          <t>한솔테크닉스</t>
+          <t>프로브잇</t>
         </is>
       </c>
       <c r="D30" s="20" t="n">
         <v>6</v>
       </c>
       <c r="E30" s="20" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F30" s="20" t="n">
         <v>0</v>
       </c>
       <c r="G30" s="20" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H30" s="22" t="n">
-        <v>-4.87</v>
-      </c>
-      <c r="I30" s="24" t="n">
-        <v>7.83</v>
+        <v>-97.06</v>
+      </c>
+      <c r="I30" s="22" t="n">
+        <v>-97.06</v>
       </c>
       <c r="J30" s="23" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +81% / 중요공시 2건 / 중요공시 7일 +100%</t>
+          <t>네이버 검색 당일 +259% / 중요공시 3건</t>
         </is>
       </c>
       <c r="K30" s="23" t="inlineStr">
         <is>
-          <t>네이버, 공시</t>
+          <t>공시, 네이버</t>
         </is>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
       <c r="A31" s="20" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B31" s="20" t="n">
@@ -1649,42 +1643,42 @@
       </c>
       <c r="C31" s="21" t="inlineStr">
         <is>
-          <t>HJ중공업</t>
+          <t>한솔테크닉스</t>
         </is>
       </c>
       <c r="D31" s="20" t="n">
         <v>6</v>
       </c>
       <c r="E31" s="20" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F31" s="20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G31" s="20" t="n">
         <v>3</v>
       </c>
-      <c r="H31" s="22" t="n">
-        <v>-3.67</v>
+      <c r="H31" s="24" t="n">
+        <v>18.2</v>
       </c>
       <c r="I31" s="24" t="n">
-        <v>3.24</v>
+        <v>20.22</v>
       </c>
       <c r="J31" s="23" t="inlineStr">
         <is>
-          <t>중요공시 2건 / 중요공시 3일 +100% / 중요공시 7일 +100%</t>
+          <t>네이버 검색 당일 +86% / 중요공시 2건 / 중요공시 7일 +100%</t>
         </is>
       </c>
       <c r="K31" s="23" t="inlineStr">
         <is>
-          <t>공시</t>
+          <t>공시, 네이버</t>
         </is>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
       <c r="A32" s="20" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B32" s="20" t="n">
@@ -1692,42 +1686,42 @@
       </c>
       <c r="C32" s="21" t="inlineStr">
         <is>
-          <t>삼성바이오로직스</t>
+          <t>비투엔</t>
         </is>
       </c>
       <c r="D32" s="20" t="n">
         <v>6</v>
       </c>
       <c r="E32" s="20" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F32" s="20" t="n">
         <v>0</v>
       </c>
       <c r="G32" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H32" s="22" t="n">
-        <v>-3.92</v>
-      </c>
-      <c r="I32" s="24" t="n">
-        <v>6.1</v>
+        <v>3</v>
+      </c>
+      <c r="H32" s="24" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="I32" s="22" t="n">
+        <v>-2.05</v>
       </c>
       <c r="J32" s="23" t="inlineStr">
         <is>
-          <t>중요공시 1건 / Google 급상승 검색어 등장 (KR)</t>
+          <t>중요공시 4건 / 중요공시 7일 +300%</t>
         </is>
       </c>
       <c r="K32" s="23" t="inlineStr">
         <is>
-          <t>Google, 공시</t>
+          <t>공시</t>
         </is>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
       <c r="A33" s="20" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B33" s="20" t="n">
@@ -1735,14 +1729,14 @@
       </c>
       <c r="C33" s="21" t="inlineStr">
         <is>
-          <t>삼성전자우</t>
+          <t>게임</t>
         </is>
       </c>
       <c r="D33" s="20" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E33" s="20" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F33" s="20" t="n">
         <v>0</v>
@@ -1750,27 +1744,25 @@
       <c r="G33" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H33" s="22" t="n">
-        <v>-2.84</v>
-      </c>
-      <c r="I33" s="24" t="n">
-        <v>7.25</v>
+      <c r="H33" s="20" t="n">
+        <v/>
+      </c>
+      <c r="I33" s="20" t="n">
+        <v/>
       </c>
       <c r="J33" s="23" t="inlineStr">
         <is>
-          <t>Google 급상승 검색어 등장 (KR)</t>
-        </is>
-      </c>
-      <c r="K33" s="23" t="inlineStr">
-        <is>
-          <t>Google</t>
-        </is>
+          <t>한국경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K33" s="23" t="n">
+        <v/>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
       <c r="A34" s="20" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B34" s="20" t="n">
@@ -1778,14 +1770,14 @@
       </c>
       <c r="C34" s="21" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>카카오</t>
         </is>
       </c>
       <c r="D34" s="20" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E34" s="20" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F34" s="20" t="n">
         <v>0</v>
@@ -1794,26 +1786,24 @@
         <v>0</v>
       </c>
       <c r="H34" s="22" t="n">
-        <v>-0.54</v>
-      </c>
-      <c r="I34" s="24" t="n">
-        <v>2.42</v>
+        <v>-2.52</v>
+      </c>
+      <c r="I34" s="22" t="n">
+        <v>-9.69</v>
       </c>
       <c r="J34" s="23" t="inlineStr">
         <is>
-          <t>Google 급상승 검색어 등장 (KR)</t>
-        </is>
-      </c>
-      <c r="K34" s="23" t="inlineStr">
-        <is>
-          <t>Google</t>
-        </is>
+          <t>한국경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K34" s="23" t="n">
+        <v/>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
       <c r="A35" s="20" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B35" s="20" t="n">
@@ -1821,42 +1811,40 @@
       </c>
       <c r="C35" s="21" t="inlineStr">
         <is>
-          <t>진원생명과학</t>
+          <t>두산로보틱스</t>
         </is>
       </c>
       <c r="D35" s="20" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E35" s="20" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F35" s="20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G35" s="20" t="n">
         <v>0</v>
       </c>
       <c r="H35" s="22" t="n">
-        <v>-17.67</v>
+        <v>-1.38</v>
       </c>
       <c r="I35" s="22" t="n">
-        <v>-24.4</v>
+        <v>-9.869999999999999</v>
       </c>
       <c r="J35" s="23" t="inlineStr">
         <is>
-          <t>중요공시 3건 / 중요공시 3일 +50%</t>
-        </is>
-      </c>
-      <c r="K35" s="23" t="inlineStr">
-        <is>
-          <t>공시</t>
-        </is>
+          <t>매일경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K35" s="23" t="n">
+        <v/>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
       <c r="A36" s="20" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B36" s="20" t="n">
@@ -1864,14 +1852,14 @@
       </c>
       <c r="C36" s="21" t="inlineStr">
         <is>
-          <t>삼성전기</t>
+          <t>삼성생명</t>
         </is>
       </c>
       <c r="D36" s="20" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E36" s="20" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F36" s="20" t="n">
         <v>0</v>
@@ -1879,27 +1867,27 @@
       <c r="G36" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H36" s="24" t="n">
-        <v>3.18</v>
+      <c r="H36" s="22" t="n">
+        <v>-9.359999999999999</v>
       </c>
       <c r="I36" s="24" t="n">
-        <v>32.44</v>
+        <v>6.5</v>
       </c>
       <c r="J36" s="23" t="inlineStr">
         <is>
-          <t>Google 급상승 검색어 등장 (KR)</t>
+          <t>네이버뉴스 헤드라인 언급 / 매일경제 헤드라인 언급</t>
         </is>
       </c>
       <c r="K36" s="23" t="inlineStr">
         <is>
-          <t>Google</t>
+          <t>네이버</t>
         </is>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
       <c r="A37" s="20" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B37" s="20" t="n">
@@ -1907,14 +1895,14 @@
       </c>
       <c r="C37" s="21" t="inlineStr">
         <is>
-          <t>삼성물산</t>
+          <t>유안타증권</t>
         </is>
       </c>
       <c r="D37" s="20" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E37" s="20" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F37" s="20" t="n">
         <v>0</v>
@@ -1922,27 +1910,25 @@
       <c r="G37" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H37" s="24" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="I37" s="24" t="n">
-        <v>13.77</v>
+      <c r="H37" s="22" t="n">
+        <v>-2.95</v>
+      </c>
+      <c r="I37" s="22" t="n">
+        <v>-8.09</v>
       </c>
       <c r="J37" s="23" t="inlineStr">
         <is>
-          <t>Google 급상승 검색어 등장 (KR)</t>
-        </is>
-      </c>
-      <c r="K37" s="23" t="inlineStr">
-        <is>
-          <t>Google</t>
-        </is>
+          <t>매일경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K37" s="23" t="n">
+        <v/>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
       <c r="A38" s="20" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B38" s="20" t="n">
@@ -1950,7 +1936,7 @@
       </c>
       <c r="C38" s="21" t="inlineStr">
         <is>
-          <t>삼성SDI</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="D38" s="20" t="n">
@@ -1965,27 +1951,27 @@
       <c r="G38" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H38" s="24" t="n">
-        <v>6.32</v>
-      </c>
-      <c r="I38" s="24" t="n">
-        <v>2.97</v>
+      <c r="H38" s="22" t="n">
+        <v>-5.73</v>
+      </c>
+      <c r="I38" s="22" t="n">
+        <v>-29.25</v>
       </c>
       <c r="J38" s="23" t="inlineStr">
         <is>
-          <t>Google 급상승 검색어 등장 (KR)</t>
+          <t>네이버 검색 당일 +122% / 한국경제 헤드라인 언급</t>
         </is>
       </c>
       <c r="K38" s="23" t="inlineStr">
         <is>
-          <t>Google</t>
+          <t>네이버</t>
         </is>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
       <c r="A39" s="20" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B39" s="20" t="n">
@@ -1993,14 +1979,14 @@
       </c>
       <c r="C39" s="21" t="inlineStr">
         <is>
-          <t>삼성제약</t>
+          <t>삼화네트웍스</t>
         </is>
       </c>
       <c r="D39" s="20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E39" s="20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F39" s="20" t="n">
         <v>0</v>
@@ -2008,27 +1994,27 @@
       <c r="G39" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H39" s="22" t="n">
-        <v>-3.9</v>
+      <c r="H39" s="24" t="n">
+        <v>5.24</v>
       </c>
       <c r="I39" s="24" t="n">
-        <v>3.92</v>
+        <v>7.86</v>
       </c>
       <c r="J39" s="23" t="inlineStr">
         <is>
-          <t>Google 급상승 검색어 등장 (KR)</t>
+          <t>네이버 검색 당일 +346% / 중요공시 2건</t>
         </is>
       </c>
       <c r="K39" s="23" t="inlineStr">
         <is>
-          <t>Google</t>
+          <t>공시, 네이버</t>
         </is>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
       <c r="A40" s="20" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B40" s="20" t="n">
@@ -2036,14 +2022,14 @@
       </c>
       <c r="C40" s="21" t="inlineStr">
         <is>
-          <t>삼성생명</t>
+          <t>노블엠앤비</t>
         </is>
       </c>
       <c r="D40" s="20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E40" s="20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F40" s="20" t="n">
         <v>0</v>
@@ -2051,27 +2037,27 @@
       <c r="G40" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H40" s="24" t="n">
-        <v>5.97</v>
-      </c>
-      <c r="I40" s="24" t="n">
-        <v>28.92</v>
+      <c r="H40" s="22" t="n">
+        <v>-94.16</v>
+      </c>
+      <c r="I40" s="22" t="n">
+        <v>-94.16</v>
       </c>
       <c r="J40" s="23" t="inlineStr">
         <is>
-          <t>Google 급상승 검색어 등장 (KR)</t>
+          <t>네이버 검색 당일 +140% / 중요공시 2건</t>
         </is>
       </c>
       <c r="K40" s="23" t="inlineStr">
         <is>
-          <t>Google</t>
+          <t>공시, 네이버</t>
         </is>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
       <c r="A41" s="20" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B41" s="20" t="n">
@@ -2079,14 +2065,14 @@
       </c>
       <c r="C41" s="21" t="inlineStr">
         <is>
-          <t>삼성증권</t>
+          <t>다스코</t>
         </is>
       </c>
       <c r="D41" s="20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E41" s="20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F41" s="20" t="n">
         <v>0</v>
@@ -2095,26 +2081,26 @@
         <v>0</v>
       </c>
       <c r="H41" s="22" t="n">
-        <v>-0.25</v>
+        <v>-15.71</v>
       </c>
       <c r="I41" s="24" t="n">
-        <v>0.08</v>
+        <v>5.22</v>
       </c>
       <c r="J41" s="23" t="inlineStr">
         <is>
-          <t>Google 급상승 검색어 등장 (KR)</t>
+          <t>네이버 검색 당일 +110% / 중요공시 1건</t>
         </is>
       </c>
       <c r="K41" s="23" t="inlineStr">
         <is>
-          <t>Google</t>
+          <t>공시, 네이버</t>
         </is>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
       <c r="A42" s="20" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B42" s="20" t="n">
@@ -2122,14 +2108,14 @@
       </c>
       <c r="C42" s="21" t="inlineStr">
         <is>
-          <t>삼성에스디에스</t>
+          <t>대원전선</t>
         </is>
       </c>
       <c r="D42" s="20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E42" s="20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F42" s="20" t="n">
         <v>0</v>
@@ -2138,26 +2124,26 @@
         <v>0</v>
       </c>
       <c r="H42" s="22" t="n">
-        <v>-4.07</v>
+        <v>-6.67</v>
       </c>
       <c r="I42" s="22" t="n">
-        <v>-10.55</v>
+        <v>-3.09</v>
       </c>
       <c r="J42" s="23" t="inlineStr">
         <is>
-          <t>Google 급상승 검색어 등장 (KR)</t>
+          <t>네이버 검색 당일 +104% / 중요공시 1건</t>
         </is>
       </c>
       <c r="K42" s="23" t="inlineStr">
         <is>
-          <t>Google</t>
+          <t>공시, 네이버</t>
         </is>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1">
       <c r="A43" s="20" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B43" s="20" t="n">
@@ -2165,14 +2151,14 @@
       </c>
       <c r="C43" s="21" t="inlineStr">
         <is>
-          <t>한화</t>
+          <t>스피어</t>
         </is>
       </c>
       <c r="D43" s="20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E43" s="20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F43" s="20" t="n">
         <v>0</v>
@@ -2181,24 +2167,26 @@
         <v>0</v>
       </c>
       <c r="H43" s="22" t="n">
-        <v>-4.71</v>
+        <v>-12.28</v>
       </c>
       <c r="I43" s="22" t="n">
-        <v>-0.95</v>
+        <v>-37.07</v>
       </c>
       <c r="J43" s="23" t="inlineStr">
         <is>
-          <t>매일경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K43" s="23" t="n">
-        <v/>
+          <t>중요공시 2건 / 매일경제 기사 언급 / 매일경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K43" s="23" t="inlineStr">
+        <is>
+          <t>공시</t>
+        </is>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
       <c r="A44" s="20" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B44" s="20" t="n">
@@ -2206,42 +2194,42 @@
       </c>
       <c r="C44" s="21" t="inlineStr">
         <is>
-          <t>남화토건</t>
+          <t>센서뷰</t>
         </is>
       </c>
       <c r="D44" s="20" t="n">
         <v>4</v>
       </c>
       <c r="E44" s="20" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F44" s="20" t="n">
         <v>0</v>
       </c>
       <c r="G44" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H44" s="24" t="n">
-        <v>12.73</v>
-      </c>
-      <c r="I44" s="24" t="n">
-        <v>45.92</v>
+        <v>3</v>
+      </c>
+      <c r="H44" s="22" t="n">
+        <v>-7.33</v>
+      </c>
+      <c r="I44" s="22" t="n">
+        <v>-13.48</v>
       </c>
       <c r="J44" s="23" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +921% / 중요공시 1건</t>
+          <t>중요공시 2건 / 중요공시 7일 +100%</t>
         </is>
       </c>
       <c r="K44" s="23" t="inlineStr">
         <is>
-          <t>네이버, 공시</t>
+          <t>공시</t>
         </is>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
       <c r="A45" s="20" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B45" s="20" t="n">
@@ -2249,40 +2237,42 @@
       </c>
       <c r="C45" s="21" t="inlineStr">
         <is>
-          <t>HMM</t>
+          <t>HJ중공업</t>
         </is>
       </c>
       <c r="D45" s="20" t="n">
         <v>4</v>
       </c>
       <c r="E45" s="20" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F45" s="20" t="n">
         <v>0</v>
       </c>
       <c r="G45" s="20" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H45" s="22" t="n">
-        <v>-1.47</v>
-      </c>
-      <c r="I45" s="24" t="n">
-        <v>0.5</v>
+        <v>-4.04</v>
+      </c>
+      <c r="I45" s="22" t="n">
+        <v>-8.15</v>
       </c>
       <c r="J45" s="23" t="inlineStr">
         <is>
-          <t>매일경제 기사 언급 / 매일경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K45" s="23" t="n">
-        <v/>
+          <t>중요공시 2건 / 중요공시 7일 +100%</t>
+        </is>
+      </c>
+      <c r="K45" s="23" t="inlineStr">
+        <is>
+          <t>공시</t>
+        </is>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
       <c r="A46" s="20" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B46" s="20" t="n">
@@ -2290,210 +2280,214 @@
       </c>
       <c r="C46" s="21" t="inlineStr">
         <is>
-          <t>센서뷰</t>
+          <t>원전</t>
         </is>
       </c>
       <c r="D46" s="20" t="n">
         <v>4</v>
       </c>
       <c r="E46" s="20" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F46" s="20" t="n">
         <v>0</v>
       </c>
       <c r="G46" s="20" t="n">
-        <v>3</v>
-      </c>
-      <c r="H46" s="22" t="n">
-        <v>-5.11</v>
-      </c>
-      <c r="I46" s="22" t="n">
-        <v>-12.29</v>
+        <v>0</v>
+      </c>
+      <c r="H46" s="20" t="n">
+        <v/>
+      </c>
+      <c r="I46" s="20" t="n">
+        <v/>
       </c>
       <c r="J46" s="23" t="inlineStr">
         <is>
-          <t>중요공시 2건 / 중요공시 7일 +100%</t>
+          <t>네이버뉴스 기사 언급 / 한국경제 헤드라인 언급</t>
         </is>
       </c>
       <c r="K46" s="23" t="inlineStr">
         <is>
-          <t>공시</t>
+          <t>네이버</t>
         </is>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
-      <c r="A47" s="20" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
-        </is>
-      </c>
-      <c r="B47" s="20" t="n">
+      <c r="A47" s="25" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B47" s="25" t="n">
         <v>34</v>
       </c>
-      <c r="C47" s="21" t="inlineStr">
-        <is>
-          <t>파두</t>
-        </is>
-      </c>
-      <c r="D47" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="E47" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="F47" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G47" s="20" t="n">
-        <v>3</v>
-      </c>
-      <c r="H47" s="22" t="n">
-        <v>-2.5</v>
-      </c>
-      <c r="I47" s="24" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="J47" s="23" t="inlineStr">
-        <is>
-          <t>중요공시 2건 / 중요공시 7일 +100%</t>
-        </is>
-      </c>
-      <c r="K47" s="23" t="inlineStr">
-        <is>
-          <t>공시</t>
+      <c r="C47" s="26" t="inlineStr">
+        <is>
+          <t>강동씨앤엘</t>
+        </is>
+      </c>
+      <c r="D47" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="E47" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="F47" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G47" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H47" s="27" t="n">
+        <v>-12.22</v>
+      </c>
+      <c r="I47" s="28" t="n">
+        <v>79.66</v>
+      </c>
+      <c r="J47" s="29" t="inlineStr">
+        <is>
+          <t>네이버 검색 당일 +1615%</t>
+        </is>
+      </c>
+      <c r="K47" s="29" t="inlineStr">
+        <is>
+          <t>네이버</t>
         </is>
       </c>
     </row>
     <row r="48" ht="18" customHeight="1">
-      <c r="A48" s="20" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
-        </is>
-      </c>
-      <c r="B48" s="20" t="n">
+      <c r="A48" s="25" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B48" s="25" t="n">
         <v>35</v>
       </c>
-      <c r="C48" s="21" t="inlineStr">
-        <is>
-          <t>현대로템</t>
-        </is>
-      </c>
-      <c r="D48" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="E48" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="F48" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G48" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H48" s="22" t="n">
-        <v>-2.13</v>
-      </c>
-      <c r="I48" s="22" t="n">
-        <v>-0.72</v>
-      </c>
-      <c r="J48" s="23" t="inlineStr">
-        <is>
-          <t>중요공시 1건 / 매일경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K48" s="23" t="inlineStr">
-        <is>
-          <t>공시</t>
+      <c r="C48" s="26" t="inlineStr">
+        <is>
+          <t>JW신약</t>
+        </is>
+      </c>
+      <c r="D48" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="E48" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="F48" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G48" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H48" s="28" t="n">
+        <v>16.92</v>
+      </c>
+      <c r="I48" s="28" t="n">
+        <v>53.8</v>
+      </c>
+      <c r="J48" s="29" t="inlineStr">
+        <is>
+          <t>네이버 검색 당일 +1499%</t>
+        </is>
+      </c>
+      <c r="K48" s="29" t="inlineStr">
+        <is>
+          <t>네이버</t>
         </is>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1">
-      <c r="A49" s="20" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
-        </is>
-      </c>
-      <c r="B49" s="20" t="n">
+      <c r="A49" s="25" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B49" s="25" t="n">
         <v>36</v>
       </c>
-      <c r="C49" s="21" t="inlineStr">
-        <is>
-          <t>태양광</t>
-        </is>
-      </c>
-      <c r="D49" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="E49" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="F49" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G49" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H49" s="20" t="n">
-        <v/>
-      </c>
-      <c r="I49" s="20" t="n">
-        <v/>
-      </c>
-      <c r="J49" s="23" t="inlineStr">
-        <is>
-          <t>매일경제 헤드라인 언급 / 매일경제 기사 언급</t>
-        </is>
-      </c>
-      <c r="K49" s="23" t="n">
-        <v/>
+      <c r="C49" s="26" t="inlineStr">
+        <is>
+          <t>남화토건</t>
+        </is>
+      </c>
+      <c r="D49" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="E49" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="F49" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G49" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H49" s="27" t="n">
+        <v>-10.33</v>
+      </c>
+      <c r="I49" s="28" t="n">
+        <v>31.77</v>
+      </c>
+      <c r="J49" s="29" t="inlineStr">
+        <is>
+          <t>네이버 검색 당일 +1018%</t>
+        </is>
+      </c>
+      <c r="K49" s="29" t="inlineStr">
+        <is>
+          <t>네이버</t>
+        </is>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
-      <c r="A50" s="20" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
-        </is>
-      </c>
-      <c r="B50" s="20" t="n">
+      <c r="A50" s="25" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B50" s="25" t="n">
         <v>37</v>
       </c>
-      <c r="C50" s="21" t="inlineStr">
-        <is>
-          <t>DB</t>
-        </is>
-      </c>
-      <c r="D50" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="E50" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="F50" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G50" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H50" s="22" t="n">
-        <v>-2.39</v>
-      </c>
-      <c r="I50" s="22" t="n">
-        <v>-6.55</v>
-      </c>
-      <c r="J50" s="23" t="inlineStr">
-        <is>
-          <t>매일경제 헤드라인 언급 / 매일경제 기사 언급</t>
-        </is>
-      </c>
-      <c r="K50" s="23" t="n">
-        <v/>
+      <c r="C50" s="26" t="inlineStr">
+        <is>
+          <t>삼익제약</t>
+        </is>
+      </c>
+      <c r="D50" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="E50" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="F50" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G50" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H50" s="28" t="n">
+        <v>6.54</v>
+      </c>
+      <c r="I50" s="28" t="n">
+        <v>16.36</v>
+      </c>
+      <c r="J50" s="29" t="inlineStr">
+        <is>
+          <t>네이버 검색 당일 +866%</t>
+        </is>
+      </c>
+      <c r="K50" s="29" t="inlineStr">
+        <is>
+          <t>네이버</t>
+        </is>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
       <c r="A51" s="25" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B51" s="25" t="n">
@@ -2501,7 +2495,7 @@
       </c>
       <c r="C51" s="26" t="inlineStr">
         <is>
-          <t>강동씨앤엘</t>
+          <t>TS트릴리온</t>
         </is>
       </c>
       <c r="D51" s="25" t="n">
@@ -2516,18 +2510,18 @@
       <c r="G51" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H51" s="27" t="n">
-        <v>29.91</v>
+      <c r="H51" s="28" t="n">
+        <v>6.7</v>
       </c>
       <c r="I51" s="27" t="n">
-        <v>121.56</v>
-      </c>
-      <c r="J51" s="28" t="inlineStr">
-        <is>
-          <t>네이버 검색 당일 +1463%</t>
-        </is>
-      </c>
-      <c r="K51" s="28" t="inlineStr">
+        <v>-15.51</v>
+      </c>
+      <c r="J51" s="29" t="inlineStr">
+        <is>
+          <t>네이버 검색 당일 +497%</t>
+        </is>
+      </c>
+      <c r="K51" s="29" t="inlineStr">
         <is>
           <t>네이버</t>
         </is>
@@ -2536,7 +2530,7 @@
     <row r="52" ht="18" customHeight="1">
       <c r="A52" s="25" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B52" s="25" t="n">
@@ -2544,7 +2538,7 @@
       </c>
       <c r="C52" s="26" t="inlineStr">
         <is>
-          <t>JW신약</t>
+          <t>예스티</t>
         </is>
       </c>
       <c r="D52" s="25" t="n">
@@ -2559,18 +2553,18 @@
       <c r="G52" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H52" s="27" t="n">
-        <v>13.08</v>
-      </c>
-      <c r="I52" s="27" t="n">
-        <v>70.94</v>
-      </c>
-      <c r="J52" s="28" t="inlineStr">
-        <is>
-          <t>네이버 검색 당일 +1428%</t>
-        </is>
-      </c>
-      <c r="K52" s="28" t="inlineStr">
+      <c r="H52" s="28" t="n">
+        <v>10.63</v>
+      </c>
+      <c r="I52" s="28" t="n">
+        <v>20.88</v>
+      </c>
+      <c r="J52" s="29" t="inlineStr">
+        <is>
+          <t>네이버 검색 당일 +497%</t>
+        </is>
+      </c>
+      <c r="K52" s="29" t="inlineStr">
         <is>
           <t>네이버</t>
         </is>
@@ -2579,7 +2573,7 @@
     <row r="53" ht="18" customHeight="1">
       <c r="A53" s="25" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B53" s="25" t="n">
@@ -2587,7 +2581,7 @@
       </c>
       <c r="C53" s="26" t="inlineStr">
         <is>
-          <t>삼익제약</t>
+          <t>현대약품</t>
         </is>
       </c>
       <c r="D53" s="25" t="n">
@@ -2602,18 +2596,18 @@
       <c r="G53" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H53" s="27" t="n">
-        <v>29.98</v>
-      </c>
-      <c r="I53" s="27" t="n">
-        <v>41.82</v>
-      </c>
-      <c r="J53" s="28" t="inlineStr">
-        <is>
-          <t>네이버 검색 당일 +800%</t>
-        </is>
-      </c>
-      <c r="K53" s="28" t="inlineStr">
+      <c r="H53" s="28" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="I53" s="28" t="n">
+        <v>10.48</v>
+      </c>
+      <c r="J53" s="29" t="inlineStr">
+        <is>
+          <t>네이버 검색 당일 +446%</t>
+        </is>
+      </c>
+      <c r="K53" s="29" t="inlineStr">
         <is>
           <t>네이버</t>
         </is>
@@ -2622,7 +2616,7 @@
     <row r="54" ht="18" customHeight="1">
       <c r="A54" s="25" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B54" s="25" t="n">
@@ -2630,7 +2624,7 @@
       </c>
       <c r="C54" s="26" t="inlineStr">
         <is>
-          <t>현대약품</t>
+          <t>위더스제약</t>
         </is>
       </c>
       <c r="D54" s="25" t="n">
@@ -2645,18 +2639,18 @@
       <c r="G54" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H54" s="29" t="n">
-        <v>-4.12</v>
-      </c>
-      <c r="I54" s="27" t="n">
-        <v>42.23</v>
-      </c>
-      <c r="J54" s="28" t="inlineStr">
-        <is>
-          <t>네이버 검색 당일 +429%</t>
-        </is>
-      </c>
-      <c r="K54" s="28" t="inlineStr">
+      <c r="H54" s="27" t="n">
+        <v>-3.95</v>
+      </c>
+      <c r="I54" s="28" t="n">
+        <v>4.03</v>
+      </c>
+      <c r="J54" s="29" t="inlineStr">
+        <is>
+          <t>네이버 검색 당일 +445%</t>
+        </is>
+      </c>
+      <c r="K54" s="29" t="inlineStr">
         <is>
           <t>네이버</t>
         </is>
@@ -2665,7 +2659,7 @@
     <row r="55" ht="18" customHeight="1">
       <c r="A55" s="25" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B55" s="25" t="n">
@@ -2673,7 +2667,7 @@
       </c>
       <c r="C55" s="26" t="inlineStr">
         <is>
-          <t>위더스제약</t>
+          <t>삼화전자</t>
         </is>
       </c>
       <c r="D55" s="25" t="n">
@@ -2689,17 +2683,17 @@
         <v>0</v>
       </c>
       <c r="H55" s="27" t="n">
-        <v>13.59</v>
-      </c>
-      <c r="I55" s="27" t="n">
-        <v>33.03</v>
-      </c>
-      <c r="J55" s="28" t="inlineStr">
-        <is>
-          <t>네이버 검색 당일 +422%</t>
-        </is>
-      </c>
-      <c r="K55" s="28" t="inlineStr">
+        <v>-14.82</v>
+      </c>
+      <c r="I55" s="28" t="n">
+        <v>13.91</v>
+      </c>
+      <c r="J55" s="29" t="inlineStr">
+        <is>
+          <t>네이버 검색 당일 +428%</t>
+        </is>
+      </c>
+      <c r="K55" s="29" t="inlineStr">
         <is>
           <t>네이버</t>
         </is>
@@ -2708,7 +2702,7 @@
     <row r="56" ht="18" customHeight="1">
       <c r="A56" s="25" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B56" s="25" t="n">
@@ -2716,7 +2710,7 @@
       </c>
       <c r="C56" s="26" t="inlineStr">
         <is>
-          <t>삼화전자</t>
+          <t>한울반도체</t>
         </is>
       </c>
       <c r="D56" s="25" t="n">
@@ -2731,18 +2725,18 @@
       <c r="G56" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H56" s="27" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="I56" s="27" t="n">
-        <v>73.59</v>
-      </c>
-      <c r="J56" s="28" t="inlineStr">
-        <is>
-          <t>네이버 검색 당일 +412%</t>
-        </is>
-      </c>
-      <c r="K56" s="28" t="inlineStr">
+      <c r="H56" s="28" t="n">
+        <v>29.91</v>
+      </c>
+      <c r="I56" s="28" t="n">
+        <v>110.65</v>
+      </c>
+      <c r="J56" s="29" t="inlineStr">
+        <is>
+          <t>네이버 검색 당일 +406%</t>
+        </is>
+      </c>
+      <c r="K56" s="29" t="inlineStr">
         <is>
           <t>네이버</t>
         </is>
@@ -2751,7 +2745,7 @@
     <row r="57" ht="18" customHeight="1">
       <c r="A57" s="25" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B57" s="25" t="n">
@@ -2774,18 +2768,18 @@
       <c r="G57" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H57" s="27" t="n">
-        <v>29.88</v>
-      </c>
-      <c r="I57" s="27" t="n">
-        <v>58.36</v>
-      </c>
-      <c r="J57" s="28" t="inlineStr">
-        <is>
-          <t>네이버 검색 당일 +237%</t>
-        </is>
-      </c>
-      <c r="K57" s="28" t="inlineStr">
+      <c r="H57" s="28" t="n">
+        <v>9.859999999999999</v>
+      </c>
+      <c r="I57" s="28" t="n">
+        <v>64.90000000000001</v>
+      </c>
+      <c r="J57" s="29" t="inlineStr">
+        <is>
+          <t>네이버 검색 당일 +289%</t>
+        </is>
+      </c>
+      <c r="K57" s="29" t="inlineStr">
         <is>
           <t>네이버</t>
         </is>
@@ -2794,7 +2788,7 @@
     <row r="58" ht="18" customHeight="1">
       <c r="A58" s="25" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B58" s="25" t="n">
@@ -2802,7 +2796,7 @@
       </c>
       <c r="C58" s="26" t="inlineStr">
         <is>
-          <t>율촌</t>
+          <t>하이스틸</t>
         </is>
       </c>
       <c r="D58" s="25" t="n">
@@ -2817,18 +2811,18 @@
       <c r="G58" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H58" s="29" t="n">
-        <v>-13.55</v>
-      </c>
-      <c r="I58" s="27" t="n">
-        <v>30.73</v>
-      </c>
-      <c r="J58" s="28" t="inlineStr">
-        <is>
-          <t>네이버 검색 당일 +208%</t>
-        </is>
-      </c>
-      <c r="K58" s="28" t="inlineStr">
+      <c r="H58" s="28" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="I58" s="28" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="J58" s="29" t="inlineStr">
+        <is>
+          <t>네이버 검색 당일 +222%</t>
+        </is>
+      </c>
+      <c r="K58" s="29" t="inlineStr">
         <is>
           <t>네이버</t>
         </is>
@@ -2837,7 +2831,7 @@
     <row r="59" ht="18" customHeight="1">
       <c r="A59" s="25" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B59" s="25" t="n">
@@ -2845,7 +2839,7 @@
       </c>
       <c r="C59" s="26" t="inlineStr">
         <is>
-          <t>성문전자</t>
+          <t>율촌</t>
         </is>
       </c>
       <c r="D59" s="25" t="n">
@@ -2860,18 +2854,18 @@
       <c r="G59" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H59" s="27" t="n">
-        <v>4.43</v>
-      </c>
-      <c r="I59" s="27" t="n">
-        <v>40.24</v>
-      </c>
-      <c r="J59" s="28" t="inlineStr">
-        <is>
-          <t>네이버 검색 당일 +187%</t>
-        </is>
-      </c>
-      <c r="K59" s="28" t="inlineStr">
+      <c r="H59" s="28" t="n">
+        <v>9.029999999999999</v>
+      </c>
+      <c r="I59" s="28" t="n">
+        <v>38.23</v>
+      </c>
+      <c r="J59" s="29" t="inlineStr">
+        <is>
+          <t>네이버 검색 당일 +219%</t>
+        </is>
+      </c>
+      <c r="K59" s="29" t="inlineStr">
         <is>
           <t>네이버</t>
         </is>
@@ -2880,7 +2874,7 @@
     <row r="60" ht="18" customHeight="1">
       <c r="A60" s="25" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B60" s="25" t="n">
@@ -2888,7 +2882,7 @@
       </c>
       <c r="C60" s="26" t="inlineStr">
         <is>
-          <t>메리츠제2호스팩</t>
+          <t>제이앤티씨</t>
         </is>
       </c>
       <c r="D60" s="25" t="n">
@@ -2903,18 +2897,18 @@
       <c r="G60" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H60" s="25" t="n">
-        <v/>
-      </c>
-      <c r="I60" s="25" t="n">
-        <v/>
-      </c>
-      <c r="J60" s="28" t="inlineStr">
-        <is>
-          <t>네이버 검색 당일 +186%</t>
-        </is>
-      </c>
-      <c r="K60" s="28" t="inlineStr">
+      <c r="H60" s="28" t="n">
+        <v>8.81</v>
+      </c>
+      <c r="I60" s="28" t="n">
+        <v>33.63</v>
+      </c>
+      <c r="J60" s="29" t="inlineStr">
+        <is>
+          <t>네이버 검색 당일 +218%</t>
+        </is>
+      </c>
+      <c r="K60" s="29" t="inlineStr">
         <is>
           <t>네이버</t>
         </is>
@@ -2923,7 +2917,7 @@
     <row r="61" ht="18" customHeight="1">
       <c r="A61" s="25" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B61" s="25" t="n">
@@ -2931,7 +2925,7 @@
       </c>
       <c r="C61" s="26" t="inlineStr">
         <is>
-          <t>피앤에스로보틱스</t>
+          <t>성문전자</t>
         </is>
       </c>
       <c r="D61" s="25" t="n">
@@ -2946,18 +2940,18 @@
       <c r="G61" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H61" s="27" t="n">
-        <v>22.04</v>
-      </c>
-      <c r="I61" s="27" t="n">
-        <v>20.74</v>
-      </c>
-      <c r="J61" s="28" t="inlineStr">
-        <is>
-          <t>네이버 검색 당일 +182%</t>
-        </is>
-      </c>
-      <c r="K61" s="28" t="inlineStr">
+      <c r="H61" s="28" t="n">
+        <v>9</v>
+      </c>
+      <c r="I61" s="28" t="n">
+        <v>51.42</v>
+      </c>
+      <c r="J61" s="29" t="inlineStr">
+        <is>
+          <t>네이버 검색 당일 +197%</t>
+        </is>
+      </c>
+      <c r="K61" s="29" t="inlineStr">
         <is>
           <t>네이버</t>
         </is>
@@ -2966,7 +2960,7 @@
     <row r="62" ht="18" customHeight="1">
       <c r="A62" s="25" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B62" s="25" t="n">
@@ -2974,7 +2968,7 @@
       </c>
       <c r="C62" s="26" t="inlineStr">
         <is>
-          <t>티웨이홀딩스</t>
+          <t>메리츠제2호스팩</t>
         </is>
       </c>
       <c r="D62" s="25" t="n">
@@ -2989,18 +2983,18 @@
       <c r="G62" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H62" s="29" t="n">
-        <v>-7.09</v>
+      <c r="H62" s="27" t="n">
+        <v>-0.8100000000000001</v>
       </c>
       <c r="I62" s="27" t="n">
-        <v>26.88</v>
-      </c>
-      <c r="J62" s="28" t="inlineStr">
-        <is>
-          <t>네이버 검색 당일 +181%</t>
-        </is>
-      </c>
-      <c r="K62" s="28" t="inlineStr">
+        <v>-0.8100000000000001</v>
+      </c>
+      <c r="J62" s="29" t="inlineStr">
+        <is>
+          <t>네이버 검색 당일 +194%</t>
+        </is>
+      </c>
+      <c r="K62" s="29" t="inlineStr">
         <is>
           <t>네이버</t>
         </is>
@@ -3009,7 +3003,7 @@
     <row r="63" ht="18" customHeight="1">
       <c r="A63" s="25" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B63" s="25" t="n">
@@ -3017,7 +3011,7 @@
       </c>
       <c r="C63" s="26" t="inlineStr">
         <is>
-          <t>부국철강</t>
+          <t>티웨이홀딩스</t>
         </is>
       </c>
       <c r="D63" s="25" t="n">
@@ -3032,18 +3026,18 @@
       <c r="G63" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H63" s="29" t="n">
-        <v>-13.76</v>
+      <c r="H63" s="27" t="n">
+        <v>-7.91</v>
       </c>
       <c r="I63" s="27" t="n">
-        <v>3.49</v>
-      </c>
-      <c r="J63" s="28" t="inlineStr">
-        <is>
-          <t>네이버 검색 당일 +170%</t>
-        </is>
-      </c>
-      <c r="K63" s="28" t="inlineStr">
+        <v>-9.94</v>
+      </c>
+      <c r="J63" s="29" t="inlineStr">
+        <is>
+          <t>네이버 검색 당일 +188%</t>
+        </is>
+      </c>
+      <c r="K63" s="29" t="inlineStr">
         <is>
           <t>네이버</t>
         </is>
@@ -3142,22 +3136,22 @@
         <v>1</v>
       </c>
       <c r="C3" s="25" t="n">
-        <v>82</v>
+        <v>62</v>
       </c>
       <c r="D3" s="25" t="n">
-        <v>82</v>
+        <v>62</v>
       </c>
       <c r="E3" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F3" s="25" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G3" s="25" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="H3" s="25" t="n"/>
@@ -3166,71 +3160,71 @@
     <row r="4" ht="18" customHeight="1">
       <c r="A4" s="26" t="inlineStr">
         <is>
-          <t>SK</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B4" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C4" s="25" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D4" s="25" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E4" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F4" s="25" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G4" s="25" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
-        </is>
-      </c>
-      <c r="H4" s="27" t="n">
-        <v>5.39</v>
-      </c>
-      <c r="I4" s="27" t="n">
-        <v>22.09</v>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="H4" s="28" t="n">
+        <v>5.61</v>
+      </c>
+      <c r="I4" s="28" t="n">
+        <v>27.58</v>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="26" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B5" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C5" s="25" t="n">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="D5" s="25" t="n">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="E5" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F5" s="25" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G5" s="25" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="H5" s="27" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="I5" s="27" t="n">
-        <v>28.56</v>
+        <v>-0.14</v>
+      </c>
+      <c r="I5" s="28" t="n">
+        <v>4.9</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
@@ -3243,158 +3237,154 @@
         <v>1</v>
       </c>
       <c r="C6" s="25" t="n">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="D6" s="25" t="n">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="E6" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F6" s="25" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G6" s="25" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
-        </is>
-      </c>
-      <c r="H6" s="29" t="n">
-        <v>-0.91</v>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="H6" s="28" t="n">
+        <v>0.92</v>
       </c>
       <c r="I6" s="27" t="n">
-        <v>2.25</v>
+        <v>-7.18</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
       <c r="A7" s="26" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>바이오</t>
         </is>
       </c>
       <c r="B7" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C7" s="25" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="D7" s="25" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="E7" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F7" s="25" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G7" s="25" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
-        </is>
-      </c>
-      <c r="H7" s="29" t="n">
-        <v>-2.34</v>
-      </c>
-      <c r="I7" s="27" t="n">
-        <v>9.77</v>
-      </c>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="H7" s="25" t="n"/>
+      <c r="I7" s="25" t="n"/>
     </row>
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="26" t="inlineStr">
         <is>
-          <t>현대차</t>
+          <t>인공지능</t>
         </is>
       </c>
       <c r="B8" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C8" s="25" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="D8" s="25" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="E8" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F8" s="25" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G8" s="25" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
-        </is>
-      </c>
-      <c r="H8" s="27" t="n">
-        <v>2</v>
-      </c>
-      <c r="I8" s="27" t="n">
-        <v>0.99</v>
-      </c>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="H8" s="25" t="n"/>
+      <c r="I8" s="25" t="n"/>
     </row>
     <row r="9" ht="18" customHeight="1">
       <c r="A9" s="26" t="inlineStr">
         <is>
-          <t>바이오</t>
+          <t>SK스퀘어</t>
         </is>
       </c>
       <c r="B9" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C9" s="25" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D9" s="25" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E9" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F9" s="25" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G9" s="25" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
-        </is>
-      </c>
-      <c r="H9" s="25" t="n"/>
-      <c r="I9" s="25" t="n"/>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="H9" s="28" t="n">
+        <v>10.67</v>
+      </c>
+      <c r="I9" s="28" t="n">
+        <v>39.42</v>
+      </c>
     </row>
     <row r="10" ht="18" customHeight="1">
       <c r="A10" s="26" t="inlineStr">
         <is>
-          <t>인공지능</t>
+          <t>제약</t>
         </is>
       </c>
       <c r="B10" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C10" s="25" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D10" s="25" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E10" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F10" s="25" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G10" s="25" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="H10" s="25" t="n"/>
@@ -3403,38 +3393,42 @@
     <row r="11" ht="18" customHeight="1">
       <c r="A11" s="26" t="inlineStr">
         <is>
-          <t>로봇</t>
+          <t>삼성바이오로직스</t>
         </is>
       </c>
       <c r="B11" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C11" s="25" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D11" s="25" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E11" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F11" s="25" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G11" s="25" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
-        </is>
-      </c>
-      <c r="H11" s="25" t="n"/>
-      <c r="I11" s="25" t="n"/>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="H11" s="27" t="n">
+        <v>-5.75</v>
+      </c>
+      <c r="I11" s="27" t="n">
+        <v>-2.78</v>
+      </c>
     </row>
     <row r="12" ht="18" customHeight="1">
       <c r="A12" s="26" t="inlineStr">
         <is>
-          <t>전기차</t>
+          <t>카카오게임즈</t>
         </is>
       </c>
       <c r="B12" s="25" t="n">
@@ -3451,126 +3445,126 @@
       </c>
       <c r="F12" s="25" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G12" s="25" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
-        </is>
-      </c>
-      <c r="H12" s="25" t="n"/>
-      <c r="I12" s="25" t="n"/>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="H12" s="28" t="n">
+        <v>13.96</v>
+      </c>
+      <c r="I12" s="28" t="n">
+        <v>9.970000000000001</v>
+      </c>
     </row>
     <row r="13" ht="18" customHeight="1">
       <c r="A13" s="26" t="inlineStr">
         <is>
-          <t>대한항공</t>
+          <t>현대차</t>
         </is>
       </c>
       <c r="B13" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C13" s="25" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D13" s="25" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E13" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F13" s="25" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G13" s="25" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
-        </is>
-      </c>
-      <c r="H13" s="29" t="n">
-        <v>-3.12</v>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="H13" s="27" t="n">
+        <v>-5.22</v>
       </c>
       <c r="I13" s="27" t="n">
-        <v>5.08</v>
+        <v>-10.2</v>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="26" t="inlineStr">
         <is>
-          <t>LG전자</t>
+          <t>로봇</t>
         </is>
       </c>
       <c r="B14" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C14" s="25" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D14" s="25" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E14" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F14" s="25" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G14" s="25" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
-        </is>
-      </c>
-      <c r="H14" s="29" t="n">
-        <v>-7.44</v>
-      </c>
-      <c r="I14" s="29" t="n">
-        <v>-6.21</v>
-      </c>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="H14" s="25" t="n"/>
+      <c r="I14" s="25" t="n"/>
     </row>
     <row r="15" ht="18" customHeight="1">
       <c r="A15" s="26" t="inlineStr">
         <is>
-          <t>삼성E&amp;A</t>
+          <t>에이팩트</t>
         </is>
       </c>
       <c r="B15" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C15" s="25" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D15" s="25" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E15" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F15" s="25" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G15" s="25" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
-        </is>
-      </c>
-      <c r="H15" s="29" t="n">
-        <v>-2.11</v>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="H15" s="27" t="n">
+        <v>-0.72</v>
       </c>
       <c r="I15" s="27" t="n">
-        <v>2.21</v>
+        <v>-9.140000000000001</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
       <c r="A16" s="26" t="inlineStr">
         <is>
-          <t>제약</t>
+          <t>LG전자</t>
         </is>
       </c>
       <c r="B16" s="25" t="n">
@@ -3587,91 +3581,87 @@
       </c>
       <c r="F16" s="25" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G16" s="25" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
-        </is>
-      </c>
-      <c r="H16" s="25" t="n"/>
-      <c r="I16" s="25" t="n"/>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="H16" s="28" t="n">
+        <v>7.57</v>
+      </c>
+      <c r="I16" s="27" t="n">
+        <v>-6.57</v>
+      </c>
     </row>
     <row r="17" ht="18" customHeight="1">
       <c r="A17" s="26" t="inlineStr">
         <is>
-          <t>HJ중공업</t>
+          <t>철강</t>
         </is>
       </c>
       <c r="B17" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C17" s="25" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D17" s="25" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E17" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F17" s="25" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G17" s="25" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
-        </is>
-      </c>
-      <c r="H17" s="29" t="n">
-        <v>-3.67</v>
-      </c>
-      <c r="I17" s="27" t="n">
-        <v>3.24</v>
-      </c>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="H17" s="25" t="n"/>
+      <c r="I17" s="25" t="n"/>
     </row>
     <row r="18" ht="18" customHeight="1">
       <c r="A18" s="26" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>태양광</t>
         </is>
       </c>
       <c r="B18" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C18" s="25" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D18" s="25" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E18" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F18" s="25" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G18" s="25" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
-        </is>
-      </c>
-      <c r="H18" s="29" t="n">
-        <v>-26.16</v>
-      </c>
-      <c r="I18" s="29" t="n">
-        <v>-19.9</v>
-      </c>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="H18" s="25" t="n"/>
+      <c r="I18" s="25" t="n"/>
     </row>
     <row r="19" ht="18" customHeight="1">
       <c r="A19" s="26" t="inlineStr">
         <is>
-          <t>넥써쓰</t>
+          <t>게임</t>
         </is>
       </c>
       <c r="B19" s="25" t="n">
@@ -3688,25 +3678,21 @@
       </c>
       <c r="F19" s="25" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G19" s="25" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
-        </is>
-      </c>
-      <c r="H19" s="29" t="n">
-        <v>-27.47</v>
-      </c>
-      <c r="I19" s="29" t="n">
-        <v>-4.83</v>
-      </c>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="H19" s="25" t="n"/>
+      <c r="I19" s="25" t="n"/>
     </row>
     <row r="20" ht="18" customHeight="1">
       <c r="A20" s="26" t="inlineStr">
         <is>
-          <t>삼성바이오로직스</t>
+          <t>두산로보틱스</t>
         </is>
       </c>
       <c r="B20" s="25" t="n">
@@ -3723,25 +3709,25 @@
       </c>
       <c r="F20" s="25" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G20" s="25" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
-        </is>
-      </c>
-      <c r="H20" s="29" t="n">
-        <v>-3.92</v>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="H20" s="27" t="n">
+        <v>-1.38</v>
       </c>
       <c r="I20" s="27" t="n">
-        <v>6.1</v>
+        <v>-9.869999999999999</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
       <c r="A21" s="26" t="inlineStr">
         <is>
-          <t>한솔테크닉스</t>
+          <t>비투엔</t>
         </is>
       </c>
       <c r="B21" s="25" t="n">
@@ -3758,200 +3744,200 @@
       </c>
       <c r="F21" s="25" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G21" s="25" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
-        </is>
-      </c>
-      <c r="H21" s="29" t="n">
-        <v>-4.87</v>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="H21" s="28" t="n">
+        <v>0.85</v>
       </c>
       <c r="I21" s="27" t="n">
-        <v>7.83</v>
+        <v>-2.05</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
       <c r="A22" s="26" t="inlineStr">
         <is>
-          <t>삼성SDI</t>
+          <t>삼성생명</t>
         </is>
       </c>
       <c r="B22" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C22" s="25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D22" s="25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E22" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F22" s="25" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G22" s="25" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="H22" s="27" t="n">
-        <v>6.32</v>
-      </c>
-      <c r="I22" s="27" t="n">
-        <v>2.97</v>
+        <v>-9.359999999999999</v>
+      </c>
+      <c r="I22" s="28" t="n">
+        <v>6.5</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
       <c r="A23" s="26" t="inlineStr">
         <is>
-          <t>삼성물산</t>
+          <t>유안타증권</t>
         </is>
       </c>
       <c r="B23" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C23" s="25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D23" s="25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E23" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F23" s="25" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G23" s="25" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="H23" s="27" t="n">
-        <v>1.24</v>
+        <v>-2.95</v>
       </c>
       <c r="I23" s="27" t="n">
-        <v>13.77</v>
+        <v>-8.09</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
       <c r="A24" s="26" t="inlineStr">
         <is>
-          <t>삼성생명</t>
+          <t>카카오</t>
         </is>
       </c>
       <c r="B24" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C24" s="25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D24" s="25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E24" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F24" s="25" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G24" s="25" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="H24" s="27" t="n">
-        <v>5.97</v>
+        <v>-2.52</v>
       </c>
       <c r="I24" s="27" t="n">
-        <v>28.92</v>
+        <v>-9.69</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
       <c r="A25" s="26" t="inlineStr">
         <is>
-          <t>삼성에스디에스</t>
+          <t>프로브잇</t>
         </is>
       </c>
       <c r="B25" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C25" s="25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D25" s="25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E25" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F25" s="25" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G25" s="25" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
-        </is>
-      </c>
-      <c r="H25" s="29" t="n">
-        <v>-4.07</v>
-      </c>
-      <c r="I25" s="29" t="n">
-        <v>-10.55</v>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="H25" s="27" t="n">
+        <v>-97.06</v>
+      </c>
+      <c r="I25" s="27" t="n">
+        <v>-97.06</v>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
       <c r="A26" s="26" t="inlineStr">
         <is>
-          <t>삼성전기</t>
+          <t>한솔테크닉스</t>
         </is>
       </c>
       <c r="B26" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C26" s="25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D26" s="25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E26" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F26" s="25" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G26" s="25" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
-        </is>
-      </c>
-      <c r="H26" s="27" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="I26" s="27" t="n">
-        <v>32.44</v>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="H26" s="28" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="I26" s="28" t="n">
+        <v>20.22</v>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
       <c r="A27" s="26" t="inlineStr">
         <is>
-          <t>삼성전자우</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="B27" s="25" t="n">
@@ -3968,200 +3954,200 @@
       </c>
       <c r="F27" s="25" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G27" s="25" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
-        </is>
-      </c>
-      <c r="H27" s="29" t="n">
-        <v>-2.84</v>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="H27" s="27" t="n">
+        <v>-5.73</v>
       </c>
       <c r="I27" s="27" t="n">
-        <v>7.25</v>
+        <v>-29.25</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
       <c r="A28" s="26" t="inlineStr">
         <is>
-          <t>삼성제약</t>
+          <t>HJ중공업</t>
         </is>
       </c>
       <c r="B28" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C28" s="25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D28" s="25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E28" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F28" s="25" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G28" s="25" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
-        </is>
-      </c>
-      <c r="H28" s="29" t="n">
-        <v>-3.9</v>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="H28" s="27" t="n">
+        <v>-4.04</v>
       </c>
       <c r="I28" s="27" t="n">
-        <v>3.92</v>
+        <v>-8.15</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
       <c r="A29" s="26" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>노블엠앤비</t>
         </is>
       </c>
       <c r="B29" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C29" s="25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D29" s="25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E29" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F29" s="25" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G29" s="25" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
-        </is>
-      </c>
-      <c r="H29" s="29" t="n">
-        <v>-0.54</v>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="H29" s="27" t="n">
+        <v>-94.16</v>
       </c>
       <c r="I29" s="27" t="n">
-        <v>2.42</v>
+        <v>-94.16</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
       <c r="A30" s="26" t="inlineStr">
         <is>
-          <t>삼성증권</t>
+          <t>다스코</t>
         </is>
       </c>
       <c r="B30" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C30" s="25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D30" s="25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E30" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F30" s="25" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G30" s="25" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
-        </is>
-      </c>
-      <c r="H30" s="29" t="n">
-        <v>-0.25</v>
-      </c>
-      <c r="I30" s="27" t="n">
-        <v>0.08</v>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="H30" s="27" t="n">
+        <v>-15.71</v>
+      </c>
+      <c r="I30" s="28" t="n">
+        <v>5.22</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
       <c r="A31" s="26" t="inlineStr">
         <is>
-          <t>진원생명과학</t>
+          <t>대원전선</t>
         </is>
       </c>
       <c r="B31" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C31" s="25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D31" s="25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E31" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F31" s="25" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G31" s="25" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
-        </is>
-      </c>
-      <c r="H31" s="29" t="n">
-        <v>-17.67</v>
-      </c>
-      <c r="I31" s="29" t="n">
-        <v>-24.4</v>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="H31" s="27" t="n">
+        <v>-6.67</v>
+      </c>
+      <c r="I31" s="27" t="n">
+        <v>-3.09</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
       <c r="A32" s="26" t="inlineStr">
         <is>
-          <t>한화</t>
+          <t>삼화네트웍스</t>
         </is>
       </c>
       <c r="B32" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C32" s="25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D32" s="25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E32" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F32" s="25" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G32" s="25" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
-        </is>
-      </c>
-      <c r="H32" s="29" t="n">
-        <v>-4.71</v>
-      </c>
-      <c r="I32" s="29" t="n">
-        <v>-0.95</v>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="H32" s="28" t="n">
+        <v>5.24</v>
+      </c>
+      <c r="I32" s="28" t="n">
+        <v>7.86</v>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
       <c r="A33" s="26" t="inlineStr">
         <is>
-          <t>DB</t>
+          <t>센서뷰</t>
         </is>
       </c>
       <c r="B33" s="25" t="n">
@@ -4178,25 +4164,25 @@
       </c>
       <c r="F33" s="25" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G33" s="25" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
-        </is>
-      </c>
-      <c r="H33" s="29" t="n">
-        <v>-2.39</v>
-      </c>
-      <c r="I33" s="29" t="n">
-        <v>-6.55</v>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="H33" s="27" t="n">
+        <v>-7.33</v>
+      </c>
+      <c r="I33" s="27" t="n">
+        <v>-13.48</v>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
       <c r="A34" s="26" t="inlineStr">
         <is>
-          <t>HMM</t>
+          <t>스피어</t>
         </is>
       </c>
       <c r="B34" s="25" t="n">
@@ -4213,25 +4199,25 @@
       </c>
       <c r="F34" s="25" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G34" s="25" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
-        </is>
-      </c>
-      <c r="H34" s="29" t="n">
-        <v>-1.47</v>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="H34" s="27" t="n">
+        <v>-12.28</v>
       </c>
       <c r="I34" s="27" t="n">
-        <v>0.5</v>
+        <v>-37.07</v>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
       <c r="A35" s="26" t="inlineStr">
         <is>
-          <t>남화토건</t>
+          <t>원전</t>
         </is>
       </c>
       <c r="B35" s="25" t="n">
@@ -4248,161 +4234,161 @@
       </c>
       <c r="F35" s="25" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G35" s="25" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
-        </is>
-      </c>
-      <c r="H35" s="27" t="n">
-        <v>12.73</v>
-      </c>
-      <c r="I35" s="27" t="n">
-        <v>45.92</v>
-      </c>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="H35" s="25" t="n"/>
+      <c r="I35" s="25" t="n"/>
     </row>
     <row r="36" ht="18" customHeight="1">
       <c r="A36" s="26" t="inlineStr">
         <is>
-          <t>센서뷰</t>
+          <t>JW신약</t>
         </is>
       </c>
       <c r="B36" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C36" s="25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D36" s="25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E36" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F36" s="25" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G36" s="25" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
-        </is>
-      </c>
-      <c r="H36" s="29" t="n">
-        <v>-5.11</v>
-      </c>
-      <c r="I36" s="29" t="n">
-        <v>-12.29</v>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="H36" s="28" t="n">
+        <v>16.92</v>
+      </c>
+      <c r="I36" s="28" t="n">
+        <v>53.8</v>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
       <c r="A37" s="26" t="inlineStr">
         <is>
-          <t>태양광</t>
+          <t>TS트릴리온</t>
         </is>
       </c>
       <c r="B37" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C37" s="25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D37" s="25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E37" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F37" s="25" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G37" s="25" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
-        </is>
-      </c>
-      <c r="H37" s="25" t="n"/>
-      <c r="I37" s="25" t="n"/>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="H37" s="28" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="I37" s="27" t="n">
+        <v>-15.51</v>
+      </c>
     </row>
     <row r="38" ht="18" customHeight="1">
       <c r="A38" s="26" t="inlineStr">
         <is>
-          <t>파두</t>
+          <t>강동씨앤엘</t>
         </is>
       </c>
       <c r="B38" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C38" s="25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D38" s="25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E38" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F38" s="25" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G38" s="25" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
-        </is>
-      </c>
-      <c r="H38" s="29" t="n">
-        <v>-2.5</v>
-      </c>
-      <c r="I38" s="27" t="n">
-        <v>0.4</v>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="H38" s="27" t="n">
+        <v>-12.22</v>
+      </c>
+      <c r="I38" s="28" t="n">
+        <v>79.66</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
       <c r="A39" s="26" t="inlineStr">
         <is>
-          <t>현대로템</t>
+          <t>남화토건</t>
         </is>
       </c>
       <c r="B39" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C39" s="25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D39" s="25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E39" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F39" s="25" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G39" s="25" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
-        </is>
-      </c>
-      <c r="H39" s="29" t="n">
-        <v>-2.13</v>
-      </c>
-      <c r="I39" s="29" t="n">
-        <v>-0.72</v>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="H39" s="27" t="n">
+        <v>-10.33</v>
+      </c>
+      <c r="I39" s="28" t="n">
+        <v>31.77</v>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
       <c r="A40" s="26" t="inlineStr">
         <is>
-          <t>JW신약</t>
+          <t>메리츠제2호스팩</t>
         </is>
       </c>
       <c r="B40" s="25" t="n">
@@ -4419,25 +4405,25 @@
       </c>
       <c r="F40" s="25" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G40" s="25" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="H40" s="27" t="n">
-        <v>13.08</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="I40" s="27" t="n">
-        <v>70.94</v>
+        <v>-0.8100000000000001</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
       <c r="A41" s="26" t="inlineStr">
         <is>
-          <t>강동씨앤엘</t>
+          <t>보해양조</t>
         </is>
       </c>
       <c r="B41" s="25" t="n">
@@ -4454,25 +4440,25 @@
       </c>
       <c r="F41" s="25" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G41" s="25" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
-        </is>
-      </c>
-      <c r="H41" s="27" t="n">
-        <v>29.91</v>
-      </c>
-      <c r="I41" s="27" t="n">
-        <v>121.56</v>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="H41" s="28" t="n">
+        <v>9.859999999999999</v>
+      </c>
+      <c r="I41" s="28" t="n">
+        <v>64.90000000000001</v>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
       <c r="A42" s="26" t="inlineStr">
         <is>
-          <t>메리츠제2호스팩</t>
+          <t>삼익제약</t>
         </is>
       </c>
       <c r="B42" s="25" t="n">
@@ -4489,21 +4475,25 @@
       </c>
       <c r="F42" s="25" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G42" s="25" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
-        </is>
-      </c>
-      <c r="H42" s="25" t="n"/>
-      <c r="I42" s="25" t="n"/>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="H42" s="28" t="n">
+        <v>6.54</v>
+      </c>
+      <c r="I42" s="28" t="n">
+        <v>16.36</v>
+      </c>
     </row>
     <row r="43" ht="18" customHeight="1">
       <c r="A43" s="26" t="inlineStr">
         <is>
-          <t>보해양조</t>
+          <t>삼화전자</t>
         </is>
       </c>
       <c r="B43" s="25" t="n">
@@ -4520,25 +4510,25 @@
       </c>
       <c r="F43" s="25" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G43" s="25" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="H43" s="27" t="n">
-        <v>29.88</v>
-      </c>
-      <c r="I43" s="27" t="n">
-        <v>58.36</v>
+        <v>-14.82</v>
+      </c>
+      <c r="I43" s="28" t="n">
+        <v>13.91</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
       <c r="A44" s="26" t="inlineStr">
         <is>
-          <t>부국철강</t>
+          <t>성문전자</t>
         </is>
       </c>
       <c r="B44" s="25" t="n">
@@ -4555,25 +4545,25 @@
       </c>
       <c r="F44" s="25" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G44" s="25" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
-        </is>
-      </c>
-      <c r="H44" s="29" t="n">
-        <v>-13.76</v>
-      </c>
-      <c r="I44" s="27" t="n">
-        <v>3.49</v>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="H44" s="28" t="n">
+        <v>9</v>
+      </c>
+      <c r="I44" s="28" t="n">
+        <v>51.42</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
       <c r="A45" s="26" t="inlineStr">
         <is>
-          <t>삼익제약</t>
+          <t>예스티</t>
         </is>
       </c>
       <c r="B45" s="25" t="n">
@@ -4590,25 +4580,25 @@
       </c>
       <c r="F45" s="25" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G45" s="25" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
-        </is>
-      </c>
-      <c r="H45" s="27" t="n">
-        <v>29.98</v>
-      </c>
-      <c r="I45" s="27" t="n">
-        <v>41.82</v>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="H45" s="28" t="n">
+        <v>10.63</v>
+      </c>
+      <c r="I45" s="28" t="n">
+        <v>20.88</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
       <c r="A46" s="26" t="inlineStr">
         <is>
-          <t>삼화전자</t>
+          <t>위더스제약</t>
         </is>
       </c>
       <c r="B46" s="25" t="n">
@@ -4625,25 +4615,25 @@
       </c>
       <c r="F46" s="25" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G46" s="25" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="H46" s="27" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="I46" s="27" t="n">
-        <v>73.59</v>
+        <v>-3.95</v>
+      </c>
+      <c r="I46" s="28" t="n">
+        <v>4.03</v>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
       <c r="A47" s="26" t="inlineStr">
         <is>
-          <t>성문전자</t>
+          <t>율촌</t>
         </is>
       </c>
       <c r="B47" s="25" t="n">
@@ -4660,25 +4650,25 @@
       </c>
       <c r="F47" s="25" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G47" s="25" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
-        </is>
-      </c>
-      <c r="H47" s="27" t="n">
-        <v>4.43</v>
-      </c>
-      <c r="I47" s="27" t="n">
-        <v>40.24</v>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="H47" s="28" t="n">
+        <v>9.029999999999999</v>
+      </c>
+      <c r="I47" s="28" t="n">
+        <v>38.23</v>
       </c>
     </row>
     <row r="48" ht="18" customHeight="1">
       <c r="A48" s="26" t="inlineStr">
         <is>
-          <t>위더스제약</t>
+          <t>제이앤티씨</t>
         </is>
       </c>
       <c r="B48" s="25" t="n">
@@ -4695,25 +4685,25 @@
       </c>
       <c r="F48" s="25" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G48" s="25" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
-        </is>
-      </c>
-      <c r="H48" s="27" t="n">
-        <v>13.59</v>
-      </c>
-      <c r="I48" s="27" t="n">
-        <v>33.03</v>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="H48" s="28" t="n">
+        <v>8.81</v>
+      </c>
+      <c r="I48" s="28" t="n">
+        <v>33.63</v>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1">
       <c r="A49" s="26" t="inlineStr">
         <is>
-          <t>율촌</t>
+          <t>티웨이홀딩스</t>
         </is>
       </c>
       <c r="B49" s="25" t="n">
@@ -4730,25 +4720,25 @@
       </c>
       <c r="F49" s="25" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G49" s="25" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
-        </is>
-      </c>
-      <c r="H49" s="29" t="n">
-        <v>-13.55</v>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="H49" s="27" t="n">
+        <v>-7.91</v>
       </c>
       <c r="I49" s="27" t="n">
-        <v>30.73</v>
+        <v>-9.94</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
       <c r="A50" s="26" t="inlineStr">
         <is>
-          <t>티웨이홀딩스</t>
+          <t>하이스틸</t>
         </is>
       </c>
       <c r="B50" s="25" t="n">
@@ -4765,25 +4755,25 @@
       </c>
       <c r="F50" s="25" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G50" s="25" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
-        </is>
-      </c>
-      <c r="H50" s="29" t="n">
-        <v>-7.09</v>
-      </c>
-      <c r="I50" s="27" t="n">
-        <v>26.88</v>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="H50" s="28" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="I50" s="28" t="n">
+        <v>2.02</v>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
       <c r="A51" s="26" t="inlineStr">
         <is>
-          <t>피앤에스로보틱스</t>
+          <t>한울반도체</t>
         </is>
       </c>
       <c r="B51" s="25" t="n">
@@ -4800,19 +4790,19 @@
       </c>
       <c r="F51" s="25" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G51" s="25" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
-        </is>
-      </c>
-      <c r="H51" s="27" t="n">
-        <v>22.04</v>
-      </c>
-      <c r="I51" s="27" t="n">
-        <v>20.74</v>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="H51" s="28" t="n">
+        <v>29.91</v>
+      </c>
+      <c r="I51" s="28" t="n">
+        <v>110.65</v>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1">
@@ -4835,19 +4825,19 @@
       </c>
       <c r="F52" s="25" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G52" s="25" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
-        </is>
-      </c>
-      <c r="H52" s="29" t="n">
-        <v>-4.12</v>
-      </c>
-      <c r="I52" s="27" t="n">
-        <v>42.23</v>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="H52" s="28" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="I52" s="28" t="n">
+        <v>10.48</v>
       </c>
     </row>
   </sheetData>
@@ -4931,19 +4921,19 @@
         <v>1</v>
       </c>
       <c r="C3" s="36" t="n">
-        <v>82</v>
+        <v>62</v>
       </c>
       <c r="D3" s="36" t="n">
-        <v>82</v>
+        <v>62</v>
       </c>
       <c r="E3" s="36" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="F3" s="37" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G3" s="37" t="inlineStr">
@@ -4962,19 +4952,19 @@
         <v>1</v>
       </c>
       <c r="C4" s="36" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="D4" s="36" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="E4" s="36" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="F4" s="37" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G4" s="37" t="inlineStr">
@@ -4986,26 +4976,26 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="35" t="inlineStr">
         <is>
-          <t>전기차</t>
+          <t>원전</t>
         </is>
       </c>
       <c r="B5" s="36" t="n">
         <v>1</v>
       </c>
       <c r="C5" s="36" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D5" s="36" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E5" s="36" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="F5" s="37" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G5" s="37" t="inlineStr">
@@ -5024,19 +5014,19 @@
         <v>1</v>
       </c>
       <c r="C6" s="36" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D6" s="36" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E6" s="36" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="F6" s="37" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G6" s="37" t="inlineStr">
@@ -5055,19 +5045,19 @@
         <v>1</v>
       </c>
       <c r="C7" s="36" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D7" s="36" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E7" s="36" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="F7" s="37" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G7" s="37" t="inlineStr">
@@ -5079,26 +5069,26 @@
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="35" t="inlineStr">
         <is>
-          <t>제약</t>
+          <t>게임</t>
         </is>
       </c>
       <c r="B8" s="36" t="n">
         <v>1</v>
       </c>
       <c r="C8" s="36" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D8" s="36" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E8" s="36" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="F8" s="37" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G8" s="37" t="inlineStr">
@@ -5110,92 +5100,100 @@
     <row r="9" ht="18" customHeight="1">
       <c r="A9" s="35" t="inlineStr">
         <is>
+          <t>철강</t>
+        </is>
+      </c>
+      <c r="B9" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" s="36" t="n">
+        <v>7</v>
+      </c>
+      <c r="D9" s="36" t="n">
+        <v>7</v>
+      </c>
+      <c r="E9" s="36" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="F9" s="37" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="G9" s="37" t="inlineStr">
+        <is>
+          <t>⚡ 관심</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="18" customHeight="1">
+      <c r="A10" s="35" t="inlineStr">
+        <is>
+          <t>제약</t>
+        </is>
+      </c>
+      <c r="B10" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" s="36" t="n">
+        <v>10</v>
+      </c>
+      <c r="D10" s="36" t="n">
+        <v>10</v>
+      </c>
+      <c r="E10" s="36" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="F10" s="37" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="G10" s="37" t="inlineStr">
+        <is>
+          <t>⚡ 관심</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="18" customHeight="1">
+      <c r="A11" s="35" t="inlineStr">
+        <is>
           <t>인공지능</t>
         </is>
       </c>
-      <c r="B9" s="36" t="n">
-        <v>1</v>
-      </c>
-      <c r="C9" s="36" t="n">
-        <v>11</v>
-      </c>
-      <c r="D9" s="36" t="n">
-        <v>11</v>
-      </c>
-      <c r="E9" s="36" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
-        </is>
-      </c>
-      <c r="F9" s="37" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
-        </is>
-      </c>
-      <c r="G9" s="37" t="inlineStr">
+      <c r="B11" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" s="36" t="n">
+        <v>13</v>
+      </c>
+      <c r="D11" s="36" t="n">
+        <v>13</v>
+      </c>
+      <c r="E11" s="36" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="F11" s="37" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="G11" s="37" t="inlineStr">
         <is>
           <t>⚡ 관심</t>
         </is>
       </c>
-    </row>
-    <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="26" t="inlineStr">
-        <is>
-          <t>이차전지</t>
-        </is>
-      </c>
-      <c r="B10" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="C10" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" s="25" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F10" s="28" t="inlineStr">
-        <is>
-          <t>감지 없음</t>
-        </is>
-      </c>
-      <c r="G10" s="28" t="inlineStr"/>
-    </row>
-    <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="26" t="inlineStr">
-        <is>
-          <t>AI반도체</t>
-        </is>
-      </c>
-      <c r="B11" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="C11" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" s="25" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F11" s="28" t="inlineStr">
-        <is>
-          <t>감지 없음</t>
-        </is>
-      </c>
-      <c r="G11" s="28" t="inlineStr"/>
     </row>
     <row r="12" ht="18" customHeight="1">
       <c r="A12" s="26" t="inlineStr">
         <is>
-          <t>방산</t>
+          <t>이차전지</t>
         </is>
       </c>
       <c r="B12" s="25" t="n">
@@ -5212,17 +5210,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F12" s="28" t="inlineStr">
+      <c r="F12" s="29" t="inlineStr">
         <is>
           <t>감지 없음</t>
         </is>
       </c>
-      <c r="G12" s="28" t="inlineStr"/>
+      <c r="G12" s="29" t="inlineStr"/>
     </row>
     <row r="13" ht="18" customHeight="1">
       <c r="A13" s="26" t="inlineStr">
         <is>
-          <t>원전</t>
+          <t>AI반도체</t>
         </is>
       </c>
       <c r="B13" s="25" t="n">
@@ -5239,17 +5237,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F13" s="28" t="inlineStr">
+      <c r="F13" s="29" t="inlineStr">
         <is>
           <t>감지 없음</t>
         </is>
       </c>
-      <c r="G13" s="28" t="inlineStr"/>
+      <c r="G13" s="29" t="inlineStr"/>
     </row>
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="26" t="inlineStr">
         <is>
-          <t>수소</t>
+          <t>전기차</t>
         </is>
       </c>
       <c r="B14" s="25" t="n">
@@ -5266,17 +5264,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F14" s="28" t="inlineStr">
+      <c r="F14" s="29" t="inlineStr">
         <is>
           <t>감지 없음</t>
         </is>
       </c>
-      <c r="G14" s="28" t="inlineStr"/>
+      <c r="G14" s="29" t="inlineStr"/>
     </row>
     <row r="15" ht="18" customHeight="1">
       <c r="A15" s="26" t="inlineStr">
         <is>
-          <t>게임</t>
+          <t>방산</t>
         </is>
       </c>
       <c r="B15" s="25" t="n">
@@ -5293,17 +5291,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F15" s="28" t="inlineStr">
+      <c r="F15" s="29" t="inlineStr">
         <is>
           <t>감지 없음</t>
         </is>
       </c>
-      <c r="G15" s="28" t="inlineStr"/>
+      <c r="G15" s="29" t="inlineStr"/>
     </row>
     <row r="16" ht="18" customHeight="1">
       <c r="A16" s="26" t="inlineStr">
         <is>
-          <t>엔터</t>
+          <t>수소</t>
         </is>
       </c>
       <c r="B16" s="25" t="n">
@@ -5320,17 +5318,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F16" s="28" t="inlineStr">
+      <c r="F16" s="29" t="inlineStr">
         <is>
           <t>감지 없음</t>
         </is>
       </c>
-      <c r="G16" s="28" t="inlineStr"/>
+      <c r="G16" s="29" t="inlineStr"/>
     </row>
     <row r="17" ht="18" customHeight="1">
       <c r="A17" s="26" t="inlineStr">
         <is>
-          <t>핀테크</t>
+          <t>엔터</t>
         </is>
       </c>
       <c r="B17" s="25" t="n">
@@ -5347,17 +5345,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F17" s="28" t="inlineStr">
+      <c r="F17" s="29" t="inlineStr">
         <is>
           <t>감지 없음</t>
         </is>
       </c>
-      <c r="G17" s="28" t="inlineStr"/>
+      <c r="G17" s="29" t="inlineStr"/>
     </row>
     <row r="18" ht="18" customHeight="1">
       <c r="A18" s="26" t="inlineStr">
         <is>
-          <t>클라우드</t>
+          <t>핀테크</t>
         </is>
       </c>
       <c r="B18" s="25" t="n">
@@ -5374,17 +5372,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F18" s="28" t="inlineStr">
+      <c r="F18" s="29" t="inlineStr">
         <is>
           <t>감지 없음</t>
         </is>
       </c>
-      <c r="G18" s="28" t="inlineStr"/>
+      <c r="G18" s="29" t="inlineStr"/>
     </row>
     <row r="19" ht="18" customHeight="1">
       <c r="A19" s="26" t="inlineStr">
         <is>
-          <t>조선</t>
+          <t>클라우드</t>
         </is>
       </c>
       <c r="B19" s="25" t="n">
@@ -5401,17 +5399,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F19" s="28" t="inlineStr">
+      <c r="F19" s="29" t="inlineStr">
         <is>
           <t>감지 없음</t>
         </is>
       </c>
-      <c r="G19" s="28" t="inlineStr"/>
+      <c r="G19" s="29" t="inlineStr"/>
     </row>
     <row r="20" ht="18" customHeight="1">
       <c r="A20" s="26" t="inlineStr">
         <is>
-          <t>철강</t>
+          <t>조선</t>
         </is>
       </c>
       <c r="B20" s="25" t="n">
@@ -5428,12 +5426,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F20" s="28" t="inlineStr">
+      <c r="F20" s="29" t="inlineStr">
         <is>
           <t>감지 없음</t>
         </is>
       </c>
-      <c r="G20" s="28" t="inlineStr"/>
+      <c r="G20" s="29" t="inlineStr"/>
     </row>
     <row r="21" ht="18" customHeight="1">
       <c r="A21" s="26" t="inlineStr">
@@ -5455,12 +5453,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F21" s="28" t="inlineStr">
+      <c r="F21" s="29" t="inlineStr">
         <is>
           <t>감지 없음</t>
         </is>
       </c>
-      <c r="G21" s="28" t="inlineStr"/>
+      <c r="G21" s="29" t="inlineStr"/>
     </row>
     <row r="22" ht="18" customHeight="1">
       <c r="A22" s="26" t="inlineStr">
@@ -5482,12 +5480,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F22" s="28" t="inlineStr">
+      <c r="F22" s="29" t="inlineStr">
         <is>
           <t>감지 없음</t>
         </is>
       </c>
-      <c r="G22" s="28" t="inlineStr"/>
+      <c r="G22" s="29" t="inlineStr"/>
     </row>
     <row r="23" ht="18" customHeight="1">
       <c r="A23" s="26" t="inlineStr">
@@ -5509,12 +5507,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F23" s="28" t="inlineStr">
+      <c r="F23" s="29" t="inlineStr">
         <is>
           <t>감지 없음</t>
         </is>
       </c>
-      <c r="G23" s="28" t="inlineStr"/>
+      <c r="G23" s="29" t="inlineStr"/>
     </row>
     <row r="24" ht="18" customHeight="1">
       <c r="A24" s="26" t="inlineStr">
@@ -5536,12 +5534,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F24" s="28" t="inlineStr">
+      <c r="F24" s="29" t="inlineStr">
         <is>
           <t>감지 없음</t>
         </is>
       </c>
-      <c r="G24" s="28" t="inlineStr"/>
+      <c r="G24" s="29" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/trend/stock_trend_history.xlsx
+++ b/trend/stock_trend_history.xlsx
@@ -57,13 +57,13 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="00E53935"/>
+      <color rgb="002563EB"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="002563EB"/>
+      <color rgb="00E53935"/>
       <sz val="10"/>
     </font>
     <font>
@@ -261,11 +261,11 @@
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -694,7 +694,7 @@
     <row r="1" ht="36" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>📊 주식 트렌드 조기 감지 대시보드   |   최종 업데이트: 2026-06-23 06:54</t>
+          <t>📊 주식 트렌드 조기 감지 대시보드   |   최종 업데이트: 2026-06-24 06:54</t>
         </is>
       </c>
     </row>
@@ -708,7 +708,7 @@
       </c>
       <c r="E3" s="3" t="n"/>
       <c r="G3" s="5" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="H3" s="3" t="n"/>
       <c r="J3" s="6" t="n">
@@ -787,21 +787,21 @@
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="11" t="inlineStr">
         <is>
-          <t>⚡ 최신(2026-06-23) 상위: 반도체  점수 62.0점</t>
+          <t>⚡ 최신(2026-06-24) 상위: 반도체  점수 114.0점</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1">
       <c r="A11" s="12" t="inlineStr">
         <is>
-          <t>⚡ 최신(2026-06-23) 상위: SK하이닉스  점수 47.0점</t>
+          <t>⚡ 최신(2026-06-24) 상위: SK  점수 48.0점</t>
         </is>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1">
       <c r="A12" s="11" t="inlineStr">
         <is>
-          <t>⚡ 최신(2026-06-23) 상위: 삼성전자  점수 26.0점</t>
+          <t>⚡ 최신(2026-06-24) 상위: 삼성전자  점수 27.0점</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B14" s="15" t="n">
@@ -928,10 +928,10 @@
         </is>
       </c>
       <c r="D14" s="15" t="n">
-        <v>62</v>
+        <v>114</v>
       </c>
       <c r="E14" s="15" t="n">
-        <v>62</v>
+        <v>114</v>
       </c>
       <c r="F14" s="15" t="n">
         <v>0</v>
@@ -947,7 +947,7 @@
       </c>
       <c r="J14" s="17" t="inlineStr">
         <is>
-          <t>매일경제 기사 언급 / 네이버뉴스 헤드라인 언급 / 매일경제 기사 언급 / 매일경제 헤드라인 언급 / 매일경제 기사 언급</t>
+          <t>네이버뉴스 헤드라인 언급 / 네이버뉴스 헤드라인 언급 / 매일경제 헤드라인 언급 / 네이버뉴스 헤드라인 언급 / 네이버뉴스 헤드라인 언급</t>
         </is>
       </c>
       <c r="K14" s="17" t="inlineStr">
@@ -959,7 +959,7 @@
     <row r="15" ht="18" customHeight="1">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B15" s="15" t="n">
@@ -967,14 +967,14 @@
       </c>
       <c r="C15" s="16" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>SK</t>
         </is>
       </c>
       <c r="D15" s="15" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E15" s="15" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F15" s="15" t="n">
         <v>0</v>
@@ -983,14 +983,14 @@
         <v>0</v>
       </c>
       <c r="H15" s="18" t="n">
-        <v>5.61</v>
-      </c>
-      <c r="I15" s="18" t="n">
-        <v>27.58</v>
+        <v>-3.42</v>
+      </c>
+      <c r="I15" s="19" t="n">
+        <v>4.75</v>
       </c>
       <c r="J15" s="17" t="inlineStr">
         <is>
-          <t>매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 기사 언급 / 네이버뉴스 헤드라인 언급</t>
+          <t>한국경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 기사 언급 / 네이버뉴스 기사 언급 / 매일경제 헤드라인 언급</t>
         </is>
       </c>
       <c r="K15" s="17" t="inlineStr">
@@ -1002,7 +1002,7 @@
     <row r="16" ht="18" customHeight="1">
       <c r="A16" s="15" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B16" s="15" t="n">
@@ -1014,10 +1014,10 @@
         </is>
       </c>
       <c r="D16" s="15" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E16" s="15" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F16" s="15" t="n">
         <v>0</v>
@@ -1025,15 +1025,15 @@
       <c r="G16" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="H16" s="19" t="n">
-        <v>-0.14</v>
+      <c r="H16" s="18" t="n">
+        <v>-12.31</v>
       </c>
       <c r="I16" s="18" t="n">
-        <v>4.9</v>
+        <v>-9.619999999999999</v>
       </c>
       <c r="J16" s="17" t="inlineStr">
         <is>
-          <t>매일경제 헤드라인 언급 / 매일경제 기사 언급 / 매일경제 기사 언급 / 네이버뉴스 헤드라인 언급 / 네이버뉴스 기사 언급</t>
+          <t>한국경제 헤드라인 언급 / 매일경제 기사 언급 / 네이버뉴스 기사 언급 / 매일경제 헤드라인 언급 / 매일경제 기사 언급</t>
         </is>
       </c>
       <c r="K16" s="17" t="inlineStr">
@@ -1045,7 +1045,7 @@
     <row r="17" ht="18" customHeight="1">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B17" s="15" t="n">
@@ -1053,14 +1053,14 @@
       </c>
       <c r="C17" s="16" t="inlineStr">
         <is>
-          <t>LG</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="D17" s="15" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="E17" s="15" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F17" s="15" t="n">
         <v>0</v>
@@ -1069,24 +1069,26 @@
         <v>0</v>
       </c>
       <c r="H17" s="18" t="n">
-        <v>0.92</v>
+        <v>-12.47</v>
       </c>
       <c r="I17" s="19" t="n">
-        <v>-7.18</v>
+        <v>7.26</v>
       </c>
       <c r="J17" s="17" t="inlineStr">
         <is>
-          <t>한국경제 헤드라인 언급 / 매일경제 기사 언급 / 한국경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K17" s="17" t="n">
-        <v/>
+          <t>한국경제 헤드라인 언급 / 매일경제 기사 언급 / 네이버뉴스 기사 언급 / 매일경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K17" s="17" t="inlineStr">
+        <is>
+          <t>네이버</t>
+        </is>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
       <c r="A18" s="15" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B18" s="15" t="n">
@@ -1094,14 +1096,14 @@
       </c>
       <c r="C18" s="16" t="inlineStr">
         <is>
-          <t>바이오</t>
+          <t>LG</t>
         </is>
       </c>
       <c r="D18" s="15" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="E18" s="15" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="F18" s="15" t="n">
         <v>0</v>
@@ -1109,27 +1111,25 @@
       <c r="G18" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="H18" s="15" t="n">
+      <c r="H18" s="18" t="n">
+        <v>-10.28</v>
+      </c>
+      <c r="I18" s="18" t="n">
+        <v>-13.58</v>
+      </c>
+      <c r="J18" s="17" t="inlineStr">
+        <is>
+          <t>매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K18" s="17" t="n">
         <v/>
-      </c>
-      <c r="I18" s="15" t="n">
-        <v/>
-      </c>
-      <c r="J18" s="17" t="inlineStr">
-        <is>
-          <t>네이버뉴스 헤드라인 언급 / 네이버뉴스 헤드라인 언급 / 네이버뉴스 헤드라인 언급 / 네이버뉴스 헤드라인 언급 / 네이버뉴스 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K18" s="17" t="inlineStr">
-        <is>
-          <t>네이버</t>
-        </is>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
       <c r="A19" s="15" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B19" s="15" t="n">
@@ -1141,10 +1141,10 @@
         </is>
       </c>
       <c r="D19" s="15" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E19" s="15" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F19" s="15" t="n">
         <v>0</v>
@@ -1172,7 +1172,7 @@
     <row r="20" ht="18" customHeight="1">
       <c r="A20" s="15" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B20" s="15" t="n">
@@ -1180,14 +1180,14 @@
       </c>
       <c r="C20" s="16" t="inlineStr">
         <is>
-          <t>SK스퀘어</t>
+          <t>로봇</t>
         </is>
       </c>
       <c r="D20" s="15" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E20" s="15" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F20" s="15" t="n">
         <v>0</v>
@@ -1195,15 +1195,15 @@
       <c r="G20" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="H20" s="18" t="n">
-        <v>10.67</v>
-      </c>
-      <c r="I20" s="18" t="n">
-        <v>39.42</v>
+      <c r="H20" s="15" t="n">
+        <v/>
+      </c>
+      <c r="I20" s="15" t="n">
+        <v/>
       </c>
       <c r="J20" s="17" t="inlineStr">
         <is>
-          <t>매일경제 헤드라인 언급 / 매일경제 기사 언급 / 매일경제 기사 언급 / 한국경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
+          <t>매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 기사 언급 / 한국경제 헤드라인 언급 / 매일경제 헤드라인 언급</t>
         </is>
       </c>
       <c r="K20" s="17" t="n">
@@ -1213,7 +1213,7 @@
     <row r="21" ht="18" customHeight="1">
       <c r="A21" s="15" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B21" s="15" t="n">
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="D21" s="15" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E21" s="15" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F21" s="15" t="n">
         <v>0</v>
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J21" s="17" t="inlineStr">
         <is>
-          <t>네이버뉴스 기사 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 헤드라인 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 헤드라인 언급</t>
+          <t>네이버뉴스 헤드라인 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 헤드라인 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 기사 언급</t>
         </is>
       </c>
       <c r="K21" s="17" t="inlineStr">
@@ -1256,7 +1256,7 @@
     <row r="22" ht="18" customHeight="1">
       <c r="A22" s="15" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B22" s="15" t="n">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="C22" s="16" t="inlineStr">
         <is>
-          <t>카카오게임즈</t>
+          <t>LG전자</t>
         </is>
       </c>
       <c r="D22" s="15" t="n">
@@ -1280,26 +1280,24 @@
         <v>0</v>
       </c>
       <c r="H22" s="18" t="n">
-        <v>13.96</v>
+        <v>-11.21</v>
       </c>
       <c r="I22" s="18" t="n">
-        <v>9.970000000000001</v>
+        <v>-13.68</v>
       </c>
       <c r="J22" s="17" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +76% / 중요공시 1건 / 한국경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K22" s="17" t="inlineStr">
-        <is>
-          <t>공시, 네이버</t>
-        </is>
+          <t>매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K22" s="17" t="n">
+        <v/>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B23" s="15" t="n">
@@ -1307,14 +1305,14 @@
       </c>
       <c r="C23" s="16" t="inlineStr">
         <is>
-          <t>삼성바이오로직스</t>
+          <t>에이팩트</t>
         </is>
       </c>
       <c r="D23" s="15" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E23" s="15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F23" s="15" t="n">
         <v>2</v>
@@ -1322,27 +1320,27 @@
       <c r="G23" s="15" t="n">
         <v>3</v>
       </c>
-      <c r="H23" s="19" t="n">
-        <v>-5.75</v>
-      </c>
-      <c r="I23" s="19" t="n">
-        <v>-2.78</v>
+      <c r="H23" s="18" t="n">
+        <v>-11.96</v>
+      </c>
+      <c r="I23" s="18" t="n">
+        <v>-17.49</v>
       </c>
       <c r="J23" s="17" t="inlineStr">
         <is>
-          <t>중요공시 2건 / 중요공시 3일 +100% / 중요공시 7일 +100% / 네이버뉴스 헤드라인 언급</t>
+          <t>중요공시 4건 / 중요공시 3일 +100% / 중요공시 7일 +100%</t>
         </is>
       </c>
       <c r="K23" s="17" t="inlineStr">
         <is>
-          <t>공시, 네이버</t>
+          <t>공시</t>
         </is>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B24" s="15" t="n">
@@ -1350,14 +1348,14 @@
       </c>
       <c r="C24" s="16" t="inlineStr">
         <is>
-          <t>현대차</t>
+          <t>바이오</t>
         </is>
       </c>
       <c r="D24" s="15" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E24" s="15" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F24" s="15" t="n">
         <v>0</v>
@@ -1365,234 +1363,240 @@
       <c r="G24" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="H24" s="19" t="n">
-        <v>-5.22</v>
-      </c>
-      <c r="I24" s="19" t="n">
-        <v>-10.2</v>
+      <c r="H24" s="15" t="n">
+        <v/>
+      </c>
+      <c r="I24" s="15" t="n">
+        <v/>
       </c>
       <c r="J24" s="17" t="inlineStr">
         <is>
-          <t>매일경제 기사 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K24" s="17" t="n">
+          <t>네이버뉴스 기사 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 헤드라인 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 기사 언급</t>
+        </is>
+      </c>
+      <c r="K24" s="17" t="inlineStr">
+        <is>
+          <t>네이버</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="18" customHeight="1">
+      <c r="A25" s="20" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B25" s="20" t="n">
+        <v>12</v>
+      </c>
+      <c r="C25" s="21" t="inlineStr">
+        <is>
+          <t>프로브잇</t>
+        </is>
+      </c>
+      <c r="D25" s="20" t="n">
+        <v>6</v>
+      </c>
+      <c r="E25" s="20" t="n">
+        <v>6</v>
+      </c>
+      <c r="F25" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" s="22" t="n">
+        <v>177.78</v>
+      </c>
+      <c r="I25" s="23" t="n">
+        <v>-91.83</v>
+      </c>
+      <c r="J25" s="24" t="inlineStr">
+        <is>
+          <t>네이버 검색 당일 +255% / 중요공시 3건</t>
+        </is>
+      </c>
+      <c r="K25" s="24" t="inlineStr">
+        <is>
+          <t>네이버, 공시</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="18" customHeight="1">
+      <c r="A26" s="20" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B26" s="20" t="n">
+        <v>13</v>
+      </c>
+      <c r="C26" s="21" t="inlineStr">
+        <is>
+          <t>대한항공</t>
+        </is>
+      </c>
+      <c r="D26" s="20" t="n">
+        <v>6</v>
+      </c>
+      <c r="E26" s="20" t="n">
+        <v>6</v>
+      </c>
+      <c r="F26" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" s="23" t="n">
+        <v>-4.25</v>
+      </c>
+      <c r="I26" s="23" t="n">
+        <v>-11.6</v>
+      </c>
+      <c r="J26" s="24" t="inlineStr">
+        <is>
+          <t>한국경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 기사 언급</t>
+        </is>
+      </c>
+      <c r="K26" s="24" t="n">
         <v/>
       </c>
     </row>
-    <row r="25" ht="18" customHeight="1">
-      <c r="A25" s="15" t="inlineStr">
-        <is>
-          <t>2026-06-23</t>
-        </is>
-      </c>
-      <c r="B25" s="15" t="n">
-        <v>12</v>
-      </c>
-      <c r="C25" s="16" t="inlineStr">
-        <is>
-          <t>에이팩트</t>
-        </is>
-      </c>
-      <c r="D25" s="15" t="n">
-        <v>8</v>
-      </c>
-      <c r="E25" s="15" t="n">
-        <v>3</v>
-      </c>
-      <c r="F25" s="15" t="n">
+    <row r="27" ht="18" customHeight="1">
+      <c r="A27" s="20" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B27" s="20" t="n">
+        <v>14</v>
+      </c>
+      <c r="C27" s="21" t="inlineStr">
+        <is>
+          <t>비투엔</t>
+        </is>
+      </c>
+      <c r="D27" s="20" t="n">
+        <v>6</v>
+      </c>
+      <c r="E27" s="20" t="n">
+        <v>3</v>
+      </c>
+      <c r="F27" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" s="20" t="n">
+        <v>3</v>
+      </c>
+      <c r="H27" s="23" t="n">
+        <v>-5.03</v>
+      </c>
+      <c r="I27" s="23" t="n">
+        <v>-7.93</v>
+      </c>
+      <c r="J27" s="24" t="inlineStr">
+        <is>
+          <t>중요공시 4건 / 중요공시 7일 +300%</t>
+        </is>
+      </c>
+      <c r="K27" s="24" t="inlineStr">
+        <is>
+          <t>공시</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="18" customHeight="1">
+      <c r="A28" s="20" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B28" s="20" t="n">
+        <v>15</v>
+      </c>
+      <c r="C28" s="21" t="inlineStr">
+        <is>
+          <t>삼성바이오로직스</t>
+        </is>
+      </c>
+      <c r="D28" s="20" t="n">
+        <v>6</v>
+      </c>
+      <c r="E28" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="F28" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="G25" s="15" t="n">
-        <v>3</v>
-      </c>
-      <c r="H25" s="19" t="n">
-        <v>-0.72</v>
-      </c>
-      <c r="I25" s="19" t="n">
-        <v>-9.140000000000001</v>
-      </c>
-      <c r="J25" s="17" t="inlineStr">
-        <is>
-          <t>중요공시 4건 / 중요공시 3일 +300% / 중요공시 7일 +100%</t>
-        </is>
-      </c>
-      <c r="K25" s="17" t="inlineStr">
+      <c r="G28" s="20" t="n">
+        <v>3</v>
+      </c>
+      <c r="H28" s="23" t="n">
+        <v>-1.7</v>
+      </c>
+      <c r="I28" s="23" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="J28" s="24" t="inlineStr">
+        <is>
+          <t>중요공시 2건 / 중요공시 3일 +100% / 중요공시 7일 +100%</t>
+        </is>
+      </c>
+      <c r="K28" s="24" t="inlineStr">
         <is>
           <t>공시</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="18" customHeight="1">
-      <c r="A26" s="15" t="inlineStr">
-        <is>
-          <t>2026-06-23</t>
-        </is>
-      </c>
-      <c r="B26" s="15" t="n">
-        <v>13</v>
-      </c>
-      <c r="C26" s="16" t="inlineStr">
-        <is>
-          <t>로봇</t>
-        </is>
-      </c>
-      <c r="D26" s="15" t="n">
-        <v>8</v>
-      </c>
-      <c r="E26" s="15" t="n">
-        <v>8</v>
-      </c>
-      <c r="F26" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G26" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H26" s="15" t="n">
+    <row r="29" ht="18" customHeight="1">
+      <c r="A29" s="20" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B29" s="20" t="n">
+        <v>16</v>
+      </c>
+      <c r="C29" s="21" t="inlineStr">
+        <is>
+          <t>전기차</t>
+        </is>
+      </c>
+      <c r="D29" s="20" t="n">
+        <v>6</v>
+      </c>
+      <c r="E29" s="20" t="n">
+        <v>6</v>
+      </c>
+      <c r="F29" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" s="20" t="n">
         <v/>
       </c>
-      <c r="I26" s="15" t="n">
+      <c r="I29" s="20" t="n">
         <v/>
       </c>
-      <c r="J26" s="17" t="inlineStr">
-        <is>
-          <t>매일경제 헤드라인 언급 / 한국경제 헤드라인 언급 / 매일경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K26" s="17" t="n">
-        <v/>
-      </c>
-    </row>
-    <row r="27" ht="18" customHeight="1">
-      <c r="A27" s="15" t="inlineStr">
-        <is>
-          <t>2026-06-23</t>
-        </is>
-      </c>
-      <c r="B27" s="15" t="n">
-        <v>14</v>
-      </c>
-      <c r="C27" s="16" t="inlineStr">
-        <is>
-          <t>LG전자</t>
-        </is>
-      </c>
-      <c r="D27" s="15" t="n">
-        <v>7</v>
-      </c>
-      <c r="E27" s="15" t="n">
-        <v>7</v>
-      </c>
-      <c r="F27" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G27" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H27" s="18" t="n">
-        <v>7.57</v>
-      </c>
-      <c r="I27" s="19" t="n">
-        <v>-6.57</v>
-      </c>
-      <c r="J27" s="17" t="inlineStr">
-        <is>
-          <t>한국경제 헤드라인 언급 / 한국경제 헤드라인 언급 / 매일경제 기사 언급</t>
-        </is>
-      </c>
-      <c r="K27" s="17" t="n">
-        <v/>
-      </c>
-    </row>
-    <row r="28" ht="18" customHeight="1">
-      <c r="A28" s="15" t="inlineStr">
-        <is>
-          <t>2026-06-23</t>
-        </is>
-      </c>
-      <c r="B28" s="15" t="n">
-        <v>15</v>
-      </c>
-      <c r="C28" s="16" t="inlineStr">
-        <is>
-          <t>철강</t>
-        </is>
-      </c>
-      <c r="D28" s="15" t="n">
-        <v>7</v>
-      </c>
-      <c r="E28" s="15" t="n">
-        <v>7</v>
-      </c>
-      <c r="F28" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G28" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H28" s="15" t="n">
-        <v/>
-      </c>
-      <c r="I28" s="15" t="n">
-        <v/>
-      </c>
-      <c r="J28" s="17" t="inlineStr">
-        <is>
-          <t>네이버뉴스 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K28" s="17" t="inlineStr">
+      <c r="J29" s="24" t="inlineStr">
+        <is>
+          <t>네이버뉴스 헤드라인 언급 / 한국경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K29" s="24" t="inlineStr">
         <is>
           <t>네이버</t>
         </is>
-      </c>
-    </row>
-    <row r="29" ht="18" customHeight="1">
-      <c r="A29" s="15" t="inlineStr">
-        <is>
-          <t>2026-06-23</t>
-        </is>
-      </c>
-      <c r="B29" s="15" t="n">
-        <v>16</v>
-      </c>
-      <c r="C29" s="16" t="inlineStr">
-        <is>
-          <t>태양광</t>
-        </is>
-      </c>
-      <c r="D29" s="15" t="n">
-        <v>7</v>
-      </c>
-      <c r="E29" s="15" t="n">
-        <v>7</v>
-      </c>
-      <c r="F29" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G29" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H29" s="15" t="n">
-        <v/>
-      </c>
-      <c r="I29" s="15" t="n">
-        <v/>
-      </c>
-      <c r="J29" s="17" t="inlineStr">
-        <is>
-          <t>매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 기사 언급</t>
-        </is>
-      </c>
-      <c r="K29" s="17" t="n">
-        <v/>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
       <c r="A30" s="20" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B30" s="20" t="n">
@@ -1600,7 +1604,7 @@
       </c>
       <c r="C30" s="21" t="inlineStr">
         <is>
-          <t>프로브잇</t>
+          <t>KT</t>
         </is>
       </c>
       <c r="D30" s="20" t="n">
@@ -1616,26 +1620,24 @@
         <v>0</v>
       </c>
       <c r="H30" s="22" t="n">
-        <v>-97.06</v>
-      </c>
-      <c r="I30" s="22" t="n">
-        <v>-97.06</v>
-      </c>
-      <c r="J30" s="23" t="inlineStr">
-        <is>
-          <t>네이버 검색 당일 +259% / 중요공시 3건</t>
-        </is>
-      </c>
-      <c r="K30" s="23" t="inlineStr">
-        <is>
-          <t>공시, 네이버</t>
-        </is>
+        <v>0.19</v>
+      </c>
+      <c r="I30" s="23" t="n">
+        <v>-7.42</v>
+      </c>
+      <c r="J30" s="24" t="inlineStr">
+        <is>
+          <t>매일경제 기사 언급 / 한국경제 헤드라인 언급 / 매일경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K30" s="24" t="n">
+        <v/>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
       <c r="A31" s="20" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B31" s="20" t="n">
@@ -1643,42 +1645,42 @@
       </c>
       <c r="C31" s="21" t="inlineStr">
         <is>
-          <t>한솔테크닉스</t>
+          <t>스피어</t>
         </is>
       </c>
       <c r="D31" s="20" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E31" s="20" t="n">
         <v>3</v>
       </c>
       <c r="F31" s="20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G31" s="20" t="n">
-        <v>3</v>
-      </c>
-      <c r="H31" s="24" t="n">
-        <v>18.2</v>
-      </c>
-      <c r="I31" s="24" t="n">
-        <v>20.22</v>
-      </c>
-      <c r="J31" s="23" t="inlineStr">
-        <is>
-          <t>네이버 검색 당일 +86% / 중요공시 2건 / 중요공시 7일 +100%</t>
-        </is>
-      </c>
-      <c r="K31" s="23" t="inlineStr">
-        <is>
-          <t>공시, 네이버</t>
+        <v>0</v>
+      </c>
+      <c r="H31" s="23" t="n">
+        <v>-10.29</v>
+      </c>
+      <c r="I31" s="23" t="n">
+        <v>-39.6</v>
+      </c>
+      <c r="J31" s="24" t="inlineStr">
+        <is>
+          <t>중요공시 4건 / 중요공시 3일 +100%</t>
+        </is>
+      </c>
+      <c r="K31" s="24" t="inlineStr">
+        <is>
+          <t>공시</t>
         </is>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
       <c r="A32" s="20" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B32" s="20" t="n">
@@ -1686,42 +1688,42 @@
       </c>
       <c r="C32" s="21" t="inlineStr">
         <is>
-          <t>비투엔</t>
+          <t>철강</t>
         </is>
       </c>
       <c r="D32" s="20" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E32" s="20" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F32" s="20" t="n">
         <v>0</v>
       </c>
       <c r="G32" s="20" t="n">
-        <v>3</v>
-      </c>
-      <c r="H32" s="24" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="I32" s="22" t="n">
-        <v>-2.05</v>
-      </c>
-      <c r="J32" s="23" t="inlineStr">
-        <is>
-          <t>중요공시 4건 / 중요공시 7일 +300%</t>
-        </is>
-      </c>
-      <c r="K32" s="23" t="inlineStr">
-        <is>
-          <t>공시</t>
+        <v>0</v>
+      </c>
+      <c r="H32" s="20" t="n">
+        <v/>
+      </c>
+      <c r="I32" s="20" t="n">
+        <v/>
+      </c>
+      <c r="J32" s="24" t="inlineStr">
+        <is>
+          <t>네이버뉴스 헤드라인 언급 / 매일경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K32" s="24" t="inlineStr">
+        <is>
+          <t>네이버</t>
         </is>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
       <c r="A33" s="20" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B33" s="20" t="n">
@@ -1729,14 +1731,14 @@
       </c>
       <c r="C33" s="21" t="inlineStr">
         <is>
-          <t>게임</t>
+          <t>현대차</t>
         </is>
       </c>
       <c r="D33" s="20" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E33" s="20" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F33" s="20" t="n">
         <v>0</v>
@@ -1744,25 +1746,25 @@
       <c r="G33" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H33" s="20" t="n">
-        <v/>
-      </c>
-      <c r="I33" s="20" t="n">
-        <v/>
-      </c>
-      <c r="J33" s="23" t="inlineStr">
-        <is>
-          <t>한국경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K33" s="23" t="n">
+      <c r="H33" s="23" t="n">
+        <v>-12.05</v>
+      </c>
+      <c r="I33" s="23" t="n">
+        <v>-20.16</v>
+      </c>
+      <c r="J33" s="24" t="inlineStr">
+        <is>
+          <t>매일경제 기사 언급 / 매일경제 헤드라인 언급 / 매일경제 기사 언급</t>
+        </is>
+      </c>
+      <c r="K33" s="24" t="n">
         <v/>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
       <c r="A34" s="20" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B34" s="20" t="n">
@@ -1770,14 +1772,14 @@
       </c>
       <c r="C34" s="21" t="inlineStr">
         <is>
-          <t>카카오</t>
+          <t>노블엠앤비</t>
         </is>
       </c>
       <c r="D34" s="20" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E34" s="20" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F34" s="20" t="n">
         <v>0</v>
@@ -1786,24 +1788,26 @@
         <v>0</v>
       </c>
       <c r="H34" s="22" t="n">
-        <v>-2.52</v>
-      </c>
-      <c r="I34" s="22" t="n">
-        <v>-9.69</v>
-      </c>
-      <c r="J34" s="23" t="inlineStr">
-        <is>
-          <t>한국경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K34" s="23" t="n">
-        <v/>
+        <v>4.17</v>
+      </c>
+      <c r="I34" s="23" t="n">
+        <v>-93.92</v>
+      </c>
+      <c r="J34" s="24" t="inlineStr">
+        <is>
+          <t>네이버 검색 당일 +155% / 중요공시 2건</t>
+        </is>
+      </c>
+      <c r="K34" s="24" t="inlineStr">
+        <is>
+          <t>네이버, 공시</t>
+        </is>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
       <c r="A35" s="20" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B35" s="20" t="n">
@@ -1811,40 +1815,42 @@
       </c>
       <c r="C35" s="21" t="inlineStr">
         <is>
-          <t>두산로보틱스</t>
+          <t>센서뷰</t>
         </is>
       </c>
       <c r="D35" s="20" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E35" s="20" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F35" s="20" t="n">
         <v>0</v>
       </c>
       <c r="G35" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H35" s="22" t="n">
-        <v>-1.38</v>
-      </c>
-      <c r="I35" s="22" t="n">
-        <v>-9.869999999999999</v>
-      </c>
-      <c r="J35" s="23" t="inlineStr">
-        <is>
-          <t>매일경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K35" s="23" t="n">
-        <v/>
+        <v>3</v>
+      </c>
+      <c r="H35" s="23" t="n">
+        <v>-2.79</v>
+      </c>
+      <c r="I35" s="23" t="n">
+        <v>-15.56</v>
+      </c>
+      <c r="J35" s="24" t="inlineStr">
+        <is>
+          <t>중요공시 2건 / 중요공시 7일 +100%</t>
+        </is>
+      </c>
+      <c r="K35" s="24" t="inlineStr">
+        <is>
+          <t>공시</t>
+        </is>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
       <c r="A36" s="20" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B36" s="20" t="n">
@@ -1852,14 +1858,14 @@
       </c>
       <c r="C36" s="21" t="inlineStr">
         <is>
-          <t>삼성생명</t>
+          <t>미래에셋증권</t>
         </is>
       </c>
       <c r="D36" s="20" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E36" s="20" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F36" s="20" t="n">
         <v>0</v>
@@ -1867,27 +1873,27 @@
       <c r="G36" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H36" s="22" t="n">
-        <v>-9.359999999999999</v>
-      </c>
-      <c r="I36" s="24" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="J36" s="23" t="inlineStr">
-        <is>
-          <t>네이버뉴스 헤드라인 언급 / 매일경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K36" s="23" t="inlineStr">
-        <is>
-          <t>네이버</t>
+      <c r="H36" s="23" t="n">
+        <v>-8.57</v>
+      </c>
+      <c r="I36" s="23" t="n">
+        <v>-17.84</v>
+      </c>
+      <c r="J36" s="24" t="inlineStr">
+        <is>
+          <t>중요공시 2건 / 네이버뉴스 기사 언급 / 네이버뉴스 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K36" s="24" t="inlineStr">
+        <is>
+          <t>네이버, 공시</t>
         </is>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
       <c r="A37" s="20" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B37" s="20" t="n">
@@ -1895,40 +1901,42 @@
       </c>
       <c r="C37" s="21" t="inlineStr">
         <is>
-          <t>유안타증권</t>
+          <t>HJ중공업</t>
         </is>
       </c>
       <c r="D37" s="20" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E37" s="20" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F37" s="20" t="n">
         <v>0</v>
       </c>
       <c r="G37" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H37" s="22" t="n">
-        <v>-2.95</v>
-      </c>
-      <c r="I37" s="22" t="n">
-        <v>-8.09</v>
-      </c>
-      <c r="J37" s="23" t="inlineStr">
-        <is>
-          <t>매일경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K37" s="23" t="n">
-        <v/>
+        <v>3</v>
+      </c>
+      <c r="H37" s="23" t="n">
+        <v>-8.41</v>
+      </c>
+      <c r="I37" s="23" t="n">
+        <v>-14.6</v>
+      </c>
+      <c r="J37" s="24" t="inlineStr">
+        <is>
+          <t>중요공시 2건 / 중요공시 7일 +100%</t>
+        </is>
+      </c>
+      <c r="K37" s="24" t="inlineStr">
+        <is>
+          <t>공시</t>
+        </is>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
       <c r="A38" s="20" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B38" s="20" t="n">
@@ -1936,14 +1944,14 @@
       </c>
       <c r="C38" s="21" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>셀트리온</t>
         </is>
       </c>
       <c r="D38" s="20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E38" s="20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F38" s="20" t="n">
         <v>0</v>
@@ -1951,27 +1959,27 @@
       <c r="G38" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H38" s="22" t="n">
-        <v>-5.73</v>
-      </c>
-      <c r="I38" s="22" t="n">
-        <v>-29.25</v>
-      </c>
-      <c r="J38" s="23" t="inlineStr">
-        <is>
-          <t>네이버 검색 당일 +122% / 한국경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K38" s="23" t="inlineStr">
-        <is>
-          <t>네이버</t>
+      <c r="H38" s="23" t="n">
+        <v>-4.75</v>
+      </c>
+      <c r="I38" s="23" t="n">
+        <v>-8.02</v>
+      </c>
+      <c r="J38" s="24" t="inlineStr">
+        <is>
+          <t>중요공시 2건 / 네이버뉴스 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K38" s="24" t="inlineStr">
+        <is>
+          <t>네이버, 공시</t>
         </is>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
       <c r="A39" s="20" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B39" s="20" t="n">
@@ -1979,7 +1987,7 @@
       </c>
       <c r="C39" s="21" t="inlineStr">
         <is>
-          <t>삼화네트웍스</t>
+          <t>팬오션</t>
         </is>
       </c>
       <c r="D39" s="20" t="n">
@@ -1994,27 +2002,27 @@
       <c r="G39" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H39" s="24" t="n">
-        <v>5.24</v>
-      </c>
-      <c r="I39" s="24" t="n">
-        <v>7.86</v>
-      </c>
-      <c r="J39" s="23" t="inlineStr">
-        <is>
-          <t>네이버 검색 당일 +346% / 중요공시 2건</t>
-        </is>
-      </c>
-      <c r="K39" s="23" t="inlineStr">
-        <is>
-          <t>공시, 네이버</t>
+      <c r="H39" s="23" t="n">
+        <v>-4.98</v>
+      </c>
+      <c r="I39" s="23" t="n">
+        <v>-12.55</v>
+      </c>
+      <c r="J39" s="24" t="inlineStr">
+        <is>
+          <t>중요공시 1건 / 네이버뉴스 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K39" s="24" t="inlineStr">
+        <is>
+          <t>네이버, 공시</t>
         </is>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
       <c r="A40" s="20" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B40" s="20" t="n">
@@ -2022,7 +2030,7 @@
       </c>
       <c r="C40" s="21" t="inlineStr">
         <is>
-          <t>노블엠앤비</t>
+          <t>한미반도체</t>
         </is>
       </c>
       <c r="D40" s="20" t="n">
@@ -2037,285 +2045,281 @@
       <c r="G40" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H40" s="22" t="n">
-        <v>-94.16</v>
-      </c>
-      <c r="I40" s="22" t="n">
-        <v>-94.16</v>
-      </c>
-      <c r="J40" s="23" t="inlineStr">
-        <is>
-          <t>네이버 검색 당일 +140% / 중요공시 2건</t>
-        </is>
-      </c>
-      <c r="K40" s="23" t="inlineStr">
-        <is>
-          <t>공시, 네이버</t>
-        </is>
+      <c r="H40" s="23" t="n">
+        <v>-14.43</v>
+      </c>
+      <c r="I40" s="23" t="n">
+        <v>-21.46</v>
+      </c>
+      <c r="J40" s="24" t="inlineStr">
+        <is>
+          <t>한국경제 헤드라인 언급 / 매일경제 기사 언급</t>
+        </is>
+      </c>
+      <c r="K40" s="24" t="n">
+        <v/>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
-      <c r="A41" s="20" t="inlineStr">
-        <is>
-          <t>2026-06-23</t>
-        </is>
-      </c>
-      <c r="B41" s="20" t="n">
+      <c r="A41" s="25" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B41" s="25" t="n">
         <v>28</v>
       </c>
-      <c r="C41" s="21" t="inlineStr">
-        <is>
-          <t>다스코</t>
-        </is>
-      </c>
-      <c r="D41" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="E41" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="F41" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G41" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H41" s="22" t="n">
-        <v>-15.71</v>
-      </c>
-      <c r="I41" s="24" t="n">
-        <v>5.22</v>
-      </c>
-      <c r="J41" s="23" t="inlineStr">
-        <is>
-          <t>네이버 검색 당일 +110% / 중요공시 1건</t>
-        </is>
-      </c>
-      <c r="K41" s="23" t="inlineStr">
-        <is>
-          <t>공시, 네이버</t>
+      <c r="C41" s="26" t="inlineStr">
+        <is>
+          <t>바이온</t>
+        </is>
+      </c>
+      <c r="D41" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="E41" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="F41" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G41" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" s="27" t="n">
+        <v>68.42</v>
+      </c>
+      <c r="I41" s="28" t="n">
+        <v>-94.7</v>
+      </c>
+      <c r="J41" s="29" t="inlineStr">
+        <is>
+          <t>네이버 검색 당일 +81% / 중요공시 2건</t>
+        </is>
+      </c>
+      <c r="K41" s="29" t="inlineStr">
+        <is>
+          <t>네이버, 공시</t>
         </is>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
-      <c r="A42" s="20" t="inlineStr">
-        <is>
-          <t>2026-06-23</t>
-        </is>
-      </c>
-      <c r="B42" s="20" t="n">
+      <c r="A42" s="25" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B42" s="25" t="n">
         <v>29</v>
       </c>
-      <c r="C42" s="21" t="inlineStr">
-        <is>
-          <t>대원전선</t>
-        </is>
-      </c>
-      <c r="D42" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="E42" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="F42" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G42" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H42" s="22" t="n">
-        <v>-6.67</v>
-      </c>
-      <c r="I42" s="22" t="n">
-        <v>-3.09</v>
-      </c>
-      <c r="J42" s="23" t="inlineStr">
-        <is>
-          <t>네이버 검색 당일 +104% / 중요공시 1건</t>
-        </is>
-      </c>
-      <c r="K42" s="23" t="inlineStr">
-        <is>
-          <t>공시, 네이버</t>
-        </is>
+      <c r="C42" s="26" t="inlineStr">
+        <is>
+          <t>키스트론</t>
+        </is>
+      </c>
+      <c r="D42" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="E42" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="F42" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G42" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" s="28" t="n">
+        <v>-10.97</v>
+      </c>
+      <c r="I42" s="27" t="n">
+        <v>18.91</v>
+      </c>
+      <c r="J42" s="29" t="inlineStr">
+        <is>
+          <t>매일경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K42" s="29" t="n">
+        <v/>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1">
-      <c r="A43" s="20" t="inlineStr">
-        <is>
-          <t>2026-06-23</t>
-        </is>
-      </c>
-      <c r="B43" s="20" t="n">
+      <c r="A43" s="25" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B43" s="25" t="n">
         <v>30</v>
       </c>
-      <c r="C43" s="21" t="inlineStr">
-        <is>
-          <t>스피어</t>
-        </is>
-      </c>
-      <c r="D43" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="E43" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="F43" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G43" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H43" s="22" t="n">
-        <v>-12.28</v>
-      </c>
-      <c r="I43" s="22" t="n">
-        <v>-37.07</v>
-      </c>
-      <c r="J43" s="23" t="inlineStr">
-        <is>
-          <t>중요공시 2건 / 매일경제 기사 언급 / 매일경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K43" s="23" t="inlineStr">
+      <c r="C43" s="26" t="inlineStr">
+        <is>
+          <t>소룩스</t>
+        </is>
+      </c>
+      <c r="D43" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="E43" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="F43" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G43" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" s="27" t="n">
+        <v>14.42</v>
+      </c>
+      <c r="I43" s="27" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="J43" s="29" t="inlineStr">
+        <is>
+          <t>중요공시 3건</t>
+        </is>
+      </c>
+      <c r="K43" s="29" t="inlineStr">
         <is>
           <t>공시</t>
         </is>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
-      <c r="A44" s="20" t="inlineStr">
-        <is>
-          <t>2026-06-23</t>
-        </is>
-      </c>
-      <c r="B44" s="20" t="n">
+      <c r="A44" s="25" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B44" s="25" t="n">
         <v>31</v>
       </c>
-      <c r="C44" s="21" t="inlineStr">
-        <is>
-          <t>센서뷰</t>
-        </is>
-      </c>
-      <c r="D44" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="E44" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="F44" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G44" s="20" t="n">
-        <v>3</v>
-      </c>
-      <c r="H44" s="22" t="n">
-        <v>-7.33</v>
-      </c>
-      <c r="I44" s="22" t="n">
-        <v>-13.48</v>
-      </c>
-      <c r="J44" s="23" t="inlineStr">
-        <is>
-          <t>중요공시 2건 / 중요공시 7일 +100%</t>
-        </is>
-      </c>
-      <c r="K44" s="23" t="inlineStr">
+      <c r="C44" s="26" t="inlineStr">
+        <is>
+          <t>KBI메탈</t>
+        </is>
+      </c>
+      <c r="D44" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="E44" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="F44" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="G44" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" s="28" t="n">
+        <v>-0.57</v>
+      </c>
+      <c r="I44" s="28" t="n">
+        <v>-7.47</v>
+      </c>
+      <c r="J44" s="29" t="inlineStr">
+        <is>
+          <t>중요공시 2건 / 중요공시 3일 +100%</t>
+        </is>
+      </c>
+      <c r="K44" s="29" t="inlineStr">
         <is>
           <t>공시</t>
         </is>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
-      <c r="A45" s="20" t="inlineStr">
-        <is>
-          <t>2026-06-23</t>
-        </is>
-      </c>
-      <c r="B45" s="20" t="n">
+      <c r="A45" s="25" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B45" s="25" t="n">
         <v>32</v>
       </c>
-      <c r="C45" s="21" t="inlineStr">
-        <is>
-          <t>HJ중공업</t>
-        </is>
-      </c>
-      <c r="D45" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="E45" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="F45" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G45" s="20" t="n">
-        <v>3</v>
-      </c>
-      <c r="H45" s="22" t="n">
-        <v>-4.04</v>
-      </c>
-      <c r="I45" s="22" t="n">
-        <v>-8.15</v>
-      </c>
-      <c r="J45" s="23" t="inlineStr">
-        <is>
-          <t>중요공시 2건 / 중요공시 7일 +100%</t>
-        </is>
-      </c>
-      <c r="K45" s="23" t="inlineStr">
+      <c r="C45" s="26" t="inlineStr">
+        <is>
+          <t>우성머티리얼스</t>
+        </is>
+      </c>
+      <c r="D45" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="E45" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="F45" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G45" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" s="28" t="n">
+        <v>-1.12</v>
+      </c>
+      <c r="I45" s="28" t="n">
+        <v>-16.13</v>
+      </c>
+      <c r="J45" s="29" t="inlineStr">
+        <is>
+          <t>중요공시 7건</t>
+        </is>
+      </c>
+      <c r="K45" s="29" t="inlineStr">
         <is>
           <t>공시</t>
         </is>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
-      <c r="A46" s="20" t="inlineStr">
-        <is>
-          <t>2026-06-23</t>
-        </is>
-      </c>
-      <c r="B46" s="20" t="n">
+      <c r="A46" s="25" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B46" s="25" t="n">
         <v>33</v>
       </c>
-      <c r="C46" s="21" t="inlineStr">
-        <is>
-          <t>원전</t>
-        </is>
-      </c>
-      <c r="D46" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="E46" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="F46" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G46" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H46" s="20" t="n">
-        <v/>
-      </c>
-      <c r="I46" s="20" t="n">
-        <v/>
-      </c>
-      <c r="J46" s="23" t="inlineStr">
-        <is>
-          <t>네이버뉴스 기사 언급 / 한국경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K46" s="23" t="inlineStr">
-        <is>
-          <t>네이버</t>
+      <c r="C46" s="26" t="inlineStr">
+        <is>
+          <t>경남제약</t>
+        </is>
+      </c>
+      <c r="D46" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="E46" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="F46" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G46" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" s="27" t="n">
+        <v>29.75</v>
+      </c>
+      <c r="I46" s="27" t="n">
+        <v>18.19</v>
+      </c>
+      <c r="J46" s="29" t="inlineStr">
+        <is>
+          <t>중요공시 4건</t>
+        </is>
+      </c>
+      <c r="K46" s="29" t="inlineStr">
+        <is>
+          <t>공시</t>
         </is>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
       <c r="A47" s="25" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B47" s="25" t="n">
@@ -2323,7 +2327,7 @@
       </c>
       <c r="C47" s="26" t="inlineStr">
         <is>
-          <t>강동씨앤엘</t>
+          <t>넥써쓰</t>
         </is>
       </c>
       <c r="D47" s="25" t="n">
@@ -2338,27 +2342,27 @@
       <c r="G47" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H47" s="27" t="n">
-        <v>-12.22</v>
+      <c r="H47" s="28" t="n">
+        <v>-11.22</v>
       </c>
       <c r="I47" s="28" t="n">
-        <v>79.66</v>
+        <v>-20.36</v>
       </c>
       <c r="J47" s="29" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +1615%</t>
+          <t>중요공시 3건</t>
         </is>
       </c>
       <c r="K47" s="29" t="inlineStr">
         <is>
-          <t>네이버</t>
+          <t>공시</t>
         </is>
       </c>
     </row>
     <row r="48" ht="18" customHeight="1">
       <c r="A48" s="25" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B48" s="25" t="n">
@@ -2366,7 +2370,7 @@
       </c>
       <c r="C48" s="26" t="inlineStr">
         <is>
-          <t>JW신약</t>
+          <t>LB세미콘</t>
         </is>
       </c>
       <c r="D48" s="25" t="n">
@@ -2382,26 +2386,26 @@
         <v>0</v>
       </c>
       <c r="H48" s="28" t="n">
-        <v>16.92</v>
+        <v>-12.95</v>
       </c>
       <c r="I48" s="28" t="n">
-        <v>53.8</v>
+        <v>-9.859999999999999</v>
       </c>
       <c r="J48" s="29" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +1499%</t>
+          <t>중요공시 3건</t>
         </is>
       </c>
       <c r="K48" s="29" t="inlineStr">
         <is>
-          <t>네이버</t>
+          <t>공시</t>
         </is>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1">
       <c r="A49" s="25" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B49" s="25" t="n">
@@ -2409,42 +2413,42 @@
       </c>
       <c r="C49" s="26" t="inlineStr">
         <is>
-          <t>남화토건</t>
+          <t>진흥기업</t>
         </is>
       </c>
       <c r="D49" s="25" t="n">
         <v>3</v>
       </c>
       <c r="E49" s="25" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F49" s="25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G49" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H49" s="27" t="n">
-        <v>-10.33</v>
+      <c r="H49" s="28" t="n">
+        <v>-7.5</v>
       </c>
       <c r="I49" s="28" t="n">
-        <v>31.77</v>
+        <v>-16.77</v>
       </c>
       <c r="J49" s="29" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +1018%</t>
+          <t>중요공시 2건 / 중요공시 3일 +100%</t>
         </is>
       </c>
       <c r="K49" s="29" t="inlineStr">
         <is>
-          <t>네이버</t>
+          <t>공시</t>
         </is>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
       <c r="A50" s="25" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B50" s="25" t="n">
@@ -2452,42 +2456,42 @@
       </c>
       <c r="C50" s="26" t="inlineStr">
         <is>
-          <t>삼익제약</t>
+          <t>시너지이노베이션</t>
         </is>
       </c>
       <c r="D50" s="25" t="n">
         <v>3</v>
       </c>
       <c r="E50" s="25" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F50" s="25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G50" s="25" t="n">
         <v>0</v>
       </c>
       <c r="H50" s="28" t="n">
-        <v>6.54</v>
+        <v>-8.279999999999999</v>
       </c>
       <c r="I50" s="28" t="n">
-        <v>16.36</v>
+        <v>-14.05</v>
       </c>
       <c r="J50" s="29" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +866%</t>
+          <t>중요공시 2건 / 중요공시 3일 +100%</t>
         </is>
       </c>
       <c r="K50" s="29" t="inlineStr">
         <is>
-          <t>네이버</t>
+          <t>공시</t>
         </is>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
       <c r="A51" s="25" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B51" s="25" t="n">
@@ -2495,7 +2499,7 @@
       </c>
       <c r="C51" s="26" t="inlineStr">
         <is>
-          <t>TS트릴리온</t>
+          <t>AI반도체</t>
         </is>
       </c>
       <c r="D51" s="25" t="n">
@@ -2510,15 +2514,15 @@
       <c r="G51" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H51" s="28" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="I51" s="27" t="n">
-        <v>-15.51</v>
+      <c r="H51" s="25" t="n">
+        <v/>
+      </c>
+      <c r="I51" s="25" t="n">
+        <v/>
       </c>
       <c r="J51" s="29" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +497%</t>
+          <t>네이버뉴스 헤드라인 언급</t>
         </is>
       </c>
       <c r="K51" s="29" t="inlineStr">
@@ -2530,7 +2534,7 @@
     <row r="52" ht="18" customHeight="1">
       <c r="A52" s="25" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B52" s="25" t="n">
@@ -2538,7 +2542,7 @@
       </c>
       <c r="C52" s="26" t="inlineStr">
         <is>
-          <t>예스티</t>
+          <t>SK텔레콤</t>
         </is>
       </c>
       <c r="D52" s="25" t="n">
@@ -2554,26 +2558,24 @@
         <v>0</v>
       </c>
       <c r="H52" s="28" t="n">
-        <v>10.63</v>
+        <v>-4.56</v>
       </c>
       <c r="I52" s="28" t="n">
-        <v>20.88</v>
+        <v>-10.19</v>
       </c>
       <c r="J52" s="29" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +497%</t>
-        </is>
-      </c>
-      <c r="K52" s="29" t="inlineStr">
-        <is>
-          <t>네이버</t>
-        </is>
+          <t>매일경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K52" s="29" t="n">
+        <v/>
       </c>
     </row>
     <row r="53" ht="18" customHeight="1">
       <c r="A53" s="25" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B53" s="25" t="n">
@@ -2581,7 +2583,7 @@
       </c>
       <c r="C53" s="26" t="inlineStr">
         <is>
-          <t>현대약품</t>
+          <t>두산로보틱스</t>
         </is>
       </c>
       <c r="D53" s="25" t="n">
@@ -2597,26 +2599,24 @@
         <v>0</v>
       </c>
       <c r="H53" s="28" t="n">
-        <v>0.86</v>
+        <v>-11.55</v>
       </c>
       <c r="I53" s="28" t="n">
-        <v>10.48</v>
+        <v>-18.53</v>
       </c>
       <c r="J53" s="29" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +446%</t>
-        </is>
-      </c>
-      <c r="K53" s="29" t="inlineStr">
-        <is>
-          <t>네이버</t>
-        </is>
+          <t>매일경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K53" s="29" t="n">
+        <v/>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
       <c r="A54" s="25" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B54" s="25" t="n">
@@ -2624,7 +2624,7 @@
       </c>
       <c r="C54" s="26" t="inlineStr">
         <is>
-          <t>위더스제약</t>
+          <t>성도이엔지</t>
         </is>
       </c>
       <c r="D54" s="25" t="n">
@@ -2639,27 +2639,25 @@
       <c r="G54" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H54" s="27" t="n">
-        <v>-3.95</v>
-      </c>
-      <c r="I54" s="28" t="n">
-        <v>4.03</v>
+      <c r="H54" s="28" t="n">
+        <v>-7.69</v>
+      </c>
+      <c r="I54" s="27" t="n">
+        <v>2.97</v>
       </c>
       <c r="J54" s="29" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +445%</t>
-        </is>
-      </c>
-      <c r="K54" s="29" t="inlineStr">
-        <is>
-          <t>네이버</t>
-        </is>
+          <t>매일경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K54" s="29" t="n">
+        <v/>
       </c>
     </row>
     <row r="55" ht="18" customHeight="1">
       <c r="A55" s="25" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B55" s="25" t="n">
@@ -2667,7 +2665,7 @@
       </c>
       <c r="C55" s="26" t="inlineStr">
         <is>
-          <t>삼화전자</t>
+          <t>방산</t>
         </is>
       </c>
       <c r="D55" s="25" t="n">
@@ -2682,27 +2680,25 @@
       <c r="G55" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H55" s="27" t="n">
-        <v>-14.82</v>
-      </c>
-      <c r="I55" s="28" t="n">
-        <v>13.91</v>
+      <c r="H55" s="25" t="n">
+        <v/>
+      </c>
+      <c r="I55" s="25" t="n">
+        <v/>
       </c>
       <c r="J55" s="29" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +428%</t>
-        </is>
-      </c>
-      <c r="K55" s="29" t="inlineStr">
-        <is>
-          <t>네이버</t>
-        </is>
+          <t>한국경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K55" s="29" t="n">
+        <v/>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1">
       <c r="A56" s="25" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B56" s="25" t="n">
@@ -2710,7 +2706,7 @@
       </c>
       <c r="C56" s="26" t="inlineStr">
         <is>
-          <t>한울반도체</t>
+          <t>태양광</t>
         </is>
       </c>
       <c r="D56" s="25" t="n">
@@ -2725,27 +2721,25 @@
       <c r="G56" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H56" s="28" t="n">
-        <v>29.91</v>
-      </c>
-      <c r="I56" s="28" t="n">
-        <v>110.65</v>
+      <c r="H56" s="25" t="n">
+        <v/>
+      </c>
+      <c r="I56" s="25" t="n">
+        <v/>
       </c>
       <c r="J56" s="29" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +406%</t>
-        </is>
-      </c>
-      <c r="K56" s="29" t="inlineStr">
-        <is>
-          <t>네이버</t>
-        </is>
+          <t>매일경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K56" s="29" t="n">
+        <v/>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1">
       <c r="A57" s="25" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B57" s="25" t="n">
@@ -2753,14 +2747,14 @@
       </c>
       <c r="C57" s="26" t="inlineStr">
         <is>
-          <t>보해양조</t>
+          <t>에이테크솔루션</t>
         </is>
       </c>
       <c r="D57" s="25" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E57" s="25" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F57" s="25" t="n">
         <v>0</v>
@@ -2769,14 +2763,14 @@
         <v>0</v>
       </c>
       <c r="H57" s="28" t="n">
-        <v>9.859999999999999</v>
-      </c>
-      <c r="I57" s="28" t="n">
-        <v>64.90000000000001</v>
+        <v>-4.39</v>
+      </c>
+      <c r="I57" s="27" t="n">
+        <v>15.25</v>
       </c>
       <c r="J57" s="29" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +289%</t>
+          <t>네이버 검색 당일 +72%</t>
         </is>
       </c>
       <c r="K57" s="29" t="inlineStr">
@@ -2788,7 +2782,7 @@
     <row r="58" ht="18" customHeight="1">
       <c r="A58" s="25" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B58" s="25" t="n">
@@ -2796,14 +2790,14 @@
       </c>
       <c r="C58" s="26" t="inlineStr">
         <is>
-          <t>하이스틸</t>
+          <t>케이뱅크</t>
         </is>
       </c>
       <c r="D58" s="25" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E58" s="25" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F58" s="25" t="n">
         <v>0</v>
@@ -2812,26 +2806,24 @@
         <v>0</v>
       </c>
       <c r="H58" s="28" t="n">
-        <v>1.24</v>
+        <v>-3.66</v>
       </c>
       <c r="I58" s="28" t="n">
-        <v>2.02</v>
+        <v>-12.06</v>
       </c>
       <c r="J58" s="29" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +222%</t>
-        </is>
-      </c>
-      <c r="K58" s="29" t="inlineStr">
-        <is>
-          <t>네이버</t>
-        </is>
+          <t>한국경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K58" s="29" t="n">
+        <v/>
       </c>
     </row>
     <row r="59" ht="18" customHeight="1">
       <c r="A59" s="25" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B59" s="25" t="n">
@@ -2839,14 +2831,14 @@
       </c>
       <c r="C59" s="26" t="inlineStr">
         <is>
-          <t>율촌</t>
+          <t>NH투자증권</t>
         </is>
       </c>
       <c r="D59" s="25" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E59" s="25" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F59" s="25" t="n">
         <v>0</v>
@@ -2855,14 +2847,14 @@
         <v>0</v>
       </c>
       <c r="H59" s="28" t="n">
-        <v>9.029999999999999</v>
+        <v>-6.66</v>
       </c>
       <c r="I59" s="28" t="n">
-        <v>38.23</v>
+        <v>-12.48</v>
       </c>
       <c r="J59" s="29" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +219%</t>
+          <t>네이버뉴스 기사 언급 / 매일경제 기사 언급</t>
         </is>
       </c>
       <c r="K59" s="29" t="inlineStr">
@@ -2874,7 +2866,7 @@
     <row r="60" ht="18" customHeight="1">
       <c r="A60" s="25" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B60" s="25" t="n">
@@ -2882,14 +2874,14 @@
       </c>
       <c r="C60" s="26" t="inlineStr">
         <is>
-          <t>제이앤티씨</t>
+          <t>삼성전기</t>
         </is>
       </c>
       <c r="D60" s="25" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E60" s="25" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F60" s="25" t="n">
         <v>0</v>
@@ -2898,26 +2890,24 @@
         <v>0</v>
       </c>
       <c r="H60" s="28" t="n">
-        <v>8.81</v>
+        <v>-10.68</v>
       </c>
       <c r="I60" s="28" t="n">
-        <v>33.63</v>
+        <v>-2.83</v>
       </c>
       <c r="J60" s="29" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +218%</t>
-        </is>
-      </c>
-      <c r="K60" s="29" t="inlineStr">
-        <is>
-          <t>네이버</t>
-        </is>
+          <t>한국경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K60" s="29" t="n">
+        <v/>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
       <c r="A61" s="25" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B61" s="25" t="n">
@@ -2925,14 +2915,14 @@
       </c>
       <c r="C61" s="26" t="inlineStr">
         <is>
-          <t>성문전자</t>
+          <t>카카오</t>
         </is>
       </c>
       <c r="D61" s="25" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E61" s="25" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F61" s="25" t="n">
         <v>0</v>
@@ -2941,26 +2931,24 @@
         <v>0</v>
       </c>
       <c r="H61" s="28" t="n">
-        <v>9</v>
+        <v>-6.93</v>
       </c>
       <c r="I61" s="28" t="n">
-        <v>51.42</v>
+        <v>-15.33</v>
       </c>
       <c r="J61" s="29" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +197%</t>
-        </is>
-      </c>
-      <c r="K61" s="29" t="inlineStr">
-        <is>
-          <t>네이버</t>
-        </is>
+          <t>한국경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K61" s="29" t="n">
+        <v/>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1">
       <c r="A62" s="25" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B62" s="25" t="n">
@@ -2968,14 +2956,14 @@
       </c>
       <c r="C62" s="26" t="inlineStr">
         <is>
-          <t>메리츠제2호스팩</t>
+          <t>원전</t>
         </is>
       </c>
       <c r="D62" s="25" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E62" s="25" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F62" s="25" t="n">
         <v>0</v>
@@ -2983,27 +2971,25 @@
       <c r="G62" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H62" s="27" t="n">
-        <v>-0.8100000000000001</v>
-      </c>
-      <c r="I62" s="27" t="n">
-        <v>-0.8100000000000001</v>
+      <c r="H62" s="25" t="n">
+        <v/>
+      </c>
+      <c r="I62" s="25" t="n">
+        <v/>
       </c>
       <c r="J62" s="29" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +194%</t>
-        </is>
-      </c>
-      <c r="K62" s="29" t="inlineStr">
-        <is>
-          <t>네이버</t>
-        </is>
+          <t>한국경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K62" s="29" t="n">
+        <v/>
       </c>
     </row>
     <row r="63" ht="18" customHeight="1">
       <c r="A63" s="25" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B63" s="25" t="n">
@@ -3011,14 +2997,14 @@
       </c>
       <c r="C63" s="26" t="inlineStr">
         <is>
-          <t>티웨이홀딩스</t>
+          <t>스테이블코인</t>
         </is>
       </c>
       <c r="D63" s="25" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E63" s="25" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F63" s="25" t="n">
         <v>0</v>
@@ -3026,21 +3012,19 @@
       <c r="G63" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H63" s="27" t="n">
-        <v>-7.91</v>
-      </c>
-      <c r="I63" s="27" t="n">
-        <v>-9.94</v>
+      <c r="H63" s="25" t="n">
+        <v/>
+      </c>
+      <c r="I63" s="25" t="n">
+        <v/>
       </c>
       <c r="J63" s="29" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +188%</t>
-        </is>
-      </c>
-      <c r="K63" s="29" t="inlineStr">
-        <is>
-          <t>네이버</t>
-        </is>
+          <t>매일경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K63" s="29" t="n">
+        <v/>
       </c>
     </row>
   </sheetData>
@@ -3136,22 +3120,22 @@
         <v>1</v>
       </c>
       <c r="C3" s="25" t="n">
-        <v>62</v>
+        <v>114</v>
       </c>
       <c r="D3" s="25" t="n">
-        <v>62</v>
+        <v>114</v>
       </c>
       <c r="E3" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F3" s="25" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G3" s="25" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="H3" s="25" t="n"/>
@@ -3160,36 +3144,36 @@
     <row r="4" ht="18" customHeight="1">
       <c r="A4" s="26" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>SK</t>
         </is>
       </c>
       <c r="B4" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C4" s="25" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D4" s="25" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E4" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F4" s="25" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G4" s="25" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="H4" s="28" t="n">
-        <v>5.61</v>
-      </c>
-      <c r="I4" s="28" t="n">
-        <v>27.58</v>
+        <v>-3.42</v>
+      </c>
+      <c r="I4" s="27" t="n">
+        <v>4.75</v>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1">
@@ -3202,96 +3186,100 @@
         <v>1</v>
       </c>
       <c r="C5" s="25" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D5" s="25" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E5" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F5" s="25" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G5" s="25" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
-        </is>
-      </c>
-      <c r="H5" s="27" t="n">
-        <v>-0.14</v>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="H5" s="28" t="n">
+        <v>-12.31</v>
       </c>
       <c r="I5" s="28" t="n">
-        <v>4.9</v>
+        <v>-9.619999999999999</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
       <c r="A6" s="26" t="inlineStr">
         <is>
-          <t>LG</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B6" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C6" s="25" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="D6" s="25" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="E6" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F6" s="25" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G6" s="25" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="H6" s="28" t="n">
-        <v>0.92</v>
+        <v>-12.47</v>
       </c>
       <c r="I6" s="27" t="n">
-        <v>-7.18</v>
+        <v>7.26</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
       <c r="A7" s="26" t="inlineStr">
         <is>
-          <t>바이오</t>
+          <t>LG</t>
         </is>
       </c>
       <c r="B7" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C7" s="25" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="D7" s="25" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="E7" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F7" s="25" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G7" s="25" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
-        </is>
-      </c>
-      <c r="H7" s="25" t="n"/>
-      <c r="I7" s="25" t="n"/>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="H7" s="28" t="n">
+        <v>-10.28</v>
+      </c>
+      <c r="I7" s="28" t="n">
+        <v>-13.58</v>
+      </c>
     </row>
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="26" t="inlineStr">
@@ -3303,22 +3291,22 @@
         <v>1</v>
       </c>
       <c r="C8" s="25" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D8" s="25" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E8" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F8" s="25" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G8" s="25" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="H8" s="25" t="n"/>
@@ -3327,73 +3315,73 @@
     <row r="9" ht="18" customHeight="1">
       <c r="A9" s="26" t="inlineStr">
         <is>
-          <t>SK스퀘어</t>
+          <t>로봇</t>
         </is>
       </c>
       <c r="B9" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C9" s="25" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D9" s="25" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E9" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F9" s="25" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G9" s="25" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
-        </is>
-      </c>
-      <c r="H9" s="28" t="n">
-        <v>10.67</v>
-      </c>
-      <c r="I9" s="28" t="n">
-        <v>39.42</v>
-      </c>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="H9" s="25" t="n"/>
+      <c r="I9" s="25" t="n"/>
     </row>
     <row r="10" ht="18" customHeight="1">
       <c r="A10" s="26" t="inlineStr">
         <is>
-          <t>제약</t>
+          <t>LG전자</t>
         </is>
       </c>
       <c r="B10" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C10" s="25" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D10" s="25" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E10" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F10" s="25" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G10" s="25" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
-        </is>
-      </c>
-      <c r="H10" s="25" t="n"/>
-      <c r="I10" s="25" t="n"/>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="H10" s="28" t="n">
+        <v>-11.21</v>
+      </c>
+      <c r="I10" s="28" t="n">
+        <v>-13.68</v>
+      </c>
     </row>
     <row r="11" ht="18" customHeight="1">
       <c r="A11" s="26" t="inlineStr">
         <is>
-          <t>삼성바이오로직스</t>
+          <t>제약</t>
         </is>
       </c>
       <c r="B11" s="25" t="n">
@@ -3410,249 +3398,249 @@
       </c>
       <c r="F11" s="25" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G11" s="25" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
-        </is>
-      </c>
-      <c r="H11" s="27" t="n">
-        <v>-5.75</v>
-      </c>
-      <c r="I11" s="27" t="n">
-        <v>-2.78</v>
-      </c>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="H11" s="25" t="n"/>
+      <c r="I11" s="25" t="n"/>
     </row>
     <row r="12" ht="18" customHeight="1">
       <c r="A12" s="26" t="inlineStr">
         <is>
-          <t>카카오게임즈</t>
+          <t>에이팩트</t>
         </is>
       </c>
       <c r="B12" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C12" s="25" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D12" s="25" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E12" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F12" s="25" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G12" s="25" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="H12" s="28" t="n">
-        <v>13.96</v>
+        <v>-11.96</v>
       </c>
       <c r="I12" s="28" t="n">
-        <v>9.970000000000001</v>
+        <v>-17.49</v>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
       <c r="A13" s="26" t="inlineStr">
         <is>
-          <t>현대차</t>
+          <t>바이오</t>
         </is>
       </c>
       <c r="B13" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C13" s="25" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D13" s="25" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E13" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F13" s="25" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G13" s="25" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
-        </is>
-      </c>
-      <c r="H13" s="27" t="n">
-        <v>-5.22</v>
-      </c>
-      <c r="I13" s="27" t="n">
-        <v>-10.2</v>
-      </c>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="H13" s="25" t="n"/>
+      <c r="I13" s="25" t="n"/>
     </row>
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="26" t="inlineStr">
         <is>
-          <t>로봇</t>
+          <t>KT</t>
         </is>
       </c>
       <c r="B14" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C14" s="25" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D14" s="25" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E14" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F14" s="25" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G14" s="25" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
-        </is>
-      </c>
-      <c r="H14" s="25" t="n"/>
-      <c r="I14" s="25" t="n"/>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="H14" s="27" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="I14" s="28" t="n">
+        <v>-7.42</v>
+      </c>
     </row>
     <row r="15" ht="18" customHeight="1">
       <c r="A15" s="26" t="inlineStr">
         <is>
-          <t>에이팩트</t>
+          <t>대한항공</t>
         </is>
       </c>
       <c r="B15" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C15" s="25" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D15" s="25" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E15" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F15" s="25" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G15" s="25" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
-        </is>
-      </c>
-      <c r="H15" s="27" t="n">
-        <v>-0.72</v>
-      </c>
-      <c r="I15" s="27" t="n">
-        <v>-9.140000000000001</v>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="H15" s="28" t="n">
+        <v>-4.25</v>
+      </c>
+      <c r="I15" s="28" t="n">
+        <v>-11.6</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
       <c r="A16" s="26" t="inlineStr">
         <is>
-          <t>LG전자</t>
+          <t>비투엔</t>
         </is>
       </c>
       <c r="B16" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C16" s="25" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D16" s="25" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E16" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F16" s="25" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G16" s="25" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="H16" s="28" t="n">
-        <v>7.57</v>
-      </c>
-      <c r="I16" s="27" t="n">
-        <v>-6.57</v>
+        <v>-5.03</v>
+      </c>
+      <c r="I16" s="28" t="n">
+        <v>-7.93</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
       <c r="A17" s="26" t="inlineStr">
         <is>
-          <t>철강</t>
+          <t>삼성바이오로직스</t>
         </is>
       </c>
       <c r="B17" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C17" s="25" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D17" s="25" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E17" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F17" s="25" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G17" s="25" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
-        </is>
-      </c>
-      <c r="H17" s="25" t="n"/>
-      <c r="I17" s="25" t="n"/>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="H17" s="28" t="n">
+        <v>-1.7</v>
+      </c>
+      <c r="I17" s="28" t="n">
+        <v>-4.5</v>
+      </c>
     </row>
     <row r="18" ht="18" customHeight="1">
       <c r="A18" s="26" t="inlineStr">
         <is>
-          <t>태양광</t>
+          <t>전기차</t>
         </is>
       </c>
       <c r="B18" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C18" s="25" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D18" s="25" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E18" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F18" s="25" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G18" s="25" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="H18" s="25" t="n"/>
@@ -3661,7 +3649,7 @@
     <row r="19" ht="18" customHeight="1">
       <c r="A19" s="26" t="inlineStr">
         <is>
-          <t>게임</t>
+          <t>프로브잇</t>
         </is>
       </c>
       <c r="B19" s="25" t="n">
@@ -3678,301 +3666,301 @@
       </c>
       <c r="F19" s="25" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G19" s="25" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
-        </is>
-      </c>
-      <c r="H19" s="25" t="n"/>
-      <c r="I19" s="25" t="n"/>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="H19" s="27" t="n">
+        <v>177.78</v>
+      </c>
+      <c r="I19" s="28" t="n">
+        <v>-91.83</v>
+      </c>
     </row>
     <row r="20" ht="18" customHeight="1">
       <c r="A20" s="26" t="inlineStr">
         <is>
-          <t>두산로보틱스</t>
+          <t>스피어</t>
         </is>
       </c>
       <c r="B20" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C20" s="25" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D20" s="25" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E20" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F20" s="25" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G20" s="25" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
-        </is>
-      </c>
-      <c r="H20" s="27" t="n">
-        <v>-1.38</v>
-      </c>
-      <c r="I20" s="27" t="n">
-        <v>-9.869999999999999</v>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="H20" s="28" t="n">
+        <v>-10.29</v>
+      </c>
+      <c r="I20" s="28" t="n">
+        <v>-39.6</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
       <c r="A21" s="26" t="inlineStr">
         <is>
-          <t>비투엔</t>
+          <t>철강</t>
         </is>
       </c>
       <c r="B21" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C21" s="25" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D21" s="25" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E21" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F21" s="25" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G21" s="25" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
-        </is>
-      </c>
-      <c r="H21" s="28" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="I21" s="27" t="n">
-        <v>-2.05</v>
-      </c>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="H21" s="25" t="n"/>
+      <c r="I21" s="25" t="n"/>
     </row>
     <row r="22" ht="18" customHeight="1">
       <c r="A22" s="26" t="inlineStr">
         <is>
-          <t>삼성생명</t>
+          <t>현대차</t>
         </is>
       </c>
       <c r="B22" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C22" s="25" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D22" s="25" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E22" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F22" s="25" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G22" s="25" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
-        </is>
-      </c>
-      <c r="H22" s="27" t="n">
-        <v>-9.359999999999999</v>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="H22" s="28" t="n">
+        <v>-12.05</v>
       </c>
       <c r="I22" s="28" t="n">
-        <v>6.5</v>
+        <v>-20.16</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
       <c r="A23" s="26" t="inlineStr">
         <is>
-          <t>유안타증권</t>
+          <t>HJ중공업</t>
         </is>
       </c>
       <c r="B23" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C23" s="25" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D23" s="25" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E23" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F23" s="25" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G23" s="25" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
-        </is>
-      </c>
-      <c r="H23" s="27" t="n">
-        <v>-2.95</v>
-      </c>
-      <c r="I23" s="27" t="n">
-        <v>-8.09</v>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="H23" s="28" t="n">
+        <v>-8.41</v>
+      </c>
+      <c r="I23" s="28" t="n">
+        <v>-14.6</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
       <c r="A24" s="26" t="inlineStr">
         <is>
-          <t>카카오</t>
+          <t>노블엠앤비</t>
         </is>
       </c>
       <c r="B24" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C24" s="25" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D24" s="25" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E24" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F24" s="25" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G24" s="25" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="H24" s="27" t="n">
-        <v>-2.52</v>
-      </c>
-      <c r="I24" s="27" t="n">
-        <v>-9.69</v>
+        <v>4.17</v>
+      </c>
+      <c r="I24" s="28" t="n">
+        <v>-93.92</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
       <c r="A25" s="26" t="inlineStr">
         <is>
-          <t>프로브잇</t>
+          <t>미래에셋증권</t>
         </is>
       </c>
       <c r="B25" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C25" s="25" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D25" s="25" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E25" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F25" s="25" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G25" s="25" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
-        </is>
-      </c>
-      <c r="H25" s="27" t="n">
-        <v>-97.06</v>
-      </c>
-      <c r="I25" s="27" t="n">
-        <v>-97.06</v>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="H25" s="28" t="n">
+        <v>-8.57</v>
+      </c>
+      <c r="I25" s="28" t="n">
+        <v>-17.84</v>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
       <c r="A26" s="26" t="inlineStr">
         <is>
-          <t>한솔테크닉스</t>
+          <t>센서뷰</t>
         </is>
       </c>
       <c r="B26" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C26" s="25" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D26" s="25" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E26" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F26" s="25" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G26" s="25" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="H26" s="28" t="n">
-        <v>18.2</v>
+        <v>-2.79</v>
       </c>
       <c r="I26" s="28" t="n">
-        <v>20.22</v>
+        <v>-15.56</v>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
       <c r="A27" s="26" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>셀트리온</t>
         </is>
       </c>
       <c r="B27" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C27" s="25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D27" s="25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E27" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F27" s="25" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G27" s="25" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
-        </is>
-      </c>
-      <c r="H27" s="27" t="n">
-        <v>-5.73</v>
-      </c>
-      <c r="I27" s="27" t="n">
-        <v>-29.25</v>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="H27" s="28" t="n">
+        <v>-4.75</v>
+      </c>
+      <c r="I27" s="28" t="n">
+        <v>-8.02</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
       <c r="A28" s="26" t="inlineStr">
         <is>
-          <t>HJ중공업</t>
+          <t>팬오션</t>
         </is>
       </c>
       <c r="B28" s="25" t="n">
@@ -3989,25 +3977,25 @@
       </c>
       <c r="F28" s="25" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G28" s="25" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
-        </is>
-      </c>
-      <c r="H28" s="27" t="n">
-        <v>-4.04</v>
-      </c>
-      <c r="I28" s="27" t="n">
-        <v>-8.15</v>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="H28" s="28" t="n">
+        <v>-4.98</v>
+      </c>
+      <c r="I28" s="28" t="n">
+        <v>-12.55</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
       <c r="A29" s="26" t="inlineStr">
         <is>
-          <t>노블엠앤비</t>
+          <t>한미반도체</t>
         </is>
       </c>
       <c r="B29" s="25" t="n">
@@ -4024,231 +4012,231 @@
       </c>
       <c r="F29" s="25" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G29" s="25" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
-        </is>
-      </c>
-      <c r="H29" s="27" t="n">
-        <v>-94.16</v>
-      </c>
-      <c r="I29" s="27" t="n">
-        <v>-94.16</v>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="H29" s="28" t="n">
+        <v>-14.43</v>
+      </c>
+      <c r="I29" s="28" t="n">
+        <v>-21.46</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
       <c r="A30" s="26" t="inlineStr">
         <is>
-          <t>다스코</t>
+          <t>AI반도체</t>
         </is>
       </c>
       <c r="B30" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C30" s="25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D30" s="25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E30" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F30" s="25" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G30" s="25" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
-        </is>
-      </c>
-      <c r="H30" s="27" t="n">
-        <v>-15.71</v>
-      </c>
-      <c r="I30" s="28" t="n">
-        <v>5.22</v>
-      </c>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="H30" s="25" t="n"/>
+      <c r="I30" s="25" t="n"/>
     </row>
     <row r="31" ht="18" customHeight="1">
       <c r="A31" s="26" t="inlineStr">
         <is>
-          <t>대원전선</t>
+          <t>KBI메탈</t>
         </is>
       </c>
       <c r="B31" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C31" s="25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D31" s="25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E31" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F31" s="25" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G31" s="25" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
-        </is>
-      </c>
-      <c r="H31" s="27" t="n">
-        <v>-6.67</v>
-      </c>
-      <c r="I31" s="27" t="n">
-        <v>-3.09</v>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="H31" s="28" t="n">
+        <v>-0.57</v>
+      </c>
+      <c r="I31" s="28" t="n">
+        <v>-7.47</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
       <c r="A32" s="26" t="inlineStr">
         <is>
-          <t>삼화네트웍스</t>
+          <t>LB세미콘</t>
         </is>
       </c>
       <c r="B32" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C32" s="25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D32" s="25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E32" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F32" s="25" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G32" s="25" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="H32" s="28" t="n">
-        <v>5.24</v>
+        <v>-12.95</v>
       </c>
       <c r="I32" s="28" t="n">
-        <v>7.86</v>
+        <v>-9.859999999999999</v>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
       <c r="A33" s="26" t="inlineStr">
         <is>
-          <t>센서뷰</t>
+          <t>SK텔레콤</t>
         </is>
       </c>
       <c r="B33" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C33" s="25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D33" s="25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E33" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F33" s="25" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G33" s="25" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
-        </is>
-      </c>
-      <c r="H33" s="27" t="n">
-        <v>-7.33</v>
-      </c>
-      <c r="I33" s="27" t="n">
-        <v>-13.48</v>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="H33" s="28" t="n">
+        <v>-4.56</v>
+      </c>
+      <c r="I33" s="28" t="n">
+        <v>-10.19</v>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
       <c r="A34" s="26" t="inlineStr">
         <is>
-          <t>스피어</t>
+          <t>경남제약</t>
         </is>
       </c>
       <c r="B34" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C34" s="25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D34" s="25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E34" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F34" s="25" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G34" s="25" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="H34" s="27" t="n">
-        <v>-12.28</v>
+        <v>29.75</v>
       </c>
       <c r="I34" s="27" t="n">
-        <v>-37.07</v>
+        <v>18.19</v>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
       <c r="A35" s="26" t="inlineStr">
         <is>
-          <t>원전</t>
+          <t>넥써쓰</t>
         </is>
       </c>
       <c r="B35" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C35" s="25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D35" s="25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E35" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F35" s="25" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G35" s="25" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
-        </is>
-      </c>
-      <c r="H35" s="25" t="n"/>
-      <c r="I35" s="25" t="n"/>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="H35" s="28" t="n">
+        <v>-11.22</v>
+      </c>
+      <c r="I35" s="28" t="n">
+        <v>-20.36</v>
+      </c>
     </row>
     <row r="36" ht="18" customHeight="1">
       <c r="A36" s="26" t="inlineStr">
         <is>
-          <t>JW신약</t>
+          <t>두산로보틱스</t>
         </is>
       </c>
       <c r="B36" s="25" t="n">
@@ -4265,25 +4253,25 @@
       </c>
       <c r="F36" s="25" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G36" s="25" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="H36" s="28" t="n">
-        <v>16.92</v>
+        <v>-11.55</v>
       </c>
       <c r="I36" s="28" t="n">
-        <v>53.8</v>
+        <v>-18.53</v>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
       <c r="A37" s="26" t="inlineStr">
         <is>
-          <t>TS트릴리온</t>
+          <t>바이온</t>
         </is>
       </c>
       <c r="B37" s="25" t="n">
@@ -4300,25 +4288,25 @@
       </c>
       <c r="F37" s="25" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G37" s="25" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
-        </is>
-      </c>
-      <c r="H37" s="28" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="I37" s="27" t="n">
-        <v>-15.51</v>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="H37" s="27" t="n">
+        <v>68.42</v>
+      </c>
+      <c r="I37" s="28" t="n">
+        <v>-94.7</v>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
       <c r="A38" s="26" t="inlineStr">
         <is>
-          <t>강동씨앤엘</t>
+          <t>방산</t>
         </is>
       </c>
       <c r="B38" s="25" t="n">
@@ -4335,25 +4323,21 @@
       </c>
       <c r="F38" s="25" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G38" s="25" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
-        </is>
-      </c>
-      <c r="H38" s="27" t="n">
-        <v>-12.22</v>
-      </c>
-      <c r="I38" s="28" t="n">
-        <v>79.66</v>
-      </c>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="H38" s="25" t="n"/>
+      <c r="I38" s="25" t="n"/>
     </row>
     <row r="39" ht="18" customHeight="1">
       <c r="A39" s="26" t="inlineStr">
         <is>
-          <t>남화토건</t>
+          <t>성도이엔지</t>
         </is>
       </c>
       <c r="B39" s="25" t="n">
@@ -4370,25 +4354,25 @@
       </c>
       <c r="F39" s="25" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G39" s="25" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
-        </is>
-      </c>
-      <c r="H39" s="27" t="n">
-        <v>-10.33</v>
-      </c>
-      <c r="I39" s="28" t="n">
-        <v>31.77</v>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="H39" s="28" t="n">
+        <v>-7.69</v>
+      </c>
+      <c r="I39" s="27" t="n">
+        <v>2.97</v>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
       <c r="A40" s="26" t="inlineStr">
         <is>
-          <t>메리츠제2호스팩</t>
+          <t>소룩스</t>
         </is>
       </c>
       <c r="B40" s="25" t="n">
@@ -4405,25 +4389,25 @@
       </c>
       <c r="F40" s="25" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G40" s="25" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="H40" s="27" t="n">
-        <v>-0.8100000000000001</v>
+        <v>14.42</v>
       </c>
       <c r="I40" s="27" t="n">
-        <v>-0.8100000000000001</v>
+        <v>1.63</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
       <c r="A41" s="26" t="inlineStr">
         <is>
-          <t>보해양조</t>
+          <t>시너지이노베이션</t>
         </is>
       </c>
       <c r="B41" s="25" t="n">
@@ -4440,25 +4424,25 @@
       </c>
       <c r="F41" s="25" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G41" s="25" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="H41" s="28" t="n">
-        <v>9.859999999999999</v>
+        <v>-8.279999999999999</v>
       </c>
       <c r="I41" s="28" t="n">
-        <v>64.90000000000001</v>
+        <v>-14.05</v>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
       <c r="A42" s="26" t="inlineStr">
         <is>
-          <t>삼익제약</t>
+          <t>우성머티리얼스</t>
         </is>
       </c>
       <c r="B42" s="25" t="n">
@@ -4475,25 +4459,25 @@
       </c>
       <c r="F42" s="25" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G42" s="25" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="H42" s="28" t="n">
-        <v>6.54</v>
+        <v>-1.12</v>
       </c>
       <c r="I42" s="28" t="n">
-        <v>16.36</v>
+        <v>-16.13</v>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1">
       <c r="A43" s="26" t="inlineStr">
         <is>
-          <t>삼화전자</t>
+          <t>진흥기업</t>
         </is>
       </c>
       <c r="B43" s="25" t="n">
@@ -4510,25 +4494,25 @@
       </c>
       <c r="F43" s="25" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G43" s="25" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
-        </is>
-      </c>
-      <c r="H43" s="27" t="n">
-        <v>-14.82</v>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="H43" s="28" t="n">
+        <v>-7.5</v>
       </c>
       <c r="I43" s="28" t="n">
-        <v>13.91</v>
+        <v>-16.77</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
       <c r="A44" s="26" t="inlineStr">
         <is>
-          <t>성문전자</t>
+          <t>키스트론</t>
         </is>
       </c>
       <c r="B44" s="25" t="n">
@@ -4545,25 +4529,25 @@
       </c>
       <c r="F44" s="25" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G44" s="25" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="H44" s="28" t="n">
-        <v>9</v>
-      </c>
-      <c r="I44" s="28" t="n">
-        <v>51.42</v>
+        <v>-10.97</v>
+      </c>
+      <c r="I44" s="27" t="n">
+        <v>18.91</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
       <c r="A45" s="26" t="inlineStr">
         <is>
-          <t>예스티</t>
+          <t>태양광</t>
         </is>
       </c>
       <c r="B45" s="25" t="n">
@@ -4580,264 +4564,252 @@
       </c>
       <c r="F45" s="25" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G45" s="25" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
-        </is>
-      </c>
-      <c r="H45" s="28" t="n">
-        <v>10.63</v>
-      </c>
-      <c r="I45" s="28" t="n">
-        <v>20.88</v>
-      </c>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="H45" s="25" t="n"/>
+      <c r="I45" s="25" t="n"/>
     </row>
     <row r="46" ht="18" customHeight="1">
       <c r="A46" s="26" t="inlineStr">
         <is>
-          <t>위더스제약</t>
+          <t>NH투자증권</t>
         </is>
       </c>
       <c r="B46" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C46" s="25" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D46" s="25" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E46" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F46" s="25" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G46" s="25" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
-        </is>
-      </c>
-      <c r="H46" s="27" t="n">
-        <v>-3.95</v>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="H46" s="28" t="n">
+        <v>-6.66</v>
       </c>
       <c r="I46" s="28" t="n">
-        <v>4.03</v>
+        <v>-12.48</v>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
       <c r="A47" s="26" t="inlineStr">
         <is>
-          <t>율촌</t>
+          <t>삼성전기</t>
         </is>
       </c>
       <c r="B47" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C47" s="25" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D47" s="25" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E47" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F47" s="25" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G47" s="25" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="H47" s="28" t="n">
-        <v>9.029999999999999</v>
+        <v>-10.68</v>
       </c>
       <c r="I47" s="28" t="n">
-        <v>38.23</v>
+        <v>-2.83</v>
       </c>
     </row>
     <row r="48" ht="18" customHeight="1">
       <c r="A48" s="26" t="inlineStr">
         <is>
-          <t>제이앤티씨</t>
+          <t>스테이블코인</t>
         </is>
       </c>
       <c r="B48" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C48" s="25" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D48" s="25" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E48" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F48" s="25" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G48" s="25" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
-        </is>
-      </c>
-      <c r="H48" s="28" t="n">
-        <v>8.81</v>
-      </c>
-      <c r="I48" s="28" t="n">
-        <v>33.63</v>
-      </c>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="H48" s="25" t="n"/>
+      <c r="I48" s="25" t="n"/>
     </row>
     <row r="49" ht="18" customHeight="1">
       <c r="A49" s="26" t="inlineStr">
         <is>
-          <t>티웨이홀딩스</t>
+          <t>에이테크솔루션</t>
         </is>
       </c>
       <c r="B49" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C49" s="25" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D49" s="25" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E49" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F49" s="25" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G49" s="25" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
-        </is>
-      </c>
-      <c r="H49" s="27" t="n">
-        <v>-7.91</v>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="H49" s="28" t="n">
+        <v>-4.39</v>
       </c>
       <c r="I49" s="27" t="n">
-        <v>-9.94</v>
+        <v>15.25</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
       <c r="A50" s="26" t="inlineStr">
         <is>
-          <t>하이스틸</t>
+          <t>원전</t>
         </is>
       </c>
       <c r="B50" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C50" s="25" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D50" s="25" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E50" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F50" s="25" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G50" s="25" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
-        </is>
-      </c>
-      <c r="H50" s="28" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="I50" s="28" t="n">
-        <v>2.02</v>
-      </c>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="H50" s="25" t="n"/>
+      <c r="I50" s="25" t="n"/>
     </row>
     <row r="51" ht="18" customHeight="1">
       <c r="A51" s="26" t="inlineStr">
         <is>
-          <t>한울반도체</t>
+          <t>카카오</t>
         </is>
       </c>
       <c r="B51" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C51" s="25" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D51" s="25" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E51" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F51" s="25" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G51" s="25" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="H51" s="28" t="n">
-        <v>29.91</v>
+        <v>-6.93</v>
       </c>
       <c r="I51" s="28" t="n">
-        <v>110.65</v>
+        <v>-15.33</v>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1">
       <c r="A52" s="26" t="inlineStr">
         <is>
-          <t>현대약품</t>
+          <t>케이뱅크</t>
         </is>
       </c>
       <c r="B52" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C52" s="25" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D52" s="25" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E52" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F52" s="25" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G52" s="25" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="H52" s="28" t="n">
-        <v>0.86</v>
+        <v>-3.66</v>
       </c>
       <c r="I52" s="28" t="n">
-        <v>10.48</v>
+        <v>-12.06</v>
       </c>
     </row>
   </sheetData>
@@ -4921,19 +4893,19 @@
         <v>1</v>
       </c>
       <c r="C3" s="36" t="n">
-        <v>62</v>
+        <v>114</v>
       </c>
       <c r="D3" s="36" t="n">
-        <v>62</v>
+        <v>114</v>
       </c>
       <c r="E3" s="36" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="F3" s="37" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G3" s="37" t="inlineStr">
@@ -4952,19 +4924,19 @@
         <v>1</v>
       </c>
       <c r="C4" s="36" t="n">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="D4" s="36" t="n">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="E4" s="36" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="F4" s="37" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G4" s="37" t="inlineStr">
@@ -4976,26 +4948,26 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="35" t="inlineStr">
         <is>
-          <t>원전</t>
+          <t>AI반도체</t>
         </is>
       </c>
       <c r="B5" s="36" t="n">
         <v>1</v>
       </c>
       <c r="C5" s="36" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D5" s="36" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E5" s="36" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="F5" s="37" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G5" s="37" t="inlineStr">
@@ -5007,26 +4979,26 @@
     <row r="6" ht="18" customHeight="1">
       <c r="A6" s="35" t="inlineStr">
         <is>
-          <t>로봇</t>
+          <t>전기차</t>
         </is>
       </c>
       <c r="B6" s="36" t="n">
         <v>1</v>
       </c>
       <c r="C6" s="36" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D6" s="36" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E6" s="36" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="F6" s="37" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G6" s="37" t="inlineStr">
@@ -5038,26 +5010,26 @@
     <row r="7" ht="18" customHeight="1">
       <c r="A7" s="35" t="inlineStr">
         <is>
-          <t>태양광</t>
+          <t>방산</t>
         </is>
       </c>
       <c r="B7" s="36" t="n">
         <v>1</v>
       </c>
       <c r="C7" s="36" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D7" s="36" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E7" s="36" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="F7" s="37" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G7" s="37" t="inlineStr">
@@ -5069,26 +5041,26 @@
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="35" t="inlineStr">
         <is>
-          <t>게임</t>
+          <t>원전</t>
         </is>
       </c>
       <c r="B8" s="36" t="n">
         <v>1</v>
       </c>
       <c r="C8" s="36" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D8" s="36" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E8" s="36" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="F8" s="37" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G8" s="37" t="inlineStr">
@@ -5100,26 +5072,26 @@
     <row r="9" ht="18" customHeight="1">
       <c r="A9" s="35" t="inlineStr">
         <is>
-          <t>철강</t>
+          <t>로봇</t>
         </is>
       </c>
       <c r="B9" s="36" t="n">
         <v>1</v>
       </c>
       <c r="C9" s="36" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D9" s="36" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E9" s="36" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="F9" s="37" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G9" s="37" t="inlineStr">
@@ -5131,26 +5103,26 @@
     <row r="10" ht="18" customHeight="1">
       <c r="A10" s="35" t="inlineStr">
         <is>
-          <t>제약</t>
+          <t>태양광</t>
         </is>
       </c>
       <c r="B10" s="36" t="n">
         <v>1</v>
       </c>
       <c r="C10" s="36" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D10" s="36" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E10" s="36" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="F10" s="37" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G10" s="37" t="inlineStr">
@@ -5162,92 +5134,100 @@
     <row r="11" ht="18" customHeight="1">
       <c r="A11" s="35" t="inlineStr">
         <is>
+          <t>철강</t>
+        </is>
+      </c>
+      <c r="B11" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" s="36" t="n">
+        <v>5</v>
+      </c>
+      <c r="D11" s="36" t="n">
+        <v>5</v>
+      </c>
+      <c r="E11" s="36" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="F11" s="37" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="G11" s="37" t="inlineStr">
+        <is>
+          <t>⚡ 관심</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="18" customHeight="1">
+      <c r="A12" s="35" t="inlineStr">
+        <is>
+          <t>제약</t>
+        </is>
+      </c>
+      <c r="B12" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" s="36" t="n">
+        <v>9</v>
+      </c>
+      <c r="D12" s="36" t="n">
+        <v>9</v>
+      </c>
+      <c r="E12" s="36" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="F12" s="37" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="G12" s="37" t="inlineStr">
+        <is>
+          <t>⚡ 관심</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="18" customHeight="1">
+      <c r="A13" s="35" t="inlineStr">
+        <is>
           <t>인공지능</t>
         </is>
       </c>
-      <c r="B11" s="36" t="n">
-        <v>1</v>
-      </c>
-      <c r="C11" s="36" t="n">
-        <v>13</v>
-      </c>
-      <c r="D11" s="36" t="n">
-        <v>13</v>
-      </c>
-      <c r="E11" s="36" t="inlineStr">
-        <is>
-          <t>2026-06-23</t>
-        </is>
-      </c>
-      <c r="F11" s="37" t="inlineStr">
-        <is>
-          <t>2026-06-23</t>
-        </is>
-      </c>
-      <c r="G11" s="37" t="inlineStr">
+      <c r="B13" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" s="36" t="n">
+        <v>15</v>
+      </c>
+      <c r="D13" s="36" t="n">
+        <v>15</v>
+      </c>
+      <c r="E13" s="36" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="F13" s="37" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="G13" s="37" t="inlineStr">
         <is>
           <t>⚡ 관심</t>
         </is>
       </c>
-    </row>
-    <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="26" t="inlineStr">
-        <is>
-          <t>이차전지</t>
-        </is>
-      </c>
-      <c r="B12" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="C12" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" s="25" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F12" s="29" t="inlineStr">
-        <is>
-          <t>감지 없음</t>
-        </is>
-      </c>
-      <c r="G12" s="29" t="inlineStr"/>
-    </row>
-    <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="26" t="inlineStr">
-        <is>
-          <t>AI반도체</t>
-        </is>
-      </c>
-      <c r="B13" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="C13" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" s="25" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F13" s="29" t="inlineStr">
-        <is>
-          <t>감지 없음</t>
-        </is>
-      </c>
-      <c r="G13" s="29" t="inlineStr"/>
     </row>
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="26" t="inlineStr">
         <is>
-          <t>전기차</t>
+          <t>이차전지</t>
         </is>
       </c>
       <c r="B14" s="25" t="n">
@@ -5274,7 +5254,7 @@
     <row r="15" ht="18" customHeight="1">
       <c r="A15" s="26" t="inlineStr">
         <is>
-          <t>방산</t>
+          <t>수소</t>
         </is>
       </c>
       <c r="B15" s="25" t="n">
@@ -5301,7 +5281,7 @@
     <row r="16" ht="18" customHeight="1">
       <c r="A16" s="26" t="inlineStr">
         <is>
-          <t>수소</t>
+          <t>게임</t>
         </is>
       </c>
       <c r="B16" s="25" t="n">

--- a/trend/stock_trend_history.xlsx
+++ b/trend/stock_trend_history.xlsx
@@ -57,13 +57,13 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="002563EB"/>
+      <color rgb="00E53935"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="00E53935"/>
+      <color rgb="002563EB"/>
       <sz val="10"/>
     </font>
     <font>
@@ -261,11 +261,11 @@
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -273,14 +273,14 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -694,7 +694,7 @@
     <row r="1" ht="36" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>📊 주식 트렌드 조기 감지 대시보드   |   최종 업데이트: 2026-06-24 06:54</t>
+          <t>📊 주식 트렌드 조기 감지 대시보드   |   최종 업데이트: 2026-06-25 06:54</t>
         </is>
       </c>
     </row>
@@ -787,21 +787,21 @@
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="11" t="inlineStr">
         <is>
-          <t>⚡ 최신(2026-06-24) 상위: 반도체  점수 114.0점</t>
+          <t>⚡ 최신(2026-06-25) 상위: 반도체  점수 100.0점</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1">
       <c r="A11" s="12" t="inlineStr">
         <is>
-          <t>⚡ 최신(2026-06-24) 상위: SK  점수 48.0점</t>
+          <t>⚡ 최신(2026-06-25) 상위: SK하이닉스  점수 37.0점</t>
         </is>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1">
       <c r="A12" s="11" t="inlineStr">
         <is>
-          <t>⚡ 최신(2026-06-24) 상위: 삼성전자  점수 27.0점</t>
+          <t>⚡ 최신(2026-06-25) 상위: 삼성전자  점수 29.0점</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B14" s="15" t="n">
@@ -928,10 +928,10 @@
         </is>
       </c>
       <c r="D14" s="15" t="n">
-        <v>114</v>
+        <v>100</v>
       </c>
       <c r="E14" s="15" t="n">
-        <v>114</v>
+        <v>100</v>
       </c>
       <c r="F14" s="15" t="n">
         <v>0</v>
@@ -947,7 +947,7 @@
       </c>
       <c r="J14" s="17" t="inlineStr">
         <is>
-          <t>네이버뉴스 헤드라인 언급 / 네이버뉴스 헤드라인 언급 / 매일경제 헤드라인 언급 / 네이버뉴스 헤드라인 언급 / 네이버뉴스 헤드라인 언급</t>
+          <t>매일경제 헤드라인 언급 / 네이버뉴스 기사 언급 / 매일경제 헤드라인 언급 / 네이버뉴스 기사 언급 / 매일경제 헤드라인 언급</t>
         </is>
       </c>
       <c r="K14" s="17" t="inlineStr">
@@ -959,7 +959,7 @@
     <row r="15" ht="18" customHeight="1">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B15" s="15" t="n">
@@ -967,14 +967,14 @@
       </c>
       <c r="C15" s="16" t="inlineStr">
         <is>
-          <t>SK</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="D15" s="15" t="n">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="E15" s="15" t="n">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="F15" s="15" t="n">
         <v>0</v>
@@ -983,26 +983,26 @@
         <v>0</v>
       </c>
       <c r="H15" s="18" t="n">
-        <v>-3.42</v>
-      </c>
-      <c r="I15" s="19" t="n">
-        <v>4.75</v>
+        <v>0.98</v>
+      </c>
+      <c r="I15" s="18" t="n">
+        <v>2.34</v>
       </c>
       <c r="J15" s="17" t="inlineStr">
         <is>
-          <t>한국경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 기사 언급 / 네이버뉴스 기사 언급 / 매일경제 헤드라인 언급</t>
+          <t>중요공시 1건 / 매일경제 기사 언급 / 매일경제 기사 언급 / 네이버뉴스 헤드라인 언급 / 네이버뉴스 기사 언급</t>
         </is>
       </c>
       <c r="K15" s="17" t="inlineStr">
         <is>
-          <t>네이버</t>
+          <t>네이버, 공시</t>
         </is>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
       <c r="A16" s="15" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B16" s="15" t="n">
@@ -1014,10 +1014,10 @@
         </is>
       </c>
       <c r="D16" s="15" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E16" s="15" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F16" s="15" t="n">
         <v>0</v>
@@ -1026,14 +1026,14 @@
         <v>0</v>
       </c>
       <c r="H16" s="18" t="n">
-        <v>-12.31</v>
-      </c>
-      <c r="I16" s="18" t="n">
-        <v>-9.619999999999999</v>
+        <v>9.84</v>
+      </c>
+      <c r="I16" s="19" t="n">
+        <v>-1.73</v>
       </c>
       <c r="J16" s="17" t="inlineStr">
         <is>
-          <t>한국경제 헤드라인 언급 / 매일경제 기사 언급 / 네이버뉴스 기사 언급 / 매일경제 헤드라인 언급 / 매일경제 기사 언급</t>
+          <t>매일경제 기사 언급 / 매일경제 기사 언급 / 매일경제 기사 언급 / 네이버뉴스 헤드라인 언급 / 네이버뉴스 기사 언급</t>
         </is>
       </c>
       <c r="K16" s="17" t="inlineStr">
@@ -1045,7 +1045,7 @@
     <row r="17" ht="18" customHeight="1">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B17" s="15" t="n">
@@ -1053,14 +1053,14 @@
       </c>
       <c r="C17" s="16" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>인공지능</t>
         </is>
       </c>
       <c r="D17" s="15" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E17" s="15" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F17" s="15" t="n">
         <v>0</v>
@@ -1068,15 +1068,15 @@
       <c r="G17" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="H17" s="18" t="n">
-        <v>-12.47</v>
-      </c>
-      <c r="I17" s="19" t="n">
-        <v>7.26</v>
+      <c r="H17" s="15" t="n">
+        <v/>
+      </c>
+      <c r="I17" s="15" t="n">
+        <v/>
       </c>
       <c r="J17" s="17" t="inlineStr">
         <is>
-          <t>한국경제 헤드라인 언급 / 매일경제 기사 언급 / 네이버뉴스 기사 언급 / 매일경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
+          <t>매일경제 기사 언급 / 네이버뉴스 기사 언급 / 매일경제 기사 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 기사 언급</t>
         </is>
       </c>
       <c r="K17" s="17" t="inlineStr">
@@ -1088,7 +1088,7 @@
     <row r="18" ht="18" customHeight="1">
       <c r="A18" s="15" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B18" s="15" t="n">
@@ -1096,14 +1096,14 @@
       </c>
       <c r="C18" s="16" t="inlineStr">
         <is>
-          <t>LG</t>
+          <t>바이오</t>
         </is>
       </c>
       <c r="D18" s="15" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E18" s="15" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="F18" s="15" t="n">
         <v>0</v>
@@ -1111,25 +1111,27 @@
       <c r="G18" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="H18" s="18" t="n">
-        <v>-10.28</v>
-      </c>
-      <c r="I18" s="18" t="n">
-        <v>-13.58</v>
+      <c r="H18" s="15" t="n">
+        <v/>
+      </c>
+      <c r="I18" s="15" t="n">
+        <v/>
       </c>
       <c r="J18" s="17" t="inlineStr">
         <is>
-          <t>매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K18" s="17" t="n">
-        <v/>
+          <t>한국경제 헤드라인 언급 / 네이버뉴스 헤드라인 언급 / 네이버뉴스 기사 언급 / 한국경제 헤드라인 언급 / 매일경제 기사 언급</t>
+        </is>
+      </c>
+      <c r="K18" s="17" t="inlineStr">
+        <is>
+          <t>네이버</t>
+        </is>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
       <c r="A19" s="15" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B19" s="15" t="n">
@@ -1137,7 +1139,7 @@
       </c>
       <c r="C19" s="16" t="inlineStr">
         <is>
-          <t>인공지능</t>
+          <t>LG</t>
         </is>
       </c>
       <c r="D19" s="15" t="n">
@@ -1152,27 +1154,25 @@
       <c r="G19" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="H19" s="15" t="n">
+      <c r="H19" s="18" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="I19" s="19" t="n">
+        <v>-11.82</v>
+      </c>
+      <c r="J19" s="17" t="inlineStr">
+        <is>
+          <t>매일경제 헤드라인 언급 / 한국경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 한국경제 헤드라인 언급 / 매일경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K19" s="17" t="n">
         <v/>
-      </c>
-      <c r="I19" s="15" t="n">
-        <v/>
-      </c>
-      <c r="J19" s="17" t="inlineStr">
-        <is>
-          <t>매일경제 기사 언급 / 네이버뉴스 기사 언급 / 매일경제 기사 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 기사 언급</t>
-        </is>
-      </c>
-      <c r="K19" s="17" t="inlineStr">
-        <is>
-          <t>네이버</t>
-        </is>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
       <c r="A20" s="15" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B20" s="15" t="n">
@@ -1184,10 +1184,10 @@
         </is>
       </c>
       <c r="D20" s="15" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E20" s="15" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F20" s="15" t="n">
         <v>0</v>
@@ -1203,17 +1203,19 @@
       </c>
       <c r="J20" s="17" t="inlineStr">
         <is>
-          <t>매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 기사 언급 / 한국경제 헤드라인 언급 / 매일경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K20" s="17" t="n">
-        <v/>
+          <t>매일경제 헤드라인 언급 / 한국경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 네이버뉴스 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K20" s="17" t="inlineStr">
+        <is>
+          <t>네이버</t>
+        </is>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
       <c r="A21" s="15" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B21" s="15" t="n">
@@ -1221,42 +1223,42 @@
       </c>
       <c r="C21" s="16" t="inlineStr">
         <is>
-          <t>제약</t>
+          <t>에이팩트</t>
         </is>
       </c>
       <c r="D21" s="15" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E21" s="15" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="F21" s="15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G21" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" s="15" t="n">
-        <v/>
-      </c>
-      <c r="I21" s="15" t="n">
-        <v/>
+        <v>3</v>
+      </c>
+      <c r="H21" s="19" t="n">
+        <v>-5.97</v>
+      </c>
+      <c r="I21" s="19" t="n">
+        <v>-26.41</v>
       </c>
       <c r="J21" s="17" t="inlineStr">
         <is>
-          <t>네이버뉴스 헤드라인 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 헤드라인 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 기사 언급</t>
+          <t>중요공시 4건 / 중요공시 3일 +100% / 중요공시 7일 +100%</t>
         </is>
       </c>
       <c r="K21" s="17" t="inlineStr">
         <is>
-          <t>네이버</t>
+          <t>공시</t>
         </is>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
       <c r="A22" s="15" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B22" s="15" t="n">
@@ -1264,14 +1266,14 @@
       </c>
       <c r="C22" s="16" t="inlineStr">
         <is>
-          <t>LG전자</t>
+          <t>제약</t>
         </is>
       </c>
       <c r="D22" s="15" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E22" s="15" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F22" s="15" t="n">
         <v>0</v>
@@ -1279,25 +1281,27 @@
       <c r="G22" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="H22" s="18" t="n">
-        <v>-11.21</v>
-      </c>
-      <c r="I22" s="18" t="n">
-        <v>-13.68</v>
+      <c r="H22" s="15" t="n">
+        <v/>
+      </c>
+      <c r="I22" s="15" t="n">
+        <v/>
       </c>
       <c r="J22" s="17" t="inlineStr">
         <is>
-          <t>매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K22" s="17" t="n">
-        <v/>
+          <t>네이버뉴스 기사 언급 / 네이버뉴스 헤드라인 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 기사 언급 / 매일경제 기사 언급</t>
+        </is>
+      </c>
+      <c r="K22" s="17" t="inlineStr">
+        <is>
+          <t>네이버</t>
+        </is>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B23" s="15" t="n">
@@ -1305,42 +1309,40 @@
       </c>
       <c r="C23" s="16" t="inlineStr">
         <is>
-          <t>에이팩트</t>
+          <t>현대차</t>
         </is>
       </c>
       <c r="D23" s="15" t="n">
         <v>8</v>
       </c>
       <c r="E23" s="15" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="F23" s="15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G23" s="15" t="n">
-        <v>3</v>
-      </c>
-      <c r="H23" s="18" t="n">
-        <v>-11.96</v>
-      </c>
-      <c r="I23" s="18" t="n">
-        <v>-17.49</v>
+        <v>0</v>
+      </c>
+      <c r="H23" s="19" t="n">
+        <v>-0.39</v>
+      </c>
+      <c r="I23" s="19" t="n">
+        <v>-17.64</v>
       </c>
       <c r="J23" s="17" t="inlineStr">
         <is>
-          <t>중요공시 4건 / 중요공시 3일 +100% / 중요공시 7일 +100%</t>
-        </is>
-      </c>
-      <c r="K23" s="17" t="inlineStr">
-        <is>
-          <t>공시</t>
-        </is>
+          <t>매일경제 헤드라인 언급 / 매일경제 기사 언급 / 매일경제 헤드라인 언급 / 매일경제 기사 언급 / 매일경제 기사 언급</t>
+        </is>
+      </c>
+      <c r="K23" s="17" t="n">
+        <v/>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B24" s="15" t="n">
@@ -1348,7 +1350,7 @@
       </c>
       <c r="C24" s="16" t="inlineStr">
         <is>
-          <t>바이오</t>
+          <t>에이프릴바이오</t>
         </is>
       </c>
       <c r="D24" s="15" t="n">
@@ -1363,27 +1365,27 @@
       <c r="G24" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="H24" s="15" t="n">
-        <v/>
-      </c>
-      <c r="I24" s="15" t="n">
-        <v/>
+      <c r="H24" s="18" t="n">
+        <v>15.57</v>
+      </c>
+      <c r="I24" s="19" t="n">
+        <v>-14.62</v>
       </c>
       <c r="J24" s="17" t="inlineStr">
         <is>
-          <t>네이버뉴스 기사 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 헤드라인 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 기사 언급</t>
+          <t>중요공시 1건 / 한국경제 헤드라인 언급 / 네이버뉴스 헤드라인 언급</t>
         </is>
       </c>
       <c r="K24" s="17" t="inlineStr">
         <is>
-          <t>네이버</t>
+          <t>네이버, 공시</t>
         </is>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
       <c r="A25" s="20" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B25" s="20" t="n">
@@ -1407,17 +1409,17 @@
         <v>0</v>
       </c>
       <c r="H25" s="22" t="n">
-        <v>177.78</v>
-      </c>
-      <c r="I25" s="23" t="n">
-        <v>-91.83</v>
-      </c>
-      <c r="J25" s="24" t="inlineStr">
-        <is>
-          <t>네이버 검색 당일 +255% / 중요공시 3건</t>
-        </is>
-      </c>
-      <c r="K25" s="24" t="inlineStr">
+        <v>-46</v>
+      </c>
+      <c r="I25" s="22" t="n">
+        <v>-95.59</v>
+      </c>
+      <c r="J25" s="23" t="inlineStr">
+        <is>
+          <t>네이버 검색 당일 +1416% / 중요공시 3건</t>
+        </is>
+      </c>
+      <c r="K25" s="23" t="inlineStr">
         <is>
           <t>네이버, 공시</t>
         </is>
@@ -1426,7 +1428,7 @@
     <row r="26" ht="18" customHeight="1">
       <c r="A26" s="20" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B26" s="20" t="n">
@@ -1434,40 +1436,42 @@
       </c>
       <c r="C26" s="21" t="inlineStr">
         <is>
-          <t>대한항공</t>
+          <t>비투엔</t>
         </is>
       </c>
       <c r="D26" s="20" t="n">
         <v>6</v>
       </c>
       <c r="E26" s="20" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F26" s="20" t="n">
         <v>0</v>
       </c>
       <c r="G26" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H26" s="23" t="n">
-        <v>-4.25</v>
-      </c>
-      <c r="I26" s="23" t="n">
-        <v>-11.6</v>
-      </c>
-      <c r="J26" s="24" t="inlineStr">
-        <is>
-          <t>한국경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 기사 언급</t>
-        </is>
-      </c>
-      <c r="K26" s="24" t="n">
-        <v/>
+        <v>3</v>
+      </c>
+      <c r="H26" s="24" t="n">
+        <v>15.89</v>
+      </c>
+      <c r="I26" s="24" t="n">
+        <v>5.85</v>
+      </c>
+      <c r="J26" s="23" t="inlineStr">
+        <is>
+          <t>중요공시 5건 / 중요공시 7일 +400%</t>
+        </is>
+      </c>
+      <c r="K26" s="23" t="inlineStr">
+        <is>
+          <t>공시</t>
+        </is>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
       <c r="A27" s="20" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B27" s="20" t="n">
@@ -1475,33 +1479,33 @@
       </c>
       <c r="C27" s="21" t="inlineStr">
         <is>
-          <t>비투엔</t>
+          <t>스피어</t>
         </is>
       </c>
       <c r="D27" s="20" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E27" s="20" t="n">
         <v>3</v>
       </c>
       <c r="F27" s="20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G27" s="20" t="n">
-        <v>3</v>
-      </c>
-      <c r="H27" s="23" t="n">
-        <v>-5.03</v>
-      </c>
-      <c r="I27" s="23" t="n">
-        <v>-7.93</v>
-      </c>
-      <c r="J27" s="24" t="inlineStr">
-        <is>
-          <t>중요공시 4건 / 중요공시 7일 +300%</t>
-        </is>
-      </c>
-      <c r="K27" s="24" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="H27" s="24" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="I27" s="22" t="n">
+        <v>-28.67</v>
+      </c>
+      <c r="J27" s="23" t="inlineStr">
+        <is>
+          <t>중요공시 4건 / 중요공시 3일 +100%</t>
+        </is>
+      </c>
+      <c r="K27" s="23" t="inlineStr">
         <is>
           <t>공시</t>
         </is>
@@ -1510,7 +1514,7 @@
     <row r="28" ht="18" customHeight="1">
       <c r="A28" s="20" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B28" s="20" t="n">
@@ -1518,33 +1522,33 @@
       </c>
       <c r="C28" s="21" t="inlineStr">
         <is>
-          <t>삼성바이오로직스</t>
+          <t>센서뷰</t>
         </is>
       </c>
       <c r="D28" s="20" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E28" s="20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F28" s="20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G28" s="20" t="n">
         <v>3</v>
       </c>
-      <c r="H28" s="23" t="n">
-        <v>-1.7</v>
-      </c>
-      <c r="I28" s="23" t="n">
-        <v>-4.5</v>
-      </c>
-      <c r="J28" s="24" t="inlineStr">
-        <is>
-          <t>중요공시 2건 / 중요공시 3일 +100% / 중요공시 7일 +100%</t>
-        </is>
-      </c>
-      <c r="K28" s="24" t="inlineStr">
+      <c r="H28" s="24" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="I28" s="22" t="n">
+        <v>-10.4</v>
+      </c>
+      <c r="J28" s="23" t="inlineStr">
+        <is>
+          <t>중요공시 2건 / 중요공시 7일 +100% / 매일경제 기사 언급</t>
+        </is>
+      </c>
+      <c r="K28" s="23" t="inlineStr">
         <is>
           <t>공시</t>
         </is>
@@ -1553,7 +1557,7 @@
     <row r="29" ht="18" customHeight="1">
       <c r="A29" s="20" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B29" s="20" t="n">
@@ -1561,14 +1565,14 @@
       </c>
       <c r="C29" s="21" t="inlineStr">
         <is>
-          <t>전기차</t>
+          <t>노블엠앤비</t>
         </is>
       </c>
       <c r="D29" s="20" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E29" s="20" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F29" s="20" t="n">
         <v>0</v>
@@ -1576,27 +1580,27 @@
       <c r="G29" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H29" s="20" t="n">
-        <v/>
-      </c>
-      <c r="I29" s="20" t="n">
-        <v/>
-      </c>
-      <c r="J29" s="24" t="inlineStr">
-        <is>
-          <t>네이버뉴스 헤드라인 언급 / 한국경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K29" s="24" t="inlineStr">
-        <is>
-          <t>네이버</t>
+      <c r="H29" s="22" t="n">
+        <v>-16</v>
+      </c>
+      <c r="I29" s="22" t="n">
+        <v>-94.89</v>
+      </c>
+      <c r="J29" s="23" t="inlineStr">
+        <is>
+          <t>네이버 검색 당일 +317% / 중요공시 2건</t>
+        </is>
+      </c>
+      <c r="K29" s="23" t="inlineStr">
+        <is>
+          <t>네이버, 공시</t>
         </is>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
       <c r="A30" s="20" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B30" s="20" t="n">
@@ -1604,14 +1608,14 @@
       </c>
       <c r="C30" s="21" t="inlineStr">
         <is>
-          <t>KT</t>
+          <t>바이온</t>
         </is>
       </c>
       <c r="D30" s="20" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E30" s="20" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F30" s="20" t="n">
         <v>0</v>
@@ -1620,24 +1624,26 @@
         <v>0</v>
       </c>
       <c r="H30" s="22" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="I30" s="23" t="n">
-        <v>-7.42</v>
-      </c>
-      <c r="J30" s="24" t="inlineStr">
-        <is>
-          <t>매일경제 기사 언급 / 한국경제 헤드라인 언급 / 매일경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K30" s="24" t="n">
-        <v/>
+        <v>-25</v>
+      </c>
+      <c r="I30" s="22" t="n">
+        <v>-96.03</v>
+      </c>
+      <c r="J30" s="23" t="inlineStr">
+        <is>
+          <t>네이버 검색 당일 +297% / 중요공시 2건</t>
+        </is>
+      </c>
+      <c r="K30" s="23" t="inlineStr">
+        <is>
+          <t>네이버, 공시</t>
+        </is>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
       <c r="A31" s="20" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B31" s="20" t="n">
@@ -1645,33 +1651,33 @@
       </c>
       <c r="C31" s="21" t="inlineStr">
         <is>
-          <t>스피어</t>
+          <t>비비안</t>
         </is>
       </c>
       <c r="D31" s="20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E31" s="20" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F31" s="20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G31" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H31" s="23" t="n">
-        <v>-10.29</v>
-      </c>
-      <c r="I31" s="23" t="n">
-        <v>-39.6</v>
-      </c>
-      <c r="J31" s="24" t="inlineStr">
-        <is>
-          <t>중요공시 4건 / 중요공시 3일 +100%</t>
-        </is>
-      </c>
-      <c r="K31" s="24" t="inlineStr">
+      <c r="H31" s="24" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="I31" s="24" t="n">
+        <v>58.32</v>
+      </c>
+      <c r="J31" s="23" t="inlineStr">
+        <is>
+          <t>중요공시 2건 / 매일경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K31" s="23" t="inlineStr">
         <is>
           <t>공시</t>
         </is>
@@ -1680,7 +1686,7 @@
     <row r="32" ht="18" customHeight="1">
       <c r="A32" s="20" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B32" s="20" t="n">
@@ -1688,14 +1694,14 @@
       </c>
       <c r="C32" s="21" t="inlineStr">
         <is>
-          <t>철강</t>
+          <t>셀트리온</t>
         </is>
       </c>
       <c r="D32" s="20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E32" s="20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F32" s="20" t="n">
         <v>0</v>
@@ -1703,27 +1709,27 @@
       <c r="G32" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H32" s="20" t="n">
-        <v/>
-      </c>
-      <c r="I32" s="20" t="n">
-        <v/>
-      </c>
-      <c r="J32" s="24" t="inlineStr">
-        <is>
-          <t>네이버뉴스 헤드라인 언급 / 매일경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K32" s="24" t="inlineStr">
-        <is>
-          <t>네이버</t>
+      <c r="H32" s="24" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="I32" s="22" t="n">
+        <v>-1.09</v>
+      </c>
+      <c r="J32" s="23" t="inlineStr">
+        <is>
+          <t>중요공시 2건 / 한국경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K32" s="23" t="inlineStr">
+        <is>
+          <t>공시</t>
         </is>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
       <c r="A33" s="20" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B33" s="20" t="n">
@@ -1731,14 +1737,14 @@
       </c>
       <c r="C33" s="21" t="inlineStr">
         <is>
-          <t>현대차</t>
+          <t>클로봇</t>
         </is>
       </c>
       <c r="D33" s="20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E33" s="20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F33" s="20" t="n">
         <v>0</v>
@@ -1746,25 +1752,27 @@
       <c r="G33" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H33" s="23" t="n">
-        <v>-12.05</v>
-      </c>
-      <c r="I33" s="23" t="n">
-        <v>-20.16</v>
-      </c>
-      <c r="J33" s="24" t="inlineStr">
-        <is>
-          <t>매일경제 기사 언급 / 매일경제 헤드라인 언급 / 매일경제 기사 언급</t>
-        </is>
-      </c>
-      <c r="K33" s="24" t="n">
-        <v/>
+      <c r="H33" s="24" t="n">
+        <v>9.380000000000001</v>
+      </c>
+      <c r="I33" s="22" t="n">
+        <v>-10.38</v>
+      </c>
+      <c r="J33" s="23" t="inlineStr">
+        <is>
+          <t>중요공시 1건 / 한국경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K33" s="23" t="inlineStr">
+        <is>
+          <t>공시</t>
+        </is>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
       <c r="A34" s="20" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B34" s="20" t="n">
@@ -1772,7 +1780,7 @@
       </c>
       <c r="C34" s="21" t="inlineStr">
         <is>
-          <t>노블엠앤비</t>
+          <t>전기차</t>
         </is>
       </c>
       <c r="D34" s="20" t="n">
@@ -1787,27 +1795,25 @@
       <c r="G34" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H34" s="22" t="n">
-        <v>4.17</v>
-      </c>
-      <c r="I34" s="23" t="n">
-        <v>-93.92</v>
-      </c>
-      <c r="J34" s="24" t="inlineStr">
-        <is>
-          <t>네이버 검색 당일 +155% / 중요공시 2건</t>
-        </is>
-      </c>
-      <c r="K34" s="24" t="inlineStr">
-        <is>
-          <t>네이버, 공시</t>
-        </is>
+      <c r="H34" s="20" t="n">
+        <v/>
+      </c>
+      <c r="I34" s="20" t="n">
+        <v/>
+      </c>
+      <c r="J34" s="23" t="inlineStr">
+        <is>
+          <t>매일경제 기사 언급 / 매일경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K34" s="23" t="n">
+        <v/>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
       <c r="A35" s="20" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B35" s="20" t="n">
@@ -1815,255 +1821,255 @@
       </c>
       <c r="C35" s="21" t="inlineStr">
         <is>
-          <t>센서뷰</t>
+          <t>스테이블코인</t>
         </is>
       </c>
       <c r="D35" s="20" t="n">
         <v>4</v>
       </c>
       <c r="E35" s="20" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F35" s="20" t="n">
         <v>0</v>
       </c>
       <c r="G35" s="20" t="n">
-        <v>3</v>
-      </c>
-      <c r="H35" s="23" t="n">
-        <v>-2.79</v>
-      </c>
-      <c r="I35" s="23" t="n">
-        <v>-15.56</v>
-      </c>
-      <c r="J35" s="24" t="inlineStr">
-        <is>
-          <t>중요공시 2건 / 중요공시 7일 +100%</t>
-        </is>
-      </c>
-      <c r="K35" s="24" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="H35" s="20" t="n">
+        <v/>
+      </c>
+      <c r="I35" s="20" t="n">
+        <v/>
+      </c>
+      <c r="J35" s="23" t="inlineStr">
+        <is>
+          <t>매일경제 헤드라인 언급 / 매일경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K35" s="23" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="36" ht="18" customHeight="1">
+      <c r="A36" s="25" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B36" s="25" t="n">
+        <v>23</v>
+      </c>
+      <c r="C36" s="26" t="inlineStr">
+        <is>
+          <t>국순당</t>
+        </is>
+      </c>
+      <c r="D36" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="E36" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="F36" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" s="27" t="n">
+        <v>6.93</v>
+      </c>
+      <c r="I36" s="27" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="J36" s="28" t="inlineStr">
+        <is>
+          <t>네이버 검색 당일 +178%</t>
+        </is>
+      </c>
+      <c r="K36" s="28" t="inlineStr">
+        <is>
+          <t>네이버</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="18" customHeight="1">
+      <c r="A37" s="25" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B37" s="25" t="n">
+        <v>24</v>
+      </c>
+      <c r="C37" s="26" t="inlineStr">
+        <is>
+          <t>조아제약</t>
+        </is>
+      </c>
+      <c r="D37" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="E37" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="F37" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G37" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" s="27" t="n">
+        <v>5.14</v>
+      </c>
+      <c r="I37" s="27" t="n">
+        <v>42.86</v>
+      </c>
+      <c r="J37" s="28" t="inlineStr">
+        <is>
+          <t>네이버 검색 당일 +144%</t>
+        </is>
+      </c>
+      <c r="K37" s="28" t="inlineStr">
+        <is>
+          <t>네이버</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="18" customHeight="1">
+      <c r="A38" s="25" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B38" s="25" t="n">
+        <v>25</v>
+      </c>
+      <c r="C38" s="26" t="inlineStr">
+        <is>
+          <t>해태제과식품</t>
+        </is>
+      </c>
+      <c r="D38" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="E38" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="F38" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G38" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" s="29" t="n">
+        <v>-3.38</v>
+      </c>
+      <c r="I38" s="27" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="J38" s="28" t="inlineStr">
+        <is>
+          <t>네이버 검색 당일 +142%</t>
+        </is>
+      </c>
+      <c r="K38" s="28" t="inlineStr">
+        <is>
+          <t>네이버</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="18" customHeight="1">
+      <c r="A39" s="25" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B39" s="25" t="n">
+        <v>26</v>
+      </c>
+      <c r="C39" s="26" t="inlineStr">
+        <is>
+          <t>미래나노텍</t>
+        </is>
+      </c>
+      <c r="D39" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="E39" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="F39" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G39" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" s="29" t="n">
+        <v>-4.76</v>
+      </c>
+      <c r="I39" s="27" t="n">
+        <v>14.36</v>
+      </c>
+      <c r="J39" s="28" t="inlineStr">
+        <is>
+          <t>네이버 검색 당일 +117%</t>
+        </is>
+      </c>
+      <c r="K39" s="28" t="inlineStr">
+        <is>
+          <t>네이버</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="18" customHeight="1">
+      <c r="A40" s="25" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B40" s="25" t="n">
+        <v>27</v>
+      </c>
+      <c r="C40" s="26" t="inlineStr">
+        <is>
+          <t>아이엠</t>
+        </is>
+      </c>
+      <c r="D40" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="E40" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="F40" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G40" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" s="27" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="I40" s="29" t="n">
+        <v>-86.36</v>
+      </c>
+      <c r="J40" s="28" t="inlineStr">
+        <is>
+          <t>중요공시 2건 / 매일경제 기사 언급</t>
+        </is>
+      </c>
+      <c r="K40" s="28" t="inlineStr">
         <is>
           <t>공시</t>
         </is>
-      </c>
-    </row>
-    <row r="36" ht="18" customHeight="1">
-      <c r="A36" s="20" t="inlineStr">
-        <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="B36" s="20" t="n">
-        <v>23</v>
-      </c>
-      <c r="C36" s="21" t="inlineStr">
-        <is>
-          <t>미래에셋증권</t>
-        </is>
-      </c>
-      <c r="D36" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="E36" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="F36" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G36" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H36" s="23" t="n">
-        <v>-8.57</v>
-      </c>
-      <c r="I36" s="23" t="n">
-        <v>-17.84</v>
-      </c>
-      <c r="J36" s="24" t="inlineStr">
-        <is>
-          <t>중요공시 2건 / 네이버뉴스 기사 언급 / 네이버뉴스 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K36" s="24" t="inlineStr">
-        <is>
-          <t>네이버, 공시</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="18" customHeight="1">
-      <c r="A37" s="20" t="inlineStr">
-        <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="B37" s="20" t="n">
-        <v>24</v>
-      </c>
-      <c r="C37" s="21" t="inlineStr">
-        <is>
-          <t>HJ중공업</t>
-        </is>
-      </c>
-      <c r="D37" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="E37" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="F37" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G37" s="20" t="n">
-        <v>3</v>
-      </c>
-      <c r="H37" s="23" t="n">
-        <v>-8.41</v>
-      </c>
-      <c r="I37" s="23" t="n">
-        <v>-14.6</v>
-      </c>
-      <c r="J37" s="24" t="inlineStr">
-        <is>
-          <t>중요공시 2건 / 중요공시 7일 +100%</t>
-        </is>
-      </c>
-      <c r="K37" s="24" t="inlineStr">
-        <is>
-          <t>공시</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="18" customHeight="1">
-      <c r="A38" s="20" t="inlineStr">
-        <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="B38" s="20" t="n">
-        <v>25</v>
-      </c>
-      <c r="C38" s="21" t="inlineStr">
-        <is>
-          <t>셀트리온</t>
-        </is>
-      </c>
-      <c r="D38" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="E38" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="F38" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G38" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H38" s="23" t="n">
-        <v>-4.75</v>
-      </c>
-      <c r="I38" s="23" t="n">
-        <v>-8.02</v>
-      </c>
-      <c r="J38" s="24" t="inlineStr">
-        <is>
-          <t>중요공시 2건 / 네이버뉴스 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K38" s="24" t="inlineStr">
-        <is>
-          <t>네이버, 공시</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="18" customHeight="1">
-      <c r="A39" s="20" t="inlineStr">
-        <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="B39" s="20" t="n">
-        <v>26</v>
-      </c>
-      <c r="C39" s="21" t="inlineStr">
-        <is>
-          <t>팬오션</t>
-        </is>
-      </c>
-      <c r="D39" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="E39" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="F39" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G39" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H39" s="23" t="n">
-        <v>-4.98</v>
-      </c>
-      <c r="I39" s="23" t="n">
-        <v>-12.55</v>
-      </c>
-      <c r="J39" s="24" t="inlineStr">
-        <is>
-          <t>중요공시 1건 / 네이버뉴스 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K39" s="24" t="inlineStr">
-        <is>
-          <t>네이버, 공시</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="18" customHeight="1">
-      <c r="A40" s="20" t="inlineStr">
-        <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="B40" s="20" t="n">
-        <v>27</v>
-      </c>
-      <c r="C40" s="21" t="inlineStr">
-        <is>
-          <t>한미반도체</t>
-        </is>
-      </c>
-      <c r="D40" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="E40" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="F40" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G40" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H40" s="23" t="n">
-        <v>-14.43</v>
-      </c>
-      <c r="I40" s="23" t="n">
-        <v>-21.46</v>
-      </c>
-      <c r="J40" s="24" t="inlineStr">
-        <is>
-          <t>한국경제 헤드라인 언급 / 매일경제 기사 언급</t>
-        </is>
-      </c>
-      <c r="K40" s="24" t="n">
-        <v/>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
       <c r="A41" s="25" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B41" s="25" t="n">
@@ -2071,7 +2077,7 @@
       </c>
       <c r="C41" s="26" t="inlineStr">
         <is>
-          <t>바이온</t>
+          <t>경남제약</t>
         </is>
       </c>
       <c r="D41" s="25" t="n">
@@ -2086,27 +2092,27 @@
       <c r="G41" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H41" s="27" t="n">
-        <v>68.42</v>
-      </c>
-      <c r="I41" s="28" t="n">
-        <v>-94.7</v>
-      </c>
-      <c r="J41" s="29" t="inlineStr">
-        <is>
-          <t>네이버 검색 당일 +81% / 중요공시 2건</t>
-        </is>
-      </c>
-      <c r="K41" s="29" t="inlineStr">
-        <is>
-          <t>네이버, 공시</t>
+      <c r="H41" s="29" t="n">
+        <v>-10.34</v>
+      </c>
+      <c r="I41" s="27" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="J41" s="28" t="inlineStr">
+        <is>
+          <t>중요공시 4건</t>
+        </is>
+      </c>
+      <c r="K41" s="28" t="inlineStr">
+        <is>
+          <t>공시</t>
         </is>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
       <c r="A42" s="25" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B42" s="25" t="n">
@@ -2114,7 +2120,7 @@
       </c>
       <c r="C42" s="26" t="inlineStr">
         <is>
-          <t>키스트론</t>
+          <t>소룩스</t>
         </is>
       </c>
       <c r="D42" s="25" t="n">
@@ -2129,25 +2135,27 @@
       <c r="G42" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H42" s="28" t="n">
-        <v>-10.97</v>
+      <c r="H42" s="27" t="n">
+        <v>15.6</v>
       </c>
       <c r="I42" s="27" t="n">
-        <v>18.91</v>
-      </c>
-      <c r="J42" s="29" t="inlineStr">
-        <is>
-          <t>매일경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K42" s="29" t="n">
-        <v/>
+        <v>19.42</v>
+      </c>
+      <c r="J42" s="28" t="inlineStr">
+        <is>
+          <t>중요공시 3건</t>
+        </is>
+      </c>
+      <c r="K42" s="28" t="inlineStr">
+        <is>
+          <t>공시</t>
+        </is>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1">
       <c r="A43" s="25" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B43" s="25" t="n">
@@ -2155,7 +2163,7 @@
       </c>
       <c r="C43" s="26" t="inlineStr">
         <is>
-          <t>소룩스</t>
+          <t>오리엔트바이오</t>
         </is>
       </c>
       <c r="D43" s="25" t="n">
@@ -2171,17 +2179,17 @@
         <v>0</v>
       </c>
       <c r="H43" s="27" t="n">
-        <v>14.42</v>
-      </c>
-      <c r="I43" s="27" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="J43" s="29" t="inlineStr">
+        <v>10.97</v>
+      </c>
+      <c r="I43" s="29" t="n">
+        <v>-6.38</v>
+      </c>
+      <c r="J43" s="28" t="inlineStr">
         <is>
           <t>중요공시 3건</t>
         </is>
       </c>
-      <c r="K43" s="29" t="inlineStr">
+      <c r="K43" s="28" t="inlineStr">
         <is>
           <t>공시</t>
         </is>
@@ -2190,7 +2198,7 @@
     <row r="44" ht="18" customHeight="1">
       <c r="A44" s="25" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B44" s="25" t="n">
@@ -2198,42 +2206,40 @@
       </c>
       <c r="C44" s="26" t="inlineStr">
         <is>
-          <t>KBI메탈</t>
+          <t>동양</t>
         </is>
       </c>
       <c r="D44" s="25" t="n">
         <v>3</v>
       </c>
       <c r="E44" s="25" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F44" s="25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G44" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H44" s="28" t="n">
-        <v>-0.57</v>
-      </c>
-      <c r="I44" s="28" t="n">
-        <v>-7.47</v>
-      </c>
-      <c r="J44" s="29" t="inlineStr">
-        <is>
-          <t>중요공시 2건 / 중요공시 3일 +100%</t>
-        </is>
-      </c>
-      <c r="K44" s="29" t="inlineStr">
-        <is>
-          <t>공시</t>
-        </is>
+      <c r="H44" s="27" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="I44" s="29" t="n">
+        <v>-3.41</v>
+      </c>
+      <c r="J44" s="28" t="inlineStr">
+        <is>
+          <t>매일경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K44" s="28" t="n">
+        <v/>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
       <c r="A45" s="25" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B45" s="25" t="n">
@@ -2241,7 +2247,7 @@
       </c>
       <c r="C45" s="26" t="inlineStr">
         <is>
-          <t>우성머티리얼스</t>
+          <t>대한항공</t>
         </is>
       </c>
       <c r="D45" s="25" t="n">
@@ -2256,27 +2262,25 @@
       <c r="G45" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H45" s="28" t="n">
-        <v>-1.12</v>
-      </c>
-      <c r="I45" s="28" t="n">
-        <v>-16.13</v>
-      </c>
-      <c r="J45" s="29" t="inlineStr">
-        <is>
-          <t>중요공시 7건</t>
-        </is>
-      </c>
-      <c r="K45" s="29" t="inlineStr">
-        <is>
-          <t>공시</t>
-        </is>
+      <c r="H45" s="27" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="I45" s="29" t="n">
+        <v>-5.03</v>
+      </c>
+      <c r="J45" s="28" t="inlineStr">
+        <is>
+          <t>매일경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K45" s="28" t="n">
+        <v/>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
       <c r="A46" s="25" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B46" s="25" t="n">
@@ -2284,33 +2288,33 @@
       </c>
       <c r="C46" s="26" t="inlineStr">
         <is>
-          <t>경남제약</t>
+          <t>성호전자</t>
         </is>
       </c>
       <c r="D46" s="25" t="n">
         <v>3</v>
       </c>
       <c r="E46" s="25" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F46" s="25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G46" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H46" s="27" t="n">
-        <v>29.75</v>
-      </c>
-      <c r="I46" s="27" t="n">
-        <v>18.19</v>
-      </c>
-      <c r="J46" s="29" t="inlineStr">
-        <is>
-          <t>중요공시 4건</t>
-        </is>
-      </c>
-      <c r="K46" s="29" t="inlineStr">
+      <c r="H46" s="29" t="n">
+        <v>-4.3</v>
+      </c>
+      <c r="I46" s="29" t="n">
+        <v>-29.63</v>
+      </c>
+      <c r="J46" s="28" t="inlineStr">
+        <is>
+          <t>중요공시 2건 / 중요공시 3일 +100%</t>
+        </is>
+      </c>
+      <c r="K46" s="28" t="inlineStr">
         <is>
           <t>공시</t>
         </is>
@@ -2319,7 +2323,7 @@
     <row r="47" ht="18" customHeight="1">
       <c r="A47" s="25" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B47" s="25" t="n">
@@ -2327,7 +2331,7 @@
       </c>
       <c r="C47" s="26" t="inlineStr">
         <is>
-          <t>넥써쓰</t>
+          <t>차AI헬스케어</t>
         </is>
       </c>
       <c r="D47" s="25" t="n">
@@ -2342,18 +2346,18 @@
       <c r="G47" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H47" s="28" t="n">
-        <v>-11.22</v>
-      </c>
-      <c r="I47" s="28" t="n">
-        <v>-20.36</v>
-      </c>
-      <c r="J47" s="29" t="inlineStr">
-        <is>
-          <t>중요공시 3건</t>
-        </is>
-      </c>
-      <c r="K47" s="29" t="inlineStr">
+      <c r="H47" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I47" s="27" t="n">
+        <v>14.85</v>
+      </c>
+      <c r="J47" s="28" t="inlineStr">
+        <is>
+          <t>중요공시 11건</t>
+        </is>
+      </c>
+      <c r="K47" s="28" t="inlineStr">
         <is>
           <t>공시</t>
         </is>
@@ -2362,7 +2366,7 @@
     <row r="48" ht="18" customHeight="1">
       <c r="A48" s="25" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B48" s="25" t="n">
@@ -2370,7 +2374,7 @@
       </c>
       <c r="C48" s="26" t="inlineStr">
         <is>
-          <t>LB세미콘</t>
+          <t>넥써쓰</t>
         </is>
       </c>
       <c r="D48" s="25" t="n">
@@ -2385,18 +2389,18 @@
       <c r="G48" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H48" s="28" t="n">
-        <v>-12.95</v>
-      </c>
-      <c r="I48" s="28" t="n">
-        <v>-9.859999999999999</v>
-      </c>
-      <c r="J48" s="29" t="inlineStr">
+      <c r="H48" s="29" t="n">
+        <v>-7.32</v>
+      </c>
+      <c r="I48" s="29" t="n">
+        <v>-38.17</v>
+      </c>
+      <c r="J48" s="28" t="inlineStr">
         <is>
           <t>중요공시 3건</t>
         </is>
       </c>
-      <c r="K48" s="29" t="inlineStr">
+      <c r="K48" s="28" t="inlineStr">
         <is>
           <t>공시</t>
         </is>
@@ -2405,7 +2409,7 @@
     <row r="49" ht="18" customHeight="1">
       <c r="A49" s="25" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B49" s="25" t="n">
@@ -2413,33 +2417,33 @@
       </c>
       <c r="C49" s="26" t="inlineStr">
         <is>
-          <t>진흥기업</t>
+          <t>아모텍</t>
         </is>
       </c>
       <c r="D49" s="25" t="n">
         <v>3</v>
       </c>
       <c r="E49" s="25" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F49" s="25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G49" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H49" s="28" t="n">
-        <v>-7.5</v>
-      </c>
-      <c r="I49" s="28" t="n">
-        <v>-16.77</v>
-      </c>
-      <c r="J49" s="29" t="inlineStr">
-        <is>
-          <t>중요공시 2건 / 중요공시 3일 +100%</t>
-        </is>
-      </c>
-      <c r="K49" s="29" t="inlineStr">
+      <c r="H49" s="29" t="n">
+        <v>-4.98</v>
+      </c>
+      <c r="I49" s="29" t="n">
+        <v>-21.8</v>
+      </c>
+      <c r="J49" s="28" t="inlineStr">
+        <is>
+          <t>중요공시 3건</t>
+        </is>
+      </c>
+      <c r="K49" s="28" t="inlineStr">
         <is>
           <t>공시</t>
         </is>
@@ -2448,7 +2452,7 @@
     <row r="50" ht="18" customHeight="1">
       <c r="A50" s="25" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B50" s="25" t="n">
@@ -2456,33 +2460,33 @@
       </c>
       <c r="C50" s="26" t="inlineStr">
         <is>
-          <t>시너지이노베이션</t>
+          <t>에이프로젠</t>
         </is>
       </c>
       <c r="D50" s="25" t="n">
         <v>3</v>
       </c>
       <c r="E50" s="25" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F50" s="25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G50" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H50" s="28" t="n">
-        <v>-8.279999999999999</v>
-      </c>
-      <c r="I50" s="28" t="n">
-        <v>-14.05</v>
-      </c>
-      <c r="J50" s="29" t="inlineStr">
-        <is>
-          <t>중요공시 2건 / 중요공시 3일 +100%</t>
-        </is>
-      </c>
-      <c r="K50" s="29" t="inlineStr">
+      <c r="H50" s="29" t="n">
+        <v>-3.2</v>
+      </c>
+      <c r="I50" s="29" t="n">
+        <v>-21.94</v>
+      </c>
+      <c r="J50" s="28" t="inlineStr">
+        <is>
+          <t>중요공시 3건</t>
+        </is>
+      </c>
+      <c r="K50" s="28" t="inlineStr">
         <is>
           <t>공시</t>
         </is>
@@ -2491,7 +2495,7 @@
     <row r="51" ht="18" customHeight="1">
       <c r="A51" s="25" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B51" s="25" t="n">
@@ -2499,42 +2503,42 @@
       </c>
       <c r="C51" s="26" t="inlineStr">
         <is>
-          <t>AI반도체</t>
+          <t>진흥기업</t>
         </is>
       </c>
       <c r="D51" s="25" t="n">
         <v>3</v>
       </c>
       <c r="E51" s="25" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F51" s="25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G51" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H51" s="25" t="n">
-        <v/>
-      </c>
-      <c r="I51" s="25" t="n">
-        <v/>
-      </c>
-      <c r="J51" s="29" t="inlineStr">
-        <is>
-          <t>네이버뉴스 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K51" s="29" t="inlineStr">
-        <is>
-          <t>네이버</t>
+      <c r="H51" s="29" t="n">
+        <v>-2.03</v>
+      </c>
+      <c r="I51" s="29" t="n">
+        <v>-15.98</v>
+      </c>
+      <c r="J51" s="28" t="inlineStr">
+        <is>
+          <t>중요공시 2건 / 중요공시 3일 +100%</t>
+        </is>
+      </c>
+      <c r="K51" s="28" t="inlineStr">
+        <is>
+          <t>공시</t>
         </is>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1">
       <c r="A52" s="25" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B52" s="25" t="n">
@@ -2542,40 +2546,42 @@
       </c>
       <c r="C52" s="26" t="inlineStr">
         <is>
-          <t>SK텔레콤</t>
+          <t>시너지이노베이션</t>
         </is>
       </c>
       <c r="D52" s="25" t="n">
         <v>3</v>
       </c>
       <c r="E52" s="25" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F52" s="25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G52" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H52" s="28" t="n">
-        <v>-4.56</v>
-      </c>
-      <c r="I52" s="28" t="n">
-        <v>-10.19</v>
-      </c>
-      <c r="J52" s="29" t="inlineStr">
-        <is>
-          <t>매일경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K52" s="29" t="n">
-        <v/>
+      <c r="H52" s="27" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="I52" s="29" t="n">
+        <v>-10.09</v>
+      </c>
+      <c r="J52" s="28" t="inlineStr">
+        <is>
+          <t>중요공시 2건 / 중요공시 3일 +100%</t>
+        </is>
+      </c>
+      <c r="K52" s="28" t="inlineStr">
+        <is>
+          <t>공시</t>
+        </is>
       </c>
     </row>
     <row r="53" ht="18" customHeight="1">
       <c r="A53" s="25" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B53" s="25" t="n">
@@ -2583,7 +2589,7 @@
       </c>
       <c r="C53" s="26" t="inlineStr">
         <is>
-          <t>두산로보틱스</t>
+          <t>ISC</t>
         </is>
       </c>
       <c r="D53" s="25" t="n">
@@ -2598,25 +2604,25 @@
       <c r="G53" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H53" s="28" t="n">
-        <v>-11.55</v>
-      </c>
-      <c r="I53" s="28" t="n">
-        <v>-18.53</v>
-      </c>
-      <c r="J53" s="29" t="inlineStr">
+      <c r="H53" s="27" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="I53" s="29" t="n">
+        <v>-2.16</v>
+      </c>
+      <c r="J53" s="28" t="inlineStr">
         <is>
           <t>매일경제 헤드라인 언급</t>
         </is>
       </c>
-      <c r="K53" s="29" t="n">
+      <c r="K53" s="28" t="n">
         <v/>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
       <c r="A54" s="25" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B54" s="25" t="n">
@@ -2624,7 +2630,7 @@
       </c>
       <c r="C54" s="26" t="inlineStr">
         <is>
-          <t>성도이엔지</t>
+          <t>테스</t>
         </is>
       </c>
       <c r="D54" s="25" t="n">
@@ -2639,25 +2645,25 @@
       <c r="G54" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H54" s="28" t="n">
-        <v>-7.69</v>
-      </c>
-      <c r="I54" s="27" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="J54" s="29" t="inlineStr">
+      <c r="H54" s="27" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="I54" s="29" t="n">
+        <v>-4.07</v>
+      </c>
+      <c r="J54" s="28" t="inlineStr">
         <is>
           <t>매일경제 헤드라인 언급</t>
         </is>
       </c>
-      <c r="K54" s="29" t="n">
+      <c r="K54" s="28" t="n">
         <v/>
       </c>
     </row>
     <row r="55" ht="18" customHeight="1">
       <c r="A55" s="25" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B55" s="25" t="n">
@@ -2665,7 +2671,7 @@
       </c>
       <c r="C55" s="26" t="inlineStr">
         <is>
-          <t>방산</t>
+          <t>LG이노텍</t>
         </is>
       </c>
       <c r="D55" s="25" t="n">
@@ -2680,25 +2686,25 @@
       <c r="G55" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H55" s="25" t="n">
-        <v/>
-      </c>
-      <c r="I55" s="25" t="n">
-        <v/>
-      </c>
-      <c r="J55" s="29" t="inlineStr">
+      <c r="H55" s="29" t="n">
+        <v>-3.43</v>
+      </c>
+      <c r="I55" s="29" t="n">
+        <v>-23.32</v>
+      </c>
+      <c r="J55" s="28" t="inlineStr">
         <is>
           <t>한국경제 헤드라인 언급</t>
         </is>
       </c>
-      <c r="K55" s="29" t="n">
+      <c r="K55" s="28" t="n">
         <v/>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1">
       <c r="A56" s="25" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B56" s="25" t="n">
@@ -2706,7 +2712,7 @@
       </c>
       <c r="C56" s="26" t="inlineStr">
         <is>
-          <t>태양광</t>
+          <t>동양파일</t>
         </is>
       </c>
       <c r="D56" s="25" t="n">
@@ -2721,25 +2727,25 @@
       <c r="G56" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H56" s="25" t="n">
-        <v/>
-      </c>
-      <c r="I56" s="25" t="n">
-        <v/>
-      </c>
-      <c r="J56" s="29" t="inlineStr">
+      <c r="H56" s="27" t="n">
+        <v>29.92</v>
+      </c>
+      <c r="I56" s="27" t="n">
+        <v>27.24</v>
+      </c>
+      <c r="J56" s="28" t="inlineStr">
         <is>
           <t>매일경제 헤드라인 언급</t>
         </is>
       </c>
-      <c r="K56" s="29" t="n">
+      <c r="K56" s="28" t="n">
         <v/>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1">
       <c r="A57" s="25" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B57" s="25" t="n">
@@ -2747,14 +2753,14 @@
       </c>
       <c r="C57" s="26" t="inlineStr">
         <is>
-          <t>에이테크솔루션</t>
+          <t>원전</t>
         </is>
       </c>
       <c r="D57" s="25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E57" s="25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F57" s="25" t="n">
         <v>0</v>
@@ -2762,18 +2768,18 @@
       <c r="G57" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H57" s="28" t="n">
-        <v>-4.39</v>
-      </c>
-      <c r="I57" s="27" t="n">
-        <v>15.25</v>
-      </c>
-      <c r="J57" s="29" t="inlineStr">
-        <is>
-          <t>네이버 검색 당일 +72%</t>
-        </is>
-      </c>
-      <c r="K57" s="29" t="inlineStr">
+      <c r="H57" s="25" t="n">
+        <v/>
+      </c>
+      <c r="I57" s="25" t="n">
+        <v/>
+      </c>
+      <c r="J57" s="28" t="inlineStr">
+        <is>
+          <t>네이버뉴스 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K57" s="28" t="inlineStr">
         <is>
           <t>네이버</t>
         </is>
@@ -2782,7 +2788,7 @@
     <row r="58" ht="18" customHeight="1">
       <c r="A58" s="25" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B58" s="25" t="n">
@@ -2790,14 +2796,14 @@
       </c>
       <c r="C58" s="26" t="inlineStr">
         <is>
-          <t>케이뱅크</t>
+          <t>철강</t>
         </is>
       </c>
       <c r="D58" s="25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E58" s="25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F58" s="25" t="n">
         <v>0</v>
@@ -2805,25 +2811,27 @@
       <c r="G58" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H58" s="28" t="n">
-        <v>-3.66</v>
-      </c>
-      <c r="I58" s="28" t="n">
-        <v>-12.06</v>
-      </c>
-      <c r="J58" s="29" t="inlineStr">
-        <is>
-          <t>한국경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K58" s="29" t="n">
+      <c r="H58" s="25" t="n">
         <v/>
+      </c>
+      <c r="I58" s="25" t="n">
+        <v/>
+      </c>
+      <c r="J58" s="28" t="inlineStr">
+        <is>
+          <t>네이버뉴스 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K58" s="28" t="inlineStr">
+        <is>
+          <t>네이버</t>
+        </is>
       </c>
     </row>
     <row r="59" ht="18" customHeight="1">
       <c r="A59" s="25" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B59" s="25" t="n">
@@ -2831,14 +2839,14 @@
       </c>
       <c r="C59" s="26" t="inlineStr">
         <is>
-          <t>NH투자증권</t>
+          <t>HMM</t>
         </is>
       </c>
       <c r="D59" s="25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E59" s="25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F59" s="25" t="n">
         <v>0</v>
@@ -2846,27 +2854,25 @@
       <c r="G59" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H59" s="28" t="n">
-        <v>-6.66</v>
-      </c>
-      <c r="I59" s="28" t="n">
-        <v>-12.48</v>
-      </c>
-      <c r="J59" s="29" t="inlineStr">
-        <is>
-          <t>네이버뉴스 기사 언급 / 매일경제 기사 언급</t>
-        </is>
-      </c>
-      <c r="K59" s="29" t="inlineStr">
-        <is>
-          <t>네이버</t>
-        </is>
+      <c r="H59" s="27" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="I59" s="29" t="n">
+        <v>-14.3</v>
+      </c>
+      <c r="J59" s="28" t="inlineStr">
+        <is>
+          <t>한국경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K59" s="28" t="n">
+        <v/>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1">
       <c r="A60" s="25" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B60" s="25" t="n">
@@ -2874,14 +2880,14 @@
       </c>
       <c r="C60" s="26" t="inlineStr">
         <is>
-          <t>삼성전기</t>
+          <t>기아</t>
         </is>
       </c>
       <c r="D60" s="25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E60" s="25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F60" s="25" t="n">
         <v>0</v>
@@ -2889,25 +2895,25 @@
       <c r="G60" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H60" s="28" t="n">
-        <v>-10.68</v>
-      </c>
-      <c r="I60" s="28" t="n">
-        <v>-2.83</v>
-      </c>
-      <c r="J60" s="29" t="inlineStr">
+      <c r="H60" s="27" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="I60" s="29" t="n">
+        <v>-16.48</v>
+      </c>
+      <c r="J60" s="28" t="inlineStr">
         <is>
           <t>한국경제 헤드라인 언급</t>
         </is>
       </c>
-      <c r="K60" s="29" t="n">
+      <c r="K60" s="28" t="n">
         <v/>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
       <c r="A61" s="25" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B61" s="25" t="n">
@@ -2915,7 +2921,7 @@
       </c>
       <c r="C61" s="26" t="inlineStr">
         <is>
-          <t>카카오</t>
+          <t>보해양조</t>
         </is>
       </c>
       <c r="D61" s="25" t="n">
@@ -2930,25 +2936,27 @@
       <c r="G61" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H61" s="28" t="n">
-        <v>-6.93</v>
-      </c>
-      <c r="I61" s="28" t="n">
-        <v>-15.33</v>
-      </c>
-      <c r="J61" s="29" t="inlineStr">
-        <is>
-          <t>한국경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K61" s="29" t="n">
-        <v/>
+      <c r="H61" s="27" t="n">
+        <v>29.93</v>
+      </c>
+      <c r="I61" s="27" t="n">
+        <v>177.58</v>
+      </c>
+      <c r="J61" s="28" t="inlineStr">
+        <is>
+          <t>네이버 검색 당일 +100%</t>
+        </is>
+      </c>
+      <c r="K61" s="28" t="inlineStr">
+        <is>
+          <t>네이버</t>
+        </is>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1">
       <c r="A62" s="25" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B62" s="25" t="n">
@@ -2956,7 +2964,7 @@
       </c>
       <c r="C62" s="26" t="inlineStr">
         <is>
-          <t>원전</t>
+          <t>부국철강</t>
         </is>
       </c>
       <c r="D62" s="25" t="n">
@@ -2971,25 +2979,27 @@
       <c r="G62" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H62" s="25" t="n">
-        <v/>
-      </c>
-      <c r="I62" s="25" t="n">
-        <v/>
-      </c>
-      <c r="J62" s="29" t="inlineStr">
-        <is>
-          <t>한국경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K62" s="29" t="n">
-        <v/>
+      <c r="H62" s="29" t="n">
+        <v>-7.99</v>
+      </c>
+      <c r="I62" s="27" t="n">
+        <v>45.78</v>
+      </c>
+      <c r="J62" s="28" t="inlineStr">
+        <is>
+          <t>네이버 검색 당일 +95%</t>
+        </is>
+      </c>
+      <c r="K62" s="28" t="inlineStr">
+        <is>
+          <t>네이버</t>
+        </is>
       </c>
     </row>
     <row r="63" ht="18" customHeight="1">
       <c r="A63" s="25" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B63" s="25" t="n">
@@ -2997,7 +3007,7 @@
       </c>
       <c r="C63" s="26" t="inlineStr">
         <is>
-          <t>스테이블코인</t>
+          <t>키스트론</t>
         </is>
       </c>
       <c r="D63" s="25" t="n">
@@ -3012,19 +3022,21 @@
       <c r="G63" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H63" s="25" t="n">
-        <v/>
-      </c>
-      <c r="I63" s="25" t="n">
-        <v/>
-      </c>
-      <c r="J63" s="29" t="inlineStr">
-        <is>
-          <t>매일경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K63" s="29" t="n">
-        <v/>
+      <c r="H63" s="27" t="n">
+        <v>4.23</v>
+      </c>
+      <c r="I63" s="27" t="n">
+        <v>23.53</v>
+      </c>
+      <c r="J63" s="28" t="inlineStr">
+        <is>
+          <t>네이버 검색 당일 +91%</t>
+        </is>
+      </c>
+      <c r="K63" s="28" t="inlineStr">
+        <is>
+          <t>네이버</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -3120,22 +3132,22 @@
         <v>1</v>
       </c>
       <c r="C3" s="25" t="n">
-        <v>114</v>
+        <v>100</v>
       </c>
       <c r="D3" s="25" t="n">
-        <v>114</v>
+        <v>100</v>
       </c>
       <c r="E3" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F3" s="25" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G3" s="25" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="H3" s="25" t="n"/>
@@ -3144,36 +3156,36 @@
     <row r="4" ht="18" customHeight="1">
       <c r="A4" s="26" t="inlineStr">
         <is>
-          <t>SK</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B4" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C4" s="25" t="n">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="D4" s="25" t="n">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="E4" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F4" s="25" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G4" s="25" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="H4" s="28" t="n">
-        <v>-3.42</v>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="H4" s="27" t="n">
+        <v>0.98</v>
       </c>
       <c r="I4" s="27" t="n">
-        <v>4.75</v>
+        <v>2.34</v>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1">
@@ -3186,105 +3198,97 @@
         <v>1</v>
       </c>
       <c r="C5" s="25" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D5" s="25" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E5" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F5" s="25" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G5" s="25" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="H5" s="28" t="n">
-        <v>-12.31</v>
-      </c>
-      <c r="I5" s="28" t="n">
-        <v>-9.619999999999999</v>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="H5" s="27" t="n">
+        <v>9.84</v>
+      </c>
+      <c r="I5" s="29" t="n">
+        <v>-1.73</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
       <c r="A6" s="26" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>인공지능</t>
         </is>
       </c>
       <c r="B6" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C6" s="25" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D6" s="25" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E6" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F6" s="25" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G6" s="25" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="H6" s="28" t="n">
-        <v>-12.47</v>
-      </c>
-      <c r="I6" s="27" t="n">
-        <v>7.26</v>
-      </c>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="H6" s="25" t="n"/>
+      <c r="I6" s="25" t="n"/>
     </row>
     <row r="7" ht="18" customHeight="1">
       <c r="A7" s="26" t="inlineStr">
         <is>
-          <t>LG</t>
+          <t>바이오</t>
         </is>
       </c>
       <c r="B7" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C7" s="25" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D7" s="25" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E7" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F7" s="25" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G7" s="25" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="H7" s="28" t="n">
-        <v>-10.28</v>
-      </c>
-      <c r="I7" s="28" t="n">
-        <v>-13.58</v>
-      </c>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="H7" s="25" t="n"/>
+      <c r="I7" s="25" t="n"/>
     </row>
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="26" t="inlineStr">
         <is>
-          <t>인공지능</t>
+          <t>LG</t>
         </is>
       </c>
       <c r="B8" s="25" t="n">
@@ -3301,16 +3305,20 @@
       </c>
       <c r="F8" s="25" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G8" s="25" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="H8" s="25" t="n"/>
-      <c r="I8" s="25" t="n"/>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="H8" s="27" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="I8" s="29" t="n">
+        <v>-11.82</v>
+      </c>
     </row>
     <row r="9" ht="18" customHeight="1">
       <c r="A9" s="26" t="inlineStr">
@@ -3322,22 +3330,22 @@
         <v>1</v>
       </c>
       <c r="C9" s="25" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D9" s="25" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E9" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F9" s="25" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G9" s="25" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="H9" s="25" t="n"/>
@@ -3346,36 +3354,36 @@
     <row r="10" ht="18" customHeight="1">
       <c r="A10" s="26" t="inlineStr">
         <is>
-          <t>LG전자</t>
+          <t>에이팩트</t>
         </is>
       </c>
       <c r="B10" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C10" s="25" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D10" s="25" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E10" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F10" s="25" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G10" s="25" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="H10" s="28" t="n">
-        <v>-11.21</v>
-      </c>
-      <c r="I10" s="28" t="n">
-        <v>-13.68</v>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="H10" s="29" t="n">
+        <v>-5.97</v>
+      </c>
+      <c r="I10" s="29" t="n">
+        <v>-26.41</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
@@ -3388,22 +3396,22 @@
         <v>1</v>
       </c>
       <c r="C11" s="25" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D11" s="25" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E11" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F11" s="25" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G11" s="25" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="H11" s="25" t="n"/>
@@ -3412,7 +3420,7 @@
     <row r="12" ht="18" customHeight="1">
       <c r="A12" s="26" t="inlineStr">
         <is>
-          <t>에이팩트</t>
+          <t>현대차</t>
         </is>
       </c>
       <c r="B12" s="25" t="n">
@@ -3429,25 +3437,25 @@
       </c>
       <c r="F12" s="25" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G12" s="25" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="H12" s="28" t="n">
-        <v>-11.96</v>
-      </c>
-      <c r="I12" s="28" t="n">
-        <v>-17.49</v>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="H12" s="29" t="n">
+        <v>-0.39</v>
+      </c>
+      <c r="I12" s="29" t="n">
+        <v>-17.64</v>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
       <c r="A13" s="26" t="inlineStr">
         <is>
-          <t>바이오</t>
+          <t>에이프릴바이오</t>
         </is>
       </c>
       <c r="B13" s="25" t="n">
@@ -3464,21 +3472,25 @@
       </c>
       <c r="F13" s="25" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G13" s="25" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="H13" s="25" t="n"/>
-      <c r="I13" s="25" t="n"/>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="H13" s="27" t="n">
+        <v>15.57</v>
+      </c>
+      <c r="I13" s="29" t="n">
+        <v>-14.62</v>
+      </c>
     </row>
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="26" t="inlineStr">
         <is>
-          <t>KT</t>
+          <t>비투엔</t>
         </is>
       </c>
       <c r="B14" s="25" t="n">
@@ -3495,25 +3507,25 @@
       </c>
       <c r="F14" s="25" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G14" s="25" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="H14" s="27" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="I14" s="28" t="n">
-        <v>-7.42</v>
+        <v>15.89</v>
+      </c>
+      <c r="I14" s="27" t="n">
+        <v>5.85</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
       <c r="A15" s="26" t="inlineStr">
         <is>
-          <t>대한항공</t>
+          <t>프로브잇</t>
         </is>
       </c>
       <c r="B15" s="25" t="n">
@@ -3530,262 +3542,266 @@
       </c>
       <c r="F15" s="25" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G15" s="25" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="H15" s="28" t="n">
-        <v>-4.25</v>
-      </c>
-      <c r="I15" s="28" t="n">
-        <v>-11.6</v>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="H15" s="29" t="n">
+        <v>-46</v>
+      </c>
+      <c r="I15" s="29" t="n">
+        <v>-95.59</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
       <c r="A16" s="26" t="inlineStr">
         <is>
-          <t>비투엔</t>
+          <t>센서뷰</t>
         </is>
       </c>
       <c r="B16" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C16" s="25" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D16" s="25" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E16" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F16" s="25" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G16" s="25" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="H16" s="28" t="n">
-        <v>-5.03</v>
-      </c>
-      <c r="I16" s="28" t="n">
-        <v>-7.93</v>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="H16" s="27" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="I16" s="29" t="n">
+        <v>-10.4</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
       <c r="A17" s="26" t="inlineStr">
         <is>
-          <t>삼성바이오로직스</t>
+          <t>스피어</t>
         </is>
       </c>
       <c r="B17" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C17" s="25" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D17" s="25" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E17" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F17" s="25" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G17" s="25" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="H17" s="28" t="n">
-        <v>-1.7</v>
-      </c>
-      <c r="I17" s="28" t="n">
-        <v>-4.5</v>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="H17" s="27" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="I17" s="29" t="n">
+        <v>-28.67</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
       <c r="A18" s="26" t="inlineStr">
         <is>
-          <t>전기차</t>
+          <t>노블엠앤비</t>
         </is>
       </c>
       <c r="B18" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C18" s="25" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D18" s="25" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E18" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F18" s="25" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G18" s="25" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="H18" s="25" t="n"/>
-      <c r="I18" s="25" t="n"/>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="H18" s="29" t="n">
+        <v>-16</v>
+      </c>
+      <c r="I18" s="29" t="n">
+        <v>-94.89</v>
+      </c>
     </row>
     <row r="19" ht="18" customHeight="1">
       <c r="A19" s="26" t="inlineStr">
         <is>
-          <t>프로브잇</t>
+          <t>바이온</t>
         </is>
       </c>
       <c r="B19" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C19" s="25" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D19" s="25" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E19" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F19" s="25" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G19" s="25" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="H19" s="27" t="n">
-        <v>177.78</v>
-      </c>
-      <c r="I19" s="28" t="n">
-        <v>-91.83</v>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="H19" s="29" t="n">
+        <v>-25</v>
+      </c>
+      <c r="I19" s="29" t="n">
+        <v>-96.03</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
       <c r="A20" s="26" t="inlineStr">
         <is>
-          <t>스피어</t>
+          <t>비비안</t>
         </is>
       </c>
       <c r="B20" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C20" s="25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D20" s="25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E20" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F20" s="25" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G20" s="25" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="H20" s="28" t="n">
-        <v>-10.29</v>
-      </c>
-      <c r="I20" s="28" t="n">
-        <v>-39.6</v>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="H20" s="27" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="I20" s="27" t="n">
+        <v>58.32</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
       <c r="A21" s="26" t="inlineStr">
         <is>
-          <t>철강</t>
+          <t>셀트리온</t>
         </is>
       </c>
       <c r="B21" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C21" s="25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D21" s="25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E21" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F21" s="25" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G21" s="25" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="H21" s="25" t="n"/>
-      <c r="I21" s="25" t="n"/>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="H21" s="27" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="I21" s="29" t="n">
+        <v>-1.09</v>
+      </c>
     </row>
     <row r="22" ht="18" customHeight="1">
       <c r="A22" s="26" t="inlineStr">
         <is>
-          <t>현대차</t>
+          <t>스테이블코인</t>
         </is>
       </c>
       <c r="B22" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C22" s="25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D22" s="25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E22" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F22" s="25" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G22" s="25" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="H22" s="28" t="n">
-        <v>-12.05</v>
-      </c>
-      <c r="I22" s="28" t="n">
-        <v>-20.16</v>
-      </c>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="H22" s="25" t="n"/>
+      <c r="I22" s="25" t="n"/>
     </row>
     <row r="23" ht="18" customHeight="1">
       <c r="A23" s="26" t="inlineStr">
         <is>
-          <t>HJ중공업</t>
+          <t>전기차</t>
         </is>
       </c>
       <c r="B23" s="25" t="n">
@@ -3802,25 +3818,21 @@
       </c>
       <c r="F23" s="25" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G23" s="25" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="H23" s="28" t="n">
-        <v>-8.41</v>
-      </c>
-      <c r="I23" s="28" t="n">
-        <v>-14.6</v>
-      </c>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="H23" s="25" t="n"/>
+      <c r="I23" s="25" t="n"/>
     </row>
     <row r="24" ht="18" customHeight="1">
       <c r="A24" s="26" t="inlineStr">
         <is>
-          <t>노블엠앤비</t>
+          <t>클로봇</t>
         </is>
       </c>
       <c r="B24" s="25" t="n">
@@ -3837,200 +3849,200 @@
       </c>
       <c r="F24" s="25" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G24" s="25" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="H24" s="27" t="n">
-        <v>4.17</v>
-      </c>
-      <c r="I24" s="28" t="n">
-        <v>-93.92</v>
+        <v>9.380000000000001</v>
+      </c>
+      <c r="I24" s="29" t="n">
+        <v>-10.38</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
       <c r="A25" s="26" t="inlineStr">
         <is>
-          <t>미래에셋증권</t>
+          <t>HMM</t>
         </is>
       </c>
       <c r="B25" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C25" s="25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D25" s="25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E25" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F25" s="25" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G25" s="25" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="H25" s="28" t="n">
-        <v>-8.57</v>
-      </c>
-      <c r="I25" s="28" t="n">
-        <v>-17.84</v>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="H25" s="27" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="I25" s="29" t="n">
+        <v>-14.3</v>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
       <c r="A26" s="26" t="inlineStr">
         <is>
-          <t>센서뷰</t>
+          <t>ISC</t>
         </is>
       </c>
       <c r="B26" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C26" s="25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D26" s="25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E26" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F26" s="25" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G26" s="25" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="H26" s="28" t="n">
-        <v>-2.79</v>
-      </c>
-      <c r="I26" s="28" t="n">
-        <v>-15.56</v>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="H26" s="27" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="I26" s="29" t="n">
+        <v>-2.16</v>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
       <c r="A27" s="26" t="inlineStr">
         <is>
-          <t>셀트리온</t>
+          <t>LG이노텍</t>
         </is>
       </c>
       <c r="B27" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C27" s="25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D27" s="25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E27" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F27" s="25" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G27" s="25" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="H27" s="28" t="n">
-        <v>-4.75</v>
-      </c>
-      <c r="I27" s="28" t="n">
-        <v>-8.02</v>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="H27" s="29" t="n">
+        <v>-3.43</v>
+      </c>
+      <c r="I27" s="29" t="n">
+        <v>-23.32</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
       <c r="A28" s="26" t="inlineStr">
         <is>
-          <t>팬오션</t>
+          <t>경남제약</t>
         </is>
       </c>
       <c r="B28" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C28" s="25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D28" s="25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E28" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F28" s="25" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G28" s="25" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="H28" s="28" t="n">
-        <v>-4.98</v>
-      </c>
-      <c r="I28" s="28" t="n">
-        <v>-12.55</v>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="H28" s="29" t="n">
+        <v>-10.34</v>
+      </c>
+      <c r="I28" s="27" t="n">
+        <v>3.23</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
       <c r="A29" s="26" t="inlineStr">
         <is>
-          <t>한미반도체</t>
+          <t>국순당</t>
         </is>
       </c>
       <c r="B29" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C29" s="25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D29" s="25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E29" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F29" s="25" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G29" s="25" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="H29" s="28" t="n">
-        <v>-14.43</v>
-      </c>
-      <c r="I29" s="28" t="n">
-        <v>-21.46</v>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="H29" s="27" t="n">
+        <v>6.93</v>
+      </c>
+      <c r="I29" s="27" t="n">
+        <v>29.6</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
       <c r="A30" s="26" t="inlineStr">
         <is>
-          <t>AI반도체</t>
+          <t>기아</t>
         </is>
       </c>
       <c r="B30" s="25" t="n">
@@ -4047,21 +4059,25 @@
       </c>
       <c r="F30" s="25" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G30" s="25" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="H30" s="25" t="n"/>
-      <c r="I30" s="25" t="n"/>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="H30" s="27" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="I30" s="29" t="n">
+        <v>-16.48</v>
+      </c>
     </row>
     <row r="31" ht="18" customHeight="1">
       <c r="A31" s="26" t="inlineStr">
         <is>
-          <t>KBI메탈</t>
+          <t>넥써쓰</t>
         </is>
       </c>
       <c r="B31" s="25" t="n">
@@ -4078,25 +4094,25 @@
       </c>
       <c r="F31" s="25" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G31" s="25" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="H31" s="28" t="n">
-        <v>-0.57</v>
-      </c>
-      <c r="I31" s="28" t="n">
-        <v>-7.47</v>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="H31" s="29" t="n">
+        <v>-7.32</v>
+      </c>
+      <c r="I31" s="29" t="n">
+        <v>-38.17</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
       <c r="A32" s="26" t="inlineStr">
         <is>
-          <t>LB세미콘</t>
+          <t>대한항공</t>
         </is>
       </c>
       <c r="B32" s="25" t="n">
@@ -4113,25 +4129,25 @@
       </c>
       <c r="F32" s="25" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G32" s="25" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="H32" s="28" t="n">
-        <v>-12.95</v>
-      </c>
-      <c r="I32" s="28" t="n">
-        <v>-9.859999999999999</v>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="H32" s="27" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="I32" s="29" t="n">
+        <v>-5.03</v>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
       <c r="A33" s="26" t="inlineStr">
         <is>
-          <t>SK텔레콤</t>
+          <t>동양</t>
         </is>
       </c>
       <c r="B33" s="25" t="n">
@@ -4148,25 +4164,25 @@
       </c>
       <c r="F33" s="25" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G33" s="25" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="H33" s="28" t="n">
-        <v>-4.56</v>
-      </c>
-      <c r="I33" s="28" t="n">
-        <v>-10.19</v>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="H33" s="27" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="I33" s="29" t="n">
+        <v>-3.41</v>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
       <c r="A34" s="26" t="inlineStr">
         <is>
-          <t>경남제약</t>
+          <t>동양파일</t>
         </is>
       </c>
       <c r="B34" s="25" t="n">
@@ -4183,25 +4199,25 @@
       </c>
       <c r="F34" s="25" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G34" s="25" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="H34" s="27" t="n">
-        <v>29.75</v>
+        <v>29.92</v>
       </c>
       <c r="I34" s="27" t="n">
-        <v>18.19</v>
+        <v>27.24</v>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
       <c r="A35" s="26" t="inlineStr">
         <is>
-          <t>넥써쓰</t>
+          <t>미래나노텍</t>
         </is>
       </c>
       <c r="B35" s="25" t="n">
@@ -4218,25 +4234,25 @@
       </c>
       <c r="F35" s="25" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G35" s="25" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="H35" s="28" t="n">
-        <v>-11.22</v>
-      </c>
-      <c r="I35" s="28" t="n">
-        <v>-20.36</v>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="H35" s="29" t="n">
+        <v>-4.76</v>
+      </c>
+      <c r="I35" s="27" t="n">
+        <v>14.36</v>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
       <c r="A36" s="26" t="inlineStr">
         <is>
-          <t>두산로보틱스</t>
+          <t>성호전자</t>
         </is>
       </c>
       <c r="B36" s="25" t="n">
@@ -4253,25 +4269,25 @@
       </c>
       <c r="F36" s="25" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G36" s="25" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="H36" s="28" t="n">
-        <v>-11.55</v>
-      </c>
-      <c r="I36" s="28" t="n">
-        <v>-18.53</v>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="H36" s="29" t="n">
+        <v>-4.3</v>
+      </c>
+      <c r="I36" s="29" t="n">
+        <v>-29.63</v>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
       <c r="A37" s="26" t="inlineStr">
         <is>
-          <t>바이온</t>
+          <t>소룩스</t>
         </is>
       </c>
       <c r="B37" s="25" t="n">
@@ -4288,25 +4304,25 @@
       </c>
       <c r="F37" s="25" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G37" s="25" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="H37" s="27" t="n">
-        <v>68.42</v>
-      </c>
-      <c r="I37" s="28" t="n">
-        <v>-94.7</v>
+        <v>15.6</v>
+      </c>
+      <c r="I37" s="27" t="n">
+        <v>19.42</v>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
       <c r="A38" s="26" t="inlineStr">
         <is>
-          <t>방산</t>
+          <t>시너지이노베이션</t>
         </is>
       </c>
       <c r="B38" s="25" t="n">
@@ -4323,21 +4339,25 @@
       </c>
       <c r="F38" s="25" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G38" s="25" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="H38" s="25" t="n"/>
-      <c r="I38" s="25" t="n"/>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="H38" s="27" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="I38" s="29" t="n">
+        <v>-10.09</v>
+      </c>
     </row>
     <row r="39" ht="18" customHeight="1">
       <c r="A39" s="26" t="inlineStr">
         <is>
-          <t>성도이엔지</t>
+          <t>아모텍</t>
         </is>
       </c>
       <c r="B39" s="25" t="n">
@@ -4354,25 +4374,25 @@
       </c>
       <c r="F39" s="25" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G39" s="25" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="H39" s="28" t="n">
-        <v>-7.69</v>
-      </c>
-      <c r="I39" s="27" t="n">
-        <v>2.97</v>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="H39" s="29" t="n">
+        <v>-4.98</v>
+      </c>
+      <c r="I39" s="29" t="n">
+        <v>-21.8</v>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
       <c r="A40" s="26" t="inlineStr">
         <is>
-          <t>소룩스</t>
+          <t>아이엠</t>
         </is>
       </c>
       <c r="B40" s="25" t="n">
@@ -4389,25 +4409,25 @@
       </c>
       <c r="F40" s="25" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G40" s="25" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="H40" s="27" t="n">
-        <v>14.42</v>
-      </c>
-      <c r="I40" s="27" t="n">
-        <v>1.63</v>
+        <v>1.89</v>
+      </c>
+      <c r="I40" s="29" t="n">
+        <v>-86.36</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
       <c r="A41" s="26" t="inlineStr">
         <is>
-          <t>시너지이노베이션</t>
+          <t>에이프로젠</t>
         </is>
       </c>
       <c r="B41" s="25" t="n">
@@ -4424,25 +4444,25 @@
       </c>
       <c r="F41" s="25" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G41" s="25" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="H41" s="28" t="n">
-        <v>-8.279999999999999</v>
-      </c>
-      <c r="I41" s="28" t="n">
-        <v>-14.05</v>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="H41" s="29" t="n">
+        <v>-3.2</v>
+      </c>
+      <c r="I41" s="29" t="n">
+        <v>-21.94</v>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
       <c r="A42" s="26" t="inlineStr">
         <is>
-          <t>우성머티리얼스</t>
+          <t>오리엔트바이오</t>
         </is>
       </c>
       <c r="B42" s="25" t="n">
@@ -4459,25 +4479,25 @@
       </c>
       <c r="F42" s="25" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G42" s="25" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="H42" s="28" t="n">
-        <v>-1.12</v>
-      </c>
-      <c r="I42" s="28" t="n">
-        <v>-16.13</v>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="H42" s="27" t="n">
+        <v>10.97</v>
+      </c>
+      <c r="I42" s="29" t="n">
+        <v>-6.38</v>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1">
       <c r="A43" s="26" t="inlineStr">
         <is>
-          <t>진흥기업</t>
+          <t>원전</t>
         </is>
       </c>
       <c r="B43" s="25" t="n">
@@ -4494,25 +4514,21 @@
       </c>
       <c r="F43" s="25" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G43" s="25" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="H43" s="28" t="n">
-        <v>-7.5</v>
-      </c>
-      <c r="I43" s="28" t="n">
-        <v>-16.77</v>
-      </c>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="H43" s="25" t="n"/>
+      <c r="I43" s="25" t="n"/>
     </row>
     <row r="44" ht="18" customHeight="1">
       <c r="A44" s="26" t="inlineStr">
         <is>
-          <t>키스트론</t>
+          <t>조아제약</t>
         </is>
       </c>
       <c r="B44" s="25" t="n">
@@ -4529,25 +4545,25 @@
       </c>
       <c r="F44" s="25" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G44" s="25" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="H44" s="28" t="n">
-        <v>-10.97</v>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="H44" s="27" t="n">
+        <v>5.14</v>
       </c>
       <c r="I44" s="27" t="n">
-        <v>18.91</v>
+        <v>42.86</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
       <c r="A45" s="26" t="inlineStr">
         <is>
-          <t>태양광</t>
+          <t>진흥기업</t>
         </is>
       </c>
       <c r="B45" s="25" t="n">
@@ -4564,157 +4580,161 @@
       </c>
       <c r="F45" s="25" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G45" s="25" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="H45" s="25" t="n"/>
-      <c r="I45" s="25" t="n"/>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="H45" s="29" t="n">
+        <v>-2.03</v>
+      </c>
+      <c r="I45" s="29" t="n">
+        <v>-15.98</v>
+      </c>
     </row>
     <row r="46" ht="18" customHeight="1">
       <c r="A46" s="26" t="inlineStr">
         <is>
-          <t>NH투자증권</t>
+          <t>차AI헬스케어</t>
         </is>
       </c>
       <c r="B46" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C46" s="25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D46" s="25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E46" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F46" s="25" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G46" s="25" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="H46" s="28" t="n">
-        <v>-6.66</v>
-      </c>
-      <c r="I46" s="28" t="n">
-        <v>-12.48</v>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="H46" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I46" s="27" t="n">
+        <v>14.85</v>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
       <c r="A47" s="26" t="inlineStr">
         <is>
-          <t>삼성전기</t>
+          <t>철강</t>
         </is>
       </c>
       <c r="B47" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C47" s="25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D47" s="25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E47" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F47" s="25" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G47" s="25" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="H47" s="28" t="n">
-        <v>-10.68</v>
-      </c>
-      <c r="I47" s="28" t="n">
-        <v>-2.83</v>
-      </c>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="H47" s="25" t="n"/>
+      <c r="I47" s="25" t="n"/>
     </row>
     <row r="48" ht="18" customHeight="1">
       <c r="A48" s="26" t="inlineStr">
         <is>
-          <t>스테이블코인</t>
+          <t>테스</t>
         </is>
       </c>
       <c r="B48" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C48" s="25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D48" s="25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E48" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F48" s="25" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G48" s="25" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="H48" s="25" t="n"/>
-      <c r="I48" s="25" t="n"/>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="H48" s="27" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="I48" s="29" t="n">
+        <v>-4.07</v>
+      </c>
     </row>
     <row r="49" ht="18" customHeight="1">
       <c r="A49" s="26" t="inlineStr">
         <is>
-          <t>에이테크솔루션</t>
+          <t>해태제과식품</t>
         </is>
       </c>
       <c r="B49" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C49" s="25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D49" s="25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E49" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F49" s="25" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G49" s="25" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="H49" s="28" t="n">
-        <v>-4.39</v>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="H49" s="29" t="n">
+        <v>-3.38</v>
       </c>
       <c r="I49" s="27" t="n">
-        <v>15.25</v>
+        <v>2.39</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
       <c r="A50" s="26" t="inlineStr">
         <is>
-          <t>원전</t>
+          <t>보해양조</t>
         </is>
       </c>
       <c r="B50" s="25" t="n">
@@ -4731,21 +4751,25 @@
       </c>
       <c r="F50" s="25" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G50" s="25" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="H50" s="25" t="n"/>
-      <c r="I50" s="25" t="n"/>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="H50" s="27" t="n">
+        <v>29.93</v>
+      </c>
+      <c r="I50" s="27" t="n">
+        <v>177.58</v>
+      </c>
     </row>
     <row r="51" ht="18" customHeight="1">
       <c r="A51" s="26" t="inlineStr">
         <is>
-          <t>카카오</t>
+          <t>부국철강</t>
         </is>
       </c>
       <c r="B51" s="25" t="n">
@@ -4762,25 +4786,25 @@
       </c>
       <c r="F51" s="25" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G51" s="25" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="H51" s="28" t="n">
-        <v>-6.93</v>
-      </c>
-      <c r="I51" s="28" t="n">
-        <v>-15.33</v>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="H51" s="29" t="n">
+        <v>-7.99</v>
+      </c>
+      <c r="I51" s="27" t="n">
+        <v>45.78</v>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1">
       <c r="A52" s="26" t="inlineStr">
         <is>
-          <t>케이뱅크</t>
+          <t>키스트론</t>
         </is>
       </c>
       <c r="B52" s="25" t="n">
@@ -4797,19 +4821,19 @@
       </c>
       <c r="F52" s="25" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G52" s="25" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="H52" s="28" t="n">
-        <v>-3.66</v>
-      </c>
-      <c r="I52" s="28" t="n">
-        <v>-12.06</v>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="H52" s="27" t="n">
+        <v>4.23</v>
+      </c>
+      <c r="I52" s="27" t="n">
+        <v>23.53</v>
       </c>
     </row>
   </sheetData>
@@ -4893,19 +4917,19 @@
         <v>1</v>
       </c>
       <c r="C3" s="36" t="n">
-        <v>114</v>
+        <v>100</v>
       </c>
       <c r="D3" s="36" t="n">
-        <v>114</v>
+        <v>100</v>
       </c>
       <c r="E3" s="36" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="F3" s="37" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G3" s="37" t="inlineStr">
@@ -4924,19 +4948,19 @@
         <v>1</v>
       </c>
       <c r="C4" s="36" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="D4" s="36" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="E4" s="36" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="F4" s="37" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G4" s="37" t="inlineStr">
@@ -4948,26 +4972,26 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="35" t="inlineStr">
         <is>
-          <t>AI반도체</t>
+          <t>전기차</t>
         </is>
       </c>
       <c r="B5" s="36" t="n">
         <v>1</v>
       </c>
       <c r="C5" s="36" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D5" s="36" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E5" s="36" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="F5" s="37" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G5" s="37" t="inlineStr">
@@ -4979,26 +5003,26 @@
     <row r="6" ht="18" customHeight="1">
       <c r="A6" s="35" t="inlineStr">
         <is>
-          <t>전기차</t>
+          <t>원전</t>
         </is>
       </c>
       <c r="B6" s="36" t="n">
         <v>1</v>
       </c>
       <c r="C6" s="36" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D6" s="36" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E6" s="36" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="F6" s="37" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G6" s="37" t="inlineStr">
@@ -5010,26 +5034,26 @@
     <row r="7" ht="18" customHeight="1">
       <c r="A7" s="35" t="inlineStr">
         <is>
-          <t>방산</t>
+          <t>로봇</t>
         </is>
       </c>
       <c r="B7" s="36" t="n">
         <v>1</v>
       </c>
       <c r="C7" s="36" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="D7" s="36" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="E7" s="36" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="F7" s="37" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G7" s="37" t="inlineStr">
@@ -5041,26 +5065,26 @@
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="35" t="inlineStr">
         <is>
-          <t>원전</t>
+          <t>철강</t>
         </is>
       </c>
       <c r="B8" s="36" t="n">
         <v>1</v>
       </c>
       <c r="C8" s="36" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D8" s="36" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E8" s="36" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="F8" s="37" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G8" s="37" t="inlineStr">
@@ -5072,26 +5096,26 @@
     <row r="9" ht="18" customHeight="1">
       <c r="A9" s="35" t="inlineStr">
         <is>
-          <t>로봇</t>
+          <t>제약</t>
         </is>
       </c>
       <c r="B9" s="36" t="n">
         <v>1</v>
       </c>
       <c r="C9" s="36" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D9" s="36" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E9" s="36" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="F9" s="37" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G9" s="37" t="inlineStr">
@@ -5103,26 +5127,26 @@
     <row r="10" ht="18" customHeight="1">
       <c r="A10" s="35" t="inlineStr">
         <is>
-          <t>태양광</t>
+          <t>인공지능</t>
         </is>
       </c>
       <c r="B10" s="36" t="n">
         <v>1</v>
       </c>
       <c r="C10" s="36" t="n">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="D10" s="36" t="n">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="E10" s="36" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="F10" s="37" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G10" s="37" t="inlineStr">
@@ -5132,102 +5156,90 @@
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="35" t="inlineStr">
-        <is>
-          <t>철강</t>
-        </is>
-      </c>
-      <c r="B11" s="36" t="n">
-        <v>1</v>
-      </c>
-      <c r="C11" s="36" t="n">
-        <v>5</v>
-      </c>
-      <c r="D11" s="36" t="n">
-        <v>5</v>
-      </c>
-      <c r="E11" s="36" t="inlineStr">
-        <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="F11" s="37" t="inlineStr">
-        <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="G11" s="37" t="inlineStr">
-        <is>
-          <t>⚡ 관심</t>
-        </is>
-      </c>
+      <c r="A11" s="26" t="inlineStr">
+        <is>
+          <t>이차전지</t>
+        </is>
+      </c>
+      <c r="B11" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F11" s="28" t="inlineStr">
+        <is>
+          <t>감지 없음</t>
+        </is>
+      </c>
+      <c r="G11" s="28" t="inlineStr"/>
     </row>
     <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="35" t="inlineStr">
-        <is>
-          <t>제약</t>
-        </is>
-      </c>
-      <c r="B12" s="36" t="n">
-        <v>1</v>
-      </c>
-      <c r="C12" s="36" t="n">
-        <v>9</v>
-      </c>
-      <c r="D12" s="36" t="n">
-        <v>9</v>
-      </c>
-      <c r="E12" s="36" t="inlineStr">
-        <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="F12" s="37" t="inlineStr">
-        <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="G12" s="37" t="inlineStr">
-        <is>
-          <t>⚡ 관심</t>
-        </is>
-      </c>
+      <c r="A12" s="26" t="inlineStr">
+        <is>
+          <t>AI반도체</t>
+        </is>
+      </c>
+      <c r="B12" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F12" s="28" t="inlineStr">
+        <is>
+          <t>감지 없음</t>
+        </is>
+      </c>
+      <c r="G12" s="28" t="inlineStr"/>
     </row>
     <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="35" t="inlineStr">
-        <is>
-          <t>인공지능</t>
-        </is>
-      </c>
-      <c r="B13" s="36" t="n">
-        <v>1</v>
-      </c>
-      <c r="C13" s="36" t="n">
-        <v>15</v>
-      </c>
-      <c r="D13" s="36" t="n">
-        <v>15</v>
-      </c>
-      <c r="E13" s="36" t="inlineStr">
-        <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="F13" s="37" t="inlineStr">
-        <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="G13" s="37" t="inlineStr">
-        <is>
-          <t>⚡ 관심</t>
-        </is>
-      </c>
+      <c r="A13" s="26" t="inlineStr">
+        <is>
+          <t>방산</t>
+        </is>
+      </c>
+      <c r="B13" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F13" s="28" t="inlineStr">
+        <is>
+          <t>감지 없음</t>
+        </is>
+      </c>
+      <c r="G13" s="28" t="inlineStr"/>
     </row>
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="26" t="inlineStr">
         <is>
-          <t>이차전지</t>
+          <t>수소</t>
         </is>
       </c>
       <c r="B14" s="25" t="n">
@@ -5244,17 +5256,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F14" s="29" t="inlineStr">
+      <c r="F14" s="28" t="inlineStr">
         <is>
           <t>감지 없음</t>
         </is>
       </c>
-      <c r="G14" s="29" t="inlineStr"/>
+      <c r="G14" s="28" t="inlineStr"/>
     </row>
     <row r="15" ht="18" customHeight="1">
       <c r="A15" s="26" t="inlineStr">
         <is>
-          <t>수소</t>
+          <t>태양광</t>
         </is>
       </c>
       <c r="B15" s="25" t="n">
@@ -5271,12 +5283,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F15" s="29" t="inlineStr">
+      <c r="F15" s="28" t="inlineStr">
         <is>
           <t>감지 없음</t>
         </is>
       </c>
-      <c r="G15" s="29" t="inlineStr"/>
+      <c r="G15" s="28" t="inlineStr"/>
     </row>
     <row r="16" ht="18" customHeight="1">
       <c r="A16" s="26" t="inlineStr">
@@ -5298,12 +5310,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F16" s="29" t="inlineStr">
+      <c r="F16" s="28" t="inlineStr">
         <is>
           <t>감지 없음</t>
         </is>
       </c>
-      <c r="G16" s="29" t="inlineStr"/>
+      <c r="G16" s="28" t="inlineStr"/>
     </row>
     <row r="17" ht="18" customHeight="1">
       <c r="A17" s="26" t="inlineStr">
@@ -5325,12 +5337,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F17" s="29" t="inlineStr">
+      <c r="F17" s="28" t="inlineStr">
         <is>
           <t>감지 없음</t>
         </is>
       </c>
-      <c r="G17" s="29" t="inlineStr"/>
+      <c r="G17" s="28" t="inlineStr"/>
     </row>
     <row r="18" ht="18" customHeight="1">
       <c r="A18" s="26" t="inlineStr">
@@ -5352,12 +5364,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F18" s="29" t="inlineStr">
+      <c r="F18" s="28" t="inlineStr">
         <is>
           <t>감지 없음</t>
         </is>
       </c>
-      <c r="G18" s="29" t="inlineStr"/>
+      <c r="G18" s="28" t="inlineStr"/>
     </row>
     <row r="19" ht="18" customHeight="1">
       <c r="A19" s="26" t="inlineStr">
@@ -5379,12 +5391,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F19" s="29" t="inlineStr">
+      <c r="F19" s="28" t="inlineStr">
         <is>
           <t>감지 없음</t>
         </is>
       </c>
-      <c r="G19" s="29" t="inlineStr"/>
+      <c r="G19" s="28" t="inlineStr"/>
     </row>
     <row r="20" ht="18" customHeight="1">
       <c r="A20" s="26" t="inlineStr">
@@ -5406,12 +5418,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F20" s="29" t="inlineStr">
+      <c r="F20" s="28" t="inlineStr">
         <is>
           <t>감지 없음</t>
         </is>
       </c>
-      <c r="G20" s="29" t="inlineStr"/>
+      <c r="G20" s="28" t="inlineStr"/>
     </row>
     <row r="21" ht="18" customHeight="1">
       <c r="A21" s="26" t="inlineStr">
@@ -5433,12 +5445,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F21" s="29" t="inlineStr">
+      <c r="F21" s="28" t="inlineStr">
         <is>
           <t>감지 없음</t>
         </is>
       </c>
-      <c r="G21" s="29" t="inlineStr"/>
+      <c r="G21" s="28" t="inlineStr"/>
     </row>
     <row r="22" ht="18" customHeight="1">
       <c r="A22" s="26" t="inlineStr">
@@ -5460,12 +5472,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F22" s="29" t="inlineStr">
+      <c r="F22" s="28" t="inlineStr">
         <is>
           <t>감지 없음</t>
         </is>
       </c>
-      <c r="G22" s="29" t="inlineStr"/>
+      <c r="G22" s="28" t="inlineStr"/>
     </row>
     <row r="23" ht="18" customHeight="1">
       <c r="A23" s="26" t="inlineStr">
@@ -5487,12 +5499,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F23" s="29" t="inlineStr">
+      <c r="F23" s="28" t="inlineStr">
         <is>
           <t>감지 없음</t>
         </is>
       </c>
-      <c r="G23" s="29" t="inlineStr"/>
+      <c r="G23" s="28" t="inlineStr"/>
     </row>
     <row r="24" ht="18" customHeight="1">
       <c r="A24" s="26" t="inlineStr">
@@ -5514,12 +5526,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F24" s="29" t="inlineStr">
+      <c r="F24" s="28" t="inlineStr">
         <is>
           <t>감지 없음</t>
         </is>
       </c>
-      <c r="G24" s="29" t="inlineStr"/>
+      <c r="G24" s="28" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/trend/stock_trend_history.xlsx
+++ b/trend/stock_trend_history.xlsx
@@ -261,11 +261,11 @@
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -273,13 +273,13 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -694,7 +694,7 @@
     <row r="1" ht="36" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>📊 주식 트렌드 조기 감지 대시보드   |   최종 업데이트: 2026-06-25 06:54</t>
+          <t>📊 주식 트렌드 조기 감지 대시보드   |   최종 업데이트: 2026-06-26 06:54</t>
         </is>
       </c>
     </row>
@@ -708,7 +708,7 @@
       </c>
       <c r="E3" s="3" t="n"/>
       <c r="G3" s="5" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="H3" s="3" t="n"/>
       <c r="J3" s="6" t="n">
@@ -787,21 +787,21 @@
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="11" t="inlineStr">
         <is>
-          <t>⚡ 최신(2026-06-25) 상위: 반도체  점수 100.0점</t>
+          <t>⚡ 최신(2026-06-26) 상위: 반도체  점수 73.0점</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1">
       <c r="A11" s="12" t="inlineStr">
         <is>
-          <t>⚡ 최신(2026-06-25) 상위: SK하이닉스  점수 37.0점</t>
+          <t>⚡ 최신(2026-06-26) 상위: SK  점수 67.0점</t>
         </is>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1">
       <c r="A12" s="11" t="inlineStr">
         <is>
-          <t>⚡ 최신(2026-06-25) 상위: 삼성전자  점수 29.0점</t>
+          <t>⚡ 최신(2026-06-26) 상위: SK하이닉스  점수 41.0점</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B14" s="15" t="n">
@@ -928,10 +928,10 @@
         </is>
       </c>
       <c r="D14" s="15" t="n">
-        <v>100</v>
+        <v>73</v>
       </c>
       <c r="E14" s="15" t="n">
-        <v>100</v>
+        <v>73</v>
       </c>
       <c r="F14" s="15" t="n">
         <v>0</v>
@@ -947,7 +947,7 @@
       </c>
       <c r="J14" s="17" t="inlineStr">
         <is>
-          <t>매일경제 헤드라인 언급 / 네이버뉴스 기사 언급 / 매일경제 헤드라인 언급 / 네이버뉴스 기사 언급 / 매일경제 헤드라인 언급</t>
+          <t>매일경제 기사 언급 / 매일경제 기사 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 헤드라인 언급 / 매일경제 헤드라인 언급</t>
         </is>
       </c>
       <c r="K14" s="17" t="inlineStr">
@@ -959,7 +959,7 @@
     <row r="15" ht="18" customHeight="1">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B15" s="15" t="n">
@@ -967,14 +967,14 @@
       </c>
       <c r="C15" s="16" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>SK</t>
         </is>
       </c>
       <c r="D15" s="15" t="n">
-        <v>37</v>
+        <v>67</v>
       </c>
       <c r="E15" s="15" t="n">
-        <v>37</v>
+        <v>67</v>
       </c>
       <c r="F15" s="15" t="n">
         <v>0</v>
@@ -983,26 +983,26 @@
         <v>0</v>
       </c>
       <c r="H15" s="18" t="n">
-        <v>0.98</v>
+        <v>20.51</v>
       </c>
       <c r="I15" s="18" t="n">
-        <v>2.34</v>
+        <v>24.89</v>
       </c>
       <c r="J15" s="17" t="inlineStr">
         <is>
-          <t>중요공시 1건 / 매일경제 기사 언급 / 매일경제 기사 언급 / 네이버뉴스 헤드라인 언급 / 네이버뉴스 기사 언급</t>
+          <t>Google 급상승 검색어 등장 (KR) / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 한국경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
         </is>
       </c>
       <c r="K15" s="17" t="inlineStr">
         <is>
-          <t>네이버, 공시</t>
+          <t>네이버, Google</t>
         </is>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
       <c r="A16" s="15" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B16" s="15" t="n">
@@ -1010,14 +1010,14 @@
       </c>
       <c r="C16" s="16" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="D16" s="15" t="n">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="E16" s="15" t="n">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="F16" s="15" t="n">
         <v>0</v>
@@ -1026,26 +1026,26 @@
         <v>0</v>
       </c>
       <c r="H16" s="18" t="n">
-        <v>9.84</v>
-      </c>
-      <c r="I16" s="19" t="n">
-        <v>-1.73</v>
+        <v>13.06</v>
+      </c>
+      <c r="I16" s="18" t="n">
+        <v>8.640000000000001</v>
       </c>
       <c r="J16" s="17" t="inlineStr">
         <is>
-          <t>매일경제 기사 언급 / 매일경제 기사 언급 / 매일경제 기사 언급 / 네이버뉴스 헤드라인 언급 / 네이버뉴스 기사 언급</t>
+          <t>중요공시 1건 / Google 급상승 검색어 등장 (KR) / 매일경제 헤드라인 언급 / 한국경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
         </is>
       </c>
       <c r="K16" s="17" t="inlineStr">
         <is>
-          <t>네이버</t>
+          <t>공시, Google, 네이버</t>
         </is>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B17" s="15" t="n">
@@ -1053,14 +1053,14 @@
       </c>
       <c r="C17" s="16" t="inlineStr">
         <is>
-          <t>인공지능</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="D17" s="15" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E17" s="15" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F17" s="15" t="n">
         <v>0</v>
@@ -1068,15 +1068,15 @@
       <c r="G17" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="H17" s="15" t="n">
-        <v/>
-      </c>
-      <c r="I17" s="15" t="n">
-        <v/>
+      <c r="H17" s="18" t="n">
+        <v>5.29</v>
+      </c>
+      <c r="I17" s="19" t="n">
+        <v>-1.1</v>
       </c>
       <c r="J17" s="17" t="inlineStr">
         <is>
-          <t>매일경제 기사 언급 / 네이버뉴스 기사 언급 / 매일경제 기사 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 기사 언급</t>
+          <t>네이버뉴스 기사 언급 / 매일경제 기사 언급 / 한국경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급</t>
         </is>
       </c>
       <c r="K17" s="17" t="inlineStr">
@@ -1088,7 +1088,7 @@
     <row r="18" ht="18" customHeight="1">
       <c r="A18" s="15" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B18" s="15" t="n">
@@ -1119,7 +1119,7 @@
       </c>
       <c r="J18" s="17" t="inlineStr">
         <is>
-          <t>한국경제 헤드라인 언급 / 네이버뉴스 헤드라인 언급 / 네이버뉴스 기사 언급 / 한국경제 헤드라인 언급 / 매일경제 기사 언급</t>
+          <t>네이버뉴스 헤드라인 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 헤드라인 언급 / 한국경제 헤드라인 언급 / 네이버뉴스 헤드라인 언급</t>
         </is>
       </c>
       <c r="K18" s="17" t="inlineStr">
@@ -1131,7 +1131,7 @@
     <row r="19" ht="18" customHeight="1">
       <c r="A19" s="15" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B19" s="15" t="n">
@@ -1139,7 +1139,7 @@
       </c>
       <c r="C19" s="16" t="inlineStr">
         <is>
-          <t>LG</t>
+          <t>인공지능</t>
         </is>
       </c>
       <c r="D19" s="15" t="n">
@@ -1154,25 +1154,27 @@
       <c r="G19" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="H19" s="18" t="n">
-        <v>0.61</v>
-      </c>
-      <c r="I19" s="19" t="n">
-        <v>-11.82</v>
+      <c r="H19" s="15" t="n">
+        <v/>
+      </c>
+      <c r="I19" s="15" t="n">
+        <v/>
       </c>
       <c r="J19" s="17" t="inlineStr">
         <is>
-          <t>매일경제 헤드라인 언급 / 한국경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 한국경제 헤드라인 언급 / 매일경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K19" s="17" t="n">
-        <v/>
+          <t>매일경제 기사 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 기사 언급 / 매일경제 기사 언급 / 매일경제 기사 언급</t>
+        </is>
+      </c>
+      <c r="K19" s="17" t="inlineStr">
+        <is>
+          <t>네이버</t>
+        </is>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
       <c r="A20" s="15" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B20" s="15" t="n">
@@ -1180,14 +1182,14 @@
       </c>
       <c r="C20" s="16" t="inlineStr">
         <is>
-          <t>로봇</t>
+          <t>카카오</t>
         </is>
       </c>
       <c r="D20" s="15" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E20" s="15" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F20" s="15" t="n">
         <v>0</v>
@@ -1195,27 +1197,25 @@
       <c r="G20" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="H20" s="15" t="n">
+      <c r="H20" s="18" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="I20" s="19" t="n">
+        <v>-12.85</v>
+      </c>
+      <c r="J20" s="17" t="inlineStr">
+        <is>
+          <t>매일경제 기사 언급 / 한국경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 기사 언급 / 한국경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K20" s="17" t="n">
         <v/>
-      </c>
-      <c r="I20" s="15" t="n">
-        <v/>
-      </c>
-      <c r="J20" s="17" t="inlineStr">
-        <is>
-          <t>매일경제 헤드라인 언급 / 한국경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 네이버뉴스 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K20" s="17" t="inlineStr">
-        <is>
-          <t>네이버</t>
-        </is>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
       <c r="A21" s="15" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B21" s="15" t="n">
@@ -1223,42 +1223,42 @@
       </c>
       <c r="C21" s="16" t="inlineStr">
         <is>
-          <t>에이팩트</t>
+          <t>현대차</t>
         </is>
       </c>
       <c r="D21" s="15" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E21" s="15" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="F21" s="15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G21" s="15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H21" s="19" t="n">
-        <v>-5.97</v>
+        <v>-1.18</v>
       </c>
       <c r="I21" s="19" t="n">
-        <v>-26.41</v>
+        <v>-16.31</v>
       </c>
       <c r="J21" s="17" t="inlineStr">
         <is>
-          <t>중요공시 4건 / 중요공시 3일 +100% / 중요공시 7일 +100%</t>
+          <t>매일경제 기사 언급 / 매일경제 헤드라인 언급 / 한국경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 네이버뉴스 기사 언급</t>
         </is>
       </c>
       <c r="K21" s="17" t="inlineStr">
         <is>
-          <t>공시</t>
+          <t>네이버</t>
         </is>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
       <c r="A22" s="15" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B22" s="15" t="n">
@@ -1266,14 +1266,14 @@
       </c>
       <c r="C22" s="16" t="inlineStr">
         <is>
-          <t>제약</t>
+          <t>로봇</t>
         </is>
       </c>
       <c r="D22" s="15" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E22" s="15" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F22" s="15" t="n">
         <v>0</v>
@@ -1289,19 +1289,17 @@
       </c>
       <c r="J22" s="17" t="inlineStr">
         <is>
-          <t>네이버뉴스 기사 언급 / 네이버뉴스 헤드라인 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 기사 언급 / 매일경제 기사 언급</t>
-        </is>
-      </c>
-      <c r="K22" s="17" t="inlineStr">
-        <is>
-          <t>네이버</t>
-        </is>
+          <t>매일경제 헤드라인 언급 / 한국경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 한국경제 헤드라인 언급 / 매일경제 기사 언급</t>
+        </is>
+      </c>
+      <c r="K22" s="17" t="n">
+        <v/>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B23" s="15" t="n">
@@ -1309,14 +1307,14 @@
       </c>
       <c r="C23" s="16" t="inlineStr">
         <is>
-          <t>현대차</t>
+          <t>LG</t>
         </is>
       </c>
       <c r="D23" s="15" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E23" s="15" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F23" s="15" t="n">
         <v>0</v>
@@ -1324,15 +1322,15 @@
       <c r="G23" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="H23" s="19" t="n">
-        <v>-0.39</v>
+      <c r="H23" s="18" t="n">
+        <v>0.2</v>
       </c>
       <c r="I23" s="19" t="n">
-        <v>-17.64</v>
+        <v>-9.550000000000001</v>
       </c>
       <c r="J23" s="17" t="inlineStr">
         <is>
-          <t>매일경제 헤드라인 언급 / 매일경제 기사 언급 / 매일경제 헤드라인 언급 / 매일경제 기사 언급 / 매일경제 기사 언급</t>
+          <t>매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급</t>
         </is>
       </c>
       <c r="K23" s="17" t="n">
@@ -1342,7 +1340,7 @@
     <row r="24" ht="18" customHeight="1">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B24" s="15" t="n">
@@ -1350,429 +1348,423 @@
       </c>
       <c r="C24" s="16" t="inlineStr">
         <is>
-          <t>에이프릴바이오</t>
+          <t>카카오뱅크</t>
         </is>
       </c>
       <c r="D24" s="15" t="n">
+        <v>9</v>
+      </c>
+      <c r="E24" s="15" t="n">
+        <v>9</v>
+      </c>
+      <c r="F24" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="I24" s="19" t="n">
+        <v>-10.7</v>
+      </c>
+      <c r="J24" s="17" t="inlineStr">
+        <is>
+          <t>중요공시 1건 / 한국경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 기사 언급 / 매일경제 기사 언급</t>
+        </is>
+      </c>
+      <c r="K24" s="17" t="inlineStr">
+        <is>
+          <t>공시</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="18" customHeight="1">
+      <c r="A25" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="B25" s="15" t="n">
+        <v>12</v>
+      </c>
+      <c r="C25" s="16" t="inlineStr">
+        <is>
+          <t>전기차</t>
+        </is>
+      </c>
+      <c r="D25" s="15" t="n">
+        <v>9</v>
+      </c>
+      <c r="E25" s="15" t="n">
+        <v>9</v>
+      </c>
+      <c r="F25" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" s="15" t="n">
+        <v/>
+      </c>
+      <c r="I25" s="15" t="n">
+        <v/>
+      </c>
+      <c r="J25" s="17" t="inlineStr">
+        <is>
+          <t>네이버뉴스 헤드라인 언급 / 네이버뉴스 헤드라인 언급 / 매일경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K25" s="17" t="inlineStr">
+        <is>
+          <t>네이버</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="18" customHeight="1">
+      <c r="A26" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="B26" s="15" t="n">
+        <v>13</v>
+      </c>
+      <c r="C26" s="16" t="inlineStr">
+        <is>
+          <t>GS</t>
+        </is>
+      </c>
+      <c r="D26" s="15" t="n">
+        <v>9</v>
+      </c>
+      <c r="E26" s="15" t="n">
+        <v>9</v>
+      </c>
+      <c r="F26" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" s="19" t="n">
+        <v>-2.87</v>
+      </c>
+      <c r="I26" s="19" t="n">
+        <v>-9.960000000000001</v>
+      </c>
+      <c r="J26" s="17" t="inlineStr">
+        <is>
+          <t>한국경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K26" s="17" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="27" ht="18" customHeight="1">
+      <c r="A27" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="B27" s="15" t="n">
+        <v>14</v>
+      </c>
+      <c r="C27" s="16" t="inlineStr">
+        <is>
+          <t>대우건설</t>
+        </is>
+      </c>
+      <c r="D27" s="15" t="n">
+        <v>8</v>
+      </c>
+      <c r="E27" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="F27" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="G27" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="H27" s="18" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="I27" s="19" t="n">
+        <v>-13.46</v>
+      </c>
+      <c r="J27" s="17" t="inlineStr">
+        <is>
+          <t>중요공시 3건 / 중요공시 3일 +200% / 중요공시 7일 +200%</t>
+        </is>
+      </c>
+      <c r="K27" s="17" t="inlineStr">
+        <is>
+          <t>공시</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="18" customHeight="1">
+      <c r="A28" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="B28" s="15" t="n">
+        <v>15</v>
+      </c>
+      <c r="C28" s="16" t="inlineStr">
+        <is>
+          <t>에이팩트</t>
+        </is>
+      </c>
+      <c r="D28" s="15" t="n">
+        <v>8</v>
+      </c>
+      <c r="E28" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="F28" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="G28" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="H28" s="19" t="n">
+        <v>-4.27</v>
+      </c>
+      <c r="I28" s="19" t="n">
+        <v>-27.86</v>
+      </c>
+      <c r="J28" s="17" t="inlineStr">
+        <is>
+          <t>중요공시 3건 / 중요공시 3일 +50% / 중요공시 7일 +50%</t>
+        </is>
+      </c>
+      <c r="K28" s="17" t="inlineStr">
+        <is>
+          <t>공시</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="18" customHeight="1">
+      <c r="A29" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="B29" s="15" t="n">
+        <v>16</v>
+      </c>
+      <c r="C29" s="16" t="inlineStr">
+        <is>
+          <t>대한항공</t>
+        </is>
+      </c>
+      <c r="D29" s="15" t="n">
         <v>7</v>
       </c>
-      <c r="E24" s="15" t="n">
+      <c r="E29" s="15" t="n">
         <v>7</v>
       </c>
-      <c r="F24" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" s="18" t="n">
-        <v>15.57</v>
-      </c>
-      <c r="I24" s="19" t="n">
-        <v>-14.62</v>
-      </c>
-      <c r="J24" s="17" t="inlineStr">
-        <is>
-          <t>중요공시 1건 / 한국경제 헤드라인 언급 / 네이버뉴스 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K24" s="17" t="inlineStr">
-        <is>
-          <t>네이버, 공시</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="18" customHeight="1">
-      <c r="A25" s="20" t="inlineStr">
-        <is>
-          <t>2026-06-25</t>
-        </is>
-      </c>
-      <c r="B25" s="20" t="n">
-        <v>12</v>
-      </c>
-      <c r="C25" s="21" t="inlineStr">
-        <is>
-          <t>프로브잇</t>
-        </is>
-      </c>
-      <c r="D25" s="20" t="n">
-        <v>6</v>
-      </c>
-      <c r="E25" s="20" t="n">
-        <v>6</v>
-      </c>
-      <c r="F25" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G25" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H25" s="22" t="n">
-        <v>-46</v>
-      </c>
-      <c r="I25" s="22" t="n">
-        <v>-95.59</v>
-      </c>
-      <c r="J25" s="23" t="inlineStr">
-        <is>
-          <t>네이버 검색 당일 +1416% / 중요공시 3건</t>
-        </is>
-      </c>
-      <c r="K25" s="23" t="inlineStr">
-        <is>
-          <t>네이버, 공시</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="18" customHeight="1">
-      <c r="A26" s="20" t="inlineStr">
-        <is>
-          <t>2026-06-25</t>
-        </is>
-      </c>
-      <c r="B26" s="20" t="n">
-        <v>13</v>
-      </c>
-      <c r="C26" s="21" t="inlineStr">
-        <is>
-          <t>비투엔</t>
-        </is>
-      </c>
-      <c r="D26" s="20" t="n">
-        <v>6</v>
-      </c>
-      <c r="E26" s="20" t="n">
-        <v>3</v>
-      </c>
-      <c r="F26" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G26" s="20" t="n">
-        <v>3</v>
-      </c>
-      <c r="H26" s="24" t="n">
-        <v>15.89</v>
-      </c>
-      <c r="I26" s="24" t="n">
-        <v>5.85</v>
-      </c>
-      <c r="J26" s="23" t="inlineStr">
-        <is>
-          <t>중요공시 5건 / 중요공시 7일 +400%</t>
-        </is>
-      </c>
-      <c r="K26" s="23" t="inlineStr">
+      <c r="F29" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" s="18" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="I29" s="18" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="J29" s="17" t="inlineStr">
+        <is>
+          <t>중요공시 1건 / 매일경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K29" s="17" t="inlineStr">
         <is>
           <t>공시</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="18" customHeight="1">
-      <c r="A27" s="20" t="inlineStr">
-        <is>
-          <t>2026-06-25</t>
-        </is>
-      </c>
-      <c r="B27" s="20" t="n">
-        <v>14</v>
-      </c>
-      <c r="C27" s="21" t="inlineStr">
-        <is>
-          <t>스피어</t>
-        </is>
-      </c>
-      <c r="D27" s="20" t="n">
-        <v>5</v>
-      </c>
-      <c r="E27" s="20" t="n">
-        <v>3</v>
-      </c>
-      <c r="F27" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="G27" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H27" s="24" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="I27" s="22" t="n">
-        <v>-28.67</v>
-      </c>
-      <c r="J27" s="23" t="inlineStr">
-        <is>
-          <t>중요공시 4건 / 중요공시 3일 +100%</t>
-        </is>
-      </c>
-      <c r="K27" s="23" t="inlineStr">
-        <is>
-          <t>공시</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="18" customHeight="1">
-      <c r="A28" s="20" t="inlineStr">
-        <is>
-          <t>2026-06-25</t>
-        </is>
-      </c>
-      <c r="B28" s="20" t="n">
-        <v>15</v>
-      </c>
-      <c r="C28" s="21" t="inlineStr">
-        <is>
-          <t>센서뷰</t>
-        </is>
-      </c>
-      <c r="D28" s="20" t="n">
-        <v>5</v>
-      </c>
-      <c r="E28" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="F28" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G28" s="20" t="n">
-        <v>3</v>
-      </c>
-      <c r="H28" s="24" t="n">
-        <v>0.96</v>
-      </c>
-      <c r="I28" s="22" t="n">
-        <v>-10.4</v>
-      </c>
-      <c r="J28" s="23" t="inlineStr">
-        <is>
-          <t>중요공시 2건 / 중요공시 7일 +100% / 매일경제 기사 언급</t>
-        </is>
-      </c>
-      <c r="K28" s="23" t="inlineStr">
-        <is>
-          <t>공시</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="18" customHeight="1">
-      <c r="A29" s="20" t="inlineStr">
-        <is>
-          <t>2026-06-25</t>
-        </is>
-      </c>
-      <c r="B29" s="20" t="n">
-        <v>16</v>
-      </c>
-      <c r="C29" s="21" t="inlineStr">
-        <is>
-          <t>노블엠앤비</t>
-        </is>
-      </c>
-      <c r="D29" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="E29" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="F29" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G29" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H29" s="22" t="n">
-        <v>-16</v>
-      </c>
-      <c r="I29" s="22" t="n">
-        <v>-94.89</v>
-      </c>
-      <c r="J29" s="23" t="inlineStr">
-        <is>
-          <t>네이버 검색 당일 +317% / 중요공시 2건</t>
-        </is>
-      </c>
-      <c r="K29" s="23" t="inlineStr">
-        <is>
-          <t>네이버, 공시</t>
-        </is>
-      </c>
-    </row>
     <row r="30" ht="18" customHeight="1">
-      <c r="A30" s="20" t="inlineStr">
-        <is>
-          <t>2026-06-25</t>
-        </is>
-      </c>
-      <c r="B30" s="20" t="n">
+      <c r="A30" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="B30" s="15" t="n">
         <v>17</v>
       </c>
-      <c r="C30" s="21" t="inlineStr">
-        <is>
-          <t>바이온</t>
-        </is>
-      </c>
-      <c r="D30" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="E30" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="F30" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G30" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H30" s="22" t="n">
-        <v>-25</v>
-      </c>
-      <c r="I30" s="22" t="n">
-        <v>-96.03</v>
-      </c>
-      <c r="J30" s="23" t="inlineStr">
-        <is>
-          <t>네이버 검색 당일 +297% / 중요공시 2건</t>
-        </is>
-      </c>
-      <c r="K30" s="23" t="inlineStr">
-        <is>
-          <t>네이버, 공시</t>
+      <c r="C30" s="16" t="inlineStr">
+        <is>
+          <t>제약</t>
+        </is>
+      </c>
+      <c r="D30" s="15" t="n">
+        <v>7</v>
+      </c>
+      <c r="E30" s="15" t="n">
+        <v>7</v>
+      </c>
+      <c r="F30" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" s="15" t="n">
+        <v/>
+      </c>
+      <c r="I30" s="15" t="n">
+        <v/>
+      </c>
+      <c r="J30" s="17" t="inlineStr">
+        <is>
+          <t>네이버뉴스 기사 언급 / 네이버뉴스 헤드라인 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 기사 언급</t>
+        </is>
+      </c>
+      <c r="K30" s="17" t="inlineStr">
+        <is>
+          <t>네이버</t>
         </is>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
-      <c r="A31" s="20" t="inlineStr">
-        <is>
-          <t>2026-06-25</t>
-        </is>
-      </c>
-      <c r="B31" s="20" t="n">
+      <c r="A31" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="B31" s="15" t="n">
         <v>18</v>
       </c>
-      <c r="C31" s="21" t="inlineStr">
-        <is>
-          <t>비비안</t>
-        </is>
-      </c>
-      <c r="D31" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="E31" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="F31" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G31" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H31" s="24" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="I31" s="24" t="n">
-        <v>58.32</v>
-      </c>
-      <c r="J31" s="23" t="inlineStr">
-        <is>
-          <t>중요공시 2건 / 매일경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K31" s="23" t="inlineStr">
-        <is>
-          <t>공시</t>
-        </is>
+      <c r="C31" s="16" t="inlineStr">
+        <is>
+          <t>LG전자</t>
+        </is>
+      </c>
+      <c r="D31" s="15" t="n">
+        <v>7</v>
+      </c>
+      <c r="E31" s="15" t="n">
+        <v>7</v>
+      </c>
+      <c r="F31" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" s="19" t="n">
+        <v>-0.73</v>
+      </c>
+      <c r="I31" s="19" t="n">
+        <v>-11.16</v>
+      </c>
+      <c r="J31" s="17" t="inlineStr">
+        <is>
+          <t>매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 기사 언급</t>
+        </is>
+      </c>
+      <c r="K31" s="17" t="n">
+        <v/>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
-      <c r="A32" s="20" t="inlineStr">
-        <is>
-          <t>2026-06-25</t>
-        </is>
-      </c>
-      <c r="B32" s="20" t="n">
+      <c r="A32" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="B32" s="15" t="n">
         <v>19</v>
       </c>
-      <c r="C32" s="21" t="inlineStr">
-        <is>
-          <t>셀트리온</t>
-        </is>
-      </c>
-      <c r="D32" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="E32" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="F32" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G32" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H32" s="24" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="I32" s="22" t="n">
-        <v>-1.09</v>
-      </c>
-      <c r="J32" s="23" t="inlineStr">
-        <is>
-          <t>중요공시 2건 / 한국경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K32" s="23" t="inlineStr">
-        <is>
-          <t>공시</t>
+      <c r="C32" s="16" t="inlineStr">
+        <is>
+          <t>철강</t>
+        </is>
+      </c>
+      <c r="D32" s="15" t="n">
+        <v>7</v>
+      </c>
+      <c r="E32" s="15" t="n">
+        <v>7</v>
+      </c>
+      <c r="F32" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" s="15" t="n">
+        <v/>
+      </c>
+      <c r="I32" s="15" t="n">
+        <v/>
+      </c>
+      <c r="J32" s="17" t="inlineStr">
+        <is>
+          <t>네이버뉴스 헤드라인 언급 / 네이버뉴스 기사 언급 / 매일경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K32" s="17" t="inlineStr">
+        <is>
+          <t>네이버</t>
         </is>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
-      <c r="A33" s="20" t="inlineStr">
-        <is>
-          <t>2026-06-25</t>
-        </is>
-      </c>
-      <c r="B33" s="20" t="n">
+      <c r="A33" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="B33" s="15" t="n">
         <v>20</v>
       </c>
-      <c r="C33" s="21" t="inlineStr">
-        <is>
-          <t>클로봇</t>
-        </is>
-      </c>
-      <c r="D33" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="E33" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="F33" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G33" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H33" s="24" t="n">
-        <v>9.380000000000001</v>
-      </c>
-      <c r="I33" s="22" t="n">
-        <v>-10.38</v>
-      </c>
-      <c r="J33" s="23" t="inlineStr">
-        <is>
-          <t>중요공시 1건 / 한국경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K33" s="23" t="inlineStr">
-        <is>
-          <t>공시</t>
-        </is>
+      <c r="C33" s="16" t="inlineStr">
+        <is>
+          <t>조선</t>
+        </is>
+      </c>
+      <c r="D33" s="15" t="n">
+        <v>7</v>
+      </c>
+      <c r="E33" s="15" t="n">
+        <v>7</v>
+      </c>
+      <c r="F33" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" s="15" t="n">
+        <v/>
+      </c>
+      <c r="I33" s="15" t="n">
+        <v/>
+      </c>
+      <c r="J33" s="17" t="inlineStr">
+        <is>
+          <t>매일경제 헤드라인 언급 / 한국경제 헤드라인 언급 / 매일경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K33" s="17" t="n">
+        <v/>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
       <c r="A34" s="20" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B34" s="20" t="n">
@@ -1780,40 +1772,42 @@
       </c>
       <c r="C34" s="21" t="inlineStr">
         <is>
-          <t>전기차</t>
+          <t>비투엔</t>
         </is>
       </c>
       <c r="D34" s="20" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E34" s="20" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F34" s="20" t="n">
         <v>0</v>
       </c>
       <c r="G34" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H34" s="20" t="n">
-        <v/>
-      </c>
-      <c r="I34" s="20" t="n">
-        <v/>
-      </c>
-      <c r="J34" s="23" t="inlineStr">
-        <is>
-          <t>매일경제 기사 언급 / 매일경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K34" s="23" t="n">
-        <v/>
+        <v>3</v>
+      </c>
+      <c r="H34" s="22" t="n">
+        <v>-6.29</v>
+      </c>
+      <c r="I34" s="23" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="J34" s="24" t="inlineStr">
+        <is>
+          <t>중요공시 5건 / 중요공시 7일 +400%</t>
+        </is>
+      </c>
+      <c r="K34" s="24" t="inlineStr">
+        <is>
+          <t>공시</t>
+        </is>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
       <c r="A35" s="20" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B35" s="20" t="n">
@@ -1821,289 +1815,289 @@
       </c>
       <c r="C35" s="21" t="inlineStr">
         <is>
-          <t>스테이블코인</t>
+          <t>스피어</t>
         </is>
       </c>
       <c r="D35" s="20" t="n">
+        <v>5</v>
+      </c>
+      <c r="E35" s="20" t="n">
+        <v>3</v>
+      </c>
+      <c r="F35" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="G35" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" s="22" t="n">
+        <v>-11.4</v>
+      </c>
+      <c r="I35" s="22" t="n">
+        <v>-30.17</v>
+      </c>
+      <c r="J35" s="24" t="inlineStr">
+        <is>
+          <t>중요공시 3건 / 중요공시 3일 +50%</t>
+        </is>
+      </c>
+      <c r="K35" s="24" t="inlineStr">
+        <is>
+          <t>공시</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="18" customHeight="1">
+      <c r="A36" s="20" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="B36" s="20" t="n">
+        <v>23</v>
+      </c>
+      <c r="C36" s="21" t="inlineStr">
+        <is>
+          <t>Netflix</t>
+        </is>
+      </c>
+      <c r="D36" s="20" t="n">
+        <v>5</v>
+      </c>
+      <c r="E36" s="20" t="n">
+        <v>5</v>
+      </c>
+      <c r="F36" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" s="20" t="n">
+        <v/>
+      </c>
+      <c r="I36" s="20" t="n">
+        <v/>
+      </c>
+      <c r="J36" s="24" t="inlineStr">
+        <is>
+          <t>Google 급상승 검색어 등장 (US)</t>
+        </is>
+      </c>
+      <c r="K36" s="24" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="18" customHeight="1">
+      <c r="A37" s="20" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="B37" s="20" t="n">
+        <v>24</v>
+      </c>
+      <c r="C37" s="21" t="inlineStr">
+        <is>
+          <t>KT</t>
+        </is>
+      </c>
+      <c r="D37" s="20" t="n">
+        <v>5</v>
+      </c>
+      <c r="E37" s="20" t="n">
+        <v>5</v>
+      </c>
+      <c r="F37" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G37" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" s="23" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="I37" s="22" t="n">
+        <v>-2.8</v>
+      </c>
+      <c r="J37" s="24" t="inlineStr">
+        <is>
+          <t>한국경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K37" s="24" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="38" ht="18" customHeight="1">
+      <c r="A38" s="20" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="B38" s="20" t="n">
+        <v>25</v>
+      </c>
+      <c r="C38" s="21" t="inlineStr">
+        <is>
+          <t>프로브잇</t>
+        </is>
+      </c>
+      <c r="D38" s="20" t="n">
         <v>4</v>
       </c>
-      <c r="E35" s="20" t="n">
+      <c r="E38" s="20" t="n">
         <v>4</v>
       </c>
-      <c r="F35" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G35" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H35" s="20" t="n">
-        <v/>
-      </c>
-      <c r="I35" s="20" t="n">
-        <v/>
-      </c>
-      <c r="J35" s="23" t="inlineStr">
-        <is>
-          <t>매일경제 헤드라인 언급 / 매일경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K35" s="23" t="n">
-        <v/>
-      </c>
-    </row>
-    <row r="36" ht="18" customHeight="1">
-      <c r="A36" s="25" t="inlineStr">
-        <is>
-          <t>2026-06-25</t>
-        </is>
-      </c>
-      <c r="B36" s="25" t="n">
-        <v>23</v>
-      </c>
-      <c r="C36" s="26" t="inlineStr">
-        <is>
-          <t>국순당</t>
-        </is>
-      </c>
-      <c r="D36" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="E36" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="F36" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="G36" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="H36" s="27" t="n">
-        <v>6.93</v>
-      </c>
-      <c r="I36" s="27" t="n">
-        <v>29.6</v>
-      </c>
-      <c r="J36" s="28" t="inlineStr">
-        <is>
-          <t>네이버 검색 당일 +178%</t>
-        </is>
-      </c>
-      <c r="K36" s="28" t="inlineStr">
-        <is>
-          <t>네이버</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="18" customHeight="1">
-      <c r="A37" s="25" t="inlineStr">
-        <is>
-          <t>2026-06-25</t>
-        </is>
-      </c>
-      <c r="B37" s="25" t="n">
-        <v>24</v>
-      </c>
-      <c r="C37" s="26" t="inlineStr">
-        <is>
-          <t>조아제약</t>
-        </is>
-      </c>
-      <c r="D37" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="E37" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="F37" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="G37" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="H37" s="27" t="n">
-        <v>5.14</v>
-      </c>
-      <c r="I37" s="27" t="n">
-        <v>42.86</v>
-      </c>
-      <c r="J37" s="28" t="inlineStr">
-        <is>
-          <t>네이버 검색 당일 +144%</t>
-        </is>
-      </c>
-      <c r="K37" s="28" t="inlineStr">
-        <is>
-          <t>네이버</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="18" customHeight="1">
-      <c r="A38" s="25" t="inlineStr">
-        <is>
-          <t>2026-06-25</t>
-        </is>
-      </c>
-      <c r="B38" s="25" t="n">
-        <v>25</v>
-      </c>
-      <c r="C38" s="26" t="inlineStr">
-        <is>
-          <t>해태제과식품</t>
-        </is>
-      </c>
-      <c r="D38" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="E38" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="F38" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="G38" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="H38" s="29" t="n">
-        <v>-3.38</v>
-      </c>
-      <c r="I38" s="27" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="J38" s="28" t="inlineStr">
-        <is>
-          <t>네이버 검색 당일 +142%</t>
-        </is>
-      </c>
-      <c r="K38" s="28" t="inlineStr">
-        <is>
-          <t>네이버</t>
+      <c r="F38" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G38" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" s="22" t="n">
+        <v>-44.44</v>
+      </c>
+      <c r="I38" s="22" t="n">
+        <v>-97.55</v>
+      </c>
+      <c r="J38" s="24" t="inlineStr">
+        <is>
+          <t>네이버 검색 당일 +1686% / 중요공시 1건</t>
+        </is>
+      </c>
+      <c r="K38" s="24" t="inlineStr">
+        <is>
+          <t>공시, 네이버</t>
         </is>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
-      <c r="A39" s="25" t="inlineStr">
-        <is>
-          <t>2026-06-25</t>
-        </is>
-      </c>
-      <c r="B39" s="25" t="n">
+      <c r="A39" s="20" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="B39" s="20" t="n">
         <v>26</v>
       </c>
-      <c r="C39" s="26" t="inlineStr">
-        <is>
-          <t>미래나노텍</t>
-        </is>
-      </c>
-      <c r="D39" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="E39" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="F39" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="G39" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="H39" s="29" t="n">
-        <v>-4.76</v>
-      </c>
-      <c r="I39" s="27" t="n">
-        <v>14.36</v>
-      </c>
-      <c r="J39" s="28" t="inlineStr">
-        <is>
-          <t>네이버 검색 당일 +117%</t>
-        </is>
-      </c>
-      <c r="K39" s="28" t="inlineStr">
-        <is>
-          <t>네이버</t>
+      <c r="C39" s="21" t="inlineStr">
+        <is>
+          <t>헝셩그룹</t>
+        </is>
+      </c>
+      <c r="D39" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="E39" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="F39" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G39" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" s="22" t="n">
+        <v>-6.53</v>
+      </c>
+      <c r="I39" s="23" t="n">
+        <v>11.09</v>
+      </c>
+      <c r="J39" s="24" t="inlineStr">
+        <is>
+          <t>네이버 검색 당일 +156% / 중요공시 2건</t>
+        </is>
+      </c>
+      <c r="K39" s="24" t="inlineStr">
+        <is>
+          <t>공시, 네이버</t>
         </is>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
-      <c r="A40" s="25" t="inlineStr">
-        <is>
-          <t>2026-06-25</t>
-        </is>
-      </c>
-      <c r="B40" s="25" t="n">
+      <c r="A40" s="20" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="B40" s="20" t="n">
         <v>27</v>
       </c>
-      <c r="C40" s="26" t="inlineStr">
-        <is>
-          <t>아이엠</t>
-        </is>
-      </c>
-      <c r="D40" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="E40" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="F40" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="G40" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="H40" s="27" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="I40" s="29" t="n">
-        <v>-86.36</v>
-      </c>
-      <c r="J40" s="28" t="inlineStr">
-        <is>
-          <t>중요공시 2건 / 매일경제 기사 언급</t>
-        </is>
-      </c>
-      <c r="K40" s="28" t="inlineStr">
-        <is>
-          <t>공시</t>
+      <c r="C40" s="21" t="inlineStr">
+        <is>
+          <t>베셀</t>
+        </is>
+      </c>
+      <c r="D40" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="E40" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="F40" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G40" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" s="23" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="I40" s="23" t="n">
+        <v>7.08</v>
+      </c>
+      <c r="J40" s="24" t="inlineStr">
+        <is>
+          <t>네이버 검색 당일 +134% / 중요공시 2건</t>
+        </is>
+      </c>
+      <c r="K40" s="24" t="inlineStr">
+        <is>
+          <t>공시, 네이버</t>
         </is>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
-      <c r="A41" s="25" t="inlineStr">
-        <is>
-          <t>2026-06-25</t>
-        </is>
-      </c>
-      <c r="B41" s="25" t="n">
+      <c r="A41" s="20" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="B41" s="20" t="n">
         <v>28</v>
       </c>
-      <c r="C41" s="26" t="inlineStr">
-        <is>
-          <t>경남제약</t>
-        </is>
-      </c>
-      <c r="D41" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="E41" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="F41" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="G41" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="H41" s="29" t="n">
-        <v>-10.34</v>
-      </c>
-      <c r="I41" s="27" t="n">
-        <v>3.23</v>
-      </c>
-      <c r="J41" s="28" t="inlineStr">
-        <is>
-          <t>중요공시 4건</t>
-        </is>
-      </c>
-      <c r="K41" s="28" t="inlineStr">
+      <c r="C41" s="21" t="inlineStr">
+        <is>
+          <t>다스코</t>
+        </is>
+      </c>
+      <c r="D41" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="E41" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="F41" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G41" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" s="23" t="n">
+        <v>29.91</v>
+      </c>
+      <c r="I41" s="23" t="n">
+        <v>53.75</v>
+      </c>
+      <c r="J41" s="24" t="inlineStr">
+        <is>
+          <t>중요공시 1건 / 매일경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K41" s="24" t="inlineStr">
         <is>
           <t>공시</t>
         </is>
@@ -2112,7 +2106,7 @@
     <row r="42" ht="18" customHeight="1">
       <c r="A42" s="25" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B42" s="25" t="n">
@@ -2120,7 +2114,7 @@
       </c>
       <c r="C42" s="26" t="inlineStr">
         <is>
-          <t>소룩스</t>
+          <t>노블엠앤비</t>
         </is>
       </c>
       <c r="D42" s="25" t="n">
@@ -2136,26 +2130,26 @@
         <v>0</v>
       </c>
       <c r="H42" s="27" t="n">
-        <v>15.6</v>
+        <v>-38.1</v>
       </c>
       <c r="I42" s="27" t="n">
-        <v>19.42</v>
+        <v>-96.84</v>
       </c>
       <c r="J42" s="28" t="inlineStr">
         <is>
-          <t>중요공시 3건</t>
+          <t>네이버 검색 당일 +614%</t>
         </is>
       </c>
       <c r="K42" s="28" t="inlineStr">
         <is>
-          <t>공시</t>
+          <t>네이버</t>
         </is>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1">
       <c r="A43" s="25" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B43" s="25" t="n">
@@ -2163,7 +2157,7 @@
       </c>
       <c r="C43" s="26" t="inlineStr">
         <is>
-          <t>오리엔트바이오</t>
+          <t>국순당</t>
         </is>
       </c>
       <c r="D43" s="25" t="n">
@@ -2179,26 +2173,26 @@
         <v>0</v>
       </c>
       <c r="H43" s="27" t="n">
-        <v>10.97</v>
+        <v>-13.18</v>
       </c>
       <c r="I43" s="29" t="n">
-        <v>-6.38</v>
+        <v>12.52</v>
       </c>
       <c r="J43" s="28" t="inlineStr">
         <is>
-          <t>중요공시 3건</t>
+          <t>네이버 검색 당일 +420%</t>
         </is>
       </c>
       <c r="K43" s="28" t="inlineStr">
         <is>
-          <t>공시</t>
+          <t>네이버</t>
         </is>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
       <c r="A44" s="25" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B44" s="25" t="n">
@@ -2206,7 +2200,7 @@
       </c>
       <c r="C44" s="26" t="inlineStr">
         <is>
-          <t>동양</t>
+          <t>바이온</t>
         </is>
       </c>
       <c r="D44" s="25" t="n">
@@ -2222,24 +2216,26 @@
         <v>0</v>
       </c>
       <c r="H44" s="27" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="I44" s="29" t="n">
-        <v>-3.41</v>
+        <v>-41.67</v>
+      </c>
+      <c r="I44" s="27" t="n">
+        <v>-97.68000000000001</v>
       </c>
       <c r="J44" s="28" t="inlineStr">
         <is>
-          <t>매일경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K44" s="28" t="n">
-        <v/>
+          <t>네이버 검색 당일 +402%</t>
+        </is>
+      </c>
+      <c r="K44" s="28" t="inlineStr">
+        <is>
+          <t>네이버</t>
+        </is>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
       <c r="A45" s="25" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B45" s="25" t="n">
@@ -2247,7 +2243,7 @@
       </c>
       <c r="C45" s="26" t="inlineStr">
         <is>
-          <t>대한항공</t>
+          <t>서암기계공업</t>
         </is>
       </c>
       <c r="D45" s="25" t="n">
@@ -2263,24 +2259,26 @@
         <v>0</v>
       </c>
       <c r="H45" s="27" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="I45" s="29" t="n">
-        <v>-5.03</v>
+        <v>-26.92</v>
+      </c>
+      <c r="I45" s="27" t="n">
+        <v>-5.42</v>
       </c>
       <c r="J45" s="28" t="inlineStr">
         <is>
-          <t>매일경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K45" s="28" t="n">
-        <v/>
+          <t>네이버 검색 당일 +350%</t>
+        </is>
+      </c>
+      <c r="K45" s="28" t="inlineStr">
+        <is>
+          <t>네이버</t>
+        </is>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
       <c r="A46" s="25" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B46" s="25" t="n">
@@ -2288,42 +2286,42 @@
       </c>
       <c r="C46" s="26" t="inlineStr">
         <is>
-          <t>성호전자</t>
+          <t>조아제약</t>
         </is>
       </c>
       <c r="D46" s="25" t="n">
         <v>3</v>
       </c>
       <c r="E46" s="25" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F46" s="25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G46" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H46" s="29" t="n">
-        <v>-4.3</v>
+      <c r="H46" s="27" t="n">
+        <v>-21.89</v>
       </c>
       <c r="I46" s="29" t="n">
-        <v>-29.63</v>
+        <v>19.76</v>
       </c>
       <c r="J46" s="28" t="inlineStr">
         <is>
-          <t>중요공시 2건 / 중요공시 3일 +100%</t>
+          <t>네이버 검색 당일 +287%</t>
         </is>
       </c>
       <c r="K46" s="28" t="inlineStr">
         <is>
-          <t>공시</t>
+          <t>네이버</t>
         </is>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
       <c r="A47" s="25" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B47" s="25" t="n">
@@ -2331,7 +2329,7 @@
       </c>
       <c r="C47" s="26" t="inlineStr">
         <is>
-          <t>차AI헬스케어</t>
+          <t>부국철강</t>
         </is>
       </c>
       <c r="D47" s="25" t="n">
@@ -2346,27 +2344,27 @@
       <c r="G47" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H47" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="I47" s="27" t="n">
-        <v>14.85</v>
+      <c r="H47" s="27" t="n">
+        <v>-20.26</v>
+      </c>
+      <c r="I47" s="29" t="n">
+        <v>6.78</v>
       </c>
       <c r="J47" s="28" t="inlineStr">
         <is>
-          <t>중요공시 11건</t>
+          <t>네이버 검색 당일 +260%</t>
         </is>
       </c>
       <c r="K47" s="28" t="inlineStr">
         <is>
-          <t>공시</t>
+          <t>네이버</t>
         </is>
       </c>
     </row>
     <row r="48" ht="18" customHeight="1">
       <c r="A48" s="25" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B48" s="25" t="n">
@@ -2374,7 +2372,7 @@
       </c>
       <c r="C48" s="26" t="inlineStr">
         <is>
-          <t>넥써쓰</t>
+          <t>위지트</t>
         </is>
       </c>
       <c r="D48" s="25" t="n">
@@ -2389,27 +2387,27 @@
       <c r="G48" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H48" s="29" t="n">
-        <v>-7.32</v>
+      <c r="H48" s="27" t="n">
+        <v>-7.25</v>
       </c>
       <c r="I48" s="29" t="n">
-        <v>-38.17</v>
+        <v>33.18</v>
       </c>
       <c r="J48" s="28" t="inlineStr">
         <is>
-          <t>중요공시 3건</t>
+          <t>네이버 검색 당일 +223%</t>
         </is>
       </c>
       <c r="K48" s="28" t="inlineStr">
         <is>
-          <t>공시</t>
+          <t>네이버</t>
         </is>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1">
       <c r="A49" s="25" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B49" s="25" t="n">
@@ -2417,7 +2415,7 @@
       </c>
       <c r="C49" s="26" t="inlineStr">
         <is>
-          <t>아모텍</t>
+          <t>보해양조</t>
         </is>
       </c>
       <c r="D49" s="25" t="n">
@@ -2432,27 +2430,27 @@
       <c r="G49" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H49" s="29" t="n">
-        <v>-4.98</v>
+      <c r="H49" s="27" t="n">
+        <v>-30</v>
       </c>
       <c r="I49" s="29" t="n">
-        <v>-21.8</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="J49" s="28" t="inlineStr">
         <is>
-          <t>중요공시 3건</t>
+          <t>네이버 검색 당일 +220%</t>
         </is>
       </c>
       <c r="K49" s="28" t="inlineStr">
         <is>
-          <t>공시</t>
+          <t>네이버</t>
         </is>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
       <c r="A50" s="25" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B50" s="25" t="n">
@@ -2460,7 +2458,7 @@
       </c>
       <c r="C50" s="26" t="inlineStr">
         <is>
-          <t>에이프로젠</t>
+          <t>디와이에이</t>
         </is>
       </c>
       <c r="D50" s="25" t="n">
@@ -2476,26 +2474,26 @@
         <v>0</v>
       </c>
       <c r="H50" s="29" t="n">
-        <v>-3.2</v>
-      </c>
-      <c r="I50" s="29" t="n">
-        <v>-21.94</v>
+        <v>3.83</v>
+      </c>
+      <c r="I50" s="27" t="n">
+        <v>-4.95</v>
       </c>
       <c r="J50" s="28" t="inlineStr">
         <is>
-          <t>중요공시 3건</t>
+          <t>네이버 검색 당일 +212%</t>
         </is>
       </c>
       <c r="K50" s="28" t="inlineStr">
         <is>
-          <t>공시</t>
+          <t>네이버</t>
         </is>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
       <c r="A51" s="25" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B51" s="25" t="n">
@@ -2503,42 +2501,42 @@
       </c>
       <c r="C51" s="26" t="inlineStr">
         <is>
-          <t>진흥기업</t>
+          <t>남화산업</t>
         </is>
       </c>
       <c r="D51" s="25" t="n">
         <v>3</v>
       </c>
       <c r="E51" s="25" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F51" s="25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G51" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H51" s="29" t="n">
-        <v>-2.03</v>
+      <c r="H51" s="27" t="n">
+        <v>-21.05</v>
       </c>
       <c r="I51" s="29" t="n">
-        <v>-15.98</v>
+        <v>3.15</v>
       </c>
       <c r="J51" s="28" t="inlineStr">
         <is>
-          <t>중요공시 2건 / 중요공시 3일 +100%</t>
+          <t>네이버 검색 당일 +194%</t>
         </is>
       </c>
       <c r="K51" s="28" t="inlineStr">
         <is>
-          <t>공시</t>
+          <t>네이버</t>
         </is>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1">
       <c r="A52" s="25" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B52" s="25" t="n">
@@ -2546,42 +2544,42 @@
       </c>
       <c r="C52" s="26" t="inlineStr">
         <is>
-          <t>시너지이노베이션</t>
+          <t>키스트론</t>
         </is>
       </c>
       <c r="D52" s="25" t="n">
         <v>3</v>
       </c>
       <c r="E52" s="25" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F52" s="25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G52" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H52" s="27" t="n">
-        <v>4.45</v>
+      <c r="H52" s="29" t="n">
+        <v>10.76</v>
       </c>
       <c r="I52" s="29" t="n">
-        <v>-10.09</v>
+        <v>25.6</v>
       </c>
       <c r="J52" s="28" t="inlineStr">
         <is>
-          <t>중요공시 2건 / 중요공시 3일 +100%</t>
+          <t>네이버 검색 당일 +171%</t>
         </is>
       </c>
       <c r="K52" s="28" t="inlineStr">
         <is>
-          <t>공시</t>
+          <t>네이버</t>
         </is>
       </c>
     </row>
     <row r="53" ht="18" customHeight="1">
       <c r="A53" s="25" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B53" s="25" t="n">
@@ -2589,7 +2587,7 @@
       </c>
       <c r="C53" s="26" t="inlineStr">
         <is>
-          <t>ISC</t>
+          <t>모헨즈</t>
         </is>
       </c>
       <c r="D53" s="25" t="n">
@@ -2605,24 +2603,26 @@
         <v>0</v>
       </c>
       <c r="H53" s="27" t="n">
-        <v>0.05</v>
+        <v>-26.57</v>
       </c>
       <c r="I53" s="29" t="n">
-        <v>-2.16</v>
+        <v>17.87</v>
       </c>
       <c r="J53" s="28" t="inlineStr">
         <is>
-          <t>매일경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K53" s="28" t="n">
-        <v/>
+          <t>네이버 검색 당일 +160%</t>
+        </is>
+      </c>
+      <c r="K53" s="28" t="inlineStr">
+        <is>
+          <t>네이버</t>
+        </is>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
       <c r="A54" s="25" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B54" s="25" t="n">
@@ -2630,7 +2630,7 @@
       </c>
       <c r="C54" s="26" t="inlineStr">
         <is>
-          <t>테스</t>
+          <t>동양파일</t>
         </is>
       </c>
       <c r="D54" s="25" t="n">
@@ -2646,24 +2646,26 @@
         <v>0</v>
       </c>
       <c r="H54" s="27" t="n">
-        <v>3.04</v>
+        <v>-9.130000000000001</v>
       </c>
       <c r="I54" s="29" t="n">
-        <v>-4.07</v>
+        <v>15.69</v>
       </c>
       <c r="J54" s="28" t="inlineStr">
         <is>
-          <t>매일경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K54" s="28" t="n">
-        <v/>
+          <t>네이버 검색 당일 +156%</t>
+        </is>
+      </c>
+      <c r="K54" s="28" t="inlineStr">
+        <is>
+          <t>네이버</t>
+        </is>
       </c>
     </row>
     <row r="55" ht="18" customHeight="1">
       <c r="A55" s="25" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B55" s="25" t="n">
@@ -2671,7 +2673,7 @@
       </c>
       <c r="C55" s="26" t="inlineStr">
         <is>
-          <t>LG이노텍</t>
+          <t>삼기에너지솔루션즈</t>
         </is>
       </c>
       <c r="D55" s="25" t="n">
@@ -2687,24 +2689,26 @@
         <v>0</v>
       </c>
       <c r="H55" s="29" t="n">
-        <v>-3.43</v>
+        <v>29.96</v>
       </c>
       <c r="I55" s="29" t="n">
-        <v>-23.32</v>
+        <v>43.5</v>
       </c>
       <c r="J55" s="28" t="inlineStr">
         <is>
-          <t>한국경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K55" s="28" t="n">
-        <v/>
+          <t>네이버 검색 당일 +106%</t>
+        </is>
+      </c>
+      <c r="K55" s="28" t="inlineStr">
+        <is>
+          <t>네이버</t>
+        </is>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1">
       <c r="A56" s="25" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B56" s="25" t="n">
@@ -2712,7 +2716,7 @@
       </c>
       <c r="C56" s="26" t="inlineStr">
         <is>
-          <t>동양파일</t>
+          <t>소룩스</t>
         </is>
       </c>
       <c r="D56" s="25" t="n">
@@ -2728,24 +2732,26 @@
         <v>0</v>
       </c>
       <c r="H56" s="27" t="n">
-        <v>29.92</v>
-      </c>
-      <c r="I56" s="27" t="n">
-        <v>27.24</v>
+        <v>-1.38</v>
+      </c>
+      <c r="I56" s="29" t="n">
+        <v>20.25</v>
       </c>
       <c r="J56" s="28" t="inlineStr">
         <is>
-          <t>매일경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K56" s="28" t="n">
-        <v/>
+          <t>중요공시 3건</t>
+        </is>
+      </c>
+      <c r="K56" s="28" t="inlineStr">
+        <is>
+          <t>공시</t>
+        </is>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1">
       <c r="A57" s="25" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B57" s="25" t="n">
@@ -2753,7 +2759,7 @@
       </c>
       <c r="C57" s="26" t="inlineStr">
         <is>
-          <t>원전</t>
+          <t>샤페론</t>
         </is>
       </c>
       <c r="D57" s="25" t="n">
@@ -2768,27 +2774,27 @@
       <c r="G57" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H57" s="25" t="n">
-        <v/>
-      </c>
-      <c r="I57" s="25" t="n">
-        <v/>
+      <c r="H57" s="27" t="n">
+        <v>-29.98</v>
+      </c>
+      <c r="I57" s="27" t="n">
+        <v>-36.75</v>
       </c>
       <c r="J57" s="28" t="inlineStr">
         <is>
-          <t>네이버뉴스 헤드라인 언급</t>
+          <t>중요공시 1건 / 한국경제 헤드라인 언급</t>
         </is>
       </c>
       <c r="K57" s="28" t="inlineStr">
         <is>
-          <t>네이버</t>
+          <t>공시</t>
         </is>
       </c>
     </row>
     <row r="58" ht="18" customHeight="1">
       <c r="A58" s="25" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B58" s="25" t="n">
@@ -2796,42 +2802,42 @@
       </c>
       <c r="C58" s="26" t="inlineStr">
         <is>
-          <t>철강</t>
+          <t>진흥기업</t>
         </is>
       </c>
       <c r="D58" s="25" t="n">
         <v>3</v>
       </c>
       <c r="E58" s="25" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F58" s="25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G58" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H58" s="25" t="n">
-        <v/>
-      </c>
-      <c r="I58" s="25" t="n">
-        <v/>
+      <c r="H58" s="27" t="n">
+        <v>-5.17</v>
+      </c>
+      <c r="I58" s="27" t="n">
+        <v>-17.83</v>
       </c>
       <c r="J58" s="28" t="inlineStr">
         <is>
-          <t>네이버뉴스 헤드라인 언급</t>
+          <t>중요공시 2건 / 중요공시 3일 +100%</t>
         </is>
       </c>
       <c r="K58" s="28" t="inlineStr">
         <is>
-          <t>네이버</t>
+          <t>공시</t>
         </is>
       </c>
     </row>
     <row r="59" ht="18" customHeight="1">
       <c r="A59" s="25" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B59" s="25" t="n">
@@ -2839,7 +2845,7 @@
       </c>
       <c r="C59" s="26" t="inlineStr">
         <is>
-          <t>HMM</t>
+          <t>SK증권</t>
         </is>
       </c>
       <c r="D59" s="25" t="n">
@@ -2854,15 +2860,15 @@
       <c r="G59" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H59" s="27" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="I59" s="29" t="n">
-        <v>-14.3</v>
+      <c r="H59" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I59" s="27" t="n">
+        <v>-14.36</v>
       </c>
       <c r="J59" s="28" t="inlineStr">
         <is>
-          <t>한국경제 헤드라인 언급</t>
+          <t>매일경제 헤드라인 언급</t>
         </is>
       </c>
       <c r="K59" s="28" t="n">
@@ -2872,7 +2878,7 @@
     <row r="60" ht="18" customHeight="1">
       <c r="A60" s="25" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B60" s="25" t="n">
@@ -2880,7 +2886,7 @@
       </c>
       <c r="C60" s="26" t="inlineStr">
         <is>
-          <t>기아</t>
+          <t>에이프릴바이오</t>
         </is>
       </c>
       <c r="D60" s="25" t="n">
@@ -2896,24 +2902,26 @@
         <v>0</v>
       </c>
       <c r="H60" s="27" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="I60" s="29" t="n">
-        <v>-16.48</v>
+        <v>-3.02</v>
+      </c>
+      <c r="I60" s="27" t="n">
+        <v>-6.78</v>
       </c>
       <c r="J60" s="28" t="inlineStr">
         <is>
-          <t>한국경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K60" s="28" t="n">
-        <v/>
+          <t>중요공시 5건</t>
+        </is>
+      </c>
+      <c r="K60" s="28" t="inlineStr">
+        <is>
+          <t>공시</t>
+        </is>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
       <c r="A61" s="25" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B61" s="25" t="n">
@@ -2921,14 +2929,14 @@
       </c>
       <c r="C61" s="26" t="inlineStr">
         <is>
-          <t>보해양조</t>
+          <t>에이프로젠</t>
         </is>
       </c>
       <c r="D61" s="25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E61" s="25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F61" s="25" t="n">
         <v>0</v>
@@ -2937,26 +2945,26 @@
         <v>0</v>
       </c>
       <c r="H61" s="27" t="n">
-        <v>29.93</v>
+        <v>-1.45</v>
       </c>
       <c r="I61" s="27" t="n">
-        <v>177.58</v>
+        <v>-18.74</v>
       </c>
       <c r="J61" s="28" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +100%</t>
+          <t>중요공시 4건</t>
         </is>
       </c>
       <c r="K61" s="28" t="inlineStr">
         <is>
-          <t>네이버</t>
+          <t>공시</t>
         </is>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1">
       <c r="A62" s="25" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B62" s="25" t="n">
@@ -2964,14 +2972,14 @@
       </c>
       <c r="C62" s="26" t="inlineStr">
         <is>
-          <t>부국철강</t>
+          <t>경남제약</t>
         </is>
       </c>
       <c r="D62" s="25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E62" s="25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F62" s="25" t="n">
         <v>0</v>
@@ -2979,27 +2987,27 @@
       <c r="G62" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H62" s="29" t="n">
-        <v>-7.99</v>
+      <c r="H62" s="27" t="n">
+        <v>-16.44</v>
       </c>
       <c r="I62" s="27" t="n">
-        <v>45.78</v>
+        <v>-10.37</v>
       </c>
       <c r="J62" s="28" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +95%</t>
+          <t>중요공시 3건</t>
         </is>
       </c>
       <c r="K62" s="28" t="inlineStr">
         <is>
-          <t>네이버</t>
+          <t>공시</t>
         </is>
       </c>
     </row>
     <row r="63" ht="18" customHeight="1">
       <c r="A63" s="25" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B63" s="25" t="n">
@@ -3007,14 +3015,14 @@
       </c>
       <c r="C63" s="26" t="inlineStr">
         <is>
-          <t>키스트론</t>
+          <t>삼호개발</t>
         </is>
       </c>
       <c r="D63" s="25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E63" s="25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F63" s="25" t="n">
         <v>0</v>
@@ -3022,20 +3030,20 @@
       <c r="G63" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H63" s="27" t="n">
-        <v>4.23</v>
-      </c>
-      <c r="I63" s="27" t="n">
-        <v>23.53</v>
+      <c r="H63" s="29" t="n">
+        <v>11.13</v>
+      </c>
+      <c r="I63" s="29" t="n">
+        <v>2.57</v>
       </c>
       <c r="J63" s="28" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +91%</t>
+          <t>중요공시 3건</t>
         </is>
       </c>
       <c r="K63" s="28" t="inlineStr">
         <is>
-          <t>네이버</t>
+          <t>공시</t>
         </is>
       </c>
     </row>
@@ -3132,22 +3140,22 @@
         <v>1</v>
       </c>
       <c r="C3" s="25" t="n">
-        <v>100</v>
+        <v>73</v>
       </c>
       <c r="D3" s="25" t="n">
-        <v>100</v>
+        <v>73</v>
       </c>
       <c r="E3" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F3" s="25" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G3" s="25" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="H3" s="25" t="n"/>
@@ -3156,103 +3164,107 @@
     <row r="4" ht="18" customHeight="1">
       <c r="A4" s="26" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>SK</t>
         </is>
       </c>
       <c r="B4" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C4" s="25" t="n">
-        <v>37</v>
+        <v>67</v>
       </c>
       <c r="D4" s="25" t="n">
-        <v>37</v>
+        <v>67</v>
       </c>
       <c r="E4" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F4" s="25" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G4" s="25" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
-        </is>
-      </c>
-      <c r="H4" s="27" t="n">
-        <v>0.98</v>
-      </c>
-      <c r="I4" s="27" t="n">
-        <v>2.34</v>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="H4" s="29" t="n">
+        <v>20.51</v>
+      </c>
+      <c r="I4" s="29" t="n">
+        <v>24.89</v>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="26" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B5" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C5" s="25" t="n">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="D5" s="25" t="n">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="E5" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F5" s="25" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G5" s="25" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
-        </is>
-      </c>
-      <c r="H5" s="27" t="n">
-        <v>9.84</v>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="H5" s="29" t="n">
+        <v>13.06</v>
       </c>
       <c r="I5" s="29" t="n">
-        <v>-1.73</v>
+        <v>8.640000000000001</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
       <c r="A6" s="26" t="inlineStr">
         <is>
-          <t>인공지능</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B6" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C6" s="25" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D6" s="25" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E6" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F6" s="25" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G6" s="25" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
-        </is>
-      </c>
-      <c r="H6" s="25" t="n"/>
-      <c r="I6" s="25" t="n"/>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="H6" s="29" t="n">
+        <v>5.29</v>
+      </c>
+      <c r="I6" s="27" t="n">
+        <v>-1.1</v>
+      </c>
     </row>
     <row r="7" ht="18" customHeight="1">
       <c r="A7" s="26" t="inlineStr">
@@ -3274,12 +3286,12 @@
       </c>
       <c r="F7" s="25" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G7" s="25" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="H7" s="25" t="n"/>
@@ -3288,7 +3300,7 @@
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="26" t="inlineStr">
         <is>
-          <t>LG</t>
+          <t>인공지능</t>
         </is>
       </c>
       <c r="B8" s="25" t="n">
@@ -3305,113 +3317,113 @@
       </c>
       <c r="F8" s="25" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G8" s="25" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
-        </is>
-      </c>
-      <c r="H8" s="27" t="n">
-        <v>0.61</v>
-      </c>
-      <c r="I8" s="29" t="n">
-        <v>-11.82</v>
-      </c>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="H8" s="25" t="n"/>
+      <c r="I8" s="25" t="n"/>
     </row>
     <row r="9" ht="18" customHeight="1">
       <c r="A9" s="26" t="inlineStr">
         <is>
-          <t>로봇</t>
+          <t>카카오</t>
         </is>
       </c>
       <c r="B9" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C9" s="25" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D9" s="25" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E9" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F9" s="25" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G9" s="25" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
-        </is>
-      </c>
-      <c r="H9" s="25" t="n"/>
-      <c r="I9" s="25" t="n"/>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="H9" s="29" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="I9" s="27" t="n">
+        <v>-12.85</v>
+      </c>
     </row>
     <row r="10" ht="18" customHeight="1">
       <c r="A10" s="26" t="inlineStr">
         <is>
-          <t>에이팩트</t>
+          <t>현대차</t>
         </is>
       </c>
       <c r="B10" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C10" s="25" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D10" s="25" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E10" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F10" s="25" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G10" s="25" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
-        </is>
-      </c>
-      <c r="H10" s="29" t="n">
-        <v>-5.97</v>
-      </c>
-      <c r="I10" s="29" t="n">
-        <v>-26.41</v>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="H10" s="27" t="n">
+        <v>-1.18</v>
+      </c>
+      <c r="I10" s="27" t="n">
+        <v>-16.31</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
       <c r="A11" s="26" t="inlineStr">
         <is>
-          <t>제약</t>
+          <t>로봇</t>
         </is>
       </c>
       <c r="B11" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C11" s="25" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D11" s="25" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E11" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F11" s="25" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G11" s="25" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="H11" s="25" t="n"/>
@@ -3420,379 +3432,367 @@
     <row r="12" ht="18" customHeight="1">
       <c r="A12" s="26" t="inlineStr">
         <is>
-          <t>현대차</t>
+          <t>LG</t>
         </is>
       </c>
       <c r="B12" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C12" s="25" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D12" s="25" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E12" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F12" s="25" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G12" s="25" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="H12" s="29" t="n">
-        <v>-0.39</v>
-      </c>
-      <c r="I12" s="29" t="n">
-        <v>-17.64</v>
+        <v>0.2</v>
+      </c>
+      <c r="I12" s="27" t="n">
+        <v>-9.550000000000001</v>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
       <c r="A13" s="26" t="inlineStr">
         <is>
-          <t>에이프릴바이오</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="B13" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C13" s="25" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D13" s="25" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E13" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F13" s="25" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G13" s="25" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="H13" s="27" t="n">
-        <v>15.57</v>
-      </c>
-      <c r="I13" s="29" t="n">
-        <v>-14.62</v>
+        <v>-2.87</v>
+      </c>
+      <c r="I13" s="27" t="n">
+        <v>-9.960000000000001</v>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="26" t="inlineStr">
         <is>
-          <t>비투엔</t>
+          <t>전기차</t>
         </is>
       </c>
       <c r="B14" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C14" s="25" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D14" s="25" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E14" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F14" s="25" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G14" s="25" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
-        </is>
-      </c>
-      <c r="H14" s="27" t="n">
-        <v>15.89</v>
-      </c>
-      <c r="I14" s="27" t="n">
-        <v>5.85</v>
-      </c>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="H14" s="25" t="n"/>
+      <c r="I14" s="25" t="n"/>
     </row>
     <row r="15" ht="18" customHeight="1">
       <c r="A15" s="26" t="inlineStr">
         <is>
-          <t>프로브잇</t>
+          <t>카카오뱅크</t>
         </is>
       </c>
       <c r="B15" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C15" s="25" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D15" s="25" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E15" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F15" s="25" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G15" s="25" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="H15" s="29" t="n">
-        <v>-46</v>
-      </c>
-      <c r="I15" s="29" t="n">
-        <v>-95.59</v>
+        <v>2</v>
+      </c>
+      <c r="I15" s="27" t="n">
+        <v>-10.7</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
       <c r="A16" s="26" t="inlineStr">
         <is>
-          <t>센서뷰</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B16" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C16" s="25" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D16" s="25" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E16" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F16" s="25" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G16" s="25" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
-        </is>
-      </c>
-      <c r="H16" s="27" t="n">
-        <v>0.96</v>
-      </c>
-      <c r="I16" s="29" t="n">
-        <v>-10.4</v>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="H16" s="29" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="I16" s="27" t="n">
+        <v>-13.46</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
       <c r="A17" s="26" t="inlineStr">
         <is>
-          <t>스피어</t>
+          <t>에이팩트</t>
         </is>
       </c>
       <c r="B17" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C17" s="25" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D17" s="25" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E17" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F17" s="25" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G17" s="25" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="H17" s="27" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="I17" s="29" t="n">
-        <v>-28.67</v>
+        <v>-4.27</v>
+      </c>
+      <c r="I17" s="27" t="n">
+        <v>-27.86</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
       <c r="A18" s="26" t="inlineStr">
         <is>
-          <t>노블엠앤비</t>
+          <t>LG전자</t>
         </is>
       </c>
       <c r="B18" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C18" s="25" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D18" s="25" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E18" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F18" s="25" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G18" s="25" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
-        </is>
-      </c>
-      <c r="H18" s="29" t="n">
-        <v>-16</v>
-      </c>
-      <c r="I18" s="29" t="n">
-        <v>-94.89</v>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="H18" s="27" t="n">
+        <v>-0.73</v>
+      </c>
+      <c r="I18" s="27" t="n">
+        <v>-11.16</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
       <c r="A19" s="26" t="inlineStr">
         <is>
-          <t>바이온</t>
+          <t>대한항공</t>
         </is>
       </c>
       <c r="B19" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C19" s="25" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D19" s="25" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E19" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F19" s="25" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G19" s="25" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="H19" s="29" t="n">
-        <v>-25</v>
+        <v>6.4</v>
       </c>
       <c r="I19" s="29" t="n">
-        <v>-96.03</v>
+        <v>0.87</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
       <c r="A20" s="26" t="inlineStr">
         <is>
-          <t>비비안</t>
+          <t>제약</t>
         </is>
       </c>
       <c r="B20" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C20" s="25" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D20" s="25" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E20" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F20" s="25" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G20" s="25" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
-        </is>
-      </c>
-      <c r="H20" s="27" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="I20" s="27" t="n">
-        <v>58.32</v>
-      </c>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="H20" s="25" t="n"/>
+      <c r="I20" s="25" t="n"/>
     </row>
     <row r="21" ht="18" customHeight="1">
       <c r="A21" s="26" t="inlineStr">
         <is>
-          <t>셀트리온</t>
+          <t>조선</t>
         </is>
       </c>
       <c r="B21" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C21" s="25" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D21" s="25" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E21" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F21" s="25" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G21" s="25" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
-        </is>
-      </c>
-      <c r="H21" s="27" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="I21" s="29" t="n">
-        <v>-1.09</v>
-      </c>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="H21" s="25" t="n"/>
+      <c r="I21" s="25" t="n"/>
     </row>
     <row r="22" ht="18" customHeight="1">
       <c r="A22" s="26" t="inlineStr">
         <is>
-          <t>스테이블코인</t>
+          <t>철강</t>
         </is>
       </c>
       <c r="B22" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C22" s="25" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D22" s="25" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E22" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F22" s="25" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G22" s="25" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="H22" s="25" t="n"/>
@@ -3801,283 +3801,283 @@
     <row r="23" ht="18" customHeight="1">
       <c r="A23" s="26" t="inlineStr">
         <is>
-          <t>전기차</t>
+          <t>비투엔</t>
         </is>
       </c>
       <c r="B23" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C23" s="25" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D23" s="25" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E23" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F23" s="25" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G23" s="25" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
-        </is>
-      </c>
-      <c r="H23" s="25" t="n"/>
-      <c r="I23" s="25" t="n"/>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="H23" s="27" t="n">
+        <v>-6.29</v>
+      </c>
+      <c r="I23" s="29" t="n">
+        <v>3.04</v>
+      </c>
     </row>
     <row r="24" ht="18" customHeight="1">
       <c r="A24" s="26" t="inlineStr">
         <is>
-          <t>클로봇</t>
+          <t>KT</t>
         </is>
       </c>
       <c r="B24" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C24" s="25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D24" s="25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E24" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F24" s="25" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G24" s="25" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
-        </is>
-      </c>
-      <c r="H24" s="27" t="n">
-        <v>9.380000000000001</v>
-      </c>
-      <c r="I24" s="29" t="n">
-        <v>-10.38</v>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="H24" s="29" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="I24" s="27" t="n">
+        <v>-2.8</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
       <c r="A25" s="26" t="inlineStr">
         <is>
-          <t>HMM</t>
+          <t>Netflix</t>
         </is>
       </c>
       <c r="B25" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C25" s="25" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D25" s="25" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E25" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F25" s="25" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G25" s="25" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
-        </is>
-      </c>
-      <c r="H25" s="27" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="I25" s="29" t="n">
-        <v>-14.3</v>
-      </c>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="H25" s="25" t="n"/>
+      <c r="I25" s="25" t="n"/>
     </row>
     <row r="26" ht="18" customHeight="1">
       <c r="A26" s="26" t="inlineStr">
         <is>
-          <t>ISC</t>
+          <t>스피어</t>
         </is>
       </c>
       <c r="B26" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C26" s="25" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D26" s="25" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E26" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F26" s="25" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G26" s="25" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="H26" s="27" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="I26" s="29" t="n">
-        <v>-2.16</v>
+        <v>-11.4</v>
+      </c>
+      <c r="I26" s="27" t="n">
+        <v>-30.17</v>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
       <c r="A27" s="26" t="inlineStr">
         <is>
-          <t>LG이노텍</t>
+          <t>다스코</t>
         </is>
       </c>
       <c r="B27" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C27" s="25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D27" s="25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E27" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F27" s="25" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G27" s="25" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="H27" s="29" t="n">
-        <v>-3.43</v>
+        <v>29.91</v>
       </c>
       <c r="I27" s="29" t="n">
-        <v>-23.32</v>
+        <v>53.75</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
       <c r="A28" s="26" t="inlineStr">
         <is>
-          <t>경남제약</t>
+          <t>베셀</t>
         </is>
       </c>
       <c r="B28" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C28" s="25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D28" s="25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E28" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F28" s="25" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G28" s="25" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="H28" s="29" t="n">
-        <v>-10.34</v>
-      </c>
-      <c r="I28" s="27" t="n">
-        <v>3.23</v>
+        <v>9.800000000000001</v>
+      </c>
+      <c r="I28" s="29" t="n">
+        <v>7.08</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
       <c r="A29" s="26" t="inlineStr">
         <is>
-          <t>국순당</t>
+          <t>프로브잇</t>
         </is>
       </c>
       <c r="B29" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C29" s="25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D29" s="25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E29" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F29" s="25" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G29" s="25" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="H29" s="27" t="n">
-        <v>6.93</v>
+        <v>-44.44</v>
       </c>
       <c r="I29" s="27" t="n">
-        <v>29.6</v>
+        <v>-97.55</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
       <c r="A30" s="26" t="inlineStr">
         <is>
-          <t>기아</t>
+          <t>헝셩그룹</t>
         </is>
       </c>
       <c r="B30" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C30" s="25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D30" s="25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E30" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F30" s="25" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G30" s="25" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="H30" s="27" t="n">
-        <v>1.09</v>
+        <v>-6.53</v>
       </c>
       <c r="I30" s="29" t="n">
-        <v>-16.48</v>
+        <v>11.09</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
       <c r="A31" s="26" t="inlineStr">
         <is>
-          <t>넥써쓰</t>
+          <t>SK증권</t>
         </is>
       </c>
       <c r="B31" s="25" t="n">
@@ -4094,25 +4094,25 @@
       </c>
       <c r="F31" s="25" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G31" s="25" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
-        </is>
-      </c>
-      <c r="H31" s="29" t="n">
-        <v>-7.32</v>
-      </c>
-      <c r="I31" s="29" t="n">
-        <v>-38.17</v>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="H31" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" s="27" t="n">
+        <v>-14.36</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
       <c r="A32" s="26" t="inlineStr">
         <is>
-          <t>대한항공</t>
+          <t>경남제약</t>
         </is>
       </c>
       <c r="B32" s="25" t="n">
@@ -4129,25 +4129,25 @@
       </c>
       <c r="F32" s="25" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G32" s="25" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="H32" s="27" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="I32" s="29" t="n">
-        <v>-5.03</v>
+        <v>-16.44</v>
+      </c>
+      <c r="I32" s="27" t="n">
+        <v>-10.37</v>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
       <c r="A33" s="26" t="inlineStr">
         <is>
-          <t>동양</t>
+          <t>국순당</t>
         </is>
       </c>
       <c r="B33" s="25" t="n">
@@ -4164,25 +4164,25 @@
       </c>
       <c r="F33" s="25" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G33" s="25" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="H33" s="27" t="n">
-        <v>7.2</v>
+        <v>-13.18</v>
       </c>
       <c r="I33" s="29" t="n">
-        <v>-3.41</v>
+        <v>12.52</v>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
       <c r="A34" s="26" t="inlineStr">
         <is>
-          <t>동양파일</t>
+          <t>남화산업</t>
         </is>
       </c>
       <c r="B34" s="25" t="n">
@@ -4199,25 +4199,25 @@
       </c>
       <c r="F34" s="25" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G34" s="25" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="H34" s="27" t="n">
-        <v>29.92</v>
-      </c>
-      <c r="I34" s="27" t="n">
-        <v>27.24</v>
+        <v>-21.05</v>
+      </c>
+      <c r="I34" s="29" t="n">
+        <v>3.15</v>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
       <c r="A35" s="26" t="inlineStr">
         <is>
-          <t>미래나노텍</t>
+          <t>노블엠앤비</t>
         </is>
       </c>
       <c r="B35" s="25" t="n">
@@ -4234,25 +4234,25 @@
       </c>
       <c r="F35" s="25" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G35" s="25" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
-        </is>
-      </c>
-      <c r="H35" s="29" t="n">
-        <v>-4.76</v>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="H35" s="27" t="n">
+        <v>-38.1</v>
       </c>
       <c r="I35" s="27" t="n">
-        <v>14.36</v>
+        <v>-96.84</v>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
       <c r="A36" s="26" t="inlineStr">
         <is>
-          <t>성호전자</t>
+          <t>동양파일</t>
         </is>
       </c>
       <c r="B36" s="25" t="n">
@@ -4269,25 +4269,25 @@
       </c>
       <c r="F36" s="25" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G36" s="25" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
-        </is>
-      </c>
-      <c r="H36" s="29" t="n">
-        <v>-4.3</v>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="H36" s="27" t="n">
+        <v>-9.130000000000001</v>
       </c>
       <c r="I36" s="29" t="n">
-        <v>-29.63</v>
+        <v>15.69</v>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
       <c r="A37" s="26" t="inlineStr">
         <is>
-          <t>소룩스</t>
+          <t>디와이에이</t>
         </is>
       </c>
       <c r="B37" s="25" t="n">
@@ -4304,25 +4304,25 @@
       </c>
       <c r="F37" s="25" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G37" s="25" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
-        </is>
-      </c>
-      <c r="H37" s="27" t="n">
-        <v>15.6</v>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="H37" s="29" t="n">
+        <v>3.83</v>
       </c>
       <c r="I37" s="27" t="n">
-        <v>19.42</v>
+        <v>-4.95</v>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
       <c r="A38" s="26" t="inlineStr">
         <is>
-          <t>시너지이노베이션</t>
+          <t>모헨즈</t>
         </is>
       </c>
       <c r="B38" s="25" t="n">
@@ -4339,25 +4339,25 @@
       </c>
       <c r="F38" s="25" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G38" s="25" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="H38" s="27" t="n">
-        <v>4.45</v>
+        <v>-26.57</v>
       </c>
       <c r="I38" s="29" t="n">
-        <v>-10.09</v>
+        <v>17.87</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
       <c r="A39" s="26" t="inlineStr">
         <is>
-          <t>아모텍</t>
+          <t>바이온</t>
         </is>
       </c>
       <c r="B39" s="25" t="n">
@@ -4374,25 +4374,25 @@
       </c>
       <c r="F39" s="25" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G39" s="25" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
-        </is>
-      </c>
-      <c r="H39" s="29" t="n">
-        <v>-4.98</v>
-      </c>
-      <c r="I39" s="29" t="n">
-        <v>-21.8</v>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="H39" s="27" t="n">
+        <v>-41.67</v>
+      </c>
+      <c r="I39" s="27" t="n">
+        <v>-97.68000000000001</v>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
       <c r="A40" s="26" t="inlineStr">
         <is>
-          <t>아이엠</t>
+          <t>보해양조</t>
         </is>
       </c>
       <c r="B40" s="25" t="n">
@@ -4409,25 +4409,25 @@
       </c>
       <c r="F40" s="25" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G40" s="25" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="H40" s="27" t="n">
-        <v>1.89</v>
+        <v>-30</v>
       </c>
       <c r="I40" s="29" t="n">
-        <v>-86.36</v>
+        <v>68.59999999999999</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
       <c r="A41" s="26" t="inlineStr">
         <is>
-          <t>에이프로젠</t>
+          <t>부국철강</t>
         </is>
       </c>
       <c r="B41" s="25" t="n">
@@ -4444,25 +4444,25 @@
       </c>
       <c r="F41" s="25" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G41" s="25" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
-        </is>
-      </c>
-      <c r="H41" s="29" t="n">
-        <v>-3.2</v>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="H41" s="27" t="n">
+        <v>-20.26</v>
       </c>
       <c r="I41" s="29" t="n">
-        <v>-21.94</v>
+        <v>6.78</v>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
       <c r="A42" s="26" t="inlineStr">
         <is>
-          <t>오리엔트바이오</t>
+          <t>삼기에너지솔루션즈</t>
         </is>
       </c>
       <c r="B42" s="25" t="n">
@@ -4479,25 +4479,25 @@
       </c>
       <c r="F42" s="25" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G42" s="25" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
-        </is>
-      </c>
-      <c r="H42" s="27" t="n">
-        <v>10.97</v>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="H42" s="29" t="n">
+        <v>29.96</v>
       </c>
       <c r="I42" s="29" t="n">
-        <v>-6.38</v>
+        <v>43.5</v>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1">
       <c r="A43" s="26" t="inlineStr">
         <is>
-          <t>원전</t>
+          <t>삼호개발</t>
         </is>
       </c>
       <c r="B43" s="25" t="n">
@@ -4514,21 +4514,25 @@
       </c>
       <c r="F43" s="25" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G43" s="25" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
-        </is>
-      </c>
-      <c r="H43" s="25" t="n"/>
-      <c r="I43" s="25" t="n"/>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="H43" s="29" t="n">
+        <v>11.13</v>
+      </c>
+      <c r="I43" s="29" t="n">
+        <v>2.57</v>
+      </c>
     </row>
     <row r="44" ht="18" customHeight="1">
       <c r="A44" s="26" t="inlineStr">
         <is>
-          <t>조아제약</t>
+          <t>샤페론</t>
         </is>
       </c>
       <c r="B44" s="25" t="n">
@@ -4545,25 +4549,25 @@
       </c>
       <c r="F44" s="25" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G44" s="25" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="H44" s="27" t="n">
-        <v>5.14</v>
+        <v>-29.98</v>
       </c>
       <c r="I44" s="27" t="n">
-        <v>42.86</v>
+        <v>-36.75</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
       <c r="A45" s="26" t="inlineStr">
         <is>
-          <t>진흥기업</t>
+          <t>서암기계공업</t>
         </is>
       </c>
       <c r="B45" s="25" t="n">
@@ -4580,25 +4584,25 @@
       </c>
       <c r="F45" s="25" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G45" s="25" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
-        </is>
-      </c>
-      <c r="H45" s="29" t="n">
-        <v>-2.03</v>
-      </c>
-      <c r="I45" s="29" t="n">
-        <v>-15.98</v>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="H45" s="27" t="n">
+        <v>-26.92</v>
+      </c>
+      <c r="I45" s="27" t="n">
+        <v>-5.42</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
       <c r="A46" s="26" t="inlineStr">
         <is>
-          <t>차AI헬스케어</t>
+          <t>소룩스</t>
         </is>
       </c>
       <c r="B46" s="25" t="n">
@@ -4615,25 +4619,25 @@
       </c>
       <c r="F46" s="25" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G46" s="25" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
-        </is>
-      </c>
-      <c r="H46" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="I46" s="27" t="n">
-        <v>14.85</v>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="H46" s="27" t="n">
+        <v>-1.38</v>
+      </c>
+      <c r="I46" s="29" t="n">
+        <v>20.25</v>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
       <c r="A47" s="26" t="inlineStr">
         <is>
-          <t>철강</t>
+          <t>에이프로젠</t>
         </is>
       </c>
       <c r="B47" s="25" t="n">
@@ -4650,21 +4654,25 @@
       </c>
       <c r="F47" s="25" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G47" s="25" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
-        </is>
-      </c>
-      <c r="H47" s="25" t="n"/>
-      <c r="I47" s="25" t="n"/>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="H47" s="27" t="n">
+        <v>-1.45</v>
+      </c>
+      <c r="I47" s="27" t="n">
+        <v>-18.74</v>
+      </c>
     </row>
     <row r="48" ht="18" customHeight="1">
       <c r="A48" s="26" t="inlineStr">
         <is>
-          <t>테스</t>
+          <t>에이프릴바이오</t>
         </is>
       </c>
       <c r="B48" s="25" t="n">
@@ -4681,25 +4689,25 @@
       </c>
       <c r="F48" s="25" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G48" s="25" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="H48" s="27" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="I48" s="29" t="n">
-        <v>-4.07</v>
+        <v>-3.02</v>
+      </c>
+      <c r="I48" s="27" t="n">
+        <v>-6.78</v>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1">
       <c r="A49" s="26" t="inlineStr">
         <is>
-          <t>해태제과식품</t>
+          <t>위지트</t>
         </is>
       </c>
       <c r="B49" s="25" t="n">
@@ -4716,89 +4724,89 @@
       </c>
       <c r="F49" s="25" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G49" s="25" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
-        </is>
-      </c>
-      <c r="H49" s="29" t="n">
-        <v>-3.38</v>
-      </c>
-      <c r="I49" s="27" t="n">
-        <v>2.39</v>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="H49" s="27" t="n">
+        <v>-7.25</v>
+      </c>
+      <c r="I49" s="29" t="n">
+        <v>33.18</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
       <c r="A50" s="26" t="inlineStr">
         <is>
-          <t>보해양조</t>
+          <t>조아제약</t>
         </is>
       </c>
       <c r="B50" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C50" s="25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D50" s="25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E50" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F50" s="25" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G50" s="25" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="H50" s="27" t="n">
-        <v>29.93</v>
-      </c>
-      <c r="I50" s="27" t="n">
-        <v>177.58</v>
+        <v>-21.89</v>
+      </c>
+      <c r="I50" s="29" t="n">
+        <v>19.76</v>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
       <c r="A51" s="26" t="inlineStr">
         <is>
-          <t>부국철강</t>
+          <t>진흥기업</t>
         </is>
       </c>
       <c r="B51" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C51" s="25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D51" s="25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E51" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F51" s="25" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G51" s="25" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
-        </is>
-      </c>
-      <c r="H51" s="29" t="n">
-        <v>-7.99</v>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="H51" s="27" t="n">
+        <v>-5.17</v>
       </c>
       <c r="I51" s="27" t="n">
-        <v>45.78</v>
+        <v>-17.83</v>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1">
@@ -4811,29 +4819,29 @@
         <v>1</v>
       </c>
       <c r="C52" s="25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D52" s="25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E52" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F52" s="25" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G52" s="25" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
-        </is>
-      </c>
-      <c r="H52" s="27" t="n">
-        <v>4.23</v>
-      </c>
-      <c r="I52" s="27" t="n">
-        <v>23.53</v>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="H52" s="29" t="n">
+        <v>10.76</v>
+      </c>
+      <c r="I52" s="29" t="n">
+        <v>25.6</v>
       </c>
     </row>
   </sheetData>
@@ -4917,19 +4925,19 @@
         <v>1</v>
       </c>
       <c r="C3" s="36" t="n">
-        <v>100</v>
+        <v>73</v>
       </c>
       <c r="D3" s="36" t="n">
-        <v>100</v>
+        <v>73</v>
       </c>
       <c r="E3" s="36" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="F3" s="37" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G3" s="37" t="inlineStr">
@@ -4955,12 +4963,12 @@
       </c>
       <c r="E4" s="36" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="F4" s="37" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G4" s="37" t="inlineStr">
@@ -4979,19 +4987,19 @@
         <v>1</v>
       </c>
       <c r="C5" s="36" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D5" s="36" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E5" s="36" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="F5" s="37" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G5" s="37" t="inlineStr">
@@ -5003,26 +5011,26 @@
     <row r="6" ht="18" customHeight="1">
       <c r="A6" s="35" t="inlineStr">
         <is>
-          <t>원전</t>
+          <t>로봇</t>
         </is>
       </c>
       <c r="B6" s="36" t="n">
         <v>1</v>
       </c>
       <c r="C6" s="36" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="D6" s="36" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="E6" s="36" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="F6" s="37" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G6" s="37" t="inlineStr">
@@ -5034,26 +5042,26 @@
     <row r="7" ht="18" customHeight="1">
       <c r="A7" s="35" t="inlineStr">
         <is>
-          <t>로봇</t>
+          <t>조선</t>
         </is>
       </c>
       <c r="B7" s="36" t="n">
         <v>1</v>
       </c>
       <c r="C7" s="36" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D7" s="36" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="E7" s="36" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="F7" s="37" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G7" s="37" t="inlineStr">
@@ -5072,19 +5080,19 @@
         <v>1</v>
       </c>
       <c r="C8" s="36" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D8" s="36" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E8" s="36" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="F8" s="37" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G8" s="37" t="inlineStr">
@@ -5103,19 +5111,19 @@
         <v>1</v>
       </c>
       <c r="C9" s="36" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D9" s="36" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E9" s="36" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="F9" s="37" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G9" s="37" t="inlineStr">
@@ -5134,19 +5142,19 @@
         <v>1</v>
       </c>
       <c r="C10" s="36" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="D10" s="36" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="E10" s="36" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="F10" s="37" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G10" s="37" t="inlineStr">
@@ -5239,7 +5247,7 @@
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="26" t="inlineStr">
         <is>
-          <t>수소</t>
+          <t>원전</t>
         </is>
       </c>
       <c r="B14" s="25" t="n">
@@ -5266,7 +5274,7 @@
     <row r="15" ht="18" customHeight="1">
       <c r="A15" s="26" t="inlineStr">
         <is>
-          <t>태양광</t>
+          <t>수소</t>
         </is>
       </c>
       <c r="B15" s="25" t="n">
@@ -5293,7 +5301,7 @@
     <row r="16" ht="18" customHeight="1">
       <c r="A16" s="26" t="inlineStr">
         <is>
-          <t>게임</t>
+          <t>태양광</t>
         </is>
       </c>
       <c r="B16" s="25" t="n">
@@ -5320,7 +5328,7 @@
     <row r="17" ht="18" customHeight="1">
       <c r="A17" s="26" t="inlineStr">
         <is>
-          <t>엔터</t>
+          <t>게임</t>
         </is>
       </c>
       <c r="B17" s="25" t="n">
@@ -5347,7 +5355,7 @@
     <row r="18" ht="18" customHeight="1">
       <c r="A18" s="26" t="inlineStr">
         <is>
-          <t>핀테크</t>
+          <t>엔터</t>
         </is>
       </c>
       <c r="B18" s="25" t="n">
@@ -5374,7 +5382,7 @@
     <row r="19" ht="18" customHeight="1">
       <c r="A19" s="26" t="inlineStr">
         <is>
-          <t>클라우드</t>
+          <t>핀테크</t>
         </is>
       </c>
       <c r="B19" s="25" t="n">
@@ -5401,7 +5409,7 @@
     <row r="20" ht="18" customHeight="1">
       <c r="A20" s="26" t="inlineStr">
         <is>
-          <t>조선</t>
+          <t>클라우드</t>
         </is>
       </c>
       <c r="B20" s="25" t="n">

--- a/trend/stock_trend_history.xlsx
+++ b/trend/stock_trend_history.xlsx
@@ -57,13 +57,13 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="00E53935"/>
+      <color rgb="002563EB"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="002563EB"/>
+      <color rgb="00E53935"/>
       <sz val="10"/>
     </font>
     <font>
@@ -261,11 +261,11 @@
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -273,13 +273,13 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -694,7 +694,7 @@
     <row r="1" ht="36" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>📊 주식 트렌드 조기 감지 대시보드   |   최종 업데이트: 2026-06-26 06:54</t>
+          <t>📊 주식 트렌드 조기 감지 대시보드   |   최종 업데이트: 2026-06-27 06:54</t>
         </is>
       </c>
     </row>
@@ -708,7 +708,7 @@
       </c>
       <c r="E3" s="3" t="n"/>
       <c r="G3" s="5" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H3" s="3" t="n"/>
       <c r="J3" s="6" t="n">
@@ -787,21 +787,21 @@
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="11" t="inlineStr">
         <is>
-          <t>⚡ 최신(2026-06-26) 상위: 반도체  점수 73.0점</t>
+          <t>⚡ 최신(2026-06-27) 상위: 반도체  점수 101.0점</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1">
       <c r="A11" s="12" t="inlineStr">
         <is>
-          <t>⚡ 최신(2026-06-26) 상위: SK  점수 67.0점</t>
+          <t>⚡ 최신(2026-06-27) 상위: SK  점수 50.0점</t>
         </is>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1">
       <c r="A12" s="11" t="inlineStr">
         <is>
-          <t>⚡ 최신(2026-06-26) 상위: SK하이닉스  점수 41.0점</t>
+          <t>⚡ 최신(2026-06-27) 상위: SK하이닉스  점수 34.0점</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B14" s="15" t="n">
@@ -928,10 +928,10 @@
         </is>
       </c>
       <c r="D14" s="15" t="n">
-        <v>73</v>
+        <v>101</v>
       </c>
       <c r="E14" s="15" t="n">
-        <v>73</v>
+        <v>101</v>
       </c>
       <c r="F14" s="15" t="n">
         <v>0</v>
@@ -947,7 +947,7 @@
       </c>
       <c r="J14" s="17" t="inlineStr">
         <is>
-          <t>매일경제 기사 언급 / 매일경제 기사 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 헤드라인 언급 / 매일경제 헤드라인 언급</t>
+          <t>매일경제 헤드라인 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 기사 언급 / 매일경제 기사 언급 / 네이버뉴스 헤드라인 언급</t>
         </is>
       </c>
       <c r="K14" s="17" t="inlineStr">
@@ -959,7 +959,7 @@
     <row r="15" ht="18" customHeight="1">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B15" s="15" t="n">
@@ -971,10 +971,10 @@
         </is>
       </c>
       <c r="D15" s="15" t="n">
-        <v>67</v>
+        <v>50</v>
       </c>
       <c r="E15" s="15" t="n">
-        <v>67</v>
+        <v>50</v>
       </c>
       <c r="F15" s="15" t="n">
         <v>0</v>
@@ -983,26 +983,26 @@
         <v>0</v>
       </c>
       <c r="H15" s="18" t="n">
-        <v>20.51</v>
-      </c>
-      <c r="I15" s="18" t="n">
-        <v>24.89</v>
+        <v>-5.01</v>
+      </c>
+      <c r="I15" s="19" t="n">
+        <v>12.57</v>
       </c>
       <c r="J15" s="17" t="inlineStr">
         <is>
-          <t>Google 급상승 검색어 등장 (KR) / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 한국경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
+          <t>매일경제 헤드라인 언급 / 네이버뉴스 헤드라인 언급 / 매일경제 기사 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급</t>
         </is>
       </c>
       <c r="K15" s="17" t="inlineStr">
         <is>
-          <t>네이버, Google</t>
+          <t>네이버</t>
         </is>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
       <c r="A16" s="15" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B16" s="15" t="n">
@@ -1014,10 +1014,10 @@
         </is>
       </c>
       <c r="D16" s="15" t="n">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="E16" s="15" t="n">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="F16" s="15" t="n">
         <v>0</v>
@@ -1026,26 +1026,26 @@
         <v>0</v>
       </c>
       <c r="H16" s="18" t="n">
-        <v>13.06</v>
+        <v>-8.359999999999999</v>
       </c>
       <c r="I16" s="18" t="n">
-        <v>8.640000000000001</v>
+        <v>-3.29</v>
       </c>
       <c r="J16" s="17" t="inlineStr">
         <is>
-          <t>중요공시 1건 / Google 급상승 검색어 등장 (KR) / 매일경제 헤드라인 언급 / 한국경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
+          <t>중요공시 1건 / 매일경제 헤드라인 언급 / 네이버뉴스 헤드라인 언급 / 매일경제 기사 언급 / 매일경제 헤드라인 언급</t>
         </is>
       </c>
       <c r="K16" s="17" t="inlineStr">
         <is>
-          <t>공시, Google, 네이버</t>
+          <t>공시, 네이버</t>
         </is>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B17" s="15" t="n">
@@ -1057,10 +1057,10 @@
         </is>
       </c>
       <c r="D17" s="15" t="n">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="E17" s="15" t="n">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="F17" s="15" t="n">
         <v>0</v>
@@ -1069,14 +1069,14 @@
         <v>0</v>
       </c>
       <c r="H17" s="18" t="n">
-        <v>5.29</v>
-      </c>
-      <c r="I17" s="19" t="n">
-        <v>-1.1</v>
+        <v>-5.3</v>
+      </c>
+      <c r="I17" s="18" t="n">
+        <v>-4.1</v>
       </c>
       <c r="J17" s="17" t="inlineStr">
         <is>
-          <t>네이버뉴스 기사 언급 / 매일경제 기사 언급 / 한국경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급</t>
+          <t>매일경제 헤드라인 언급 / 네이버뉴스 헤드라인 언급 / 매일경제 기사 언급 / 매일경제 기사 언급 / 한국경제 헤드라인 언급</t>
         </is>
       </c>
       <c r="K17" s="17" t="inlineStr">
@@ -1088,7 +1088,7 @@
     <row r="18" ht="18" customHeight="1">
       <c r="A18" s="15" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B18" s="15" t="n">
@@ -1096,14 +1096,14 @@
       </c>
       <c r="C18" s="16" t="inlineStr">
         <is>
-          <t>바이오</t>
+          <t>LG</t>
         </is>
       </c>
       <c r="D18" s="15" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="E18" s="15" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="F18" s="15" t="n">
         <v>0</v>
@@ -1111,27 +1111,25 @@
       <c r="G18" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="H18" s="15" t="n">
+      <c r="H18" s="18" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="I18" s="18" t="n">
+        <v>-9.460000000000001</v>
+      </c>
+      <c r="J18" s="17" t="inlineStr">
+        <is>
+          <t>매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K18" s="17" t="n">
         <v/>
-      </c>
-      <c r="I18" s="15" t="n">
-        <v/>
-      </c>
-      <c r="J18" s="17" t="inlineStr">
-        <is>
-          <t>네이버뉴스 헤드라인 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 헤드라인 언급 / 한국경제 헤드라인 언급 / 네이버뉴스 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K18" s="17" t="inlineStr">
-        <is>
-          <t>네이버</t>
-        </is>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
       <c r="A19" s="15" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B19" s="15" t="n">
@@ -1139,14 +1137,14 @@
       </c>
       <c r="C19" s="16" t="inlineStr">
         <is>
-          <t>인공지능</t>
+          <t>바이오</t>
         </is>
       </c>
       <c r="D19" s="15" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="E19" s="15" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="F19" s="15" t="n">
         <v>0</v>
@@ -1162,7 +1160,7 @@
       </c>
       <c r="J19" s="17" t="inlineStr">
         <is>
-          <t>매일경제 기사 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 기사 언급 / 매일경제 기사 언급 / 매일경제 기사 언급</t>
+          <t>네이버뉴스 기사 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급</t>
         </is>
       </c>
       <c r="K19" s="17" t="inlineStr">
@@ -1174,7 +1172,7 @@
     <row r="20" ht="18" customHeight="1">
       <c r="A20" s="15" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B20" s="15" t="n">
@@ -1182,14 +1180,14 @@
       </c>
       <c r="C20" s="16" t="inlineStr">
         <is>
-          <t>카카오</t>
+          <t>인공지능</t>
         </is>
       </c>
       <c r="D20" s="15" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="E20" s="15" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="F20" s="15" t="n">
         <v>0</v>
@@ -1197,25 +1195,27 @@
       <c r="G20" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="H20" s="18" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="I20" s="19" t="n">
-        <v>-12.85</v>
+      <c r="H20" s="15" t="n">
+        <v/>
+      </c>
+      <c r="I20" s="15" t="n">
+        <v/>
       </c>
       <c r="J20" s="17" t="inlineStr">
         <is>
-          <t>매일경제 기사 언급 / 한국경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 기사 언급 / 한국경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K20" s="17" t="n">
-        <v/>
+          <t>매일경제 기사 언급 / 매일경제 기사 언급 / 매일경제 기사 언급 / 매일경제 기사 언급 / 매일경제 기사 언급</t>
+        </is>
+      </c>
+      <c r="K20" s="17" t="inlineStr">
+        <is>
+          <t>네이버</t>
+        </is>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
       <c r="A21" s="15" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B21" s="15" t="n">
@@ -1223,42 +1223,42 @@
       </c>
       <c r="C21" s="16" t="inlineStr">
         <is>
-          <t>현대차</t>
+          <t>파두</t>
         </is>
       </c>
       <c r="D21" s="15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E21" s="15" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="F21" s="15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G21" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" s="19" t="n">
-        <v>-1.18</v>
-      </c>
-      <c r="I21" s="19" t="n">
-        <v>-16.31</v>
+        <v>3</v>
+      </c>
+      <c r="H21" s="18" t="n">
+        <v>-5.14</v>
+      </c>
+      <c r="I21" s="18" t="n">
+        <v>-18.15</v>
       </c>
       <c r="J21" s="17" t="inlineStr">
         <is>
-          <t>매일경제 기사 언급 / 매일경제 헤드라인 언급 / 한국경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 네이버뉴스 기사 언급</t>
+          <t>중요공시 3건 / 중요공시 3일 +200% / 중요공시 7일 +50% / 네이버뉴스 헤드라인 언급 / 네이버뉴스 헤드라인 언급</t>
         </is>
       </c>
       <c r="K21" s="17" t="inlineStr">
         <is>
-          <t>네이버</t>
+          <t>공시, 네이버</t>
         </is>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
       <c r="A22" s="15" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B22" s="15" t="n">
@@ -1266,14 +1266,14 @@
       </c>
       <c r="C22" s="16" t="inlineStr">
         <is>
-          <t>로봇</t>
+          <t>전기차</t>
         </is>
       </c>
       <c r="D22" s="15" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E22" s="15" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F22" s="15" t="n">
         <v>0</v>
@@ -1289,7 +1289,7 @@
       </c>
       <c r="J22" s="17" t="inlineStr">
         <is>
-          <t>매일경제 헤드라인 언급 / 한국경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 한국경제 헤드라인 언급 / 매일경제 기사 언급</t>
+          <t>한국경제 헤드라인 언급 / 한국경제 헤드라인 언급 / 한국경제 헤드라인 언급 / 매일경제 기사 언급 / 한국경제 헤드라인 언급</t>
         </is>
       </c>
       <c r="K22" s="17" t="n">
@@ -1299,7 +1299,7 @@
     <row r="23" ht="18" customHeight="1">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B23" s="15" t="n">
@@ -1307,40 +1307,42 @@
       </c>
       <c r="C23" s="16" t="inlineStr">
         <is>
-          <t>LG</t>
+          <t>젠큐릭스</t>
         </is>
       </c>
       <c r="D23" s="15" t="n">
         <v>11</v>
       </c>
       <c r="E23" s="15" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="F23" s="15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G23" s="15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H23" s="18" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="I23" s="19" t="n">
-        <v>-9.550000000000001</v>
+        <v>-1.9</v>
+      </c>
+      <c r="I23" s="18" t="n">
+        <v>-12.13</v>
       </c>
       <c r="J23" s="17" t="inlineStr">
         <is>
-          <t>매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K23" s="17" t="n">
-        <v/>
+          <t>중요공시 3건 / 중요공시 3일 +200% / 중요공시 7일 +200% / 매일경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K23" s="17" t="inlineStr">
+        <is>
+          <t>공시</t>
+        </is>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B24" s="15" t="n">
@@ -1348,7 +1350,7 @@
       </c>
       <c r="C24" s="16" t="inlineStr">
         <is>
-          <t>카카오뱅크</t>
+          <t>LG이노텍</t>
         </is>
       </c>
       <c r="D24" s="15" t="n">
@@ -1364,26 +1366,24 @@
         <v>0</v>
       </c>
       <c r="H24" s="18" t="n">
-        <v>2</v>
-      </c>
-      <c r="I24" s="19" t="n">
-        <v>-10.7</v>
+        <v>-2.31</v>
+      </c>
+      <c r="I24" s="18" t="n">
+        <v>-18.69</v>
       </c>
       <c r="J24" s="17" t="inlineStr">
         <is>
-          <t>중요공시 1건 / 한국경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 기사 언급 / 매일경제 기사 언급</t>
-        </is>
-      </c>
-      <c r="K24" s="17" t="inlineStr">
-        <is>
-          <t>공시</t>
-        </is>
+          <t>매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K24" s="17" t="n">
+        <v/>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
       <c r="A25" s="15" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B25" s="15" t="n">
@@ -1391,7 +1391,7 @@
       </c>
       <c r="C25" s="16" t="inlineStr">
         <is>
-          <t>전기차</t>
+          <t>카카오</t>
         </is>
       </c>
       <c r="D25" s="15" t="n">
@@ -1406,27 +1406,25 @@
       <c r="G25" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="H25" s="15" t="n">
+      <c r="H25" s="18" t="n">
+        <v>-3.21</v>
+      </c>
+      <c r="I25" s="18" t="n">
+        <v>-12.19</v>
+      </c>
+      <c r="J25" s="17" t="inlineStr">
+        <is>
+          <t>매일경제 기사 언급 / 한국경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 기사 언급 / 매일경제 기사 언급</t>
+        </is>
+      </c>
+      <c r="K25" s="17" t="n">
         <v/>
-      </c>
-      <c r="I25" s="15" t="n">
-        <v/>
-      </c>
-      <c r="J25" s="17" t="inlineStr">
-        <is>
-          <t>네이버뉴스 헤드라인 언급 / 네이버뉴스 헤드라인 언급 / 매일경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K25" s="17" t="inlineStr">
-        <is>
-          <t>네이버</t>
-        </is>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
       <c r="A26" s="15" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B26" s="15" t="n">
@@ -1434,40 +1432,42 @@
       </c>
       <c r="C26" s="16" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>성호전자</t>
         </is>
       </c>
       <c r="D26" s="15" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E26" s="15" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="F26" s="15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G26" s="15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H26" s="19" t="n">
-        <v>-2.87</v>
-      </c>
-      <c r="I26" s="19" t="n">
-        <v>-9.960000000000001</v>
+        <v>0.52</v>
+      </c>
+      <c r="I26" s="18" t="n">
+        <v>-24.25</v>
       </c>
       <c r="J26" s="17" t="inlineStr">
         <is>
-          <t>한국경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K26" s="17" t="n">
-        <v/>
+          <t>중요공시 3건 / 중요공시 3일 +200% / 중요공시 7일 +50%</t>
+        </is>
+      </c>
+      <c r="K26" s="17" t="inlineStr">
+        <is>
+          <t>공시</t>
+        </is>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
       <c r="A27" s="15" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B27" s="15" t="n">
@@ -1475,7 +1475,7 @@
       </c>
       <c r="C27" s="16" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>스피어</t>
         </is>
       </c>
       <c r="D27" s="15" t="n">
@@ -1491,14 +1491,14 @@
         <v>3</v>
       </c>
       <c r="H27" s="18" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="I27" s="19" t="n">
-        <v>-13.46</v>
+        <v>-8.76</v>
+      </c>
+      <c r="I27" s="18" t="n">
+        <v>-31.49</v>
       </c>
       <c r="J27" s="17" t="inlineStr">
         <is>
-          <t>중요공시 3건 / 중요공시 3일 +200% / 중요공시 7일 +200%</t>
+          <t>중요공시 5건 / 중요공시 3일 +150% / 중요공시 7일 +67%</t>
         </is>
       </c>
       <c r="K27" s="17" t="inlineStr">
@@ -1510,7 +1510,7 @@
     <row r="28" ht="18" customHeight="1">
       <c r="A28" s="15" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B28" s="15" t="n">
@@ -1518,7 +1518,7 @@
       </c>
       <c r="C28" s="16" t="inlineStr">
         <is>
-          <t>에이팩트</t>
+          <t>페니트리움바이오</t>
         </is>
       </c>
       <c r="D28" s="15" t="n">
@@ -1533,15 +1533,15 @@
       <c r="G28" s="15" t="n">
         <v>3</v>
       </c>
-      <c r="H28" s="19" t="n">
-        <v>-4.27</v>
-      </c>
-      <c r="I28" s="19" t="n">
-        <v>-27.86</v>
+      <c r="H28" s="18" t="n">
+        <v>-2.96</v>
+      </c>
+      <c r="I28" s="18" t="n">
+        <v>-11.93</v>
       </c>
       <c r="J28" s="17" t="inlineStr">
         <is>
-          <t>중요공시 3건 / 중요공시 3일 +50% / 중요공시 7일 +50%</t>
+          <t>중요공시 3건 / 중요공시 3일 +200% / 중요공시 7일 +200%</t>
         </is>
       </c>
       <c r="K28" s="17" t="inlineStr">
@@ -1553,7 +1553,7 @@
     <row r="29" ht="18" customHeight="1">
       <c r="A29" s="15" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B29" s="15" t="n">
@@ -1561,14 +1561,14 @@
       </c>
       <c r="C29" s="16" t="inlineStr">
         <is>
-          <t>대한항공</t>
+          <t>한미반도체</t>
         </is>
       </c>
       <c r="D29" s="15" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E29" s="15" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F29" s="15" t="n">
         <v>0</v>
@@ -1577,26 +1577,26 @@
         <v>0</v>
       </c>
       <c r="H29" s="18" t="n">
-        <v>6.4</v>
+        <v>-5.68</v>
       </c>
       <c r="I29" s="18" t="n">
-        <v>0.87</v>
+        <v>-12.71</v>
       </c>
       <c r="J29" s="17" t="inlineStr">
         <is>
-          <t>중요공시 1건 / 매일경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
+          <t>네이버뉴스 기사 언급 / 한국경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 기사 언급</t>
         </is>
       </c>
       <c r="K29" s="17" t="inlineStr">
         <is>
-          <t>공시</t>
+          <t>네이버</t>
         </is>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
       <c r="A30" s="15" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B30" s="15" t="n">
@@ -1604,7 +1604,7 @@
       </c>
       <c r="C30" s="16" t="inlineStr">
         <is>
-          <t>제약</t>
+          <t>소룩스</t>
         </is>
       </c>
       <c r="D30" s="15" t="n">
@@ -1619,27 +1619,27 @@
       <c r="G30" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="H30" s="15" t="n">
-        <v/>
-      </c>
-      <c r="I30" s="15" t="n">
-        <v/>
+      <c r="H30" s="18" t="n">
+        <v>-4.21</v>
+      </c>
+      <c r="I30" s="19" t="n">
+        <v>19.47</v>
       </c>
       <c r="J30" s="17" t="inlineStr">
         <is>
-          <t>네이버뉴스 기사 언급 / 네이버뉴스 헤드라인 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 기사 언급</t>
+          <t>중요공시 3건 / 네이버뉴스 헤드라인 언급</t>
         </is>
       </c>
       <c r="K30" s="17" t="inlineStr">
         <is>
-          <t>네이버</t>
+          <t>공시, 네이버</t>
         </is>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
       <c r="A31" s="15" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B31" s="15" t="n">
@@ -1647,7 +1647,7 @@
       </c>
       <c r="C31" s="16" t="inlineStr">
         <is>
-          <t>LG전자</t>
+          <t>원익IPS</t>
         </is>
       </c>
       <c r="D31" s="15" t="n">
@@ -1663,24 +1663,26 @@
         <v>0</v>
       </c>
       <c r="H31" s="19" t="n">
-        <v>-0.73</v>
+        <v>5.88</v>
       </c>
       <c r="I31" s="19" t="n">
-        <v>-11.16</v>
+        <v>5</v>
       </c>
       <c r="J31" s="17" t="inlineStr">
         <is>
-          <t>매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 기사 언급</t>
-        </is>
-      </c>
-      <c r="K31" s="17" t="n">
-        <v/>
+          <t>네이버뉴스 헤드라인 언급 / 네이버뉴스 헤드라인 언급 / 매일경제 기사 언급</t>
+        </is>
+      </c>
+      <c r="K31" s="17" t="inlineStr">
+        <is>
+          <t>네이버</t>
+        </is>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
       <c r="A32" s="15" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B32" s="15" t="n">
@@ -1688,7 +1690,7 @@
       </c>
       <c r="C32" s="16" t="inlineStr">
         <is>
-          <t>철강</t>
+          <t>로봇</t>
         </is>
       </c>
       <c r="D32" s="15" t="n">
@@ -1711,60 +1713,60 @@
       </c>
       <c r="J32" s="17" t="inlineStr">
         <is>
-          <t>네이버뉴스 헤드라인 언급 / 네이버뉴스 기사 언급 / 매일경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K32" s="17" t="inlineStr">
+          <t>매일경제 헤드라인 언급 / 매일경제 기사 언급 / 매일경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K32" s="17" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="33" ht="18" customHeight="1">
+      <c r="A33" s="20" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="B33" s="20" t="n">
+        <v>20</v>
+      </c>
+      <c r="C33" s="21" t="inlineStr">
+        <is>
+          <t>광주신세계</t>
+        </is>
+      </c>
+      <c r="D33" s="20" t="n">
+        <v>6</v>
+      </c>
+      <c r="E33" s="20" t="n">
+        <v>6</v>
+      </c>
+      <c r="F33" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" s="22" t="n">
+        <v>29.98</v>
+      </c>
+      <c r="I33" s="22" t="n">
+        <v>50.71</v>
+      </c>
+      <c r="J33" s="23" t="inlineStr">
+        <is>
+          <t>네이버 검색 당일 +654% / 매일경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K33" s="23" t="inlineStr">
         <is>
           <t>네이버</t>
         </is>
-      </c>
-    </row>
-    <row r="33" ht="18" customHeight="1">
-      <c r="A33" s="15" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="B33" s="15" t="n">
-        <v>20</v>
-      </c>
-      <c r="C33" s="16" t="inlineStr">
-        <is>
-          <t>조선</t>
-        </is>
-      </c>
-      <c r="D33" s="15" t="n">
-        <v>7</v>
-      </c>
-      <c r="E33" s="15" t="n">
-        <v>7</v>
-      </c>
-      <c r="F33" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G33" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H33" s="15" t="n">
-        <v/>
-      </c>
-      <c r="I33" s="15" t="n">
-        <v/>
-      </c>
-      <c r="J33" s="17" t="inlineStr">
-        <is>
-          <t>매일경제 헤드라인 언급 / 한국경제 헤드라인 언급 / 매일경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K33" s="17" t="n">
-        <v/>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
       <c r="A34" s="20" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B34" s="20" t="n">
@@ -1772,42 +1774,42 @@
       </c>
       <c r="C34" s="21" t="inlineStr">
         <is>
-          <t>비투엔</t>
+          <t>다스코</t>
         </is>
       </c>
       <c r="D34" s="20" t="n">
         <v>6</v>
       </c>
       <c r="E34" s="20" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F34" s="20" t="n">
         <v>0</v>
       </c>
       <c r="G34" s="20" t="n">
-        <v>3</v>
-      </c>
-      <c r="H34" s="22" t="n">
-        <v>-6.29</v>
-      </c>
-      <c r="I34" s="23" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="J34" s="24" t="inlineStr">
-        <is>
-          <t>중요공시 5건 / 중요공시 7일 +400%</t>
-        </is>
-      </c>
-      <c r="K34" s="24" t="inlineStr">
-        <is>
-          <t>공시</t>
+        <v>0</v>
+      </c>
+      <c r="H34" s="24" t="n">
+        <v>-16.32</v>
+      </c>
+      <c r="I34" s="24" t="n">
+        <v>-1.01</v>
+      </c>
+      <c r="J34" s="23" t="inlineStr">
+        <is>
+          <t>네이버 검색 당일 +58% / 중요공시 1건 / 매일경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K34" s="23" t="inlineStr">
+        <is>
+          <t>공시, 네이버</t>
         </is>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
       <c r="A35" s="20" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B35" s="20" t="n">
@@ -1815,42 +1817,40 @@
       </c>
       <c r="C35" s="21" t="inlineStr">
         <is>
-          <t>스피어</t>
+          <t>LG전자</t>
         </is>
       </c>
       <c r="D35" s="20" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E35" s="20" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F35" s="20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G35" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H35" s="22" t="n">
-        <v>-11.4</v>
-      </c>
-      <c r="I35" s="22" t="n">
-        <v>-30.17</v>
-      </c>
-      <c r="J35" s="24" t="inlineStr">
-        <is>
-          <t>중요공시 3건 / 중요공시 3일 +50%</t>
-        </is>
-      </c>
-      <c r="K35" s="24" t="inlineStr">
-        <is>
-          <t>공시</t>
-        </is>
+      <c r="H35" s="24" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="I35" s="24" t="n">
+        <v>-7.38</v>
+      </c>
+      <c r="J35" s="23" t="inlineStr">
+        <is>
+          <t>한국경제 헤드라인 언급 / 매일경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K35" s="23" t="n">
+        <v/>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
       <c r="A36" s="20" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B36" s="20" t="n">
@@ -1858,14 +1858,14 @@
       </c>
       <c r="C36" s="21" t="inlineStr">
         <is>
-          <t>Netflix</t>
+          <t>대한항공</t>
         </is>
       </c>
       <c r="D36" s="20" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E36" s="20" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F36" s="20" t="n">
         <v>0</v>
@@ -1873,27 +1873,27 @@
       <c r="G36" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H36" s="20" t="n">
-        <v/>
-      </c>
-      <c r="I36" s="20" t="n">
-        <v/>
-      </c>
-      <c r="J36" s="24" t="inlineStr">
-        <is>
-          <t>Google 급상승 검색어 등장 (US)</t>
-        </is>
-      </c>
-      <c r="K36" s="24" t="inlineStr">
-        <is>
-          <t>Google</t>
+      <c r="H36" s="24" t="n">
+        <v>-3.61</v>
+      </c>
+      <c r="I36" s="22" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="J36" s="23" t="inlineStr">
+        <is>
+          <t>중요공시 3건 / 매일경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K36" s="23" t="inlineStr">
+        <is>
+          <t>공시</t>
         </is>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
       <c r="A37" s="20" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B37" s="20" t="n">
@@ -1901,40 +1901,42 @@
       </c>
       <c r="C37" s="21" t="inlineStr">
         <is>
-          <t>KT</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="D37" s="20" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E37" s="20" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F37" s="20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G37" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H37" s="23" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="I37" s="22" t="n">
-        <v>-2.8</v>
-      </c>
-      <c r="J37" s="24" t="inlineStr">
-        <is>
-          <t>한국경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K37" s="24" t="n">
-        <v/>
+        <v>3</v>
+      </c>
+      <c r="H37" s="24" t="n">
+        <v>-8.41</v>
+      </c>
+      <c r="I37" s="24" t="n">
+        <v>-14.4</v>
+      </c>
+      <c r="J37" s="23" t="inlineStr">
+        <is>
+          <t>중요공시 2건 / 중요공시 3일 +100% / 중요공시 7일 +100%</t>
+        </is>
+      </c>
+      <c r="K37" s="23" t="inlineStr">
+        <is>
+          <t>공시</t>
+        </is>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
       <c r="A38" s="20" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B38" s="20" t="n">
@@ -1942,42 +1944,42 @@
       </c>
       <c r="C38" s="21" t="inlineStr">
         <is>
-          <t>프로브잇</t>
+          <t>에이팩트</t>
         </is>
       </c>
       <c r="D38" s="20" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E38" s="20" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F38" s="20" t="n">
         <v>0</v>
       </c>
       <c r="G38" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H38" s="22" t="n">
-        <v>-44.44</v>
-      </c>
-      <c r="I38" s="22" t="n">
-        <v>-97.55</v>
-      </c>
-      <c r="J38" s="24" t="inlineStr">
-        <is>
-          <t>네이버 검색 당일 +1686% / 중요공시 1건</t>
-        </is>
-      </c>
-      <c r="K38" s="24" t="inlineStr">
-        <is>
-          <t>공시, 네이버</t>
+        <v>3</v>
+      </c>
+      <c r="H38" s="24" t="n">
+        <v>-6.74</v>
+      </c>
+      <c r="I38" s="24" t="n">
+        <v>-26.62</v>
+      </c>
+      <c r="J38" s="23" t="inlineStr">
+        <is>
+          <t>중요공시 3건 / 중요공시 7일 +50%</t>
+        </is>
+      </c>
+      <c r="K38" s="23" t="inlineStr">
+        <is>
+          <t>공시</t>
         </is>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
       <c r="A39" s="20" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B39" s="20" t="n">
@@ -1985,14 +1987,14 @@
       </c>
       <c r="C39" s="21" t="inlineStr">
         <is>
-          <t>헝셩그룹</t>
+          <t>KB금융</t>
         </is>
       </c>
       <c r="D39" s="20" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E39" s="20" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F39" s="20" t="n">
         <v>0</v>
@@ -2000,27 +2002,27 @@
       <c r="G39" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H39" s="22" t="n">
-        <v>-6.53</v>
-      </c>
-      <c r="I39" s="23" t="n">
-        <v>11.09</v>
-      </c>
-      <c r="J39" s="24" t="inlineStr">
-        <is>
-          <t>네이버 검색 당일 +156% / 중요공시 2건</t>
-        </is>
-      </c>
-      <c r="K39" s="24" t="inlineStr">
-        <is>
-          <t>공시, 네이버</t>
+      <c r="H39" s="24" t="n">
+        <v>-1.71</v>
+      </c>
+      <c r="I39" s="24" t="n">
+        <v>-5.69</v>
+      </c>
+      <c r="J39" s="23" t="inlineStr">
+        <is>
+          <t>중요공시 1건 / 한국경제 헤드라인 언급 / 매일경제 기사 언급 / 매일경제 기사 언급</t>
+        </is>
+      </c>
+      <c r="K39" s="23" t="inlineStr">
+        <is>
+          <t>공시</t>
         </is>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
       <c r="A40" s="20" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B40" s="20" t="n">
@@ -2028,14 +2030,14 @@
       </c>
       <c r="C40" s="21" t="inlineStr">
         <is>
-          <t>베셀</t>
+          <t>카카오뱅크</t>
         </is>
       </c>
       <c r="D40" s="20" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E40" s="20" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F40" s="20" t="n">
         <v>0</v>
@@ -2043,27 +2045,27 @@
       <c r="G40" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H40" s="23" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="I40" s="23" t="n">
-        <v>7.08</v>
-      </c>
-      <c r="J40" s="24" t="inlineStr">
-        <is>
-          <t>네이버 검색 당일 +134% / 중요공시 2건</t>
-        </is>
-      </c>
-      <c r="K40" s="24" t="inlineStr">
-        <is>
-          <t>공시, 네이버</t>
+      <c r="H40" s="24" t="n">
+        <v>-3.42</v>
+      </c>
+      <c r="I40" s="24" t="n">
+        <v>-10.84</v>
+      </c>
+      <c r="J40" s="23" t="inlineStr">
+        <is>
+          <t>중요공시 1건 / 매일경제 헤드라인 언급 / 매일경제 기사 언급 / 매일경제 기사 언급</t>
+        </is>
+      </c>
+      <c r="K40" s="23" t="inlineStr">
+        <is>
+          <t>공시</t>
         </is>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
       <c r="A41" s="20" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B41" s="20" t="n">
@@ -2071,644 +2073,640 @@
       </c>
       <c r="C41" s="21" t="inlineStr">
         <is>
-          <t>다스코</t>
+          <t>게임</t>
         </is>
       </c>
       <c r="D41" s="20" t="n">
+        <v>6</v>
+      </c>
+      <c r="E41" s="20" t="n">
+        <v>6</v>
+      </c>
+      <c r="F41" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G41" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" s="20" t="n">
+        <v/>
+      </c>
+      <c r="I41" s="20" t="n">
+        <v/>
+      </c>
+      <c r="J41" s="23" t="inlineStr">
+        <is>
+          <t>매일경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K41" s="23" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="42" ht="18" customHeight="1">
+      <c r="A42" s="20" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="B42" s="20" t="n">
+        <v>29</v>
+      </c>
+      <c r="C42" s="21" t="inlineStr">
+        <is>
+          <t>제약</t>
+        </is>
+      </c>
+      <c r="D42" s="20" t="n">
+        <v>6</v>
+      </c>
+      <c r="E42" s="20" t="n">
+        <v>6</v>
+      </c>
+      <c r="F42" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G42" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" s="20" t="n">
+        <v/>
+      </c>
+      <c r="I42" s="20" t="n">
+        <v/>
+      </c>
+      <c r="J42" s="23" t="inlineStr">
+        <is>
+          <t>네이버뉴스 기사 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 기사 언급 / 한국경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K42" s="23" t="inlineStr">
+        <is>
+          <t>네이버</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="18" customHeight="1">
+      <c r="A43" s="20" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="B43" s="20" t="n">
+        <v>30</v>
+      </c>
+      <c r="C43" s="21" t="inlineStr">
+        <is>
+          <t>차바이오텍</t>
+        </is>
+      </c>
+      <c r="D43" s="20" t="n">
+        <v>5</v>
+      </c>
+      <c r="E43" s="20" t="n">
+        <v>3</v>
+      </c>
+      <c r="F43" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="G43" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" s="24" t="n">
+        <v>-4.12</v>
+      </c>
+      <c r="I43" s="24" t="n">
+        <v>-12.15</v>
+      </c>
+      <c r="J43" s="23" t="inlineStr">
+        <is>
+          <t>중요공시 4건 / 중요공시 3일 +300%</t>
+        </is>
+      </c>
+      <c r="K43" s="23" t="inlineStr">
+        <is>
+          <t>공시</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="18" customHeight="1">
+      <c r="A44" s="20" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="B44" s="20" t="n">
+        <v>31</v>
+      </c>
+      <c r="C44" s="21" t="inlineStr">
+        <is>
+          <t>리가켐바이오</t>
+        </is>
+      </c>
+      <c r="D44" s="20" t="n">
+        <v>5</v>
+      </c>
+      <c r="E44" s="20" t="n">
+        <v>5</v>
+      </c>
+      <c r="F44" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G44" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" s="24" t="n">
+        <v>-8.279999999999999</v>
+      </c>
+      <c r="I44" s="22" t="n">
+        <v>6.17</v>
+      </c>
+      <c r="J44" s="23" t="inlineStr">
+        <is>
+          <t>중요공시 2건 / 매일경제 헤드라인 언급 / 매일경제 기사 언급</t>
+        </is>
+      </c>
+      <c r="K44" s="23" t="inlineStr">
+        <is>
+          <t>공시</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="18" customHeight="1">
+      <c r="A45" s="20" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="B45" s="20" t="n">
+        <v>32</v>
+      </c>
+      <c r="C45" s="21" t="inlineStr">
+        <is>
+          <t>헝셩그룹</t>
+        </is>
+      </c>
+      <c r="D45" s="20" t="n">
         <v>4</v>
       </c>
-      <c r="E41" s="20" t="n">
+      <c r="E45" s="20" t="n">
         <v>4</v>
       </c>
-      <c r="F41" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G41" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H41" s="23" t="n">
-        <v>29.91</v>
-      </c>
-      <c r="I41" s="23" t="n">
-        <v>53.75</v>
-      </c>
-      <c r="J41" s="24" t="inlineStr">
+      <c r="F45" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G45" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" s="24" t="n">
+        <v>-2.71</v>
+      </c>
+      <c r="I45" s="22" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="J45" s="23" t="inlineStr">
+        <is>
+          <t>네이버 검색 당일 +241% / 중요공시 2건</t>
+        </is>
+      </c>
+      <c r="K45" s="23" t="inlineStr">
+        <is>
+          <t>공시, 네이버</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="18" customHeight="1">
+      <c r="A46" s="20" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="B46" s="20" t="n">
+        <v>33</v>
+      </c>
+      <c r="C46" s="21" t="inlineStr">
+        <is>
+          <t>크리스탈신소재</t>
+        </is>
+      </c>
+      <c r="D46" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="E46" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="F46" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G46" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" s="22" t="n">
+        <v>18.81</v>
+      </c>
+      <c r="I46" s="24" t="n">
+        <v>-28.03</v>
+      </c>
+      <c r="J46" s="23" t="inlineStr">
+        <is>
+          <t>네이버 검색 당일 +178% / 중요공시 1건</t>
+        </is>
+      </c>
+      <c r="K46" s="23" t="inlineStr">
+        <is>
+          <t>공시, 네이버</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="18" customHeight="1">
+      <c r="A47" s="20" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="B47" s="20" t="n">
+        <v>34</v>
+      </c>
+      <c r="C47" s="21" t="inlineStr">
+        <is>
+          <t>베셀</t>
+        </is>
+      </c>
+      <c r="D47" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="E47" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="F47" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G47" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H47" s="22" t="n">
+        <v>9.69</v>
+      </c>
+      <c r="I47" s="22" t="n">
+        <v>34.27</v>
+      </c>
+      <c r="J47" s="23" t="inlineStr">
+        <is>
+          <t>네이버 검색 당일 +169% / 중요공시 2건</t>
+        </is>
+      </c>
+      <c r="K47" s="23" t="inlineStr">
+        <is>
+          <t>공시, 네이버</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="18" customHeight="1">
+      <c r="A48" s="20" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="B48" s="20" t="n">
+        <v>35</v>
+      </c>
+      <c r="C48" s="21" t="inlineStr">
+        <is>
+          <t>금호건설</t>
+        </is>
+      </c>
+      <c r="D48" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="E48" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="F48" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G48" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H48" s="22" t="n">
+        <v>30</v>
+      </c>
+      <c r="I48" s="22" t="n">
+        <v>57.86</v>
+      </c>
+      <c r="J48" s="23" t="inlineStr">
+        <is>
+          <t>네이버 검색 당일 +142% / 중요공시 1건</t>
+        </is>
+      </c>
+      <c r="K48" s="23" t="inlineStr">
+        <is>
+          <t>공시, 네이버</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="18" customHeight="1">
+      <c r="A49" s="20" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="B49" s="20" t="n">
+        <v>36</v>
+      </c>
+      <c r="C49" s="21" t="inlineStr">
+        <is>
+          <t>시너지이노베이션</t>
+        </is>
+      </c>
+      <c r="D49" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="E49" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="F49" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G49" s="20" t="n">
+        <v>3</v>
+      </c>
+      <c r="H49" s="24" t="n">
+        <v>-1.93</v>
+      </c>
+      <c r="I49" s="24" t="n">
+        <v>-7.84</v>
+      </c>
+      <c r="J49" s="23" t="inlineStr">
+        <is>
+          <t>중요공시 2건 / 중요공시 7일 +100%</t>
+        </is>
+      </c>
+      <c r="K49" s="23" t="inlineStr">
+        <is>
+          <t>공시</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="18" customHeight="1">
+      <c r="A50" s="20" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="B50" s="20" t="n">
+        <v>37</v>
+      </c>
+      <c r="C50" s="21" t="inlineStr">
+        <is>
+          <t>에코프로</t>
+        </is>
+      </c>
+      <c r="D50" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="E50" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="F50" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G50" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H50" s="24" t="n">
+        <v>-6.47</v>
+      </c>
+      <c r="I50" s="24" t="n">
+        <v>-17.76</v>
+      </c>
+      <c r="J50" s="23" t="inlineStr">
+        <is>
+          <t>중요공시 1건 / 네이버뉴스 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K50" s="23" t="inlineStr">
+        <is>
+          <t>공시, 네이버</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="18" customHeight="1">
+      <c r="A51" s="20" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="B51" s="20" t="n">
+        <v>38</v>
+      </c>
+      <c r="C51" s="21" t="inlineStr">
+        <is>
+          <t>심텍</t>
+        </is>
+      </c>
+      <c r="D51" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="E51" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="F51" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G51" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H51" s="24" t="n">
+        <v>-1.11</v>
+      </c>
+      <c r="I51" s="22" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J51" s="23" t="inlineStr">
+        <is>
+          <t>중요공시 1건 / 네이버뉴스 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K51" s="23" t="inlineStr">
+        <is>
+          <t>공시, 네이버</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="18" customHeight="1">
+      <c r="A52" s="20" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="B52" s="20" t="n">
+        <v>39</v>
+      </c>
+      <c r="C52" s="21" t="inlineStr">
+        <is>
+          <t>SK텔레콤</t>
+        </is>
+      </c>
+      <c r="D52" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="E52" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="F52" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G52" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H52" s="24" t="n">
+        <v>-0.88</v>
+      </c>
+      <c r="I52" s="24" t="n">
+        <v>-4.53</v>
+      </c>
+      <c r="J52" s="23" t="inlineStr">
         <is>
           <t>중요공시 1건 / 매일경제 헤드라인 언급</t>
         </is>
       </c>
-      <c r="K41" s="24" t="inlineStr">
+      <c r="K52" s="23" t="inlineStr">
         <is>
           <t>공시</t>
         </is>
       </c>
     </row>
-    <row r="42" ht="18" customHeight="1">
-      <c r="A42" s="25" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="B42" s="25" t="n">
-        <v>29</v>
-      </c>
-      <c r="C42" s="26" t="inlineStr">
-        <is>
-          <t>노블엠앤비</t>
-        </is>
-      </c>
-      <c r="D42" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="E42" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="F42" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="G42" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="H42" s="27" t="n">
-        <v>-38.1</v>
-      </c>
-      <c r="I42" s="27" t="n">
-        <v>-96.84</v>
-      </c>
-      <c r="J42" s="28" t="inlineStr">
-        <is>
-          <t>네이버 검색 당일 +614%</t>
-        </is>
-      </c>
-      <c r="K42" s="28" t="inlineStr">
+    <row r="53" ht="18" customHeight="1">
+      <c r="A53" s="20" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="B53" s="20" t="n">
+        <v>40</v>
+      </c>
+      <c r="C53" s="21" t="inlineStr">
+        <is>
+          <t>카카오게임즈</t>
+        </is>
+      </c>
+      <c r="D53" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="E53" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="F53" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G53" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H53" s="24" t="n">
+        <v>-9.41</v>
+      </c>
+      <c r="I53" s="24" t="n">
+        <v>-21.34</v>
+      </c>
+      <c r="J53" s="23" t="inlineStr">
+        <is>
+          <t>중요공시 1건 / 한국경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K53" s="23" t="inlineStr">
+        <is>
+          <t>공시</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="18" customHeight="1">
+      <c r="A54" s="20" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="B54" s="20" t="n">
+        <v>41</v>
+      </c>
+      <c r="C54" s="21" t="inlineStr">
+        <is>
+          <t>방산</t>
+        </is>
+      </c>
+      <c r="D54" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="E54" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="F54" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G54" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H54" s="20" t="n">
+        <v/>
+      </c>
+      <c r="I54" s="20" t="n">
+        <v/>
+      </c>
+      <c r="J54" s="23" t="inlineStr">
+        <is>
+          <t>네이버뉴스 기사 언급 / 매일경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K54" s="23" t="inlineStr">
         <is>
           <t>네이버</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="18" customHeight="1">
-      <c r="A43" s="25" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="B43" s="25" t="n">
-        <v>30</v>
-      </c>
-      <c r="C43" s="26" t="inlineStr">
-        <is>
-          <t>국순당</t>
-        </is>
-      </c>
-      <c r="D43" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="E43" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="F43" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="G43" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="H43" s="27" t="n">
-        <v>-13.18</v>
-      </c>
-      <c r="I43" s="29" t="n">
-        <v>12.52</v>
-      </c>
-      <c r="J43" s="28" t="inlineStr">
-        <is>
-          <t>네이버 검색 당일 +420%</t>
-        </is>
-      </c>
-      <c r="K43" s="28" t="inlineStr">
-        <is>
-          <t>네이버</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="18" customHeight="1">
-      <c r="A44" s="25" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="B44" s="25" t="n">
-        <v>31</v>
-      </c>
-      <c r="C44" s="26" t="inlineStr">
-        <is>
-          <t>바이온</t>
-        </is>
-      </c>
-      <c r="D44" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="E44" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="F44" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="G44" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="H44" s="27" t="n">
-        <v>-41.67</v>
-      </c>
-      <c r="I44" s="27" t="n">
-        <v>-97.68000000000001</v>
-      </c>
-      <c r="J44" s="28" t="inlineStr">
-        <is>
-          <t>네이버 검색 당일 +402%</t>
-        </is>
-      </c>
-      <c r="K44" s="28" t="inlineStr">
-        <is>
-          <t>네이버</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="18" customHeight="1">
-      <c r="A45" s="25" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="B45" s="25" t="n">
-        <v>32</v>
-      </c>
-      <c r="C45" s="26" t="inlineStr">
-        <is>
-          <t>서암기계공업</t>
-        </is>
-      </c>
-      <c r="D45" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="E45" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="F45" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="G45" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="H45" s="27" t="n">
-        <v>-26.92</v>
-      </c>
-      <c r="I45" s="27" t="n">
-        <v>-5.42</v>
-      </c>
-      <c r="J45" s="28" t="inlineStr">
-        <is>
-          <t>네이버 검색 당일 +350%</t>
-        </is>
-      </c>
-      <c r="K45" s="28" t="inlineStr">
-        <is>
-          <t>네이버</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="18" customHeight="1">
-      <c r="A46" s="25" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="B46" s="25" t="n">
-        <v>33</v>
-      </c>
-      <c r="C46" s="26" t="inlineStr">
-        <is>
-          <t>조아제약</t>
-        </is>
-      </c>
-      <c r="D46" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="E46" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="F46" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="G46" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="H46" s="27" t="n">
-        <v>-21.89</v>
-      </c>
-      <c r="I46" s="29" t="n">
-        <v>19.76</v>
-      </c>
-      <c r="J46" s="28" t="inlineStr">
-        <is>
-          <t>네이버 검색 당일 +287%</t>
-        </is>
-      </c>
-      <c r="K46" s="28" t="inlineStr">
-        <is>
-          <t>네이버</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="18" customHeight="1">
-      <c r="A47" s="25" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="B47" s="25" t="n">
-        <v>34</v>
-      </c>
-      <c r="C47" s="26" t="inlineStr">
-        <is>
-          <t>부국철강</t>
-        </is>
-      </c>
-      <c r="D47" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="E47" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="F47" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="G47" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="H47" s="27" t="n">
-        <v>-20.26</v>
-      </c>
-      <c r="I47" s="29" t="n">
-        <v>6.78</v>
-      </c>
-      <c r="J47" s="28" t="inlineStr">
-        <is>
-          <t>네이버 검색 당일 +260%</t>
-        </is>
-      </c>
-      <c r="K47" s="28" t="inlineStr">
-        <is>
-          <t>네이버</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="18" customHeight="1">
-      <c r="A48" s="25" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="B48" s="25" t="n">
-        <v>35</v>
-      </c>
-      <c r="C48" s="26" t="inlineStr">
-        <is>
-          <t>위지트</t>
-        </is>
-      </c>
-      <c r="D48" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="E48" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="F48" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="G48" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="H48" s="27" t="n">
-        <v>-7.25</v>
-      </c>
-      <c r="I48" s="29" t="n">
-        <v>33.18</v>
-      </c>
-      <c r="J48" s="28" t="inlineStr">
-        <is>
-          <t>네이버 검색 당일 +223%</t>
-        </is>
-      </c>
-      <c r="K48" s="28" t="inlineStr">
-        <is>
-          <t>네이버</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="18" customHeight="1">
-      <c r="A49" s="25" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="B49" s="25" t="n">
-        <v>36</v>
-      </c>
-      <c r="C49" s="26" t="inlineStr">
-        <is>
-          <t>보해양조</t>
-        </is>
-      </c>
-      <c r="D49" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="E49" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="F49" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="G49" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="H49" s="27" t="n">
-        <v>-30</v>
-      </c>
-      <c r="I49" s="29" t="n">
-        <v>68.59999999999999</v>
-      </c>
-      <c r="J49" s="28" t="inlineStr">
-        <is>
-          <t>네이버 검색 당일 +220%</t>
-        </is>
-      </c>
-      <c r="K49" s="28" t="inlineStr">
-        <is>
-          <t>네이버</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="18" customHeight="1">
-      <c r="A50" s="25" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="B50" s="25" t="n">
-        <v>37</v>
-      </c>
-      <c r="C50" s="26" t="inlineStr">
-        <is>
-          <t>디와이에이</t>
-        </is>
-      </c>
-      <c r="D50" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="E50" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="F50" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="G50" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="H50" s="29" t="n">
-        <v>3.83</v>
-      </c>
-      <c r="I50" s="27" t="n">
-        <v>-4.95</v>
-      </c>
-      <c r="J50" s="28" t="inlineStr">
-        <is>
-          <t>네이버 검색 당일 +212%</t>
-        </is>
-      </c>
-      <c r="K50" s="28" t="inlineStr">
-        <is>
-          <t>네이버</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="18" customHeight="1">
-      <c r="A51" s="25" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="B51" s="25" t="n">
-        <v>38</v>
-      </c>
-      <c r="C51" s="26" t="inlineStr">
-        <is>
-          <t>남화산업</t>
-        </is>
-      </c>
-      <c r="D51" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="E51" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="F51" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="G51" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="H51" s="27" t="n">
-        <v>-21.05</v>
-      </c>
-      <c r="I51" s="29" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="J51" s="28" t="inlineStr">
-        <is>
-          <t>네이버 검색 당일 +194%</t>
-        </is>
-      </c>
-      <c r="K51" s="28" t="inlineStr">
-        <is>
-          <t>네이버</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="18" customHeight="1">
-      <c r="A52" s="25" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="B52" s="25" t="n">
-        <v>39</v>
-      </c>
-      <c r="C52" s="26" t="inlineStr">
-        <is>
-          <t>키스트론</t>
-        </is>
-      </c>
-      <c r="D52" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="E52" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="F52" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="G52" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="H52" s="29" t="n">
-        <v>10.76</v>
-      </c>
-      <c r="I52" s="29" t="n">
-        <v>25.6</v>
-      </c>
-      <c r="J52" s="28" t="inlineStr">
-        <is>
-          <t>네이버 검색 당일 +171%</t>
-        </is>
-      </c>
-      <c r="K52" s="28" t="inlineStr">
-        <is>
-          <t>네이버</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="18" customHeight="1">
-      <c r="A53" s="25" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="B53" s="25" t="n">
-        <v>40</v>
-      </c>
-      <c r="C53" s="26" t="inlineStr">
-        <is>
-          <t>모헨즈</t>
-        </is>
-      </c>
-      <c r="D53" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="E53" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="F53" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="G53" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="H53" s="27" t="n">
-        <v>-26.57</v>
-      </c>
-      <c r="I53" s="29" t="n">
-        <v>17.87</v>
-      </c>
-      <c r="J53" s="28" t="inlineStr">
-        <is>
-          <t>네이버 검색 당일 +160%</t>
-        </is>
-      </c>
-      <c r="K53" s="28" t="inlineStr">
-        <is>
-          <t>네이버</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="18" customHeight="1">
-      <c r="A54" s="25" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="B54" s="25" t="n">
-        <v>41</v>
-      </c>
-      <c r="C54" s="26" t="inlineStr">
-        <is>
-          <t>동양파일</t>
-        </is>
-      </c>
-      <c r="D54" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="E54" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="F54" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="G54" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="H54" s="27" t="n">
-        <v>-9.130000000000001</v>
-      </c>
-      <c r="I54" s="29" t="n">
-        <v>15.69</v>
-      </c>
-      <c r="J54" s="28" t="inlineStr">
-        <is>
-          <t>네이버 검색 당일 +156%</t>
-        </is>
-      </c>
-      <c r="K54" s="28" t="inlineStr">
-        <is>
-          <t>네이버</t>
-        </is>
-      </c>
-    </row>
     <row r="55" ht="18" customHeight="1">
-      <c r="A55" s="25" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="B55" s="25" t="n">
+      <c r="A55" s="20" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="B55" s="20" t="n">
         <v>42</v>
       </c>
-      <c r="C55" s="26" t="inlineStr">
-        <is>
-          <t>삼기에너지솔루션즈</t>
-        </is>
-      </c>
-      <c r="D55" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="E55" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="F55" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="G55" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="H55" s="29" t="n">
-        <v>29.96</v>
-      </c>
-      <c r="I55" s="29" t="n">
-        <v>43.5</v>
-      </c>
-      <c r="J55" s="28" t="inlineStr">
-        <is>
-          <t>네이버 검색 당일 +106%</t>
-        </is>
-      </c>
-      <c r="K55" s="28" t="inlineStr">
-        <is>
-          <t>네이버</t>
-        </is>
+      <c r="C55" s="21" t="inlineStr">
+        <is>
+          <t>조선</t>
+        </is>
+      </c>
+      <c r="D55" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="E55" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="F55" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G55" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H55" s="20" t="n">
+        <v/>
+      </c>
+      <c r="I55" s="20" t="n">
+        <v/>
+      </c>
+      <c r="J55" s="23" t="inlineStr">
+        <is>
+          <t>매일경제 기사 언급 / 매일경제 헤드라인 언급 / 매일경제 기사 언급</t>
+        </is>
+      </c>
+      <c r="K55" s="23" t="n">
+        <v/>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1">
       <c r="A56" s="25" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B56" s="25" t="n">
@@ -2716,7 +2714,7 @@
       </c>
       <c r="C56" s="26" t="inlineStr">
         <is>
-          <t>소룩스</t>
+          <t>프로브잇</t>
         </is>
       </c>
       <c r="D56" s="25" t="n">
@@ -2732,26 +2730,26 @@
         <v>0</v>
       </c>
       <c r="H56" s="27" t="n">
-        <v>-1.38</v>
-      </c>
-      <c r="I56" s="29" t="n">
-        <v>20.25</v>
+        <v>-40</v>
+      </c>
+      <c r="I56" s="27" t="n">
+        <v>-98.53</v>
       </c>
       <c r="J56" s="28" t="inlineStr">
         <is>
-          <t>중요공시 3건</t>
+          <t>네이버 검색 당일 +1853%</t>
         </is>
       </c>
       <c r="K56" s="28" t="inlineStr">
         <is>
-          <t>공시</t>
+          <t>네이버</t>
         </is>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1">
       <c r="A57" s="25" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B57" s="25" t="n">
@@ -2759,7 +2757,7 @@
       </c>
       <c r="C57" s="26" t="inlineStr">
         <is>
-          <t>샤페론</t>
+          <t>노블엠앤비</t>
         </is>
       </c>
       <c r="D57" s="25" t="n">
@@ -2775,26 +2773,26 @@
         <v>0</v>
       </c>
       <c r="H57" s="27" t="n">
-        <v>-29.98</v>
+        <v>-7.69</v>
       </c>
       <c r="I57" s="27" t="n">
-        <v>-36.75</v>
+        <v>-97.08</v>
       </c>
       <c r="J57" s="28" t="inlineStr">
         <is>
-          <t>중요공시 1건 / 한국경제 헤드라인 언급</t>
+          <t>네이버 검색 당일 +714%</t>
         </is>
       </c>
       <c r="K57" s="28" t="inlineStr">
         <is>
-          <t>공시</t>
+          <t>네이버</t>
         </is>
       </c>
     </row>
     <row r="58" ht="18" customHeight="1">
       <c r="A58" s="25" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B58" s="25" t="n">
@@ -2802,42 +2800,42 @@
       </c>
       <c r="C58" s="26" t="inlineStr">
         <is>
-          <t>진흥기업</t>
+          <t>서암기계공업</t>
         </is>
       </c>
       <c r="D58" s="25" t="n">
         <v>3</v>
       </c>
       <c r="E58" s="25" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F58" s="25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G58" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H58" s="27" t="n">
-        <v>-5.17</v>
-      </c>
-      <c r="I58" s="27" t="n">
-        <v>-17.83</v>
+      <c r="H58" s="29" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="I58" s="29" t="n">
+        <v>1.52</v>
       </c>
       <c r="J58" s="28" t="inlineStr">
         <is>
-          <t>중요공시 2건 / 중요공시 3일 +100%</t>
+          <t>네이버 검색 당일 +600%</t>
         </is>
       </c>
       <c r="K58" s="28" t="inlineStr">
         <is>
-          <t>공시</t>
+          <t>네이버</t>
         </is>
       </c>
     </row>
     <row r="59" ht="18" customHeight="1">
       <c r="A59" s="25" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B59" s="25" t="n">
@@ -2845,7 +2843,7 @@
       </c>
       <c r="C59" s="26" t="inlineStr">
         <is>
-          <t>SK증권</t>
+          <t>남화산업</t>
         </is>
       </c>
       <c r="D59" s="25" t="n">
@@ -2860,25 +2858,27 @@
       <c r="G59" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H59" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="I59" s="27" t="n">
-        <v>-14.36</v>
+      <c r="H59" s="29" t="n">
+        <v>29.97</v>
+      </c>
+      <c r="I59" s="29" t="n">
+        <v>30.84</v>
       </c>
       <c r="J59" s="28" t="inlineStr">
         <is>
-          <t>매일경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K59" s="28" t="n">
-        <v/>
+          <t>네이버 검색 당일 +548%</t>
+        </is>
+      </c>
+      <c r="K59" s="28" t="inlineStr">
+        <is>
+          <t>네이버</t>
+        </is>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1">
       <c r="A60" s="25" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B60" s="25" t="n">
@@ -2886,7 +2886,7 @@
       </c>
       <c r="C60" s="26" t="inlineStr">
         <is>
-          <t>에이프릴바이오</t>
+          <t>바이온</t>
         </is>
       </c>
       <c r="D60" s="25" t="n">
@@ -2902,26 +2902,26 @@
         <v>0</v>
       </c>
       <c r="H60" s="27" t="n">
-        <v>-3.02</v>
+        <v>-50</v>
       </c>
       <c r="I60" s="27" t="n">
-        <v>-6.78</v>
+        <v>-98.84</v>
       </c>
       <c r="J60" s="28" t="inlineStr">
         <is>
-          <t>중요공시 5건</t>
+          <t>네이버 검색 당일 +473%</t>
         </is>
       </c>
       <c r="K60" s="28" t="inlineStr">
         <is>
-          <t>공시</t>
+          <t>네이버</t>
         </is>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
       <c r="A61" s="25" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B61" s="25" t="n">
@@ -2929,7 +2929,7 @@
       </c>
       <c r="C61" s="26" t="inlineStr">
         <is>
-          <t>에이프로젠</t>
+          <t>조아제약</t>
         </is>
       </c>
       <c r="D61" s="25" t="n">
@@ -2944,27 +2944,27 @@
       <c r="G61" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H61" s="27" t="n">
-        <v>-1.45</v>
-      </c>
-      <c r="I61" s="27" t="n">
-        <v>-18.74</v>
+      <c r="H61" s="29" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="I61" s="29" t="n">
+        <v>44.97</v>
       </c>
       <c r="J61" s="28" t="inlineStr">
         <is>
-          <t>중요공시 4건</t>
+          <t>네이버 검색 당일 +410%</t>
         </is>
       </c>
       <c r="K61" s="28" t="inlineStr">
         <is>
-          <t>공시</t>
+          <t>네이버</t>
         </is>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1">
       <c r="A62" s="25" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B62" s="25" t="n">
@@ -2972,7 +2972,7 @@
       </c>
       <c r="C62" s="26" t="inlineStr">
         <is>
-          <t>경남제약</t>
+          <t>삼기에너지솔루션즈</t>
         </is>
       </c>
       <c r="D62" s="25" t="n">
@@ -2988,26 +2988,26 @@
         <v>0</v>
       </c>
       <c r="H62" s="27" t="n">
-        <v>-16.44</v>
-      </c>
-      <c r="I62" s="27" t="n">
-        <v>-10.37</v>
+        <v>-18.39</v>
+      </c>
+      <c r="I62" s="29" t="n">
+        <v>21.26</v>
       </c>
       <c r="J62" s="28" t="inlineStr">
         <is>
-          <t>중요공시 3건</t>
+          <t>네이버 검색 당일 +398%</t>
         </is>
       </c>
       <c r="K62" s="28" t="inlineStr">
         <is>
-          <t>공시</t>
+          <t>네이버</t>
         </is>
       </c>
     </row>
     <row r="63" ht="18" customHeight="1">
       <c r="A63" s="25" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B63" s="25" t="n">
@@ -3015,7 +3015,7 @@
       </c>
       <c r="C63" s="26" t="inlineStr">
         <is>
-          <t>삼호개발</t>
+          <t>보해양조</t>
         </is>
       </c>
       <c r="D63" s="25" t="n">
@@ -3030,20 +3030,20 @@
       <c r="G63" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H63" s="29" t="n">
-        <v>11.13</v>
+      <c r="H63" s="27" t="n">
+        <v>-15.91</v>
       </c>
       <c r="I63" s="29" t="n">
-        <v>2.57</v>
+        <v>9.15</v>
       </c>
       <c r="J63" s="28" t="inlineStr">
         <is>
-          <t>중요공시 3건</t>
+          <t>네이버 검색 당일 +354%</t>
         </is>
       </c>
       <c r="K63" s="28" t="inlineStr">
         <is>
-          <t>공시</t>
+          <t>네이버</t>
         </is>
       </c>
     </row>
@@ -3140,22 +3140,22 @@
         <v>1</v>
       </c>
       <c r="C3" s="25" t="n">
-        <v>73</v>
+        <v>101</v>
       </c>
       <c r="D3" s="25" t="n">
-        <v>73</v>
+        <v>101</v>
       </c>
       <c r="E3" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F3" s="25" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="G3" s="25" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="H3" s="25" t="n"/>
@@ -3171,29 +3171,29 @@
         <v>1</v>
       </c>
       <c r="C4" s="25" t="n">
-        <v>67</v>
+        <v>50</v>
       </c>
       <c r="D4" s="25" t="n">
-        <v>67</v>
+        <v>50</v>
       </c>
       <c r="E4" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F4" s="25" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="G4" s="25" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="H4" s="29" t="n">
-        <v>20.51</v>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="H4" s="27" t="n">
+        <v>-5.01</v>
       </c>
       <c r="I4" s="29" t="n">
-        <v>24.89</v>
+        <v>12.57</v>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1">
@@ -3206,29 +3206,29 @@
         <v>1</v>
       </c>
       <c r="C5" s="25" t="n">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="D5" s="25" t="n">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="E5" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F5" s="25" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="G5" s="25" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="H5" s="29" t="n">
-        <v>13.06</v>
-      </c>
-      <c r="I5" s="29" t="n">
-        <v>8.640000000000001</v>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="H5" s="27" t="n">
+        <v>-8.359999999999999</v>
+      </c>
+      <c r="I5" s="27" t="n">
+        <v>-3.29</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
@@ -3241,88 +3241,92 @@
         <v>1</v>
       </c>
       <c r="C6" s="25" t="n">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="D6" s="25" t="n">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="E6" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F6" s="25" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="G6" s="25" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="H6" s="29" t="n">
-        <v>5.29</v>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="H6" s="27" t="n">
+        <v>-5.3</v>
       </c>
       <c r="I6" s="27" t="n">
-        <v>-1.1</v>
+        <v>-4.1</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
       <c r="A7" s="26" t="inlineStr">
         <is>
-          <t>바이오</t>
+          <t>LG</t>
         </is>
       </c>
       <c r="B7" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C7" s="25" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D7" s="25" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="E7" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F7" s="25" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="G7" s="25" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="H7" s="25" t="n"/>
-      <c r="I7" s="25" t="n"/>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="H7" s="27" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="I7" s="27" t="n">
+        <v>-9.460000000000001</v>
+      </c>
     </row>
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="26" t="inlineStr">
         <is>
-          <t>인공지능</t>
+          <t>바이오</t>
         </is>
       </c>
       <c r="B8" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C8" s="25" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="D8" s="25" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="E8" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F8" s="25" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="G8" s="25" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="H8" s="25" t="n"/>
@@ -3331,99 +3335,95 @@
     <row r="9" ht="18" customHeight="1">
       <c r="A9" s="26" t="inlineStr">
         <is>
-          <t>카카오</t>
+          <t>인공지능</t>
         </is>
       </c>
       <c r="B9" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C9" s="25" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="D9" s="25" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="E9" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F9" s="25" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="G9" s="25" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="H9" s="29" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="I9" s="27" t="n">
-        <v>-12.85</v>
-      </c>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="H9" s="25" t="n"/>
+      <c r="I9" s="25" t="n"/>
     </row>
     <row r="10" ht="18" customHeight="1">
       <c r="A10" s="26" t="inlineStr">
         <is>
-          <t>현대차</t>
+          <t>파두</t>
         </is>
       </c>
       <c r="B10" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C10" s="25" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D10" s="25" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E10" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F10" s="25" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="G10" s="25" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="H10" s="27" t="n">
-        <v>-1.18</v>
+        <v>-5.14</v>
       </c>
       <c r="I10" s="27" t="n">
-        <v>-16.31</v>
+        <v>-18.15</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
       <c r="A11" s="26" t="inlineStr">
         <is>
-          <t>로봇</t>
+          <t>전기차</t>
         </is>
       </c>
       <c r="B11" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C11" s="25" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D11" s="25" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E11" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F11" s="25" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="G11" s="25" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="H11" s="25" t="n"/>
@@ -3432,7 +3432,7 @@
     <row r="12" ht="18" customHeight="1">
       <c r="A12" s="26" t="inlineStr">
         <is>
-          <t>LG</t>
+          <t>젠큐릭스</t>
         </is>
       </c>
       <c r="B12" s="25" t="n">
@@ -3449,25 +3449,25 @@
       </c>
       <c r="F12" s="25" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="G12" s="25" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="H12" s="29" t="n">
-        <v>0.2</v>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="H12" s="27" t="n">
+        <v>-1.9</v>
       </c>
       <c r="I12" s="27" t="n">
-        <v>-9.550000000000001</v>
+        <v>-12.13</v>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
       <c r="A13" s="26" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>LG이노텍</t>
         </is>
       </c>
       <c r="B13" s="25" t="n">
@@ -3484,25 +3484,25 @@
       </c>
       <c r="F13" s="25" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="G13" s="25" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="H13" s="27" t="n">
-        <v>-2.87</v>
+        <v>-2.31</v>
       </c>
       <c r="I13" s="27" t="n">
-        <v>-9.960000000000001</v>
+        <v>-18.69</v>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="26" t="inlineStr">
         <is>
-          <t>전기차</t>
+          <t>카카오</t>
         </is>
       </c>
       <c r="B14" s="25" t="n">
@@ -3519,56 +3519,60 @@
       </c>
       <c r="F14" s="25" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="G14" s="25" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="H14" s="25" t="n"/>
-      <c r="I14" s="25" t="n"/>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="H14" s="27" t="n">
+        <v>-3.21</v>
+      </c>
+      <c r="I14" s="27" t="n">
+        <v>-12.19</v>
+      </c>
     </row>
     <row r="15" ht="18" customHeight="1">
       <c r="A15" s="26" t="inlineStr">
         <is>
-          <t>카카오뱅크</t>
+          <t>성호전자</t>
         </is>
       </c>
       <c r="B15" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C15" s="25" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D15" s="25" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E15" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F15" s="25" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="G15" s="25" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="H15" s="29" t="n">
-        <v>2</v>
+        <v>0.52</v>
       </c>
       <c r="I15" s="27" t="n">
-        <v>-10.7</v>
+        <v>-24.25</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
       <c r="A16" s="26" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>스피어</t>
         </is>
       </c>
       <c r="B16" s="25" t="n">
@@ -3585,25 +3589,25 @@
       </c>
       <c r="F16" s="25" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="G16" s="25" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="H16" s="29" t="n">
-        <v>1.95</v>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="H16" s="27" t="n">
+        <v>-8.76</v>
       </c>
       <c r="I16" s="27" t="n">
-        <v>-13.46</v>
+        <v>-31.49</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
       <c r="A17" s="26" t="inlineStr">
         <is>
-          <t>에이팩트</t>
+          <t>페니트리움바이오</t>
         </is>
       </c>
       <c r="B17" s="25" t="n">
@@ -3620,60 +3624,60 @@
       </c>
       <c r="F17" s="25" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="G17" s="25" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="H17" s="27" t="n">
-        <v>-4.27</v>
+        <v>-2.96</v>
       </c>
       <c r="I17" s="27" t="n">
-        <v>-27.86</v>
+        <v>-11.93</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
       <c r="A18" s="26" t="inlineStr">
         <is>
-          <t>LG전자</t>
+          <t>한미반도체</t>
         </is>
       </c>
       <c r="B18" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C18" s="25" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D18" s="25" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E18" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F18" s="25" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="G18" s="25" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="H18" s="27" t="n">
-        <v>-0.73</v>
+        <v>-5.68</v>
       </c>
       <c r="I18" s="27" t="n">
-        <v>-11.16</v>
+        <v>-12.71</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
       <c r="A19" s="26" t="inlineStr">
         <is>
-          <t>대한항공</t>
+          <t>로봇</t>
         </is>
       </c>
       <c r="B19" s="25" t="n">
@@ -3690,25 +3694,21 @@
       </c>
       <c r="F19" s="25" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="G19" s="25" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="H19" s="29" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="I19" s="29" t="n">
-        <v>0.87</v>
-      </c>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="H19" s="25" t="n"/>
+      <c r="I19" s="25" t="n"/>
     </row>
     <row r="20" ht="18" customHeight="1">
       <c r="A20" s="26" t="inlineStr">
         <is>
-          <t>제약</t>
+          <t>소룩스</t>
         </is>
       </c>
       <c r="B20" s="25" t="n">
@@ -3725,21 +3725,25 @@
       </c>
       <c r="F20" s="25" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="G20" s="25" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="H20" s="25" t="n"/>
-      <c r="I20" s="25" t="n"/>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="H20" s="27" t="n">
+        <v>-4.21</v>
+      </c>
+      <c r="I20" s="29" t="n">
+        <v>19.47</v>
+      </c>
     </row>
     <row r="21" ht="18" customHeight="1">
       <c r="A21" s="26" t="inlineStr">
         <is>
-          <t>조선</t>
+          <t>원익IPS</t>
         </is>
       </c>
       <c r="B21" s="25" t="n">
@@ -3756,52 +3760,60 @@
       </c>
       <c r="F21" s="25" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="G21" s="25" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="H21" s="25" t="n"/>
-      <c r="I21" s="25" t="n"/>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="H21" s="29" t="n">
+        <v>5.88</v>
+      </c>
+      <c r="I21" s="29" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="22" ht="18" customHeight="1">
       <c r="A22" s="26" t="inlineStr">
         <is>
-          <t>철강</t>
+          <t>KB금융</t>
         </is>
       </c>
       <c r="B22" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C22" s="25" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D22" s="25" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E22" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F22" s="25" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="G22" s="25" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="H22" s="25" t="n"/>
-      <c r="I22" s="25" t="n"/>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="H22" s="27" t="n">
+        <v>-1.71</v>
+      </c>
+      <c r="I22" s="27" t="n">
+        <v>-5.69</v>
+      </c>
     </row>
     <row r="23" ht="18" customHeight="1">
       <c r="A23" s="26" t="inlineStr">
         <is>
-          <t>비투엔</t>
+          <t>LG전자</t>
         </is>
       </c>
       <c r="B23" s="25" t="n">
@@ -3818,756 +3830,744 @@
       </c>
       <c r="F23" s="25" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="G23" s="25" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="H23" s="27" t="n">
-        <v>-6.29</v>
-      </c>
-      <c r="I23" s="29" t="n">
-        <v>3.04</v>
+        <v>-3.5</v>
+      </c>
+      <c r="I23" s="27" t="n">
+        <v>-7.38</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
       <c r="A24" s="26" t="inlineStr">
         <is>
-          <t>KT</t>
+          <t>게임</t>
         </is>
       </c>
       <c r="B24" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C24" s="25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D24" s="25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E24" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F24" s="25" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="G24" s="25" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="H24" s="29" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="I24" s="27" t="n">
-        <v>-2.8</v>
-      </c>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="H24" s="25" t="n"/>
+      <c r="I24" s="25" t="n"/>
     </row>
     <row r="25" ht="18" customHeight="1">
       <c r="A25" s="26" t="inlineStr">
         <is>
-          <t>Netflix</t>
+          <t>광주신세계</t>
         </is>
       </c>
       <c r="B25" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C25" s="25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D25" s="25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E25" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F25" s="25" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="G25" s="25" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="H25" s="25" t="n"/>
-      <c r="I25" s="25" t="n"/>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="H25" s="29" t="n">
+        <v>29.98</v>
+      </c>
+      <c r="I25" s="29" t="n">
+        <v>50.71</v>
+      </c>
     </row>
     <row r="26" ht="18" customHeight="1">
       <c r="A26" s="26" t="inlineStr">
         <is>
-          <t>스피어</t>
+          <t>다스코</t>
         </is>
       </c>
       <c r="B26" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C26" s="25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D26" s="25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E26" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F26" s="25" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="G26" s="25" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="H26" s="27" t="n">
-        <v>-11.4</v>
+        <v>-16.32</v>
       </c>
       <c r="I26" s="27" t="n">
-        <v>-30.17</v>
+        <v>-1.01</v>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
       <c r="A27" s="26" t="inlineStr">
         <is>
-          <t>다스코</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B27" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C27" s="25" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D27" s="25" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E27" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F27" s="25" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="G27" s="25" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="H27" s="29" t="n">
-        <v>29.91</v>
-      </c>
-      <c r="I27" s="29" t="n">
-        <v>53.75</v>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="H27" s="27" t="n">
+        <v>-8.41</v>
+      </c>
+      <c r="I27" s="27" t="n">
+        <v>-14.4</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
       <c r="A28" s="26" t="inlineStr">
         <is>
-          <t>베셀</t>
+          <t>대한항공</t>
         </is>
       </c>
       <c r="B28" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C28" s="25" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D28" s="25" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E28" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F28" s="25" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="G28" s="25" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="H28" s="29" t="n">
-        <v>9.800000000000001</v>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="H28" s="27" t="n">
+        <v>-3.61</v>
       </c>
       <c r="I28" s="29" t="n">
-        <v>7.08</v>
+        <v>0.36</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
       <c r="A29" s="26" t="inlineStr">
         <is>
-          <t>프로브잇</t>
+          <t>에이팩트</t>
         </is>
       </c>
       <c r="B29" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C29" s="25" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D29" s="25" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E29" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F29" s="25" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="G29" s="25" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="H29" s="27" t="n">
-        <v>-44.44</v>
+        <v>-6.74</v>
       </c>
       <c r="I29" s="27" t="n">
-        <v>-97.55</v>
+        <v>-26.62</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
       <c r="A30" s="26" t="inlineStr">
         <is>
-          <t>헝셩그룹</t>
+          <t>제약</t>
         </is>
       </c>
       <c r="B30" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C30" s="25" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D30" s="25" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E30" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F30" s="25" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="G30" s="25" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="H30" s="27" t="n">
-        <v>-6.53</v>
-      </c>
-      <c r="I30" s="29" t="n">
-        <v>11.09</v>
-      </c>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="H30" s="25" t="n"/>
+      <c r="I30" s="25" t="n"/>
     </row>
     <row r="31" ht="18" customHeight="1">
       <c r="A31" s="26" t="inlineStr">
         <is>
-          <t>SK증권</t>
+          <t>카카오뱅크</t>
         </is>
       </c>
       <c r="B31" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C31" s="25" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D31" s="25" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E31" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F31" s="25" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="G31" s="25" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="H31" s="25" t="n">
-        <v>0</v>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="H31" s="27" t="n">
+        <v>-3.42</v>
       </c>
       <c r="I31" s="27" t="n">
-        <v>-14.36</v>
+        <v>-10.84</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
       <c r="A32" s="26" t="inlineStr">
         <is>
-          <t>경남제약</t>
+          <t>리가켐바이오</t>
         </is>
       </c>
       <c r="B32" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C32" s="25" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D32" s="25" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E32" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F32" s="25" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="G32" s="25" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="H32" s="27" t="n">
-        <v>-16.44</v>
-      </c>
-      <c r="I32" s="27" t="n">
-        <v>-10.37</v>
+        <v>-8.279999999999999</v>
+      </c>
+      <c r="I32" s="29" t="n">
+        <v>6.17</v>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
       <c r="A33" s="26" t="inlineStr">
         <is>
-          <t>국순당</t>
+          <t>차바이오텍</t>
         </is>
       </c>
       <c r="B33" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C33" s="25" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D33" s="25" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E33" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F33" s="25" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="G33" s="25" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="H33" s="27" t="n">
-        <v>-13.18</v>
-      </c>
-      <c r="I33" s="29" t="n">
-        <v>12.52</v>
+        <v>-4.12</v>
+      </c>
+      <c r="I33" s="27" t="n">
+        <v>-12.15</v>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
       <c r="A34" s="26" t="inlineStr">
         <is>
-          <t>남화산업</t>
+          <t>SK텔레콤</t>
         </is>
       </c>
       <c r="B34" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C34" s="25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D34" s="25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E34" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F34" s="25" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="G34" s="25" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="H34" s="27" t="n">
-        <v>-21.05</v>
-      </c>
-      <c r="I34" s="29" t="n">
-        <v>3.15</v>
+        <v>-0.88</v>
+      </c>
+      <c r="I34" s="27" t="n">
+        <v>-4.53</v>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
       <c r="A35" s="26" t="inlineStr">
         <is>
-          <t>노블엠앤비</t>
+          <t>금호건설</t>
         </is>
       </c>
       <c r="B35" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C35" s="25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D35" s="25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E35" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F35" s="25" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="G35" s="25" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="H35" s="27" t="n">
-        <v>-38.1</v>
-      </c>
-      <c r="I35" s="27" t="n">
-        <v>-96.84</v>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="H35" s="29" t="n">
+        <v>30</v>
+      </c>
+      <c r="I35" s="29" t="n">
+        <v>57.86</v>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
       <c r="A36" s="26" t="inlineStr">
         <is>
-          <t>동양파일</t>
+          <t>방산</t>
         </is>
       </c>
       <c r="B36" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C36" s="25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D36" s="25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E36" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F36" s="25" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="G36" s="25" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="H36" s="27" t="n">
-        <v>-9.130000000000001</v>
-      </c>
-      <c r="I36" s="29" t="n">
-        <v>15.69</v>
-      </c>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="H36" s="25" t="n"/>
+      <c r="I36" s="25" t="n"/>
     </row>
     <row r="37" ht="18" customHeight="1">
       <c r="A37" s="26" t="inlineStr">
         <is>
-          <t>디와이에이</t>
+          <t>베셀</t>
         </is>
       </c>
       <c r="B37" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C37" s="25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D37" s="25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E37" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F37" s="25" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="G37" s="25" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="H37" s="29" t="n">
-        <v>3.83</v>
-      </c>
-      <c r="I37" s="27" t="n">
-        <v>-4.95</v>
+        <v>9.69</v>
+      </c>
+      <c r="I37" s="29" t="n">
+        <v>34.27</v>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
       <c r="A38" s="26" t="inlineStr">
         <is>
-          <t>모헨즈</t>
+          <t>시너지이노베이션</t>
         </is>
       </c>
       <c r="B38" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C38" s="25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D38" s="25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E38" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F38" s="25" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="G38" s="25" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="H38" s="27" t="n">
-        <v>-26.57</v>
-      </c>
-      <c r="I38" s="29" t="n">
-        <v>17.87</v>
+        <v>-1.93</v>
+      </c>
+      <c r="I38" s="27" t="n">
+        <v>-7.84</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
       <c r="A39" s="26" t="inlineStr">
         <is>
-          <t>바이온</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="B39" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C39" s="25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D39" s="25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E39" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F39" s="25" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="G39" s="25" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="H39" s="27" t="n">
-        <v>-41.67</v>
-      </c>
-      <c r="I39" s="27" t="n">
-        <v>-97.68000000000001</v>
+        <v>-1.11</v>
+      </c>
+      <c r="I39" s="29" t="n">
+        <v>0.4</v>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
       <c r="A40" s="26" t="inlineStr">
         <is>
-          <t>보해양조</t>
+          <t>에코프로</t>
         </is>
       </c>
       <c r="B40" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C40" s="25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D40" s="25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E40" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F40" s="25" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="G40" s="25" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="H40" s="27" t="n">
-        <v>-30</v>
-      </c>
-      <c r="I40" s="29" t="n">
-        <v>68.59999999999999</v>
+        <v>-6.47</v>
+      </c>
+      <c r="I40" s="27" t="n">
+        <v>-17.76</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
       <c r="A41" s="26" t="inlineStr">
         <is>
-          <t>부국철강</t>
+          <t>조선</t>
         </is>
       </c>
       <c r="B41" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C41" s="25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D41" s="25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E41" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F41" s="25" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="G41" s="25" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="H41" s="27" t="n">
-        <v>-20.26</v>
-      </c>
-      <c r="I41" s="29" t="n">
-        <v>6.78</v>
-      </c>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="H41" s="25" t="n"/>
+      <c r="I41" s="25" t="n"/>
     </row>
     <row r="42" ht="18" customHeight="1">
       <c r="A42" s="26" t="inlineStr">
         <is>
-          <t>삼기에너지솔루션즈</t>
+          <t>카카오게임즈</t>
         </is>
       </c>
       <c r="B42" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C42" s="25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D42" s="25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E42" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F42" s="25" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="G42" s="25" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="H42" s="29" t="n">
-        <v>29.96</v>
-      </c>
-      <c r="I42" s="29" t="n">
-        <v>43.5</v>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="H42" s="27" t="n">
+        <v>-9.41</v>
+      </c>
+      <c r="I42" s="27" t="n">
+        <v>-21.34</v>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1">
       <c r="A43" s="26" t="inlineStr">
         <is>
-          <t>삼호개발</t>
+          <t>크리스탈신소재</t>
         </is>
       </c>
       <c r="B43" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C43" s="25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D43" s="25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E43" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F43" s="25" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="G43" s="25" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="H43" s="29" t="n">
-        <v>11.13</v>
-      </c>
-      <c r="I43" s="29" t="n">
-        <v>2.57</v>
+        <v>18.81</v>
+      </c>
+      <c r="I43" s="27" t="n">
+        <v>-28.03</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
       <c r="A44" s="26" t="inlineStr">
         <is>
-          <t>샤페론</t>
+          <t>헝셩그룹</t>
         </is>
       </c>
       <c r="B44" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C44" s="25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D44" s="25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E44" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F44" s="25" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="G44" s="25" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="H44" s="27" t="n">
-        <v>-29.98</v>
-      </c>
-      <c r="I44" s="27" t="n">
-        <v>-36.75</v>
+        <v>-2.71</v>
+      </c>
+      <c r="I44" s="29" t="n">
+        <v>15.4</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
       <c r="A45" s="26" t="inlineStr">
         <is>
-          <t>서암기계공업</t>
+          <t>남화산업</t>
         </is>
       </c>
       <c r="B45" s="25" t="n">
@@ -4584,25 +4584,25 @@
       </c>
       <c r="F45" s="25" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="G45" s="25" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="H45" s="27" t="n">
-        <v>-26.92</v>
-      </c>
-      <c r="I45" s="27" t="n">
-        <v>-5.42</v>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="H45" s="29" t="n">
+        <v>29.97</v>
+      </c>
+      <c r="I45" s="29" t="n">
+        <v>30.84</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
       <c r="A46" s="26" t="inlineStr">
         <is>
-          <t>소룩스</t>
+          <t>노블엠앤비</t>
         </is>
       </c>
       <c r="B46" s="25" t="n">
@@ -4619,25 +4619,25 @@
       </c>
       <c r="F46" s="25" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="G46" s="25" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="H46" s="27" t="n">
-        <v>-1.38</v>
-      </c>
-      <c r="I46" s="29" t="n">
-        <v>20.25</v>
+        <v>-7.69</v>
+      </c>
+      <c r="I46" s="27" t="n">
+        <v>-97.08</v>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
       <c r="A47" s="26" t="inlineStr">
         <is>
-          <t>에이프로젠</t>
+          <t>바이온</t>
         </is>
       </c>
       <c r="B47" s="25" t="n">
@@ -4654,25 +4654,25 @@
       </c>
       <c r="F47" s="25" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="G47" s="25" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="H47" s="27" t="n">
-        <v>-1.45</v>
+        <v>-50</v>
       </c>
       <c r="I47" s="27" t="n">
-        <v>-18.74</v>
+        <v>-98.84</v>
       </c>
     </row>
     <row r="48" ht="18" customHeight="1">
       <c r="A48" s="26" t="inlineStr">
         <is>
-          <t>에이프릴바이오</t>
+          <t>보해양조</t>
         </is>
       </c>
       <c r="B48" s="25" t="n">
@@ -4689,25 +4689,25 @@
       </c>
       <c r="F48" s="25" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="G48" s="25" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="H48" s="27" t="n">
-        <v>-3.02</v>
-      </c>
-      <c r="I48" s="27" t="n">
-        <v>-6.78</v>
+        <v>-15.91</v>
+      </c>
+      <c r="I48" s="29" t="n">
+        <v>9.15</v>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1">
       <c r="A49" s="26" t="inlineStr">
         <is>
-          <t>위지트</t>
+          <t>삼기에너지솔루션즈</t>
         </is>
       </c>
       <c r="B49" s="25" t="n">
@@ -4724,25 +4724,25 @@
       </c>
       <c r="F49" s="25" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="G49" s="25" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="H49" s="27" t="n">
-        <v>-7.25</v>
+        <v>-18.39</v>
       </c>
       <c r="I49" s="29" t="n">
-        <v>33.18</v>
+        <v>21.26</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
       <c r="A50" s="26" t="inlineStr">
         <is>
-          <t>조아제약</t>
+          <t>서암기계공업</t>
         </is>
       </c>
       <c r="B50" s="25" t="n">
@@ -4759,25 +4759,25 @@
       </c>
       <c r="F50" s="25" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="G50" s="25" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="H50" s="27" t="n">
-        <v>-21.89</v>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="H50" s="29" t="n">
+        <v>3.72</v>
       </c>
       <c r="I50" s="29" t="n">
-        <v>19.76</v>
+        <v>1.52</v>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
       <c r="A51" s="26" t="inlineStr">
         <is>
-          <t>진흥기업</t>
+          <t>조아제약</t>
         </is>
       </c>
       <c r="B51" s="25" t="n">
@@ -4794,25 +4794,25 @@
       </c>
       <c r="F51" s="25" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="G51" s="25" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="H51" s="27" t="n">
-        <v>-5.17</v>
-      </c>
-      <c r="I51" s="27" t="n">
-        <v>-17.83</v>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="H51" s="29" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="I51" s="29" t="n">
+        <v>44.97</v>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1">
       <c r="A52" s="26" t="inlineStr">
         <is>
-          <t>키스트론</t>
+          <t>프로브잇</t>
         </is>
       </c>
       <c r="B52" s="25" t="n">
@@ -4829,19 +4829,19 @@
       </c>
       <c r="F52" s="25" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="G52" s="25" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="H52" s="29" t="n">
-        <v>10.76</v>
-      </c>
-      <c r="I52" s="29" t="n">
-        <v>25.6</v>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="H52" s="27" t="n">
+        <v>-40</v>
+      </c>
+      <c r="I52" s="27" t="n">
+        <v>-98.53</v>
       </c>
     </row>
   </sheetData>
@@ -4925,19 +4925,19 @@
         <v>1</v>
       </c>
       <c r="C3" s="36" t="n">
-        <v>73</v>
+        <v>101</v>
       </c>
       <c r="D3" s="36" t="n">
-        <v>73</v>
+        <v>101</v>
       </c>
       <c r="E3" s="36" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="F3" s="37" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="G3" s="37" t="inlineStr">
@@ -4956,19 +4956,19 @@
         <v>1</v>
       </c>
       <c r="C4" s="36" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D4" s="36" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E4" s="36" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="F4" s="37" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="G4" s="37" t="inlineStr">
@@ -4987,19 +4987,19 @@
         <v>1</v>
       </c>
       <c r="C5" s="36" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D5" s="36" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E5" s="36" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="F5" s="37" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="G5" s="37" t="inlineStr">
@@ -5011,26 +5011,26 @@
     <row r="6" ht="18" customHeight="1">
       <c r="A6" s="35" t="inlineStr">
         <is>
-          <t>로봇</t>
+          <t>방산</t>
         </is>
       </c>
       <c r="B6" s="36" t="n">
         <v>1</v>
       </c>
       <c r="C6" s="36" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="D6" s="36" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="E6" s="36" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="F6" s="37" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="G6" s="37" t="inlineStr">
@@ -5042,7 +5042,7 @@
     <row r="7" ht="18" customHeight="1">
       <c r="A7" s="35" t="inlineStr">
         <is>
-          <t>조선</t>
+          <t>로봇</t>
         </is>
       </c>
       <c r="B7" s="36" t="n">
@@ -5056,12 +5056,12 @@
       </c>
       <c r="E7" s="36" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="F7" s="37" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="G7" s="37" t="inlineStr">
@@ -5073,26 +5073,26 @@
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="35" t="inlineStr">
         <is>
-          <t>철강</t>
+          <t>게임</t>
         </is>
       </c>
       <c r="B8" s="36" t="n">
         <v>1</v>
       </c>
       <c r="C8" s="36" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D8" s="36" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E8" s="36" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="F8" s="37" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="G8" s="37" t="inlineStr">
@@ -5104,26 +5104,26 @@
     <row r="9" ht="18" customHeight="1">
       <c r="A9" s="35" t="inlineStr">
         <is>
-          <t>제약</t>
+          <t>조선</t>
         </is>
       </c>
       <c r="B9" s="36" t="n">
         <v>1</v>
       </c>
       <c r="C9" s="36" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D9" s="36" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E9" s="36" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="F9" s="37" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="G9" s="37" t="inlineStr">
@@ -5135,65 +5135,69 @@
     <row r="10" ht="18" customHeight="1">
       <c r="A10" s="35" t="inlineStr">
         <is>
+          <t>제약</t>
+        </is>
+      </c>
+      <c r="B10" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" s="36" t="n">
+        <v>6</v>
+      </c>
+      <c r="D10" s="36" t="n">
+        <v>6</v>
+      </c>
+      <c r="E10" s="36" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="F10" s="37" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="G10" s="37" t="inlineStr">
+        <is>
+          <t>⚡ 관심</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="18" customHeight="1">
+      <c r="A11" s="35" t="inlineStr">
+        <is>
           <t>인공지능</t>
         </is>
       </c>
-      <c r="B10" s="36" t="n">
-        <v>1</v>
-      </c>
-      <c r="C10" s="36" t="n">
-        <v>15</v>
-      </c>
-      <c r="D10" s="36" t="n">
-        <v>15</v>
-      </c>
-      <c r="E10" s="36" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="F10" s="37" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="G10" s="37" t="inlineStr">
+      <c r="B11" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" s="36" t="n">
+        <v>19</v>
+      </c>
+      <c r="D11" s="36" t="n">
+        <v>19</v>
+      </c>
+      <c r="E11" s="36" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="F11" s="37" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="G11" s="37" t="inlineStr">
         <is>
           <t>⚡ 관심</t>
         </is>
       </c>
-    </row>
-    <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="26" t="inlineStr">
-        <is>
-          <t>이차전지</t>
-        </is>
-      </c>
-      <c r="B11" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="C11" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" s="25" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F11" s="28" t="inlineStr">
-        <is>
-          <t>감지 없음</t>
-        </is>
-      </c>
-      <c r="G11" s="28" t="inlineStr"/>
     </row>
     <row r="12" ht="18" customHeight="1">
       <c r="A12" s="26" t="inlineStr">
         <is>
-          <t>AI반도체</t>
+          <t>이차전지</t>
         </is>
       </c>
       <c r="B12" s="25" t="n">
@@ -5220,7 +5224,7 @@
     <row r="13" ht="18" customHeight="1">
       <c r="A13" s="26" t="inlineStr">
         <is>
-          <t>방산</t>
+          <t>AI반도체</t>
         </is>
       </c>
       <c r="B13" s="25" t="n">
@@ -5328,7 +5332,7 @@
     <row r="17" ht="18" customHeight="1">
       <c r="A17" s="26" t="inlineStr">
         <is>
-          <t>게임</t>
+          <t>엔터</t>
         </is>
       </c>
       <c r="B17" s="25" t="n">
@@ -5355,7 +5359,7 @@
     <row r="18" ht="18" customHeight="1">
       <c r="A18" s="26" t="inlineStr">
         <is>
-          <t>엔터</t>
+          <t>핀테크</t>
         </is>
       </c>
       <c r="B18" s="25" t="n">
@@ -5382,7 +5386,7 @@
     <row r="19" ht="18" customHeight="1">
       <c r="A19" s="26" t="inlineStr">
         <is>
-          <t>핀테크</t>
+          <t>클라우드</t>
         </is>
       </c>
       <c r="B19" s="25" t="n">
@@ -5409,7 +5413,7 @@
     <row r="20" ht="18" customHeight="1">
       <c r="A20" s="26" t="inlineStr">
         <is>
-          <t>클라우드</t>
+          <t>철강</t>
         </is>
       </c>
       <c r="B20" s="25" t="n">

--- a/trend/stock_trend_history.xlsx
+++ b/trend/stock_trend_history.xlsx
@@ -694,7 +694,7 @@
     <row r="1" ht="36" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>📊 주식 트렌드 조기 감지 대시보드   |   최종 업데이트: 2026-06-27 06:54</t>
+          <t>📊 주식 트렌드 조기 감지 대시보드   |   최종 업데이트: 2026-06-28 06:54</t>
         </is>
       </c>
     </row>
@@ -708,7 +708,7 @@
       </c>
       <c r="E3" s="3" t="n"/>
       <c r="G3" s="5" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="H3" s="3" t="n"/>
       <c r="J3" s="6" t="n">
@@ -787,21 +787,21 @@
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="11" t="inlineStr">
         <is>
-          <t>⚡ 최신(2026-06-27) 상위: 반도체  점수 101.0점</t>
+          <t>⚡ 최신(2026-06-28) 상위: 반도체  점수 104.0점</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1">
       <c r="A11" s="12" t="inlineStr">
         <is>
-          <t>⚡ 최신(2026-06-27) 상위: SK  점수 50.0점</t>
+          <t>⚡ 최신(2026-06-28) 상위: SK  점수 50.0점</t>
         </is>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1">
       <c r="A12" s="11" t="inlineStr">
         <is>
-          <t>⚡ 최신(2026-06-27) 상위: SK하이닉스  점수 34.0점</t>
+          <t>⚡ 최신(2026-06-28) 상위: SK하이닉스  점수 35.0점</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B14" s="15" t="n">
@@ -928,10 +928,10 @@
         </is>
       </c>
       <c r="D14" s="15" t="n">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="E14" s="15" t="n">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="F14" s="15" t="n">
         <v>0</v>
@@ -947,7 +947,7 @@
       </c>
       <c r="J14" s="17" t="inlineStr">
         <is>
-          <t>매일경제 헤드라인 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 기사 언급 / 매일경제 기사 언급 / 네이버뉴스 헤드라인 언급</t>
+          <t>매일경제 헤드라인 언급 / 네이버뉴스 헤드라인 언급 / 매일경제 기사 언급 / 네이버뉴스 헤드라인 언급 / 매일경제 기사 언급</t>
         </is>
       </c>
       <c r="K14" s="17" t="inlineStr">
@@ -959,7 +959,7 @@
     <row r="15" ht="18" customHeight="1">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B15" s="15" t="n">
@@ -990,7 +990,7 @@
       </c>
       <c r="J15" s="17" t="inlineStr">
         <is>
-          <t>매일경제 헤드라인 언급 / 네이버뉴스 헤드라인 언급 / 매일경제 기사 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급</t>
+          <t>매일경제 헤드라인 언급 / 매일경제 기사 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급</t>
         </is>
       </c>
       <c r="K15" s="17" t="inlineStr">
@@ -1002,7 +1002,7 @@
     <row r="16" ht="18" customHeight="1">
       <c r="A16" s="15" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B16" s="15" t="n">
@@ -1014,10 +1014,10 @@
         </is>
       </c>
       <c r="D16" s="15" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E16" s="15" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F16" s="15" t="n">
         <v>0</v>
@@ -1033,7 +1033,7 @@
       </c>
       <c r="J16" s="17" t="inlineStr">
         <is>
-          <t>중요공시 1건 / 매일경제 헤드라인 언급 / 네이버뉴스 헤드라인 언급 / 매일경제 기사 언급 / 매일경제 헤드라인 언급</t>
+          <t>중요공시 1건 / 매일경제 헤드라인 언급 / 매일경제 기사 언급 / 매일경제 헤드라인 언급 / 매일경제 기사 언급</t>
         </is>
       </c>
       <c r="K16" s="17" t="inlineStr">
@@ -1045,7 +1045,7 @@
     <row r="17" ht="18" customHeight="1">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B17" s="15" t="n">
@@ -1057,10 +1057,10 @@
         </is>
       </c>
       <c r="D17" s="15" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E17" s="15" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F17" s="15" t="n">
         <v>0</v>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="J17" s="17" t="inlineStr">
         <is>
-          <t>매일경제 헤드라인 언급 / 네이버뉴스 헤드라인 언급 / 매일경제 기사 언급 / 매일경제 기사 언급 / 한국경제 헤드라인 언급</t>
+          <t>매일경제 헤드라인 언급 / 매일경제 기사 언급 / 네이버뉴스 기사 언급 / 매일경제 헤드라인 언급 / 네이버뉴스 기사 언급</t>
         </is>
       </c>
       <c r="K17" s="17" t="inlineStr">
@@ -1088,7 +1088,7 @@
     <row r="18" ht="18" customHeight="1">
       <c r="A18" s="15" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B18" s="15" t="n">
@@ -1129,7 +1129,7 @@
     <row r="19" ht="18" customHeight="1">
       <c r="A19" s="15" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B19" s="15" t="n">
@@ -1137,14 +1137,14 @@
       </c>
       <c r="C19" s="16" t="inlineStr">
         <is>
-          <t>바이오</t>
+          <t>인공지능</t>
         </is>
       </c>
       <c r="D19" s="15" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="E19" s="15" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="F19" s="15" t="n">
         <v>0</v>
@@ -1160,7 +1160,7 @@
       </c>
       <c r="J19" s="17" t="inlineStr">
         <is>
-          <t>네이버뉴스 기사 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급</t>
+          <t>네이버뉴스 기사 언급 / 매일경제 기사 언급 / 매일경제 기사 언급 / 매일경제 기사 언급 / 매일경제 기사 언급</t>
         </is>
       </c>
       <c r="K19" s="17" t="inlineStr">
@@ -1172,7 +1172,7 @@
     <row r="20" ht="18" customHeight="1">
       <c r="A20" s="15" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B20" s="15" t="n">
@@ -1180,14 +1180,14 @@
       </c>
       <c r="C20" s="16" t="inlineStr">
         <is>
-          <t>인공지능</t>
+          <t>바이오</t>
         </is>
       </c>
       <c r="D20" s="15" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="E20" s="15" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="F20" s="15" t="n">
         <v>0</v>
@@ -1203,7 +1203,7 @@
       </c>
       <c r="J20" s="17" t="inlineStr">
         <is>
-          <t>매일경제 기사 언급 / 매일경제 기사 언급 / 매일경제 기사 언급 / 매일경제 기사 언급 / 매일경제 기사 언급</t>
+          <t>매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 네이버뉴스 헤드라인 언급 / 네이버뉴스 기사 언급</t>
         </is>
       </c>
       <c r="K20" s="17" t="inlineStr">
@@ -1215,7 +1215,7 @@
     <row r="21" ht="18" customHeight="1">
       <c r="A21" s="15" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B21" s="15" t="n">
@@ -1223,42 +1223,42 @@
       </c>
       <c r="C21" s="16" t="inlineStr">
         <is>
-          <t>파두</t>
+          <t>로봇</t>
         </is>
       </c>
       <c r="D21" s="15" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E21" s="15" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F21" s="15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G21" s="15" t="n">
-        <v>3</v>
-      </c>
-      <c r="H21" s="18" t="n">
-        <v>-5.14</v>
-      </c>
-      <c r="I21" s="18" t="n">
-        <v>-18.15</v>
+        <v>0</v>
+      </c>
+      <c r="H21" s="15" t="n">
+        <v/>
+      </c>
+      <c r="I21" s="15" t="n">
+        <v/>
       </c>
       <c r="J21" s="17" t="inlineStr">
         <is>
-          <t>중요공시 3건 / 중요공시 3일 +200% / 중요공시 7일 +50% / 네이버뉴스 헤드라인 언급 / 네이버뉴스 헤드라인 언급</t>
+          <t>매일경제 헤드라인 언급 / 네이버뉴스 헤드라인 언급 / 매일경제 기사 언급 / 매일경제 헤드라인 언급</t>
         </is>
       </c>
       <c r="K21" s="17" t="inlineStr">
         <is>
-          <t>공시, 네이버</t>
+          <t>네이버</t>
         </is>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
       <c r="A22" s="15" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B22" s="15" t="n">
@@ -1266,40 +1266,42 @@
       </c>
       <c r="C22" s="16" t="inlineStr">
         <is>
-          <t>전기차</t>
+          <t>젠큐릭스</t>
         </is>
       </c>
       <c r="D22" s="15" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E22" s="15" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="F22" s="15" t="n">
         <v>0</v>
       </c>
       <c r="G22" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" s="15" t="n">
-        <v/>
-      </c>
-      <c r="I22" s="15" t="n">
-        <v/>
+        <v>3</v>
+      </c>
+      <c r="H22" s="18" t="n">
+        <v>-1.9</v>
+      </c>
+      <c r="I22" s="18" t="n">
+        <v>-12.13</v>
       </c>
       <c r="J22" s="17" t="inlineStr">
         <is>
-          <t>한국경제 헤드라인 언급 / 한국경제 헤드라인 언급 / 한국경제 헤드라인 언급 / 매일경제 기사 언급 / 한국경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K22" s="17" t="n">
-        <v/>
+          <t>중요공시 3건 / 중요공시 7일 +200% / 매일경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K22" s="17" t="inlineStr">
+        <is>
+          <t>공시</t>
+        </is>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B23" s="15" t="n">
@@ -1307,42 +1309,40 @@
       </c>
       <c r="C23" s="16" t="inlineStr">
         <is>
-          <t>젠큐릭스</t>
+          <t>LG이노텍</t>
         </is>
       </c>
       <c r="D23" s="15" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E23" s="15" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F23" s="15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G23" s="15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H23" s="18" t="n">
-        <v>-1.9</v>
+        <v>-2.31</v>
       </c>
       <c r="I23" s="18" t="n">
-        <v>-12.13</v>
+        <v>-18.69</v>
       </c>
       <c r="J23" s="17" t="inlineStr">
         <is>
-          <t>중요공시 3건 / 중요공시 3일 +200% / 중요공시 7일 +200% / 매일경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K23" s="17" t="inlineStr">
-        <is>
-          <t>공시</t>
-        </is>
+          <t>매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K23" s="17" t="n">
+        <v/>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B24" s="15" t="n">
@@ -1350,7 +1350,7 @@
       </c>
       <c r="C24" s="16" t="inlineStr">
         <is>
-          <t>LG이노텍</t>
+          <t>카카오</t>
         </is>
       </c>
       <c r="D24" s="15" t="n">
@@ -1366,14 +1366,14 @@
         <v>0</v>
       </c>
       <c r="H24" s="18" t="n">
-        <v>-2.31</v>
+        <v>-3.21</v>
       </c>
       <c r="I24" s="18" t="n">
-        <v>-18.69</v>
+        <v>-12.19</v>
       </c>
       <c r="J24" s="17" t="inlineStr">
         <is>
-          <t>매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급</t>
+          <t>매일경제 기사 언급 / 한국경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 기사 언급 / 매일경제 기사 언급</t>
         </is>
       </c>
       <c r="K24" s="17" t="n">
@@ -1383,7 +1383,7 @@
     <row r="25" ht="18" customHeight="1">
       <c r="A25" s="15" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B25" s="15" t="n">
@@ -1391,40 +1391,42 @@
       </c>
       <c r="C25" s="16" t="inlineStr">
         <is>
-          <t>카카오</t>
+          <t>성호전자</t>
         </is>
       </c>
       <c r="D25" s="15" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E25" s="15" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="F25" s="15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G25" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H25" s="18" t="n">
-        <v>-3.21</v>
+        <v>3</v>
+      </c>
+      <c r="H25" s="19" t="n">
+        <v>0.52</v>
       </c>
       <c r="I25" s="18" t="n">
-        <v>-12.19</v>
+        <v>-24.25</v>
       </c>
       <c r="J25" s="17" t="inlineStr">
         <is>
-          <t>매일경제 기사 언급 / 한국경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 기사 언급 / 매일경제 기사 언급</t>
-        </is>
-      </c>
-      <c r="K25" s="17" t="n">
-        <v/>
+          <t>중요공시 3건 / 중요공시 3일 +200% / 중요공시 7일 +50%</t>
+        </is>
+      </c>
+      <c r="K25" s="17" t="inlineStr">
+        <is>
+          <t>공시</t>
+        </is>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
       <c r="A26" s="15" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B26" s="15" t="n">
@@ -1432,7 +1434,7 @@
       </c>
       <c r="C26" s="16" t="inlineStr">
         <is>
-          <t>성호전자</t>
+          <t>파두</t>
         </is>
       </c>
       <c r="D26" s="15" t="n">
@@ -1447,11 +1449,11 @@
       <c r="G26" s="15" t="n">
         <v>3</v>
       </c>
-      <c r="H26" s="19" t="n">
-        <v>0.52</v>
+      <c r="H26" s="18" t="n">
+        <v>-5.14</v>
       </c>
       <c r="I26" s="18" t="n">
-        <v>-24.25</v>
+        <v>-18.15</v>
       </c>
       <c r="J26" s="17" t="inlineStr">
         <is>
@@ -1467,7 +1469,7 @@
     <row r="27" ht="18" customHeight="1">
       <c r="A27" s="15" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B27" s="15" t="n">
@@ -1475,7 +1477,7 @@
       </c>
       <c r="C27" s="16" t="inlineStr">
         <is>
-          <t>스피어</t>
+          <t>페니트리움바이오</t>
         </is>
       </c>
       <c r="D27" s="15" t="n">
@@ -1491,14 +1493,14 @@
         <v>3</v>
       </c>
       <c r="H27" s="18" t="n">
-        <v>-8.76</v>
+        <v>-2.96</v>
       </c>
       <c r="I27" s="18" t="n">
-        <v>-31.49</v>
+        <v>-11.93</v>
       </c>
       <c r="J27" s="17" t="inlineStr">
         <is>
-          <t>중요공시 5건 / 중요공시 3일 +150% / 중요공시 7일 +67%</t>
+          <t>중요공시 3건 / 중요공시 3일 +200% / 중요공시 7일 +50%</t>
         </is>
       </c>
       <c r="K27" s="17" t="inlineStr">
@@ -1510,7 +1512,7 @@
     <row r="28" ht="18" customHeight="1">
       <c r="A28" s="15" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B28" s="15" t="n">
@@ -1518,42 +1520,42 @@
       </c>
       <c r="C28" s="16" t="inlineStr">
         <is>
-          <t>페니트리움바이오</t>
+          <t>다스코</t>
         </is>
       </c>
       <c r="D28" s="15" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E28" s="15" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F28" s="15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G28" s="15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H28" s="18" t="n">
-        <v>-2.96</v>
+        <v>-16.32</v>
       </c>
       <c r="I28" s="18" t="n">
-        <v>-11.93</v>
+        <v>-1.01</v>
       </c>
       <c r="J28" s="17" t="inlineStr">
         <is>
-          <t>중요공시 3건 / 중요공시 3일 +200% / 중요공시 7일 +200%</t>
+          <t>네이버 검색 당일 +134% / 중요공시 1건 / 매일경제 헤드라인 언급</t>
         </is>
       </c>
       <c r="K28" s="17" t="inlineStr">
         <is>
-          <t>공시</t>
+          <t>공시, 네이버</t>
         </is>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
       <c r="A29" s="15" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B29" s="15" t="n">
@@ -1561,14 +1563,14 @@
       </c>
       <c r="C29" s="16" t="inlineStr">
         <is>
-          <t>한미반도체</t>
+          <t>전기차</t>
         </is>
       </c>
       <c r="D29" s="15" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E29" s="15" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F29" s="15" t="n">
         <v>0</v>
@@ -1576,154 +1578,154 @@
       <c r="G29" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="H29" s="18" t="n">
-        <v>-5.68</v>
-      </c>
-      <c r="I29" s="18" t="n">
-        <v>-12.71</v>
+      <c r="H29" s="15" t="n">
+        <v/>
+      </c>
+      <c r="I29" s="15" t="n">
+        <v/>
       </c>
       <c r="J29" s="17" t="inlineStr">
         <is>
-          <t>네이버뉴스 기사 언급 / 한국경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 기사 언급</t>
-        </is>
-      </c>
-      <c r="K29" s="17" t="inlineStr">
+          <t>한국경제 헤드라인 언급 / 매일경제 기사 언급 / 한국경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K29" s="17" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="30" ht="18" customHeight="1">
+      <c r="A30" s="20" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B30" s="20" t="n">
+        <v>17</v>
+      </c>
+      <c r="C30" s="21" t="inlineStr">
+        <is>
+          <t>광주신세계</t>
+        </is>
+      </c>
+      <c r="D30" s="20" t="n">
+        <v>6</v>
+      </c>
+      <c r="E30" s="20" t="n">
+        <v>6</v>
+      </c>
+      <c r="F30" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" s="22" t="n">
+        <v>29.98</v>
+      </c>
+      <c r="I30" s="22" t="n">
+        <v>50.71</v>
+      </c>
+      <c r="J30" s="23" t="inlineStr">
+        <is>
+          <t>네이버 검색 당일 +1339% / 매일경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K30" s="23" t="inlineStr">
         <is>
           <t>네이버</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="18" customHeight="1">
-      <c r="A30" s="15" t="inlineStr">
-        <is>
-          <t>2026-06-27</t>
-        </is>
-      </c>
-      <c r="B30" s="15" t="n">
-        <v>17</v>
-      </c>
-      <c r="C30" s="16" t="inlineStr">
-        <is>
-          <t>소룩스</t>
-        </is>
-      </c>
-      <c r="D30" s="15" t="n">
-        <v>7</v>
-      </c>
-      <c r="E30" s="15" t="n">
-        <v>7</v>
-      </c>
-      <c r="F30" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G30" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H30" s="18" t="n">
-        <v>-4.21</v>
-      </c>
-      <c r="I30" s="19" t="n">
-        <v>19.47</v>
-      </c>
-      <c r="J30" s="17" t="inlineStr">
-        <is>
-          <t>중요공시 3건 / 네이버뉴스 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K30" s="17" t="inlineStr">
+    <row r="31" ht="18" customHeight="1">
+      <c r="A31" s="20" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B31" s="20" t="n">
+        <v>18</v>
+      </c>
+      <c r="C31" s="21" t="inlineStr">
+        <is>
+          <t>헝셩그룹</t>
+        </is>
+      </c>
+      <c r="D31" s="20" t="n">
+        <v>6</v>
+      </c>
+      <c r="E31" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="F31" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="G31" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" s="24" t="n">
+        <v>-2.71</v>
+      </c>
+      <c r="I31" s="22" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="J31" s="23" t="inlineStr">
+        <is>
+          <t>네이버 검색 당일 +291% / 중요공시 2건 / 중요공시 3일 +100%</t>
+        </is>
+      </c>
+      <c r="K31" s="23" t="inlineStr">
         <is>
           <t>공시, 네이버</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="18" customHeight="1">
-      <c r="A31" s="15" t="inlineStr">
-        <is>
-          <t>2026-06-27</t>
-        </is>
-      </c>
-      <c r="B31" s="15" t="n">
-        <v>18</v>
-      </c>
-      <c r="C31" s="16" t="inlineStr">
-        <is>
-          <t>원익IPS</t>
-        </is>
-      </c>
-      <c r="D31" s="15" t="n">
-        <v>7</v>
-      </c>
-      <c r="E31" s="15" t="n">
-        <v>7</v>
-      </c>
-      <c r="F31" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G31" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H31" s="19" t="n">
-        <v>5.88</v>
-      </c>
-      <c r="I31" s="19" t="n">
-        <v>5</v>
-      </c>
-      <c r="J31" s="17" t="inlineStr">
-        <is>
-          <t>네이버뉴스 헤드라인 언급 / 네이버뉴스 헤드라인 언급 / 매일경제 기사 언급</t>
-        </is>
-      </c>
-      <c r="K31" s="17" t="inlineStr">
-        <is>
-          <t>네이버</t>
-        </is>
-      </c>
-    </row>
     <row r="32" ht="18" customHeight="1">
-      <c r="A32" s="15" t="inlineStr">
-        <is>
-          <t>2026-06-27</t>
-        </is>
-      </c>
-      <c r="B32" s="15" t="n">
+      <c r="A32" s="20" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B32" s="20" t="n">
         <v>19</v>
       </c>
-      <c r="C32" s="16" t="inlineStr">
-        <is>
-          <t>로봇</t>
-        </is>
-      </c>
-      <c r="D32" s="15" t="n">
-        <v>7</v>
-      </c>
-      <c r="E32" s="15" t="n">
-        <v>7</v>
-      </c>
-      <c r="F32" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G32" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H32" s="15" t="n">
-        <v/>
-      </c>
-      <c r="I32" s="15" t="n">
-        <v/>
-      </c>
-      <c r="J32" s="17" t="inlineStr">
-        <is>
-          <t>매일경제 헤드라인 언급 / 매일경제 기사 언급 / 매일경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K32" s="17" t="n">
-        <v/>
+      <c r="C32" s="21" t="inlineStr">
+        <is>
+          <t>삼호개발</t>
+        </is>
+      </c>
+      <c r="D32" s="20" t="n">
+        <v>6</v>
+      </c>
+      <c r="E32" s="20" t="n">
+        <v>6</v>
+      </c>
+      <c r="F32" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" s="22" t="n">
+        <v>8.69</v>
+      </c>
+      <c r="I32" s="22" t="n">
+        <v>16.77</v>
+      </c>
+      <c r="J32" s="23" t="inlineStr">
+        <is>
+          <t>네이버 검색 당일 +132% / 중요공시 3건</t>
+        </is>
+      </c>
+      <c r="K32" s="23" t="inlineStr">
+        <is>
+          <t>공시, 네이버</t>
+        </is>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
       <c r="A33" s="20" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B33" s="20" t="n">
@@ -1731,7 +1733,7 @@
       </c>
       <c r="C33" s="21" t="inlineStr">
         <is>
-          <t>광주신세계</t>
+          <t>LG전자</t>
         </is>
       </c>
       <c r="D33" s="20" t="n">
@@ -1746,27 +1748,25 @@
       <c r="G33" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H33" s="22" t="n">
-        <v>29.98</v>
-      </c>
-      <c r="I33" s="22" t="n">
-        <v>50.71</v>
+      <c r="H33" s="24" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="I33" s="24" t="n">
+        <v>-7.38</v>
       </c>
       <c r="J33" s="23" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +654% / 매일경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K33" s="23" t="inlineStr">
-        <is>
-          <t>네이버</t>
-        </is>
+          <t>한국경제 헤드라인 언급 / 매일경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K33" s="23" t="n">
+        <v/>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
       <c r="A34" s="20" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B34" s="20" t="n">
@@ -1774,7 +1774,7 @@
       </c>
       <c r="C34" s="21" t="inlineStr">
         <is>
-          <t>다스코</t>
+          <t>대한항공</t>
         </is>
       </c>
       <c r="D34" s="20" t="n">
@@ -1790,26 +1790,26 @@
         <v>0</v>
       </c>
       <c r="H34" s="24" t="n">
-        <v>-16.32</v>
-      </c>
-      <c r="I34" s="24" t="n">
-        <v>-1.01</v>
+        <v>-3.61</v>
+      </c>
+      <c r="I34" s="22" t="n">
+        <v>0.36</v>
       </c>
       <c r="J34" s="23" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +58% / 중요공시 1건 / 매일경제 헤드라인 언급</t>
+          <t>중요공시 3건 / 매일경제 헤드라인 언급</t>
         </is>
       </c>
       <c r="K34" s="23" t="inlineStr">
         <is>
-          <t>공시, 네이버</t>
+          <t>공시</t>
         </is>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
       <c r="A35" s="20" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B35" s="20" t="n">
@@ -1817,40 +1817,42 @@
       </c>
       <c r="C35" s="21" t="inlineStr">
         <is>
-          <t>LG전자</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="D35" s="20" t="n">
         <v>6</v>
       </c>
       <c r="E35" s="20" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F35" s="20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G35" s="20" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H35" s="24" t="n">
-        <v>-3.5</v>
+        <v>-8.41</v>
       </c>
       <c r="I35" s="24" t="n">
-        <v>-7.38</v>
+        <v>-14.4</v>
       </c>
       <c r="J35" s="23" t="inlineStr">
         <is>
-          <t>한국경제 헤드라인 언급 / 매일경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K35" s="23" t="n">
-        <v/>
+          <t>중요공시 2건 / 중요공시 3일 +100% / 중요공시 7일 +100%</t>
+        </is>
+      </c>
+      <c r="K35" s="23" t="inlineStr">
+        <is>
+          <t>공시</t>
+        </is>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
       <c r="A36" s="20" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B36" s="20" t="n">
@@ -1858,30 +1860,30 @@
       </c>
       <c r="C36" s="21" t="inlineStr">
         <is>
-          <t>대한항공</t>
+          <t>스피어</t>
         </is>
       </c>
       <c r="D36" s="20" t="n">
         <v>6</v>
       </c>
       <c r="E36" s="20" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F36" s="20" t="n">
         <v>0</v>
       </c>
       <c r="G36" s="20" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H36" s="24" t="n">
-        <v>-3.61</v>
-      </c>
-      <c r="I36" s="22" t="n">
-        <v>0.36</v>
+        <v>-8.76</v>
+      </c>
+      <c r="I36" s="24" t="n">
+        <v>-31.49</v>
       </c>
       <c r="J36" s="23" t="inlineStr">
         <is>
-          <t>중요공시 3건 / 매일경제 헤드라인 언급</t>
+          <t>중요공시 5건 / 중요공시 7일 +150%</t>
         </is>
       </c>
       <c r="K36" s="23" t="inlineStr">
@@ -1893,7 +1895,7 @@
     <row r="37" ht="18" customHeight="1">
       <c r="A37" s="20" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B37" s="20" t="n">
@@ -1901,30 +1903,30 @@
       </c>
       <c r="C37" s="21" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>KB금융</t>
         </is>
       </c>
       <c r="D37" s="20" t="n">
         <v>6</v>
       </c>
       <c r="E37" s="20" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F37" s="20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G37" s="20" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H37" s="24" t="n">
-        <v>-8.41</v>
+        <v>-1.71</v>
       </c>
       <c r="I37" s="24" t="n">
-        <v>-14.4</v>
+        <v>-5.69</v>
       </c>
       <c r="J37" s="23" t="inlineStr">
         <is>
-          <t>중요공시 2건 / 중요공시 3일 +100% / 중요공시 7일 +100%</t>
+          <t>중요공시 1건 / 한국경제 헤드라인 언급 / 매일경제 기사 언급 / 매일경제 기사 언급</t>
         </is>
       </c>
       <c r="K37" s="23" t="inlineStr">
@@ -1936,7 +1938,7 @@
     <row r="38" ht="18" customHeight="1">
       <c r="A38" s="20" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B38" s="20" t="n">
@@ -1944,30 +1946,30 @@
       </c>
       <c r="C38" s="21" t="inlineStr">
         <is>
-          <t>에이팩트</t>
+          <t>카카오뱅크</t>
         </is>
       </c>
       <c r="D38" s="20" t="n">
         <v>6</v>
       </c>
       <c r="E38" s="20" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F38" s="20" t="n">
         <v>0</v>
       </c>
       <c r="G38" s="20" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H38" s="24" t="n">
-        <v>-6.74</v>
+        <v>-3.42</v>
       </c>
       <c r="I38" s="24" t="n">
-        <v>-26.62</v>
+        <v>-10.84</v>
       </c>
       <c r="J38" s="23" t="inlineStr">
         <is>
-          <t>중요공시 3건 / 중요공시 7일 +50%</t>
+          <t>중요공시 1건 / 매일경제 헤드라인 언급 / 매일경제 기사 언급 / 매일경제 기사 언급</t>
         </is>
       </c>
       <c r="K38" s="23" t="inlineStr">
@@ -1979,7 +1981,7 @@
     <row r="39" ht="18" customHeight="1">
       <c r="A39" s="20" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B39" s="20" t="n">
@@ -1987,7 +1989,7 @@
       </c>
       <c r="C39" s="21" t="inlineStr">
         <is>
-          <t>KB금융</t>
+          <t>삼성물산</t>
         </is>
       </c>
       <c r="D39" s="20" t="n">
@@ -2003,26 +2005,24 @@
         <v>0</v>
       </c>
       <c r="H39" s="24" t="n">
-        <v>-1.71</v>
-      </c>
-      <c r="I39" s="24" t="n">
-        <v>-5.69</v>
+        <v>-4.72</v>
+      </c>
+      <c r="I39" s="22" t="n">
+        <v>0.61</v>
       </c>
       <c r="J39" s="23" t="inlineStr">
         <is>
-          <t>중요공시 1건 / 한국경제 헤드라인 언급 / 매일경제 기사 언급 / 매일경제 기사 언급</t>
-        </is>
-      </c>
-      <c r="K39" s="23" t="inlineStr">
-        <is>
-          <t>공시</t>
-        </is>
+          <t>매일경제 헤드라인 언급 / 매일경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K39" s="23" t="n">
+        <v/>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
       <c r="A40" s="20" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B40" s="20" t="n">
@@ -2030,7 +2030,7 @@
       </c>
       <c r="C40" s="21" t="inlineStr">
         <is>
-          <t>카카오뱅크</t>
+          <t>현대차</t>
         </is>
       </c>
       <c r="D40" s="20" t="n">
@@ -2046,26 +2046,26 @@
         <v>0</v>
       </c>
       <c r="H40" s="24" t="n">
-        <v>-3.42</v>
+        <v>-4.47</v>
       </c>
       <c r="I40" s="24" t="n">
-        <v>-10.84</v>
+        <v>-21.62</v>
       </c>
       <c r="J40" s="23" t="inlineStr">
         <is>
-          <t>중요공시 1건 / 매일경제 헤드라인 언급 / 매일경제 기사 언급 / 매일경제 기사 언급</t>
+          <t>매일경제 기사 언급 / 네이버뉴스 헤드라인 언급 / 매일경제 헤드라인 언급</t>
         </is>
       </c>
       <c r="K40" s="23" t="inlineStr">
         <is>
-          <t>공시</t>
+          <t>네이버</t>
         </is>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
       <c r="A41" s="20" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B41" s="20" t="n">
@@ -2073,14 +2073,14 @@
       </c>
       <c r="C41" s="21" t="inlineStr">
         <is>
-          <t>게임</t>
+          <t>소룩스</t>
         </is>
       </c>
       <c r="D41" s="20" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E41" s="20" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F41" s="20" t="n">
         <v>0</v>
@@ -2088,25 +2088,27 @@
       <c r="G41" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H41" s="20" t="n">
-        <v/>
-      </c>
-      <c r="I41" s="20" t="n">
-        <v/>
+      <c r="H41" s="24" t="n">
+        <v>-4.21</v>
+      </c>
+      <c r="I41" s="22" t="n">
+        <v>19.47</v>
       </c>
       <c r="J41" s="23" t="inlineStr">
         <is>
-          <t>매일경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K41" s="23" t="n">
-        <v/>
+          <t>네이버 검색 당일 +76% / 중요공시 3건</t>
+        </is>
+      </c>
+      <c r="K41" s="23" t="inlineStr">
+        <is>
+          <t>공시, 네이버</t>
+        </is>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
       <c r="A42" s="20" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B42" s="20" t="n">
@@ -2114,14 +2116,14 @@
       </c>
       <c r="C42" s="21" t="inlineStr">
         <is>
-          <t>제약</t>
+          <t>리가켐바이오</t>
         </is>
       </c>
       <c r="D42" s="20" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E42" s="20" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F42" s="20" t="n">
         <v>0</v>
@@ -2129,27 +2131,27 @@
       <c r="G42" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H42" s="20" t="n">
-        <v/>
-      </c>
-      <c r="I42" s="20" t="n">
-        <v/>
+      <c r="H42" s="24" t="n">
+        <v>-8.279999999999999</v>
+      </c>
+      <c r="I42" s="22" t="n">
+        <v>6.17</v>
       </c>
       <c r="J42" s="23" t="inlineStr">
         <is>
-          <t>네이버뉴스 기사 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 기사 언급 / 한국경제 헤드라인 언급</t>
+          <t>중요공시 2건 / 매일경제 헤드라인 언급 / 매일경제 기사 언급</t>
         </is>
       </c>
       <c r="K42" s="23" t="inlineStr">
         <is>
-          <t>네이버</t>
+          <t>공시</t>
         </is>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1">
       <c r="A43" s="20" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B43" s="20" t="n">
@@ -2157,42 +2159,42 @@
       </c>
       <c r="C43" s="21" t="inlineStr">
         <is>
-          <t>차바이오텍</t>
+          <t>금호건설</t>
         </is>
       </c>
       <c r="D43" s="20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E43" s="20" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F43" s="20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G43" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H43" s="24" t="n">
-        <v>-4.12</v>
-      </c>
-      <c r="I43" s="24" t="n">
-        <v>-12.15</v>
+      <c r="H43" s="22" t="n">
+        <v>30</v>
+      </c>
+      <c r="I43" s="22" t="n">
+        <v>57.86</v>
       </c>
       <c r="J43" s="23" t="inlineStr">
         <is>
-          <t>중요공시 4건 / 중요공시 3일 +300%</t>
+          <t>네이버 검색 당일 +348% / 중요공시 1건</t>
         </is>
       </c>
       <c r="K43" s="23" t="inlineStr">
         <is>
-          <t>공시</t>
+          <t>공시, 네이버</t>
         </is>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
       <c r="A44" s="20" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B44" s="20" t="n">
@@ -2200,14 +2202,14 @@
       </c>
       <c r="C44" s="21" t="inlineStr">
         <is>
-          <t>리가켐바이오</t>
+          <t>크리스탈신소재</t>
         </is>
       </c>
       <c r="D44" s="20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E44" s="20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F44" s="20" t="n">
         <v>0</v>
@@ -2215,27 +2217,27 @@
       <c r="G44" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H44" s="24" t="n">
-        <v>-8.279999999999999</v>
-      </c>
-      <c r="I44" s="22" t="n">
-        <v>6.17</v>
+      <c r="H44" s="22" t="n">
+        <v>18.81</v>
+      </c>
+      <c r="I44" s="24" t="n">
+        <v>-28.03</v>
       </c>
       <c r="J44" s="23" t="inlineStr">
         <is>
-          <t>중요공시 2건 / 매일경제 헤드라인 언급 / 매일경제 기사 언급</t>
+          <t>네이버 검색 당일 +317% / 중요공시 1건</t>
         </is>
       </c>
       <c r="K44" s="23" t="inlineStr">
         <is>
-          <t>공시</t>
+          <t>공시, 네이버</t>
         </is>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
       <c r="A45" s="20" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B45" s="20" t="n">
@@ -2243,7 +2245,7 @@
       </c>
       <c r="C45" s="21" t="inlineStr">
         <is>
-          <t>헝셩그룹</t>
+          <t>티이엠씨씨엔에스</t>
         </is>
       </c>
       <c r="D45" s="20" t="n">
@@ -2258,15 +2260,15 @@
       <c r="G45" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H45" s="24" t="n">
-        <v>-2.71</v>
+      <c r="H45" s="22" t="n">
+        <v>30</v>
       </c>
       <c r="I45" s="22" t="n">
-        <v>15.4</v>
+        <v>10.36</v>
       </c>
       <c r="J45" s="23" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +241% / 중요공시 2건</t>
+          <t>네이버 검색 당일 +273% / 중요공시 1건</t>
         </is>
       </c>
       <c r="K45" s="23" t="inlineStr">
@@ -2278,7 +2280,7 @@
     <row r="46" ht="18" customHeight="1">
       <c r="A46" s="20" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B46" s="20" t="n">
@@ -2286,7 +2288,7 @@
       </c>
       <c r="C46" s="21" t="inlineStr">
         <is>
-          <t>크리스탈신소재</t>
+          <t>베셀</t>
         </is>
       </c>
       <c r="D46" s="20" t="n">
@@ -2302,14 +2304,14 @@
         <v>0</v>
       </c>
       <c r="H46" s="22" t="n">
-        <v>18.81</v>
-      </c>
-      <c r="I46" s="24" t="n">
-        <v>-28.03</v>
+        <v>9.69</v>
+      </c>
+      <c r="I46" s="22" t="n">
+        <v>34.27</v>
       </c>
       <c r="J46" s="23" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +178% / 중요공시 1건</t>
+          <t>네이버 검색 당일 +222% / 중요공시 2건</t>
         </is>
       </c>
       <c r="K46" s="23" t="inlineStr">
@@ -2321,7 +2323,7 @@
     <row r="47" ht="18" customHeight="1">
       <c r="A47" s="20" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B47" s="20" t="n">
@@ -2329,7 +2331,7 @@
       </c>
       <c r="C47" s="21" t="inlineStr">
         <is>
-          <t>베셀</t>
+          <t>남화토건</t>
         </is>
       </c>
       <c r="D47" s="20" t="n">
@@ -2345,14 +2347,14 @@
         <v>0</v>
       </c>
       <c r="H47" s="22" t="n">
-        <v>9.69</v>
+        <v>29.96</v>
       </c>
       <c r="I47" s="22" t="n">
-        <v>34.27</v>
+        <v>28.96</v>
       </c>
       <c r="J47" s="23" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +169% / 중요공시 2건</t>
+          <t>네이버 검색 당일 +162% / 중요공시 1건</t>
         </is>
       </c>
       <c r="K47" s="23" t="inlineStr">
@@ -2364,7 +2366,7 @@
     <row r="48" ht="18" customHeight="1">
       <c r="A48" s="20" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B48" s="20" t="n">
@@ -2372,7 +2374,7 @@
       </c>
       <c r="C48" s="21" t="inlineStr">
         <is>
-          <t>금호건설</t>
+          <t>뉴인텍</t>
         </is>
       </c>
       <c r="D48" s="20" t="n">
@@ -2388,14 +2390,14 @@
         <v>0</v>
       </c>
       <c r="H48" s="22" t="n">
-        <v>30</v>
+        <v>29.93</v>
       </c>
       <c r="I48" s="22" t="n">
-        <v>57.86</v>
+        <v>47.06</v>
       </c>
       <c r="J48" s="23" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +142% / 중요공시 1건</t>
+          <t>네이버 검색 당일 +144% / 중요공시 1건</t>
         </is>
       </c>
       <c r="K48" s="23" t="inlineStr">
@@ -2407,7 +2409,7 @@
     <row r="49" ht="18" customHeight="1">
       <c r="A49" s="20" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B49" s="20" t="n">
@@ -2415,42 +2417,42 @@
       </c>
       <c r="C49" s="21" t="inlineStr">
         <is>
-          <t>시너지이노베이션</t>
+          <t>에코프로</t>
         </is>
       </c>
       <c r="D49" s="20" t="n">
         <v>4</v>
       </c>
       <c r="E49" s="20" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F49" s="20" t="n">
         <v>0</v>
       </c>
       <c r="G49" s="20" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H49" s="24" t="n">
-        <v>-1.93</v>
+        <v>-6.47</v>
       </c>
       <c r="I49" s="24" t="n">
-        <v>-7.84</v>
+        <v>-17.76</v>
       </c>
       <c r="J49" s="23" t="inlineStr">
         <is>
-          <t>중요공시 2건 / 중요공시 7일 +100%</t>
+          <t>중요공시 1건 / 네이버뉴스 헤드라인 언급</t>
         </is>
       </c>
       <c r="K49" s="23" t="inlineStr">
         <is>
-          <t>공시</t>
+          <t>공시, 네이버</t>
         </is>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
       <c r="A50" s="20" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B50" s="20" t="n">
@@ -2458,7 +2460,7 @@
       </c>
       <c r="C50" s="21" t="inlineStr">
         <is>
-          <t>에코프로</t>
+          <t>SK텔레콤</t>
         </is>
       </c>
       <c r="D50" s="20" t="n">
@@ -2474,26 +2476,26 @@
         <v>0</v>
       </c>
       <c r="H50" s="24" t="n">
-        <v>-6.47</v>
+        <v>-0.88</v>
       </c>
       <c r="I50" s="24" t="n">
-        <v>-17.76</v>
+        <v>-4.53</v>
       </c>
       <c r="J50" s="23" t="inlineStr">
         <is>
-          <t>중요공시 1건 / 네이버뉴스 헤드라인 언급</t>
+          <t>중요공시 1건 / 매일경제 헤드라인 언급</t>
         </is>
       </c>
       <c r="K50" s="23" t="inlineStr">
         <is>
-          <t>공시, 네이버</t>
+          <t>공시</t>
         </is>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
       <c r="A51" s="20" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B51" s="20" t="n">
@@ -2501,7 +2503,7 @@
       </c>
       <c r="C51" s="21" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>카카오게임즈</t>
         </is>
       </c>
       <c r="D51" s="20" t="n">
@@ -2517,26 +2519,26 @@
         <v>0</v>
       </c>
       <c r="H51" s="24" t="n">
-        <v>-1.11</v>
-      </c>
-      <c r="I51" s="22" t="n">
-        <v>0.4</v>
+        <v>-9.41</v>
+      </c>
+      <c r="I51" s="24" t="n">
+        <v>-21.34</v>
       </c>
       <c r="J51" s="23" t="inlineStr">
         <is>
-          <t>중요공시 1건 / 네이버뉴스 헤드라인 언급</t>
+          <t>중요공시 1건 / 한국경제 헤드라인 언급</t>
         </is>
       </c>
       <c r="K51" s="23" t="inlineStr">
         <is>
-          <t>공시, 네이버</t>
+          <t>공시</t>
         </is>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1">
       <c r="A52" s="20" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B52" s="20" t="n">
@@ -2544,7 +2546,7 @@
       </c>
       <c r="C52" s="21" t="inlineStr">
         <is>
-          <t>SK텔레콤</t>
+          <t>한미반도체</t>
         </is>
       </c>
       <c r="D52" s="20" t="n">
@@ -2560,26 +2562,24 @@
         <v>0</v>
       </c>
       <c r="H52" s="24" t="n">
-        <v>-0.88</v>
+        <v>-5.68</v>
       </c>
       <c r="I52" s="24" t="n">
-        <v>-4.53</v>
+        <v>-12.71</v>
       </c>
       <c r="J52" s="23" t="inlineStr">
         <is>
-          <t>중요공시 1건 / 매일경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K52" s="23" t="inlineStr">
-        <is>
-          <t>공시</t>
-        </is>
+          <t>매일경제 헤드라인 언급 / 매일경제 기사 언급</t>
+        </is>
+      </c>
+      <c r="K52" s="23" t="n">
+        <v/>
       </c>
     </row>
     <row r="53" ht="18" customHeight="1">
       <c r="A53" s="20" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B53" s="20" t="n">
@@ -2587,7 +2587,7 @@
       </c>
       <c r="C53" s="21" t="inlineStr">
         <is>
-          <t>카카오게임즈</t>
+          <t>제약</t>
         </is>
       </c>
       <c r="D53" s="20" t="n">
@@ -2602,27 +2602,27 @@
       <c r="G53" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H53" s="24" t="n">
-        <v>-9.41</v>
-      </c>
-      <c r="I53" s="24" t="n">
-        <v>-21.34</v>
+      <c r="H53" s="20" t="n">
+        <v/>
+      </c>
+      <c r="I53" s="20" t="n">
+        <v/>
       </c>
       <c r="J53" s="23" t="inlineStr">
         <is>
-          <t>중요공시 1건 / 한국경제 헤드라인 언급</t>
+          <t>네이버뉴스 기사 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 기사 언급</t>
         </is>
       </c>
       <c r="K53" s="23" t="inlineStr">
         <is>
-          <t>공시</t>
+          <t>네이버</t>
         </is>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
       <c r="A54" s="20" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B54" s="20" t="n">
@@ -2630,7 +2630,7 @@
       </c>
       <c r="C54" s="21" t="inlineStr">
         <is>
-          <t>방산</t>
+          <t>조선</t>
         </is>
       </c>
       <c r="D54" s="20" t="n">
@@ -2653,60 +2653,60 @@
       </c>
       <c r="J54" s="23" t="inlineStr">
         <is>
-          <t>네이버뉴스 기사 언급 / 매일경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K54" s="23" t="inlineStr">
+          <t>매일경제 기사 언급 / 매일경제 헤드라인 언급 / 매일경제 기사 언급</t>
+        </is>
+      </c>
+      <c r="K54" s="23" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="55" ht="18" customHeight="1">
+      <c r="A55" s="25" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B55" s="25" t="n">
+        <v>42</v>
+      </c>
+      <c r="C55" s="26" t="inlineStr">
+        <is>
+          <t>프로브잇</t>
+        </is>
+      </c>
+      <c r="D55" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="E55" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="F55" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G55" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H55" s="27" t="n">
+        <v>-40</v>
+      </c>
+      <c r="I55" s="27" t="n">
+        <v>-98.53</v>
+      </c>
+      <c r="J55" s="28" t="inlineStr">
+        <is>
+          <t>네이버 검색 당일 +1980%</t>
+        </is>
+      </c>
+      <c r="K55" s="28" t="inlineStr">
         <is>
           <t>네이버</t>
         </is>
-      </c>
-    </row>
-    <row r="55" ht="18" customHeight="1">
-      <c r="A55" s="20" t="inlineStr">
-        <is>
-          <t>2026-06-27</t>
-        </is>
-      </c>
-      <c r="B55" s="20" t="n">
-        <v>42</v>
-      </c>
-      <c r="C55" s="21" t="inlineStr">
-        <is>
-          <t>조선</t>
-        </is>
-      </c>
-      <c r="D55" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="E55" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="F55" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G55" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H55" s="20" t="n">
-        <v/>
-      </c>
-      <c r="I55" s="20" t="n">
-        <v/>
-      </c>
-      <c r="J55" s="23" t="inlineStr">
-        <is>
-          <t>매일경제 기사 언급 / 매일경제 헤드라인 언급 / 매일경제 기사 언급</t>
-        </is>
-      </c>
-      <c r="K55" s="23" t="n">
-        <v/>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1">
       <c r="A56" s="25" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B56" s="25" t="n">
@@ -2714,7 +2714,7 @@
       </c>
       <c r="C56" s="26" t="inlineStr">
         <is>
-          <t>프로브잇</t>
+          <t>NPX</t>
         </is>
       </c>
       <c r="D56" s="25" t="n">
@@ -2730,14 +2730,14 @@
         <v>0</v>
       </c>
       <c r="H56" s="27" t="n">
-        <v>-40</v>
+        <v>-97.41</v>
       </c>
       <c r="I56" s="27" t="n">
-        <v>-98.53</v>
+        <v>-97.41</v>
       </c>
       <c r="J56" s="28" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +1853%</t>
+          <t>네이버 검색 당일 +1112%</t>
         </is>
       </c>
       <c r="K56" s="28" t="inlineStr">
@@ -2749,7 +2749,7 @@
     <row r="57" ht="18" customHeight="1">
       <c r="A57" s="25" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B57" s="25" t="n">
@@ -2757,7 +2757,7 @@
       </c>
       <c r="C57" s="26" t="inlineStr">
         <is>
-          <t>노블엠앤비</t>
+          <t>남화산업</t>
         </is>
       </c>
       <c r="D57" s="25" t="n">
@@ -2772,15 +2772,15 @@
       <c r="G57" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H57" s="27" t="n">
-        <v>-7.69</v>
-      </c>
-      <c r="I57" s="27" t="n">
-        <v>-97.08</v>
+      <c r="H57" s="29" t="n">
+        <v>29.97</v>
+      </c>
+      <c r="I57" s="29" t="n">
+        <v>30.84</v>
       </c>
       <c r="J57" s="28" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +714%</t>
+          <t>네이버 검색 당일 +858%</t>
         </is>
       </c>
       <c r="K57" s="28" t="inlineStr">
@@ -2792,7 +2792,7 @@
     <row r="58" ht="18" customHeight="1">
       <c r="A58" s="25" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B58" s="25" t="n">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="C58" s="26" t="inlineStr">
         <is>
-          <t>서암기계공업</t>
+          <t>노블엠앤비</t>
         </is>
       </c>
       <c r="D58" s="25" t="n">
@@ -2815,15 +2815,15 @@
       <c r="G58" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H58" s="29" t="n">
-        <v>3.72</v>
-      </c>
-      <c r="I58" s="29" t="n">
-        <v>1.52</v>
+      <c r="H58" s="27" t="n">
+        <v>-7.69</v>
+      </c>
+      <c r="I58" s="27" t="n">
+        <v>-97.08</v>
       </c>
       <c r="J58" s="28" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +600%</t>
+          <t>네이버 검색 당일 +783%</t>
         </is>
       </c>
       <c r="K58" s="28" t="inlineStr">
@@ -2835,7 +2835,7 @@
     <row r="59" ht="18" customHeight="1">
       <c r="A59" s="25" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B59" s="25" t="n">
@@ -2843,7 +2843,7 @@
       </c>
       <c r="C59" s="26" t="inlineStr">
         <is>
-          <t>남화산업</t>
+          <t>삼기에너지솔루션즈</t>
         </is>
       </c>
       <c r="D59" s="25" t="n">
@@ -2858,15 +2858,15 @@
       <c r="G59" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H59" s="29" t="n">
-        <v>29.97</v>
+      <c r="H59" s="27" t="n">
+        <v>-18.39</v>
       </c>
       <c r="I59" s="29" t="n">
-        <v>30.84</v>
+        <v>21.26</v>
       </c>
       <c r="J59" s="28" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +548%</t>
+          <t>네이버 검색 당일 +770%</t>
         </is>
       </c>
       <c r="K59" s="28" t="inlineStr">
@@ -2878,7 +2878,7 @@
     <row r="60" ht="18" customHeight="1">
       <c r="A60" s="25" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B60" s="25" t="n">
@@ -2886,7 +2886,7 @@
       </c>
       <c r="C60" s="26" t="inlineStr">
         <is>
-          <t>바이온</t>
+          <t>서암기계공업</t>
         </is>
       </c>
       <c r="D60" s="25" t="n">
@@ -2901,15 +2901,15 @@
       <c r="G60" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H60" s="27" t="n">
-        <v>-50</v>
-      </c>
-      <c r="I60" s="27" t="n">
-        <v>-98.84</v>
+      <c r="H60" s="29" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="I60" s="29" t="n">
+        <v>1.52</v>
       </c>
       <c r="J60" s="28" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +473%</t>
+          <t>네이버 검색 당일 +748%</t>
         </is>
       </c>
       <c r="K60" s="28" t="inlineStr">
@@ -2921,7 +2921,7 @@
     <row r="61" ht="18" customHeight="1">
       <c r="A61" s="25" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B61" s="25" t="n">
@@ -2929,7 +2929,7 @@
       </c>
       <c r="C61" s="26" t="inlineStr">
         <is>
-          <t>조아제약</t>
+          <t>바이온</t>
         </is>
       </c>
       <c r="D61" s="25" t="n">
@@ -2944,15 +2944,15 @@
       <c r="G61" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H61" s="29" t="n">
-        <v>4.55</v>
-      </c>
-      <c r="I61" s="29" t="n">
-        <v>44.97</v>
+      <c r="H61" s="27" t="n">
+        <v>-50</v>
+      </c>
+      <c r="I61" s="27" t="n">
+        <v>-98.84</v>
       </c>
       <c r="J61" s="28" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +410%</t>
+          <t>네이버 검색 당일 +545%</t>
         </is>
       </c>
       <c r="K61" s="28" t="inlineStr">
@@ -2964,7 +2964,7 @@
     <row r="62" ht="18" customHeight="1">
       <c r="A62" s="25" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B62" s="25" t="n">
@@ -2972,7 +2972,7 @@
       </c>
       <c r="C62" s="26" t="inlineStr">
         <is>
-          <t>삼기에너지솔루션즈</t>
+          <t>디와이에이</t>
         </is>
       </c>
       <c r="D62" s="25" t="n">
@@ -2987,15 +2987,15 @@
       <c r="G62" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H62" s="27" t="n">
-        <v>-18.39</v>
+      <c r="H62" s="29" t="n">
+        <v>25.79</v>
       </c>
       <c r="I62" s="29" t="n">
-        <v>21.26</v>
+        <v>31.47</v>
       </c>
       <c r="J62" s="28" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +398%</t>
+          <t>네이버 검색 당일 +495%</t>
         </is>
       </c>
       <c r="K62" s="28" t="inlineStr">
@@ -3007,7 +3007,7 @@
     <row r="63" ht="18" customHeight="1">
       <c r="A63" s="25" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B63" s="25" t="n">
@@ -3015,7 +3015,7 @@
       </c>
       <c r="C63" s="26" t="inlineStr">
         <is>
-          <t>보해양조</t>
+          <t>조아제약</t>
         </is>
       </c>
       <c r="D63" s="25" t="n">
@@ -3030,15 +3030,15 @@
       <c r="G63" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H63" s="27" t="n">
-        <v>-15.91</v>
+      <c r="H63" s="29" t="n">
+        <v>4.55</v>
       </c>
       <c r="I63" s="29" t="n">
-        <v>9.15</v>
+        <v>44.97</v>
       </c>
       <c r="J63" s="28" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +354%</t>
+          <t>네이버 검색 당일 +475%</t>
         </is>
       </c>
       <c r="K63" s="28" t="inlineStr">
@@ -3140,22 +3140,22 @@
         <v>1</v>
       </c>
       <c r="C3" s="25" t="n">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="D3" s="25" t="n">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="E3" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F3" s="25" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="G3" s="25" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="H3" s="25" t="n"/>
@@ -3181,12 +3181,12 @@
       </c>
       <c r="F4" s="25" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="G4" s="25" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="H4" s="27" t="n">
@@ -3206,22 +3206,22 @@
         <v>1</v>
       </c>
       <c r="C5" s="25" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D5" s="25" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E5" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F5" s="25" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="G5" s="25" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="H5" s="27" t="n">
@@ -3241,22 +3241,22 @@
         <v>1</v>
       </c>
       <c r="C6" s="25" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D6" s="25" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E6" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F6" s="25" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="G6" s="25" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="H6" s="27" t="n">
@@ -3286,12 +3286,12 @@
       </c>
       <c r="F7" s="25" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="G7" s="25" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="H7" s="27" t="n">
@@ -3304,29 +3304,29 @@
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="26" t="inlineStr">
         <is>
-          <t>바이오</t>
+          <t>인공지능</t>
         </is>
       </c>
       <c r="B8" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C8" s="25" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="D8" s="25" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="E8" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F8" s="25" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="G8" s="25" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="H8" s="25" t="n"/>
@@ -3335,29 +3335,29 @@
     <row r="9" ht="18" customHeight="1">
       <c r="A9" s="26" t="inlineStr">
         <is>
-          <t>인공지능</t>
+          <t>바이오</t>
         </is>
       </c>
       <c r="B9" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C9" s="25" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="D9" s="25" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="E9" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F9" s="25" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="G9" s="25" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="H9" s="25" t="n"/>
@@ -3366,68 +3366,68 @@
     <row r="10" ht="18" customHeight="1">
       <c r="A10" s="26" t="inlineStr">
         <is>
-          <t>파두</t>
+          <t>로봇</t>
         </is>
       </c>
       <c r="B10" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C10" s="25" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="D10" s="25" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E10" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F10" s="25" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="G10" s="25" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
-        </is>
-      </c>
-      <c r="H10" s="27" t="n">
-        <v>-5.14</v>
-      </c>
-      <c r="I10" s="27" t="n">
-        <v>-18.15</v>
-      </c>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="H10" s="25" t="n"/>
+      <c r="I10" s="25" t="n"/>
     </row>
     <row r="11" ht="18" customHeight="1">
       <c r="A11" s="26" t="inlineStr">
         <is>
-          <t>전기차</t>
+          <t>LG이노텍</t>
         </is>
       </c>
       <c r="B11" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C11" s="25" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D11" s="25" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E11" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F11" s="25" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="G11" s="25" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
-        </is>
-      </c>
-      <c r="H11" s="25" t="n"/>
-      <c r="I11" s="25" t="n"/>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="H11" s="27" t="n">
+        <v>-2.31</v>
+      </c>
+      <c r="I11" s="27" t="n">
+        <v>-18.69</v>
+      </c>
     </row>
     <row r="12" ht="18" customHeight="1">
       <c r="A12" s="26" t="inlineStr">
@@ -3439,22 +3439,22 @@
         <v>1</v>
       </c>
       <c r="C12" s="25" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D12" s="25" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E12" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F12" s="25" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="G12" s="25" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="H12" s="27" t="n">
@@ -3467,7 +3467,7 @@
     <row r="13" ht="18" customHeight="1">
       <c r="A13" s="26" t="inlineStr">
         <is>
-          <t>LG이노텍</t>
+          <t>카카오</t>
         </is>
       </c>
       <c r="B13" s="25" t="n">
@@ -3484,60 +3484,60 @@
       </c>
       <c r="F13" s="25" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="G13" s="25" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="H13" s="27" t="n">
-        <v>-2.31</v>
+        <v>-3.21</v>
       </c>
       <c r="I13" s="27" t="n">
-        <v>-18.69</v>
+        <v>-12.19</v>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="26" t="inlineStr">
         <is>
-          <t>카카오</t>
+          <t>성호전자</t>
         </is>
       </c>
       <c r="B14" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C14" s="25" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D14" s="25" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E14" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F14" s="25" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="G14" s="25" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
-        </is>
-      </c>
-      <c r="H14" s="27" t="n">
-        <v>-3.21</v>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="H14" s="29" t="n">
+        <v>0.52</v>
       </c>
       <c r="I14" s="27" t="n">
-        <v>-12.19</v>
+        <v>-24.25</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
       <c r="A15" s="26" t="inlineStr">
         <is>
-          <t>성호전자</t>
+          <t>파두</t>
         </is>
       </c>
       <c r="B15" s="25" t="n">
@@ -3554,25 +3554,25 @@
       </c>
       <c r="F15" s="25" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="G15" s="25" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
-        </is>
-      </c>
-      <c r="H15" s="29" t="n">
-        <v>0.52</v>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="H15" s="27" t="n">
+        <v>-5.14</v>
       </c>
       <c r="I15" s="27" t="n">
-        <v>-24.25</v>
+        <v>-18.15</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
       <c r="A16" s="26" t="inlineStr">
         <is>
-          <t>스피어</t>
+          <t>페니트리움바이오</t>
         </is>
       </c>
       <c r="B16" s="25" t="n">
@@ -3589,196 +3589,196 @@
       </c>
       <c r="F16" s="25" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="G16" s="25" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="H16" s="27" t="n">
-        <v>-8.76</v>
+        <v>-2.96</v>
       </c>
       <c r="I16" s="27" t="n">
-        <v>-31.49</v>
+        <v>-11.93</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
       <c r="A17" s="26" t="inlineStr">
         <is>
-          <t>페니트리움바이오</t>
+          <t>다스코</t>
         </is>
       </c>
       <c r="B17" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C17" s="25" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D17" s="25" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E17" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F17" s="25" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="G17" s="25" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="H17" s="27" t="n">
-        <v>-2.96</v>
+        <v>-16.32</v>
       </c>
       <c r="I17" s="27" t="n">
-        <v>-11.93</v>
+        <v>-1.01</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
       <c r="A18" s="26" t="inlineStr">
         <is>
-          <t>한미반도체</t>
+          <t>전기차</t>
         </is>
       </c>
       <c r="B18" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C18" s="25" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D18" s="25" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E18" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F18" s="25" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="G18" s="25" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
-        </is>
-      </c>
-      <c r="H18" s="27" t="n">
-        <v>-5.68</v>
-      </c>
-      <c r="I18" s="27" t="n">
-        <v>-12.71</v>
-      </c>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="H18" s="25" t="n"/>
+      <c r="I18" s="25" t="n"/>
     </row>
     <row r="19" ht="18" customHeight="1">
       <c r="A19" s="26" t="inlineStr">
         <is>
-          <t>로봇</t>
+          <t>KB금융</t>
         </is>
       </c>
       <c r="B19" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C19" s="25" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D19" s="25" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E19" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F19" s="25" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="G19" s="25" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
-        </is>
-      </c>
-      <c r="H19" s="25" t="n"/>
-      <c r="I19" s="25" t="n"/>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="H19" s="27" t="n">
+        <v>-1.71</v>
+      </c>
+      <c r="I19" s="27" t="n">
+        <v>-5.69</v>
+      </c>
     </row>
     <row r="20" ht="18" customHeight="1">
       <c r="A20" s="26" t="inlineStr">
         <is>
-          <t>소룩스</t>
+          <t>LG전자</t>
         </is>
       </c>
       <c r="B20" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C20" s="25" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D20" s="25" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E20" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F20" s="25" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="G20" s="25" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="H20" s="27" t="n">
-        <v>-4.21</v>
-      </c>
-      <c r="I20" s="29" t="n">
-        <v>19.47</v>
+        <v>-3.5</v>
+      </c>
+      <c r="I20" s="27" t="n">
+        <v>-7.38</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
       <c r="A21" s="26" t="inlineStr">
         <is>
-          <t>원익IPS</t>
+          <t>광주신세계</t>
         </is>
       </c>
       <c r="B21" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C21" s="25" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D21" s="25" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E21" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F21" s="25" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="G21" s="25" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="H21" s="29" t="n">
-        <v>5.88</v>
+        <v>29.98</v>
       </c>
       <c r="I21" s="29" t="n">
-        <v>5</v>
+        <v>50.71</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
       <c r="A22" s="26" t="inlineStr">
         <is>
-          <t>KB금융</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B22" s="25" t="n">
@@ -3795,25 +3795,25 @@
       </c>
       <c r="F22" s="25" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="G22" s="25" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="H22" s="27" t="n">
-        <v>-1.71</v>
+        <v>-8.41</v>
       </c>
       <c r="I22" s="27" t="n">
-        <v>-5.69</v>
+        <v>-14.4</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
       <c r="A23" s="26" t="inlineStr">
         <is>
-          <t>LG전자</t>
+          <t>대한항공</t>
         </is>
       </c>
       <c r="B23" s="25" t="n">
@@ -3830,25 +3830,25 @@
       </c>
       <c r="F23" s="25" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="G23" s="25" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="H23" s="27" t="n">
-        <v>-3.5</v>
-      </c>
-      <c r="I23" s="27" t="n">
-        <v>-7.38</v>
+        <v>-3.61</v>
+      </c>
+      <c r="I23" s="29" t="n">
+        <v>0.36</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
       <c r="A24" s="26" t="inlineStr">
         <is>
-          <t>게임</t>
+          <t>삼성물산</t>
         </is>
       </c>
       <c r="B24" s="25" t="n">
@@ -3865,21 +3865,25 @@
       </c>
       <c r="F24" s="25" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="G24" s="25" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
-        </is>
-      </c>
-      <c r="H24" s="25" t="n"/>
-      <c r="I24" s="25" t="n"/>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="H24" s="27" t="n">
+        <v>-4.72</v>
+      </c>
+      <c r="I24" s="29" t="n">
+        <v>0.61</v>
+      </c>
     </row>
     <row r="25" ht="18" customHeight="1">
       <c r="A25" s="26" t="inlineStr">
         <is>
-          <t>광주신세계</t>
+          <t>삼호개발</t>
         </is>
       </c>
       <c r="B25" s="25" t="n">
@@ -3896,25 +3900,25 @@
       </c>
       <c r="F25" s="25" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="G25" s="25" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="H25" s="29" t="n">
-        <v>29.98</v>
+        <v>8.69</v>
       </c>
       <c r="I25" s="29" t="n">
-        <v>50.71</v>
+        <v>16.77</v>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
       <c r="A26" s="26" t="inlineStr">
         <is>
-          <t>다스코</t>
+          <t>스피어</t>
         </is>
       </c>
       <c r="B26" s="25" t="n">
@@ -3931,25 +3935,25 @@
       </c>
       <c r="F26" s="25" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="G26" s="25" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="H26" s="27" t="n">
-        <v>-16.32</v>
+        <v>-8.76</v>
       </c>
       <c r="I26" s="27" t="n">
-        <v>-1.01</v>
+        <v>-31.49</v>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
       <c r="A27" s="26" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>카카오뱅크</t>
         </is>
       </c>
       <c r="B27" s="25" t="n">
@@ -3966,25 +3970,25 @@
       </c>
       <c r="F27" s="25" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="G27" s="25" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="H27" s="27" t="n">
-        <v>-8.41</v>
+        <v>-3.42</v>
       </c>
       <c r="I27" s="27" t="n">
-        <v>-14.4</v>
+        <v>-10.84</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
       <c r="A28" s="26" t="inlineStr">
         <is>
-          <t>대한항공</t>
+          <t>헝셩그룹</t>
         </is>
       </c>
       <c r="B28" s="25" t="n">
@@ -4001,25 +4005,25 @@
       </c>
       <c r="F28" s="25" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="G28" s="25" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="H28" s="27" t="n">
-        <v>-3.61</v>
+        <v>-2.71</v>
       </c>
       <c r="I28" s="29" t="n">
-        <v>0.36</v>
+        <v>15.4</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
       <c r="A29" s="26" t="inlineStr">
         <is>
-          <t>에이팩트</t>
+          <t>현대차</t>
         </is>
       </c>
       <c r="B29" s="25" t="n">
@@ -4036,161 +4040,165 @@
       </c>
       <c r="F29" s="25" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="G29" s="25" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="H29" s="27" t="n">
-        <v>-6.74</v>
+        <v>-4.47</v>
       </c>
       <c r="I29" s="27" t="n">
-        <v>-26.62</v>
+        <v>-21.62</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
       <c r="A30" s="26" t="inlineStr">
         <is>
-          <t>제약</t>
+          <t>리가켐바이오</t>
         </is>
       </c>
       <c r="B30" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C30" s="25" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D30" s="25" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E30" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F30" s="25" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="G30" s="25" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
-        </is>
-      </c>
-      <c r="H30" s="25" t="n"/>
-      <c r="I30" s="25" t="n"/>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="H30" s="27" t="n">
+        <v>-8.279999999999999</v>
+      </c>
+      <c r="I30" s="29" t="n">
+        <v>6.17</v>
+      </c>
     </row>
     <row r="31" ht="18" customHeight="1">
       <c r="A31" s="26" t="inlineStr">
         <is>
-          <t>카카오뱅크</t>
+          <t>소룩스</t>
         </is>
       </c>
       <c r="B31" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C31" s="25" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D31" s="25" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E31" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F31" s="25" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="G31" s="25" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="H31" s="27" t="n">
-        <v>-3.42</v>
-      </c>
-      <c r="I31" s="27" t="n">
-        <v>-10.84</v>
+        <v>-4.21</v>
+      </c>
+      <c r="I31" s="29" t="n">
+        <v>19.47</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
       <c r="A32" s="26" t="inlineStr">
         <is>
-          <t>리가켐바이오</t>
+          <t>SK텔레콤</t>
         </is>
       </c>
       <c r="B32" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C32" s="25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D32" s="25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E32" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F32" s="25" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="G32" s="25" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="H32" s="27" t="n">
-        <v>-8.279999999999999</v>
-      </c>
-      <c r="I32" s="29" t="n">
-        <v>6.17</v>
+        <v>-0.88</v>
+      </c>
+      <c r="I32" s="27" t="n">
+        <v>-4.53</v>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
       <c r="A33" s="26" t="inlineStr">
         <is>
-          <t>차바이오텍</t>
+          <t>금호건설</t>
         </is>
       </c>
       <c r="B33" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C33" s="25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D33" s="25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E33" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F33" s="25" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="G33" s="25" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
-        </is>
-      </c>
-      <c r="H33" s="27" t="n">
-        <v>-4.12</v>
-      </c>
-      <c r="I33" s="27" t="n">
-        <v>-12.15</v>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="H33" s="29" t="n">
+        <v>30</v>
+      </c>
+      <c r="I33" s="29" t="n">
+        <v>57.86</v>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
       <c r="A34" s="26" t="inlineStr">
         <is>
-          <t>SK텔레콤</t>
+          <t>남화토건</t>
         </is>
       </c>
       <c r="B34" s="25" t="n">
@@ -4207,25 +4215,25 @@
       </c>
       <c r="F34" s="25" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="G34" s="25" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
-        </is>
-      </c>
-      <c r="H34" s="27" t="n">
-        <v>-0.88</v>
-      </c>
-      <c r="I34" s="27" t="n">
-        <v>-4.53</v>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="H34" s="29" t="n">
+        <v>29.96</v>
+      </c>
+      <c r="I34" s="29" t="n">
+        <v>28.96</v>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
       <c r="A35" s="26" t="inlineStr">
         <is>
-          <t>금호건설</t>
+          <t>뉴인텍</t>
         </is>
       </c>
       <c r="B35" s="25" t="n">
@@ -4242,25 +4250,25 @@
       </c>
       <c r="F35" s="25" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="G35" s="25" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="H35" s="29" t="n">
-        <v>30</v>
+        <v>29.93</v>
       </c>
       <c r="I35" s="29" t="n">
-        <v>57.86</v>
+        <v>47.06</v>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
       <c r="A36" s="26" t="inlineStr">
         <is>
-          <t>방산</t>
+          <t>베셀</t>
         </is>
       </c>
       <c r="B36" s="25" t="n">
@@ -4277,21 +4285,25 @@
       </c>
       <c r="F36" s="25" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="G36" s="25" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
-        </is>
-      </c>
-      <c r="H36" s="25" t="n"/>
-      <c r="I36" s="25" t="n"/>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="H36" s="29" t="n">
+        <v>9.69</v>
+      </c>
+      <c r="I36" s="29" t="n">
+        <v>34.27</v>
+      </c>
     </row>
     <row r="37" ht="18" customHeight="1">
       <c r="A37" s="26" t="inlineStr">
         <is>
-          <t>베셀</t>
+          <t>에코프로</t>
         </is>
       </c>
       <c r="B37" s="25" t="n">
@@ -4308,25 +4320,25 @@
       </c>
       <c r="F37" s="25" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="G37" s="25" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
-        </is>
-      </c>
-      <c r="H37" s="29" t="n">
-        <v>9.69</v>
-      </c>
-      <c r="I37" s="29" t="n">
-        <v>34.27</v>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="H37" s="27" t="n">
+        <v>-6.47</v>
+      </c>
+      <c r="I37" s="27" t="n">
+        <v>-17.76</v>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
       <c r="A38" s="26" t="inlineStr">
         <is>
-          <t>시너지이노베이션</t>
+          <t>제약</t>
         </is>
       </c>
       <c r="B38" s="25" t="n">
@@ -4343,25 +4355,21 @@
       </c>
       <c r="F38" s="25" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="G38" s="25" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
-        </is>
-      </c>
-      <c r="H38" s="27" t="n">
-        <v>-1.93</v>
-      </c>
-      <c r="I38" s="27" t="n">
-        <v>-7.84</v>
-      </c>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="H38" s="25" t="n"/>
+      <c r="I38" s="25" t="n"/>
     </row>
     <row r="39" ht="18" customHeight="1">
       <c r="A39" s="26" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>조선</t>
         </is>
       </c>
       <c r="B39" s="25" t="n">
@@ -4378,25 +4386,21 @@
       </c>
       <c r="F39" s="25" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="G39" s="25" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
-        </is>
-      </c>
-      <c r="H39" s="27" t="n">
-        <v>-1.11</v>
-      </c>
-      <c r="I39" s="29" t="n">
-        <v>0.4</v>
-      </c>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="H39" s="25" t="n"/>
+      <c r="I39" s="25" t="n"/>
     </row>
     <row r="40" ht="18" customHeight="1">
       <c r="A40" s="26" t="inlineStr">
         <is>
-          <t>에코프로</t>
+          <t>카카오게임즈</t>
         </is>
       </c>
       <c r="B40" s="25" t="n">
@@ -4413,25 +4417,25 @@
       </c>
       <c r="F40" s="25" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="G40" s="25" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="H40" s="27" t="n">
-        <v>-6.47</v>
+        <v>-9.41</v>
       </c>
       <c r="I40" s="27" t="n">
-        <v>-17.76</v>
+        <v>-21.34</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
       <c r="A41" s="26" t="inlineStr">
         <is>
-          <t>조선</t>
+          <t>크리스탈신소재</t>
         </is>
       </c>
       <c r="B41" s="25" t="n">
@@ -4448,21 +4452,25 @@
       </c>
       <c r="F41" s="25" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="G41" s="25" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
-        </is>
-      </c>
-      <c r="H41" s="25" t="n"/>
-      <c r="I41" s="25" t="n"/>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="H41" s="29" t="n">
+        <v>18.81</v>
+      </c>
+      <c r="I41" s="27" t="n">
+        <v>-28.03</v>
+      </c>
     </row>
     <row r="42" ht="18" customHeight="1">
       <c r="A42" s="26" t="inlineStr">
         <is>
-          <t>카카오게임즈</t>
+          <t>티이엠씨씨엔에스</t>
         </is>
       </c>
       <c r="B42" s="25" t="n">
@@ -4479,25 +4487,25 @@
       </c>
       <c r="F42" s="25" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="G42" s="25" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
-        </is>
-      </c>
-      <c r="H42" s="27" t="n">
-        <v>-9.41</v>
-      </c>
-      <c r="I42" s="27" t="n">
-        <v>-21.34</v>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="H42" s="29" t="n">
+        <v>30</v>
+      </c>
+      <c r="I42" s="29" t="n">
+        <v>10.36</v>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1">
       <c r="A43" s="26" t="inlineStr">
         <is>
-          <t>크리스탈신소재</t>
+          <t>한미반도체</t>
         </is>
       </c>
       <c r="B43" s="25" t="n">
@@ -4514,54 +4522,54 @@
       </c>
       <c r="F43" s="25" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="G43" s="25" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
-        </is>
-      </c>
-      <c r="H43" s="29" t="n">
-        <v>18.81</v>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="H43" s="27" t="n">
+        <v>-5.68</v>
       </c>
       <c r="I43" s="27" t="n">
-        <v>-28.03</v>
+        <v>-12.71</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
       <c r="A44" s="26" t="inlineStr">
         <is>
-          <t>헝셩그룹</t>
+          <t>NPX</t>
         </is>
       </c>
       <c r="B44" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C44" s="25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D44" s="25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E44" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F44" s="25" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="G44" s="25" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="H44" s="27" t="n">
-        <v>-2.71</v>
-      </c>
-      <c r="I44" s="29" t="n">
-        <v>15.4</v>
+        <v>-97.41</v>
+      </c>
+      <c r="I44" s="27" t="n">
+        <v>-97.41</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
@@ -4584,12 +4592,12 @@
       </c>
       <c r="F45" s="25" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="G45" s="25" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="H45" s="29" t="n">
@@ -4619,12 +4627,12 @@
       </c>
       <c r="F46" s="25" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="G46" s="25" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="H46" s="27" t="n">
@@ -4637,7 +4645,7 @@
     <row r="47" ht="18" customHeight="1">
       <c r="A47" s="26" t="inlineStr">
         <is>
-          <t>바이온</t>
+          <t>디와이에이</t>
         </is>
       </c>
       <c r="B47" s="25" t="n">
@@ -4654,25 +4662,25 @@
       </c>
       <c r="F47" s="25" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="G47" s="25" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
-        </is>
-      </c>
-      <c r="H47" s="27" t="n">
-        <v>-50</v>
-      </c>
-      <c r="I47" s="27" t="n">
-        <v>-98.84</v>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="H47" s="29" t="n">
+        <v>25.79</v>
+      </c>
+      <c r="I47" s="29" t="n">
+        <v>31.47</v>
       </c>
     </row>
     <row r="48" ht="18" customHeight="1">
       <c r="A48" s="26" t="inlineStr">
         <is>
-          <t>보해양조</t>
+          <t>바이온</t>
         </is>
       </c>
       <c r="B48" s="25" t="n">
@@ -4689,19 +4697,19 @@
       </c>
       <c r="F48" s="25" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="G48" s="25" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="H48" s="27" t="n">
-        <v>-15.91</v>
-      </c>
-      <c r="I48" s="29" t="n">
-        <v>9.15</v>
+        <v>-50</v>
+      </c>
+      <c r="I48" s="27" t="n">
+        <v>-98.84</v>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1">
@@ -4724,12 +4732,12 @@
       </c>
       <c r="F49" s="25" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="G49" s="25" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="H49" s="27" t="n">
@@ -4759,12 +4767,12 @@
       </c>
       <c r="F50" s="25" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="G50" s="25" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="H50" s="29" t="n">
@@ -4794,12 +4802,12 @@
       </c>
       <c r="F51" s="25" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="G51" s="25" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="H51" s="29" t="n">
@@ -4829,12 +4837,12 @@
       </c>
       <c r="F52" s="25" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="G52" s="25" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="H52" s="27" t="n">
@@ -4925,19 +4933,19 @@
         <v>1</v>
       </c>
       <c r="C3" s="36" t="n">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="D3" s="36" t="n">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="E3" s="36" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="F3" s="37" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="G3" s="37" t="inlineStr">
@@ -4956,19 +4964,19 @@
         <v>1</v>
       </c>
       <c r="C4" s="36" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="D4" s="36" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="E4" s="36" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="F4" s="37" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="G4" s="37" t="inlineStr">
@@ -4987,19 +4995,19 @@
         <v>1</v>
       </c>
       <c r="C5" s="36" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="D5" s="36" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="E5" s="36" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="F5" s="37" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="G5" s="37" t="inlineStr">
@@ -5011,26 +5019,26 @@
     <row r="6" ht="18" customHeight="1">
       <c r="A6" s="35" t="inlineStr">
         <is>
-          <t>방산</t>
+          <t>로봇</t>
         </is>
       </c>
       <c r="B6" s="36" t="n">
         <v>1</v>
       </c>
       <c r="C6" s="36" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D6" s="36" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E6" s="36" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="F6" s="37" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="G6" s="37" t="inlineStr">
@@ -5042,26 +5050,26 @@
     <row r="7" ht="18" customHeight="1">
       <c r="A7" s="35" t="inlineStr">
         <is>
-          <t>로봇</t>
+          <t>조선</t>
         </is>
       </c>
       <c r="B7" s="36" t="n">
         <v>1</v>
       </c>
       <c r="C7" s="36" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D7" s="36" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E7" s="36" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="F7" s="37" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="G7" s="37" t="inlineStr">
@@ -5073,26 +5081,26 @@
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="35" t="inlineStr">
         <is>
-          <t>게임</t>
+          <t>제약</t>
         </is>
       </c>
       <c r="B8" s="36" t="n">
         <v>1</v>
       </c>
       <c r="C8" s="36" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D8" s="36" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E8" s="36" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="F8" s="37" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="G8" s="37" t="inlineStr">
@@ -5104,26 +5112,26 @@
     <row r="9" ht="18" customHeight="1">
       <c r="A9" s="35" t="inlineStr">
         <is>
-          <t>조선</t>
+          <t>인공지능</t>
         </is>
       </c>
       <c r="B9" s="36" t="n">
         <v>1</v>
       </c>
       <c r="C9" s="36" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="D9" s="36" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="E9" s="36" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="F9" s="37" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="G9" s="37" t="inlineStr">
@@ -5133,71 +5141,63 @@
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="35" t="inlineStr">
-        <is>
-          <t>제약</t>
-        </is>
-      </c>
-      <c r="B10" s="36" t="n">
-        <v>1</v>
-      </c>
-      <c r="C10" s="36" t="n">
-        <v>6</v>
-      </c>
-      <c r="D10" s="36" t="n">
-        <v>6</v>
-      </c>
-      <c r="E10" s="36" t="inlineStr">
-        <is>
-          <t>2026-06-27</t>
-        </is>
-      </c>
-      <c r="F10" s="37" t="inlineStr">
-        <is>
-          <t>2026-06-27</t>
-        </is>
-      </c>
-      <c r="G10" s="37" t="inlineStr">
-        <is>
-          <t>⚡ 관심</t>
-        </is>
-      </c>
+      <c r="A10" s="26" t="inlineStr">
+        <is>
+          <t>이차전지</t>
+        </is>
+      </c>
+      <c r="B10" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F10" s="28" t="inlineStr">
+        <is>
+          <t>감지 없음</t>
+        </is>
+      </c>
+      <c r="G10" s="28" t="inlineStr"/>
     </row>
     <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="35" t="inlineStr">
-        <is>
-          <t>인공지능</t>
-        </is>
-      </c>
-      <c r="B11" s="36" t="n">
-        <v>1</v>
-      </c>
-      <c r="C11" s="36" t="n">
-        <v>19</v>
-      </c>
-      <c r="D11" s="36" t="n">
-        <v>19</v>
-      </c>
-      <c r="E11" s="36" t="inlineStr">
-        <is>
-          <t>2026-06-27</t>
-        </is>
-      </c>
-      <c r="F11" s="37" t="inlineStr">
-        <is>
-          <t>2026-06-27</t>
-        </is>
-      </c>
-      <c r="G11" s="37" t="inlineStr">
-        <is>
-          <t>⚡ 관심</t>
-        </is>
-      </c>
+      <c r="A11" s="26" t="inlineStr">
+        <is>
+          <t>AI반도체</t>
+        </is>
+      </c>
+      <c r="B11" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F11" s="28" t="inlineStr">
+        <is>
+          <t>감지 없음</t>
+        </is>
+      </c>
+      <c r="G11" s="28" t="inlineStr"/>
     </row>
     <row r="12" ht="18" customHeight="1">
       <c r="A12" s="26" t="inlineStr">
         <is>
-          <t>이차전지</t>
+          <t>방산</t>
         </is>
       </c>
       <c r="B12" s="25" t="n">
@@ -5224,7 +5224,7 @@
     <row r="13" ht="18" customHeight="1">
       <c r="A13" s="26" t="inlineStr">
         <is>
-          <t>AI반도체</t>
+          <t>원전</t>
         </is>
       </c>
       <c r="B13" s="25" t="n">
@@ -5251,7 +5251,7 @@
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="26" t="inlineStr">
         <is>
-          <t>원전</t>
+          <t>수소</t>
         </is>
       </c>
       <c r="B14" s="25" t="n">
@@ -5278,7 +5278,7 @@
     <row r="15" ht="18" customHeight="1">
       <c r="A15" s="26" t="inlineStr">
         <is>
-          <t>수소</t>
+          <t>태양광</t>
         </is>
       </c>
       <c r="B15" s="25" t="n">
@@ -5305,7 +5305,7 @@
     <row r="16" ht="18" customHeight="1">
       <c r="A16" s="26" t="inlineStr">
         <is>
-          <t>태양광</t>
+          <t>게임</t>
         </is>
       </c>
       <c r="B16" s="25" t="n">

--- a/trend/stock_trend_history.xlsx
+++ b/trend/stock_trend_history.xlsx
@@ -694,7 +694,7 @@
     <row r="1" ht="36" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>📊 주식 트렌드 조기 감지 대시보드   |   최종 업데이트: 2026-06-28 06:54</t>
+          <t>📊 주식 트렌드 조기 감지 대시보드   |   최종 업데이트: 2026-06-29 06:54</t>
         </is>
       </c>
     </row>
@@ -708,7 +708,7 @@
       </c>
       <c r="E3" s="3" t="n"/>
       <c r="G3" s="5" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="H3" s="3" t="n"/>
       <c r="J3" s="6" t="n">
@@ -787,21 +787,21 @@
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="11" t="inlineStr">
         <is>
-          <t>⚡ 최신(2026-06-28) 상위: 반도체  점수 104.0점</t>
+          <t>⚡ 최신(2026-06-29) 상위: 반도체  점수 101.0점</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1">
       <c r="A11" s="12" t="inlineStr">
         <is>
-          <t>⚡ 최신(2026-06-28) 상위: SK  점수 50.0점</t>
+          <t>⚡ 최신(2026-06-29) 상위: SK  점수 44.0점</t>
         </is>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1">
       <c r="A12" s="11" t="inlineStr">
         <is>
-          <t>⚡ 최신(2026-06-28) 상위: SK하이닉스  점수 35.0점</t>
+          <t>⚡ 최신(2026-06-29) 상위: 바이오  점수 39.0점</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B14" s="15" t="n">
@@ -928,10 +928,10 @@
         </is>
       </c>
       <c r="D14" s="15" t="n">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="E14" s="15" t="n">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="F14" s="15" t="n">
         <v>0</v>
@@ -947,7 +947,7 @@
       </c>
       <c r="J14" s="17" t="inlineStr">
         <is>
-          <t>매일경제 헤드라인 언급 / 네이버뉴스 헤드라인 언급 / 매일경제 기사 언급 / 네이버뉴스 헤드라인 언급 / 매일경제 기사 언급</t>
+          <t>네이버뉴스 헤드라인 언급 / 매일경제 헤드라인 언급 / 네이버뉴스 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 기사 언급</t>
         </is>
       </c>
       <c r="K14" s="17" t="inlineStr">
@@ -959,7 +959,7 @@
     <row r="15" ht="18" customHeight="1">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B15" s="15" t="n">
@@ -971,10 +971,10 @@
         </is>
       </c>
       <c r="D15" s="15" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="E15" s="15" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="F15" s="15" t="n">
         <v>0</v>
@@ -990,7 +990,7 @@
       </c>
       <c r="J15" s="17" t="inlineStr">
         <is>
-          <t>매일경제 헤드라인 언급 / 매일경제 기사 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급</t>
+          <t>네이버뉴스 기사 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급</t>
         </is>
       </c>
       <c r="K15" s="17" t="inlineStr">
@@ -1002,7 +1002,7 @@
     <row r="16" ht="18" customHeight="1">
       <c r="A16" s="15" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B16" s="15" t="n">
@@ -1010,14 +1010,14 @@
       </c>
       <c r="C16" s="16" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>바이오</t>
         </is>
       </c>
       <c r="D16" s="15" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="E16" s="15" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="F16" s="15" t="n">
         <v>0</v>
@@ -1025,27 +1025,27 @@
       <c r="G16" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="H16" s="18" t="n">
-        <v>-8.359999999999999</v>
-      </c>
-      <c r="I16" s="18" t="n">
-        <v>-3.29</v>
+      <c r="H16" s="15" t="n">
+        <v/>
+      </c>
+      <c r="I16" s="15" t="n">
+        <v/>
       </c>
       <c r="J16" s="17" t="inlineStr">
         <is>
-          <t>중요공시 1건 / 매일경제 헤드라인 언급 / 매일경제 기사 언급 / 매일경제 헤드라인 언급 / 매일경제 기사 언급</t>
+          <t>Google 급상승 검색어 등장 (KR) / 네이버뉴스 헤드라인 언급 / 네이버뉴스 기사 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급</t>
         </is>
       </c>
       <c r="K16" s="17" t="inlineStr">
         <is>
-          <t>공시, 네이버</t>
+          <t>네이버, Google</t>
         </is>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B17" s="15" t="n">
@@ -1057,10 +1057,10 @@
         </is>
       </c>
       <c r="D17" s="15" t="n">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="E17" s="15" t="n">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="F17" s="15" t="n">
         <v>0</v>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="J17" s="17" t="inlineStr">
         <is>
-          <t>매일경제 헤드라인 언급 / 매일경제 기사 언급 / 네이버뉴스 기사 언급 / 매일경제 헤드라인 언급 / 네이버뉴스 기사 언급</t>
+          <t>네이버뉴스 기사 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 기사 언급 / 한국경제 헤드라인 언급</t>
         </is>
       </c>
       <c r="K17" s="17" t="inlineStr">
@@ -1088,7 +1088,7 @@
     <row r="18" ht="18" customHeight="1">
       <c r="A18" s="15" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B18" s="15" t="n">
@@ -1096,14 +1096,14 @@
       </c>
       <c r="C18" s="16" t="inlineStr">
         <is>
-          <t>LG</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="D18" s="15" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E18" s="15" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F18" s="15" t="n">
         <v>0</v>
@@ -1112,24 +1112,26 @@
         <v>0</v>
       </c>
       <c r="H18" s="18" t="n">
-        <v>-0.8</v>
+        <v>-8.359999999999999</v>
       </c>
       <c r="I18" s="18" t="n">
-        <v>-9.460000000000001</v>
+        <v>-3.29</v>
       </c>
       <c r="J18" s="17" t="inlineStr">
         <is>
-          <t>매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K18" s="17" t="n">
-        <v/>
+          <t>중요공시 1건 / 네이버뉴스 기사 언급 / 매일경제 헤드라인 언급 / 매일경제 기사 언급 / 매일경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K18" s="17" t="inlineStr">
+        <is>
+          <t>네이버, 공시</t>
+        </is>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
       <c r="A19" s="15" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B19" s="15" t="n">
@@ -1141,10 +1143,10 @@
         </is>
       </c>
       <c r="D19" s="15" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E19" s="15" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F19" s="15" t="n">
         <v>0</v>
@@ -1160,7 +1162,7 @@
       </c>
       <c r="J19" s="17" t="inlineStr">
         <is>
-          <t>네이버뉴스 기사 언급 / 매일경제 기사 언급 / 매일경제 기사 언급 / 매일경제 기사 언급 / 매일경제 기사 언급</t>
+          <t>매일경제 기사 언급 / 매일경제 기사 언급 / 매일경제 기사 언급 / 매일경제 기사 언급 / 네이버뉴스 기사 언급</t>
         </is>
       </c>
       <c r="K19" s="17" t="inlineStr">
@@ -1172,7 +1174,7 @@
     <row r="20" ht="18" customHeight="1">
       <c r="A20" s="15" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B20" s="15" t="n">
@@ -1180,14 +1182,14 @@
       </c>
       <c r="C20" s="16" t="inlineStr">
         <is>
-          <t>바이오</t>
+          <t>LG</t>
         </is>
       </c>
       <c r="D20" s="15" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E20" s="15" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="F20" s="15" t="n">
         <v>0</v>
@@ -1195,27 +1197,25 @@
       <c r="G20" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="H20" s="15" t="n">
+      <c r="H20" s="18" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="I20" s="18" t="n">
+        <v>-9.460000000000001</v>
+      </c>
+      <c r="J20" s="17" t="inlineStr">
+        <is>
+          <t>매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 기사 언급</t>
+        </is>
+      </c>
+      <c r="K20" s="17" t="n">
         <v/>
-      </c>
-      <c r="I20" s="15" t="n">
-        <v/>
-      </c>
-      <c r="J20" s="17" t="inlineStr">
-        <is>
-          <t>매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 네이버뉴스 헤드라인 언급 / 네이버뉴스 기사 언급</t>
-        </is>
-      </c>
-      <c r="K20" s="17" t="inlineStr">
-        <is>
-          <t>네이버</t>
-        </is>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
       <c r="A21" s="15" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B21" s="15" t="n">
@@ -1227,10 +1227,10 @@
         </is>
       </c>
       <c r="D21" s="15" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E21" s="15" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F21" s="15" t="n">
         <v>0</v>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="J21" s="17" t="inlineStr">
         <is>
-          <t>매일경제 헤드라인 언급 / 네이버뉴스 헤드라인 언급 / 매일경제 기사 언급 / 매일경제 헤드라인 언급</t>
+          <t>매일경제 헤드라인 언급 / 네이버뉴스 기사 언급 / 매일경제 헤드라인 언급 / 매일경제 기사 언급 / 한국경제 헤드라인 언급</t>
         </is>
       </c>
       <c r="K21" s="17" t="inlineStr">
@@ -1258,7 +1258,7 @@
     <row r="22" ht="18" customHeight="1">
       <c r="A22" s="15" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B22" s="15" t="n">
@@ -1266,42 +1266,42 @@
       </c>
       <c r="C22" s="16" t="inlineStr">
         <is>
-          <t>젠큐릭스</t>
+          <t>제약</t>
         </is>
       </c>
       <c r="D22" s="15" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E22" s="15" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="F22" s="15" t="n">
         <v>0</v>
       </c>
       <c r="G22" s="15" t="n">
-        <v>3</v>
-      </c>
-      <c r="H22" s="18" t="n">
-        <v>-1.9</v>
-      </c>
-      <c r="I22" s="18" t="n">
-        <v>-12.13</v>
+        <v>0</v>
+      </c>
+      <c r="H22" s="15" t="n">
+        <v/>
+      </c>
+      <c r="I22" s="15" t="n">
+        <v/>
       </c>
       <c r="J22" s="17" t="inlineStr">
         <is>
-          <t>중요공시 3건 / 중요공시 7일 +200% / 매일경제 헤드라인 언급</t>
+          <t>네이버뉴스 헤드라인 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 기사 언급</t>
         </is>
       </c>
       <c r="K22" s="17" t="inlineStr">
         <is>
-          <t>공시</t>
+          <t>네이버</t>
         </is>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B23" s="15" t="n">
@@ -1309,14 +1309,14 @@
       </c>
       <c r="C23" s="16" t="inlineStr">
         <is>
-          <t>LG이노텍</t>
+          <t>방산</t>
         </is>
       </c>
       <c r="D23" s="15" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E23" s="15" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F23" s="15" t="n">
         <v>0</v>
@@ -1324,15 +1324,15 @@
       <c r="G23" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="H23" s="18" t="n">
-        <v>-2.31</v>
-      </c>
-      <c r="I23" s="18" t="n">
-        <v>-18.69</v>
+      <c r="H23" s="15" t="n">
+        <v/>
+      </c>
+      <c r="I23" s="15" t="n">
+        <v/>
       </c>
       <c r="J23" s="17" t="inlineStr">
         <is>
-          <t>매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급</t>
+          <t>매일경제 헤드라인 언급 / 한국경제 헤드라인 언급 / 한국경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
         </is>
       </c>
       <c r="K23" s="17" t="n">
@@ -1342,7 +1342,7 @@
     <row r="24" ht="18" customHeight="1">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B24" s="15" t="n">
@@ -1350,40 +1350,42 @@
       </c>
       <c r="C24" s="16" t="inlineStr">
         <is>
-          <t>카카오</t>
+          <t>젠큐릭스</t>
         </is>
       </c>
       <c r="D24" s="15" t="n">
         <v>9</v>
       </c>
       <c r="E24" s="15" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F24" s="15" t="n">
         <v>0</v>
       </c>
       <c r="G24" s="15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H24" s="18" t="n">
-        <v>-3.21</v>
+        <v>-1.9</v>
       </c>
       <c r="I24" s="18" t="n">
-        <v>-12.19</v>
+        <v>-12.13</v>
       </c>
       <c r="J24" s="17" t="inlineStr">
         <is>
-          <t>매일경제 기사 언급 / 한국경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 기사 언급 / 매일경제 기사 언급</t>
-        </is>
-      </c>
-      <c r="K24" s="17" t="n">
-        <v/>
+          <t>중요공시 3건 / 중요공시 7일 +200% / 매일경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K24" s="17" t="inlineStr">
+        <is>
+          <t>공시</t>
+        </is>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
       <c r="A25" s="15" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B25" s="15" t="n">
@@ -1391,42 +1393,40 @@
       </c>
       <c r="C25" s="16" t="inlineStr">
         <is>
-          <t>성호전자</t>
+          <t>LG이노텍</t>
         </is>
       </c>
       <c r="D25" s="15" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E25" s="15" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="F25" s="15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G25" s="15" t="n">
-        <v>3</v>
-      </c>
-      <c r="H25" s="19" t="n">
-        <v>0.52</v>
+        <v>0</v>
+      </c>
+      <c r="H25" s="18" t="n">
+        <v>-2.31</v>
       </c>
       <c r="I25" s="18" t="n">
-        <v>-24.25</v>
+        <v>-18.69</v>
       </c>
       <c r="J25" s="17" t="inlineStr">
         <is>
-          <t>중요공시 3건 / 중요공시 3일 +200% / 중요공시 7일 +50%</t>
-        </is>
-      </c>
-      <c r="K25" s="17" t="inlineStr">
-        <is>
-          <t>공시</t>
-        </is>
+          <t>매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K25" s="17" t="n">
+        <v/>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
       <c r="A26" s="15" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B26" s="15" t="n">
@@ -1434,7 +1434,7 @@
       </c>
       <c r="C26" s="16" t="inlineStr">
         <is>
-          <t>파두</t>
+          <t>성호전자</t>
         </is>
       </c>
       <c r="D26" s="15" t="n">
@@ -1449,15 +1449,15 @@
       <c r="G26" s="15" t="n">
         <v>3</v>
       </c>
-      <c r="H26" s="18" t="n">
-        <v>-5.14</v>
+      <c r="H26" s="19" t="n">
+        <v>0.52</v>
       </c>
       <c r="I26" s="18" t="n">
-        <v>-18.15</v>
+        <v>-24.25</v>
       </c>
       <c r="J26" s="17" t="inlineStr">
         <is>
-          <t>중요공시 3건 / 중요공시 3일 +200% / 중요공시 7일 +50%</t>
+          <t>중요공시 3건 / 중요공시 3일 +50% / 중요공시 7일 +200%</t>
         </is>
       </c>
       <c r="K26" s="17" t="inlineStr">
@@ -1467,136 +1467,136 @@
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
-      <c r="A27" s="15" t="inlineStr">
-        <is>
-          <t>2026-06-28</t>
-        </is>
-      </c>
-      <c r="B27" s="15" t="n">
+      <c r="A27" s="20" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B27" s="20" t="n">
         <v>14</v>
       </c>
-      <c r="C27" s="16" t="inlineStr">
-        <is>
-          <t>페니트리움바이오</t>
-        </is>
-      </c>
-      <c r="D27" s="15" t="n">
-        <v>8</v>
-      </c>
-      <c r="E27" s="15" t="n">
-        <v>3</v>
-      </c>
-      <c r="F27" s="15" t="n">
-        <v>2</v>
-      </c>
-      <c r="G27" s="15" t="n">
-        <v>3</v>
-      </c>
-      <c r="H27" s="18" t="n">
-        <v>-2.96</v>
-      </c>
-      <c r="I27" s="18" t="n">
-        <v>-11.93</v>
-      </c>
-      <c r="J27" s="17" t="inlineStr">
-        <is>
-          <t>중요공시 3건 / 중요공시 3일 +200% / 중요공시 7일 +50%</t>
-        </is>
-      </c>
-      <c r="K27" s="17" t="inlineStr">
-        <is>
-          <t>공시</t>
+      <c r="C27" s="21" t="inlineStr">
+        <is>
+          <t>삼호개발</t>
+        </is>
+      </c>
+      <c r="D27" s="20" t="n">
+        <v>6</v>
+      </c>
+      <c r="E27" s="20" t="n">
+        <v>6</v>
+      </c>
+      <c r="F27" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" s="22" t="n">
+        <v>8.69</v>
+      </c>
+      <c r="I27" s="22" t="n">
+        <v>16.77</v>
+      </c>
+      <c r="J27" s="23" t="inlineStr">
+        <is>
+          <t>네이버 검색 당일 +171% / 중요공시 3건</t>
+        </is>
+      </c>
+      <c r="K27" s="23" t="inlineStr">
+        <is>
+          <t>네이버, 공시</t>
         </is>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
-      <c r="A28" s="15" t="inlineStr">
-        <is>
-          <t>2026-06-28</t>
-        </is>
-      </c>
-      <c r="B28" s="15" t="n">
+      <c r="A28" s="20" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B28" s="20" t="n">
         <v>15</v>
       </c>
-      <c r="C28" s="16" t="inlineStr">
-        <is>
-          <t>다스코</t>
-        </is>
-      </c>
-      <c r="D28" s="15" t="n">
-        <v>7</v>
-      </c>
-      <c r="E28" s="15" t="n">
-        <v>7</v>
-      </c>
-      <c r="F28" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G28" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H28" s="18" t="n">
-        <v>-16.32</v>
-      </c>
-      <c r="I28" s="18" t="n">
-        <v>-1.01</v>
-      </c>
-      <c r="J28" s="17" t="inlineStr">
-        <is>
-          <t>네이버 검색 당일 +134% / 중요공시 1건 / 매일경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K28" s="17" t="inlineStr">
-        <is>
-          <t>공시, 네이버</t>
+      <c r="C28" s="21" t="inlineStr">
+        <is>
+          <t>샤페론</t>
+        </is>
+      </c>
+      <c r="D28" s="20" t="n">
+        <v>6</v>
+      </c>
+      <c r="E28" s="20" t="n">
+        <v>6</v>
+      </c>
+      <c r="F28" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" s="24" t="n">
+        <v>-25.16</v>
+      </c>
+      <c r="I28" s="24" t="n">
+        <v>-56.14</v>
+      </c>
+      <c r="J28" s="23" t="inlineStr">
+        <is>
+          <t>네이버 검색 당일 +61% / 중요공시 1건 / 네이버뉴스 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K28" s="23" t="inlineStr">
+        <is>
+          <t>네이버, 공시</t>
         </is>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
-      <c r="A29" s="15" t="inlineStr">
-        <is>
-          <t>2026-06-28</t>
-        </is>
-      </c>
-      <c r="B29" s="15" t="n">
+      <c r="A29" s="20" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B29" s="20" t="n">
         <v>16</v>
       </c>
-      <c r="C29" s="16" t="inlineStr">
-        <is>
-          <t>전기차</t>
-        </is>
-      </c>
-      <c r="D29" s="15" t="n">
-        <v>7</v>
-      </c>
-      <c r="E29" s="15" t="n">
-        <v>7</v>
-      </c>
-      <c r="F29" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G29" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H29" s="15" t="n">
-        <v/>
-      </c>
-      <c r="I29" s="15" t="n">
-        <v/>
-      </c>
-      <c r="J29" s="17" t="inlineStr">
-        <is>
-          <t>한국경제 헤드라인 언급 / 매일경제 기사 언급 / 한국경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K29" s="17" t="n">
+      <c r="C29" s="21" t="inlineStr">
+        <is>
+          <t>LG전자</t>
+        </is>
+      </c>
+      <c r="D29" s="20" t="n">
+        <v>6</v>
+      </c>
+      <c r="E29" s="20" t="n">
+        <v>6</v>
+      </c>
+      <c r="F29" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" s="24" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="I29" s="24" t="n">
+        <v>-7.38</v>
+      </c>
+      <c r="J29" s="23" t="inlineStr">
+        <is>
+          <t>한국경제 헤드라인 언급 / 매일경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K29" s="23" t="n">
         <v/>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
       <c r="A30" s="20" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B30" s="20" t="n">
@@ -1604,42 +1604,42 @@
       </c>
       <c r="C30" s="21" t="inlineStr">
         <is>
-          <t>광주신세계</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="D30" s="20" t="n">
         <v>6</v>
       </c>
       <c r="E30" s="20" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F30" s="20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G30" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H30" s="22" t="n">
-        <v>29.98</v>
-      </c>
-      <c r="I30" s="22" t="n">
-        <v>50.71</v>
+        <v>3</v>
+      </c>
+      <c r="H30" s="24" t="n">
+        <v>-8.41</v>
+      </c>
+      <c r="I30" s="24" t="n">
+        <v>-14.4</v>
       </c>
       <c r="J30" s="23" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +1339% / 매일경제 헤드라인 언급</t>
+          <t>중요공시 2건 / 중요공시 3일 +100% / 중요공시 7일 +100%</t>
         </is>
       </c>
       <c r="K30" s="23" t="inlineStr">
         <is>
-          <t>네이버</t>
+          <t>공시</t>
         </is>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
       <c r="A31" s="20" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B31" s="20" t="n">
@@ -1647,42 +1647,42 @@
       </c>
       <c r="C31" s="21" t="inlineStr">
         <is>
-          <t>헝셩그룹</t>
+          <t>스피어</t>
         </is>
       </c>
       <c r="D31" s="20" t="n">
         <v>6</v>
       </c>
       <c r="E31" s="20" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F31" s="20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G31" s="20" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H31" s="24" t="n">
-        <v>-2.71</v>
-      </c>
-      <c r="I31" s="22" t="n">
-        <v>15.4</v>
+        <v>-8.76</v>
+      </c>
+      <c r="I31" s="24" t="n">
+        <v>-31.49</v>
       </c>
       <c r="J31" s="23" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +291% / 중요공시 2건 / 중요공시 3일 +100%</t>
+          <t>중요공시 5건 / 중요공시 7일 +67%</t>
         </is>
       </c>
       <c r="K31" s="23" t="inlineStr">
         <is>
-          <t>공시, 네이버</t>
+          <t>공시</t>
         </is>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
       <c r="A32" s="20" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B32" s="20" t="n">
@@ -1690,42 +1690,42 @@
       </c>
       <c r="C32" s="21" t="inlineStr">
         <is>
-          <t>삼호개발</t>
+          <t>차바이오텍</t>
         </is>
       </c>
       <c r="D32" s="20" t="n">
         <v>6</v>
       </c>
       <c r="E32" s="20" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F32" s="20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G32" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H32" s="22" t="n">
-        <v>8.69</v>
-      </c>
-      <c r="I32" s="22" t="n">
-        <v>16.77</v>
+      <c r="H32" s="24" t="n">
+        <v>-4.12</v>
+      </c>
+      <c r="I32" s="24" t="n">
+        <v>-12.15</v>
       </c>
       <c r="J32" s="23" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +132% / 중요공시 3건</t>
+          <t>중요공시 4건 / 중요공시 3일 +300% / 네이버뉴스 기사 언급</t>
         </is>
       </c>
       <c r="K32" s="23" t="inlineStr">
         <is>
-          <t>공시, 네이버</t>
+          <t>네이버, 공시</t>
         </is>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
       <c r="A33" s="20" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B33" s="20" t="n">
@@ -1733,40 +1733,42 @@
       </c>
       <c r="C33" s="21" t="inlineStr">
         <is>
-          <t>LG전자</t>
+          <t>에이팩트</t>
         </is>
       </c>
       <c r="D33" s="20" t="n">
         <v>6</v>
       </c>
       <c r="E33" s="20" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F33" s="20" t="n">
         <v>0</v>
       </c>
       <c r="G33" s="20" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H33" s="24" t="n">
-        <v>-3.5</v>
+        <v>-6.74</v>
       </c>
       <c r="I33" s="24" t="n">
-        <v>-7.38</v>
+        <v>-26.62</v>
       </c>
       <c r="J33" s="23" t="inlineStr">
         <is>
-          <t>한국경제 헤드라인 언급 / 매일경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K33" s="23" t="n">
-        <v/>
+          <t>중요공시 3건 / 중요공시 7일 +200%</t>
+        </is>
+      </c>
+      <c r="K33" s="23" t="inlineStr">
+        <is>
+          <t>공시</t>
+        </is>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
       <c r="A34" s="20" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B34" s="20" t="n">
@@ -1774,30 +1776,30 @@
       </c>
       <c r="C34" s="21" t="inlineStr">
         <is>
-          <t>대한항공</t>
+          <t>페니트리움바이오</t>
         </is>
       </c>
       <c r="D34" s="20" t="n">
         <v>6</v>
       </c>
       <c r="E34" s="20" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F34" s="20" t="n">
         <v>0</v>
       </c>
       <c r="G34" s="20" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H34" s="24" t="n">
-        <v>-3.61</v>
-      </c>
-      <c r="I34" s="22" t="n">
-        <v>0.36</v>
+        <v>-2.96</v>
+      </c>
+      <c r="I34" s="24" t="n">
+        <v>-11.93</v>
       </c>
       <c r="J34" s="23" t="inlineStr">
         <is>
-          <t>중요공시 3건 / 매일경제 헤드라인 언급</t>
+          <t>중요공시 3건 / 중요공시 7일 +200%</t>
         </is>
       </c>
       <c r="K34" s="23" t="inlineStr">
@@ -1809,7 +1811,7 @@
     <row r="35" ht="18" customHeight="1">
       <c r="A35" s="20" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B35" s="20" t="n">
@@ -1817,42 +1819,42 @@
       </c>
       <c r="C35" s="21" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>삼성바이오로직스</t>
         </is>
       </c>
       <c r="D35" s="20" t="n">
         <v>6</v>
       </c>
       <c r="E35" s="20" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F35" s="20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G35" s="20" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H35" s="24" t="n">
-        <v>-8.41</v>
+        <v>-3.1</v>
       </c>
       <c r="I35" s="24" t="n">
-        <v>-14.4</v>
+        <v>-2.26</v>
       </c>
       <c r="J35" s="23" t="inlineStr">
         <is>
-          <t>중요공시 2건 / 중요공시 3일 +100% / 중요공시 7일 +100%</t>
+          <t>중요공시 1건 / Google 급상승 검색어 등장 (KR)</t>
         </is>
       </c>
       <c r="K35" s="23" t="inlineStr">
         <is>
-          <t>공시</t>
+          <t>공시, Google</t>
         </is>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
       <c r="A36" s="20" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B36" s="20" t="n">
@@ -1860,42 +1862,42 @@
       </c>
       <c r="C36" s="21" t="inlineStr">
         <is>
-          <t>스피어</t>
+          <t>오텍</t>
         </is>
       </c>
       <c r="D36" s="20" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E36" s="20" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F36" s="20" t="n">
         <v>0</v>
       </c>
       <c r="G36" s="20" t="n">
-        <v>3</v>
-      </c>
-      <c r="H36" s="24" t="n">
-        <v>-8.76</v>
-      </c>
-      <c r="I36" s="24" t="n">
-        <v>-31.49</v>
+        <v>0</v>
+      </c>
+      <c r="H36" s="22" t="n">
+        <v>13.75</v>
+      </c>
+      <c r="I36" s="22" t="n">
+        <v>32.47</v>
       </c>
       <c r="J36" s="23" t="inlineStr">
         <is>
-          <t>중요공시 5건 / 중요공시 7일 +150%</t>
+          <t>네이버 검색 당일 +88% / 네이버뉴스 기사 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 기사 언급</t>
         </is>
       </c>
       <c r="K36" s="23" t="inlineStr">
         <is>
-          <t>공시</t>
+          <t>네이버</t>
         </is>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
       <c r="A37" s="20" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B37" s="20" t="n">
@@ -1903,14 +1905,14 @@
       </c>
       <c r="C37" s="21" t="inlineStr">
         <is>
-          <t>KB금융</t>
+          <t>소룩스</t>
         </is>
       </c>
       <c r="D37" s="20" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E37" s="20" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F37" s="20" t="n">
         <v>0</v>
@@ -1919,26 +1921,26 @@
         <v>0</v>
       </c>
       <c r="H37" s="24" t="n">
-        <v>-1.71</v>
-      </c>
-      <c r="I37" s="24" t="n">
-        <v>-5.69</v>
+        <v>-4.21</v>
+      </c>
+      <c r="I37" s="22" t="n">
+        <v>19.47</v>
       </c>
       <c r="J37" s="23" t="inlineStr">
         <is>
-          <t>중요공시 1건 / 한국경제 헤드라인 언급 / 매일경제 기사 언급 / 매일경제 기사 언급</t>
+          <t>네이버 검색 당일 +84% / 중요공시 3건</t>
         </is>
       </c>
       <c r="K37" s="23" t="inlineStr">
         <is>
-          <t>공시</t>
+          <t>네이버, 공시</t>
         </is>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
       <c r="A38" s="20" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B38" s="20" t="n">
@@ -1946,30 +1948,30 @@
       </c>
       <c r="C38" s="21" t="inlineStr">
         <is>
-          <t>카카오뱅크</t>
+          <t>에이프릴바이오</t>
         </is>
       </c>
       <c r="D38" s="20" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E38" s="20" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F38" s="20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G38" s="20" t="n">
         <v>0</v>
       </c>
       <c r="H38" s="24" t="n">
-        <v>-3.42</v>
-      </c>
-      <c r="I38" s="24" t="n">
-        <v>-10.84</v>
+        <v>-0.13</v>
+      </c>
+      <c r="I38" s="22" t="n">
+        <v>1.72</v>
       </c>
       <c r="J38" s="23" t="inlineStr">
         <is>
-          <t>중요공시 1건 / 매일경제 헤드라인 언급 / 매일경제 기사 언급 / 매일경제 기사 언급</t>
+          <t>중요공시 5건 / 중요공시 3일 +400%</t>
         </is>
       </c>
       <c r="K38" s="23" t="inlineStr">
@@ -1981,7 +1983,7 @@
     <row r="39" ht="18" customHeight="1">
       <c r="A39" s="20" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B39" s="20" t="n">
@@ -1989,40 +1991,42 @@
       </c>
       <c r="C39" s="21" t="inlineStr">
         <is>
-          <t>삼성물산</t>
+          <t>파두</t>
         </is>
       </c>
       <c r="D39" s="20" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E39" s="20" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F39" s="20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G39" s="20" t="n">
         <v>0</v>
       </c>
       <c r="H39" s="24" t="n">
-        <v>-4.72</v>
-      </c>
-      <c r="I39" s="22" t="n">
-        <v>0.61</v>
+        <v>-5.14</v>
+      </c>
+      <c r="I39" s="24" t="n">
+        <v>-18.15</v>
       </c>
       <c r="J39" s="23" t="inlineStr">
         <is>
-          <t>매일경제 헤드라인 언급 / 매일경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K39" s="23" t="n">
-        <v/>
+          <t>중요공시 3건 / 중요공시 3일 +200%</t>
+        </is>
+      </c>
+      <c r="K39" s="23" t="inlineStr">
+        <is>
+          <t>공시</t>
+        </is>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
       <c r="A40" s="20" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B40" s="20" t="n">
@@ -2030,14 +2034,14 @@
       </c>
       <c r="C40" s="21" t="inlineStr">
         <is>
-          <t>현대차</t>
+          <t>리가켐바이오</t>
         </is>
       </c>
       <c r="D40" s="20" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E40" s="20" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F40" s="20" t="n">
         <v>0</v>
@@ -2046,26 +2050,26 @@
         <v>0</v>
       </c>
       <c r="H40" s="24" t="n">
-        <v>-4.47</v>
-      </c>
-      <c r="I40" s="24" t="n">
-        <v>-21.62</v>
+        <v>-8.279999999999999</v>
+      </c>
+      <c r="I40" s="22" t="n">
+        <v>6.17</v>
       </c>
       <c r="J40" s="23" t="inlineStr">
         <is>
-          <t>매일경제 기사 언급 / 네이버뉴스 헤드라인 언급 / 매일경제 헤드라인 언급</t>
+          <t>중요공시 2건 / 매일경제 헤드라인 언급 / 매일경제 기사 언급</t>
         </is>
       </c>
       <c r="K40" s="23" t="inlineStr">
         <is>
-          <t>네이버</t>
+          <t>공시</t>
         </is>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
       <c r="A41" s="20" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B41" s="20" t="n">
@@ -2073,7 +2077,7 @@
       </c>
       <c r="C41" s="21" t="inlineStr">
         <is>
-          <t>소룩스</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="D41" s="20" t="n">
@@ -2089,26 +2093,26 @@
         <v>0</v>
       </c>
       <c r="H41" s="24" t="n">
-        <v>-4.21</v>
-      </c>
-      <c r="I41" s="22" t="n">
-        <v>19.47</v>
+        <v>-2.67</v>
+      </c>
+      <c r="I41" s="24" t="n">
+        <v>-11.52</v>
       </c>
       <c r="J41" s="23" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +76% / 중요공시 3건</t>
+          <t>네이버뉴스 헤드라인 언급 / 매일경제 헤드라인 언급</t>
         </is>
       </c>
       <c r="K41" s="23" t="inlineStr">
         <is>
-          <t>공시, 네이버</t>
+          <t>네이버</t>
         </is>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
       <c r="A42" s="20" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B42" s="20" t="n">
@@ -2116,7 +2120,7 @@
       </c>
       <c r="C42" s="21" t="inlineStr">
         <is>
-          <t>리가켐바이오</t>
+          <t>카카오</t>
         </is>
       </c>
       <c r="D42" s="20" t="n">
@@ -2132,26 +2136,26 @@
         <v>0</v>
       </c>
       <c r="H42" s="24" t="n">
-        <v>-8.279999999999999</v>
-      </c>
-      <c r="I42" s="22" t="n">
-        <v>6.17</v>
+        <v>-3.21</v>
+      </c>
+      <c r="I42" s="24" t="n">
+        <v>-12.19</v>
       </c>
       <c r="J42" s="23" t="inlineStr">
         <is>
-          <t>중요공시 2건 / 매일경제 헤드라인 언급 / 매일경제 기사 언급</t>
+          <t>네이버뉴스 헤드라인 언급 / 매일경제 헤드라인 언급</t>
         </is>
       </c>
       <c r="K42" s="23" t="inlineStr">
         <is>
-          <t>공시</t>
+          <t>네이버</t>
         </is>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1">
       <c r="A43" s="20" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B43" s="20" t="n">
@@ -2159,14 +2163,14 @@
       </c>
       <c r="C43" s="21" t="inlineStr">
         <is>
-          <t>금호건설</t>
+          <t>태양광</t>
         </is>
       </c>
       <c r="D43" s="20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E43" s="20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F43" s="20" t="n">
         <v>0</v>
@@ -2174,27 +2178,27 @@
       <c r="G43" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H43" s="22" t="n">
-        <v>30</v>
-      </c>
-      <c r="I43" s="22" t="n">
-        <v>57.86</v>
+      <c r="H43" s="20" t="n">
+        <v/>
+      </c>
+      <c r="I43" s="20" t="n">
+        <v/>
       </c>
       <c r="J43" s="23" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +348% / 중요공시 1건</t>
+          <t>네이버뉴스 헤드라인 언급 / 매일경제 헤드라인 언급</t>
         </is>
       </c>
       <c r="K43" s="23" t="inlineStr">
         <is>
-          <t>공시, 네이버</t>
+          <t>네이버</t>
         </is>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
       <c r="A44" s="20" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B44" s="20" t="n">
@@ -2202,14 +2206,14 @@
       </c>
       <c r="C44" s="21" t="inlineStr">
         <is>
-          <t>크리스탈신소재</t>
+          <t>조선</t>
         </is>
       </c>
       <c r="D44" s="20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E44" s="20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F44" s="20" t="n">
         <v>0</v>
@@ -2217,27 +2221,25 @@
       <c r="G44" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H44" s="22" t="n">
-        <v>18.81</v>
-      </c>
-      <c r="I44" s="24" t="n">
-        <v>-28.03</v>
+      <c r="H44" s="20" t="n">
+        <v/>
+      </c>
+      <c r="I44" s="20" t="n">
+        <v/>
       </c>
       <c r="J44" s="23" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +317% / 중요공시 1건</t>
-        </is>
-      </c>
-      <c r="K44" s="23" t="inlineStr">
-        <is>
-          <t>공시, 네이버</t>
-        </is>
+          <t>매일경제 헤드라인 언급 / 매일경제 기사 언급 / 매일경제 기사 언급</t>
+        </is>
+      </c>
+      <c r="K44" s="23" t="n">
+        <v/>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
       <c r="A45" s="20" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B45" s="20" t="n">
@@ -2245,7 +2247,7 @@
       </c>
       <c r="C45" s="21" t="inlineStr">
         <is>
-          <t>티이엠씨씨엔에스</t>
+          <t>금호건설</t>
         </is>
       </c>
       <c r="D45" s="20" t="n">
@@ -2264,23 +2266,23 @@
         <v>30</v>
       </c>
       <c r="I45" s="22" t="n">
-        <v>10.36</v>
+        <v>57.86</v>
       </c>
       <c r="J45" s="23" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +273% / 중요공시 1건</t>
+          <t>네이버 검색 당일 +397% / 중요공시 1건</t>
         </is>
       </c>
       <c r="K45" s="23" t="inlineStr">
         <is>
-          <t>공시, 네이버</t>
+          <t>네이버, 공시</t>
         </is>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
       <c r="A46" s="20" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B46" s="20" t="n">
@@ -2288,7 +2290,7 @@
       </c>
       <c r="C46" s="21" t="inlineStr">
         <is>
-          <t>베셀</t>
+          <t>티이엠씨씨엔에스</t>
         </is>
       </c>
       <c r="D46" s="20" t="n">
@@ -2304,26 +2306,26 @@
         <v>0</v>
       </c>
       <c r="H46" s="22" t="n">
-        <v>9.69</v>
+        <v>30</v>
       </c>
       <c r="I46" s="22" t="n">
-        <v>34.27</v>
+        <v>10.36</v>
       </c>
       <c r="J46" s="23" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +222% / 중요공시 2건</t>
+          <t>네이버 검색 당일 +388% / 중요공시 1건</t>
         </is>
       </c>
       <c r="K46" s="23" t="inlineStr">
         <is>
-          <t>공시, 네이버</t>
+          <t>네이버, 공시</t>
         </is>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
       <c r="A47" s="20" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B47" s="20" t="n">
@@ -2331,7 +2333,7 @@
       </c>
       <c r="C47" s="21" t="inlineStr">
         <is>
-          <t>남화토건</t>
+          <t>크리스탈신소재</t>
         </is>
       </c>
       <c r="D47" s="20" t="n">
@@ -2347,26 +2349,26 @@
         <v>0</v>
       </c>
       <c r="H47" s="22" t="n">
-        <v>29.96</v>
-      </c>
-      <c r="I47" s="22" t="n">
-        <v>28.96</v>
+        <v>18.81</v>
+      </c>
+      <c r="I47" s="24" t="n">
+        <v>-28.03</v>
       </c>
       <c r="J47" s="23" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +162% / 중요공시 1건</t>
+          <t>네이버 검색 당일 +336% / 중요공시 1건</t>
         </is>
       </c>
       <c r="K47" s="23" t="inlineStr">
         <is>
-          <t>공시, 네이버</t>
+          <t>네이버, 공시</t>
         </is>
       </c>
     </row>
     <row r="48" ht="18" customHeight="1">
       <c r="A48" s="20" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B48" s="20" t="n">
@@ -2374,7 +2376,7 @@
       </c>
       <c r="C48" s="21" t="inlineStr">
         <is>
-          <t>뉴인텍</t>
+          <t>헝셩그룹</t>
         </is>
       </c>
       <c r="D48" s="20" t="n">
@@ -2389,27 +2391,27 @@
       <c r="G48" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H48" s="22" t="n">
-        <v>29.93</v>
+      <c r="H48" s="24" t="n">
+        <v>-2.71</v>
       </c>
       <c r="I48" s="22" t="n">
-        <v>47.06</v>
+        <v>15.4</v>
       </c>
       <c r="J48" s="23" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +144% / 중요공시 1건</t>
+          <t>네이버 검색 당일 +299% / 중요공시 2건</t>
         </is>
       </c>
       <c r="K48" s="23" t="inlineStr">
         <is>
-          <t>공시, 네이버</t>
+          <t>네이버, 공시</t>
         </is>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1">
       <c r="A49" s="20" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B49" s="20" t="n">
@@ -2417,7 +2419,7 @@
       </c>
       <c r="C49" s="21" t="inlineStr">
         <is>
-          <t>에코프로</t>
+          <t>베셀</t>
         </is>
       </c>
       <c r="D49" s="20" t="n">
@@ -2432,27 +2434,27 @@
       <c r="G49" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H49" s="24" t="n">
-        <v>-6.47</v>
-      </c>
-      <c r="I49" s="24" t="n">
-        <v>-17.76</v>
+      <c r="H49" s="22" t="n">
+        <v>9.69</v>
+      </c>
+      <c r="I49" s="22" t="n">
+        <v>34.27</v>
       </c>
       <c r="J49" s="23" t="inlineStr">
         <is>
-          <t>중요공시 1건 / 네이버뉴스 헤드라인 언급</t>
+          <t>네이버 검색 당일 +235% / 중요공시 2건</t>
         </is>
       </c>
       <c r="K49" s="23" t="inlineStr">
         <is>
-          <t>공시, 네이버</t>
+          <t>네이버, 공시</t>
         </is>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
       <c r="A50" s="20" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B50" s="20" t="n">
@@ -2460,7 +2462,7 @@
       </c>
       <c r="C50" s="21" t="inlineStr">
         <is>
-          <t>SK텔레콤</t>
+          <t>남화토건</t>
         </is>
       </c>
       <c r="D50" s="20" t="n">
@@ -2475,27 +2477,27 @@
       <c r="G50" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H50" s="24" t="n">
-        <v>-0.88</v>
-      </c>
-      <c r="I50" s="24" t="n">
-        <v>-4.53</v>
+      <c r="H50" s="22" t="n">
+        <v>29.96</v>
+      </c>
+      <c r="I50" s="22" t="n">
+        <v>28.96</v>
       </c>
       <c r="J50" s="23" t="inlineStr">
         <is>
-          <t>중요공시 1건 / 매일경제 헤드라인 언급</t>
+          <t>네이버 검색 당일 +181% / 중요공시 1건</t>
         </is>
       </c>
       <c r="K50" s="23" t="inlineStr">
         <is>
-          <t>공시</t>
+          <t>네이버, 공시</t>
         </is>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
       <c r="A51" s="20" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B51" s="20" t="n">
@@ -2503,7 +2505,7 @@
       </c>
       <c r="C51" s="21" t="inlineStr">
         <is>
-          <t>카카오게임즈</t>
+          <t>뉴인텍</t>
         </is>
       </c>
       <c r="D51" s="20" t="n">
@@ -2518,27 +2520,27 @@
       <c r="G51" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H51" s="24" t="n">
-        <v>-9.41</v>
-      </c>
-      <c r="I51" s="24" t="n">
-        <v>-21.34</v>
+      <c r="H51" s="22" t="n">
+        <v>29.93</v>
+      </c>
+      <c r="I51" s="22" t="n">
+        <v>47.06</v>
       </c>
       <c r="J51" s="23" t="inlineStr">
         <is>
-          <t>중요공시 1건 / 한국경제 헤드라인 언급</t>
+          <t>네이버 검색 당일 +165% / 중요공시 1건</t>
         </is>
       </c>
       <c r="K51" s="23" t="inlineStr">
         <is>
-          <t>공시</t>
+          <t>네이버, 공시</t>
         </is>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1">
       <c r="A52" s="20" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B52" s="20" t="n">
@@ -2546,7 +2548,7 @@
       </c>
       <c r="C52" s="21" t="inlineStr">
         <is>
-          <t>한미반도체</t>
+          <t>다스코</t>
         </is>
       </c>
       <c r="D52" s="20" t="n">
@@ -2562,24 +2564,26 @@
         <v>0</v>
       </c>
       <c r="H52" s="24" t="n">
-        <v>-5.68</v>
+        <v>-16.32</v>
       </c>
       <c r="I52" s="24" t="n">
-        <v>-12.71</v>
+        <v>-1.01</v>
       </c>
       <c r="J52" s="23" t="inlineStr">
         <is>
-          <t>매일경제 헤드라인 언급 / 매일경제 기사 언급</t>
-        </is>
-      </c>
-      <c r="K52" s="23" t="n">
-        <v/>
+          <t>네이버 검색 당일 +146% / 중요공시 1건</t>
+        </is>
+      </c>
+      <c r="K52" s="23" t="inlineStr">
+        <is>
+          <t>네이버, 공시</t>
+        </is>
       </c>
     </row>
     <row r="53" ht="18" customHeight="1">
       <c r="A53" s="20" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B53" s="20" t="n">
@@ -2587,7 +2591,7 @@
       </c>
       <c r="C53" s="21" t="inlineStr">
         <is>
-          <t>제약</t>
+          <t>남광토건</t>
         </is>
       </c>
       <c r="D53" s="20" t="n">
@@ -2602,27 +2606,27 @@
       <c r="G53" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H53" s="20" t="n">
-        <v/>
-      </c>
-      <c r="I53" s="20" t="n">
-        <v/>
+      <c r="H53" s="22" t="n">
+        <v>6.41</v>
+      </c>
+      <c r="I53" s="22" t="n">
+        <v>5.06</v>
       </c>
       <c r="J53" s="23" t="inlineStr">
         <is>
-          <t>네이버뉴스 기사 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 기사 언급</t>
+          <t>중요공시 3건</t>
         </is>
       </c>
       <c r="K53" s="23" t="inlineStr">
         <is>
-          <t>네이버</t>
+          <t>공시</t>
         </is>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
       <c r="A54" s="20" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B54" s="20" t="n">
@@ -2630,7 +2634,7 @@
       </c>
       <c r="C54" s="21" t="inlineStr">
         <is>
-          <t>조선</t>
+          <t>SK텔레콤</t>
         </is>
       </c>
       <c r="D54" s="20" t="n">
@@ -2645,240 +2649,238 @@
       <c r="G54" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H54" s="20" t="n">
+      <c r="H54" s="24" t="n">
+        <v>-0.88</v>
+      </c>
+      <c r="I54" s="24" t="n">
+        <v>-4.53</v>
+      </c>
+      <c r="J54" s="23" t="inlineStr">
+        <is>
+          <t>중요공시 1건 / 매일경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K54" s="23" t="inlineStr">
+        <is>
+          <t>공시</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="18" customHeight="1">
+      <c r="A55" s="20" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B55" s="20" t="n">
+        <v>42</v>
+      </c>
+      <c r="C55" s="21" t="inlineStr">
+        <is>
+          <t>카카오게임즈</t>
+        </is>
+      </c>
+      <c r="D55" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="E55" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="F55" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G55" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H55" s="24" t="n">
+        <v>-9.41</v>
+      </c>
+      <c r="I55" s="24" t="n">
+        <v>-21.34</v>
+      </c>
+      <c r="J55" s="23" t="inlineStr">
+        <is>
+          <t>중요공시 1건 / 네이버뉴스 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K55" s="23" t="inlineStr">
+        <is>
+          <t>네이버, 공시</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="18" customHeight="1">
+      <c r="A56" s="20" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B56" s="20" t="n">
+        <v>43</v>
+      </c>
+      <c r="C56" s="21" t="inlineStr">
+        <is>
+          <t>셀트리온</t>
+        </is>
+      </c>
+      <c r="D56" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="E56" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="F56" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G56" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H56" s="24" t="n">
+        <v>-4.16</v>
+      </c>
+      <c r="I56" s="24" t="n">
+        <v>-2.58</v>
+      </c>
+      <c r="J56" s="23" t="inlineStr">
+        <is>
+          <t>중요공시 1건 / 네이버뉴스 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K56" s="23" t="inlineStr">
+        <is>
+          <t>네이버, 공시</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="18" customHeight="1">
+      <c r="A57" s="20" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B57" s="20" t="n">
+        <v>44</v>
+      </c>
+      <c r="C57" s="21" t="inlineStr">
+        <is>
+          <t>게임</t>
+        </is>
+      </c>
+      <c r="D57" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="E57" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="F57" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G57" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H57" s="20" t="n">
         <v/>
       </c>
-      <c r="I54" s="20" t="n">
+      <c r="I57" s="20" t="n">
         <v/>
       </c>
-      <c r="J54" s="23" t="inlineStr">
-        <is>
-          <t>매일경제 기사 언급 / 매일경제 헤드라인 언급 / 매일경제 기사 언급</t>
-        </is>
-      </c>
-      <c r="K54" s="23" t="n">
+      <c r="J57" s="23" t="inlineStr">
+        <is>
+          <t>네이버뉴스 헤드라인 언급 / 네이버뉴스 기사 언급</t>
+        </is>
+      </c>
+      <c r="K57" s="23" t="inlineStr">
+        <is>
+          <t>네이버</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="18" customHeight="1">
+      <c r="A58" s="20" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B58" s="20" t="n">
+        <v>45</v>
+      </c>
+      <c r="C58" s="21" t="inlineStr">
+        <is>
+          <t>한미반도체</t>
+        </is>
+      </c>
+      <c r="D58" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="E58" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="F58" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G58" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H58" s="24" t="n">
+        <v>-5.68</v>
+      </c>
+      <c r="I58" s="24" t="n">
+        <v>-12.71</v>
+      </c>
+      <c r="J58" s="23" t="inlineStr">
+        <is>
+          <t>매일경제 헤드라인 언급 / 매일경제 기사 언급</t>
+        </is>
+      </c>
+      <c r="K58" s="23" t="n">
         <v/>
       </c>
     </row>
-    <row r="55" ht="18" customHeight="1">
-      <c r="A55" s="25" t="inlineStr">
-        <is>
-          <t>2026-06-28</t>
-        </is>
-      </c>
-      <c r="B55" s="25" t="n">
-        <v>42</v>
-      </c>
-      <c r="C55" s="26" t="inlineStr">
-        <is>
-          <t>프로브잇</t>
-        </is>
-      </c>
-      <c r="D55" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="E55" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="F55" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="G55" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="H55" s="27" t="n">
-        <v>-40</v>
-      </c>
-      <c r="I55" s="27" t="n">
-        <v>-98.53</v>
-      </c>
-      <c r="J55" s="28" t="inlineStr">
-        <is>
-          <t>네이버 검색 당일 +1980%</t>
-        </is>
-      </c>
-      <c r="K55" s="28" t="inlineStr">
-        <is>
-          <t>네이버</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" ht="18" customHeight="1">
-      <c r="A56" s="25" t="inlineStr">
-        <is>
-          <t>2026-06-28</t>
-        </is>
-      </c>
-      <c r="B56" s="25" t="n">
-        <v>43</v>
-      </c>
-      <c r="C56" s="26" t="inlineStr">
-        <is>
-          <t>NPX</t>
-        </is>
-      </c>
-      <c r="D56" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="E56" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="F56" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="G56" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="H56" s="27" t="n">
-        <v>-97.41</v>
-      </c>
-      <c r="I56" s="27" t="n">
-        <v>-97.41</v>
-      </c>
-      <c r="J56" s="28" t="inlineStr">
-        <is>
-          <t>네이버 검색 당일 +1112%</t>
-        </is>
-      </c>
-      <c r="K56" s="28" t="inlineStr">
-        <is>
-          <t>네이버</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="18" customHeight="1">
-      <c r="A57" s="25" t="inlineStr">
-        <is>
-          <t>2026-06-28</t>
-        </is>
-      </c>
-      <c r="B57" s="25" t="n">
-        <v>44</v>
-      </c>
-      <c r="C57" s="26" t="inlineStr">
-        <is>
-          <t>남화산업</t>
-        </is>
-      </c>
-      <c r="D57" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="E57" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="F57" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="G57" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="H57" s="29" t="n">
-        <v>29.97</v>
-      </c>
-      <c r="I57" s="29" t="n">
-        <v>30.84</v>
-      </c>
-      <c r="J57" s="28" t="inlineStr">
-        <is>
-          <t>네이버 검색 당일 +858%</t>
-        </is>
-      </c>
-      <c r="K57" s="28" t="inlineStr">
-        <is>
-          <t>네이버</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" ht="18" customHeight="1">
-      <c r="A58" s="25" t="inlineStr">
-        <is>
-          <t>2026-06-28</t>
-        </is>
-      </c>
-      <c r="B58" s="25" t="n">
-        <v>45</v>
-      </c>
-      <c r="C58" s="26" t="inlineStr">
-        <is>
-          <t>노블엠앤비</t>
-        </is>
-      </c>
-      <c r="D58" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="E58" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="F58" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="G58" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="H58" s="27" t="n">
-        <v>-7.69</v>
-      </c>
-      <c r="I58" s="27" t="n">
-        <v>-97.08</v>
-      </c>
-      <c r="J58" s="28" t="inlineStr">
-        <is>
-          <t>네이버 검색 당일 +783%</t>
-        </is>
-      </c>
-      <c r="K58" s="28" t="inlineStr">
-        <is>
-          <t>네이버</t>
-        </is>
-      </c>
-    </row>
     <row r="59" ht="18" customHeight="1">
-      <c r="A59" s="25" t="inlineStr">
-        <is>
-          <t>2026-06-28</t>
-        </is>
-      </c>
-      <c r="B59" s="25" t="n">
+      <c r="A59" s="20" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B59" s="20" t="n">
         <v>46</v>
       </c>
-      <c r="C59" s="26" t="inlineStr">
-        <is>
-          <t>삼기에너지솔루션즈</t>
-        </is>
-      </c>
-      <c r="D59" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="E59" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="F59" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="G59" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="H59" s="27" t="n">
-        <v>-18.39</v>
-      </c>
-      <c r="I59" s="29" t="n">
-        <v>21.26</v>
-      </c>
-      <c r="J59" s="28" t="inlineStr">
-        <is>
-          <t>네이버 검색 당일 +770%</t>
-        </is>
-      </c>
-      <c r="K59" s="28" t="inlineStr">
-        <is>
-          <t>네이버</t>
-        </is>
+      <c r="C59" s="21" t="inlineStr">
+        <is>
+          <t>전기차</t>
+        </is>
+      </c>
+      <c r="D59" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="E59" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="F59" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G59" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H59" s="20" t="n">
+        <v/>
+      </c>
+      <c r="I59" s="20" t="n">
+        <v/>
+      </c>
+      <c r="J59" s="23" t="inlineStr">
+        <is>
+          <t>매일경제 기사 언급 / 매일경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K59" s="23" t="n">
+        <v/>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1">
       <c r="A60" s="25" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B60" s="25" t="n">
@@ -2886,7 +2888,7 @@
       </c>
       <c r="C60" s="26" t="inlineStr">
         <is>
-          <t>서암기계공업</t>
+          <t>프로브잇</t>
         </is>
       </c>
       <c r="D60" s="25" t="n">
@@ -2901,15 +2903,15 @@
       <c r="G60" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H60" s="29" t="n">
-        <v>3.72</v>
-      </c>
-      <c r="I60" s="29" t="n">
-        <v>1.52</v>
+      <c r="H60" s="27" t="n">
+        <v>-40</v>
+      </c>
+      <c r="I60" s="27" t="n">
+        <v>-98.53</v>
       </c>
       <c r="J60" s="28" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +748%</t>
+          <t>네이버 검색 당일 +2008%</t>
         </is>
       </c>
       <c r="K60" s="28" t="inlineStr">
@@ -2921,7 +2923,7 @@
     <row r="61" ht="18" customHeight="1">
       <c r="A61" s="25" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B61" s="25" t="n">
@@ -2929,7 +2931,7 @@
       </c>
       <c r="C61" s="26" t="inlineStr">
         <is>
-          <t>바이온</t>
+          <t>광주신세계</t>
         </is>
       </c>
       <c r="D61" s="25" t="n">
@@ -2944,15 +2946,15 @@
       <c r="G61" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H61" s="27" t="n">
-        <v>-50</v>
-      </c>
-      <c r="I61" s="27" t="n">
-        <v>-98.84</v>
+      <c r="H61" s="29" t="n">
+        <v>29.98</v>
+      </c>
+      <c r="I61" s="29" t="n">
+        <v>50.71</v>
       </c>
       <c r="J61" s="28" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +545%</t>
+          <t>네이버 검색 당일 +1484%</t>
         </is>
       </c>
       <c r="K61" s="28" t="inlineStr">
@@ -2964,7 +2966,7 @@
     <row r="62" ht="18" customHeight="1">
       <c r="A62" s="25" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B62" s="25" t="n">
@@ -2972,7 +2974,7 @@
       </c>
       <c r="C62" s="26" t="inlineStr">
         <is>
-          <t>디와이에이</t>
+          <t>NPX</t>
         </is>
       </c>
       <c r="D62" s="25" t="n">
@@ -2987,15 +2989,15 @@
       <c r="G62" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H62" s="29" t="n">
-        <v>25.79</v>
-      </c>
-      <c r="I62" s="29" t="n">
-        <v>31.47</v>
+      <c r="H62" s="27" t="n">
+        <v>-97.41</v>
+      </c>
+      <c r="I62" s="27" t="n">
+        <v>-97.41</v>
       </c>
       <c r="J62" s="28" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +495%</t>
+          <t>네이버 검색 당일 +1237%</t>
         </is>
       </c>
       <c r="K62" s="28" t="inlineStr">
@@ -3007,7 +3009,7 @@
     <row r="63" ht="18" customHeight="1">
       <c r="A63" s="25" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B63" s="25" t="n">
@@ -3015,7 +3017,7 @@
       </c>
       <c r="C63" s="26" t="inlineStr">
         <is>
-          <t>조아제약</t>
+          <t>남화산업</t>
         </is>
       </c>
       <c r="D63" s="25" t="n">
@@ -3031,14 +3033,14 @@
         <v>0</v>
       </c>
       <c r="H63" s="29" t="n">
-        <v>4.55</v>
+        <v>29.97</v>
       </c>
       <c r="I63" s="29" t="n">
-        <v>44.97</v>
+        <v>30.84</v>
       </c>
       <c r="J63" s="28" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +475%</t>
+          <t>네이버 검색 당일 +931%</t>
         </is>
       </c>
       <c r="K63" s="28" t="inlineStr">
@@ -3140,22 +3142,22 @@
         <v>1</v>
       </c>
       <c r="C3" s="25" t="n">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="D3" s="25" t="n">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="E3" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F3" s="25" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G3" s="25" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="H3" s="25" t="n"/>
@@ -3171,22 +3173,22 @@
         <v>1</v>
       </c>
       <c r="C4" s="25" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="D4" s="25" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="E4" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F4" s="25" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G4" s="25" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="H4" s="27" t="n">
@@ -3199,37 +3201,33 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="26" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>바이오</t>
         </is>
       </c>
       <c r="B5" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C5" s="25" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="D5" s="25" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="E5" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F5" s="25" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G5" s="25" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
-        </is>
-      </c>
-      <c r="H5" s="27" t="n">
-        <v>-8.359999999999999</v>
-      </c>
-      <c r="I5" s="27" t="n">
-        <v>-3.29</v>
-      </c>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="H5" s="25" t="n"/>
+      <c r="I5" s="25" t="n"/>
     </row>
     <row r="6" ht="18" customHeight="1">
       <c r="A6" s="26" t="inlineStr">
@@ -3241,22 +3239,22 @@
         <v>1</v>
       </c>
       <c r="C6" s="25" t="n">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="D6" s="25" t="n">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="E6" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F6" s="25" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G6" s="25" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="H6" s="27" t="n">
@@ -3269,36 +3267,36 @@
     <row r="7" ht="18" customHeight="1">
       <c r="A7" s="26" t="inlineStr">
         <is>
-          <t>LG</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B7" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C7" s="25" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D7" s="25" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E7" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F7" s="25" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G7" s="25" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="H7" s="27" t="n">
-        <v>-0.8</v>
+        <v>-8.359999999999999</v>
       </c>
       <c r="I7" s="27" t="n">
-        <v>-9.460000000000001</v>
+        <v>-3.29</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
@@ -3311,22 +3309,22 @@
         <v>1</v>
       </c>
       <c r="C8" s="25" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D8" s="25" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E8" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F8" s="25" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G8" s="25" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="H8" s="25" t="n"/>
@@ -3335,33 +3333,37 @@
     <row r="9" ht="18" customHeight="1">
       <c r="A9" s="26" t="inlineStr">
         <is>
-          <t>바이오</t>
+          <t>LG</t>
         </is>
       </c>
       <c r="B9" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C9" s="25" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="D9" s="25" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E9" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F9" s="25" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G9" s="25" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
-        </is>
-      </c>
-      <c r="H9" s="25" t="n"/>
-      <c r="I9" s="25" t="n"/>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="H9" s="27" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="I9" s="27" t="n">
+        <v>-9.460000000000001</v>
+      </c>
     </row>
     <row r="10" ht="18" customHeight="1">
       <c r="A10" s="26" t="inlineStr">
@@ -3373,22 +3375,22 @@
         <v>1</v>
       </c>
       <c r="C10" s="25" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D10" s="25" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E10" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F10" s="25" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G10" s="25" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="H10" s="25" t="n"/>
@@ -3397,77 +3399,69 @@
     <row r="11" ht="18" customHeight="1">
       <c r="A11" s="26" t="inlineStr">
         <is>
-          <t>LG이노텍</t>
+          <t>제약</t>
         </is>
       </c>
       <c r="B11" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C11" s="25" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D11" s="25" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E11" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F11" s="25" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G11" s="25" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
-        </is>
-      </c>
-      <c r="H11" s="27" t="n">
-        <v>-2.31</v>
-      </c>
-      <c r="I11" s="27" t="n">
-        <v>-18.69</v>
-      </c>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="H11" s="25" t="n"/>
+      <c r="I11" s="25" t="n"/>
     </row>
     <row r="12" ht="18" customHeight="1">
       <c r="A12" s="26" t="inlineStr">
         <is>
-          <t>젠큐릭스</t>
+          <t>방산</t>
         </is>
       </c>
       <c r="B12" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C12" s="25" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D12" s="25" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E12" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F12" s="25" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G12" s="25" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
-        </is>
-      </c>
-      <c r="H12" s="27" t="n">
-        <v>-1.9</v>
-      </c>
-      <c r="I12" s="27" t="n">
-        <v>-12.13</v>
-      </c>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="H12" s="25" t="n"/>
+      <c r="I12" s="25" t="n"/>
     </row>
     <row r="13" ht="18" customHeight="1">
       <c r="A13" s="26" t="inlineStr">
         <is>
-          <t>카카오</t>
+          <t>LG이노텍</t>
         </is>
       </c>
       <c r="B13" s="25" t="n">
@@ -3484,60 +3478,60 @@
       </c>
       <c r="F13" s="25" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G13" s="25" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="H13" s="27" t="n">
-        <v>-3.21</v>
+        <v>-2.31</v>
       </c>
       <c r="I13" s="27" t="n">
-        <v>-12.19</v>
+        <v>-18.69</v>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="26" t="inlineStr">
         <is>
-          <t>성호전자</t>
+          <t>젠큐릭스</t>
         </is>
       </c>
       <c r="B14" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C14" s="25" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D14" s="25" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E14" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F14" s="25" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G14" s="25" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
-        </is>
-      </c>
-      <c r="H14" s="29" t="n">
-        <v>0.52</v>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="H14" s="27" t="n">
+        <v>-1.9</v>
       </c>
       <c r="I14" s="27" t="n">
-        <v>-24.25</v>
+        <v>-12.13</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
       <c r="A15" s="26" t="inlineStr">
         <is>
-          <t>파두</t>
+          <t>성호전자</t>
         </is>
       </c>
       <c r="B15" s="25" t="n">
@@ -3554,126 +3548,130 @@
       </c>
       <c r="F15" s="25" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G15" s="25" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
-        </is>
-      </c>
-      <c r="H15" s="27" t="n">
-        <v>-5.14</v>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="H15" s="29" t="n">
+        <v>0.52</v>
       </c>
       <c r="I15" s="27" t="n">
-        <v>-18.15</v>
+        <v>-24.25</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
       <c r="A16" s="26" t="inlineStr">
         <is>
-          <t>페니트리움바이오</t>
+          <t>LG전자</t>
         </is>
       </c>
       <c r="B16" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C16" s="25" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D16" s="25" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E16" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F16" s="25" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G16" s="25" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="H16" s="27" t="n">
-        <v>-2.96</v>
+        <v>-3.5</v>
       </c>
       <c r="I16" s="27" t="n">
-        <v>-11.93</v>
+        <v>-7.38</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
       <c r="A17" s="26" t="inlineStr">
         <is>
-          <t>다스코</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B17" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C17" s="25" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D17" s="25" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E17" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F17" s="25" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G17" s="25" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="H17" s="27" t="n">
-        <v>-16.32</v>
+        <v>-8.41</v>
       </c>
       <c r="I17" s="27" t="n">
-        <v>-1.01</v>
+        <v>-14.4</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
       <c r="A18" s="26" t="inlineStr">
         <is>
-          <t>전기차</t>
+          <t>삼성바이오로직스</t>
         </is>
       </c>
       <c r="B18" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C18" s="25" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D18" s="25" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E18" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F18" s="25" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G18" s="25" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
-        </is>
-      </c>
-      <c r="H18" s="25" t="n"/>
-      <c r="I18" s="25" t="n"/>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="H18" s="27" t="n">
+        <v>-3.1</v>
+      </c>
+      <c r="I18" s="27" t="n">
+        <v>-2.26</v>
+      </c>
     </row>
     <row r="19" ht="18" customHeight="1">
       <c r="A19" s="26" t="inlineStr">
         <is>
-          <t>KB금융</t>
+          <t>삼호개발</t>
         </is>
       </c>
       <c r="B19" s="25" t="n">
@@ -3690,25 +3688,25 @@
       </c>
       <c r="F19" s="25" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G19" s="25" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
-        </is>
-      </c>
-      <c r="H19" s="27" t="n">
-        <v>-1.71</v>
-      </c>
-      <c r="I19" s="27" t="n">
-        <v>-5.69</v>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="H19" s="29" t="n">
+        <v>8.69</v>
+      </c>
+      <c r="I19" s="29" t="n">
+        <v>16.77</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
       <c r="A20" s="26" t="inlineStr">
         <is>
-          <t>LG전자</t>
+          <t>샤페론</t>
         </is>
       </c>
       <c r="B20" s="25" t="n">
@@ -3725,25 +3723,25 @@
       </c>
       <c r="F20" s="25" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G20" s="25" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="H20" s="27" t="n">
-        <v>-3.5</v>
+        <v>-25.16</v>
       </c>
       <c r="I20" s="27" t="n">
-        <v>-7.38</v>
+        <v>-56.14</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
       <c r="A21" s="26" t="inlineStr">
         <is>
-          <t>광주신세계</t>
+          <t>스피어</t>
         </is>
       </c>
       <c r="B21" s="25" t="n">
@@ -3760,25 +3758,25 @@
       </c>
       <c r="F21" s="25" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G21" s="25" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
-        </is>
-      </c>
-      <c r="H21" s="29" t="n">
-        <v>29.98</v>
-      </c>
-      <c r="I21" s="29" t="n">
-        <v>50.71</v>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="H21" s="27" t="n">
+        <v>-8.76</v>
+      </c>
+      <c r="I21" s="27" t="n">
+        <v>-31.49</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
       <c r="A22" s="26" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>에이팩트</t>
         </is>
       </c>
       <c r="B22" s="25" t="n">
@@ -3795,25 +3793,25 @@
       </c>
       <c r="F22" s="25" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G22" s="25" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="H22" s="27" t="n">
-        <v>-8.41</v>
+        <v>-6.74</v>
       </c>
       <c r="I22" s="27" t="n">
-        <v>-14.4</v>
+        <v>-26.62</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
       <c r="A23" s="26" t="inlineStr">
         <is>
-          <t>대한항공</t>
+          <t>차바이오텍</t>
         </is>
       </c>
       <c r="B23" s="25" t="n">
@@ -3830,25 +3828,25 @@
       </c>
       <c r="F23" s="25" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G23" s="25" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="H23" s="27" t="n">
-        <v>-3.61</v>
-      </c>
-      <c r="I23" s="29" t="n">
-        <v>0.36</v>
+        <v>-4.12</v>
+      </c>
+      <c r="I23" s="27" t="n">
+        <v>-12.15</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
       <c r="A24" s="26" t="inlineStr">
         <is>
-          <t>삼성물산</t>
+          <t>페니트리움바이오</t>
         </is>
       </c>
       <c r="B24" s="25" t="n">
@@ -3865,200 +3863,200 @@
       </c>
       <c r="F24" s="25" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G24" s="25" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="H24" s="27" t="n">
-        <v>-4.72</v>
-      </c>
-      <c r="I24" s="29" t="n">
-        <v>0.61</v>
+        <v>-2.96</v>
+      </c>
+      <c r="I24" s="27" t="n">
+        <v>-11.93</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
       <c r="A25" s="26" t="inlineStr">
         <is>
-          <t>삼호개발</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="B25" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C25" s="25" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D25" s="25" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E25" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F25" s="25" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G25" s="25" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
-        </is>
-      </c>
-      <c r="H25" s="29" t="n">
-        <v>8.69</v>
-      </c>
-      <c r="I25" s="29" t="n">
-        <v>16.77</v>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="H25" s="27" t="n">
+        <v>-2.67</v>
+      </c>
+      <c r="I25" s="27" t="n">
+        <v>-11.52</v>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
       <c r="A26" s="26" t="inlineStr">
         <is>
-          <t>스피어</t>
+          <t>리가켐바이오</t>
         </is>
       </c>
       <c r="B26" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C26" s="25" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D26" s="25" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E26" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F26" s="25" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G26" s="25" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="H26" s="27" t="n">
-        <v>-8.76</v>
-      </c>
-      <c r="I26" s="27" t="n">
-        <v>-31.49</v>
+        <v>-8.279999999999999</v>
+      </c>
+      <c r="I26" s="29" t="n">
+        <v>6.17</v>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
       <c r="A27" s="26" t="inlineStr">
         <is>
-          <t>카카오뱅크</t>
+          <t>소룩스</t>
         </is>
       </c>
       <c r="B27" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C27" s="25" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D27" s="25" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E27" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F27" s="25" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G27" s="25" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="H27" s="27" t="n">
-        <v>-3.42</v>
-      </c>
-      <c r="I27" s="27" t="n">
-        <v>-10.84</v>
+        <v>-4.21</v>
+      </c>
+      <c r="I27" s="29" t="n">
+        <v>19.47</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
       <c r="A28" s="26" t="inlineStr">
         <is>
-          <t>헝셩그룹</t>
+          <t>에이프릴바이오</t>
         </is>
       </c>
       <c r="B28" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C28" s="25" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D28" s="25" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E28" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F28" s="25" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G28" s="25" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="H28" s="27" t="n">
-        <v>-2.71</v>
+        <v>-0.13</v>
       </c>
       <c r="I28" s="29" t="n">
-        <v>15.4</v>
+        <v>1.72</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
       <c r="A29" s="26" t="inlineStr">
         <is>
-          <t>현대차</t>
+          <t>오텍</t>
         </is>
       </c>
       <c r="B29" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C29" s="25" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D29" s="25" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E29" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F29" s="25" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G29" s="25" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
-        </is>
-      </c>
-      <c r="H29" s="27" t="n">
-        <v>-4.47</v>
-      </c>
-      <c r="I29" s="27" t="n">
-        <v>-21.62</v>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="H29" s="29" t="n">
+        <v>13.75</v>
+      </c>
+      <c r="I29" s="29" t="n">
+        <v>32.47</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
       <c r="A30" s="26" t="inlineStr">
         <is>
-          <t>리가켐바이오</t>
+          <t>조선</t>
         </is>
       </c>
       <c r="B30" s="25" t="n">
@@ -4075,25 +4073,21 @@
       </c>
       <c r="F30" s="25" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G30" s="25" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
-        </is>
-      </c>
-      <c r="H30" s="27" t="n">
-        <v>-8.279999999999999</v>
-      </c>
-      <c r="I30" s="29" t="n">
-        <v>6.17</v>
-      </c>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="H30" s="25" t="n"/>
+      <c r="I30" s="25" t="n"/>
     </row>
     <row r="31" ht="18" customHeight="1">
       <c r="A31" s="26" t="inlineStr">
         <is>
-          <t>소룩스</t>
+          <t>카카오</t>
         </is>
       </c>
       <c r="B31" s="25" t="n">
@@ -4110,95 +4104,91 @@
       </c>
       <c r="F31" s="25" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G31" s="25" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="H31" s="27" t="n">
-        <v>-4.21</v>
-      </c>
-      <c r="I31" s="29" t="n">
-        <v>19.47</v>
+        <v>-3.21</v>
+      </c>
+      <c r="I31" s="27" t="n">
+        <v>-12.19</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
       <c r="A32" s="26" t="inlineStr">
         <is>
-          <t>SK텔레콤</t>
+          <t>태양광</t>
         </is>
       </c>
       <c r="B32" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C32" s="25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D32" s="25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E32" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F32" s="25" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G32" s="25" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
-        </is>
-      </c>
-      <c r="H32" s="27" t="n">
-        <v>-0.88</v>
-      </c>
-      <c r="I32" s="27" t="n">
-        <v>-4.53</v>
-      </c>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="H32" s="25" t="n"/>
+      <c r="I32" s="25" t="n"/>
     </row>
     <row r="33" ht="18" customHeight="1">
       <c r="A33" s="26" t="inlineStr">
         <is>
-          <t>금호건설</t>
+          <t>파두</t>
         </is>
       </c>
       <c r="B33" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C33" s="25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D33" s="25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E33" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F33" s="25" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G33" s="25" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
-        </is>
-      </c>
-      <c r="H33" s="29" t="n">
-        <v>30</v>
-      </c>
-      <c r="I33" s="29" t="n">
-        <v>57.86</v>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="H33" s="27" t="n">
+        <v>-5.14</v>
+      </c>
+      <c r="I33" s="27" t="n">
+        <v>-18.15</v>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
       <c r="A34" s="26" t="inlineStr">
         <is>
-          <t>남화토건</t>
+          <t>SK텔레콤</t>
         </is>
       </c>
       <c r="B34" s="25" t="n">
@@ -4215,25 +4205,25 @@
       </c>
       <c r="F34" s="25" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G34" s="25" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
-        </is>
-      </c>
-      <c r="H34" s="29" t="n">
-        <v>29.96</v>
-      </c>
-      <c r="I34" s="29" t="n">
-        <v>28.96</v>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="H34" s="27" t="n">
+        <v>-0.88</v>
+      </c>
+      <c r="I34" s="27" t="n">
+        <v>-4.53</v>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
       <c r="A35" s="26" t="inlineStr">
         <is>
-          <t>뉴인텍</t>
+          <t>게임</t>
         </is>
       </c>
       <c r="B35" s="25" t="n">
@@ -4250,25 +4240,21 @@
       </c>
       <c r="F35" s="25" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G35" s="25" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
-        </is>
-      </c>
-      <c r="H35" s="29" t="n">
-        <v>29.93</v>
-      </c>
-      <c r="I35" s="29" t="n">
-        <v>47.06</v>
-      </c>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="H35" s="25" t="n"/>
+      <c r="I35" s="25" t="n"/>
     </row>
     <row r="36" ht="18" customHeight="1">
       <c r="A36" s="26" t="inlineStr">
         <is>
-          <t>베셀</t>
+          <t>금호건설</t>
         </is>
       </c>
       <c r="B36" s="25" t="n">
@@ -4285,25 +4271,25 @@
       </c>
       <c r="F36" s="25" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G36" s="25" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="H36" s="29" t="n">
-        <v>9.69</v>
+        <v>30</v>
       </c>
       <c r="I36" s="29" t="n">
-        <v>34.27</v>
+        <v>57.86</v>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
       <c r="A37" s="26" t="inlineStr">
         <is>
-          <t>에코프로</t>
+          <t>남광토건</t>
         </is>
       </c>
       <c r="B37" s="25" t="n">
@@ -4320,25 +4306,25 @@
       </c>
       <c r="F37" s="25" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G37" s="25" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
-        </is>
-      </c>
-      <c r="H37" s="27" t="n">
-        <v>-6.47</v>
-      </c>
-      <c r="I37" s="27" t="n">
-        <v>-17.76</v>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="H37" s="29" t="n">
+        <v>6.41</v>
+      </c>
+      <c r="I37" s="29" t="n">
+        <v>5.06</v>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
       <c r="A38" s="26" t="inlineStr">
         <is>
-          <t>제약</t>
+          <t>남화토건</t>
         </is>
       </c>
       <c r="B38" s="25" t="n">
@@ -4355,21 +4341,25 @@
       </c>
       <c r="F38" s="25" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G38" s="25" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
-        </is>
-      </c>
-      <c r="H38" s="25" t="n"/>
-      <c r="I38" s="25" t="n"/>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="H38" s="29" t="n">
+        <v>29.96</v>
+      </c>
+      <c r="I38" s="29" t="n">
+        <v>28.96</v>
+      </c>
     </row>
     <row r="39" ht="18" customHeight="1">
       <c r="A39" s="26" t="inlineStr">
         <is>
-          <t>조선</t>
+          <t>뉴인텍</t>
         </is>
       </c>
       <c r="B39" s="25" t="n">
@@ -4386,21 +4376,25 @@
       </c>
       <c r="F39" s="25" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G39" s="25" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
-        </is>
-      </c>
-      <c r="H39" s="25" t="n"/>
-      <c r="I39" s="25" t="n"/>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="H39" s="29" t="n">
+        <v>29.93</v>
+      </c>
+      <c r="I39" s="29" t="n">
+        <v>47.06</v>
+      </c>
     </row>
     <row r="40" ht="18" customHeight="1">
       <c r="A40" s="26" t="inlineStr">
         <is>
-          <t>카카오게임즈</t>
+          <t>다스코</t>
         </is>
       </c>
       <c r="B40" s="25" t="n">
@@ -4417,25 +4411,25 @@
       </c>
       <c r="F40" s="25" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G40" s="25" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="H40" s="27" t="n">
-        <v>-9.41</v>
+        <v>-16.32</v>
       </c>
       <c r="I40" s="27" t="n">
-        <v>-21.34</v>
+        <v>-1.01</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
       <c r="A41" s="26" t="inlineStr">
         <is>
-          <t>크리스탈신소재</t>
+          <t>베셀</t>
         </is>
       </c>
       <c r="B41" s="25" t="n">
@@ -4452,25 +4446,25 @@
       </c>
       <c r="F41" s="25" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G41" s="25" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="H41" s="29" t="n">
-        <v>18.81</v>
-      </c>
-      <c r="I41" s="27" t="n">
-        <v>-28.03</v>
+        <v>9.69</v>
+      </c>
+      <c r="I41" s="29" t="n">
+        <v>34.27</v>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
       <c r="A42" s="26" t="inlineStr">
         <is>
-          <t>티이엠씨씨엔에스</t>
+          <t>셀트리온</t>
         </is>
       </c>
       <c r="B42" s="25" t="n">
@@ -4487,25 +4481,25 @@
       </c>
       <c r="F42" s="25" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G42" s="25" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
-        </is>
-      </c>
-      <c r="H42" s="29" t="n">
-        <v>30</v>
-      </c>
-      <c r="I42" s="29" t="n">
-        <v>10.36</v>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="H42" s="27" t="n">
+        <v>-4.16</v>
+      </c>
+      <c r="I42" s="27" t="n">
+        <v>-2.58</v>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1">
       <c r="A43" s="26" t="inlineStr">
         <is>
-          <t>한미반도체</t>
+          <t>전기차</t>
         </is>
       </c>
       <c r="B43" s="25" t="n">
@@ -4522,200 +4516,196 @@
       </c>
       <c r="F43" s="25" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G43" s="25" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
-        </is>
-      </c>
-      <c r="H43" s="27" t="n">
-        <v>-5.68</v>
-      </c>
-      <c r="I43" s="27" t="n">
-        <v>-12.71</v>
-      </c>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="H43" s="25" t="n"/>
+      <c r="I43" s="25" t="n"/>
     </row>
     <row r="44" ht="18" customHeight="1">
       <c r="A44" s="26" t="inlineStr">
         <is>
-          <t>NPX</t>
+          <t>카카오게임즈</t>
         </is>
       </c>
       <c r="B44" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C44" s="25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D44" s="25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E44" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F44" s="25" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G44" s="25" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="H44" s="27" t="n">
-        <v>-97.41</v>
+        <v>-9.41</v>
       </c>
       <c r="I44" s="27" t="n">
-        <v>-97.41</v>
+        <v>-21.34</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
       <c r="A45" s="26" t="inlineStr">
         <is>
-          <t>남화산업</t>
+          <t>크리스탈신소재</t>
         </is>
       </c>
       <c r="B45" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C45" s="25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D45" s="25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E45" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F45" s="25" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G45" s="25" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="H45" s="29" t="n">
-        <v>29.97</v>
-      </c>
-      <c r="I45" s="29" t="n">
-        <v>30.84</v>
+        <v>18.81</v>
+      </c>
+      <c r="I45" s="27" t="n">
+        <v>-28.03</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
       <c r="A46" s="26" t="inlineStr">
         <is>
-          <t>노블엠앤비</t>
+          <t>티이엠씨씨엔에스</t>
         </is>
       </c>
       <c r="B46" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C46" s="25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D46" s="25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E46" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F46" s="25" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G46" s="25" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
-        </is>
-      </c>
-      <c r="H46" s="27" t="n">
-        <v>-7.69</v>
-      </c>
-      <c r="I46" s="27" t="n">
-        <v>-97.08</v>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="H46" s="29" t="n">
+        <v>30</v>
+      </c>
+      <c r="I46" s="29" t="n">
+        <v>10.36</v>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
       <c r="A47" s="26" t="inlineStr">
         <is>
-          <t>디와이에이</t>
+          <t>한미반도체</t>
         </is>
       </c>
       <c r="B47" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C47" s="25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D47" s="25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E47" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F47" s="25" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G47" s="25" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
-        </is>
-      </c>
-      <c r="H47" s="29" t="n">
-        <v>25.79</v>
-      </c>
-      <c r="I47" s="29" t="n">
-        <v>31.47</v>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="H47" s="27" t="n">
+        <v>-5.68</v>
+      </c>
+      <c r="I47" s="27" t="n">
+        <v>-12.71</v>
       </c>
     </row>
     <row r="48" ht="18" customHeight="1">
       <c r="A48" s="26" t="inlineStr">
         <is>
-          <t>바이온</t>
+          <t>헝셩그룹</t>
         </is>
       </c>
       <c r="B48" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C48" s="25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D48" s="25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E48" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F48" s="25" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G48" s="25" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="H48" s="27" t="n">
-        <v>-50</v>
-      </c>
-      <c r="I48" s="27" t="n">
-        <v>-98.84</v>
+        <v>-2.71</v>
+      </c>
+      <c r="I48" s="29" t="n">
+        <v>15.4</v>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1">
       <c r="A49" s="26" t="inlineStr">
         <is>
-          <t>삼기에너지솔루션즈</t>
+          <t>NPX</t>
         </is>
       </c>
       <c r="B49" s="25" t="n">
@@ -4732,25 +4722,25 @@
       </c>
       <c r="F49" s="25" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G49" s="25" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="H49" s="27" t="n">
-        <v>-18.39</v>
-      </c>
-      <c r="I49" s="29" t="n">
-        <v>21.26</v>
+        <v>-97.41</v>
+      </c>
+      <c r="I49" s="27" t="n">
+        <v>-97.41</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
       <c r="A50" s="26" t="inlineStr">
         <is>
-          <t>서암기계공업</t>
+          <t>광주신세계</t>
         </is>
       </c>
       <c r="B50" s="25" t="n">
@@ -4767,25 +4757,25 @@
       </c>
       <c r="F50" s="25" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G50" s="25" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="H50" s="29" t="n">
-        <v>3.72</v>
+        <v>29.98</v>
       </c>
       <c r="I50" s="29" t="n">
-        <v>1.52</v>
+        <v>50.71</v>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
       <c r="A51" s="26" t="inlineStr">
         <is>
-          <t>조아제약</t>
+          <t>남화산업</t>
         </is>
       </c>
       <c r="B51" s="25" t="n">
@@ -4802,19 +4792,19 @@
       </c>
       <c r="F51" s="25" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G51" s="25" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="H51" s="29" t="n">
-        <v>4.55</v>
+        <v>29.97</v>
       </c>
       <c r="I51" s="29" t="n">
-        <v>44.97</v>
+        <v>30.84</v>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1">
@@ -4837,12 +4827,12 @@
       </c>
       <c r="F52" s="25" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G52" s="25" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="H52" s="27" t="n">
@@ -4933,19 +4923,19 @@
         <v>1</v>
       </c>
       <c r="C3" s="36" t="n">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="D3" s="36" t="n">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="E3" s="36" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="F3" s="37" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G3" s="37" t="inlineStr">
@@ -4964,19 +4954,19 @@
         <v>1</v>
       </c>
       <c r="C4" s="36" t="n">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="D4" s="36" t="n">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="E4" s="36" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="F4" s="37" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G4" s="37" t="inlineStr">
@@ -4995,19 +4985,19 @@
         <v>1</v>
       </c>
       <c r="C5" s="36" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D5" s="36" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E5" s="36" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="F5" s="37" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G5" s="37" t="inlineStr">
@@ -5019,26 +5009,26 @@
     <row r="6" ht="18" customHeight="1">
       <c r="A6" s="35" t="inlineStr">
         <is>
-          <t>로봇</t>
+          <t>방산</t>
         </is>
       </c>
       <c r="B6" s="36" t="n">
         <v>1</v>
       </c>
       <c r="C6" s="36" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D6" s="36" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E6" s="36" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="F6" s="37" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G6" s="37" t="inlineStr">
@@ -5050,26 +5040,26 @@
     <row r="7" ht="18" customHeight="1">
       <c r="A7" s="35" t="inlineStr">
         <is>
-          <t>조선</t>
+          <t>로봇</t>
         </is>
       </c>
       <c r="B7" s="36" t="n">
         <v>1</v>
       </c>
       <c r="C7" s="36" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="D7" s="36" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="E7" s="36" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="F7" s="37" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G7" s="37" t="inlineStr">
@@ -5081,26 +5071,26 @@
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="35" t="inlineStr">
         <is>
-          <t>제약</t>
+          <t>태양광</t>
         </is>
       </c>
       <c r="B8" s="36" t="n">
         <v>1</v>
       </c>
       <c r="C8" s="36" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D8" s="36" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E8" s="36" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="F8" s="37" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G8" s="37" t="inlineStr">
@@ -5112,119 +5102,131 @@
     <row r="9" ht="18" customHeight="1">
       <c r="A9" s="35" t="inlineStr">
         <is>
+          <t>게임</t>
+        </is>
+      </c>
+      <c r="B9" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" s="36" t="n">
+        <v>4</v>
+      </c>
+      <c r="D9" s="36" t="n">
+        <v>4</v>
+      </c>
+      <c r="E9" s="36" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="F9" s="37" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="G9" s="37" t="inlineStr">
+        <is>
+          <t>⚡ 관심</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="18" customHeight="1">
+      <c r="A10" s="35" t="inlineStr">
+        <is>
+          <t>조선</t>
+        </is>
+      </c>
+      <c r="B10" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" s="36" t="n">
+        <v>5</v>
+      </c>
+      <c r="D10" s="36" t="n">
+        <v>5</v>
+      </c>
+      <c r="E10" s="36" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="F10" s="37" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="G10" s="37" t="inlineStr">
+        <is>
+          <t>⚡ 관심</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="18" customHeight="1">
+      <c r="A11" s="35" t="inlineStr">
+        <is>
+          <t>제약</t>
+        </is>
+      </c>
+      <c r="B11" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" s="36" t="n">
+        <v>13</v>
+      </c>
+      <c r="D11" s="36" t="n">
+        <v>13</v>
+      </c>
+      <c r="E11" s="36" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="F11" s="37" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="G11" s="37" t="inlineStr">
+        <is>
+          <t>⚡ 관심</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="18" customHeight="1">
+      <c r="A12" s="35" t="inlineStr">
+        <is>
           <t>인공지능</t>
         </is>
       </c>
-      <c r="B9" s="36" t="n">
-        <v>1</v>
-      </c>
-      <c r="C9" s="36" t="n">
-        <v>18</v>
-      </c>
-      <c r="D9" s="36" t="n">
-        <v>18</v>
-      </c>
-      <c r="E9" s="36" t="inlineStr">
-        <is>
-          <t>2026-06-28</t>
-        </is>
-      </c>
-      <c r="F9" s="37" t="inlineStr">
-        <is>
-          <t>2026-06-28</t>
-        </is>
-      </c>
-      <c r="G9" s="37" t="inlineStr">
+      <c r="B12" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" s="36" t="n">
+        <v>21</v>
+      </c>
+      <c r="D12" s="36" t="n">
+        <v>21</v>
+      </c>
+      <c r="E12" s="36" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="F12" s="37" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="G12" s="37" t="inlineStr">
         <is>
           <t>⚡ 관심</t>
         </is>
       </c>
-    </row>
-    <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="26" t="inlineStr">
-        <is>
-          <t>이차전지</t>
-        </is>
-      </c>
-      <c r="B10" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="C10" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" s="25" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F10" s="28" t="inlineStr">
-        <is>
-          <t>감지 없음</t>
-        </is>
-      </c>
-      <c r="G10" s="28" t="inlineStr"/>
-    </row>
-    <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="26" t="inlineStr">
-        <is>
-          <t>AI반도체</t>
-        </is>
-      </c>
-      <c r="B11" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="C11" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" s="25" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F11" s="28" t="inlineStr">
-        <is>
-          <t>감지 없음</t>
-        </is>
-      </c>
-      <c r="G11" s="28" t="inlineStr"/>
-    </row>
-    <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="26" t="inlineStr">
-        <is>
-          <t>방산</t>
-        </is>
-      </c>
-      <c r="B12" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="C12" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" s="25" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F12" s="28" t="inlineStr">
-        <is>
-          <t>감지 없음</t>
-        </is>
-      </c>
-      <c r="G12" s="28" t="inlineStr"/>
     </row>
     <row r="13" ht="18" customHeight="1">
       <c r="A13" s="26" t="inlineStr">
         <is>
-          <t>원전</t>
+          <t>이차전지</t>
         </is>
       </c>
       <c r="B13" s="25" t="n">
@@ -5251,7 +5253,7 @@
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="26" t="inlineStr">
         <is>
-          <t>수소</t>
+          <t>AI반도체</t>
         </is>
       </c>
       <c r="B14" s="25" t="n">
@@ -5278,7 +5280,7 @@
     <row r="15" ht="18" customHeight="1">
       <c r="A15" s="26" t="inlineStr">
         <is>
-          <t>태양광</t>
+          <t>원전</t>
         </is>
       </c>
       <c r="B15" s="25" t="n">
@@ -5305,7 +5307,7 @@
     <row r="16" ht="18" customHeight="1">
       <c r="A16" s="26" t="inlineStr">
         <is>
-          <t>게임</t>
+          <t>수소</t>
         </is>
       </c>
       <c r="B16" s="25" t="n">

--- a/trend/stock_trend_history.xlsx
+++ b/trend/stock_trend_history.xlsx
@@ -258,13 +258,13 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -694,7 +694,7 @@
     <row r="1" ht="36" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>📊 주식 트렌드 조기 감지 대시보드   |   최종 업데이트: 2026-06-29 06:54</t>
+          <t>📊 주식 트렌드 조기 감지 대시보드   |   최종 업데이트: 2026-06-30 06:54</t>
         </is>
       </c>
     </row>
@@ -708,7 +708,7 @@
       </c>
       <c r="E3" s="3" t="n"/>
       <c r="G3" s="5" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="H3" s="3" t="n"/>
       <c r="J3" s="6" t="n">
@@ -787,21 +787,21 @@
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="11" t="inlineStr">
         <is>
-          <t>⚡ 최신(2026-06-29) 상위: 반도체  점수 101.0점</t>
+          <t>⚡ 최신(2026-06-30) 상위: 반도체  점수 121.0점</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1">
       <c r="A11" s="12" t="inlineStr">
         <is>
-          <t>⚡ 최신(2026-06-29) 상위: SK  점수 44.0점</t>
+          <t>⚡ 최신(2026-06-30) 상위: SK  점수 40.0점</t>
         </is>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1">
       <c r="A12" s="11" t="inlineStr">
         <is>
-          <t>⚡ 최신(2026-06-29) 상위: 바이오  점수 39.0점</t>
+          <t>⚡ 최신(2026-06-30) 상위: 삼성전자  점수 30.0점</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B14" s="15" t="n">
@@ -928,10 +928,10 @@
         </is>
       </c>
       <c r="D14" s="15" t="n">
-        <v>101</v>
+        <v>121</v>
       </c>
       <c r="E14" s="15" t="n">
-        <v>101</v>
+        <v>121</v>
       </c>
       <c r="F14" s="15" t="n">
         <v>0</v>
@@ -947,7 +947,7 @@
       </c>
       <c r="J14" s="17" t="inlineStr">
         <is>
-          <t>네이버뉴스 헤드라인 언급 / 매일경제 헤드라인 언급 / 네이버뉴스 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 기사 언급</t>
+          <t>매일경제 기사 언급 / 매일경제 헤드라인 언급 / 네이버뉴스 헤드라인 언급 / 네이버뉴스 기사 언급 / 한국경제 헤드라인 언급</t>
         </is>
       </c>
       <c r="K14" s="17" t="inlineStr">
@@ -959,7 +959,7 @@
     <row r="15" ht="18" customHeight="1">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B15" s="15" t="n">
@@ -971,10 +971,10 @@
         </is>
       </c>
       <c r="D15" s="15" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="E15" s="15" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="F15" s="15" t="n">
         <v>0</v>
@@ -983,14 +983,14 @@
         <v>0</v>
       </c>
       <c r="H15" s="18" t="n">
-        <v>-5.01</v>
+        <v>-3.68</v>
       </c>
       <c r="I15" s="19" t="n">
-        <v>12.57</v>
+        <v>7.53</v>
       </c>
       <c r="J15" s="17" t="inlineStr">
         <is>
-          <t>네이버뉴스 기사 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급</t>
+          <t>매일경제 헤드라인 언급 / 한국경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
         </is>
       </c>
       <c r="K15" s="17" t="inlineStr">
@@ -1002,7 +1002,7 @@
     <row r="16" ht="18" customHeight="1">
       <c r="A16" s="15" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B16" s="15" t="n">
@@ -1010,14 +1010,14 @@
       </c>
       <c r="C16" s="16" t="inlineStr">
         <is>
-          <t>바이오</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="D16" s="15" t="n">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="E16" s="15" t="n">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="F16" s="15" t="n">
         <v>0</v>
@@ -1025,27 +1025,27 @@
       <c r="G16" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="H16" s="15" t="n">
-        <v/>
-      </c>
-      <c r="I16" s="15" t="n">
-        <v/>
+      <c r="H16" s="18" t="n">
+        <v>-4.86</v>
+      </c>
+      <c r="I16" s="18" t="n">
+        <v>-8.630000000000001</v>
       </c>
       <c r="J16" s="17" t="inlineStr">
         <is>
-          <t>Google 급상승 검색어 등장 (KR) / 네이버뉴스 헤드라인 언급 / 네이버뉴스 기사 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급</t>
+          <t>네이버뉴스 헤드라인 언급 / 한국경제 헤드라인 언급 / 매일경제 기사 언급 / 매일경제 기사 언급 / 매일경제 기사 언급</t>
         </is>
       </c>
       <c r="K16" s="17" t="inlineStr">
         <is>
-          <t>네이버, Google</t>
+          <t>네이버</t>
         </is>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B17" s="15" t="n">
@@ -1053,14 +1053,14 @@
       </c>
       <c r="C17" s="16" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>인공지능</t>
         </is>
       </c>
       <c r="D17" s="15" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="E17" s="15" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="F17" s="15" t="n">
         <v>0</v>
@@ -1068,15 +1068,15 @@
       <c r="G17" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="H17" s="18" t="n">
-        <v>-5.3</v>
-      </c>
-      <c r="I17" s="18" t="n">
-        <v>-4.1</v>
+      <c r="H17" s="15" t="n">
+        <v/>
+      </c>
+      <c r="I17" s="15" t="n">
+        <v/>
       </c>
       <c r="J17" s="17" t="inlineStr">
         <is>
-          <t>네이버뉴스 기사 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 기사 언급 / 한국경제 헤드라인 언급</t>
+          <t>매일경제 기사 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 기사 언급 / 매일경제 기사 언급 / 매일경제 기사 언급</t>
         </is>
       </c>
       <c r="K17" s="17" t="inlineStr">
@@ -1088,7 +1088,7 @@
     <row r="18" ht="18" customHeight="1">
       <c r="A18" s="15" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B18" s="15" t="n">
@@ -1096,14 +1096,14 @@
       </c>
       <c r="C18" s="16" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>바이오</t>
         </is>
       </c>
       <c r="D18" s="15" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E18" s="15" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F18" s="15" t="n">
         <v>0</v>
@@ -1111,27 +1111,27 @@
       <c r="G18" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="H18" s="18" t="n">
-        <v>-8.359999999999999</v>
-      </c>
-      <c r="I18" s="18" t="n">
-        <v>-3.29</v>
+      <c r="H18" s="15" t="n">
+        <v/>
+      </c>
+      <c r="I18" s="15" t="n">
+        <v/>
       </c>
       <c r="J18" s="17" t="inlineStr">
         <is>
-          <t>중요공시 1건 / 네이버뉴스 기사 언급 / 매일경제 헤드라인 언급 / 매일경제 기사 언급 / 매일경제 헤드라인 언급</t>
+          <t>네이버뉴스 헤드라인 언급 / 매일경제 헤드라인 언급 / 네이버뉴스 헤드라인 언급 / 매일경제 기사 언급 / 네이버뉴스 헤드라인 언급</t>
         </is>
       </c>
       <c r="K18" s="17" t="inlineStr">
         <is>
-          <t>네이버, 공시</t>
+          <t>네이버</t>
         </is>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
       <c r="A19" s="15" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B19" s="15" t="n">
@@ -1139,14 +1139,14 @@
       </c>
       <c r="C19" s="16" t="inlineStr">
         <is>
-          <t>인공지능</t>
+          <t>LG</t>
         </is>
       </c>
       <c r="D19" s="15" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E19" s="15" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F19" s="15" t="n">
         <v>0</v>
@@ -1154,15 +1154,15 @@
       <c r="G19" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="H19" s="15" t="n">
-        <v/>
-      </c>
-      <c r="I19" s="15" t="n">
-        <v/>
+      <c r="H19" s="19" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="I19" s="18" t="n">
+        <v>-8.279999999999999</v>
       </c>
       <c r="J19" s="17" t="inlineStr">
         <is>
-          <t>매일경제 기사 언급 / 매일경제 기사 언급 / 매일경제 기사 언급 / 매일경제 기사 언급 / 네이버뉴스 기사 언급</t>
+          <t>매일경제 헤드라인 언급 / 네이버뉴스 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 기사 언급 / 한국경제 헤드라인 언급</t>
         </is>
       </c>
       <c r="K19" s="17" t="inlineStr">
@@ -1174,7 +1174,7 @@
     <row r="20" ht="18" customHeight="1">
       <c r="A20" s="15" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B20" s="15" t="n">
@@ -1182,14 +1182,14 @@
       </c>
       <c r="C20" s="16" t="inlineStr">
         <is>
-          <t>LG</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="D20" s="15" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E20" s="15" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F20" s="15" t="n">
         <v>0</v>
@@ -1198,24 +1198,26 @@
         <v>0</v>
       </c>
       <c r="H20" s="18" t="n">
-        <v>-0.8</v>
+        <v>-1.68</v>
       </c>
       <c r="I20" s="18" t="n">
-        <v>-9.460000000000001</v>
+        <v>-9.970000000000001</v>
       </c>
       <c r="J20" s="17" t="inlineStr">
         <is>
-          <t>매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 기사 언급</t>
-        </is>
-      </c>
-      <c r="K20" s="17" t="n">
-        <v/>
+          <t>중요공시 1건 / 한국경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 기사 언급 / 매일경제 기사 언급</t>
+        </is>
+      </c>
+      <c r="K20" s="17" t="inlineStr">
+        <is>
+          <t>공시, 네이버</t>
+        </is>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
       <c r="A21" s="15" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B21" s="15" t="n">
@@ -1227,10 +1229,10 @@
         </is>
       </c>
       <c r="D21" s="15" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E21" s="15" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F21" s="15" t="n">
         <v>0</v>
@@ -1246,19 +1248,17 @@
       </c>
       <c r="J21" s="17" t="inlineStr">
         <is>
-          <t>매일경제 헤드라인 언급 / 네이버뉴스 기사 언급 / 매일경제 헤드라인 언급 / 매일경제 기사 언급 / 한국경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K21" s="17" t="inlineStr">
-        <is>
-          <t>네이버</t>
-        </is>
+          <t>한국경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 한국경제 헤드라인 언급 / 매일경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K21" s="17" t="n">
+        <v/>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
       <c r="A22" s="15" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B22" s="15" t="n">
@@ -1270,10 +1270,10 @@
         </is>
       </c>
       <c r="D22" s="15" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E22" s="15" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F22" s="15" t="n">
         <v>0</v>
@@ -1289,7 +1289,7 @@
       </c>
       <c r="J22" s="17" t="inlineStr">
         <is>
-          <t>네이버뉴스 헤드라인 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 기사 언급</t>
+          <t>네이버뉴스 헤드라인 언급 / 네이버뉴스 헤드라인 언급 / 네이버뉴스 헤드라인 언급 / 네이버뉴스 기사 언급 / 매일경제 기사 언급</t>
         </is>
       </c>
       <c r="K22" s="17" t="inlineStr">
@@ -1301,7 +1301,7 @@
     <row r="23" ht="18" customHeight="1">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B23" s="15" t="n">
@@ -1309,14 +1309,14 @@
       </c>
       <c r="C23" s="16" t="inlineStr">
         <is>
-          <t>방산</t>
+          <t>전기차</t>
         </is>
       </c>
       <c r="D23" s="15" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E23" s="15" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F23" s="15" t="n">
         <v>0</v>
@@ -1332,17 +1332,19 @@
       </c>
       <c r="J23" s="17" t="inlineStr">
         <is>
-          <t>매일경제 헤드라인 언급 / 한국경제 헤드라인 언급 / 한국경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K23" s="17" t="n">
-        <v/>
+          <t>매일경제 기사 언급 / 매일경제 헤드라인 언급 / 네이버뉴스 기사 언급 / 매일경제 기사 언급 / 매일경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K23" s="17" t="inlineStr">
+        <is>
+          <t>네이버</t>
+        </is>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B24" s="15" t="n">
@@ -1350,42 +1352,42 @@
       </c>
       <c r="C24" s="16" t="inlineStr">
         <is>
-          <t>젠큐릭스</t>
+          <t>현대차</t>
         </is>
       </c>
       <c r="D24" s="15" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E24" s="15" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="F24" s="15" t="n">
         <v>0</v>
       </c>
       <c r="G24" s="15" t="n">
-        <v>3</v>
-      </c>
-      <c r="H24" s="18" t="n">
-        <v>-1.9</v>
+        <v>0</v>
+      </c>
+      <c r="H24" s="19" t="n">
+        <v>3.43</v>
       </c>
       <c r="I24" s="18" t="n">
-        <v>-12.13</v>
+        <v>-14.46</v>
       </c>
       <c r="J24" s="17" t="inlineStr">
         <is>
-          <t>중요공시 3건 / 중요공시 7일 +200% / 매일경제 헤드라인 언급</t>
+          <t>매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 네이버뉴스 헤드라인 언급</t>
         </is>
       </c>
       <c r="K24" s="17" t="inlineStr">
         <is>
-          <t>공시</t>
+          <t>네이버</t>
         </is>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
       <c r="A25" s="15" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B25" s="15" t="n">
@@ -1393,7 +1395,7 @@
       </c>
       <c r="C25" s="16" t="inlineStr">
         <is>
-          <t>LG이노텍</t>
+          <t>삼호개발</t>
         </is>
       </c>
       <c r="D25" s="15" t="n">
@@ -1409,24 +1411,26 @@
         <v>0</v>
       </c>
       <c r="H25" s="18" t="n">
-        <v>-2.31</v>
-      </c>
-      <c r="I25" s="18" t="n">
-        <v>-18.69</v>
+        <v>-2.17</v>
+      </c>
+      <c r="I25" s="19" t="n">
+        <v>17.02</v>
       </c>
       <c r="J25" s="17" t="inlineStr">
         <is>
-          <t>매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K25" s="17" t="n">
-        <v/>
+          <t>네이버 검색 당일 +208% / 중요공시 3건 / 매일경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K25" s="17" t="inlineStr">
+        <is>
+          <t>공시, 네이버</t>
+        </is>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
       <c r="A26" s="15" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B26" s="15" t="n">
@@ -1434,203 +1438,201 @@
       </c>
       <c r="C26" s="16" t="inlineStr">
         <is>
+          <t>LG화학</t>
+        </is>
+      </c>
+      <c r="D26" s="15" t="n">
+        <v>9</v>
+      </c>
+      <c r="E26" s="15" t="n">
+        <v>9</v>
+      </c>
+      <c r="F26" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" s="19" t="n">
+        <v>13.65</v>
+      </c>
+      <c r="I26" s="18" t="n">
+        <v>-4.64</v>
+      </c>
+      <c r="J26" s="17" t="inlineStr">
+        <is>
+          <t>매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K26" s="17" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="27" ht="18" customHeight="1">
+      <c r="A27" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B27" s="15" t="n">
+        <v>14</v>
+      </c>
+      <c r="C27" s="16" t="inlineStr">
+        <is>
+          <t>원전</t>
+        </is>
+      </c>
+      <c r="D27" s="15" t="n">
+        <v>9</v>
+      </c>
+      <c r="E27" s="15" t="n">
+        <v>9</v>
+      </c>
+      <c r="F27" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" s="15" t="n">
+        <v/>
+      </c>
+      <c r="I27" s="15" t="n">
+        <v/>
+      </c>
+      <c r="J27" s="17" t="inlineStr">
+        <is>
+          <t>매일경제 헤드라인 언급 / 한국경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K27" s="17" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="28" ht="18" customHeight="1">
+      <c r="A28" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B28" s="15" t="n">
+        <v>15</v>
+      </c>
+      <c r="C28" s="16" t="inlineStr">
+        <is>
           <t>성호전자</t>
         </is>
       </c>
-      <c r="D26" s="15" t="n">
+      <c r="D28" s="15" t="n">
         <v>8</v>
       </c>
-      <c r="E26" s="15" t="n">
+      <c r="E28" s="15" t="n">
         <v>3</v>
       </c>
-      <c r="F26" s="15" t="n">
+      <c r="F28" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="G26" s="15" t="n">
+      <c r="G28" s="15" t="n">
         <v>3</v>
       </c>
-      <c r="H26" s="19" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="I26" s="18" t="n">
-        <v>-24.25</v>
-      </c>
-      <c r="J26" s="17" t="inlineStr">
-        <is>
-          <t>중요공시 3건 / 중요공시 3일 +50% / 중요공시 7일 +200%</t>
-        </is>
-      </c>
-      <c r="K26" s="17" t="inlineStr">
+      <c r="H28" s="18" t="n">
+        <v>-1.56</v>
+      </c>
+      <c r="I28" s="18" t="n">
+        <v>-22.9</v>
+      </c>
+      <c r="J28" s="17" t="inlineStr">
+        <is>
+          <t>중요공시 3건 / 중요공시 3일 +200% / 중요공시 7일 +200%</t>
+        </is>
+      </c>
+      <c r="K28" s="17" t="inlineStr">
         <is>
           <t>공시</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="18" customHeight="1">
-      <c r="A27" s="20" t="inlineStr">
-        <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="B27" s="20" t="n">
-        <v>14</v>
-      </c>
-      <c r="C27" s="21" t="inlineStr">
-        <is>
-          <t>삼호개발</t>
-        </is>
-      </c>
-      <c r="D27" s="20" t="n">
-        <v>6</v>
-      </c>
-      <c r="E27" s="20" t="n">
-        <v>6</v>
-      </c>
-      <c r="F27" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G27" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H27" s="22" t="n">
-        <v>8.69</v>
-      </c>
-      <c r="I27" s="22" t="n">
-        <v>16.77</v>
-      </c>
-      <c r="J27" s="23" t="inlineStr">
-        <is>
-          <t>네이버 검색 당일 +171% / 중요공시 3건</t>
-        </is>
-      </c>
-      <c r="K27" s="23" t="inlineStr">
-        <is>
-          <t>네이버, 공시</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="18" customHeight="1">
-      <c r="A28" s="20" t="inlineStr">
-        <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="B28" s="20" t="n">
-        <v>15</v>
-      </c>
-      <c r="C28" s="21" t="inlineStr">
-        <is>
-          <t>샤페론</t>
-        </is>
-      </c>
-      <c r="D28" s="20" t="n">
-        <v>6</v>
-      </c>
-      <c r="E28" s="20" t="n">
-        <v>6</v>
-      </c>
-      <c r="F28" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G28" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H28" s="24" t="n">
-        <v>-25.16</v>
-      </c>
-      <c r="I28" s="24" t="n">
-        <v>-56.14</v>
-      </c>
-      <c r="J28" s="23" t="inlineStr">
-        <is>
-          <t>네이버 검색 당일 +61% / 중요공시 1건 / 네이버뉴스 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K28" s="23" t="inlineStr">
-        <is>
-          <t>네이버, 공시</t>
-        </is>
-      </c>
-    </row>
     <row r="29" ht="18" customHeight="1">
-      <c r="A29" s="20" t="inlineStr">
-        <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="B29" s="20" t="n">
+      <c r="A29" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B29" s="15" t="n">
         <v>16</v>
       </c>
-      <c r="C29" s="21" t="inlineStr">
-        <is>
-          <t>LG전자</t>
-        </is>
-      </c>
-      <c r="D29" s="20" t="n">
-        <v>6</v>
-      </c>
-      <c r="E29" s="20" t="n">
-        <v>6</v>
-      </c>
-      <c r="F29" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G29" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H29" s="24" t="n">
-        <v>-3.5</v>
-      </c>
-      <c r="I29" s="24" t="n">
-        <v>-7.38</v>
-      </c>
-      <c r="J29" s="23" t="inlineStr">
-        <is>
-          <t>한국경제 헤드라인 언급 / 매일경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K29" s="23" t="n">
-        <v/>
+      <c r="C29" s="16" t="inlineStr">
+        <is>
+          <t>스피어</t>
+        </is>
+      </c>
+      <c r="D29" s="15" t="n">
+        <v>8</v>
+      </c>
+      <c r="E29" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="F29" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="G29" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="H29" s="19" t="n">
+        <v>17.63</v>
+      </c>
+      <c r="I29" s="18" t="n">
+        <v>-8.130000000000001</v>
+      </c>
+      <c r="J29" s="17" t="inlineStr">
+        <is>
+          <t>중요공시 7건 / 중요공시 3일 +133% / 중요공시 7일 +250%</t>
+        </is>
+      </c>
+      <c r="K29" s="17" t="inlineStr">
+        <is>
+          <t>공시</t>
+        </is>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
-      <c r="A30" s="20" t="inlineStr">
-        <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="B30" s="20" t="n">
+      <c r="A30" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B30" s="15" t="n">
         <v>17</v>
       </c>
-      <c r="C30" s="21" t="inlineStr">
-        <is>
-          <t>대우건설</t>
-        </is>
-      </c>
-      <c r="D30" s="20" t="n">
-        <v>6</v>
-      </c>
-      <c r="E30" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="F30" s="20" t="n">
+      <c r="C30" s="16" t="inlineStr">
+        <is>
+          <t>파두</t>
+        </is>
+      </c>
+      <c r="D30" s="15" t="n">
+        <v>8</v>
+      </c>
+      <c r="E30" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="F30" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="G30" s="20" t="n">
+      <c r="G30" s="15" t="n">
         <v>3</v>
       </c>
-      <c r="H30" s="24" t="n">
-        <v>-8.41</v>
-      </c>
-      <c r="I30" s="24" t="n">
-        <v>-14.4</v>
-      </c>
-      <c r="J30" s="23" t="inlineStr">
-        <is>
-          <t>중요공시 2건 / 중요공시 3일 +100% / 중요공시 7일 +100%</t>
-        </is>
-      </c>
-      <c r="K30" s="23" t="inlineStr">
+      <c r="H30" s="19" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="I30" s="18" t="n">
+        <v>-26.06</v>
+      </c>
+      <c r="J30" s="17" t="inlineStr">
+        <is>
+          <t>중요공시 3건 / 중요공시 3일 +200% / 중요공시 7일 +50%</t>
+        </is>
+      </c>
+      <c r="K30" s="17" t="inlineStr">
         <is>
           <t>공시</t>
         </is>
@@ -1639,7 +1641,7 @@
     <row r="31" ht="18" customHeight="1">
       <c r="A31" s="20" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B31" s="20" t="n">
@@ -1647,42 +1649,42 @@
       </c>
       <c r="C31" s="21" t="inlineStr">
         <is>
-          <t>스피어</t>
+          <t>아크솔루션스</t>
         </is>
       </c>
       <c r="D31" s="20" t="n">
         <v>6</v>
       </c>
       <c r="E31" s="20" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F31" s="20" t="n">
         <v>0</v>
       </c>
       <c r="G31" s="20" t="n">
-        <v>3</v>
-      </c>
-      <c r="H31" s="24" t="n">
-        <v>-8.76</v>
-      </c>
-      <c r="I31" s="24" t="n">
-        <v>-31.49</v>
+        <v>0</v>
+      </c>
+      <c r="H31" s="22" t="n">
+        <v>-97.40000000000001</v>
+      </c>
+      <c r="I31" s="22" t="n">
+        <v>-97.40000000000001</v>
       </c>
       <c r="J31" s="23" t="inlineStr">
         <is>
-          <t>중요공시 5건 / 중요공시 7일 +67%</t>
+          <t>네이버 검색 당일 +197% / 중요공시 3건</t>
         </is>
       </c>
       <c r="K31" s="23" t="inlineStr">
         <is>
-          <t>공시</t>
+          <t>공시, 네이버</t>
         </is>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
       <c r="A32" s="20" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B32" s="20" t="n">
@@ -1690,7 +1692,7 @@
       </c>
       <c r="C32" s="21" t="inlineStr">
         <is>
-          <t>차바이오텍</t>
+          <t>뉴인텍</t>
         </is>
       </c>
       <c r="D32" s="20" t="n">
@@ -1705,27 +1707,27 @@
       <c r="G32" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H32" s="24" t="n">
-        <v>-4.12</v>
+      <c r="H32" s="22" t="n">
+        <v>-20.41</v>
       </c>
       <c r="I32" s="24" t="n">
-        <v>-12.15</v>
+        <v>17.04</v>
       </c>
       <c r="J32" s="23" t="inlineStr">
         <is>
-          <t>중요공시 4건 / 중요공시 3일 +300% / 네이버뉴스 기사 언급</t>
+          <t>네이버 검색 당일 +181% / 중요공시 2건 / 중요공시 3일 +100%</t>
         </is>
       </c>
       <c r="K32" s="23" t="inlineStr">
         <is>
-          <t>네이버, 공시</t>
+          <t>공시, 네이버</t>
         </is>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
       <c r="A33" s="20" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B33" s="20" t="n">
@@ -1733,42 +1735,42 @@
       </c>
       <c r="C33" s="21" t="inlineStr">
         <is>
-          <t>에이팩트</t>
+          <t>앱튼</t>
         </is>
       </c>
       <c r="D33" s="20" t="n">
         <v>6</v>
       </c>
       <c r="E33" s="20" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F33" s="20" t="n">
         <v>0</v>
       </c>
       <c r="G33" s="20" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H33" s="24" t="n">
-        <v>-6.74</v>
+        <v>29.98</v>
       </c>
       <c r="I33" s="24" t="n">
-        <v>-26.62</v>
+        <v>109.15</v>
       </c>
       <c r="J33" s="23" t="inlineStr">
         <is>
-          <t>중요공시 3건 / 중요공시 7일 +200%</t>
+          <t>네이버 검색 당일 +138% / 중요공시 5건</t>
         </is>
       </c>
       <c r="K33" s="23" t="inlineStr">
         <is>
-          <t>공시</t>
+          <t>공시, 네이버</t>
         </is>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
       <c r="A34" s="20" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B34" s="20" t="n">
@@ -1776,42 +1778,40 @@
       </c>
       <c r="C34" s="21" t="inlineStr">
         <is>
-          <t>페니트리움바이오</t>
+          <t>원익IPS</t>
         </is>
       </c>
       <c r="D34" s="20" t="n">
         <v>6</v>
       </c>
       <c r="E34" s="20" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F34" s="20" t="n">
         <v>0</v>
       </c>
       <c r="G34" s="20" t="n">
-        <v>3</v>
-      </c>
-      <c r="H34" s="24" t="n">
-        <v>-2.96</v>
-      </c>
-      <c r="I34" s="24" t="n">
-        <v>-11.93</v>
+        <v>0</v>
+      </c>
+      <c r="H34" s="22" t="n">
+        <v>-2.93</v>
+      </c>
+      <c r="I34" s="22" t="n">
+        <v>-7.83</v>
       </c>
       <c r="J34" s="23" t="inlineStr">
         <is>
-          <t>중요공시 3건 / 중요공시 7일 +200%</t>
-        </is>
-      </c>
-      <c r="K34" s="23" t="inlineStr">
-        <is>
-          <t>공시</t>
-        </is>
+          <t>한국경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K34" s="23" t="n">
+        <v/>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
       <c r="A35" s="20" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B35" s="20" t="n">
@@ -1819,7 +1819,7 @@
       </c>
       <c r="C35" s="21" t="inlineStr">
         <is>
-          <t>삼성바이오로직스</t>
+          <t>한화생명</t>
         </is>
       </c>
       <c r="D35" s="20" t="n">
@@ -1835,26 +1835,24 @@
         <v>0</v>
       </c>
       <c r="H35" s="24" t="n">
-        <v>-3.1</v>
-      </c>
-      <c r="I35" s="24" t="n">
-        <v>-2.26</v>
+        <v>2.71</v>
+      </c>
+      <c r="I35" s="22" t="n">
+        <v>-9.199999999999999</v>
       </c>
       <c r="J35" s="23" t="inlineStr">
         <is>
-          <t>중요공시 1건 / Google 급상승 검색어 등장 (KR)</t>
-        </is>
-      </c>
-      <c r="K35" s="23" t="inlineStr">
-        <is>
-          <t>공시, Google</t>
-        </is>
+          <t>매일경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K35" s="23" t="n">
+        <v/>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
       <c r="A36" s="20" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B36" s="20" t="n">
@@ -1862,42 +1860,42 @@
       </c>
       <c r="C36" s="21" t="inlineStr">
         <is>
-          <t>오텍</t>
+          <t>차바이오텍</t>
         </is>
       </c>
       <c r="D36" s="20" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E36" s="20" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F36" s="20" t="n">
         <v>0</v>
       </c>
       <c r="G36" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H36" s="22" t="n">
-        <v>13.75</v>
-      </c>
-      <c r="I36" s="22" t="n">
-        <v>32.47</v>
+        <v>3</v>
+      </c>
+      <c r="H36" s="24" t="n">
+        <v>10.78</v>
+      </c>
+      <c r="I36" s="24" t="n">
+        <v>0.26</v>
       </c>
       <c r="J36" s="23" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +88% / 네이버뉴스 기사 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 기사 언급</t>
+          <t>중요공시 4건 / 중요공시 7일 +300%</t>
         </is>
       </c>
       <c r="K36" s="23" t="inlineStr">
         <is>
-          <t>네이버</t>
+          <t>공시</t>
         </is>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
       <c r="A37" s="20" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B37" s="20" t="n">
@@ -1905,42 +1903,42 @@
       </c>
       <c r="C37" s="21" t="inlineStr">
         <is>
-          <t>소룩스</t>
+          <t>페니트리움바이오</t>
         </is>
       </c>
       <c r="D37" s="20" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E37" s="20" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F37" s="20" t="n">
         <v>0</v>
       </c>
       <c r="G37" s="20" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H37" s="24" t="n">
-        <v>-4.21</v>
+        <v>2.16</v>
       </c>
       <c r="I37" s="22" t="n">
-        <v>19.47</v>
+        <v>-7.21</v>
       </c>
       <c r="J37" s="23" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +84% / 중요공시 3건</t>
+          <t>중요공시 3건 / 중요공시 7일 +200%</t>
         </is>
       </c>
       <c r="K37" s="23" t="inlineStr">
         <is>
-          <t>네이버, 공시</t>
+          <t>공시</t>
         </is>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
       <c r="A38" s="20" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B38" s="20" t="n">
@@ -1948,42 +1946,40 @@
       </c>
       <c r="C38" s="21" t="inlineStr">
         <is>
-          <t>에이프릴바이오</t>
+          <t>방산</t>
         </is>
       </c>
       <c r="D38" s="20" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E38" s="20" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F38" s="20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G38" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H38" s="24" t="n">
-        <v>-0.13</v>
-      </c>
-      <c r="I38" s="22" t="n">
-        <v>1.72</v>
+      <c r="H38" s="20" t="n">
+        <v/>
+      </c>
+      <c r="I38" s="20" t="n">
+        <v/>
       </c>
       <c r="J38" s="23" t="inlineStr">
         <is>
-          <t>중요공시 5건 / 중요공시 3일 +400%</t>
-        </is>
-      </c>
-      <c r="K38" s="23" t="inlineStr">
-        <is>
-          <t>공시</t>
-        </is>
+          <t>매일경제 헤드라인 언급 / 매일경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K38" s="23" t="n">
+        <v/>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
       <c r="A39" s="20" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B39" s="20" t="n">
@@ -1991,42 +1987,42 @@
       </c>
       <c r="C39" s="21" t="inlineStr">
         <is>
-          <t>파두</t>
+          <t>소룩스</t>
         </is>
       </c>
       <c r="D39" s="20" t="n">
         <v>5</v>
       </c>
       <c r="E39" s="20" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F39" s="20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G39" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H39" s="24" t="n">
-        <v>-5.14</v>
+      <c r="H39" s="22" t="n">
+        <v>-4.76</v>
       </c>
       <c r="I39" s="24" t="n">
-        <v>-18.15</v>
+        <v>18.99</v>
       </c>
       <c r="J39" s="23" t="inlineStr">
         <is>
-          <t>중요공시 3건 / 중요공시 3일 +200%</t>
+          <t>네이버 검색 당일 +92% / 중요공시 3건</t>
         </is>
       </c>
       <c r="K39" s="23" t="inlineStr">
         <is>
-          <t>공시</t>
+          <t>공시, 네이버</t>
         </is>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
       <c r="A40" s="20" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B40" s="20" t="n">
@@ -2034,30 +2030,30 @@
       </c>
       <c r="C40" s="21" t="inlineStr">
         <is>
-          <t>리가켐바이오</t>
+          <t>대한항공</t>
         </is>
       </c>
       <c r="D40" s="20" t="n">
         <v>5</v>
       </c>
       <c r="E40" s="20" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F40" s="20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G40" s="20" t="n">
         <v>0</v>
       </c>
       <c r="H40" s="24" t="n">
-        <v>-8.279999999999999</v>
-      </c>
-      <c r="I40" s="22" t="n">
-        <v>6.17</v>
+        <v>1.07</v>
+      </c>
+      <c r="I40" s="24" t="n">
+        <v>4.81</v>
       </c>
       <c r="J40" s="23" t="inlineStr">
         <is>
-          <t>중요공시 2건 / 매일경제 헤드라인 언급 / 매일경제 기사 언급</t>
+          <t>중요공시 3건 / 중요공시 3일 +200%</t>
         </is>
       </c>
       <c r="K40" s="23" t="inlineStr">
@@ -2069,7 +2065,7 @@
     <row r="41" ht="18" customHeight="1">
       <c r="A41" s="20" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B41" s="20" t="n">
@@ -2077,42 +2073,42 @@
       </c>
       <c r="C41" s="21" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>남광토건</t>
         </is>
       </c>
       <c r="D41" s="20" t="n">
         <v>5</v>
       </c>
       <c r="E41" s="20" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F41" s="20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G41" s="20" t="n">
         <v>0</v>
       </c>
       <c r="H41" s="24" t="n">
-        <v>-2.67</v>
+        <v>2.41</v>
       </c>
       <c r="I41" s="24" t="n">
-        <v>-11.52</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="J41" s="23" t="inlineStr">
         <is>
-          <t>네이버뉴스 헤드라인 언급 / 매일경제 헤드라인 언급</t>
+          <t>중요공시 3건 / 중요공시 3일 +50%</t>
         </is>
       </c>
       <c r="K41" s="23" t="inlineStr">
         <is>
-          <t>네이버</t>
+          <t>공시</t>
         </is>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
       <c r="A42" s="20" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B42" s="20" t="n">
@@ -2120,7 +2116,7 @@
       </c>
       <c r="C42" s="21" t="inlineStr">
         <is>
-          <t>카카오</t>
+          <t>KB금융</t>
         </is>
       </c>
       <c r="D42" s="20" t="n">
@@ -2136,26 +2132,26 @@
         <v>0</v>
       </c>
       <c r="H42" s="24" t="n">
-        <v>-3.21</v>
-      </c>
-      <c r="I42" s="24" t="n">
-        <v>-12.19</v>
+        <v>2.95</v>
+      </c>
+      <c r="I42" s="22" t="n">
+        <v>-2.1</v>
       </c>
       <c r="J42" s="23" t="inlineStr">
         <is>
-          <t>네이버뉴스 헤드라인 언급 / 매일경제 헤드라인 언급</t>
+          <t>중요공시 1건 / 한국경제 헤드라인 언급 / 네이버뉴스 헤드라인 언급</t>
         </is>
       </c>
       <c r="K42" s="23" t="inlineStr">
         <is>
-          <t>네이버</t>
+          <t>공시, 네이버</t>
         </is>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1">
       <c r="A43" s="20" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B43" s="20" t="n">
@@ -2163,7 +2159,7 @@
       </c>
       <c r="C43" s="21" t="inlineStr">
         <is>
-          <t>태양광</t>
+          <t>채비</t>
         </is>
       </c>
       <c r="D43" s="20" t="n">
@@ -2178,27 +2174,27 @@
       <c r="G43" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H43" s="20" t="n">
-        <v/>
-      </c>
-      <c r="I43" s="20" t="n">
-        <v/>
+      <c r="H43" s="24" t="n">
+        <v>16.69</v>
+      </c>
+      <c r="I43" s="22" t="n">
+        <v>-3.89</v>
       </c>
       <c r="J43" s="23" t="inlineStr">
         <is>
-          <t>네이버뉴스 헤드라인 언급 / 매일경제 헤드라인 언급</t>
+          <t>중요공시 1건 / 매일경제 헤드라인 언급 / 매일경제 기사 언급</t>
         </is>
       </c>
       <c r="K43" s="23" t="inlineStr">
         <is>
-          <t>네이버</t>
+          <t>공시</t>
         </is>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
       <c r="A44" s="20" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B44" s="20" t="n">
@@ -2206,7 +2202,7 @@
       </c>
       <c r="C44" s="21" t="inlineStr">
         <is>
-          <t>조선</t>
+          <t>기아</t>
         </is>
       </c>
       <c r="D44" s="20" t="n">
@@ -2221,25 +2217,27 @@
       <c r="G44" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H44" s="20" t="n">
-        <v/>
-      </c>
-      <c r="I44" s="20" t="n">
-        <v/>
+      <c r="H44" s="24" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="I44" s="22" t="n">
+        <v>-7.13</v>
       </c>
       <c r="J44" s="23" t="inlineStr">
         <is>
-          <t>매일경제 헤드라인 언급 / 매일경제 기사 언급 / 매일경제 기사 언급</t>
-        </is>
-      </c>
-      <c r="K44" s="23" t="n">
-        <v/>
+          <t>Google 급상승 검색어 등장 (KR)</t>
+        </is>
+      </c>
+      <c r="K44" s="23" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
       <c r="A45" s="20" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B45" s="20" t="n">
@@ -2247,14 +2245,14 @@
       </c>
       <c r="C45" s="21" t="inlineStr">
         <is>
-          <t>금호건설</t>
+          <t>네이버</t>
         </is>
       </c>
       <c r="D45" s="20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E45" s="20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F45" s="20" t="n">
         <v>0</v>
@@ -2262,27 +2260,25 @@
       <c r="G45" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H45" s="22" t="n">
-        <v>30</v>
-      </c>
-      <c r="I45" s="22" t="n">
-        <v>57.86</v>
+      <c r="H45" s="20" t="n">
+        <v/>
+      </c>
+      <c r="I45" s="20" t="n">
+        <v/>
       </c>
       <c r="J45" s="23" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +397% / 중요공시 1건</t>
-        </is>
-      </c>
-      <c r="K45" s="23" t="inlineStr">
-        <is>
-          <t>네이버, 공시</t>
-        </is>
+          <t>한국경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K45" s="23" t="n">
+        <v/>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
       <c r="A46" s="20" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B46" s="20" t="n">
@@ -2290,14 +2286,14 @@
       </c>
       <c r="C46" s="21" t="inlineStr">
         <is>
-          <t>티이엠씨씨엔에스</t>
+          <t>태양광</t>
         </is>
       </c>
       <c r="D46" s="20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E46" s="20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F46" s="20" t="n">
         <v>0</v>
@@ -2305,27 +2301,27 @@
       <c r="G46" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H46" s="22" t="n">
-        <v>30</v>
-      </c>
-      <c r="I46" s="22" t="n">
-        <v>10.36</v>
+      <c r="H46" s="20" t="n">
+        <v/>
+      </c>
+      <c r="I46" s="20" t="n">
+        <v/>
       </c>
       <c r="J46" s="23" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +388% / 중요공시 1건</t>
+          <t>네이버뉴스 헤드라인 언급 / 매일경제 헤드라인 언급</t>
         </is>
       </c>
       <c r="K46" s="23" t="inlineStr">
         <is>
-          <t>네이버, 공시</t>
+          <t>네이버</t>
         </is>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
       <c r="A47" s="20" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B47" s="20" t="n">
@@ -2333,14 +2329,14 @@
       </c>
       <c r="C47" s="21" t="inlineStr">
         <is>
-          <t>크리스탈신소재</t>
+          <t>삼성전기</t>
         </is>
       </c>
       <c r="D47" s="20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E47" s="20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F47" s="20" t="n">
         <v>0</v>
@@ -2348,27 +2344,25 @@
       <c r="G47" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H47" s="22" t="n">
-        <v>18.81</v>
-      </c>
-      <c r="I47" s="24" t="n">
-        <v>-28.03</v>
+      <c r="H47" s="24" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="I47" s="22" t="n">
+        <v>-8.529999999999999</v>
       </c>
       <c r="J47" s="23" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +336% / 중요공시 1건</t>
-        </is>
-      </c>
-      <c r="K47" s="23" t="inlineStr">
-        <is>
-          <t>네이버, 공시</t>
-        </is>
+          <t>매일경제 기사 언급 / 한국경제 헤드라인 언급 / 매일경제 기사 언급</t>
+        </is>
+      </c>
+      <c r="K47" s="23" t="n">
+        <v/>
       </c>
     </row>
     <row r="48" ht="18" customHeight="1">
       <c r="A48" s="20" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B48" s="20" t="n">
@@ -2376,7 +2370,7 @@
       </c>
       <c r="C48" s="21" t="inlineStr">
         <is>
-          <t>헝셩그룹</t>
+          <t>티이엠씨씨엔에스</t>
         </is>
       </c>
       <c r="D48" s="20" t="n">
@@ -2391,27 +2385,27 @@
       <c r="G48" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H48" s="24" t="n">
-        <v>-2.71</v>
-      </c>
-      <c r="I48" s="22" t="n">
-        <v>15.4</v>
+      <c r="H48" s="22" t="n">
+        <v>-0.31</v>
+      </c>
+      <c r="I48" s="24" t="n">
+        <v>14.49</v>
       </c>
       <c r="J48" s="23" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +299% / 중요공시 2건</t>
+          <t>네이버 검색 당일 +524% / 중요공시 1건</t>
         </is>
       </c>
       <c r="K48" s="23" t="inlineStr">
         <is>
-          <t>네이버, 공시</t>
+          <t>공시, 네이버</t>
         </is>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1">
       <c r="A49" s="20" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B49" s="20" t="n">
@@ -2434,27 +2428,27 @@
       <c r="G49" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H49" s="22" t="n">
-        <v>9.69</v>
-      </c>
-      <c r="I49" s="22" t="n">
-        <v>34.27</v>
+      <c r="H49" s="24" t="n">
+        <v>10.24</v>
+      </c>
+      <c r="I49" s="24" t="n">
+        <v>13.91</v>
       </c>
       <c r="J49" s="23" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +235% / 중요공시 2건</t>
+          <t>네이버 검색 당일 +244% / 중요공시 2건</t>
         </is>
       </c>
       <c r="K49" s="23" t="inlineStr">
         <is>
-          <t>네이버, 공시</t>
+          <t>공시, 네이버</t>
         </is>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
       <c r="A50" s="20" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B50" s="20" t="n">
@@ -2462,7 +2456,7 @@
       </c>
       <c r="C50" s="21" t="inlineStr">
         <is>
-          <t>남화토건</t>
+          <t>다스코</t>
         </is>
       </c>
       <c r="D50" s="20" t="n">
@@ -2477,27 +2471,27 @@
       <c r="G50" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H50" s="22" t="n">
-        <v>29.96</v>
-      </c>
-      <c r="I50" s="22" t="n">
-        <v>28.96</v>
+      <c r="H50" s="24" t="n">
+        <v>29.99</v>
+      </c>
+      <c r="I50" s="24" t="n">
+        <v>52.65</v>
       </c>
       <c r="J50" s="23" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +181% / 중요공시 1건</t>
+          <t>네이버 검색 당일 +159% / 중요공시 1건</t>
         </is>
       </c>
       <c r="K50" s="23" t="inlineStr">
         <is>
-          <t>네이버, 공시</t>
+          <t>공시, 네이버</t>
         </is>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
       <c r="A51" s="20" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B51" s="20" t="n">
@@ -2505,7 +2499,7 @@
       </c>
       <c r="C51" s="21" t="inlineStr">
         <is>
-          <t>뉴인텍</t>
+          <t>카카오</t>
         </is>
       </c>
       <c r="D51" s="20" t="n">
@@ -2520,27 +2514,25 @@
       <c r="G51" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H51" s="22" t="n">
-        <v>29.93</v>
+      <c r="H51" s="24" t="n">
+        <v>8.140000000000001</v>
       </c>
       <c r="I51" s="22" t="n">
-        <v>47.06</v>
+        <v>-2.58</v>
       </c>
       <c r="J51" s="23" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +165% / 중요공시 1건</t>
-        </is>
-      </c>
-      <c r="K51" s="23" t="inlineStr">
-        <is>
-          <t>네이버, 공시</t>
-        </is>
+          <t>매일경제 헤드라인 언급 / 매일경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K51" s="23" t="n">
+        <v/>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1">
       <c r="A52" s="20" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B52" s="20" t="n">
@@ -2548,7 +2540,7 @@
       </c>
       <c r="C52" s="21" t="inlineStr">
         <is>
-          <t>다스코</t>
+          <t>LG전자</t>
         </is>
       </c>
       <c r="D52" s="20" t="n">
@@ -2564,26 +2556,24 @@
         <v>0</v>
       </c>
       <c r="H52" s="24" t="n">
-        <v>-16.32</v>
-      </c>
-      <c r="I52" s="24" t="n">
-        <v>-1.01</v>
+        <v>0.41</v>
+      </c>
+      <c r="I52" s="22" t="n">
+        <v>-13.54</v>
       </c>
       <c r="J52" s="23" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +146% / 중요공시 1건</t>
-        </is>
-      </c>
-      <c r="K52" s="23" t="inlineStr">
-        <is>
-          <t>네이버, 공시</t>
-        </is>
+          <t>매일경제 기사 언급 / 매일경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K52" s="23" t="n">
+        <v/>
       </c>
     </row>
     <row r="53" ht="18" customHeight="1">
       <c r="A53" s="20" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B53" s="20" t="n">
@@ -2591,30 +2581,30 @@
       </c>
       <c r="C53" s="21" t="inlineStr">
         <is>
-          <t>남광토건</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="D53" s="20" t="n">
         <v>4</v>
       </c>
       <c r="E53" s="20" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F53" s="20" t="n">
         <v>0</v>
       </c>
       <c r="G53" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H53" s="22" t="n">
-        <v>6.41</v>
+        <v>3</v>
+      </c>
+      <c r="H53" s="24" t="n">
+        <v>8.91</v>
       </c>
       <c r="I53" s="22" t="n">
-        <v>5.06</v>
+        <v>-9.130000000000001</v>
       </c>
       <c r="J53" s="23" t="inlineStr">
         <is>
-          <t>중요공시 3건</t>
+          <t>중요공시 2건 / 중요공시 7일 +100%</t>
         </is>
       </c>
       <c r="K53" s="23" t="inlineStr">
@@ -2626,7 +2616,7 @@
     <row r="54" ht="18" customHeight="1">
       <c r="A54" s="20" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B54" s="20" t="n">
@@ -2634,7 +2624,7 @@
       </c>
       <c r="C54" s="21" t="inlineStr">
         <is>
-          <t>SK텔레콤</t>
+          <t>올릭스</t>
         </is>
       </c>
       <c r="D54" s="20" t="n">
@@ -2650,14 +2640,14 @@
         <v>0</v>
       </c>
       <c r="H54" s="24" t="n">
-        <v>-0.88</v>
+        <v>24.22</v>
       </c>
       <c r="I54" s="24" t="n">
-        <v>-4.53</v>
+        <v>27.93</v>
       </c>
       <c r="J54" s="23" t="inlineStr">
         <is>
-          <t>중요공시 1건 / 매일경제 헤드라인 언급</t>
+          <t>중요공시 2건 / 매일경제 헤드라인 언급</t>
         </is>
       </c>
       <c r="K54" s="23" t="inlineStr">
@@ -2669,7 +2659,7 @@
     <row r="55" ht="18" customHeight="1">
       <c r="A55" s="20" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B55" s="20" t="n">
@@ -2677,42 +2667,42 @@
       </c>
       <c r="C55" s="21" t="inlineStr">
         <is>
-          <t>카카오게임즈</t>
+          <t>시너지이노베이션</t>
         </is>
       </c>
       <c r="D55" s="20" t="n">
         <v>4</v>
       </c>
       <c r="E55" s="20" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F55" s="20" t="n">
         <v>0</v>
       </c>
       <c r="G55" s="20" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H55" s="24" t="n">
-        <v>-9.41</v>
+        <v>7.34</v>
       </c>
       <c r="I55" s="24" t="n">
-        <v>-21.34</v>
+        <v>0.06</v>
       </c>
       <c r="J55" s="23" t="inlineStr">
         <is>
-          <t>중요공시 1건 / 네이버뉴스 헤드라인 언급</t>
+          <t>중요공시 2건 / 중요공시 7일 +100%</t>
         </is>
       </c>
       <c r="K55" s="23" t="inlineStr">
         <is>
-          <t>네이버, 공시</t>
+          <t>공시</t>
         </is>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1">
       <c r="A56" s="20" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B56" s="20" t="n">
@@ -2720,42 +2710,42 @@
       </c>
       <c r="C56" s="21" t="inlineStr">
         <is>
-          <t>셀트리온</t>
+          <t>모바일어플라이언스</t>
         </is>
       </c>
       <c r="D56" s="20" t="n">
         <v>4</v>
       </c>
       <c r="E56" s="20" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F56" s="20" t="n">
         <v>0</v>
       </c>
       <c r="G56" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H56" s="24" t="n">
-        <v>-4.16</v>
-      </c>
-      <c r="I56" s="24" t="n">
-        <v>-2.58</v>
+        <v>3</v>
+      </c>
+      <c r="H56" s="22" t="n">
+        <v>-3.64</v>
+      </c>
+      <c r="I56" s="22" t="n">
+        <v>-13.13</v>
       </c>
       <c r="J56" s="23" t="inlineStr">
         <is>
-          <t>중요공시 1건 / 네이버뉴스 헤드라인 언급</t>
+          <t>중요공시 2건 / 중요공시 7일 +100%</t>
         </is>
       </c>
       <c r="K56" s="23" t="inlineStr">
         <is>
-          <t>네이버, 공시</t>
+          <t>공시</t>
         </is>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1">
       <c r="A57" s="20" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B57" s="20" t="n">
@@ -2763,42 +2753,42 @@
       </c>
       <c r="C57" s="21" t="inlineStr">
         <is>
-          <t>게임</t>
+          <t>에임드바이오</t>
         </is>
       </c>
       <c r="D57" s="20" t="n">
         <v>4</v>
       </c>
       <c r="E57" s="20" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F57" s="20" t="n">
         <v>0</v>
       </c>
       <c r="G57" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H57" s="20" t="n">
-        <v/>
-      </c>
-      <c r="I57" s="20" t="n">
-        <v/>
+        <v>3</v>
+      </c>
+      <c r="H57" s="24" t="n">
+        <v>16.04</v>
+      </c>
+      <c r="I57" s="24" t="n">
+        <v>6.11</v>
       </c>
       <c r="J57" s="23" t="inlineStr">
         <is>
-          <t>네이버뉴스 헤드라인 언급 / 네이버뉴스 기사 언급</t>
+          <t>중요공시 2건 / 중요공시 7일 +100%</t>
         </is>
       </c>
       <c r="K57" s="23" t="inlineStr">
         <is>
-          <t>네이버</t>
+          <t>공시</t>
         </is>
       </c>
     </row>
     <row r="58" ht="18" customHeight="1">
       <c r="A58" s="20" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B58" s="20" t="n">
@@ -2806,7 +2796,7 @@
       </c>
       <c r="C58" s="21" t="inlineStr">
         <is>
-          <t>한미반도체</t>
+          <t>현대로템</t>
         </is>
       </c>
       <c r="D58" s="20" t="n">
@@ -2822,24 +2812,26 @@
         <v>0</v>
       </c>
       <c r="H58" s="24" t="n">
-        <v>-5.68</v>
-      </c>
-      <c r="I58" s="24" t="n">
-        <v>-12.71</v>
+        <v>8.890000000000001</v>
+      </c>
+      <c r="I58" s="22" t="n">
+        <v>-9.140000000000001</v>
       </c>
       <c r="J58" s="23" t="inlineStr">
         <is>
-          <t>매일경제 헤드라인 언급 / 매일경제 기사 언급</t>
-        </is>
-      </c>
-      <c r="K58" s="23" t="n">
-        <v/>
+          <t>중요공시 1건 / 매일경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K58" s="23" t="inlineStr">
+        <is>
+          <t>공시</t>
+        </is>
       </c>
     </row>
     <row r="59" ht="18" customHeight="1">
       <c r="A59" s="20" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B59" s="20" t="n">
@@ -2847,7 +2839,7 @@
       </c>
       <c r="C59" s="21" t="inlineStr">
         <is>
-          <t>전기차</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="D59" s="20" t="n">
@@ -2862,15 +2854,15 @@
       <c r="G59" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H59" s="20" t="n">
-        <v/>
-      </c>
-      <c r="I59" s="20" t="n">
-        <v/>
+      <c r="H59" s="24" t="n">
+        <v>7.68</v>
+      </c>
+      <c r="I59" s="22" t="n">
+        <v>-0.44</v>
       </c>
       <c r="J59" s="23" t="inlineStr">
         <is>
-          <t>매일경제 기사 언급 / 매일경제 헤드라인 언급</t>
+          <t>한국경제 헤드라인 언급 / 매일경제 기사 언급</t>
         </is>
       </c>
       <c r="K59" s="23" t="n">
@@ -2878,52 +2870,50 @@
       </c>
     </row>
     <row r="60" ht="18" customHeight="1">
-      <c r="A60" s="25" t="inlineStr">
-        <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="B60" s="25" t="n">
+      <c r="A60" s="20" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B60" s="20" t="n">
         <v>47</v>
       </c>
-      <c r="C60" s="26" t="inlineStr">
-        <is>
-          <t>프로브잇</t>
-        </is>
-      </c>
-      <c r="D60" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="E60" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="F60" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="G60" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="H60" s="27" t="n">
-        <v>-40</v>
-      </c>
-      <c r="I60" s="27" t="n">
-        <v>-98.53</v>
-      </c>
-      <c r="J60" s="28" t="inlineStr">
-        <is>
-          <t>네이버 검색 당일 +2008%</t>
-        </is>
-      </c>
-      <c r="K60" s="28" t="inlineStr">
-        <is>
-          <t>네이버</t>
-        </is>
+      <c r="C60" s="21" t="inlineStr">
+        <is>
+          <t>하이브</t>
+        </is>
+      </c>
+      <c r="D60" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="E60" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="F60" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G60" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H60" s="24" t="n">
+        <v>9.84</v>
+      </c>
+      <c r="I60" s="22" t="n">
+        <v>-8.31</v>
+      </c>
+      <c r="J60" s="23" t="inlineStr">
+        <is>
+          <t>매일경제 헤드라인 언급 / 매일경제 기사 언급</t>
+        </is>
+      </c>
+      <c r="K60" s="23" t="n">
+        <v/>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
       <c r="A61" s="25" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B61" s="25" t="n">
@@ -2931,7 +2921,7 @@
       </c>
       <c r="C61" s="26" t="inlineStr">
         <is>
-          <t>광주신세계</t>
+          <t>프로브잇</t>
         </is>
       </c>
       <c r="D61" s="25" t="n">
@@ -2946,15 +2936,15 @@
       <c r="G61" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H61" s="29" t="n">
-        <v>29.98</v>
-      </c>
-      <c r="I61" s="29" t="n">
-        <v>50.71</v>
+      <c r="H61" s="27" t="n">
+        <v>-44.44</v>
+      </c>
+      <c r="I61" s="27" t="n">
+        <v>-72.22</v>
       </c>
       <c r="J61" s="28" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +1484%</t>
+          <t>네이버 검색 당일 +2031%</t>
         </is>
       </c>
       <c r="K61" s="28" t="inlineStr">
@@ -2966,7 +2956,7 @@
     <row r="62" ht="18" customHeight="1">
       <c r="A62" s="25" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B62" s="25" t="n">
@@ -2974,7 +2964,7 @@
       </c>
       <c r="C62" s="26" t="inlineStr">
         <is>
-          <t>NPX</t>
+          <t>광주신세계</t>
         </is>
       </c>
       <c r="D62" s="25" t="n">
@@ -2990,14 +2980,14 @@
         <v>0</v>
       </c>
       <c r="H62" s="27" t="n">
-        <v>-97.41</v>
-      </c>
-      <c r="I62" s="27" t="n">
-        <v>-97.41</v>
+        <v>-4.73</v>
+      </c>
+      <c r="I62" s="29" t="n">
+        <v>44.83</v>
       </c>
       <c r="J62" s="28" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +1237%</t>
+          <t>네이버 검색 당일 +1608%</t>
         </is>
       </c>
       <c r="K62" s="28" t="inlineStr">
@@ -3009,7 +2999,7 @@
     <row r="63" ht="18" customHeight="1">
       <c r="A63" s="25" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B63" s="25" t="n">
@@ -3017,7 +3007,7 @@
       </c>
       <c r="C63" s="26" t="inlineStr">
         <is>
-          <t>남화산업</t>
+          <t>NPX</t>
         </is>
       </c>
       <c r="D63" s="25" t="n">
@@ -3032,15 +3022,15 @@
       <c r="G63" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H63" s="29" t="n">
-        <v>29.97</v>
-      </c>
-      <c r="I63" s="29" t="n">
-        <v>30.84</v>
+      <c r="H63" s="27" t="n">
+        <v>-49.52</v>
+      </c>
+      <c r="I63" s="27" t="n">
+        <v>-98.69</v>
       </c>
       <c r="J63" s="28" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +931%</t>
+          <t>네이버 검색 당일 +1347%</t>
         </is>
       </c>
       <c r="K63" s="28" t="inlineStr">
@@ -3142,22 +3132,22 @@
         <v>1</v>
       </c>
       <c r="C3" s="25" t="n">
-        <v>101</v>
+        <v>121</v>
       </c>
       <c r="D3" s="25" t="n">
-        <v>101</v>
+        <v>121</v>
       </c>
       <c r="E3" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F3" s="25" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G3" s="25" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="H3" s="25" t="n"/>
@@ -3173,196 +3163,196 @@
         <v>1</v>
       </c>
       <c r="C4" s="25" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="D4" s="25" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="E4" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F4" s="25" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G4" s="25" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="H4" s="27" t="n">
-        <v>-5.01</v>
+        <v>-3.68</v>
       </c>
       <c r="I4" s="29" t="n">
-        <v>12.57</v>
+        <v>7.53</v>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="26" t="inlineStr">
         <is>
-          <t>바이오</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B5" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C5" s="25" t="n">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="D5" s="25" t="n">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="E5" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F5" s="25" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G5" s="25" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="H5" s="25" t="n"/>
-      <c r="I5" s="25" t="n"/>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="H5" s="27" t="n">
+        <v>-4.86</v>
+      </c>
+      <c r="I5" s="27" t="n">
+        <v>-8.630000000000001</v>
+      </c>
     </row>
     <row r="6" ht="18" customHeight="1">
       <c r="A6" s="26" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>인공지능</t>
         </is>
       </c>
       <c r="B6" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C6" s="25" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="D6" s="25" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="E6" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F6" s="25" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G6" s="25" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="H6" s="27" t="n">
-        <v>-5.3</v>
-      </c>
-      <c r="I6" s="27" t="n">
-        <v>-4.1</v>
-      </c>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="H6" s="25" t="n"/>
+      <c r="I6" s="25" t="n"/>
     </row>
     <row r="7" ht="18" customHeight="1">
       <c r="A7" s="26" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>바이오</t>
         </is>
       </c>
       <c r="B7" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C7" s="25" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D7" s="25" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E7" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F7" s="25" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G7" s="25" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="H7" s="27" t="n">
-        <v>-8.359999999999999</v>
-      </c>
-      <c r="I7" s="27" t="n">
-        <v>-3.29</v>
-      </c>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="H7" s="25" t="n"/>
+      <c r="I7" s="25" t="n"/>
     </row>
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="26" t="inlineStr">
         <is>
-          <t>인공지능</t>
+          <t>LG</t>
         </is>
       </c>
       <c r="B8" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C8" s="25" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D8" s="25" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E8" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F8" s="25" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G8" s="25" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="H8" s="25" t="n"/>
-      <c r="I8" s="25" t="n"/>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="H8" s="29" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="I8" s="27" t="n">
+        <v>-8.279999999999999</v>
+      </c>
     </row>
     <row r="9" ht="18" customHeight="1">
       <c r="A9" s="26" t="inlineStr">
         <is>
-          <t>LG</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B9" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C9" s="25" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D9" s="25" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E9" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F9" s="25" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G9" s="25" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="H9" s="27" t="n">
-        <v>-0.8</v>
+        <v>-1.68</v>
       </c>
       <c r="I9" s="27" t="n">
-        <v>-9.460000000000001</v>
+        <v>-9.970000000000001</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
@@ -3375,22 +3365,22 @@
         <v>1</v>
       </c>
       <c r="C10" s="25" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D10" s="25" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E10" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F10" s="25" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G10" s="25" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="H10" s="25" t="n"/>
@@ -3406,22 +3396,22 @@
         <v>1</v>
       </c>
       <c r="C11" s="25" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D11" s="25" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E11" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F11" s="25" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G11" s="25" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="H11" s="25" t="n"/>
@@ -3430,29 +3420,29 @@
     <row r="12" ht="18" customHeight="1">
       <c r="A12" s="26" t="inlineStr">
         <is>
-          <t>방산</t>
+          <t>전기차</t>
         </is>
       </c>
       <c r="B12" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C12" s="25" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D12" s="25" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E12" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F12" s="25" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G12" s="25" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="H12" s="25" t="n"/>
@@ -3461,42 +3451,42 @@
     <row r="13" ht="18" customHeight="1">
       <c r="A13" s="26" t="inlineStr">
         <is>
-          <t>LG이노텍</t>
+          <t>현대차</t>
         </is>
       </c>
       <c r="B13" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C13" s="25" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D13" s="25" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E13" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F13" s="25" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G13" s="25" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="H13" s="27" t="n">
-        <v>-2.31</v>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="H13" s="29" t="n">
+        <v>3.43</v>
       </c>
       <c r="I13" s="27" t="n">
-        <v>-18.69</v>
+        <v>-14.46</v>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="26" t="inlineStr">
         <is>
-          <t>젠큐릭스</t>
+          <t>LG화학</t>
         </is>
       </c>
       <c r="B14" s="25" t="n">
@@ -3513,200 +3503,196 @@
       </c>
       <c r="F14" s="25" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G14" s="25" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="H14" s="27" t="n">
-        <v>-1.9</v>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="H14" s="29" t="n">
+        <v>13.65</v>
       </c>
       <c r="I14" s="27" t="n">
-        <v>-12.13</v>
+        <v>-4.64</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
       <c r="A15" s="26" t="inlineStr">
         <is>
-          <t>성호전자</t>
+          <t>삼호개발</t>
         </is>
       </c>
       <c r="B15" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C15" s="25" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D15" s="25" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E15" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F15" s="25" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G15" s="25" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="H15" s="29" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="I15" s="27" t="n">
-        <v>-24.25</v>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="H15" s="27" t="n">
+        <v>-2.17</v>
+      </c>
+      <c r="I15" s="29" t="n">
+        <v>17.02</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
       <c r="A16" s="26" t="inlineStr">
         <is>
-          <t>LG전자</t>
+          <t>원전</t>
         </is>
       </c>
       <c r="B16" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C16" s="25" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D16" s="25" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E16" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F16" s="25" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G16" s="25" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="H16" s="27" t="n">
-        <v>-3.5</v>
-      </c>
-      <c r="I16" s="27" t="n">
-        <v>-7.38</v>
-      </c>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="H16" s="25" t="n"/>
+      <c r="I16" s="25" t="n"/>
     </row>
     <row r="17" ht="18" customHeight="1">
       <c r="A17" s="26" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>성호전자</t>
         </is>
       </c>
       <c r="B17" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C17" s="25" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D17" s="25" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E17" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F17" s="25" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G17" s="25" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="H17" s="27" t="n">
-        <v>-8.41</v>
+        <v>-1.56</v>
       </c>
       <c r="I17" s="27" t="n">
-        <v>-14.4</v>
+        <v>-22.9</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
       <c r="A18" s="26" t="inlineStr">
         <is>
-          <t>삼성바이오로직스</t>
+          <t>스피어</t>
         </is>
       </c>
       <c r="B18" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C18" s="25" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D18" s="25" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E18" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F18" s="25" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G18" s="25" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="H18" s="27" t="n">
-        <v>-3.1</v>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="H18" s="29" t="n">
+        <v>17.63</v>
       </c>
       <c r="I18" s="27" t="n">
-        <v>-2.26</v>
+        <v>-8.130000000000001</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
       <c r="A19" s="26" t="inlineStr">
         <is>
-          <t>삼호개발</t>
+          <t>파두</t>
         </is>
       </c>
       <c r="B19" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C19" s="25" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D19" s="25" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E19" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F19" s="25" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G19" s="25" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="H19" s="29" t="n">
-        <v>8.69</v>
-      </c>
-      <c r="I19" s="29" t="n">
-        <v>16.77</v>
+        <v>3.25</v>
+      </c>
+      <c r="I19" s="27" t="n">
+        <v>-26.06</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
       <c r="A20" s="26" t="inlineStr">
         <is>
-          <t>샤페론</t>
+          <t>뉴인텍</t>
         </is>
       </c>
       <c r="B20" s="25" t="n">
@@ -3723,25 +3709,25 @@
       </c>
       <c r="F20" s="25" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G20" s="25" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="H20" s="27" t="n">
-        <v>-25.16</v>
-      </c>
-      <c r="I20" s="27" t="n">
-        <v>-56.14</v>
+        <v>-20.41</v>
+      </c>
+      <c r="I20" s="29" t="n">
+        <v>17.04</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
       <c r="A21" s="26" t="inlineStr">
         <is>
-          <t>스피어</t>
+          <t>방산</t>
         </is>
       </c>
       <c r="B21" s="25" t="n">
@@ -3758,25 +3744,21 @@
       </c>
       <c r="F21" s="25" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G21" s="25" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="H21" s="27" t="n">
-        <v>-8.76</v>
-      </c>
-      <c r="I21" s="27" t="n">
-        <v>-31.49</v>
-      </c>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="H21" s="25" t="n"/>
+      <c r="I21" s="25" t="n"/>
     </row>
     <row r="22" ht="18" customHeight="1">
       <c r="A22" s="26" t="inlineStr">
         <is>
-          <t>에이팩트</t>
+          <t>아크솔루션스</t>
         </is>
       </c>
       <c r="B22" s="25" t="n">
@@ -3793,25 +3775,25 @@
       </c>
       <c r="F22" s="25" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G22" s="25" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="H22" s="27" t="n">
-        <v>-6.74</v>
+        <v>-97.40000000000001</v>
       </c>
       <c r="I22" s="27" t="n">
-        <v>-26.62</v>
+        <v>-97.40000000000001</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
       <c r="A23" s="26" t="inlineStr">
         <is>
-          <t>차바이오텍</t>
+          <t>앱튼</t>
         </is>
       </c>
       <c r="B23" s="25" t="n">
@@ -3828,25 +3810,25 @@
       </c>
       <c r="F23" s="25" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G23" s="25" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="H23" s="27" t="n">
-        <v>-4.12</v>
-      </c>
-      <c r="I23" s="27" t="n">
-        <v>-12.15</v>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="H23" s="29" t="n">
+        <v>29.98</v>
+      </c>
+      <c r="I23" s="29" t="n">
+        <v>109.15</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
       <c r="A24" s="26" t="inlineStr">
         <is>
-          <t>페니트리움바이오</t>
+          <t>원익IPS</t>
         </is>
       </c>
       <c r="B24" s="25" t="n">
@@ -3863,130 +3845,130 @@
       </c>
       <c r="F24" s="25" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G24" s="25" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="H24" s="27" t="n">
-        <v>-2.96</v>
+        <v>-2.93</v>
       </c>
       <c r="I24" s="27" t="n">
-        <v>-11.93</v>
+        <v>-7.83</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
       <c r="A25" s="26" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>차바이오텍</t>
         </is>
       </c>
       <c r="B25" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C25" s="25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D25" s="25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E25" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F25" s="25" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G25" s="25" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="H25" s="27" t="n">
-        <v>-2.67</v>
-      </c>
-      <c r="I25" s="27" t="n">
-        <v>-11.52</v>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="H25" s="29" t="n">
+        <v>10.78</v>
+      </c>
+      <c r="I25" s="29" t="n">
+        <v>0.26</v>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
       <c r="A26" s="26" t="inlineStr">
         <is>
-          <t>리가켐바이오</t>
+          <t>페니트리움바이오</t>
         </is>
       </c>
       <c r="B26" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C26" s="25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D26" s="25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E26" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F26" s="25" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G26" s="25" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="H26" s="27" t="n">
-        <v>-8.279999999999999</v>
-      </c>
-      <c r="I26" s="29" t="n">
-        <v>6.17</v>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="H26" s="29" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="I26" s="27" t="n">
+        <v>-7.21</v>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
       <c r="A27" s="26" t="inlineStr">
         <is>
-          <t>소룩스</t>
+          <t>한화생명</t>
         </is>
       </c>
       <c r="B27" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C27" s="25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D27" s="25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E27" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F27" s="25" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G27" s="25" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="H27" s="27" t="n">
-        <v>-4.21</v>
-      </c>
-      <c r="I27" s="29" t="n">
-        <v>19.47</v>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="H27" s="29" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="I27" s="27" t="n">
+        <v>-9.199999999999999</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
       <c r="A28" s="26" t="inlineStr">
         <is>
-          <t>에이프릴바이오</t>
+          <t>KB금융</t>
         </is>
       </c>
       <c r="B28" s="25" t="n">
@@ -4003,25 +3985,25 @@
       </c>
       <c r="F28" s="25" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G28" s="25" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="H28" s="27" t="n">
-        <v>-0.13</v>
-      </c>
-      <c r="I28" s="29" t="n">
-        <v>1.72</v>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="H28" s="29" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="I28" s="27" t="n">
+        <v>-2.1</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
       <c r="A29" s="26" t="inlineStr">
         <is>
-          <t>오텍</t>
+          <t>기아</t>
         </is>
       </c>
       <c r="B29" s="25" t="n">
@@ -4038,25 +4020,25 @@
       </c>
       <c r="F29" s="25" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G29" s="25" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="H29" s="29" t="n">
-        <v>13.75</v>
-      </c>
-      <c r="I29" s="29" t="n">
-        <v>32.47</v>
+        <v>3.92</v>
+      </c>
+      <c r="I29" s="27" t="n">
+        <v>-7.13</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
       <c r="A30" s="26" t="inlineStr">
         <is>
-          <t>조선</t>
+          <t>남광토건</t>
         </is>
       </c>
       <c r="B30" s="25" t="n">
@@ -4073,21 +4055,25 @@
       </c>
       <c r="F30" s="25" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G30" s="25" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="H30" s="25" t="n"/>
-      <c r="I30" s="25" t="n"/>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="H30" s="29" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="I30" s="29" t="n">
+        <v>9.539999999999999</v>
+      </c>
     </row>
     <row r="31" ht="18" customHeight="1">
       <c r="A31" s="26" t="inlineStr">
         <is>
-          <t>카카오</t>
+          <t>네이버</t>
         </is>
       </c>
       <c r="B31" s="25" t="n">
@@ -4104,25 +4090,21 @@
       </c>
       <c r="F31" s="25" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G31" s="25" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="H31" s="27" t="n">
-        <v>-3.21</v>
-      </c>
-      <c r="I31" s="27" t="n">
-        <v>-12.19</v>
-      </c>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="H31" s="25" t="n"/>
+      <c r="I31" s="25" t="n"/>
     </row>
     <row r="32" ht="18" customHeight="1">
       <c r="A32" s="26" t="inlineStr">
         <is>
-          <t>태양광</t>
+          <t>대한항공</t>
         </is>
       </c>
       <c r="B32" s="25" t="n">
@@ -4139,21 +4121,25 @@
       </c>
       <c r="F32" s="25" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G32" s="25" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="H32" s="25" t="n"/>
-      <c r="I32" s="25" t="n"/>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="H32" s="29" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="I32" s="29" t="n">
+        <v>4.81</v>
+      </c>
     </row>
     <row r="33" ht="18" customHeight="1">
       <c r="A33" s="26" t="inlineStr">
         <is>
-          <t>파두</t>
+          <t>삼성전기</t>
         </is>
       </c>
       <c r="B33" s="25" t="n">
@@ -4170,126 +4156,126 @@
       </c>
       <c r="F33" s="25" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G33" s="25" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="H33" s="27" t="n">
-        <v>-5.14</v>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="H33" s="29" t="n">
+        <v>2.26</v>
       </c>
       <c r="I33" s="27" t="n">
-        <v>-18.15</v>
+        <v>-8.529999999999999</v>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
       <c r="A34" s="26" t="inlineStr">
         <is>
-          <t>SK텔레콤</t>
+          <t>소룩스</t>
         </is>
       </c>
       <c r="B34" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C34" s="25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D34" s="25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E34" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F34" s="25" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G34" s="25" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="H34" s="27" t="n">
-        <v>-0.88</v>
-      </c>
-      <c r="I34" s="27" t="n">
-        <v>-4.53</v>
+        <v>-4.76</v>
+      </c>
+      <c r="I34" s="29" t="n">
+        <v>18.99</v>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
       <c r="A35" s="26" t="inlineStr">
         <is>
-          <t>게임</t>
+          <t>채비</t>
         </is>
       </c>
       <c r="B35" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C35" s="25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D35" s="25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E35" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F35" s="25" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G35" s="25" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="H35" s="25" t="n"/>
-      <c r="I35" s="25" t="n"/>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="H35" s="29" t="n">
+        <v>16.69</v>
+      </c>
+      <c r="I35" s="27" t="n">
+        <v>-3.89</v>
+      </c>
     </row>
     <row r="36" ht="18" customHeight="1">
       <c r="A36" s="26" t="inlineStr">
         <is>
-          <t>금호건설</t>
+          <t>태양광</t>
         </is>
       </c>
       <c r="B36" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C36" s="25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D36" s="25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E36" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F36" s="25" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G36" s="25" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="H36" s="29" t="n">
-        <v>30</v>
-      </c>
-      <c r="I36" s="29" t="n">
-        <v>57.86</v>
-      </c>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="H36" s="25" t="n"/>
+      <c r="I36" s="25" t="n"/>
     </row>
     <row r="37" ht="18" customHeight="1">
       <c r="A37" s="26" t="inlineStr">
         <is>
-          <t>남광토건</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="B37" s="25" t="n">
@@ -4306,25 +4292,25 @@
       </c>
       <c r="F37" s="25" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G37" s="25" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="H37" s="29" t="n">
-        <v>6.41</v>
-      </c>
-      <c r="I37" s="29" t="n">
-        <v>5.06</v>
+        <v>7.68</v>
+      </c>
+      <c r="I37" s="27" t="n">
+        <v>-0.44</v>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
       <c r="A38" s="26" t="inlineStr">
         <is>
-          <t>남화토건</t>
+          <t>LG전자</t>
         </is>
       </c>
       <c r="B38" s="25" t="n">
@@ -4341,25 +4327,25 @@
       </c>
       <c r="F38" s="25" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G38" s="25" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="H38" s="29" t="n">
-        <v>29.96</v>
-      </c>
-      <c r="I38" s="29" t="n">
-        <v>28.96</v>
+        <v>0.41</v>
+      </c>
+      <c r="I38" s="27" t="n">
+        <v>-13.54</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
       <c r="A39" s="26" t="inlineStr">
         <is>
-          <t>뉴인텍</t>
+          <t>다스코</t>
         </is>
       </c>
       <c r="B39" s="25" t="n">
@@ -4376,25 +4362,25 @@
       </c>
       <c r="F39" s="25" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G39" s="25" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="H39" s="29" t="n">
-        <v>29.93</v>
+        <v>29.99</v>
       </c>
       <c r="I39" s="29" t="n">
-        <v>47.06</v>
+        <v>52.65</v>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
       <c r="A40" s="26" t="inlineStr">
         <is>
-          <t>다스코</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B40" s="25" t="n">
@@ -4411,25 +4397,25 @@
       </c>
       <c r="F40" s="25" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G40" s="25" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="H40" s="27" t="n">
-        <v>-16.32</v>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="H40" s="29" t="n">
+        <v>8.91</v>
       </c>
       <c r="I40" s="27" t="n">
-        <v>-1.01</v>
+        <v>-9.130000000000001</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
       <c r="A41" s="26" t="inlineStr">
         <is>
-          <t>베셀</t>
+          <t>모바일어플라이언스</t>
         </is>
       </c>
       <c r="B41" s="25" t="n">
@@ -4446,25 +4432,25 @@
       </c>
       <c r="F41" s="25" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G41" s="25" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="H41" s="29" t="n">
-        <v>9.69</v>
-      </c>
-      <c r="I41" s="29" t="n">
-        <v>34.27</v>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="H41" s="27" t="n">
+        <v>-3.64</v>
+      </c>
+      <c r="I41" s="27" t="n">
+        <v>-13.13</v>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
       <c r="A42" s="26" t="inlineStr">
         <is>
-          <t>셀트리온</t>
+          <t>베셀</t>
         </is>
       </c>
       <c r="B42" s="25" t="n">
@@ -4481,25 +4467,25 @@
       </c>
       <c r="F42" s="25" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G42" s="25" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="H42" s="27" t="n">
-        <v>-4.16</v>
-      </c>
-      <c r="I42" s="27" t="n">
-        <v>-2.58</v>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="H42" s="29" t="n">
+        <v>10.24</v>
+      </c>
+      <c r="I42" s="29" t="n">
+        <v>13.91</v>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1">
       <c r="A43" s="26" t="inlineStr">
         <is>
-          <t>전기차</t>
+          <t>시너지이노베이션</t>
         </is>
       </c>
       <c r="B43" s="25" t="n">
@@ -4516,21 +4502,25 @@
       </c>
       <c r="F43" s="25" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G43" s="25" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="H43" s="25" t="n"/>
-      <c r="I43" s="25" t="n"/>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="H43" s="29" t="n">
+        <v>7.34</v>
+      </c>
+      <c r="I43" s="29" t="n">
+        <v>0.06</v>
+      </c>
     </row>
     <row r="44" ht="18" customHeight="1">
       <c r="A44" s="26" t="inlineStr">
         <is>
-          <t>카카오게임즈</t>
+          <t>에임드바이오</t>
         </is>
       </c>
       <c r="B44" s="25" t="n">
@@ -4547,25 +4537,25 @@
       </c>
       <c r="F44" s="25" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G44" s="25" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="H44" s="27" t="n">
-        <v>-9.41</v>
-      </c>
-      <c r="I44" s="27" t="n">
-        <v>-21.34</v>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="H44" s="29" t="n">
+        <v>16.04</v>
+      </c>
+      <c r="I44" s="29" t="n">
+        <v>6.11</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
       <c r="A45" s="26" t="inlineStr">
         <is>
-          <t>크리스탈신소재</t>
+          <t>올릭스</t>
         </is>
       </c>
       <c r="B45" s="25" t="n">
@@ -4582,25 +4572,25 @@
       </c>
       <c r="F45" s="25" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G45" s="25" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="H45" s="29" t="n">
-        <v>18.81</v>
-      </c>
-      <c r="I45" s="27" t="n">
-        <v>-28.03</v>
+        <v>24.22</v>
+      </c>
+      <c r="I45" s="29" t="n">
+        <v>27.93</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
       <c r="A46" s="26" t="inlineStr">
         <is>
-          <t>티이엠씨씨엔에스</t>
+          <t>카카오</t>
         </is>
       </c>
       <c r="B46" s="25" t="n">
@@ -4617,25 +4607,25 @@
       </c>
       <c r="F46" s="25" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G46" s="25" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="H46" s="29" t="n">
-        <v>30</v>
-      </c>
-      <c r="I46" s="29" t="n">
-        <v>10.36</v>
+        <v>8.140000000000001</v>
+      </c>
+      <c r="I46" s="27" t="n">
+        <v>-2.58</v>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
       <c r="A47" s="26" t="inlineStr">
         <is>
-          <t>한미반도체</t>
+          <t>티이엠씨씨엔에스</t>
         </is>
       </c>
       <c r="B47" s="25" t="n">
@@ -4652,25 +4642,25 @@
       </c>
       <c r="F47" s="25" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G47" s="25" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="H47" s="27" t="n">
-        <v>-5.68</v>
-      </c>
-      <c r="I47" s="27" t="n">
-        <v>-12.71</v>
+        <v>-0.31</v>
+      </c>
+      <c r="I47" s="29" t="n">
+        <v>14.49</v>
       </c>
     </row>
     <row r="48" ht="18" customHeight="1">
       <c r="A48" s="26" t="inlineStr">
         <is>
-          <t>헝셩그룹</t>
+          <t>하이브</t>
         </is>
       </c>
       <c r="B48" s="25" t="n">
@@ -4687,60 +4677,60 @@
       </c>
       <c r="F48" s="25" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G48" s="25" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="H48" s="27" t="n">
-        <v>-2.71</v>
-      </c>
-      <c r="I48" s="29" t="n">
-        <v>15.4</v>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="H48" s="29" t="n">
+        <v>9.84</v>
+      </c>
+      <c r="I48" s="27" t="n">
+        <v>-8.31</v>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1">
       <c r="A49" s="26" t="inlineStr">
         <is>
-          <t>NPX</t>
+          <t>현대로템</t>
         </is>
       </c>
       <c r="B49" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C49" s="25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D49" s="25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E49" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F49" s="25" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G49" s="25" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="H49" s="27" t="n">
-        <v>-97.41</v>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="H49" s="29" t="n">
+        <v>8.890000000000001</v>
       </c>
       <c r="I49" s="27" t="n">
-        <v>-97.41</v>
+        <v>-9.140000000000001</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
       <c r="A50" s="26" t="inlineStr">
         <is>
-          <t>광주신세계</t>
+          <t>NPX</t>
         </is>
       </c>
       <c r="B50" s="25" t="n">
@@ -4757,25 +4747,25 @@
       </c>
       <c r="F50" s="25" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G50" s="25" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="H50" s="29" t="n">
-        <v>29.98</v>
-      </c>
-      <c r="I50" s="29" t="n">
-        <v>50.71</v>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="H50" s="27" t="n">
+        <v>-49.52</v>
+      </c>
+      <c r="I50" s="27" t="n">
+        <v>-98.69</v>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
       <c r="A51" s="26" t="inlineStr">
         <is>
-          <t>남화산업</t>
+          <t>광주신세계</t>
         </is>
       </c>
       <c r="B51" s="25" t="n">
@@ -4792,19 +4782,19 @@
       </c>
       <c r="F51" s="25" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G51" s="25" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="H51" s="29" t="n">
-        <v>29.97</v>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="H51" s="27" t="n">
+        <v>-4.73</v>
       </c>
       <c r="I51" s="29" t="n">
-        <v>30.84</v>
+        <v>44.83</v>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1">
@@ -4827,19 +4817,19 @@
       </c>
       <c r="F52" s="25" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G52" s="25" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="H52" s="27" t="n">
-        <v>-40</v>
+        <v>-44.44</v>
       </c>
       <c r="I52" s="27" t="n">
-        <v>-98.53</v>
+        <v>-72.22</v>
       </c>
     </row>
   </sheetData>
@@ -4923,19 +4913,19 @@
         <v>1</v>
       </c>
       <c r="C3" s="36" t="n">
-        <v>101</v>
+        <v>121</v>
       </c>
       <c r="D3" s="36" t="n">
-        <v>101</v>
+        <v>121</v>
       </c>
       <c r="E3" s="36" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="F3" s="37" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G3" s="37" t="inlineStr">
@@ -4954,19 +4944,19 @@
         <v>1</v>
       </c>
       <c r="C4" s="36" t="n">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="D4" s="36" t="n">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="E4" s="36" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="F4" s="37" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G4" s="37" t="inlineStr">
@@ -4985,19 +4975,19 @@
         <v>1</v>
       </c>
       <c r="C5" s="36" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="D5" s="36" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="E5" s="36" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="F5" s="37" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G5" s="37" t="inlineStr">
@@ -5016,19 +5006,19 @@
         <v>1</v>
       </c>
       <c r="C6" s="36" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="D6" s="36" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E6" s="36" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="F6" s="37" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G6" s="37" t="inlineStr">
@@ -5040,26 +5030,26 @@
     <row r="7" ht="18" customHeight="1">
       <c r="A7" s="35" t="inlineStr">
         <is>
-          <t>로봇</t>
+          <t>원전</t>
         </is>
       </c>
       <c r="B7" s="36" t="n">
         <v>1</v>
       </c>
       <c r="C7" s="36" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="D7" s="36" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E7" s="36" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="F7" s="37" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G7" s="37" t="inlineStr">
@@ -5071,26 +5061,26 @@
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="35" t="inlineStr">
         <is>
-          <t>태양광</t>
+          <t>로봇</t>
         </is>
       </c>
       <c r="B8" s="36" t="n">
         <v>1</v>
       </c>
       <c r="C8" s="36" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="D8" s="36" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="E8" s="36" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="F8" s="37" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G8" s="37" t="inlineStr">
@@ -5102,26 +5092,26 @@
     <row r="9" ht="18" customHeight="1">
       <c r="A9" s="35" t="inlineStr">
         <is>
-          <t>게임</t>
+          <t>태양광</t>
         </is>
       </c>
       <c r="B9" s="36" t="n">
         <v>1</v>
       </c>
       <c r="C9" s="36" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D9" s="36" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E9" s="36" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="F9" s="37" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G9" s="37" t="inlineStr">
@@ -5133,26 +5123,26 @@
     <row r="10" ht="18" customHeight="1">
       <c r="A10" s="35" t="inlineStr">
         <is>
-          <t>조선</t>
+          <t>제약</t>
         </is>
       </c>
       <c r="B10" s="36" t="n">
         <v>1</v>
       </c>
       <c r="C10" s="36" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="D10" s="36" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="E10" s="36" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="F10" s="37" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G10" s="37" t="inlineStr">
@@ -5164,26 +5154,26 @@
     <row r="11" ht="18" customHeight="1">
       <c r="A11" s="35" t="inlineStr">
         <is>
-          <t>제약</t>
+          <t>인공지능</t>
         </is>
       </c>
       <c r="B11" s="36" t="n">
         <v>1</v>
       </c>
       <c r="C11" s="36" t="n">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="D11" s="36" t="n">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="E11" s="36" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="F11" s="37" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G11" s="37" t="inlineStr">
@@ -5193,40 +5183,36 @@
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="35" t="inlineStr">
-        <is>
-          <t>인공지능</t>
-        </is>
-      </c>
-      <c r="B12" s="36" t="n">
-        <v>1</v>
-      </c>
-      <c r="C12" s="36" t="n">
-        <v>21</v>
-      </c>
-      <c r="D12" s="36" t="n">
-        <v>21</v>
-      </c>
-      <c r="E12" s="36" t="inlineStr">
-        <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="F12" s="37" t="inlineStr">
-        <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="G12" s="37" t="inlineStr">
-        <is>
-          <t>⚡ 관심</t>
-        </is>
-      </c>
+      <c r="A12" s="26" t="inlineStr">
+        <is>
+          <t>이차전지</t>
+        </is>
+      </c>
+      <c r="B12" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F12" s="28" t="inlineStr">
+        <is>
+          <t>감지 없음</t>
+        </is>
+      </c>
+      <c r="G12" s="28" t="inlineStr"/>
     </row>
     <row r="13" ht="18" customHeight="1">
       <c r="A13" s="26" t="inlineStr">
         <is>
-          <t>이차전지</t>
+          <t>AI반도체</t>
         </is>
       </c>
       <c r="B13" s="25" t="n">
@@ -5253,7 +5239,7 @@
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="26" t="inlineStr">
         <is>
-          <t>AI반도체</t>
+          <t>수소</t>
         </is>
       </c>
       <c r="B14" s="25" t="n">
@@ -5280,7 +5266,7 @@
     <row r="15" ht="18" customHeight="1">
       <c r="A15" s="26" t="inlineStr">
         <is>
-          <t>원전</t>
+          <t>게임</t>
         </is>
       </c>
       <c r="B15" s="25" t="n">
@@ -5307,7 +5293,7 @@
     <row r="16" ht="18" customHeight="1">
       <c r="A16" s="26" t="inlineStr">
         <is>
-          <t>수소</t>
+          <t>엔터</t>
         </is>
       </c>
       <c r="B16" s="25" t="n">
@@ -5334,7 +5320,7 @@
     <row r="17" ht="18" customHeight="1">
       <c r="A17" s="26" t="inlineStr">
         <is>
-          <t>엔터</t>
+          <t>핀테크</t>
         </is>
       </c>
       <c r="B17" s="25" t="n">
@@ -5361,7 +5347,7 @@
     <row r="18" ht="18" customHeight="1">
       <c r="A18" s="26" t="inlineStr">
         <is>
-          <t>핀테크</t>
+          <t>클라우드</t>
         </is>
       </c>
       <c r="B18" s="25" t="n">
@@ -5388,7 +5374,7 @@
     <row r="19" ht="18" customHeight="1">
       <c r="A19" s="26" t="inlineStr">
         <is>
-          <t>클라우드</t>
+          <t>조선</t>
         </is>
       </c>
       <c r="B19" s="25" t="n">

--- a/trend/stock_trend_history.xlsx
+++ b/trend/stock_trend_history.xlsx
@@ -258,13 +258,13 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -694,7 +694,7 @@
     <row r="1" ht="36" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>📊 주식 트렌드 조기 감지 대시보드   |   최종 업데이트: 2026-06-30 06:54</t>
+          <t>📊 주식 트렌드 조기 감지 대시보드   |   최종 업데이트: 2026-07-01 06:54</t>
         </is>
       </c>
     </row>
@@ -708,7 +708,7 @@
       </c>
       <c r="E3" s="3" t="n"/>
       <c r="G3" s="5" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H3" s="3" t="n"/>
       <c r="J3" s="6" t="n">
@@ -787,21 +787,21 @@
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="11" t="inlineStr">
         <is>
-          <t>⚡ 최신(2026-06-30) 상위: 반도체  점수 121.0점</t>
+          <t>⚡ 최신(2026-07-01) 상위: 반도체  점수 108.0점</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1">
       <c r="A11" s="12" t="inlineStr">
         <is>
-          <t>⚡ 최신(2026-06-30) 상위: SK  점수 40.0점</t>
+          <t>⚡ 최신(2026-07-01) 상위: 현대차  점수 27.0점</t>
         </is>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1">
       <c r="A12" s="11" t="inlineStr">
         <is>
-          <t>⚡ 최신(2026-06-30) 상위: 삼성전자  점수 30.0점</t>
+          <t>⚡ 최신(2026-07-01) 상위: 로봇  점수 27.0점</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B14" s="15" t="n">
@@ -928,10 +928,10 @@
         </is>
       </c>
       <c r="D14" s="15" t="n">
-        <v>121</v>
+        <v>108</v>
       </c>
       <c r="E14" s="15" t="n">
-        <v>121</v>
+        <v>108</v>
       </c>
       <c r="F14" s="15" t="n">
         <v>0</v>
@@ -947,7 +947,7 @@
       </c>
       <c r="J14" s="17" t="inlineStr">
         <is>
-          <t>매일경제 기사 언급 / 매일경제 헤드라인 언급 / 네이버뉴스 헤드라인 언급 / 네이버뉴스 기사 언급 / 한국경제 헤드라인 언급</t>
+          <t>네이버뉴스 헤드라인 언급 / 네이버뉴스 헤드라인 언급 / 매일경제 헤드라인 언급 / 네이버뉴스 헤드라인 언급 / 네이버뉴스 헤드라인 언급</t>
         </is>
       </c>
       <c r="K14" s="17" t="inlineStr">
@@ -959,7 +959,7 @@
     <row r="15" ht="18" customHeight="1">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B15" s="15" t="n">
@@ -967,14 +967,14 @@
       </c>
       <c r="C15" s="16" t="inlineStr">
         <is>
-          <t>SK</t>
+          <t>현대차</t>
         </is>
       </c>
       <c r="D15" s="15" t="n">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="E15" s="15" t="n">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="F15" s="15" t="n">
         <v>0</v>
@@ -983,14 +983,14 @@
         <v>0</v>
       </c>
       <c r="H15" s="18" t="n">
-        <v>-3.68</v>
-      </c>
-      <c r="I15" s="19" t="n">
-        <v>7.53</v>
+        <v>-0.4</v>
+      </c>
+      <c r="I15" s="18" t="n">
+        <v>-3.13</v>
       </c>
       <c r="J15" s="17" t="inlineStr">
         <is>
-          <t>매일경제 헤드라인 언급 / 한국경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
+          <t>네이버뉴스 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 기사 언급 / 매일경제 헤드라인 언급</t>
         </is>
       </c>
       <c r="K15" s="17" t="inlineStr">
@@ -1002,7 +1002,7 @@
     <row r="16" ht="18" customHeight="1">
       <c r="A16" s="15" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B16" s="15" t="n">
@@ -1010,14 +1010,14 @@
       </c>
       <c r="C16" s="16" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>로봇</t>
         </is>
       </c>
       <c r="D16" s="15" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="E16" s="15" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="F16" s="15" t="n">
         <v>0</v>
@@ -1025,15 +1025,15 @@
       <c r="G16" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="H16" s="18" t="n">
-        <v>-4.86</v>
-      </c>
-      <c r="I16" s="18" t="n">
-        <v>-8.630000000000001</v>
+      <c r="H16" s="15" t="n">
+        <v/>
+      </c>
+      <c r="I16" s="15" t="n">
+        <v/>
       </c>
       <c r="J16" s="17" t="inlineStr">
         <is>
-          <t>네이버뉴스 헤드라인 언급 / 한국경제 헤드라인 언급 / 매일경제 기사 언급 / 매일경제 기사 언급 / 매일경제 기사 언급</t>
+          <t>네이버뉴스 헤드라인 언급 / 한국경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급</t>
         </is>
       </c>
       <c r="K16" s="17" t="inlineStr">
@@ -1045,7 +1045,7 @@
     <row r="17" ht="18" customHeight="1">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B17" s="15" t="n">
@@ -1053,14 +1053,14 @@
       </c>
       <c r="C17" s="16" t="inlineStr">
         <is>
-          <t>인공지능</t>
+          <t>SK</t>
         </is>
       </c>
       <c r="D17" s="15" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E17" s="15" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F17" s="15" t="n">
         <v>0</v>
@@ -1068,15 +1068,15 @@
       <c r="G17" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="H17" s="15" t="n">
-        <v/>
-      </c>
-      <c r="I17" s="15" t="n">
-        <v/>
+      <c r="H17" s="19" t="n">
+        <v>6.24</v>
+      </c>
+      <c r="I17" s="19" t="n">
+        <v>18.3</v>
       </c>
       <c r="J17" s="17" t="inlineStr">
         <is>
-          <t>매일경제 기사 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 기사 언급 / 매일경제 기사 언급 / 매일경제 기사 언급</t>
+          <t>매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 한국경제 헤드라인 언급 / 매일경제 기사 언급 / 한국경제 헤드라인 언급</t>
         </is>
       </c>
       <c r="K17" s="17" t="inlineStr">
@@ -1088,7 +1088,7 @@
     <row r="18" ht="18" customHeight="1">
       <c r="A18" s="15" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B18" s="15" t="n">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="C18" s="16" t="inlineStr">
         <is>
-          <t>바이오</t>
+          <t>인공지능</t>
         </is>
       </c>
       <c r="D18" s="15" t="n">
@@ -1119,7 +1119,7 @@
       </c>
       <c r="J18" s="17" t="inlineStr">
         <is>
-          <t>네이버뉴스 헤드라인 언급 / 매일경제 헤드라인 언급 / 네이버뉴스 헤드라인 언급 / 매일경제 기사 언급 / 네이버뉴스 헤드라인 언급</t>
+          <t>매일경제 기사 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 기사 언급 / 매일경제 기사 언급 / 매일경제 기사 언급</t>
         </is>
       </c>
       <c r="K18" s="17" t="inlineStr">
@@ -1131,7 +1131,7 @@
     <row r="19" ht="18" customHeight="1">
       <c r="A19" s="15" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B19" s="15" t="n">
@@ -1139,42 +1139,42 @@
       </c>
       <c r="C19" s="16" t="inlineStr">
         <is>
-          <t>LG</t>
+          <t>에코프로</t>
         </is>
       </c>
       <c r="D19" s="15" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E19" s="15" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="F19" s="15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G19" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="H19" s="19" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="I19" s="18" t="n">
-        <v>-8.279999999999999</v>
+      <c r="H19" s="18" t="n">
+        <v>-9.66</v>
+      </c>
+      <c r="I19" s="19" t="n">
+        <v>3.5</v>
       </c>
       <c r="J19" s="17" t="inlineStr">
         <is>
-          <t>매일경제 헤드라인 언급 / 네이버뉴스 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 기사 언급 / 한국경제 헤드라인 언급</t>
+          <t>중요공시 3건 / 중요공시 3일 +200% / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
         </is>
       </c>
       <c r="K19" s="17" t="inlineStr">
         <is>
-          <t>네이버</t>
+          <t>공시</t>
         </is>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
       <c r="A20" s="15" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B20" s="15" t="n">
@@ -1186,10 +1186,10 @@
         </is>
       </c>
       <c r="D20" s="15" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E20" s="15" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F20" s="15" t="n">
         <v>0</v>
@@ -1197,27 +1197,27 @@
       <c r="G20" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="H20" s="18" t="n">
-        <v>-1.68</v>
-      </c>
-      <c r="I20" s="18" t="n">
-        <v>-9.970000000000001</v>
+      <c r="H20" s="19" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="I20" s="19" t="n">
+        <v>3.72</v>
       </c>
       <c r="J20" s="17" t="inlineStr">
         <is>
-          <t>중요공시 1건 / 한국경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 기사 언급 / 매일경제 기사 언급</t>
+          <t>중요공시 1건 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 기사 언급 / 한국경제 헤드라인 언급</t>
         </is>
       </c>
       <c r="K20" s="17" t="inlineStr">
         <is>
-          <t>공시, 네이버</t>
+          <t>네이버, 공시</t>
         </is>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
       <c r="A21" s="15" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B21" s="15" t="n">
@@ -1225,14 +1225,14 @@
       </c>
       <c r="C21" s="16" t="inlineStr">
         <is>
-          <t>로봇</t>
+          <t>삼성전기</t>
         </is>
       </c>
       <c r="D21" s="15" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E21" s="15" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F21" s="15" t="n">
         <v>0</v>
@@ -1240,25 +1240,27 @@
       <c r="G21" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="H21" s="15" t="n">
-        <v/>
-      </c>
-      <c r="I21" s="15" t="n">
-        <v/>
+      <c r="H21" s="19" t="n">
+        <v>7.16</v>
+      </c>
+      <c r="I21" s="19" t="n">
+        <v>9.75</v>
       </c>
       <c r="J21" s="17" t="inlineStr">
         <is>
-          <t>한국경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 한국경제 헤드라인 언급 / 매일경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K21" s="17" t="n">
-        <v/>
+          <t>중요공시 1건 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K21" s="17" t="inlineStr">
+        <is>
+          <t>공시</t>
+        </is>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
       <c r="A22" s="15" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B22" s="15" t="n">
@@ -1266,14 +1268,14 @@
       </c>
       <c r="C22" s="16" t="inlineStr">
         <is>
-          <t>제약</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="D22" s="15" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E22" s="15" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F22" s="15" t="n">
         <v>0</v>
@@ -1281,15 +1283,15 @@
       <c r="G22" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="H22" s="15" t="n">
-        <v/>
-      </c>
-      <c r="I22" s="15" t="n">
-        <v/>
+      <c r="H22" s="19" t="n">
+        <v>3.41</v>
+      </c>
+      <c r="I22" s="19" t="n">
+        <v>7.74</v>
       </c>
       <c r="J22" s="17" t="inlineStr">
         <is>
-          <t>네이버뉴스 헤드라인 언급 / 네이버뉴스 헤드라인 언급 / 네이버뉴스 헤드라인 언급 / 네이버뉴스 기사 언급 / 매일경제 기사 언급</t>
+          <t>매일경제 기사 언급 / 한국경제 헤드라인 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 기사 언급 / 매일경제 헤드라인 언급</t>
         </is>
       </c>
       <c r="K22" s="17" t="inlineStr">
@@ -1301,7 +1303,7 @@
     <row r="23" ht="18" customHeight="1">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B23" s="15" t="n">
@@ -1309,14 +1311,14 @@
       </c>
       <c r="C23" s="16" t="inlineStr">
         <is>
-          <t>전기차</t>
+          <t>바이오</t>
         </is>
       </c>
       <c r="D23" s="15" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E23" s="15" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F23" s="15" t="n">
         <v>0</v>
@@ -1332,7 +1334,7 @@
       </c>
       <c r="J23" s="17" t="inlineStr">
         <is>
-          <t>매일경제 기사 언급 / 매일경제 헤드라인 언급 / 네이버뉴스 기사 언급 / 매일경제 기사 언급 / 매일경제 헤드라인 언급</t>
+          <t>네이버뉴스 기사 언급 / 네이버뉴스 헤드라인 언급 / 네이버뉴스 헤드라인 언급 / 매일경제 헤드라인 언급 / 네이버뉴스 기사 언급</t>
         </is>
       </c>
       <c r="K23" s="17" t="inlineStr">
@@ -1344,7 +1346,7 @@
     <row r="24" ht="18" customHeight="1">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B24" s="15" t="n">
@@ -1352,14 +1354,14 @@
       </c>
       <c r="C24" s="16" t="inlineStr">
         <is>
-          <t>현대차</t>
+          <t>LG</t>
         </is>
       </c>
       <c r="D24" s="15" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E24" s="15" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F24" s="15" t="n">
         <v>0</v>
@@ -1367,15 +1369,15 @@
       <c r="G24" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="H24" s="19" t="n">
-        <v>3.43</v>
+      <c r="H24" s="18" t="n">
+        <v>-3.47</v>
       </c>
       <c r="I24" s="18" t="n">
-        <v>-14.46</v>
+        <v>-1.32</v>
       </c>
       <c r="J24" s="17" t="inlineStr">
         <is>
-          <t>매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 네이버뉴스 헤드라인 언급</t>
+          <t>한국경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 한국경제 헤드라인 언급 / 네이버뉴스 헤드라인 언급</t>
         </is>
       </c>
       <c r="K24" s="17" t="inlineStr">
@@ -1387,7 +1389,7 @@
     <row r="25" ht="18" customHeight="1">
       <c r="A25" s="15" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B25" s="15" t="n">
@@ -1395,14 +1397,14 @@
       </c>
       <c r="C25" s="16" t="inlineStr">
         <is>
-          <t>삼호개발</t>
+          <t>철강</t>
         </is>
       </c>
       <c r="D25" s="15" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E25" s="15" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="F25" s="15" t="n">
         <v>0</v>
@@ -1410,27 +1412,27 @@
       <c r="G25" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="H25" s="18" t="n">
-        <v>-2.17</v>
-      </c>
-      <c r="I25" s="19" t="n">
-        <v>17.02</v>
+      <c r="H25" s="15" t="n">
+        <v/>
+      </c>
+      <c r="I25" s="15" t="n">
+        <v/>
       </c>
       <c r="J25" s="17" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +208% / 중요공시 3건 / 매일경제 헤드라인 언급</t>
+          <t>매일경제 헤드라인 언급 / 네이버뉴스 헤드라인 언급 / 네이버뉴스 헤드라인 언급 / 한국경제 헤드라인 언급 / 네이버뉴스 기사 언급</t>
         </is>
       </c>
       <c r="K25" s="17" t="inlineStr">
         <is>
-          <t>공시, 네이버</t>
+          <t>네이버</t>
         </is>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
       <c r="A26" s="15" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B26" s="15" t="n">
@@ -1438,14 +1440,14 @@
       </c>
       <c r="C26" s="16" t="inlineStr">
         <is>
-          <t>LG화학</t>
+          <t>에코프로비엠</t>
         </is>
       </c>
       <c r="D26" s="15" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E26" s="15" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F26" s="15" t="n">
         <v>0</v>
@@ -1453,25 +1455,27 @@
       <c r="G26" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="H26" s="19" t="n">
-        <v>13.65</v>
+      <c r="H26" s="18" t="n">
+        <v>-7.77</v>
       </c>
       <c r="I26" s="18" t="n">
-        <v>-4.64</v>
+        <v>-5.57</v>
       </c>
       <c r="J26" s="17" t="inlineStr">
         <is>
-          <t>매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K26" s="17" t="n">
-        <v/>
+          <t>중요공시 2건 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K26" s="17" t="inlineStr">
+        <is>
+          <t>공시</t>
+        </is>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
       <c r="A27" s="15" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B27" s="15" t="n">
@@ -1479,14 +1483,14 @@
       </c>
       <c r="C27" s="16" t="inlineStr">
         <is>
-          <t>원전</t>
+          <t>제약</t>
         </is>
       </c>
       <c r="D27" s="15" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E27" s="15" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F27" s="15" t="n">
         <v>0</v>
@@ -1502,17 +1506,19 @@
       </c>
       <c r="J27" s="17" t="inlineStr">
         <is>
-          <t>매일경제 헤드라인 언급 / 한국경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K27" s="17" t="n">
-        <v/>
+          <t>네이버뉴스 헤드라인 언급 / 매일경제 헤드라인 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 기사 언급</t>
+        </is>
+      </c>
+      <c r="K27" s="17" t="inlineStr">
+        <is>
+          <t>네이버</t>
+        </is>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
       <c r="A28" s="15" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B28" s="15" t="n">
@@ -1520,42 +1526,42 @@
       </c>
       <c r="C28" s="16" t="inlineStr">
         <is>
-          <t>성호전자</t>
+          <t>KT</t>
         </is>
       </c>
       <c r="D28" s="15" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E28" s="15" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="F28" s="15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G28" s="15" t="n">
-        <v>3</v>
-      </c>
-      <c r="H28" s="18" t="n">
-        <v>-1.56</v>
-      </c>
-      <c r="I28" s="18" t="n">
-        <v>-22.9</v>
+        <v>0</v>
+      </c>
+      <c r="H28" s="19" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="I28" s="19" t="n">
+        <v>0.95</v>
       </c>
       <c r="J28" s="17" t="inlineStr">
         <is>
-          <t>중요공시 3건 / 중요공시 3일 +200% / 중요공시 7일 +200%</t>
+          <t>Google 급상승 검색어 등장 (US) / 매일경제 헤드라인 언급 / 매일경제 기사 언급</t>
         </is>
       </c>
       <c r="K28" s="17" t="inlineStr">
         <is>
-          <t>공시</t>
+          <t>Google</t>
         </is>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
       <c r="A29" s="15" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B29" s="15" t="n">
@@ -1563,42 +1569,40 @@
       </c>
       <c r="C29" s="16" t="inlineStr">
         <is>
-          <t>스피어</t>
+          <t>LG전자</t>
         </is>
       </c>
       <c r="D29" s="15" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E29" s="15" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="F29" s="15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G29" s="15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H29" s="19" t="n">
-        <v>17.63</v>
-      </c>
-      <c r="I29" s="18" t="n">
-        <v>-8.130000000000001</v>
+        <v>3.2</v>
+      </c>
+      <c r="I29" s="19" t="n">
+        <v>0.5</v>
       </c>
       <c r="J29" s="17" t="inlineStr">
         <is>
-          <t>중요공시 7건 / 중요공시 3일 +133% / 중요공시 7일 +250%</t>
-        </is>
-      </c>
-      <c r="K29" s="17" t="inlineStr">
-        <is>
-          <t>공시</t>
-        </is>
+          <t>한국경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K29" s="17" t="n">
+        <v/>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
       <c r="A30" s="15" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B30" s="15" t="n">
@@ -1606,85 +1610,83 @@
       </c>
       <c r="C30" s="16" t="inlineStr">
         <is>
-          <t>파두</t>
+          <t>전기차</t>
         </is>
       </c>
       <c r="D30" s="15" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E30" s="15" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="F30" s="15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G30" s="15" t="n">
-        <v>3</v>
-      </c>
-      <c r="H30" s="19" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="I30" s="18" t="n">
-        <v>-26.06</v>
+        <v>0</v>
+      </c>
+      <c r="H30" s="15" t="n">
+        <v/>
+      </c>
+      <c r="I30" s="15" t="n">
+        <v/>
       </c>
       <c r="J30" s="17" t="inlineStr">
         <is>
-          <t>중요공시 3건 / 중요공시 3일 +200% / 중요공시 7일 +50%</t>
-        </is>
-      </c>
-      <c r="K30" s="17" t="inlineStr">
+          <t>매일경제 헤드라인 언급 / 한국경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K30" s="17" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="31" ht="18" customHeight="1">
+      <c r="A31" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B31" s="15" t="n">
+        <v>18</v>
+      </c>
+      <c r="C31" s="16" t="inlineStr">
+        <is>
+          <t>대한항공</t>
+        </is>
+      </c>
+      <c r="D31" s="15" t="n">
+        <v>7</v>
+      </c>
+      <c r="E31" s="15" t="n">
+        <v>7</v>
+      </c>
+      <c r="F31" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" s="18" t="n">
+        <v>-2.82</v>
+      </c>
+      <c r="I31" s="19" t="n">
+        <v>6.37</v>
+      </c>
+      <c r="J31" s="17" t="inlineStr">
+        <is>
+          <t>중요공시 3건 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K31" s="17" t="inlineStr">
         <is>
           <t>공시</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="18" customHeight="1">
-      <c r="A31" s="20" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="B31" s="20" t="n">
-        <v>18</v>
-      </c>
-      <c r="C31" s="21" t="inlineStr">
-        <is>
-          <t>아크솔루션스</t>
-        </is>
-      </c>
-      <c r="D31" s="20" t="n">
-        <v>6</v>
-      </c>
-      <c r="E31" s="20" t="n">
-        <v>6</v>
-      </c>
-      <c r="F31" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G31" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H31" s="22" t="n">
-        <v>-97.40000000000001</v>
-      </c>
-      <c r="I31" s="22" t="n">
-        <v>-97.40000000000001</v>
-      </c>
-      <c r="J31" s="23" t="inlineStr">
-        <is>
-          <t>네이버 검색 당일 +197% / 중요공시 3건</t>
-        </is>
-      </c>
-      <c r="K31" s="23" t="inlineStr">
-        <is>
-          <t>공시, 네이버</t>
         </is>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
       <c r="A32" s="20" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B32" s="20" t="n">
@@ -1692,42 +1694,40 @@
       </c>
       <c r="C32" s="21" t="inlineStr">
         <is>
-          <t>뉴인텍</t>
+          <t>스트라드비젼</t>
         </is>
       </c>
       <c r="D32" s="20" t="n">
         <v>6</v>
       </c>
       <c r="E32" s="20" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F32" s="20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G32" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H32" s="22" t="n">
-        <v>-20.41</v>
-      </c>
-      <c r="I32" s="24" t="n">
-        <v>17.04</v>
-      </c>
-      <c r="J32" s="23" t="inlineStr">
-        <is>
-          <t>네이버 검색 당일 +181% / 중요공시 2건 / 중요공시 3일 +100%</t>
-        </is>
-      </c>
-      <c r="K32" s="23" t="inlineStr">
-        <is>
-          <t>공시, 네이버</t>
-        </is>
+      <c r="H32" s="20" t="n">
+        <v/>
+      </c>
+      <c r="I32" s="20" t="n">
+        <v/>
+      </c>
+      <c r="J32" s="22" t="inlineStr">
+        <is>
+          <t>매일경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K32" s="22" t="n">
+        <v/>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
       <c r="A33" s="20" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B33" s="20" t="n">
@@ -1735,42 +1735,42 @@
       </c>
       <c r="C33" s="21" t="inlineStr">
         <is>
-          <t>앱튼</t>
+          <t>모바일어플라이언스</t>
         </is>
       </c>
       <c r="D33" s="20" t="n">
         <v>6</v>
       </c>
       <c r="E33" s="20" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F33" s="20" t="n">
         <v>0</v>
       </c>
       <c r="G33" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H33" s="24" t="n">
-        <v>29.98</v>
-      </c>
-      <c r="I33" s="24" t="n">
-        <v>109.15</v>
-      </c>
-      <c r="J33" s="23" t="inlineStr">
-        <is>
-          <t>네이버 검색 당일 +138% / 중요공시 5건</t>
-        </is>
-      </c>
-      <c r="K33" s="23" t="inlineStr">
-        <is>
-          <t>공시, 네이버</t>
+        <v>3</v>
+      </c>
+      <c r="H33" s="23" t="n">
+        <v>29.9</v>
+      </c>
+      <c r="I33" s="23" t="n">
+        <v>17.76</v>
+      </c>
+      <c r="J33" s="22" t="inlineStr">
+        <is>
+          <t>중요공시 3건 / 중요공시 7일 +200%</t>
+        </is>
+      </c>
+      <c r="K33" s="22" t="inlineStr">
+        <is>
+          <t>공시</t>
         </is>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
       <c r="A34" s="20" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B34" s="20" t="n">
@@ -1778,40 +1778,42 @@
       </c>
       <c r="C34" s="21" t="inlineStr">
         <is>
-          <t>원익IPS</t>
+          <t>성호전자</t>
         </is>
       </c>
       <c r="D34" s="20" t="n">
         <v>6</v>
       </c>
       <c r="E34" s="20" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F34" s="20" t="n">
         <v>0</v>
       </c>
       <c r="G34" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H34" s="22" t="n">
-        <v>-2.93</v>
-      </c>
-      <c r="I34" s="22" t="n">
-        <v>-7.83</v>
-      </c>
-      <c r="J34" s="23" t="inlineStr">
-        <is>
-          <t>한국경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K34" s="23" t="n">
-        <v/>
+        <v>3</v>
+      </c>
+      <c r="H34" s="23" t="n">
+        <v>4.22</v>
+      </c>
+      <c r="I34" s="24" t="n">
+        <v>-5.57</v>
+      </c>
+      <c r="J34" s="22" t="inlineStr">
+        <is>
+          <t>중요공시 3건 / 중요공시 7일 +200%</t>
+        </is>
+      </c>
+      <c r="K34" s="22" t="inlineStr">
+        <is>
+          <t>공시</t>
+        </is>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
       <c r="A35" s="20" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B35" s="20" t="n">
@@ -1819,40 +1821,42 @@
       </c>
       <c r="C35" s="21" t="inlineStr">
         <is>
-          <t>한화생명</t>
+          <t>스피어</t>
         </is>
       </c>
       <c r="D35" s="20" t="n">
         <v>6</v>
       </c>
       <c r="E35" s="20" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F35" s="20" t="n">
         <v>0</v>
       </c>
       <c r="G35" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H35" s="24" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="I35" s="22" t="n">
-        <v>-9.199999999999999</v>
-      </c>
-      <c r="J35" s="23" t="inlineStr">
-        <is>
-          <t>매일경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K35" s="23" t="n">
-        <v/>
+        <v>3</v>
+      </c>
+      <c r="H35" s="23" t="n">
+        <v>14.74</v>
+      </c>
+      <c r="I35" s="23" t="n">
+        <v>17.51</v>
+      </c>
+      <c r="J35" s="22" t="inlineStr">
+        <is>
+          <t>중요공시 7건 / 중요공시 7일 +250%</t>
+        </is>
+      </c>
+      <c r="K35" s="22" t="inlineStr">
+        <is>
+          <t>공시</t>
+        </is>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
       <c r="A36" s="20" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B36" s="20" t="n">
@@ -1860,7 +1864,7 @@
       </c>
       <c r="C36" s="21" t="inlineStr">
         <is>
-          <t>차바이오텍</t>
+          <t>파두</t>
         </is>
       </c>
       <c r="D36" s="20" t="n">
@@ -1875,18 +1879,18 @@
       <c r="G36" s="20" t="n">
         <v>3</v>
       </c>
-      <c r="H36" s="24" t="n">
-        <v>10.78</v>
+      <c r="H36" s="23" t="n">
+        <v>2.1</v>
       </c>
       <c r="I36" s="24" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="J36" s="23" t="inlineStr">
-        <is>
-          <t>중요공시 4건 / 중요공시 7일 +300%</t>
-        </is>
-      </c>
-      <c r="K36" s="23" t="inlineStr">
+        <v>-2.56</v>
+      </c>
+      <c r="J36" s="22" t="inlineStr">
+        <is>
+          <t>중요공시 4건 / 중요공시 7일 +100%</t>
+        </is>
+      </c>
+      <c r="K36" s="22" t="inlineStr">
         <is>
           <t>공시</t>
         </is>
@@ -1895,7 +1899,7 @@
     <row r="37" ht="18" customHeight="1">
       <c r="A37" s="20" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B37" s="20" t="n">
@@ -1903,7 +1907,7 @@
       </c>
       <c r="C37" s="21" t="inlineStr">
         <is>
-          <t>페니트리움바이오</t>
+          <t>차바이오텍</t>
         </is>
       </c>
       <c r="D37" s="20" t="n">
@@ -1919,17 +1923,17 @@
         <v>3</v>
       </c>
       <c r="H37" s="24" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="I37" s="22" t="n">
-        <v>-7.21</v>
-      </c>
-      <c r="J37" s="23" t="inlineStr">
-        <is>
-          <t>중요공시 3건 / 중요공시 7일 +200%</t>
-        </is>
-      </c>
-      <c r="K37" s="23" t="inlineStr">
+        <v>-6.46</v>
+      </c>
+      <c r="I37" s="24" t="n">
+        <v>-5.32</v>
+      </c>
+      <c r="J37" s="22" t="inlineStr">
+        <is>
+          <t>중요공시 4건 / 중요공시 7일 +300%</t>
+        </is>
+      </c>
+      <c r="K37" s="22" t="inlineStr">
         <is>
           <t>공시</t>
         </is>
@@ -1938,7 +1942,7 @@
     <row r="38" ht="18" customHeight="1">
       <c r="A38" s="20" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B38" s="20" t="n">
@@ -1946,40 +1950,42 @@
       </c>
       <c r="C38" s="21" t="inlineStr">
         <is>
-          <t>방산</t>
+          <t>HJ중공업</t>
         </is>
       </c>
       <c r="D38" s="20" t="n">
         <v>6</v>
       </c>
       <c r="E38" s="20" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F38" s="20" t="n">
         <v>0</v>
       </c>
       <c r="G38" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H38" s="20" t="n">
-        <v/>
-      </c>
-      <c r="I38" s="20" t="n">
-        <v/>
-      </c>
-      <c r="J38" s="23" t="inlineStr">
-        <is>
-          <t>매일경제 헤드라인 언급 / 매일경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K38" s="23" t="n">
-        <v/>
+        <v>3</v>
+      </c>
+      <c r="H38" s="24" t="n">
+        <v>-10.24</v>
+      </c>
+      <c r="I38" s="23" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="J38" s="22" t="inlineStr">
+        <is>
+          <t>중요공시 3건 / 중요공시 7일 +50%</t>
+        </is>
+      </c>
+      <c r="K38" s="22" t="inlineStr">
+        <is>
+          <t>공시</t>
+        </is>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
       <c r="A39" s="20" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B39" s="20" t="n">
@@ -1987,42 +1993,42 @@
       </c>
       <c r="C39" s="21" t="inlineStr">
         <is>
-          <t>소룩스</t>
+          <t>페니트리움바이오</t>
         </is>
       </c>
       <c r="D39" s="20" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E39" s="20" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F39" s="20" t="n">
         <v>0</v>
       </c>
       <c r="G39" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H39" s="22" t="n">
-        <v>-4.76</v>
+        <v>3</v>
+      </c>
+      <c r="H39" s="24" t="n">
+        <v>-1.54</v>
       </c>
       <c r="I39" s="24" t="n">
-        <v>18.99</v>
-      </c>
-      <c r="J39" s="23" t="inlineStr">
-        <is>
-          <t>네이버 검색 당일 +92% / 중요공시 3건</t>
-        </is>
-      </c>
-      <c r="K39" s="23" t="inlineStr">
-        <is>
-          <t>공시, 네이버</t>
+        <v>-2.74</v>
+      </c>
+      <c r="J39" s="22" t="inlineStr">
+        <is>
+          <t>중요공시 3건 / 중요공시 7일 +200%</t>
+        </is>
+      </c>
+      <c r="K39" s="22" t="inlineStr">
+        <is>
+          <t>공시</t>
         </is>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
       <c r="A40" s="20" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B40" s="20" t="n">
@@ -2030,42 +2036,40 @@
       </c>
       <c r="C40" s="21" t="inlineStr">
         <is>
-          <t>대한항공</t>
+          <t>DB</t>
         </is>
       </c>
       <c r="D40" s="20" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E40" s="20" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F40" s="20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G40" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H40" s="24" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="I40" s="24" t="n">
-        <v>4.81</v>
-      </c>
-      <c r="J40" s="23" t="inlineStr">
-        <is>
-          <t>중요공시 3건 / 중요공시 3일 +200%</t>
-        </is>
-      </c>
-      <c r="K40" s="23" t="inlineStr">
-        <is>
-          <t>공시</t>
-        </is>
+      <c r="H40" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="I40" s="23" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="J40" s="22" t="inlineStr">
+        <is>
+          <t>한국경제 헤드라인 언급 / 매일경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K40" s="22" t="n">
+        <v/>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
       <c r="A41" s="20" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B41" s="20" t="n">
@@ -2073,42 +2077,40 @@
       </c>
       <c r="C41" s="21" t="inlineStr">
         <is>
-          <t>남광토건</t>
+          <t>스테이블코인</t>
         </is>
       </c>
       <c r="D41" s="20" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E41" s="20" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F41" s="20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G41" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H41" s="24" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="I41" s="24" t="n">
-        <v>9.539999999999999</v>
-      </c>
-      <c r="J41" s="23" t="inlineStr">
-        <is>
-          <t>중요공시 3건 / 중요공시 3일 +50%</t>
-        </is>
-      </c>
-      <c r="K41" s="23" t="inlineStr">
-        <is>
-          <t>공시</t>
-        </is>
+      <c r="H41" s="20" t="n">
+        <v/>
+      </c>
+      <c r="I41" s="20" t="n">
+        <v/>
+      </c>
+      <c r="J41" s="22" t="inlineStr">
+        <is>
+          <t>매일경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K41" s="22" t="n">
+        <v/>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
       <c r="A42" s="20" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B42" s="20" t="n">
@@ -2116,7 +2118,7 @@
       </c>
       <c r="C42" s="21" t="inlineStr">
         <is>
-          <t>KB금융</t>
+          <t>아크솔루션스</t>
         </is>
       </c>
       <c r="D42" s="20" t="n">
@@ -2131,27 +2133,27 @@
       <c r="G42" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H42" s="24" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="I42" s="22" t="n">
-        <v>-2.1</v>
-      </c>
-      <c r="J42" s="23" t="inlineStr">
-        <is>
-          <t>중요공시 1건 / 한국경제 헤드라인 언급 / 네이버뉴스 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K42" s="23" t="inlineStr">
-        <is>
-          <t>공시, 네이버</t>
+      <c r="H42" s="23" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="I42" s="24" t="n">
+        <v>-97.38</v>
+      </c>
+      <c r="J42" s="22" t="inlineStr">
+        <is>
+          <t>네이버 검색 당일 +91% / 중요공시 3건</t>
+        </is>
+      </c>
+      <c r="K42" s="22" t="inlineStr">
+        <is>
+          <t>네이버, 공시</t>
         </is>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1">
       <c r="A43" s="20" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B43" s="20" t="n">
@@ -2159,7 +2161,7 @@
       </c>
       <c r="C43" s="21" t="inlineStr">
         <is>
-          <t>채비</t>
+          <t>KB금융</t>
         </is>
       </c>
       <c r="D43" s="20" t="n">
@@ -2174,18 +2176,18 @@
       <c r="G43" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H43" s="24" t="n">
-        <v>16.69</v>
-      </c>
-      <c r="I43" s="22" t="n">
-        <v>-3.89</v>
-      </c>
-      <c r="J43" s="23" t="inlineStr">
+      <c r="H43" s="23" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="I43" s="23" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="J43" s="22" t="inlineStr">
         <is>
           <t>중요공시 1건 / 매일경제 헤드라인 언급 / 매일경제 기사 언급</t>
         </is>
       </c>
-      <c r="K43" s="23" t="inlineStr">
+      <c r="K43" s="22" t="inlineStr">
         <is>
           <t>공시</t>
         </is>
@@ -2194,7 +2196,7 @@
     <row r="44" ht="18" customHeight="1">
       <c r="A44" s="20" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B44" s="20" t="n">
@@ -2202,7 +2204,7 @@
       </c>
       <c r="C44" s="21" t="inlineStr">
         <is>
-          <t>기아</t>
+          <t>NH투자증권</t>
         </is>
       </c>
       <c r="D44" s="20" t="n">
@@ -2217,27 +2219,25 @@
       <c r="G44" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H44" s="24" t="n">
-        <v>3.92</v>
-      </c>
-      <c r="I44" s="22" t="n">
-        <v>-7.13</v>
-      </c>
-      <c r="J44" s="23" t="inlineStr">
-        <is>
-          <t>Google 급상승 검색어 등장 (KR)</t>
-        </is>
-      </c>
-      <c r="K44" s="23" t="inlineStr">
-        <is>
-          <t>Google</t>
-        </is>
+      <c r="H44" s="23" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="I44" s="23" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="J44" s="22" t="inlineStr">
+        <is>
+          <t>매일경제 기사 언급 / 한국경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K44" s="22" t="n">
+        <v/>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
       <c r="A45" s="20" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B45" s="20" t="n">
@@ -2245,14 +2245,14 @@
       </c>
       <c r="C45" s="21" t="inlineStr">
         <is>
-          <t>네이버</t>
+          <t>골프존홀딩스</t>
         </is>
       </c>
       <c r="D45" s="20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E45" s="20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F45" s="20" t="n">
         <v>0</v>
@@ -2260,25 +2260,27 @@
       <c r="G45" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H45" s="20" t="n">
-        <v/>
-      </c>
-      <c r="I45" s="20" t="n">
-        <v/>
-      </c>
-      <c r="J45" s="23" t="inlineStr">
-        <is>
-          <t>한국경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K45" s="23" t="n">
-        <v/>
+      <c r="H45" s="23" t="n">
+        <v>19.89</v>
+      </c>
+      <c r="I45" s="23" t="n">
+        <v>47.66</v>
+      </c>
+      <c r="J45" s="22" t="inlineStr">
+        <is>
+          <t>네이버 검색 당일 +369% / 중요공시 1건</t>
+        </is>
+      </c>
+      <c r="K45" s="22" t="inlineStr">
+        <is>
+          <t>네이버, 공시</t>
+        </is>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
       <c r="A46" s="20" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B46" s="20" t="n">
@@ -2286,42 +2288,42 @@
       </c>
       <c r="C46" s="21" t="inlineStr">
         <is>
-          <t>태양광</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="D46" s="20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E46" s="20" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F46" s="20" t="n">
         <v>0</v>
       </c>
       <c r="G46" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H46" s="20" t="n">
-        <v/>
-      </c>
-      <c r="I46" s="20" t="n">
-        <v/>
-      </c>
-      <c r="J46" s="23" t="inlineStr">
-        <is>
-          <t>네이버뉴스 헤드라인 언급 / 매일경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K46" s="23" t="inlineStr">
-        <is>
-          <t>네이버</t>
+        <v>3</v>
+      </c>
+      <c r="H46" s="24" t="n">
+        <v>-4.9</v>
+      </c>
+      <c r="I46" s="24" t="n">
+        <v>-2.79</v>
+      </c>
+      <c r="J46" s="22" t="inlineStr">
+        <is>
+          <t>중요공시 2건 / 중요공시 7일 +100%</t>
+        </is>
+      </c>
+      <c r="K46" s="22" t="inlineStr">
+        <is>
+          <t>공시</t>
         </is>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
       <c r="A47" s="20" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B47" s="20" t="n">
@@ -2329,40 +2331,42 @@
       </c>
       <c r="C47" s="21" t="inlineStr">
         <is>
-          <t>삼성전기</t>
+          <t>한화엔진</t>
         </is>
       </c>
       <c r="D47" s="20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E47" s="20" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F47" s="20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G47" s="20" t="n">
         <v>0</v>
       </c>
       <c r="H47" s="24" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="I47" s="22" t="n">
-        <v>-8.529999999999999</v>
-      </c>
-      <c r="J47" s="23" t="inlineStr">
-        <is>
-          <t>매일경제 기사 언급 / 한국경제 헤드라인 언급 / 매일경제 기사 언급</t>
-        </is>
-      </c>
-      <c r="K47" s="23" t="n">
-        <v/>
+        <v>-0.97</v>
+      </c>
+      <c r="I47" s="24" t="n">
+        <v>-4.67</v>
+      </c>
+      <c r="J47" s="22" t="inlineStr">
+        <is>
+          <t>중요공시 2건 / 중요공시 3일 +100% / 매일경제 기사 언급</t>
+        </is>
+      </c>
+      <c r="K47" s="22" t="inlineStr">
+        <is>
+          <t>공시</t>
+        </is>
       </c>
     </row>
     <row r="48" ht="18" customHeight="1">
       <c r="A48" s="20" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B48" s="20" t="n">
@@ -2370,7 +2374,7 @@
       </c>
       <c r="C48" s="21" t="inlineStr">
         <is>
-          <t>티이엠씨씨엔에스</t>
+          <t>CMG제약</t>
         </is>
       </c>
       <c r="D48" s="20" t="n">
@@ -2385,27 +2389,27 @@
       <c r="G48" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H48" s="22" t="n">
-        <v>-0.31</v>
-      </c>
-      <c r="I48" s="24" t="n">
-        <v>14.49</v>
-      </c>
-      <c r="J48" s="23" t="inlineStr">
-        <is>
-          <t>네이버 검색 당일 +524% / 중요공시 1건</t>
-        </is>
-      </c>
-      <c r="K48" s="23" t="inlineStr">
-        <is>
-          <t>공시, 네이버</t>
+      <c r="H48" s="24" t="n">
+        <v>-2.86</v>
+      </c>
+      <c r="I48" s="23" t="n">
+        <v>3.79</v>
+      </c>
+      <c r="J48" s="22" t="inlineStr">
+        <is>
+          <t>중요공시 1건 / 매일경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K48" s="22" t="inlineStr">
+        <is>
+          <t>공시</t>
         </is>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1">
       <c r="A49" s="20" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B49" s="20" t="n">
@@ -2413,7 +2417,7 @@
       </c>
       <c r="C49" s="21" t="inlineStr">
         <is>
-          <t>베셀</t>
+          <t>카카오뱅크</t>
         </is>
       </c>
       <c r="D49" s="20" t="n">
@@ -2429,26 +2433,26 @@
         <v>0</v>
       </c>
       <c r="H49" s="24" t="n">
-        <v>10.24</v>
-      </c>
-      <c r="I49" s="24" t="n">
-        <v>13.91</v>
-      </c>
-      <c r="J49" s="23" t="inlineStr">
-        <is>
-          <t>네이버 검색 당일 +244% / 중요공시 2건</t>
-        </is>
-      </c>
-      <c r="K49" s="23" t="inlineStr">
-        <is>
-          <t>공시, 네이버</t>
+        <v>-1.18</v>
+      </c>
+      <c r="I49" s="23" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="J49" s="22" t="inlineStr">
+        <is>
+          <t>중요공시 1건 / 매일경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K49" s="22" t="inlineStr">
+        <is>
+          <t>공시</t>
         </is>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
       <c r="A50" s="20" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B50" s="20" t="n">
@@ -2456,7 +2460,7 @@
       </c>
       <c r="C50" s="21" t="inlineStr">
         <is>
-          <t>다스코</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="D50" s="20" t="n">
@@ -2472,448 +2476,452 @@
         <v>0</v>
       </c>
       <c r="H50" s="24" t="n">
-        <v>29.99</v>
-      </c>
-      <c r="I50" s="24" t="n">
-        <v>52.65</v>
-      </c>
-      <c r="J50" s="23" t="inlineStr">
-        <is>
-          <t>네이버 검색 당일 +159% / 중요공시 1건</t>
-        </is>
-      </c>
-      <c r="K50" s="23" t="inlineStr">
-        <is>
-          <t>공시, 네이버</t>
-        </is>
+        <v>-2.19</v>
+      </c>
+      <c r="I50" s="23" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="J50" s="22" t="inlineStr">
+        <is>
+          <t>매일경제 헤드라인 언급 / 매일경제 기사 언급</t>
+        </is>
+      </c>
+      <c r="K50" s="22" t="n">
+        <v/>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
-      <c r="A51" s="20" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="B51" s="20" t="n">
+      <c r="A51" s="25" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B51" s="25" t="n">
         <v>38</v>
       </c>
-      <c r="C51" s="21" t="inlineStr">
-        <is>
-          <t>카카오</t>
-        </is>
-      </c>
-      <c r="D51" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="E51" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="F51" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G51" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H51" s="24" t="n">
-        <v>8.140000000000001</v>
-      </c>
-      <c r="I51" s="22" t="n">
-        <v>-2.58</v>
-      </c>
-      <c r="J51" s="23" t="inlineStr">
-        <is>
-          <t>매일경제 헤드라인 언급 / 매일경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K51" s="23" t="n">
+      <c r="C51" s="26" t="inlineStr">
+        <is>
+          <t>져스텍</t>
+        </is>
+      </c>
+      <c r="D51" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="E51" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="F51" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G51" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H51" s="27" t="n">
+        <v>-5.08</v>
+      </c>
+      <c r="I51" s="27" t="n">
+        <v>-5.08</v>
+      </c>
+      <c r="J51" s="28" t="inlineStr">
+        <is>
+          <t>네이버 검색 당일 +476%</t>
+        </is>
+      </c>
+      <c r="K51" s="28" t="inlineStr">
+        <is>
+          <t>네이버</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="18" customHeight="1">
+      <c r="A52" s="25" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B52" s="25" t="n">
+        <v>39</v>
+      </c>
+      <c r="C52" s="26" t="inlineStr">
+        <is>
+          <t>앱튼</t>
+        </is>
+      </c>
+      <c r="D52" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="E52" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="F52" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G52" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H52" s="29" t="n">
+        <v>29.72</v>
+      </c>
+      <c r="I52" s="29" t="n">
+        <v>180.8</v>
+      </c>
+      <c r="J52" s="28" t="inlineStr">
+        <is>
+          <t>중요공시 5건</t>
+        </is>
+      </c>
+      <c r="K52" s="28" t="inlineStr">
+        <is>
+          <t>공시</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="18" customHeight="1">
+      <c r="A53" s="25" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B53" s="25" t="n">
+        <v>40</v>
+      </c>
+      <c r="C53" s="26" t="inlineStr">
+        <is>
+          <t>지니너스</t>
+        </is>
+      </c>
+      <c r="D53" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="E53" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="F53" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G53" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H53" s="29" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="I53" s="29" t="n">
+        <v>11.87</v>
+      </c>
+      <c r="J53" s="28" t="inlineStr">
+        <is>
+          <t>매일경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K53" s="28" t="n">
         <v/>
       </c>
     </row>
-    <row r="52" ht="18" customHeight="1">
-      <c r="A52" s="20" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="B52" s="20" t="n">
-        <v>39</v>
-      </c>
-      <c r="C52" s="21" t="inlineStr">
-        <is>
-          <t>LG전자</t>
-        </is>
-      </c>
-      <c r="D52" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="E52" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="F52" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G52" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H52" s="24" t="n">
-        <v>0.41</v>
-      </c>
-      <c r="I52" s="22" t="n">
-        <v>-13.54</v>
-      </c>
-      <c r="J52" s="23" t="inlineStr">
-        <is>
-          <t>매일경제 기사 언급 / 매일경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K52" s="23" t="n">
-        <v/>
-      </c>
-    </row>
-    <row r="53" ht="18" customHeight="1">
-      <c r="A53" s="20" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="B53" s="20" t="n">
-        <v>40</v>
-      </c>
-      <c r="C53" s="21" t="inlineStr">
-        <is>
-          <t>대우건설</t>
-        </is>
-      </c>
-      <c r="D53" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="E53" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="F53" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G53" s="20" t="n">
-        <v>3</v>
-      </c>
-      <c r="H53" s="24" t="n">
-        <v>8.91</v>
-      </c>
-      <c r="I53" s="22" t="n">
-        <v>-9.130000000000001</v>
-      </c>
-      <c r="J53" s="23" t="inlineStr">
-        <is>
-          <t>중요공시 2건 / 중요공시 7일 +100%</t>
-        </is>
-      </c>
-      <c r="K53" s="23" t="inlineStr">
+    <row r="54" ht="18" customHeight="1">
+      <c r="A54" s="25" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B54" s="25" t="n">
+        <v>41</v>
+      </c>
+      <c r="C54" s="26" t="inlineStr">
+        <is>
+          <t>우리금융지주</t>
+        </is>
+      </c>
+      <c r="D54" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="E54" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="F54" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G54" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H54" s="27" t="n">
+        <v>-0.34</v>
+      </c>
+      <c r="I54" s="27" t="n">
+        <v>-1.53</v>
+      </c>
+      <c r="J54" s="28" t="inlineStr">
+        <is>
+          <t>네이버뉴스 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K54" s="28" t="inlineStr">
+        <is>
+          <t>네이버</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="18" customHeight="1">
+      <c r="A55" s="25" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B55" s="25" t="n">
+        <v>42</v>
+      </c>
+      <c r="C55" s="26" t="inlineStr">
+        <is>
+          <t>SK스퀘어</t>
+        </is>
+      </c>
+      <c r="D55" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="E55" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="F55" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="G55" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H55" s="29" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="I55" s="27" t="n">
+        <v>-7.37</v>
+      </c>
+      <c r="J55" s="28" t="inlineStr">
+        <is>
+          <t>중요공시 2건 / 중요공시 3일 +100%</t>
+        </is>
+      </c>
+      <c r="K55" s="28" t="inlineStr">
         <is>
           <t>공시</t>
         </is>
       </c>
     </row>
-    <row r="54" ht="18" customHeight="1">
-      <c r="A54" s="20" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="B54" s="20" t="n">
-        <v>41</v>
-      </c>
-      <c r="C54" s="21" t="inlineStr">
-        <is>
-          <t>올릭스</t>
-        </is>
-      </c>
-      <c r="D54" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="E54" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="F54" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G54" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H54" s="24" t="n">
-        <v>24.22</v>
-      </c>
-      <c r="I54" s="24" t="n">
-        <v>27.93</v>
-      </c>
-      <c r="J54" s="23" t="inlineStr">
-        <is>
-          <t>중요공시 2건 / 매일경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K54" s="23" t="inlineStr">
+    <row r="56" ht="18" customHeight="1">
+      <c r="A56" s="25" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B56" s="25" t="n">
+        <v>43</v>
+      </c>
+      <c r="C56" s="26" t="inlineStr">
+        <is>
+          <t>에이프릴바이오</t>
+        </is>
+      </c>
+      <c r="D56" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="E56" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="F56" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G56" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H56" s="27" t="n">
+        <v>-4.81</v>
+      </c>
+      <c r="I56" s="29" t="n">
+        <v>18.05</v>
+      </c>
+      <c r="J56" s="28" t="inlineStr">
+        <is>
+          <t>중요공시 5건</t>
+        </is>
+      </c>
+      <c r="K56" s="28" t="inlineStr">
         <is>
           <t>공시</t>
         </is>
       </c>
     </row>
-    <row r="55" ht="18" customHeight="1">
-      <c r="A55" s="20" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="B55" s="20" t="n">
-        <v>42</v>
-      </c>
-      <c r="C55" s="21" t="inlineStr">
-        <is>
-          <t>시너지이노베이션</t>
-        </is>
-      </c>
-      <c r="D55" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="E55" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="F55" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G55" s="20" t="n">
-        <v>3</v>
-      </c>
-      <c r="H55" s="24" t="n">
-        <v>7.34</v>
-      </c>
-      <c r="I55" s="24" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="J55" s="23" t="inlineStr">
-        <is>
-          <t>중요공시 2건 / 중요공시 7일 +100%</t>
-        </is>
-      </c>
-      <c r="K55" s="23" t="inlineStr">
+    <row r="57" ht="18" customHeight="1">
+      <c r="A57" s="25" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B57" s="25" t="n">
+        <v>44</v>
+      </c>
+      <c r="C57" s="26" t="inlineStr">
+        <is>
+          <t>CSA 코스믹</t>
+        </is>
+      </c>
+      <c r="D57" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="E57" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="F57" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G57" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H57" s="27" t="n">
+        <v>-1.67</v>
+      </c>
+      <c r="I57" s="27" t="n">
+        <v>-7.81</v>
+      </c>
+      <c r="J57" s="28" t="inlineStr">
+        <is>
+          <t>중요공시 4건</t>
+        </is>
+      </c>
+      <c r="K57" s="28" t="inlineStr">
         <is>
           <t>공시</t>
         </is>
       </c>
     </row>
-    <row r="56" ht="18" customHeight="1">
-      <c r="A56" s="20" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="B56" s="20" t="n">
-        <v>43</v>
-      </c>
-      <c r="C56" s="21" t="inlineStr">
-        <is>
-          <t>모바일어플라이언스</t>
-        </is>
-      </c>
-      <c r="D56" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="E56" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="F56" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G56" s="20" t="n">
-        <v>3</v>
-      </c>
-      <c r="H56" s="22" t="n">
-        <v>-3.64</v>
-      </c>
-      <c r="I56" s="22" t="n">
-        <v>-13.13</v>
-      </c>
-      <c r="J56" s="23" t="inlineStr">
-        <is>
-          <t>중요공시 2건 / 중요공시 7일 +100%</t>
-        </is>
-      </c>
-      <c r="K56" s="23" t="inlineStr">
+    <row r="58" ht="18" customHeight="1">
+      <c r="A58" s="25" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B58" s="25" t="n">
+        <v>45</v>
+      </c>
+      <c r="C58" s="26" t="inlineStr">
+        <is>
+          <t>플리토</t>
+        </is>
+      </c>
+      <c r="D58" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="E58" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="F58" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G58" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H58" s="29" t="n">
+        <v>5.48</v>
+      </c>
+      <c r="I58" s="29" t="n">
+        <v>24.19</v>
+      </c>
+      <c r="J58" s="28" t="inlineStr">
+        <is>
+          <t>중요공시 4건</t>
+        </is>
+      </c>
+      <c r="K58" s="28" t="inlineStr">
         <is>
           <t>공시</t>
         </is>
       </c>
     </row>
-    <row r="57" ht="18" customHeight="1">
-      <c r="A57" s="20" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="B57" s="20" t="n">
-        <v>44</v>
-      </c>
-      <c r="C57" s="21" t="inlineStr">
-        <is>
-          <t>에임드바이오</t>
-        </is>
-      </c>
-      <c r="D57" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="E57" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="F57" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G57" s="20" t="n">
-        <v>3</v>
-      </c>
-      <c r="H57" s="24" t="n">
-        <v>16.04</v>
-      </c>
-      <c r="I57" s="24" t="n">
-        <v>6.11</v>
-      </c>
-      <c r="J57" s="23" t="inlineStr">
-        <is>
-          <t>중요공시 2건 / 중요공시 7일 +100%</t>
-        </is>
-      </c>
-      <c r="K57" s="23" t="inlineStr">
+    <row r="59" ht="18" customHeight="1">
+      <c r="A59" s="25" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B59" s="25" t="n">
+        <v>46</v>
+      </c>
+      <c r="C59" s="26" t="inlineStr">
+        <is>
+          <t>삼호개발</t>
+        </is>
+      </c>
+      <c r="D59" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="E59" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="F59" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G59" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H59" s="27" t="n">
+        <v>-9.699999999999999</v>
+      </c>
+      <c r="I59" s="29" t="n">
+        <v>7.24</v>
+      </c>
+      <c r="J59" s="28" t="inlineStr">
+        <is>
+          <t>중요공시 3건</t>
+        </is>
+      </c>
+      <c r="K59" s="28" t="inlineStr">
         <is>
           <t>공시</t>
         </is>
       </c>
     </row>
-    <row r="58" ht="18" customHeight="1">
-      <c r="A58" s="20" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="B58" s="20" t="n">
-        <v>45</v>
-      </c>
-      <c r="C58" s="21" t="inlineStr">
-        <is>
-          <t>현대로템</t>
-        </is>
-      </c>
-      <c r="D58" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="E58" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="F58" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G58" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H58" s="24" t="n">
-        <v>8.890000000000001</v>
-      </c>
-      <c r="I58" s="22" t="n">
-        <v>-9.140000000000001</v>
-      </c>
-      <c r="J58" s="23" t="inlineStr">
-        <is>
-          <t>중요공시 1건 / 매일경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K58" s="23" t="inlineStr">
+    <row r="60" ht="18" customHeight="1">
+      <c r="A60" s="25" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B60" s="25" t="n">
+        <v>47</v>
+      </c>
+      <c r="C60" s="26" t="inlineStr">
+        <is>
+          <t>아모텍</t>
+        </is>
+      </c>
+      <c r="D60" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="E60" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="F60" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G60" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H60" s="27" t="n">
+        <v>-3.35</v>
+      </c>
+      <c r="I60" s="27" t="n">
+        <v>-17.97</v>
+      </c>
+      <c r="J60" s="28" t="inlineStr">
+        <is>
+          <t>중요공시 3건</t>
+        </is>
+      </c>
+      <c r="K60" s="28" t="inlineStr">
         <is>
           <t>공시</t>
         </is>
-      </c>
-    </row>
-    <row r="59" ht="18" customHeight="1">
-      <c r="A59" s="20" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="B59" s="20" t="n">
-        <v>46</v>
-      </c>
-      <c r="C59" s="21" t="inlineStr">
-        <is>
-          <t>GS</t>
-        </is>
-      </c>
-      <c r="D59" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="E59" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="F59" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G59" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H59" s="24" t="n">
-        <v>7.68</v>
-      </c>
-      <c r="I59" s="22" t="n">
-        <v>-0.44</v>
-      </c>
-      <c r="J59" s="23" t="inlineStr">
-        <is>
-          <t>한국경제 헤드라인 언급 / 매일경제 기사 언급</t>
-        </is>
-      </c>
-      <c r="K59" s="23" t="n">
-        <v/>
-      </c>
-    </row>
-    <row r="60" ht="18" customHeight="1">
-      <c r="A60" s="20" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="B60" s="20" t="n">
-        <v>47</v>
-      </c>
-      <c r="C60" s="21" t="inlineStr">
-        <is>
-          <t>하이브</t>
-        </is>
-      </c>
-      <c r="D60" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="E60" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="F60" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G60" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H60" s="24" t="n">
-        <v>9.84</v>
-      </c>
-      <c r="I60" s="22" t="n">
-        <v>-8.31</v>
-      </c>
-      <c r="J60" s="23" t="inlineStr">
-        <is>
-          <t>매일경제 헤드라인 언급 / 매일경제 기사 언급</t>
-        </is>
-      </c>
-      <c r="K60" s="23" t="n">
-        <v/>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
       <c r="A61" s="25" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B61" s="25" t="n">
@@ -2921,7 +2929,7 @@
       </c>
       <c r="C61" s="26" t="inlineStr">
         <is>
-          <t>프로브잇</t>
+          <t>대명에너지</t>
         </is>
       </c>
       <c r="D61" s="25" t="n">
@@ -2937,26 +2945,26 @@
         <v>0</v>
       </c>
       <c r="H61" s="27" t="n">
-        <v>-44.44</v>
-      </c>
-      <c r="I61" s="27" t="n">
-        <v>-72.22</v>
+        <v>-9.93</v>
+      </c>
+      <c r="I61" s="29" t="n">
+        <v>25.67</v>
       </c>
       <c r="J61" s="28" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +2031%</t>
+          <t>중요공시 3건</t>
         </is>
       </c>
       <c r="K61" s="28" t="inlineStr">
         <is>
-          <t>네이버</t>
+          <t>공시</t>
         </is>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1">
       <c r="A62" s="25" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B62" s="25" t="n">
@@ -2964,7 +2972,7 @@
       </c>
       <c r="C62" s="26" t="inlineStr">
         <is>
-          <t>광주신세계</t>
+          <t>클래시스</t>
         </is>
       </c>
       <c r="D62" s="25" t="n">
@@ -2980,26 +2988,26 @@
         <v>0</v>
       </c>
       <c r="H62" s="27" t="n">
-        <v>-4.73</v>
+        <v>-5.57</v>
       </c>
       <c r="I62" s="29" t="n">
-        <v>44.83</v>
+        <v>6.27</v>
       </c>
       <c r="J62" s="28" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +1608%</t>
+          <t>중요공시 3건</t>
         </is>
       </c>
       <c r="K62" s="28" t="inlineStr">
         <is>
-          <t>네이버</t>
+          <t>공시</t>
         </is>
       </c>
     </row>
     <row r="63" ht="18" customHeight="1">
       <c r="A63" s="25" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B63" s="25" t="n">
@@ -3007,35 +3015,35 @@
       </c>
       <c r="C63" s="26" t="inlineStr">
         <is>
-          <t>NPX</t>
+          <t>뉴인텍</t>
         </is>
       </c>
       <c r="D63" s="25" t="n">
         <v>3</v>
       </c>
       <c r="E63" s="25" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F63" s="25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G63" s="25" t="n">
         <v>0</v>
       </c>
       <c r="H63" s="27" t="n">
-        <v>-49.52</v>
-      </c>
-      <c r="I63" s="27" t="n">
-        <v>-98.69</v>
+        <v>-13.78</v>
+      </c>
+      <c r="I63" s="29" t="n">
+        <v>8.859999999999999</v>
       </c>
       <c r="J63" s="28" t="inlineStr">
         <is>
-          <t>네이버 검색 당일 +1347%</t>
+          <t>중요공시 2건 / 중요공시 3일 +100%</t>
         </is>
       </c>
       <c r="K63" s="28" t="inlineStr">
         <is>
-          <t>네이버</t>
+          <t>공시</t>
         </is>
       </c>
     </row>
@@ -3132,22 +3140,22 @@
         <v>1</v>
       </c>
       <c r="C3" s="25" t="n">
-        <v>121</v>
+        <v>108</v>
       </c>
       <c r="D3" s="25" t="n">
-        <v>121</v>
+        <v>108</v>
       </c>
       <c r="E3" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F3" s="25" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G3" s="25" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="H3" s="25" t="n"/>
@@ -3156,108 +3164,108 @@
     <row r="4" ht="18" customHeight="1">
       <c r="A4" s="26" t="inlineStr">
         <is>
-          <t>SK</t>
+          <t>로봇</t>
         </is>
       </c>
       <c r="B4" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C4" s="25" t="n">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="D4" s="25" t="n">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="E4" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F4" s="25" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G4" s="25" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="H4" s="27" t="n">
-        <v>-3.68</v>
-      </c>
-      <c r="I4" s="29" t="n">
-        <v>7.53</v>
-      </c>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="H4" s="25" t="n"/>
+      <c r="I4" s="25" t="n"/>
     </row>
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="26" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>현대차</t>
         </is>
       </c>
       <c r="B5" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C5" s="25" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D5" s="25" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="E5" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F5" s="25" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G5" s="25" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="H5" s="27" t="n">
-        <v>-4.86</v>
+        <v>-0.4</v>
       </c>
       <c r="I5" s="27" t="n">
-        <v>-8.630000000000001</v>
+        <v>-3.13</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
       <c r="A6" s="26" t="inlineStr">
         <is>
-          <t>인공지능</t>
+          <t>SK</t>
         </is>
       </c>
       <c r="B6" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C6" s="25" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D6" s="25" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E6" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F6" s="25" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G6" s="25" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="H6" s="25" t="n"/>
-      <c r="I6" s="25" t="n"/>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="H6" s="29" t="n">
+        <v>6.24</v>
+      </c>
+      <c r="I6" s="29" t="n">
+        <v>18.3</v>
+      </c>
     </row>
     <row r="7" ht="18" customHeight="1">
       <c r="A7" s="26" t="inlineStr">
         <is>
-          <t>바이오</t>
+          <t>인공지능</t>
         </is>
       </c>
       <c r="B7" s="25" t="n">
@@ -3274,12 +3282,12 @@
       </c>
       <c r="F7" s="25" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G7" s="25" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="H7" s="25" t="n"/>
@@ -3288,161 +3296,169 @@
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="26" t="inlineStr">
         <is>
-          <t>LG</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B8" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C8" s="25" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D8" s="25" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E8" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F8" s="25" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G8" s="25" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="H8" s="29" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="I8" s="27" t="n">
-        <v>-8.279999999999999</v>
+        <v>0.84</v>
+      </c>
+      <c r="I8" s="29" t="n">
+        <v>3.72</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
       <c r="A9" s="26" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>삼성전기</t>
         </is>
       </c>
       <c r="B9" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C9" s="25" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D9" s="25" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E9" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F9" s="25" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G9" s="25" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="H9" s="27" t="n">
-        <v>-1.68</v>
-      </c>
-      <c r="I9" s="27" t="n">
-        <v>-9.970000000000001</v>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="H9" s="29" t="n">
+        <v>7.16</v>
+      </c>
+      <c r="I9" s="29" t="n">
+        <v>9.75</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
       <c r="A10" s="26" t="inlineStr">
         <is>
-          <t>로봇</t>
+          <t>에코프로</t>
         </is>
       </c>
       <c r="B10" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C10" s="25" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D10" s="25" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E10" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F10" s="25" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G10" s="25" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="H10" s="25" t="n"/>
-      <c r="I10" s="25" t="n"/>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="H10" s="27" t="n">
+        <v>-9.66</v>
+      </c>
+      <c r="I10" s="29" t="n">
+        <v>3.5</v>
+      </c>
     </row>
     <row r="11" ht="18" customHeight="1">
       <c r="A11" s="26" t="inlineStr">
         <is>
-          <t>제약</t>
+          <t>LG</t>
         </is>
       </c>
       <c r="B11" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C11" s="25" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D11" s="25" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E11" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F11" s="25" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G11" s="25" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="H11" s="25" t="n"/>
-      <c r="I11" s="25" t="n"/>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="H11" s="27" t="n">
+        <v>-3.47</v>
+      </c>
+      <c r="I11" s="27" t="n">
+        <v>-1.32</v>
+      </c>
     </row>
     <row r="12" ht="18" customHeight="1">
       <c r="A12" s="26" t="inlineStr">
         <is>
-          <t>전기차</t>
+          <t>바이오</t>
         </is>
       </c>
       <c r="B12" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C12" s="25" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D12" s="25" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E12" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F12" s="25" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G12" s="25" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="H12" s="25" t="n"/>
@@ -3451,134 +3467,130 @@
     <row r="13" ht="18" customHeight="1">
       <c r="A13" s="26" t="inlineStr">
         <is>
-          <t>현대차</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B13" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C13" s="25" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D13" s="25" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E13" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F13" s="25" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G13" s="25" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="H13" s="29" t="n">
-        <v>3.43</v>
-      </c>
-      <c r="I13" s="27" t="n">
-        <v>-14.46</v>
+        <v>3.41</v>
+      </c>
+      <c r="I13" s="29" t="n">
+        <v>7.74</v>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="26" t="inlineStr">
         <is>
-          <t>LG화학</t>
+          <t>철강</t>
         </is>
       </c>
       <c r="B14" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C14" s="25" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D14" s="25" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E14" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F14" s="25" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G14" s="25" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="H14" s="29" t="n">
-        <v>13.65</v>
-      </c>
-      <c r="I14" s="27" t="n">
-        <v>-4.64</v>
-      </c>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="H14" s="25" t="n"/>
+      <c r="I14" s="25" t="n"/>
     </row>
     <row r="15" ht="18" customHeight="1">
       <c r="A15" s="26" t="inlineStr">
         <is>
-          <t>삼호개발</t>
+          <t>에코프로비엠</t>
         </is>
       </c>
       <c r="B15" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C15" s="25" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D15" s="25" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E15" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F15" s="25" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G15" s="25" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="H15" s="27" t="n">
-        <v>-2.17</v>
-      </c>
-      <c r="I15" s="29" t="n">
-        <v>17.02</v>
+        <v>-7.77</v>
+      </c>
+      <c r="I15" s="27" t="n">
+        <v>-5.57</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
       <c r="A16" s="26" t="inlineStr">
         <is>
-          <t>원전</t>
+          <t>제약</t>
         </is>
       </c>
       <c r="B16" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C16" s="25" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D16" s="25" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E16" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F16" s="25" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G16" s="25" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="H16" s="25" t="n"/>
@@ -3587,147 +3599,143 @@
     <row r="17" ht="18" customHeight="1">
       <c r="A17" s="26" t="inlineStr">
         <is>
-          <t>성호전자</t>
+          <t>KT</t>
         </is>
       </c>
       <c r="B17" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C17" s="25" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D17" s="25" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E17" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F17" s="25" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G17" s="25" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="H17" s="27" t="n">
-        <v>-1.56</v>
-      </c>
-      <c r="I17" s="27" t="n">
-        <v>-22.9</v>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="H17" s="29" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="I17" s="29" t="n">
+        <v>0.95</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
       <c r="A18" s="26" t="inlineStr">
         <is>
-          <t>스피어</t>
+          <t>LG전자</t>
         </is>
       </c>
       <c r="B18" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C18" s="25" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D18" s="25" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E18" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F18" s="25" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G18" s="25" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="H18" s="29" t="n">
-        <v>17.63</v>
-      </c>
-      <c r="I18" s="27" t="n">
-        <v>-8.130000000000001</v>
+        <v>3.2</v>
+      </c>
+      <c r="I18" s="29" t="n">
+        <v>0.5</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
       <c r="A19" s="26" t="inlineStr">
         <is>
-          <t>파두</t>
+          <t>전기차</t>
         </is>
       </c>
       <c r="B19" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C19" s="25" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D19" s="25" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E19" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F19" s="25" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G19" s="25" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="H19" s="29" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="I19" s="27" t="n">
-        <v>-26.06</v>
-      </c>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="H19" s="25" t="n"/>
+      <c r="I19" s="25" t="n"/>
     </row>
     <row r="20" ht="18" customHeight="1">
       <c r="A20" s="26" t="inlineStr">
         <is>
-          <t>뉴인텍</t>
+          <t>대한항공</t>
         </is>
       </c>
       <c r="B20" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C20" s="25" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D20" s="25" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E20" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F20" s="25" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G20" s="25" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="H20" s="27" t="n">
-        <v>-20.41</v>
+        <v>-2.82</v>
       </c>
       <c r="I20" s="29" t="n">
-        <v>17.04</v>
+        <v>6.37</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
       <c r="A21" s="26" t="inlineStr">
         <is>
-          <t>방산</t>
+          <t>DB</t>
         </is>
       </c>
       <c r="B21" s="25" t="n">
@@ -3744,21 +3752,25 @@
       </c>
       <c r="F21" s="25" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G21" s="25" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="H21" s="25" t="n"/>
-      <c r="I21" s="25" t="n"/>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="H21" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="I21" s="29" t="n">
+        <v>1.11</v>
+      </c>
     </row>
     <row r="22" ht="18" customHeight="1">
       <c r="A22" s="26" t="inlineStr">
         <is>
-          <t>아크솔루션스</t>
+          <t>HJ중공업</t>
         </is>
       </c>
       <c r="B22" s="25" t="n">
@@ -3775,25 +3787,25 @@
       </c>
       <c r="F22" s="25" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G22" s="25" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="H22" s="27" t="n">
-        <v>-97.40000000000001</v>
-      </c>
-      <c r="I22" s="27" t="n">
-        <v>-97.40000000000001</v>
+        <v>-10.24</v>
+      </c>
+      <c r="I22" s="29" t="n">
+        <v>2.81</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
       <c r="A23" s="26" t="inlineStr">
         <is>
-          <t>앱튼</t>
+          <t>모바일어플라이언스</t>
         </is>
       </c>
       <c r="B23" s="25" t="n">
@@ -3810,25 +3822,25 @@
       </c>
       <c r="F23" s="25" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G23" s="25" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="H23" s="29" t="n">
-        <v>29.98</v>
+        <v>29.9</v>
       </c>
       <c r="I23" s="29" t="n">
-        <v>109.15</v>
+        <v>17.76</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
       <c r="A24" s="26" t="inlineStr">
         <is>
-          <t>원익IPS</t>
+          <t>성호전자</t>
         </is>
       </c>
       <c r="B24" s="25" t="n">
@@ -3845,25 +3857,25 @@
       </c>
       <c r="F24" s="25" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G24" s="25" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="H24" s="27" t="n">
-        <v>-2.93</v>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="H24" s="29" t="n">
+        <v>4.22</v>
       </c>
       <c r="I24" s="27" t="n">
-        <v>-7.83</v>
+        <v>-5.57</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
       <c r="A25" s="26" t="inlineStr">
         <is>
-          <t>차바이오텍</t>
+          <t>스테이블코인</t>
         </is>
       </c>
       <c r="B25" s="25" t="n">
@@ -3880,25 +3892,21 @@
       </c>
       <c r="F25" s="25" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G25" s="25" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="H25" s="29" t="n">
-        <v>10.78</v>
-      </c>
-      <c r="I25" s="29" t="n">
-        <v>0.26</v>
-      </c>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="H25" s="25" t="n"/>
+      <c r="I25" s="25" t="n"/>
     </row>
     <row r="26" ht="18" customHeight="1">
       <c r="A26" s="26" t="inlineStr">
         <is>
-          <t>페니트리움바이오</t>
+          <t>스트라드비젼</t>
         </is>
       </c>
       <c r="B26" s="25" t="n">
@@ -3915,25 +3923,21 @@
       </c>
       <c r="F26" s="25" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G26" s="25" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="H26" s="29" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="I26" s="27" t="n">
-        <v>-7.21</v>
-      </c>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="H26" s="25" t="n"/>
+      <c r="I26" s="25" t="n"/>
     </row>
     <row r="27" ht="18" customHeight="1">
       <c r="A27" s="26" t="inlineStr">
         <is>
-          <t>한화생명</t>
+          <t>스피어</t>
         </is>
       </c>
       <c r="B27" s="25" t="n">
@@ -3950,130 +3954,130 @@
       </c>
       <c r="F27" s="25" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G27" s="25" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="H27" s="29" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="I27" s="27" t="n">
-        <v>-9.199999999999999</v>
+        <v>14.74</v>
+      </c>
+      <c r="I27" s="29" t="n">
+        <v>17.51</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
       <c r="A28" s="26" t="inlineStr">
         <is>
-          <t>KB금융</t>
+          <t>차바이오텍</t>
         </is>
       </c>
       <c r="B28" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C28" s="25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D28" s="25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E28" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F28" s="25" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G28" s="25" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="H28" s="29" t="n">
-        <v>2.95</v>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="H28" s="27" t="n">
+        <v>-6.46</v>
       </c>
       <c r="I28" s="27" t="n">
-        <v>-2.1</v>
+        <v>-5.32</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
       <c r="A29" s="26" t="inlineStr">
         <is>
-          <t>기아</t>
+          <t>파두</t>
         </is>
       </c>
       <c r="B29" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C29" s="25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D29" s="25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E29" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F29" s="25" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G29" s="25" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="H29" s="29" t="n">
-        <v>3.92</v>
+        <v>2.1</v>
       </c>
       <c r="I29" s="27" t="n">
-        <v>-7.13</v>
+        <v>-2.56</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
       <c r="A30" s="26" t="inlineStr">
         <is>
-          <t>남광토건</t>
+          <t>페니트리움바이오</t>
         </is>
       </c>
       <c r="B30" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C30" s="25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D30" s="25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E30" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F30" s="25" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G30" s="25" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="H30" s="29" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="I30" s="29" t="n">
-        <v>9.539999999999999</v>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="H30" s="27" t="n">
+        <v>-1.54</v>
+      </c>
+      <c r="I30" s="27" t="n">
+        <v>-2.74</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
       <c r="A31" s="26" t="inlineStr">
         <is>
-          <t>네이버</t>
+          <t>KB금융</t>
         </is>
       </c>
       <c r="B31" s="25" t="n">
@@ -4090,21 +4094,25 @@
       </c>
       <c r="F31" s="25" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G31" s="25" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="H31" s="25" t="n"/>
-      <c r="I31" s="25" t="n"/>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="H31" s="29" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="I31" s="29" t="n">
+        <v>3.45</v>
+      </c>
     </row>
     <row r="32" ht="18" customHeight="1">
       <c r="A32" s="26" t="inlineStr">
         <is>
-          <t>대한항공</t>
+          <t>NH투자증권</t>
         </is>
       </c>
       <c r="B32" s="25" t="n">
@@ -4121,25 +4129,25 @@
       </c>
       <c r="F32" s="25" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G32" s="25" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="H32" s="29" t="n">
-        <v>1.07</v>
+        <v>0.86</v>
       </c>
       <c r="I32" s="29" t="n">
-        <v>4.81</v>
+        <v>2.26</v>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
       <c r="A33" s="26" t="inlineStr">
         <is>
-          <t>삼성전기</t>
+          <t>아크솔루션스</t>
         </is>
       </c>
       <c r="B33" s="25" t="n">
@@ -4156,126 +4164,130 @@
       </c>
       <c r="F33" s="25" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G33" s="25" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="H33" s="29" t="n">
-        <v>2.26</v>
+        <v>0.87</v>
       </c>
       <c r="I33" s="27" t="n">
-        <v>-8.529999999999999</v>
+        <v>-97.38</v>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
       <c r="A34" s="26" t="inlineStr">
         <is>
-          <t>소룩스</t>
+          <t>CMG제약</t>
         </is>
       </c>
       <c r="B34" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C34" s="25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D34" s="25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E34" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F34" s="25" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G34" s="25" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="H34" s="27" t="n">
-        <v>-4.76</v>
+        <v>-2.86</v>
       </c>
       <c r="I34" s="29" t="n">
-        <v>18.99</v>
+        <v>3.79</v>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
       <c r="A35" s="26" t="inlineStr">
         <is>
-          <t>채비</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="B35" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C35" s="25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D35" s="25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E35" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F35" s="25" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G35" s="25" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="H35" s="29" t="n">
-        <v>16.69</v>
-      </c>
-      <c r="I35" s="27" t="n">
-        <v>-3.89</v>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="H35" s="27" t="n">
+        <v>-2.19</v>
+      </c>
+      <c r="I35" s="29" t="n">
+        <v>1.44</v>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
       <c r="A36" s="26" t="inlineStr">
         <is>
-          <t>태양광</t>
+          <t>골프존홀딩스</t>
         </is>
       </c>
       <c r="B36" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C36" s="25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D36" s="25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E36" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F36" s="25" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G36" s="25" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="H36" s="25" t="n"/>
-      <c r="I36" s="25" t="n"/>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="H36" s="29" t="n">
+        <v>19.89</v>
+      </c>
+      <c r="I36" s="29" t="n">
+        <v>47.66</v>
+      </c>
     </row>
     <row r="37" ht="18" customHeight="1">
       <c r="A37" s="26" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B37" s="25" t="n">
@@ -4292,25 +4304,25 @@
       </c>
       <c r="F37" s="25" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G37" s="25" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="H37" s="29" t="n">
-        <v>7.68</v>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="H37" s="27" t="n">
+        <v>-4.9</v>
       </c>
       <c r="I37" s="27" t="n">
-        <v>-0.44</v>
+        <v>-2.79</v>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
       <c r="A38" s="26" t="inlineStr">
         <is>
-          <t>LG전자</t>
+          <t>카카오뱅크</t>
         </is>
       </c>
       <c r="B38" s="25" t="n">
@@ -4327,25 +4339,25 @@
       </c>
       <c r="F38" s="25" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G38" s="25" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="H38" s="29" t="n">
-        <v>0.41</v>
-      </c>
-      <c r="I38" s="27" t="n">
-        <v>-13.54</v>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="H38" s="27" t="n">
+        <v>-1.18</v>
+      </c>
+      <c r="I38" s="29" t="n">
+        <v>3.21</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
       <c r="A39" s="26" t="inlineStr">
         <is>
-          <t>다스코</t>
+          <t>한화엔진</t>
         </is>
       </c>
       <c r="B39" s="25" t="n">
@@ -4362,375 +4374,375 @@
       </c>
       <c r="F39" s="25" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G39" s="25" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="H39" s="29" t="n">
-        <v>29.99</v>
-      </c>
-      <c r="I39" s="29" t="n">
-        <v>52.65</v>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="H39" s="27" t="n">
+        <v>-0.97</v>
+      </c>
+      <c r="I39" s="27" t="n">
+        <v>-4.67</v>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
       <c r="A40" s="26" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>CSA 코스믹</t>
         </is>
       </c>
       <c r="B40" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C40" s="25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D40" s="25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E40" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F40" s="25" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G40" s="25" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="H40" s="29" t="n">
-        <v>8.91</v>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="H40" s="27" t="n">
+        <v>-1.67</v>
       </c>
       <c r="I40" s="27" t="n">
-        <v>-9.130000000000001</v>
+        <v>-7.81</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
       <c r="A41" s="26" t="inlineStr">
         <is>
-          <t>모바일어플라이언스</t>
+          <t>SK스퀘어</t>
         </is>
       </c>
       <c r="B41" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C41" s="25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D41" s="25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E41" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F41" s="25" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G41" s="25" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="H41" s="27" t="n">
-        <v>-3.64</v>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="H41" s="29" t="n">
+        <v>3.48</v>
       </c>
       <c r="I41" s="27" t="n">
-        <v>-13.13</v>
+        <v>-7.37</v>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
       <c r="A42" s="26" t="inlineStr">
         <is>
-          <t>베셀</t>
+          <t>뉴인텍</t>
         </is>
       </c>
       <c r="B42" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C42" s="25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D42" s="25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E42" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F42" s="25" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G42" s="25" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="H42" s="29" t="n">
-        <v>10.24</v>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="H42" s="27" t="n">
+        <v>-13.78</v>
       </c>
       <c r="I42" s="29" t="n">
-        <v>13.91</v>
+        <v>8.859999999999999</v>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1">
       <c r="A43" s="26" t="inlineStr">
         <is>
-          <t>시너지이노베이션</t>
+          <t>대명에너지</t>
         </is>
       </c>
       <c r="B43" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C43" s="25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D43" s="25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E43" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F43" s="25" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G43" s="25" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="H43" s="29" t="n">
-        <v>7.34</v>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="H43" s="27" t="n">
+        <v>-9.93</v>
       </c>
       <c r="I43" s="29" t="n">
-        <v>0.06</v>
+        <v>25.67</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
       <c r="A44" s="26" t="inlineStr">
         <is>
-          <t>에임드바이오</t>
+          <t>삼호개발</t>
         </is>
       </c>
       <c r="B44" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C44" s="25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D44" s="25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E44" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F44" s="25" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G44" s="25" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="H44" s="29" t="n">
-        <v>16.04</v>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="H44" s="27" t="n">
+        <v>-9.699999999999999</v>
       </c>
       <c r="I44" s="29" t="n">
-        <v>6.11</v>
+        <v>7.24</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
       <c r="A45" s="26" t="inlineStr">
         <is>
-          <t>올릭스</t>
+          <t>아모텍</t>
         </is>
       </c>
       <c r="B45" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C45" s="25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D45" s="25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E45" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F45" s="25" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G45" s="25" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="H45" s="29" t="n">
-        <v>24.22</v>
-      </c>
-      <c r="I45" s="29" t="n">
-        <v>27.93</v>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="H45" s="27" t="n">
+        <v>-3.35</v>
+      </c>
+      <c r="I45" s="27" t="n">
+        <v>-17.97</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
       <c r="A46" s="26" t="inlineStr">
         <is>
-          <t>카카오</t>
+          <t>앱튼</t>
         </is>
       </c>
       <c r="B46" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C46" s="25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D46" s="25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E46" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F46" s="25" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G46" s="25" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="H46" s="29" t="n">
-        <v>8.140000000000001</v>
-      </c>
-      <c r="I46" s="27" t="n">
-        <v>-2.58</v>
+        <v>29.72</v>
+      </c>
+      <c r="I46" s="29" t="n">
+        <v>180.8</v>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
       <c r="A47" s="26" t="inlineStr">
         <is>
-          <t>티이엠씨씨엔에스</t>
+          <t>에이프릴바이오</t>
         </is>
       </c>
       <c r="B47" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C47" s="25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D47" s="25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E47" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F47" s="25" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G47" s="25" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="H47" s="27" t="n">
-        <v>-0.31</v>
+        <v>-4.81</v>
       </c>
       <c r="I47" s="29" t="n">
-        <v>14.49</v>
+        <v>18.05</v>
       </c>
     </row>
     <row r="48" ht="18" customHeight="1">
       <c r="A48" s="26" t="inlineStr">
         <is>
-          <t>하이브</t>
+          <t>우리금융지주</t>
         </is>
       </c>
       <c r="B48" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C48" s="25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D48" s="25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E48" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F48" s="25" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G48" s="25" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="H48" s="29" t="n">
-        <v>9.84</v>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="H48" s="27" t="n">
+        <v>-0.34</v>
       </c>
       <c r="I48" s="27" t="n">
-        <v>-8.31</v>
+        <v>-1.53</v>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1">
       <c r="A49" s="26" t="inlineStr">
         <is>
-          <t>현대로템</t>
+          <t>져스텍</t>
         </is>
       </c>
       <c r="B49" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C49" s="25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D49" s="25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E49" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F49" s="25" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G49" s="25" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="H49" s="29" t="n">
-        <v>8.890000000000001</v>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="H49" s="27" t="n">
+        <v>-5.08</v>
       </c>
       <c r="I49" s="27" t="n">
-        <v>-9.140000000000001</v>
+        <v>-5.08</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
       <c r="A50" s="26" t="inlineStr">
         <is>
-          <t>NPX</t>
+          <t>지니너스</t>
         </is>
       </c>
       <c r="B50" s="25" t="n">
@@ -4747,25 +4759,25 @@
       </c>
       <c r="F50" s="25" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G50" s="25" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="H50" s="27" t="n">
-        <v>-49.52</v>
-      </c>
-      <c r="I50" s="27" t="n">
-        <v>-98.69</v>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="H50" s="29" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="I50" s="29" t="n">
+        <v>11.87</v>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
       <c r="A51" s="26" t="inlineStr">
         <is>
-          <t>광주신세계</t>
+          <t>클래시스</t>
         </is>
       </c>
       <c r="B51" s="25" t="n">
@@ -4782,25 +4794,25 @@
       </c>
       <c r="F51" s="25" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G51" s="25" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="H51" s="27" t="n">
-        <v>-4.73</v>
+        <v>-5.57</v>
       </c>
       <c r="I51" s="29" t="n">
-        <v>44.83</v>
+        <v>6.27</v>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1">
       <c r="A52" s="26" t="inlineStr">
         <is>
-          <t>프로브잇</t>
+          <t>플리토</t>
         </is>
       </c>
       <c r="B52" s="25" t="n">
@@ -4817,19 +4829,19 @@
       </c>
       <c r="F52" s="25" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G52" s="25" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="H52" s="27" t="n">
-        <v>-44.44</v>
-      </c>
-      <c r="I52" s="27" t="n">
-        <v>-72.22</v>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="H52" s="29" t="n">
+        <v>5.48</v>
+      </c>
+      <c r="I52" s="29" t="n">
+        <v>24.19</v>
       </c>
     </row>
   </sheetData>
@@ -4913,19 +4925,19 @@
         <v>1</v>
       </c>
       <c r="C3" s="36" t="n">
-        <v>121</v>
+        <v>108</v>
       </c>
       <c r="D3" s="36" t="n">
-        <v>121</v>
+        <v>108</v>
       </c>
       <c r="E3" s="36" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="F3" s="37" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G3" s="37" t="inlineStr">
@@ -4944,19 +4956,19 @@
         <v>1</v>
       </c>
       <c r="C4" s="36" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="D4" s="36" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="E4" s="36" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="F4" s="37" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G4" s="37" t="inlineStr">
@@ -4975,19 +4987,19 @@
         <v>1</v>
       </c>
       <c r="C5" s="36" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D5" s="36" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E5" s="36" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="F5" s="37" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G5" s="37" t="inlineStr">
@@ -4999,26 +5011,26 @@
     <row r="6" ht="18" customHeight="1">
       <c r="A6" s="35" t="inlineStr">
         <is>
-          <t>방산</t>
+          <t>로봇</t>
         </is>
       </c>
       <c r="B6" s="36" t="n">
         <v>1</v>
       </c>
       <c r="C6" s="36" t="n">
-        <v>6</v>
+        <v>27</v>
       </c>
       <c r="D6" s="36" t="n">
-        <v>6</v>
+        <v>27</v>
       </c>
       <c r="E6" s="36" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="F6" s="37" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G6" s="37" t="inlineStr">
@@ -5030,26 +5042,26 @@
     <row r="7" ht="18" customHeight="1">
       <c r="A7" s="35" t="inlineStr">
         <is>
-          <t>원전</t>
+          <t>철강</t>
         </is>
       </c>
       <c r="B7" s="36" t="n">
         <v>1</v>
       </c>
       <c r="C7" s="36" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D7" s="36" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E7" s="36" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="F7" s="37" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G7" s="37" t="inlineStr">
@@ -5061,26 +5073,26 @@
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="35" t="inlineStr">
         <is>
-          <t>로봇</t>
+          <t>제약</t>
         </is>
       </c>
       <c r="B8" s="36" t="n">
         <v>1</v>
       </c>
       <c r="C8" s="36" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="D8" s="36" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="E8" s="36" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="F8" s="37" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G8" s="37" t="inlineStr">
@@ -5092,26 +5104,26 @@
     <row r="9" ht="18" customHeight="1">
       <c r="A9" s="35" t="inlineStr">
         <is>
-          <t>태양광</t>
+          <t>인공지능</t>
         </is>
       </c>
       <c r="B9" s="36" t="n">
         <v>1</v>
       </c>
       <c r="C9" s="36" t="n">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="D9" s="36" t="n">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="E9" s="36" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="F9" s="37" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G9" s="37" t="inlineStr">
@@ -5121,71 +5133,63 @@
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="35" t="inlineStr">
-        <is>
-          <t>제약</t>
-        </is>
-      </c>
-      <c r="B10" s="36" t="n">
-        <v>1</v>
-      </c>
-      <c r="C10" s="36" t="n">
-        <v>16</v>
-      </c>
-      <c r="D10" s="36" t="n">
-        <v>16</v>
-      </c>
-      <c r="E10" s="36" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="F10" s="37" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="G10" s="37" t="inlineStr">
-        <is>
-          <t>⚡ 관심</t>
-        </is>
-      </c>
+      <c r="A10" s="26" t="inlineStr">
+        <is>
+          <t>이차전지</t>
+        </is>
+      </c>
+      <c r="B10" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F10" s="28" t="inlineStr">
+        <is>
+          <t>감지 없음</t>
+        </is>
+      </c>
+      <c r="G10" s="28" t="inlineStr"/>
     </row>
     <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="35" t="inlineStr">
-        <is>
-          <t>인공지능</t>
-        </is>
-      </c>
-      <c r="B11" s="36" t="n">
-        <v>1</v>
-      </c>
-      <c r="C11" s="36" t="n">
-        <v>29</v>
-      </c>
-      <c r="D11" s="36" t="n">
-        <v>29</v>
-      </c>
-      <c r="E11" s="36" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="F11" s="37" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="G11" s="37" t="inlineStr">
-        <is>
-          <t>⚡ 관심</t>
-        </is>
-      </c>
+      <c r="A11" s="26" t="inlineStr">
+        <is>
+          <t>AI반도체</t>
+        </is>
+      </c>
+      <c r="B11" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F11" s="28" t="inlineStr">
+        <is>
+          <t>감지 없음</t>
+        </is>
+      </c>
+      <c r="G11" s="28" t="inlineStr"/>
     </row>
     <row r="12" ht="18" customHeight="1">
       <c r="A12" s="26" t="inlineStr">
         <is>
-          <t>이차전지</t>
+          <t>방산</t>
         </is>
       </c>
       <c r="B12" s="25" t="n">
@@ -5212,7 +5216,7 @@
     <row r="13" ht="18" customHeight="1">
       <c r="A13" s="26" t="inlineStr">
         <is>
-          <t>AI반도체</t>
+          <t>원전</t>
         </is>
       </c>
       <c r="B13" s="25" t="n">
@@ -5266,7 +5270,7 @@
     <row r="15" ht="18" customHeight="1">
       <c r="A15" s="26" t="inlineStr">
         <is>
-          <t>게임</t>
+          <t>태양광</t>
         </is>
       </c>
       <c r="B15" s="25" t="n">
@@ -5293,7 +5297,7 @@
     <row r="16" ht="18" customHeight="1">
       <c r="A16" s="26" t="inlineStr">
         <is>
-          <t>엔터</t>
+          <t>게임</t>
         </is>
       </c>
       <c r="B16" s="25" t="n">
@@ -5320,7 +5324,7 @@
     <row r="17" ht="18" customHeight="1">
       <c r="A17" s="26" t="inlineStr">
         <is>
-          <t>핀테크</t>
+          <t>엔터</t>
         </is>
       </c>
       <c r="B17" s="25" t="n">
@@ -5347,7 +5351,7 @@
     <row r="18" ht="18" customHeight="1">
       <c r="A18" s="26" t="inlineStr">
         <is>
-          <t>클라우드</t>
+          <t>핀테크</t>
         </is>
       </c>
       <c r="B18" s="25" t="n">
@@ -5374,7 +5378,7 @@
     <row r="19" ht="18" customHeight="1">
       <c r="A19" s="26" t="inlineStr">
         <is>
-          <t>조선</t>
+          <t>클라우드</t>
         </is>
       </c>
       <c r="B19" s="25" t="n">
@@ -5401,7 +5405,7 @@
     <row r="20" ht="18" customHeight="1">
       <c r="A20" s="26" t="inlineStr">
         <is>
-          <t>철강</t>
+          <t>조선</t>
         </is>
       </c>
       <c r="B20" s="25" t="n">

--- a/trend/stock_trend_history.xlsx
+++ b/trend/stock_trend_history.xlsx
@@ -258,13 +258,13 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -694,7 +694,7 @@
     <row r="1" ht="36" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>📊 주식 트렌드 조기 감지 대시보드   |   최종 업데이트: 2026-07-01 06:54</t>
+          <t>📊 주식 트렌드 조기 감지 대시보드   |   최종 업데이트: 2026-07-02 06:54</t>
         </is>
       </c>
     </row>
@@ -708,7 +708,7 @@
       </c>
       <c r="E3" s="3" t="n"/>
       <c r="G3" s="5" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H3" s="3" t="n"/>
       <c r="J3" s="6" t="n">
@@ -787,21 +787,21 @@
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="11" t="inlineStr">
         <is>
-          <t>⚡ 최신(2026-07-01) 상위: 반도체  점수 108.0점</t>
+          <t>⚡ 최신(2026-07-02) 상위: 반도체  점수 96.0점</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1">
       <c r="A11" s="12" t="inlineStr">
         <is>
-          <t>⚡ 최신(2026-07-01) 상위: 현대차  점수 27.0점</t>
+          <t>⚡ 최신(2026-07-02) 상위: SK  점수 44.0점</t>
         </is>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1">
       <c r="A12" s="11" t="inlineStr">
         <is>
-          <t>⚡ 최신(2026-07-01) 상위: 로봇  점수 27.0점</t>
+          <t>⚡ 최신(2026-07-02) 상위: 삼성전자  점수 41.0점</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B14" s="15" t="n">
@@ -928,10 +928,10 @@
         </is>
       </c>
       <c r="D14" s="15" t="n">
-        <v>108</v>
+        <v>96</v>
       </c>
       <c r="E14" s="15" t="n">
-        <v>108</v>
+        <v>96</v>
       </c>
       <c r="F14" s="15" t="n">
         <v>0</v>
@@ -947,7 +947,7 @@
       </c>
       <c r="J14" s="17" t="inlineStr">
         <is>
-          <t>네이버뉴스 헤드라인 언급 / 네이버뉴스 헤드라인 언급 / 매일경제 헤드라인 언급 / 네이버뉴스 헤드라인 언급 / 네이버뉴스 헤드라인 언급</t>
+          <t>네이버뉴스 기사 언급 / 네이버뉴스 헤드라인 언급 / 매일경제 기사 언급 / 매일경제 헤드라인 언급 / 네이버뉴스 기사 언급</t>
         </is>
       </c>
       <c r="K14" s="17" t="inlineStr">
@@ -959,7 +959,7 @@
     <row r="15" ht="18" customHeight="1">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B15" s="15" t="n">
@@ -967,14 +967,14 @@
       </c>
       <c r="C15" s="16" t="inlineStr">
         <is>
-          <t>현대차</t>
+          <t>SK</t>
         </is>
       </c>
       <c r="D15" s="15" t="n">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="E15" s="15" t="n">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="F15" s="15" t="n">
         <v>0</v>
@@ -983,14 +983,14 @@
         <v>0</v>
       </c>
       <c r="H15" s="18" t="n">
-        <v>-0.4</v>
-      </c>
-      <c r="I15" s="18" t="n">
-        <v>-3.13</v>
+        <v>-8.51</v>
+      </c>
+      <c r="I15" s="19" t="n">
+        <v>7.16</v>
       </c>
       <c r="J15" s="17" t="inlineStr">
         <is>
-          <t>네이버뉴스 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 기사 언급 / 매일경제 헤드라인 언급</t>
+          <t>네이버뉴스 헤드라인 언급 / 매일경제 헤드라인 언급 / 네이버뉴스 헤드라인 언급 / 한국경제 헤드라인 언급 / 매일경제 헤드라인 언급</t>
         </is>
       </c>
       <c r="K15" s="17" t="inlineStr">
@@ -1002,7 +1002,7 @@
     <row r="16" ht="18" customHeight="1">
       <c r="A16" s="15" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B16" s="15" t="n">
@@ -1010,14 +1010,14 @@
       </c>
       <c r="C16" s="16" t="inlineStr">
         <is>
-          <t>로봇</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="D16" s="15" t="n">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="E16" s="15" t="n">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="F16" s="15" t="n">
         <v>0</v>
@@ -1025,15 +1025,15 @@
       <c r="G16" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="H16" s="15" t="n">
-        <v/>
-      </c>
-      <c r="I16" s="15" t="n">
-        <v/>
+      <c r="H16" s="18" t="n">
+        <v>-5.84</v>
+      </c>
+      <c r="I16" s="18" t="n">
+        <v>-7.64</v>
       </c>
       <c r="J16" s="17" t="inlineStr">
         <is>
-          <t>네이버뉴스 헤드라인 언급 / 한국경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급</t>
+          <t>매일경제 헤드라인 언급 / 한국경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 네이버뉴스 헤드라인 언급 / 매일경제 기사 언급</t>
         </is>
       </c>
       <c r="K16" s="17" t="inlineStr">
@@ -1045,7 +1045,7 @@
     <row r="17" ht="18" customHeight="1">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B17" s="15" t="n">
@@ -1053,42 +1053,42 @@
       </c>
       <c r="C17" s="16" t="inlineStr">
         <is>
-          <t>SK</t>
+          <t>에코프로</t>
         </is>
       </c>
       <c r="D17" s="15" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="E17" s="15" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="F17" s="15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G17" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="H17" s="19" t="n">
-        <v>6.24</v>
-      </c>
-      <c r="I17" s="19" t="n">
-        <v>18.3</v>
+      <c r="H17" s="18" t="n">
+        <v>-12.76</v>
+      </c>
+      <c r="I17" s="18" t="n">
+        <v>-13.65</v>
       </c>
       <c r="J17" s="17" t="inlineStr">
         <is>
-          <t>매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 한국경제 헤드라인 언급 / 매일경제 기사 언급 / 한국경제 헤드라인 언급</t>
+          <t>중요공시 2건 / 중요공시 3일 +100% / Google 급상승 검색어 등장 (KR) / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급</t>
         </is>
       </c>
       <c r="K17" s="17" t="inlineStr">
         <is>
-          <t>네이버</t>
+          <t>Google, 공시</t>
         </is>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
       <c r="A18" s="15" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B18" s="15" t="n">
@@ -1096,14 +1096,14 @@
       </c>
       <c r="C18" s="16" t="inlineStr">
         <is>
-          <t>인공지능</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="D18" s="15" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E18" s="15" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F18" s="15" t="n">
         <v>0</v>
@@ -1111,15 +1111,15 @@
       <c r="G18" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="H18" s="15" t="n">
-        <v/>
-      </c>
-      <c r="I18" s="15" t="n">
-        <v/>
+      <c r="H18" s="18" t="n">
+        <v>-3.4</v>
+      </c>
+      <c r="I18" s="18" t="n">
+        <v>-0.78</v>
       </c>
       <c r="J18" s="17" t="inlineStr">
         <is>
-          <t>매일경제 기사 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 기사 언급 / 매일경제 기사 언급 / 매일경제 기사 언급</t>
+          <t>네이버뉴스 헤드라인 언급 / 매일경제 헤드라인 언급 / 네이버뉴스 헤드라인 언급 / 한국경제 헤드라인 언급 / 매일경제 기사 언급</t>
         </is>
       </c>
       <c r="K18" s="17" t="inlineStr">
@@ -1131,7 +1131,7 @@
     <row r="19" ht="18" customHeight="1">
       <c r="A19" s="15" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B19" s="15" t="n">
@@ -1139,42 +1139,42 @@
       </c>
       <c r="C19" s="16" t="inlineStr">
         <is>
-          <t>에코프로</t>
+          <t>인공지능</t>
         </is>
       </c>
       <c r="D19" s="15" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="E19" s="15" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F19" s="15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G19" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="H19" s="18" t="n">
-        <v>-9.66</v>
-      </c>
-      <c r="I19" s="19" t="n">
-        <v>3.5</v>
+      <c r="H19" s="15" t="n">
+        <v/>
+      </c>
+      <c r="I19" s="15" t="n">
+        <v/>
       </c>
       <c r="J19" s="17" t="inlineStr">
         <is>
-          <t>중요공시 3건 / 중요공시 3일 +200% / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
+          <t>네이버뉴스 기사 언급 / 매일경제 기사 언급 / 네이버뉴스 기사 언급 / 매일경제 기사 언급 / 매일경제 기사 언급</t>
         </is>
       </c>
       <c r="K19" s="17" t="inlineStr">
         <is>
-          <t>공시</t>
+          <t>네이버</t>
         </is>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
       <c r="A20" s="15" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B20" s="15" t="n">
@@ -1182,14 +1182,14 @@
       </c>
       <c r="C20" s="16" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>LG</t>
         </is>
       </c>
       <c r="D20" s="15" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E20" s="15" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="F20" s="15" t="n">
         <v>0</v>
@@ -1197,27 +1197,27 @@
       <c r="G20" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="H20" s="19" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="I20" s="19" t="n">
-        <v>3.72</v>
+      <c r="H20" s="18" t="n">
+        <v>-0.72</v>
+      </c>
+      <c r="I20" s="18" t="n">
+        <v>-2.62</v>
       </c>
       <c r="J20" s="17" t="inlineStr">
         <is>
-          <t>중요공시 1건 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 기사 언급 / 한국경제 헤드라인 언급</t>
+          <t>Google 급상승 검색어 등장 (KR) / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급</t>
         </is>
       </c>
       <c r="K20" s="17" t="inlineStr">
         <is>
-          <t>네이버, 공시</t>
+          <t>Google</t>
         </is>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
       <c r="A21" s="15" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B21" s="15" t="n">
@@ -1229,10 +1229,10 @@
         </is>
       </c>
       <c r="D21" s="15" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E21" s="15" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F21" s="15" t="n">
         <v>0</v>
@@ -1241,14 +1241,14 @@
         <v>0</v>
       </c>
       <c r="H21" s="19" t="n">
-        <v>7.16</v>
+        <v>0.96</v>
       </c>
       <c r="I21" s="19" t="n">
-        <v>9.75</v>
+        <v>12.27</v>
       </c>
       <c r="J21" s="17" t="inlineStr">
         <is>
-          <t>중요공시 1건 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
+          <t>중요공시 1건 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 기사 언급 / 매일경제 헤드라인 언급</t>
         </is>
       </c>
       <c r="K21" s="17" t="inlineStr">
@@ -1260,7 +1260,7 @@
     <row r="22" ht="18" customHeight="1">
       <c r="A22" s="15" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B22" s="15" t="n">
@@ -1268,14 +1268,14 @@
       </c>
       <c r="C22" s="16" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>바이오</t>
         </is>
       </c>
       <c r="D22" s="15" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E22" s="15" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="F22" s="15" t="n">
         <v>0</v>
@@ -1283,15 +1283,15 @@
       <c r="G22" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="H22" s="19" t="n">
-        <v>3.41</v>
-      </c>
-      <c r="I22" s="19" t="n">
-        <v>7.74</v>
+      <c r="H22" s="15" t="n">
+        <v/>
+      </c>
+      <c r="I22" s="15" t="n">
+        <v/>
       </c>
       <c r="J22" s="17" t="inlineStr">
         <is>
-          <t>매일경제 기사 언급 / 한국경제 헤드라인 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 기사 언급 / 매일경제 헤드라인 언급</t>
+          <t>매일경제 헤드라인 언급 / 네이버뉴스 헤드라인 언급 / 네이버뉴스 헤드라인 언급 / 한국경제 헤드라인 언급 / 네이버뉴스 헤드라인 언급</t>
         </is>
       </c>
       <c r="K22" s="17" t="inlineStr">
@@ -1303,7 +1303,7 @@
     <row r="23" ht="18" customHeight="1">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B23" s="15" t="n">
@@ -1311,14 +1311,14 @@
       </c>
       <c r="C23" s="16" t="inlineStr">
         <is>
-          <t>바이오</t>
+          <t>전기차</t>
         </is>
       </c>
       <c r="D23" s="15" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E23" s="15" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F23" s="15" t="n">
         <v>0</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="J23" s="17" t="inlineStr">
         <is>
-          <t>네이버뉴스 기사 언급 / 네이버뉴스 헤드라인 언급 / 네이버뉴스 헤드라인 언급 / 매일경제 헤드라인 언급 / 네이버뉴스 기사 언급</t>
+          <t>네이버뉴스 헤드라인 언급 / 매일경제 기사 언급 / 한국경제 헤드라인 언급 / 한국경제 헤드라인 언급 / 매일경제 헤드라인 언급</t>
         </is>
       </c>
       <c r="K23" s="17" t="inlineStr">
@@ -1346,7 +1346,7 @@
     <row r="24" ht="18" customHeight="1">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B24" s="15" t="n">
@@ -1354,14 +1354,14 @@
       </c>
       <c r="C24" s="16" t="inlineStr">
         <is>
-          <t>LG</t>
+          <t>에코프로비엠</t>
         </is>
       </c>
       <c r="D24" s="15" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E24" s="15" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F24" s="15" t="n">
         <v>0</v>
@@ -1370,26 +1370,26 @@
         <v>0</v>
       </c>
       <c r="H24" s="18" t="n">
-        <v>-3.47</v>
+        <v>-6.88</v>
       </c>
       <c r="I24" s="18" t="n">
-        <v>-1.32</v>
+        <v>-12.98</v>
       </c>
       <c r="J24" s="17" t="inlineStr">
         <is>
-          <t>한국경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 한국경제 헤드라인 언급 / 네이버뉴스 헤드라인 언급</t>
+          <t>중요공시 3건 / Google 급상승 검색어 등장 (KR) / 매일경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
         </is>
       </c>
       <c r="K24" s="17" t="inlineStr">
         <is>
-          <t>네이버</t>
+          <t>Google, 공시</t>
         </is>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
       <c r="A25" s="15" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B25" s="15" t="n">
@@ -1397,14 +1397,14 @@
       </c>
       <c r="C25" s="16" t="inlineStr">
         <is>
-          <t>철강</t>
+          <t>현대차</t>
         </is>
       </c>
       <c r="D25" s="15" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E25" s="15" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F25" s="15" t="n">
         <v>0</v>
@@ -1412,27 +1412,25 @@
       <c r="G25" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="H25" s="15" t="n">
+      <c r="H25" s="18" t="n">
+        <v>-1.52</v>
+      </c>
+      <c r="I25" s="18" t="n">
+        <v>-4.22</v>
+      </c>
+      <c r="J25" s="17" t="inlineStr">
+        <is>
+          <t>매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K25" s="17" t="n">
         <v/>
-      </c>
-      <c r="I25" s="15" t="n">
-        <v/>
-      </c>
-      <c r="J25" s="17" t="inlineStr">
-        <is>
-          <t>매일경제 헤드라인 언급 / 네이버뉴스 헤드라인 언급 / 네이버뉴스 헤드라인 언급 / 한국경제 헤드라인 언급 / 네이버뉴스 기사 언급</t>
-        </is>
-      </c>
-      <c r="K25" s="17" t="inlineStr">
-        <is>
-          <t>네이버</t>
-        </is>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
       <c r="A26" s="15" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B26" s="15" t="n">
@@ -1440,7 +1438,7 @@
       </c>
       <c r="C26" s="16" t="inlineStr">
         <is>
-          <t>에코프로비엠</t>
+          <t>SK스퀘어</t>
         </is>
       </c>
       <c r="D26" s="15" t="n">
@@ -1455,27 +1453,27 @@
       <c r="G26" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="H26" s="18" t="n">
-        <v>-7.77</v>
+      <c r="H26" s="19" t="n">
+        <v>3.54</v>
       </c>
       <c r="I26" s="18" t="n">
-        <v>-5.57</v>
+        <v>-2.33</v>
       </c>
       <c r="J26" s="17" t="inlineStr">
         <is>
-          <t>중요공시 2건 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
+          <t>중요공시 1건 / 네이버뉴스 헤드라인 언급 / 네이버뉴스 헤드라인 언급 / 매일경제 헤드라인 언급</t>
         </is>
       </c>
       <c r="K26" s="17" t="inlineStr">
         <is>
-          <t>공시</t>
+          <t>네이버, 공시</t>
         </is>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
       <c r="A27" s="15" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B27" s="15" t="n">
@@ -1483,14 +1481,14 @@
       </c>
       <c r="C27" s="16" t="inlineStr">
         <is>
-          <t>제약</t>
+          <t>스테이블코인</t>
         </is>
       </c>
       <c r="D27" s="15" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E27" s="15" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F27" s="15" t="n">
         <v>0</v>
@@ -1506,19 +1504,17 @@
       </c>
       <c r="J27" s="17" t="inlineStr">
         <is>
-          <t>네이버뉴스 헤드라인 언급 / 매일경제 헤드라인 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 기사 언급</t>
-        </is>
-      </c>
-      <c r="K27" s="17" t="inlineStr">
-        <is>
-          <t>네이버</t>
-        </is>
+          <t>매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 기사 언급 / 매일경제 기사 언급 / 매일경제 기사 언급</t>
+        </is>
+      </c>
+      <c r="K27" s="17" t="n">
+        <v/>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
       <c r="A28" s="15" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B28" s="15" t="n">
@@ -1526,7 +1522,7 @@
       </c>
       <c r="C28" s="16" t="inlineStr">
         <is>
-          <t>KT</t>
+          <t>방산</t>
         </is>
       </c>
       <c r="D28" s="15" t="n">
@@ -1541,27 +1537,25 @@
       <c r="G28" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="H28" s="19" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="I28" s="19" t="n">
-        <v>0.95</v>
+      <c r="H28" s="15" t="n">
+        <v/>
+      </c>
+      <c r="I28" s="15" t="n">
+        <v/>
       </c>
       <c r="J28" s="17" t="inlineStr">
         <is>
-          <t>Google 급상승 검색어 등장 (US) / 매일경제 헤드라인 언급 / 매일경제 기사 언급</t>
-        </is>
-      </c>
-      <c r="K28" s="17" t="inlineStr">
-        <is>
-          <t>Google</t>
-        </is>
+          <t>한국경제 헤드라인 언급 / 한국경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K28" s="17" t="n">
+        <v/>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
       <c r="A29" s="15" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B29" s="15" t="n">
@@ -1569,40 +1563,42 @@
       </c>
       <c r="C29" s="16" t="inlineStr">
         <is>
-          <t>LG전자</t>
+          <t>셀트리온</t>
         </is>
       </c>
       <c r="D29" s="15" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E29" s="15" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F29" s="15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G29" s="15" t="n">
         <v>0</v>
       </c>
       <c r="H29" s="19" t="n">
-        <v>3.2</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="I29" s="19" t="n">
-        <v>0.5</v>
+        <v>1.04</v>
       </c>
       <c r="J29" s="17" t="inlineStr">
         <is>
-          <t>한국경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K29" s="17" t="n">
-        <v/>
+          <t>중요공시 2건 / 중요공시 3일 +100% / Google 급상승 검색어 등장 (KR)</t>
+        </is>
+      </c>
+      <c r="K29" s="17" t="inlineStr">
+        <is>
+          <t>Google, 공시</t>
+        </is>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
       <c r="A30" s="15" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B30" s="15" t="n">
@@ -1610,14 +1606,14 @@
       </c>
       <c r="C30" s="16" t="inlineStr">
         <is>
-          <t>전기차</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="D30" s="15" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E30" s="15" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F30" s="15" t="n">
         <v>0</v>
@@ -1625,59 +1621,61 @@
       <c r="G30" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="H30" s="15" t="n">
-        <v/>
-      </c>
-      <c r="I30" s="15" t="n">
-        <v/>
+      <c r="H30" s="19" t="n">
+        <v>10.11</v>
+      </c>
+      <c r="I30" s="19" t="n">
+        <v>10.44</v>
       </c>
       <c r="J30" s="17" t="inlineStr">
         <is>
-          <t>매일경제 헤드라인 언급 / 한국경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K30" s="17" t="n">
-        <v/>
+          <t>Google 급상승 검색어 등장 (US) / 매일경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K30" s="17" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
-      <c r="A31" s="15" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="B31" s="15" t="n">
+      <c r="A31" s="20" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B31" s="20" t="n">
         <v>18</v>
       </c>
-      <c r="C31" s="16" t="inlineStr">
-        <is>
-          <t>대한항공</t>
-        </is>
-      </c>
-      <c r="D31" s="15" t="n">
-        <v>7</v>
-      </c>
-      <c r="E31" s="15" t="n">
-        <v>7</v>
-      </c>
-      <c r="F31" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G31" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H31" s="18" t="n">
-        <v>-2.82</v>
-      </c>
-      <c r="I31" s="19" t="n">
-        <v>6.37</v>
-      </c>
-      <c r="J31" s="17" t="inlineStr">
-        <is>
-          <t>중요공시 3건 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K31" s="17" t="inlineStr">
+      <c r="C31" s="21" t="inlineStr">
+        <is>
+          <t>모바일어플라이언스</t>
+        </is>
+      </c>
+      <c r="D31" s="20" t="n">
+        <v>6</v>
+      </c>
+      <c r="E31" s="20" t="n">
+        <v>3</v>
+      </c>
+      <c r="F31" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" s="20" t="n">
+        <v>3</v>
+      </c>
+      <c r="H31" s="22" t="n">
+        <v>-29.89</v>
+      </c>
+      <c r="I31" s="22" t="n">
+        <v>-15.87</v>
+      </c>
+      <c r="J31" s="23" t="inlineStr">
+        <is>
+          <t>중요공시 3건 / 중요공시 7일 +200%</t>
+        </is>
+      </c>
+      <c r="K31" s="23" t="inlineStr">
         <is>
           <t>공시</t>
         </is>
@@ -1686,7 +1684,7 @@
     <row r="32" ht="18" customHeight="1">
       <c r="A32" s="20" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B32" s="20" t="n">
@@ -1694,40 +1692,42 @@
       </c>
       <c r="C32" s="21" t="inlineStr">
         <is>
-          <t>스트라드비젼</t>
+          <t>스피어</t>
         </is>
       </c>
       <c r="D32" s="20" t="n">
         <v>6</v>
       </c>
       <c r="E32" s="20" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F32" s="20" t="n">
         <v>0</v>
       </c>
       <c r="G32" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H32" s="20" t="n">
-        <v/>
-      </c>
-      <c r="I32" s="20" t="n">
-        <v/>
-      </c>
-      <c r="J32" s="22" t="inlineStr">
-        <is>
-          <t>매일경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K32" s="22" t="n">
-        <v/>
+        <v>3</v>
+      </c>
+      <c r="H32" s="24" t="n">
+        <v>20.13</v>
+      </c>
+      <c r="I32" s="24" t="n">
+        <v>31.07</v>
+      </c>
+      <c r="J32" s="23" t="inlineStr">
+        <is>
+          <t>중요공시 7건 / 중요공시 7일 +250%</t>
+        </is>
+      </c>
+      <c r="K32" s="23" t="inlineStr">
+        <is>
+          <t>공시</t>
+        </is>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
       <c r="A33" s="20" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B33" s="20" t="n">
@@ -1735,7 +1735,7 @@
       </c>
       <c r="C33" s="21" t="inlineStr">
         <is>
-          <t>모바일어플라이언스</t>
+          <t>파두</t>
         </is>
       </c>
       <c r="D33" s="20" t="n">
@@ -1750,18 +1750,18 @@
       <c r="G33" s="20" t="n">
         <v>3</v>
       </c>
-      <c r="H33" s="23" t="n">
-        <v>29.9</v>
-      </c>
-      <c r="I33" s="23" t="n">
-        <v>17.76</v>
-      </c>
-      <c r="J33" s="22" t="inlineStr">
-        <is>
-          <t>중요공시 3건 / 중요공시 7일 +200%</t>
-        </is>
-      </c>
-      <c r="K33" s="22" t="inlineStr">
+      <c r="H33" s="22" t="n">
+        <v>-5.6</v>
+      </c>
+      <c r="I33" s="22" t="n">
+        <v>-4.29</v>
+      </c>
+      <c r="J33" s="23" t="inlineStr">
+        <is>
+          <t>중요공시 4건 / 중요공시 7일 +100%</t>
+        </is>
+      </c>
+      <c r="K33" s="23" t="inlineStr">
         <is>
           <t>공시</t>
         </is>
@@ -1770,7 +1770,7 @@
     <row r="34" ht="18" customHeight="1">
       <c r="A34" s="20" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B34" s="20" t="n">
@@ -1778,7 +1778,7 @@
       </c>
       <c r="C34" s="21" t="inlineStr">
         <is>
-          <t>성호전자</t>
+          <t>HJ중공업</t>
         </is>
       </c>
       <c r="D34" s="20" t="n">
@@ -1793,18 +1793,18 @@
       <c r="G34" s="20" t="n">
         <v>3</v>
       </c>
-      <c r="H34" s="23" t="n">
-        <v>4.22</v>
-      </c>
-      <c r="I34" s="24" t="n">
-        <v>-5.57</v>
-      </c>
-      <c r="J34" s="22" t="inlineStr">
-        <is>
-          <t>중요공시 3건 / 중요공시 7일 +200%</t>
-        </is>
-      </c>
-      <c r="K34" s="22" t="inlineStr">
+      <c r="H34" s="24" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="I34" s="22" t="n">
+        <v>-2.4</v>
+      </c>
+      <c r="J34" s="23" t="inlineStr">
+        <is>
+          <t>중요공시 3건 / 중요공시 7일 +50%</t>
+        </is>
+      </c>
+      <c r="K34" s="23" t="inlineStr">
         <is>
           <t>공시</t>
         </is>
@@ -1813,7 +1813,7 @@
     <row r="35" ht="18" customHeight="1">
       <c r="A35" s="20" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B35" s="20" t="n">
@@ -1821,42 +1821,42 @@
       </c>
       <c r="C35" s="21" t="inlineStr">
         <is>
-          <t>스피어</t>
+          <t>제약</t>
         </is>
       </c>
       <c r="D35" s="20" t="n">
         <v>6</v>
       </c>
       <c r="E35" s="20" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F35" s="20" t="n">
         <v>0</v>
       </c>
       <c r="G35" s="20" t="n">
-        <v>3</v>
-      </c>
-      <c r="H35" s="23" t="n">
-        <v>14.74</v>
-      </c>
-      <c r="I35" s="23" t="n">
-        <v>17.51</v>
-      </c>
-      <c r="J35" s="22" t="inlineStr">
-        <is>
-          <t>중요공시 7건 / 중요공시 7일 +250%</t>
-        </is>
-      </c>
-      <c r="K35" s="22" t="inlineStr">
-        <is>
-          <t>공시</t>
+        <v>0</v>
+      </c>
+      <c r="H35" s="20" t="n">
+        <v/>
+      </c>
+      <c r="I35" s="20" t="n">
+        <v/>
+      </c>
+      <c r="J35" s="23" t="inlineStr">
+        <is>
+          <t>매일경제 기사 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 기사 언급</t>
+        </is>
+      </c>
+      <c r="K35" s="23" t="inlineStr">
+        <is>
+          <t>네이버</t>
         </is>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
       <c r="A36" s="20" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B36" s="20" t="n">
@@ -1864,42 +1864,42 @@
       </c>
       <c r="C36" s="21" t="inlineStr">
         <is>
-          <t>파두</t>
+          <t>로봇</t>
         </is>
       </c>
       <c r="D36" s="20" t="n">
         <v>6</v>
       </c>
       <c r="E36" s="20" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F36" s="20" t="n">
         <v>0</v>
       </c>
       <c r="G36" s="20" t="n">
-        <v>3</v>
-      </c>
-      <c r="H36" s="23" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="I36" s="24" t="n">
-        <v>-2.56</v>
-      </c>
-      <c r="J36" s="22" t="inlineStr">
-        <is>
-          <t>중요공시 4건 / 중요공시 7일 +100%</t>
-        </is>
-      </c>
-      <c r="K36" s="22" t="inlineStr">
-        <is>
-          <t>공시</t>
+        <v>0</v>
+      </c>
+      <c r="H36" s="20" t="n">
+        <v/>
+      </c>
+      <c r="I36" s="20" t="n">
+        <v/>
+      </c>
+      <c r="J36" s="23" t="inlineStr">
+        <is>
+          <t>매일경제 헤드라인 언급 / 매일경제 기사 언급 / 네이버뉴스 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K36" s="23" t="inlineStr">
+        <is>
+          <t>네이버</t>
         </is>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
       <c r="A37" s="20" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B37" s="20" t="n">
@@ -1907,42 +1907,42 @@
       </c>
       <c r="C37" s="21" t="inlineStr">
         <is>
-          <t>차바이오텍</t>
+          <t>클라우드</t>
         </is>
       </c>
       <c r="D37" s="20" t="n">
         <v>6</v>
       </c>
       <c r="E37" s="20" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F37" s="20" t="n">
         <v>0</v>
       </c>
       <c r="G37" s="20" t="n">
-        <v>3</v>
-      </c>
-      <c r="H37" s="24" t="n">
-        <v>-6.46</v>
-      </c>
-      <c r="I37" s="24" t="n">
-        <v>-5.32</v>
-      </c>
-      <c r="J37" s="22" t="inlineStr">
-        <is>
-          <t>중요공시 4건 / 중요공시 7일 +300%</t>
-        </is>
-      </c>
-      <c r="K37" s="22" t="inlineStr">
-        <is>
-          <t>공시</t>
+        <v>0</v>
+      </c>
+      <c r="H37" s="20" t="n">
+        <v/>
+      </c>
+      <c r="I37" s="20" t="n">
+        <v/>
+      </c>
+      <c r="J37" s="23" t="inlineStr">
+        <is>
+          <t>네이버뉴스 헤드라인 언급 / 한국경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K37" s="23" t="inlineStr">
+        <is>
+          <t>네이버</t>
         </is>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
       <c r="A38" s="20" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B38" s="20" t="n">
@@ -1950,33 +1950,33 @@
       </c>
       <c r="C38" s="21" t="inlineStr">
         <is>
-          <t>HJ중공업</t>
+          <t>삼호개발</t>
         </is>
       </c>
       <c r="D38" s="20" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E38" s="20" t="n">
         <v>3</v>
       </c>
       <c r="F38" s="20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G38" s="20" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H38" s="24" t="n">
-        <v>-10.24</v>
-      </c>
-      <c r="I38" s="23" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="J38" s="22" t="inlineStr">
-        <is>
-          <t>중요공시 3건 / 중요공시 7일 +50%</t>
-        </is>
-      </c>
-      <c r="K38" s="22" t="inlineStr">
+        <v>29.91</v>
+      </c>
+      <c r="I38" s="24" t="n">
+        <v>38.63</v>
+      </c>
+      <c r="J38" s="23" t="inlineStr">
+        <is>
+          <t>중요공시 6건 / 중요공시 3일 +100%</t>
+        </is>
+      </c>
+      <c r="K38" s="23" t="inlineStr">
         <is>
           <t>공시</t>
         </is>
@@ -1985,7 +1985,7 @@
     <row r="39" ht="18" customHeight="1">
       <c r="A39" s="20" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B39" s="20" t="n">
@@ -1993,42 +1993,40 @@
       </c>
       <c r="C39" s="21" t="inlineStr">
         <is>
-          <t>페니트리움바이오</t>
+          <t>대한전선</t>
         </is>
       </c>
       <c r="D39" s="20" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E39" s="20" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F39" s="20" t="n">
         <v>0</v>
       </c>
       <c r="G39" s="20" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H39" s="24" t="n">
-        <v>-1.54</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="I39" s="24" t="n">
-        <v>-2.74</v>
-      </c>
-      <c r="J39" s="22" t="inlineStr">
-        <is>
-          <t>중요공시 3건 / 중요공시 7일 +200%</t>
-        </is>
-      </c>
-      <c r="K39" s="22" t="inlineStr">
-        <is>
-          <t>공시</t>
-        </is>
+        <v>7.76</v>
+      </c>
+      <c r="J39" s="23" t="inlineStr">
+        <is>
+          <t>매일경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K39" s="23" t="n">
+        <v/>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
       <c r="A40" s="20" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B40" s="20" t="n">
@@ -2036,14 +2034,14 @@
       </c>
       <c r="C40" s="21" t="inlineStr">
         <is>
-          <t>DB</t>
+          <t>롯데손해보험</t>
         </is>
       </c>
       <c r="D40" s="20" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E40" s="20" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F40" s="20" t="n">
         <v>0</v>
@@ -2051,25 +2049,27 @@
       <c r="G40" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H40" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="I40" s="23" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="J40" s="22" t="inlineStr">
-        <is>
-          <t>한국경제 헤드라인 언급 / 매일경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K40" s="22" t="n">
-        <v/>
+      <c r="H40" s="22" t="n">
+        <v>-7.03</v>
+      </c>
+      <c r="I40" s="24" t="n">
+        <v>21.73</v>
+      </c>
+      <c r="J40" s="23" t="inlineStr">
+        <is>
+          <t>Google 급상승 검색어 등장 (KR)</t>
+        </is>
+      </c>
+      <c r="K40" s="23" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
       <c r="A41" s="20" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B41" s="20" t="n">
@@ -2077,14 +2077,14 @@
       </c>
       <c r="C41" s="21" t="inlineStr">
         <is>
-          <t>스테이블코인</t>
+          <t>한화손해보험</t>
         </is>
       </c>
       <c r="D41" s="20" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E41" s="20" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F41" s="20" t="n">
         <v>0</v>
@@ -2092,25 +2092,27 @@
       <c r="G41" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H41" s="20" t="n">
-        <v/>
-      </c>
-      <c r="I41" s="20" t="n">
-        <v/>
-      </c>
-      <c r="J41" s="22" t="inlineStr">
-        <is>
-          <t>매일경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K41" s="22" t="n">
-        <v/>
+      <c r="H41" s="22" t="n">
+        <v>-2.37</v>
+      </c>
+      <c r="I41" s="22" t="n">
+        <v>-0.86</v>
+      </c>
+      <c r="J41" s="23" t="inlineStr">
+        <is>
+          <t>Google 급상승 검색어 등장 (KR)</t>
+        </is>
+      </c>
+      <c r="K41" s="23" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
       <c r="A42" s="20" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B42" s="20" t="n">
@@ -2118,7 +2120,7 @@
       </c>
       <c r="C42" s="21" t="inlineStr">
         <is>
-          <t>아크솔루션스</t>
+          <t>에코프로머티</t>
         </is>
       </c>
       <c r="D42" s="20" t="n">
@@ -2133,27 +2135,27 @@
       <c r="G42" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H42" s="23" t="n">
-        <v>0.87</v>
-      </c>
-      <c r="I42" s="24" t="n">
-        <v>-97.38</v>
-      </c>
-      <c r="J42" s="22" t="inlineStr">
-        <is>
-          <t>네이버 검색 당일 +91% / 중요공시 3건</t>
-        </is>
-      </c>
-      <c r="K42" s="22" t="inlineStr">
-        <is>
-          <t>네이버, 공시</t>
+      <c r="H42" s="22" t="n">
+        <v>-6.47</v>
+      </c>
+      <c r="I42" s="22" t="n">
+        <v>-11.42</v>
+      </c>
+      <c r="J42" s="23" t="inlineStr">
+        <is>
+          <t>Google 급상승 검색어 등장 (KR)</t>
+        </is>
+      </c>
+      <c r="K42" s="23" t="inlineStr">
+        <is>
+          <t>Google</t>
         </is>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1">
       <c r="A43" s="20" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B43" s="20" t="n">
@@ -2161,7 +2163,7 @@
       </c>
       <c r="C43" s="21" t="inlineStr">
         <is>
-          <t>KB금융</t>
+          <t>에코프로에이치엔</t>
         </is>
       </c>
       <c r="D43" s="20" t="n">
@@ -2176,27 +2178,27 @@
       <c r="G43" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H43" s="23" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="I43" s="23" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="J43" s="22" t="inlineStr">
-        <is>
-          <t>중요공시 1건 / 매일경제 헤드라인 언급 / 매일경제 기사 언급</t>
-        </is>
-      </c>
-      <c r="K43" s="22" t="inlineStr">
-        <is>
-          <t>공시</t>
+      <c r="H43" s="22" t="n">
+        <v>-4.41</v>
+      </c>
+      <c r="I43" s="24" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="J43" s="23" t="inlineStr">
+        <is>
+          <t>Google 급상승 검색어 등장 (KR)</t>
+        </is>
+      </c>
+      <c r="K43" s="23" t="inlineStr">
+        <is>
+          <t>Google</t>
         </is>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
       <c r="A44" s="20" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B44" s="20" t="n">
@@ -2204,7 +2206,7 @@
       </c>
       <c r="C44" s="21" t="inlineStr">
         <is>
-          <t>NH투자증권</t>
+          <t>포스코DX</t>
         </is>
       </c>
       <c r="D44" s="20" t="n">
@@ -2219,25 +2221,27 @@
       <c r="G44" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H44" s="23" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="I44" s="23" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="J44" s="22" t="inlineStr">
-        <is>
-          <t>매일경제 기사 언급 / 한국경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K44" s="22" t="n">
-        <v/>
+      <c r="H44" s="24" t="n">
+        <v>4.85</v>
+      </c>
+      <c r="I44" s="24" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="J44" s="23" t="inlineStr">
+        <is>
+          <t>Google 급상승 검색어 등장 (KR)</t>
+        </is>
+      </c>
+      <c r="K44" s="23" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
       <c r="A45" s="20" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B45" s="20" t="n">
@@ -2245,14 +2249,14 @@
       </c>
       <c r="C45" s="21" t="inlineStr">
         <is>
-          <t>골프존홀딩스</t>
+          <t>포스코퓨처엠</t>
         </is>
       </c>
       <c r="D45" s="20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E45" s="20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F45" s="20" t="n">
         <v>0</v>
@@ -2260,27 +2264,27 @@
       <c r="G45" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H45" s="23" t="n">
-        <v>19.89</v>
-      </c>
-      <c r="I45" s="23" t="n">
-        <v>47.66</v>
-      </c>
-      <c r="J45" s="22" t="inlineStr">
-        <is>
-          <t>네이버 검색 당일 +369% / 중요공시 1건</t>
-        </is>
-      </c>
-      <c r="K45" s="22" t="inlineStr">
-        <is>
-          <t>네이버, 공시</t>
+      <c r="H45" s="22" t="n">
+        <v>-3.08</v>
+      </c>
+      <c r="I45" s="22" t="n">
+        <v>-4.44</v>
+      </c>
+      <c r="J45" s="23" t="inlineStr">
+        <is>
+          <t>Google 급상승 검색어 등장 (KR)</t>
+        </is>
+      </c>
+      <c r="K45" s="23" t="inlineStr">
+        <is>
+          <t>Google</t>
         </is>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
       <c r="A46" s="20" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B46" s="20" t="n">
@@ -2288,42 +2292,42 @@
       </c>
       <c r="C46" s="21" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>포스코인터내셔널</t>
         </is>
       </c>
       <c r="D46" s="20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E46" s="20" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F46" s="20" t="n">
         <v>0</v>
       </c>
       <c r="G46" s="20" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H46" s="24" t="n">
-        <v>-4.9</v>
+        <v>4.37</v>
       </c>
       <c r="I46" s="24" t="n">
-        <v>-2.79</v>
-      </c>
-      <c r="J46" s="22" t="inlineStr">
-        <is>
-          <t>중요공시 2건 / 중요공시 7일 +100%</t>
-        </is>
-      </c>
-      <c r="K46" s="22" t="inlineStr">
-        <is>
-          <t>공시</t>
+        <v>1.58</v>
+      </c>
+      <c r="J46" s="23" t="inlineStr">
+        <is>
+          <t>Google 급상승 검색어 등장 (KR)</t>
+        </is>
+      </c>
+      <c r="K46" s="23" t="inlineStr">
+        <is>
+          <t>Google</t>
         </is>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
       <c r="A47" s="20" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B47" s="20" t="n">
@@ -2331,42 +2335,42 @@
       </c>
       <c r="C47" s="21" t="inlineStr">
         <is>
-          <t>한화엔진</t>
+          <t>포스코스틸리온</t>
         </is>
       </c>
       <c r="D47" s="20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E47" s="20" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F47" s="20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G47" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H47" s="24" t="n">
-        <v>-0.97</v>
-      </c>
-      <c r="I47" s="24" t="n">
-        <v>-4.67</v>
-      </c>
-      <c r="J47" s="22" t="inlineStr">
-        <is>
-          <t>중요공시 2건 / 중요공시 3일 +100% / 매일경제 기사 언급</t>
-        </is>
-      </c>
-      <c r="K47" s="22" t="inlineStr">
-        <is>
-          <t>공시</t>
+      <c r="H47" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I47" s="22" t="n">
+        <v>-2.65</v>
+      </c>
+      <c r="J47" s="23" t="inlineStr">
+        <is>
+          <t>Google 급상승 검색어 등장 (KR)</t>
+        </is>
+      </c>
+      <c r="K47" s="23" t="inlineStr">
+        <is>
+          <t>Google</t>
         </is>
       </c>
     </row>
     <row r="48" ht="18" customHeight="1">
       <c r="A48" s="20" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B48" s="20" t="n">
@@ -2374,14 +2378,14 @@
       </c>
       <c r="C48" s="21" t="inlineStr">
         <is>
-          <t>CMG제약</t>
+          <t>DB</t>
         </is>
       </c>
       <c r="D48" s="20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E48" s="20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F48" s="20" t="n">
         <v>0</v>
@@ -2389,27 +2393,27 @@
       <c r="G48" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H48" s="24" t="n">
-        <v>-2.86</v>
-      </c>
-      <c r="I48" s="23" t="n">
-        <v>3.79</v>
-      </c>
-      <c r="J48" s="22" t="inlineStr">
-        <is>
-          <t>중요공시 1건 / 매일경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K48" s="22" t="inlineStr">
-        <is>
-          <t>공시</t>
+      <c r="H48" s="22" t="n">
+        <v>-1.21</v>
+      </c>
+      <c r="I48" s="24" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="J48" s="23" t="inlineStr">
+        <is>
+          <t>한국경제 헤드라인 언급 / 네이버뉴스 기사 언급 / 매일경제 기사 언급</t>
+        </is>
+      </c>
+      <c r="K48" s="23" t="inlineStr">
+        <is>
+          <t>네이버</t>
         </is>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1">
       <c r="A49" s="20" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B49" s="20" t="n">
@@ -2417,7 +2421,7 @@
       </c>
       <c r="C49" s="21" t="inlineStr">
         <is>
-          <t>카카오뱅크</t>
+          <t>아크솔루션스</t>
         </is>
       </c>
       <c r="D49" s="20" t="n">
@@ -2432,27 +2436,27 @@
       <c r="G49" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H49" s="24" t="n">
-        <v>-1.18</v>
-      </c>
-      <c r="I49" s="23" t="n">
-        <v>3.21</v>
-      </c>
-      <c r="J49" s="22" t="inlineStr">
-        <is>
-          <t>중요공시 1건 / 매일경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K49" s="22" t="inlineStr">
-        <is>
-          <t>공시</t>
+      <c r="H49" s="22" t="n">
+        <v>-22.41</v>
+      </c>
+      <c r="I49" s="22" t="n">
+        <v>-97.97</v>
+      </c>
+      <c r="J49" s="23" t="inlineStr">
+        <is>
+          <t>네이버 검색 당일 +181% / 중요공시 2건</t>
+        </is>
+      </c>
+      <c r="K49" s="23" t="inlineStr">
+        <is>
+          <t>공시, 네이버</t>
         </is>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
       <c r="A50" s="20" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B50" s="20" t="n">
@@ -2460,7 +2464,7 @@
       </c>
       <c r="C50" s="21" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>GS건설</t>
         </is>
       </c>
       <c r="D50" s="20" t="n">
@@ -2476,237 +2480,241 @@
         <v>0</v>
       </c>
       <c r="H50" s="24" t="n">
-        <v>-2.19</v>
-      </c>
-      <c r="I50" s="23" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="J50" s="22" t="inlineStr">
-        <is>
-          <t>매일경제 헤드라인 언급 / 매일경제 기사 언급</t>
-        </is>
-      </c>
-      <c r="K50" s="22" t="n">
+        <v>19.92</v>
+      </c>
+      <c r="I50" s="24" t="n">
+        <v>20.16</v>
+      </c>
+      <c r="J50" s="23" t="inlineStr">
+        <is>
+          <t>중요공시 1건 / 매일경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K50" s="23" t="inlineStr">
+        <is>
+          <t>공시</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="18" customHeight="1">
+      <c r="A51" s="20" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B51" s="20" t="n">
+        <v>38</v>
+      </c>
+      <c r="C51" s="21" t="inlineStr">
+        <is>
+          <t>성호전자</t>
+        </is>
+      </c>
+      <c r="D51" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="E51" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="F51" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G51" s="20" t="n">
+        <v>3</v>
+      </c>
+      <c r="H51" s="24" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="I51" s="24" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="J51" s="23" t="inlineStr">
+        <is>
+          <t>중요공시 2건 / 중요공시 7일 +100%</t>
+        </is>
+      </c>
+      <c r="K51" s="23" t="inlineStr">
+        <is>
+          <t>공시</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="18" customHeight="1">
+      <c r="A52" s="20" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B52" s="20" t="n">
+        <v>39</v>
+      </c>
+      <c r="C52" s="21" t="inlineStr">
+        <is>
+          <t>대우건설</t>
+        </is>
+      </c>
+      <c r="D52" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="E52" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="F52" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G52" s="20" t="n">
+        <v>3</v>
+      </c>
+      <c r="H52" s="24" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="I52" s="22" t="n">
+        <v>-0.31</v>
+      </c>
+      <c r="J52" s="23" t="inlineStr">
+        <is>
+          <t>중요공시 2건 / 중요공시 7일 +100%</t>
+        </is>
+      </c>
+      <c r="K52" s="23" t="inlineStr">
+        <is>
+          <t>공시</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="18" customHeight="1">
+      <c r="A53" s="20" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B53" s="20" t="n">
+        <v>40</v>
+      </c>
+      <c r="C53" s="21" t="inlineStr">
+        <is>
+          <t>에임드바이오</t>
+        </is>
+      </c>
+      <c r="D53" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="E53" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="F53" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G53" s="20" t="n">
+        <v>3</v>
+      </c>
+      <c r="H53" s="24" t="n">
+        <v>7.17</v>
+      </c>
+      <c r="I53" s="24" t="n">
+        <v>7.39</v>
+      </c>
+      <c r="J53" s="23" t="inlineStr">
+        <is>
+          <t>중요공시 2건 / 중요공시 7일 +100%</t>
+        </is>
+      </c>
+      <c r="K53" s="23" t="inlineStr">
+        <is>
+          <t>공시</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="18" customHeight="1">
+      <c r="A54" s="20" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B54" s="20" t="n">
+        <v>41</v>
+      </c>
+      <c r="C54" s="21" t="inlineStr">
+        <is>
+          <t>HD현대중공업</t>
+        </is>
+      </c>
+      <c r="D54" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="E54" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="F54" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G54" s="20" t="n">
+        <v>3</v>
+      </c>
+      <c r="H54" s="24" t="n">
+        <v>3.89</v>
+      </c>
+      <c r="I54" s="24" t="n">
+        <v>4.77</v>
+      </c>
+      <c r="J54" s="23" t="inlineStr">
+        <is>
+          <t>중요공시 2건 / 중요공시 7일 +100%</t>
+        </is>
+      </c>
+      <c r="K54" s="23" t="inlineStr">
+        <is>
+          <t>공시</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="18" customHeight="1">
+      <c r="A55" s="20" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B55" s="20" t="n">
+        <v>42</v>
+      </c>
+      <c r="C55" s="21" t="inlineStr">
+        <is>
+          <t>철강</t>
+        </is>
+      </c>
+      <c r="D55" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="E55" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="F55" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G55" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H55" s="20" t="n">
         <v/>
       </c>
-    </row>
-    <row r="51" ht="18" customHeight="1">
-      <c r="A51" s="25" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="B51" s="25" t="n">
-        <v>38</v>
-      </c>
-      <c r="C51" s="26" t="inlineStr">
-        <is>
-          <t>져스텍</t>
-        </is>
-      </c>
-      <c r="D51" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="E51" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="F51" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="G51" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="H51" s="27" t="n">
-        <v>-5.08</v>
-      </c>
-      <c r="I51" s="27" t="n">
-        <v>-5.08</v>
-      </c>
-      <c r="J51" s="28" t="inlineStr">
-        <is>
-          <t>네이버 검색 당일 +476%</t>
-        </is>
-      </c>
-      <c r="K51" s="28" t="inlineStr">
+      <c r="I55" s="20" t="n">
+        <v/>
+      </c>
+      <c r="J55" s="23" t="inlineStr">
+        <is>
+          <t>매일경제 헤드라인 언급 / 네이버뉴스 기사 언급</t>
+        </is>
+      </c>
+      <c r="K55" s="23" t="inlineStr">
         <is>
           <t>네이버</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="18" customHeight="1">
-      <c r="A52" s="25" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="B52" s="25" t="n">
-        <v>39</v>
-      </c>
-      <c r="C52" s="26" t="inlineStr">
-        <is>
-          <t>앱튼</t>
-        </is>
-      </c>
-      <c r="D52" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="E52" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="F52" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="G52" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="H52" s="29" t="n">
-        <v>29.72</v>
-      </c>
-      <c r="I52" s="29" t="n">
-        <v>180.8</v>
-      </c>
-      <c r="J52" s="28" t="inlineStr">
-        <is>
-          <t>중요공시 5건</t>
-        </is>
-      </c>
-      <c r="K52" s="28" t="inlineStr">
-        <is>
-          <t>공시</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="18" customHeight="1">
-      <c r="A53" s="25" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="B53" s="25" t="n">
-        <v>40</v>
-      </c>
-      <c r="C53" s="26" t="inlineStr">
-        <is>
-          <t>지니너스</t>
-        </is>
-      </c>
-      <c r="D53" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="E53" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="F53" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="G53" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="H53" s="29" t="n">
-        <v>6.75</v>
-      </c>
-      <c r="I53" s="29" t="n">
-        <v>11.87</v>
-      </c>
-      <c r="J53" s="28" t="inlineStr">
-        <is>
-          <t>매일경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K53" s="28" t="n">
-        <v/>
-      </c>
-    </row>
-    <row r="54" ht="18" customHeight="1">
-      <c r="A54" s="25" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="B54" s="25" t="n">
-        <v>41</v>
-      </c>
-      <c r="C54" s="26" t="inlineStr">
-        <is>
-          <t>우리금융지주</t>
-        </is>
-      </c>
-      <c r="D54" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="E54" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="F54" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="G54" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="H54" s="27" t="n">
-        <v>-0.34</v>
-      </c>
-      <c r="I54" s="27" t="n">
-        <v>-1.53</v>
-      </c>
-      <c r="J54" s="28" t="inlineStr">
-        <is>
-          <t>네이버뉴스 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K54" s="28" t="inlineStr">
-        <is>
-          <t>네이버</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="18" customHeight="1">
-      <c r="A55" s="25" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="B55" s="25" t="n">
-        <v>42</v>
-      </c>
-      <c r="C55" s="26" t="inlineStr">
-        <is>
-          <t>SK스퀘어</t>
-        </is>
-      </c>
-      <c r="D55" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="E55" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="F55" s="25" t="n">
-        <v>2</v>
-      </c>
-      <c r="G55" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="H55" s="29" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="I55" s="27" t="n">
-        <v>-7.37</v>
-      </c>
-      <c r="J55" s="28" t="inlineStr">
-        <is>
-          <t>중요공시 2건 / 중요공시 3일 +100%</t>
-        </is>
-      </c>
-      <c r="K55" s="28" t="inlineStr">
-        <is>
-          <t>공시</t>
         </is>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1">
       <c r="A56" s="25" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B56" s="25" t="n">
@@ -2714,7 +2722,7 @@
       </c>
       <c r="C56" s="26" t="inlineStr">
         <is>
-          <t>에이프릴바이오</t>
+          <t>져스텍</t>
         </is>
       </c>
       <c r="D56" s="25" t="n">
@@ -2730,26 +2738,26 @@
         <v>0</v>
       </c>
       <c r="H56" s="27" t="n">
-        <v>-4.81</v>
-      </c>
-      <c r="I56" s="29" t="n">
-        <v>18.05</v>
+        <v>-10.7</v>
+      </c>
+      <c r="I56" s="27" t="n">
+        <v>-15.23</v>
       </c>
       <c r="J56" s="28" t="inlineStr">
         <is>
-          <t>중요공시 5건</t>
+          <t>네이버 검색 당일 +600%</t>
         </is>
       </c>
       <c r="K56" s="28" t="inlineStr">
         <is>
-          <t>공시</t>
+          <t>네이버</t>
         </is>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1">
       <c r="A57" s="25" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B57" s="25" t="n">
@@ -2757,7 +2765,7 @@
       </c>
       <c r="C57" s="26" t="inlineStr">
         <is>
-          <t>CSA 코스믹</t>
+          <t>스트라드비젼</t>
         </is>
       </c>
       <c r="D57" s="25" t="n">
@@ -2773,26 +2781,26 @@
         <v>0</v>
       </c>
       <c r="H57" s="27" t="n">
-        <v>-1.67</v>
+        <v>-18.89</v>
       </c>
       <c r="I57" s="27" t="n">
-        <v>-7.81</v>
+        <v>-18.89</v>
       </c>
       <c r="J57" s="28" t="inlineStr">
         <is>
-          <t>중요공시 4건</t>
+          <t>네이버 검색 당일 +291%</t>
         </is>
       </c>
       <c r="K57" s="28" t="inlineStr">
         <is>
-          <t>공시</t>
+          <t>네이버</t>
         </is>
       </c>
     </row>
     <row r="58" ht="18" customHeight="1">
       <c r="A58" s="25" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B58" s="25" t="n">
@@ -2800,7 +2808,7 @@
       </c>
       <c r="C58" s="26" t="inlineStr">
         <is>
-          <t>플리토</t>
+          <t>에스폴리텍</t>
         </is>
       </c>
       <c r="D58" s="25" t="n">
@@ -2816,26 +2824,26 @@
         <v>0</v>
       </c>
       <c r="H58" s="29" t="n">
-        <v>5.48</v>
+        <v>4.07</v>
       </c>
       <c r="I58" s="29" t="n">
-        <v>24.19</v>
+        <v>30.19</v>
       </c>
       <c r="J58" s="28" t="inlineStr">
         <is>
-          <t>중요공시 4건</t>
+          <t>네이버 검색 당일 +108%</t>
         </is>
       </c>
       <c r="K58" s="28" t="inlineStr">
         <is>
-          <t>공시</t>
+          <t>네이버</t>
         </is>
       </c>
     </row>
     <row r="59" ht="18" customHeight="1">
       <c r="A59" s="25" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B59" s="25" t="n">
@@ -2843,7 +2851,7 @@
       </c>
       <c r="C59" s="26" t="inlineStr">
         <is>
-          <t>삼호개발</t>
+          <t>금호건설</t>
         </is>
       </c>
       <c r="D59" s="25" t="n">
@@ -2858,27 +2866,27 @@
       <c r="G59" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H59" s="27" t="n">
-        <v>-9.699999999999999</v>
+      <c r="H59" s="29" t="n">
+        <v>29.94</v>
       </c>
       <c r="I59" s="29" t="n">
-        <v>7.24</v>
+        <v>200.1</v>
       </c>
       <c r="J59" s="28" t="inlineStr">
         <is>
-          <t>중요공시 3건</t>
+          <t>네이버 검색 당일 +79% / 중요공시 1건</t>
         </is>
       </c>
       <c r="K59" s="28" t="inlineStr">
         <is>
-          <t>공시</t>
+          <t>공시, 네이버</t>
         </is>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1">
       <c r="A60" s="25" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B60" s="25" t="n">
@@ -2886,7 +2894,7 @@
       </c>
       <c r="C60" s="26" t="inlineStr">
         <is>
-          <t>아모텍</t>
+          <t>금호전기</t>
         </is>
       </c>
       <c r="D60" s="25" t="n">
@@ -2901,27 +2909,27 @@
       <c r="G60" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H60" s="27" t="n">
-        <v>-3.35</v>
-      </c>
-      <c r="I60" s="27" t="n">
-        <v>-17.97</v>
+      <c r="H60" s="29" t="n">
+        <v>18.31</v>
+      </c>
+      <c r="I60" s="29" t="n">
+        <v>177.8</v>
       </c>
       <c r="J60" s="28" t="inlineStr">
         <is>
-          <t>중요공시 3건</t>
+          <t>네이버 검색 당일 +60% / 중요공시 2건</t>
         </is>
       </c>
       <c r="K60" s="28" t="inlineStr">
         <is>
-          <t>공시</t>
+          <t>공시, 네이버</t>
         </is>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
       <c r="A61" s="25" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B61" s="25" t="n">
@@ -2929,7 +2937,7 @@
       </c>
       <c r="C61" s="26" t="inlineStr">
         <is>
-          <t>대명에너지</t>
+          <t>앱튼</t>
         </is>
       </c>
       <c r="D61" s="25" t="n">
@@ -2944,15 +2952,15 @@
       <c r="G61" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H61" s="27" t="n">
-        <v>-9.93</v>
+      <c r="H61" s="29" t="n">
+        <v>15.94</v>
       </c>
       <c r="I61" s="29" t="n">
-        <v>25.67</v>
+        <v>230.26</v>
       </c>
       <c r="J61" s="28" t="inlineStr">
         <is>
-          <t>중요공시 3건</t>
+          <t>중요공시 4건</t>
         </is>
       </c>
       <c r="K61" s="28" t="inlineStr">
@@ -2964,7 +2972,7 @@
     <row r="62" ht="18" customHeight="1">
       <c r="A62" s="25" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B62" s="25" t="n">
@@ -2972,7 +2980,7 @@
       </c>
       <c r="C62" s="26" t="inlineStr">
         <is>
-          <t>클래시스</t>
+          <t>SK네트웍스</t>
         </is>
       </c>
       <c r="D62" s="25" t="n">
@@ -2987,27 +2995,25 @@
       <c r="G62" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H62" s="27" t="n">
-        <v>-5.57</v>
+      <c r="H62" s="29" t="n">
+        <v>2.39</v>
       </c>
       <c r="I62" s="29" t="n">
-        <v>6.27</v>
+        <v>7.97</v>
       </c>
       <c r="J62" s="28" t="inlineStr">
         <is>
-          <t>중요공시 3건</t>
-        </is>
-      </c>
-      <c r="K62" s="28" t="inlineStr">
-        <is>
-          <t>공시</t>
-        </is>
+          <t>매일경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K62" s="28" t="n">
+        <v/>
       </c>
     </row>
     <row r="63" ht="18" customHeight="1">
       <c r="A63" s="25" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B63" s="25" t="n">
@@ -3015,30 +3021,30 @@
       </c>
       <c r="C63" s="26" t="inlineStr">
         <is>
-          <t>뉴인텍</t>
+          <t>대한항공</t>
         </is>
       </c>
       <c r="D63" s="25" t="n">
         <v>3</v>
       </c>
       <c r="E63" s="25" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F63" s="25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G63" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H63" s="27" t="n">
-        <v>-13.78</v>
+      <c r="H63" s="29" t="n">
+        <v>0.91</v>
       </c>
       <c r="I63" s="29" t="n">
-        <v>8.859999999999999</v>
+        <v>1.65</v>
       </c>
       <c r="J63" s="28" t="inlineStr">
         <is>
-          <t>중요공시 2건 / 중요공시 3일 +100%</t>
+          <t>중요공시 3건</t>
         </is>
       </c>
       <c r="K63" s="28" t="inlineStr">
@@ -3140,22 +3146,22 @@
         <v>1</v>
       </c>
       <c r="C3" s="25" t="n">
-        <v>108</v>
+        <v>96</v>
       </c>
       <c r="D3" s="25" t="n">
-        <v>108</v>
+        <v>96</v>
       </c>
       <c r="E3" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F3" s="25" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G3" s="25" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="H3" s="25" t="n"/>
@@ -3164,301 +3170,301 @@
     <row r="4" ht="18" customHeight="1">
       <c r="A4" s="26" t="inlineStr">
         <is>
-          <t>로봇</t>
+          <t>SK</t>
         </is>
       </c>
       <c r="B4" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C4" s="25" t="n">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="D4" s="25" t="n">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="E4" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F4" s="25" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G4" s="25" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="H4" s="25" t="n"/>
-      <c r="I4" s="25" t="n"/>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="H4" s="27" t="n">
+        <v>-8.51</v>
+      </c>
+      <c r="I4" s="29" t="n">
+        <v>7.16</v>
+      </c>
     </row>
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="26" t="inlineStr">
         <is>
-          <t>현대차</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B5" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C5" s="25" t="n">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="D5" s="25" t="n">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="E5" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F5" s="25" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G5" s="25" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="H5" s="27" t="n">
-        <v>-0.4</v>
+        <v>-5.84</v>
       </c>
       <c r="I5" s="27" t="n">
-        <v>-3.13</v>
+        <v>-7.64</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
       <c r="A6" s="26" t="inlineStr">
         <is>
-          <t>SK</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B6" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C6" s="25" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="D6" s="25" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="E6" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F6" s="25" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G6" s="25" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="H6" s="29" t="n">
-        <v>6.24</v>
-      </c>
-      <c r="I6" s="29" t="n">
-        <v>18.3</v>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="H6" s="27" t="n">
+        <v>-3.4</v>
+      </c>
+      <c r="I6" s="27" t="n">
+        <v>-0.78</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
       <c r="A7" s="26" t="inlineStr">
         <is>
-          <t>인공지능</t>
+          <t>에코프로</t>
         </is>
       </c>
       <c r="B7" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C7" s="25" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D7" s="25" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E7" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F7" s="25" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G7" s="25" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="H7" s="25" t="n"/>
-      <c r="I7" s="25" t="n"/>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="H7" s="27" t="n">
+        <v>-12.76</v>
+      </c>
+      <c r="I7" s="27" t="n">
+        <v>-13.65</v>
+      </c>
     </row>
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="26" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>인공지능</t>
         </is>
       </c>
       <c r="B8" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C8" s="25" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="D8" s="25" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="E8" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F8" s="25" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G8" s="25" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="H8" s="29" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="I8" s="29" t="n">
-        <v>3.72</v>
-      </c>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="H8" s="25" t="n"/>
+      <c r="I8" s="25" t="n"/>
     </row>
     <row r="9" ht="18" customHeight="1">
       <c r="A9" s="26" t="inlineStr">
         <is>
-          <t>삼성전기</t>
+          <t>LG</t>
         </is>
       </c>
       <c r="B9" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C9" s="25" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D9" s="25" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E9" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F9" s="25" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G9" s="25" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="H9" s="29" t="n">
-        <v>7.16</v>
-      </c>
-      <c r="I9" s="29" t="n">
-        <v>9.75</v>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="H9" s="27" t="n">
+        <v>-0.72</v>
+      </c>
+      <c r="I9" s="27" t="n">
+        <v>-2.62</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
       <c r="A10" s="26" t="inlineStr">
         <is>
-          <t>에코프로</t>
+          <t>바이오</t>
         </is>
       </c>
       <c r="B10" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C10" s="25" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D10" s="25" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E10" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F10" s="25" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G10" s="25" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="H10" s="27" t="n">
-        <v>-9.66</v>
-      </c>
-      <c r="I10" s="29" t="n">
-        <v>3.5</v>
-      </c>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="H10" s="25" t="n"/>
+      <c r="I10" s="25" t="n"/>
     </row>
     <row r="11" ht="18" customHeight="1">
       <c r="A11" s="26" t="inlineStr">
         <is>
-          <t>LG</t>
+          <t>삼성전기</t>
         </is>
       </c>
       <c r="B11" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C11" s="25" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="D11" s="25" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E11" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F11" s="25" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G11" s="25" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="H11" s="27" t="n">
-        <v>-3.47</v>
-      </c>
-      <c r="I11" s="27" t="n">
-        <v>-1.32</v>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="H11" s="29" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="I11" s="29" t="n">
+        <v>12.27</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
       <c r="A12" s="26" t="inlineStr">
         <is>
-          <t>바이오</t>
+          <t>전기차</t>
         </is>
       </c>
       <c r="B12" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C12" s="25" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D12" s="25" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E12" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F12" s="25" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G12" s="25" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="H12" s="25" t="n"/>
@@ -3467,73 +3473,77 @@
     <row r="13" ht="18" customHeight="1">
       <c r="A13" s="26" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>에코프로비엠</t>
         </is>
       </c>
       <c r="B13" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C13" s="25" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D13" s="25" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E13" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F13" s="25" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G13" s="25" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="H13" s="29" t="n">
-        <v>3.41</v>
-      </c>
-      <c r="I13" s="29" t="n">
-        <v>7.74</v>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="H13" s="27" t="n">
+        <v>-6.88</v>
+      </c>
+      <c r="I13" s="27" t="n">
+        <v>-12.98</v>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="26" t="inlineStr">
         <is>
-          <t>철강</t>
+          <t>현대차</t>
         </is>
       </c>
       <c r="B14" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C14" s="25" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D14" s="25" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E14" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F14" s="25" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G14" s="25" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="H14" s="25" t="n"/>
-      <c r="I14" s="25" t="n"/>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="H14" s="27" t="n">
+        <v>-1.52</v>
+      </c>
+      <c r="I14" s="27" t="n">
+        <v>-4.22</v>
+      </c>
     </row>
     <row r="15" ht="18" customHeight="1">
       <c r="A15" s="26" t="inlineStr">
         <is>
-          <t>에코프로비엠</t>
+          <t>SK스퀘어</t>
         </is>
       </c>
       <c r="B15" s="25" t="n">
@@ -3550,47 +3560,47 @@
       </c>
       <c r="F15" s="25" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G15" s="25" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="H15" s="27" t="n">
-        <v>-7.77</v>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="H15" s="29" t="n">
+        <v>3.54</v>
       </c>
       <c r="I15" s="27" t="n">
-        <v>-5.57</v>
+        <v>-2.33</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
       <c r="A16" s="26" t="inlineStr">
         <is>
-          <t>제약</t>
+          <t>방산</t>
         </is>
       </c>
       <c r="B16" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C16" s="25" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D16" s="25" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E16" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F16" s="25" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G16" s="25" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="H16" s="25" t="n"/>
@@ -3599,7 +3609,7 @@
     <row r="17" ht="18" customHeight="1">
       <c r="A17" s="26" t="inlineStr">
         <is>
-          <t>KT</t>
+          <t>스테이블코인</t>
         </is>
       </c>
       <c r="B17" s="25" t="n">
@@ -3616,126 +3626,126 @@
       </c>
       <c r="F17" s="25" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G17" s="25" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="H17" s="29" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="I17" s="29" t="n">
-        <v>0.95</v>
-      </c>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="H17" s="25" t="n"/>
+      <c r="I17" s="25" t="n"/>
     </row>
     <row r="18" ht="18" customHeight="1">
       <c r="A18" s="26" t="inlineStr">
         <is>
-          <t>LG전자</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="B18" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C18" s="25" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D18" s="25" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E18" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F18" s="25" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G18" s="25" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="H18" s="29" t="n">
-        <v>3.2</v>
+        <v>10.11</v>
       </c>
       <c r="I18" s="29" t="n">
-        <v>0.5</v>
+        <v>10.44</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
       <c r="A19" s="26" t="inlineStr">
         <is>
-          <t>전기차</t>
+          <t>셀트리온</t>
         </is>
       </c>
       <c r="B19" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C19" s="25" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D19" s="25" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E19" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F19" s="25" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G19" s="25" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="H19" s="25" t="n"/>
-      <c r="I19" s="25" t="n"/>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="H19" s="29" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="I19" s="29" t="n">
+        <v>1.04</v>
+      </c>
     </row>
     <row r="20" ht="18" customHeight="1">
       <c r="A20" s="26" t="inlineStr">
         <is>
-          <t>대한항공</t>
+          <t>HJ중공업</t>
         </is>
       </c>
       <c r="B20" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C20" s="25" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D20" s="25" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E20" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F20" s="25" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G20" s="25" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="H20" s="27" t="n">
-        <v>-2.82</v>
-      </c>
-      <c r="I20" s="29" t="n">
-        <v>6.37</v>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="H20" s="29" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="I20" s="27" t="n">
+        <v>-2.4</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
       <c r="A21" s="26" t="inlineStr">
         <is>
-          <t>DB</t>
+          <t>로봇</t>
         </is>
       </c>
       <c r="B21" s="25" t="n">
@@ -3752,25 +3762,21 @@
       </c>
       <c r="F21" s="25" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G21" s="25" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="H21" s="29" t="n">
-        <v>1</v>
-      </c>
-      <c r="I21" s="29" t="n">
-        <v>1.11</v>
-      </c>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="H21" s="25" t="n"/>
+      <c r="I21" s="25" t="n"/>
     </row>
     <row r="22" ht="18" customHeight="1">
       <c r="A22" s="26" t="inlineStr">
         <is>
-          <t>HJ중공업</t>
+          <t>모바일어플라이언스</t>
         </is>
       </c>
       <c r="B22" s="25" t="n">
@@ -3787,25 +3793,25 @@
       </c>
       <c r="F22" s="25" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G22" s="25" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="H22" s="27" t="n">
-        <v>-10.24</v>
-      </c>
-      <c r="I22" s="29" t="n">
-        <v>2.81</v>
+        <v>-29.89</v>
+      </c>
+      <c r="I22" s="27" t="n">
+        <v>-15.87</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
       <c r="A23" s="26" t="inlineStr">
         <is>
-          <t>모바일어플라이언스</t>
+          <t>스피어</t>
         </is>
       </c>
       <c r="B23" s="25" t="n">
@@ -3822,25 +3828,25 @@
       </c>
       <c r="F23" s="25" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G23" s="25" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="H23" s="29" t="n">
-        <v>29.9</v>
+        <v>20.13</v>
       </c>
       <c r="I23" s="29" t="n">
-        <v>17.76</v>
+        <v>31.07</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
       <c r="A24" s="26" t="inlineStr">
         <is>
-          <t>성호전자</t>
+          <t>제약</t>
         </is>
       </c>
       <c r="B24" s="25" t="n">
@@ -3857,25 +3863,21 @@
       </c>
       <c r="F24" s="25" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G24" s="25" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="H24" s="29" t="n">
-        <v>4.22</v>
-      </c>
-      <c r="I24" s="27" t="n">
-        <v>-5.57</v>
-      </c>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="H24" s="25" t="n"/>
+      <c r="I24" s="25" t="n"/>
     </row>
     <row r="25" ht="18" customHeight="1">
       <c r="A25" s="26" t="inlineStr">
         <is>
-          <t>스테이블코인</t>
+          <t>클라우드</t>
         </is>
       </c>
       <c r="B25" s="25" t="n">
@@ -3892,12 +3894,12 @@
       </c>
       <c r="F25" s="25" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G25" s="25" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="H25" s="25" t="n"/>
@@ -3906,7 +3908,7 @@
     <row r="26" ht="18" customHeight="1">
       <c r="A26" s="26" t="inlineStr">
         <is>
-          <t>스트라드비젼</t>
+          <t>파두</t>
         </is>
       </c>
       <c r="B26" s="25" t="n">
@@ -3923,161 +3925,165 @@
       </c>
       <c r="F26" s="25" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G26" s="25" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="H26" s="25" t="n"/>
-      <c r="I26" s="25" t="n"/>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="H26" s="27" t="n">
+        <v>-5.6</v>
+      </c>
+      <c r="I26" s="27" t="n">
+        <v>-4.29</v>
+      </c>
     </row>
     <row r="27" ht="18" customHeight="1">
       <c r="A27" s="26" t="inlineStr">
         <is>
-          <t>스피어</t>
+          <t>DB</t>
         </is>
       </c>
       <c r="B27" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C27" s="25" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D27" s="25" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E27" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F27" s="25" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G27" s="25" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="H27" s="29" t="n">
-        <v>14.74</v>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="H27" s="27" t="n">
+        <v>-1.21</v>
       </c>
       <c r="I27" s="29" t="n">
-        <v>17.51</v>
+        <v>2.63</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
       <c r="A28" s="26" t="inlineStr">
         <is>
-          <t>차바이오텍</t>
+          <t>대한전선</t>
         </is>
       </c>
       <c r="B28" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C28" s="25" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D28" s="25" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E28" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F28" s="25" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G28" s="25" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="H28" s="27" t="n">
-        <v>-6.46</v>
-      </c>
-      <c r="I28" s="27" t="n">
-        <v>-5.32</v>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="H28" s="29" t="n">
+        <v>8.550000000000001</v>
+      </c>
+      <c r="I28" s="29" t="n">
+        <v>7.76</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
       <c r="A29" s="26" t="inlineStr">
         <is>
-          <t>파두</t>
+          <t>롯데손해보험</t>
         </is>
       </c>
       <c r="B29" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C29" s="25" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D29" s="25" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E29" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F29" s="25" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G29" s="25" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="H29" s="29" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="I29" s="27" t="n">
-        <v>-2.56</v>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="H29" s="27" t="n">
+        <v>-7.03</v>
+      </c>
+      <c r="I29" s="29" t="n">
+        <v>21.73</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
       <c r="A30" s="26" t="inlineStr">
         <is>
-          <t>페니트리움바이오</t>
+          <t>삼호개발</t>
         </is>
       </c>
       <c r="B30" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C30" s="25" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D30" s="25" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E30" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F30" s="25" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G30" s="25" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="H30" s="27" t="n">
-        <v>-1.54</v>
-      </c>
-      <c r="I30" s="27" t="n">
-        <v>-2.74</v>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="H30" s="29" t="n">
+        <v>29.91</v>
+      </c>
+      <c r="I30" s="29" t="n">
+        <v>38.63</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
       <c r="A31" s="26" t="inlineStr">
         <is>
-          <t>KB금융</t>
+          <t>에코프로머티</t>
         </is>
       </c>
       <c r="B31" s="25" t="n">
@@ -4094,25 +4100,25 @@
       </c>
       <c r="F31" s="25" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G31" s="25" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="H31" s="29" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="I31" s="29" t="n">
-        <v>3.45</v>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="H31" s="27" t="n">
+        <v>-6.47</v>
+      </c>
+      <c r="I31" s="27" t="n">
+        <v>-11.42</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
       <c r="A32" s="26" t="inlineStr">
         <is>
-          <t>NH투자증권</t>
+          <t>에코프로에이치엔</t>
         </is>
       </c>
       <c r="B32" s="25" t="n">
@@ -4129,25 +4135,25 @@
       </c>
       <c r="F32" s="25" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G32" s="25" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="H32" s="29" t="n">
-        <v>0.86</v>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="H32" s="27" t="n">
+        <v>-4.41</v>
       </c>
       <c r="I32" s="29" t="n">
-        <v>2.26</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
       <c r="A33" s="26" t="inlineStr">
         <is>
-          <t>아크솔루션스</t>
+          <t>포스코DX</t>
         </is>
       </c>
       <c r="B33" s="25" t="n">
@@ -4164,165 +4170,165 @@
       </c>
       <c r="F33" s="25" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G33" s="25" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="H33" s="29" t="n">
-        <v>0.87</v>
-      </c>
-      <c r="I33" s="27" t="n">
-        <v>-97.38</v>
+        <v>4.85</v>
+      </c>
+      <c r="I33" s="29" t="n">
+        <v>1.79</v>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
       <c r="A34" s="26" t="inlineStr">
         <is>
-          <t>CMG제약</t>
+          <t>포스코스틸리온</t>
         </is>
       </c>
       <c r="B34" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C34" s="25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D34" s="25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E34" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F34" s="25" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G34" s="25" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="H34" s="27" t="n">
-        <v>-2.86</v>
-      </c>
-      <c r="I34" s="29" t="n">
-        <v>3.79</v>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="H34" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" s="27" t="n">
+        <v>-2.65</v>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
       <c r="A35" s="26" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>포스코인터내셔널</t>
         </is>
       </c>
       <c r="B35" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C35" s="25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D35" s="25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E35" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F35" s="25" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G35" s="25" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="H35" s="27" t="n">
-        <v>-2.19</v>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="H35" s="29" t="n">
+        <v>4.37</v>
       </c>
       <c r="I35" s="29" t="n">
-        <v>1.44</v>
+        <v>1.58</v>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
       <c r="A36" s="26" t="inlineStr">
         <is>
-          <t>골프존홀딩스</t>
+          <t>포스코퓨처엠</t>
         </is>
       </c>
       <c r="B36" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C36" s="25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D36" s="25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E36" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F36" s="25" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G36" s="25" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="H36" s="29" t="n">
-        <v>19.89</v>
-      </c>
-      <c r="I36" s="29" t="n">
-        <v>47.66</v>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="H36" s="27" t="n">
+        <v>-3.08</v>
+      </c>
+      <c r="I36" s="27" t="n">
+        <v>-4.44</v>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
       <c r="A37" s="26" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>한화손해보험</t>
         </is>
       </c>
       <c r="B37" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C37" s="25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D37" s="25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E37" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F37" s="25" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G37" s="25" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="H37" s="27" t="n">
-        <v>-4.9</v>
+        <v>-2.37</v>
       </c>
       <c r="I37" s="27" t="n">
-        <v>-2.79</v>
+        <v>-0.86</v>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
       <c r="A38" s="26" t="inlineStr">
         <is>
-          <t>카카오뱅크</t>
+          <t>GS건설</t>
         </is>
       </c>
       <c r="B38" s="25" t="n">
@@ -4339,25 +4345,25 @@
       </c>
       <c r="F38" s="25" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G38" s="25" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="H38" s="27" t="n">
-        <v>-1.18</v>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="H38" s="29" t="n">
+        <v>19.92</v>
       </c>
       <c r="I38" s="29" t="n">
-        <v>3.21</v>
+        <v>20.16</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
       <c r="A39" s="26" t="inlineStr">
         <is>
-          <t>한화엔진</t>
+          <t>HD현대중공업</t>
         </is>
       </c>
       <c r="B39" s="25" t="n">
@@ -4374,200 +4380,196 @@
       </c>
       <c r="F39" s="25" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G39" s="25" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="H39" s="27" t="n">
-        <v>-0.97</v>
-      </c>
-      <c r="I39" s="27" t="n">
-        <v>-4.67</v>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="H39" s="29" t="n">
+        <v>3.89</v>
+      </c>
+      <c r="I39" s="29" t="n">
+        <v>4.77</v>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
       <c r="A40" s="26" t="inlineStr">
         <is>
-          <t>CSA 코스믹</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B40" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C40" s="25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D40" s="25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E40" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F40" s="25" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G40" s="25" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="H40" s="27" t="n">
-        <v>-1.67</v>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="H40" s="29" t="n">
+        <v>3.08</v>
       </c>
       <c r="I40" s="27" t="n">
-        <v>-7.81</v>
+        <v>-0.31</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
       <c r="A41" s="26" t="inlineStr">
         <is>
-          <t>SK스퀘어</t>
+          <t>성호전자</t>
         </is>
       </c>
       <c r="B41" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C41" s="25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D41" s="25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E41" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F41" s="25" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G41" s="25" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="H41" s="29" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="I41" s="27" t="n">
-        <v>-7.37</v>
+        <v>3.2</v>
+      </c>
+      <c r="I41" s="29" t="n">
+        <v>1.83</v>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
       <c r="A42" s="26" t="inlineStr">
         <is>
-          <t>뉴인텍</t>
+          <t>아크솔루션스</t>
         </is>
       </c>
       <c r="B42" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C42" s="25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D42" s="25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E42" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F42" s="25" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G42" s="25" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="H42" s="27" t="n">
-        <v>-13.78</v>
-      </c>
-      <c r="I42" s="29" t="n">
-        <v>8.859999999999999</v>
+        <v>-22.41</v>
+      </c>
+      <c r="I42" s="27" t="n">
+        <v>-97.97</v>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1">
       <c r="A43" s="26" t="inlineStr">
         <is>
-          <t>대명에너지</t>
+          <t>에임드바이오</t>
         </is>
       </c>
       <c r="B43" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C43" s="25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D43" s="25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E43" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F43" s="25" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G43" s="25" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="H43" s="27" t="n">
-        <v>-9.93</v>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="H43" s="29" t="n">
+        <v>7.17</v>
       </c>
       <c r="I43" s="29" t="n">
-        <v>25.67</v>
+        <v>7.39</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
       <c r="A44" s="26" t="inlineStr">
         <is>
-          <t>삼호개발</t>
+          <t>철강</t>
         </is>
       </c>
       <c r="B44" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C44" s="25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D44" s="25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E44" s="32" t="n">
         <v>1</v>
       </c>
       <c r="F44" s="25" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G44" s="25" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="H44" s="27" t="n">
-        <v>-9.699999999999999</v>
-      </c>
-      <c r="I44" s="29" t="n">
-        <v>7.24</v>
-      </c>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="H44" s="25" t="n"/>
+      <c r="I44" s="25" t="n"/>
     </row>
     <row r="45" ht="18" customHeight="1">
       <c r="A45" s="26" t="inlineStr">
         <is>
-          <t>아모텍</t>
+          <t>SK네트웍스</t>
         </is>
       </c>
       <c r="B45" s="25" t="n">
@@ -4584,25 +4586,25 @@
       </c>
       <c r="F45" s="25" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G45" s="25" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="H45" s="27" t="n">
-        <v>-3.35</v>
-      </c>
-      <c r="I45" s="27" t="n">
-        <v>-17.97</v>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="H45" s="29" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="I45" s="29" t="n">
+        <v>7.97</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
       <c r="A46" s="26" t="inlineStr">
         <is>
-          <t>앱튼</t>
+          <t>금호건설</t>
         </is>
       </c>
       <c r="B46" s="25" t="n">
@@ -4619,25 +4621,25 @@
       </c>
       <c r="F46" s="25" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G46" s="25" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="H46" s="29" t="n">
-        <v>29.72</v>
+        <v>29.94</v>
       </c>
       <c r="I46" s="29" t="n">
-        <v>180.8</v>
+        <v>200.1</v>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
       <c r="A47" s="26" t="inlineStr">
         <is>
-          <t>에이프릴바이오</t>
+          <t>금호전기</t>
         </is>
       </c>
       <c r="B47" s="25" t="n">
@@ -4654,25 +4656,25 @@
       </c>
       <c r="F47" s="25" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G47" s="25" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="H47" s="27" t="n">
-        <v>-4.81</v>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="H47" s="29" t="n">
+        <v>18.31</v>
       </c>
       <c r="I47" s="29" t="n">
-        <v>18.05</v>
+        <v>177.8</v>
       </c>
     </row>
     <row r="48" ht="18" customHeight="1">
       <c r="A48" s="26" t="inlineStr">
         <is>
-          <t>우리금융지주</t>
+          <t>대한항공</t>
         </is>
       </c>
       <c r="B48" s="25" t="n">
@@ -4689,25 +4691,25 @@
       </c>
       <c r="F48" s="25" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G48" s="25" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="H48" s="27" t="n">
-        <v>-0.34</v>
-      </c>
-      <c r="I48" s="27" t="n">
-        <v>-1.53</v>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="H48" s="29" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="I48" s="29" t="n">
+        <v>1.65</v>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1">
       <c r="A49" s="26" t="inlineStr">
         <is>
-          <t>져스텍</t>
+          <t>스트라드비젼</t>
         </is>
       </c>
       <c r="B49" s="25" t="n">
@@ -4724,25 +4726,25 @@
       </c>
       <c r="F49" s="25" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G49" s="25" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="H49" s="27" t="n">
-        <v>-5.08</v>
+        <v>-18.89</v>
       </c>
       <c r="I49" s="27" t="n">
-        <v>-5.08</v>
+        <v>-18.89</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
       <c r="A50" s="26" t="inlineStr">
         <is>
-          <t>지니너스</t>
+          <t>앱튼</t>
         </is>
       </c>
       <c r="B50" s="25" t="n">
@@ -4759,25 +4761,25 @@
       </c>
       <c r="F50" s="25" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G50" s="25" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="H50" s="29" t="n">
-        <v>6.75</v>
+        <v>15.94</v>
       </c>
       <c r="I50" s="29" t="n">
-        <v>11.87</v>
+        <v>230.26</v>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
       <c r="A51" s="26" t="inlineStr">
         <is>
-          <t>클래시스</t>
+          <t>에스폴리텍</t>
         </is>
       </c>
       <c r="B51" s="25" t="n">
@@ -4794,25 +4796,25 @@
       </c>
       <c r="F51" s="25" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G51" s="25" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="H51" s="27" t="n">
-        <v>-5.57</v>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="H51" s="29" t="n">
+        <v>4.07</v>
       </c>
       <c r="I51" s="29" t="n">
-        <v>6.27</v>
+        <v>30.19</v>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1">
       <c r="A52" s="26" t="inlineStr">
         <is>
-          <t>플리토</t>
+          <t>져스텍</t>
         </is>
       </c>
       <c r="B52" s="25" t="n">
@@ -4829,19 +4831,19 @@
       </c>
       <c r="F52" s="25" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G52" s="25" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="H52" s="29" t="n">
-        <v>5.48</v>
-      </c>
-      <c r="I52" s="29" t="n">
-        <v>24.19</v>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="H52" s="27" t="n">
+        <v>-10.7</v>
+      </c>
+      <c r="I52" s="27" t="n">
+        <v>-15.23</v>
       </c>
     </row>
   </sheetData>
@@ -4925,19 +4927,19 @@
         <v>1</v>
       </c>
       <c r="C3" s="36" t="n">
-        <v>108</v>
+        <v>96</v>
       </c>
       <c r="D3" s="36" t="n">
-        <v>108</v>
+        <v>96</v>
       </c>
       <c r="E3" s="36" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="F3" s="37" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G3" s="37" t="inlineStr">
@@ -4956,19 +4958,19 @@
         <v>1</v>
       </c>
       <c r="C4" s="36" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="D4" s="36" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E4" s="36" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="F4" s="37" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G4" s="37" t="inlineStr">
@@ -4987,19 +4989,19 @@
         <v>1</v>
       </c>
       <c r="C5" s="36" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="D5" s="36" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="E5" s="36" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="F5" s="37" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G5" s="37" t="inlineStr">
@@ -5011,26 +5013,26 @@
     <row r="6" ht="18" customHeight="1">
       <c r="A6" s="35" t="inlineStr">
         <is>
-          <t>로봇</t>
+          <t>방산</t>
         </is>
       </c>
       <c r="B6" s="36" t="n">
         <v>1</v>
       </c>
       <c r="C6" s="36" t="n">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="D6" s="36" t="n">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="E6" s="36" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="F6" s="37" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G6" s="37" t="inlineStr">
@@ -5042,26 +5044,26 @@
     <row r="7" ht="18" customHeight="1">
       <c r="A7" s="35" t="inlineStr">
         <is>
-          <t>철강</t>
+          <t>로봇</t>
         </is>
       </c>
       <c r="B7" s="36" t="n">
         <v>1</v>
       </c>
       <c r="C7" s="36" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="D7" s="36" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E7" s="36" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="F7" s="37" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G7" s="37" t="inlineStr">
@@ -5073,26 +5075,26 @@
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="35" t="inlineStr">
         <is>
-          <t>제약</t>
+          <t>클라우드</t>
         </is>
       </c>
       <c r="B8" s="36" t="n">
         <v>1</v>
       </c>
       <c r="C8" s="36" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D8" s="36" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E8" s="36" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="F8" s="37" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G8" s="37" t="inlineStr">
@@ -5104,92 +5106,100 @@
     <row r="9" ht="18" customHeight="1">
       <c r="A9" s="35" t="inlineStr">
         <is>
+          <t>철강</t>
+        </is>
+      </c>
+      <c r="B9" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" s="36" t="n">
+        <v>4</v>
+      </c>
+      <c r="D9" s="36" t="n">
+        <v>4</v>
+      </c>
+      <c r="E9" s="36" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="F9" s="37" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="G9" s="37" t="inlineStr">
+        <is>
+          <t>⚡ 관심</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="18" customHeight="1">
+      <c r="A10" s="35" t="inlineStr">
+        <is>
+          <t>제약</t>
+        </is>
+      </c>
+      <c r="B10" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" s="36" t="n">
+        <v>6</v>
+      </c>
+      <c r="D10" s="36" t="n">
+        <v>6</v>
+      </c>
+      <c r="E10" s="36" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="F10" s="37" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="G10" s="37" t="inlineStr">
+        <is>
+          <t>⚡ 관심</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="18" customHeight="1">
+      <c r="A11" s="35" t="inlineStr">
+        <is>
           <t>인공지능</t>
         </is>
       </c>
-      <c r="B9" s="36" t="n">
-        <v>1</v>
-      </c>
-      <c r="C9" s="36" t="n">
-        <v>21</v>
-      </c>
-      <c r="D9" s="36" t="n">
-        <v>21</v>
-      </c>
-      <c r="E9" s="36" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="F9" s="37" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="G9" s="37" t="inlineStr">
+      <c r="B11" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" s="36" t="n">
+        <v>22</v>
+      </c>
+      <c r="D11" s="36" t="n">
+        <v>22</v>
+      </c>
+      <c r="E11" s="36" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="F11" s="37" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="G11" s="37" t="inlineStr">
         <is>
           <t>⚡ 관심</t>
         </is>
       </c>
-    </row>
-    <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="26" t="inlineStr">
-        <is>
-          <t>이차전지</t>
-        </is>
-      </c>
-      <c r="B10" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="C10" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" s="25" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F10" s="28" t="inlineStr">
-        <is>
-          <t>감지 없음</t>
-        </is>
-      </c>
-      <c r="G10" s="28" t="inlineStr"/>
-    </row>
-    <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="26" t="inlineStr">
-        <is>
-          <t>AI반도체</t>
-        </is>
-      </c>
-      <c r="B11" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="C11" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" s="25" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F11" s="28" t="inlineStr">
-        <is>
-          <t>감지 없음</t>
-        </is>
-      </c>
-      <c r="G11" s="28" t="inlineStr"/>
     </row>
     <row r="12" ht="18" customHeight="1">
       <c r="A12" s="26" t="inlineStr">
         <is>
-          <t>방산</t>
+          <t>이차전지</t>
         </is>
       </c>
       <c r="B12" s="25" t="n">
@@ -5216,7 +5226,7 @@
     <row r="13" ht="18" customHeight="1">
       <c r="A13" s="26" t="inlineStr">
         <is>
-          <t>원전</t>
+          <t>AI반도체</t>
         </is>
       </c>
       <c r="B13" s="25" t="n">
@@ -5243,7 +5253,7 @@
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="26" t="inlineStr">
         <is>
-          <t>수소</t>
+          <t>원전</t>
         </is>
       </c>
       <c r="B14" s="25" t="n">
@@ -5270,7 +5280,7 @@
     <row r="15" ht="18" customHeight="1">
       <c r="A15" s="26" t="inlineStr">
         <is>
-          <t>태양광</t>
+          <t>수소</t>
         </is>
       </c>
       <c r="B15" s="25" t="n">
@@ -5297,7 +5307,7 @@
     <row r="16" ht="18" customHeight="1">
       <c r="A16" s="26" t="inlineStr">
         <is>
-          <t>게임</t>
+          <t>태양광</t>
         </is>
       </c>
       <c r="B16" s="25" t="n">
@@ -5324,7 +5334,7 @@
     <row r="17" ht="18" customHeight="1">
       <c r="A17" s="26" t="inlineStr">
         <is>
-          <t>엔터</t>
+          <t>게임</t>
         </is>
       </c>
       <c r="B17" s="25" t="n">
@@ -5351,7 +5361,7 @@
     <row r="18" ht="18" customHeight="1">
       <c r="A18" s="26" t="inlineStr">
         <is>
-          <t>핀테크</t>
+          <t>엔터</t>
         </is>
       </c>
       <c r="B18" s="25" t="n">
@@ -5378,7 +5388,7 @@
     <row r="19" ht="18" customHeight="1">
       <c r="A19" s="26" t="inlineStr">
         <is>
-          <t>클라우드</t>
+          <t>핀테크</t>
         </is>
       </c>
       <c r="B19" s="25" t="n">

--- a/trend/stock_trend_history.xlsx
+++ b/trend/stock_trend_history.xlsx
@@ -258,13 +258,13 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -273,13 +273,13 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -694,7 +694,7 @@
     <row r="1" ht="36" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>📊 주식 트렌드 조기 감지 대시보드   |   최종 업데이트: 2026-07-02 06:54</t>
+          <t>📊 주식 트렌드 조기 감지 대시보드   |   최종 업데이트: 2026-07-03 06:54</t>
         </is>
       </c>
     </row>
@@ -708,7 +708,7 @@
       </c>
       <c r="E3" s="3" t="n"/>
       <c r="G3" s="5" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="H3" s="3" t="n"/>
       <c r="J3" s="6" t="n">
@@ -787,21 +787,21 @@
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="11" t="inlineStr">
         <is>
-          <t>⚡ 최신(2026-07-02) 상위: 반도체  점수 96.0점</t>
+          <t>⚡ 최신(2026-07-03) 상위: 반도체  점수 82.0점</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1">
       <c r="A11" s="12" t="inlineStr">
         <is>
-          <t>⚡ 최신(2026-07-02) 상위: SK  점수 44.0점</t>
+          <t>⚡ 최신(2026-07-03) 상위: SK  점수 44.0점</t>
         </is>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1">
       <c r="A12" s="11" t="inlineStr">
         <is>
-          <t>⚡ 최신(2026-07-02) 상위: 삼성전자  점수 41.0점</t>
+          <t>⚡ 최신(2026-07-03) 상위: 바이오  점수 24.0점</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B14" s="15" t="n">
@@ -928,10 +928,10 @@
         </is>
       </c>
       <c r="D14" s="15" t="n">
-        <v>96</v>
+        <v>82</v>
       </c>
       <c r="E14" s="15" t="n">
-        <v>96</v>
+        <v>82</v>
       </c>
       <c r="F14" s="15" t="n">
         <v>0</v>
@@ -947,7 +947,7 @@
       </c>
       <c r="J14" s="17" t="inlineStr">
         <is>
-          <t>네이버뉴스 기사 언급 / 네이버뉴스 헤드라인 언급 / 매일경제 기사 언급 / 매일경제 헤드라인 언급 / 네이버뉴스 기사 언급</t>
+          <t>매일경제 헤드라인 언급 / 매일경제 기사 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 헤드라인 언급 / 한국경제 헤드라인 언급</t>
         </is>
       </c>
       <c r="K14" s="17" t="inlineStr">
@@ -959,7 +959,7 @@
     <row r="15" ht="18" customHeight="1">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B15" s="15" t="n">
@@ -983,14 +983,14 @@
         <v>0</v>
       </c>
       <c r="H15" s="18" t="n">
-        <v>-8.51</v>
-      </c>
-      <c r="I15" s="19" t="n">
-        <v>7.16</v>
+        <v>-10.48</v>
+      </c>
+      <c r="I15" s="18" t="n">
+        <v>-20.4</v>
       </c>
       <c r="J15" s="17" t="inlineStr">
         <is>
-          <t>네이버뉴스 헤드라인 언급 / 매일경제 헤드라인 언급 / 네이버뉴스 헤드라인 언급 / 한국경제 헤드라인 언급 / 매일경제 헤드라인 언급</t>
+          <t>매일경제 기사 언급 / 한국경제 헤드라인 언급 / 매일경제 기사 언급 / 네이버뉴스 기사 언급 / 한국경제 헤드라인 언급</t>
         </is>
       </c>
       <c r="K15" s="17" t="inlineStr">
@@ -1002,7 +1002,7 @@
     <row r="16" ht="18" customHeight="1">
       <c r="A16" s="15" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B16" s="15" t="n">
@@ -1010,14 +1010,14 @@
       </c>
       <c r="C16" s="16" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>바이오</t>
         </is>
       </c>
       <c r="D16" s="15" t="n">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="E16" s="15" t="n">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="F16" s="15" t="n">
         <v>0</v>
@@ -1025,15 +1025,15 @@
       <c r="G16" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="H16" s="18" t="n">
-        <v>-5.84</v>
-      </c>
-      <c r="I16" s="18" t="n">
-        <v>-7.64</v>
+      <c r="H16" s="15" t="n">
+        <v/>
+      </c>
+      <c r="I16" s="15" t="n">
+        <v/>
       </c>
       <c r="J16" s="17" t="inlineStr">
         <is>
-          <t>매일경제 헤드라인 언급 / 한국경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 네이버뉴스 헤드라인 언급 / 매일경제 기사 언급</t>
+          <t>한국경제 헤드라인 언급 / 매일경제 기사 언급 / 매일경제 헤드라인 언급 / 네이버뉴스 헤드라인 언급 / 네이버뉴스 헤드라인 언급</t>
         </is>
       </c>
       <c r="K16" s="17" t="inlineStr">
@@ -1045,7 +1045,7 @@
     <row r="17" ht="18" customHeight="1">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B17" s="15" t="n">
@@ -1053,42 +1053,40 @@
       </c>
       <c r="C17" s="16" t="inlineStr">
         <is>
-          <t>에코프로</t>
+          <t>로봇</t>
         </is>
       </c>
       <c r="D17" s="15" t="n">
         <v>22</v>
       </c>
       <c r="E17" s="15" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F17" s="15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G17" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="H17" s="18" t="n">
-        <v>-12.76</v>
-      </c>
-      <c r="I17" s="18" t="n">
-        <v>-13.65</v>
+      <c r="H17" s="15" t="n">
+        <v/>
+      </c>
+      <c r="I17" s="15" t="n">
+        <v/>
       </c>
       <c r="J17" s="17" t="inlineStr">
         <is>
-          <t>중요공시 2건 / 중요공시 3일 +100% / Google 급상승 검색어 등장 (KR) / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K17" s="17" t="inlineStr">
-        <is>
-          <t>Google, 공시</t>
-        </is>
+          <t>한국경제 헤드라인 언급 / 한국경제 헤드라인 언급 / 한국경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 기사 언급</t>
+        </is>
+      </c>
+      <c r="K17" s="17" t="n">
+        <v/>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
       <c r="A18" s="15" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B18" s="15" t="n">
@@ -1096,14 +1094,14 @@
       </c>
       <c r="C18" s="16" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="D18" s="15" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E18" s="15" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F18" s="15" t="n">
         <v>0</v>
@@ -1112,14 +1110,14 @@
         <v>0</v>
       </c>
       <c r="H18" s="18" t="n">
-        <v>-3.4</v>
+        <v>-9.06</v>
       </c>
       <c r="I18" s="18" t="n">
-        <v>-0.78</v>
+        <v>-20.22</v>
       </c>
       <c r="J18" s="17" t="inlineStr">
         <is>
-          <t>네이버뉴스 헤드라인 언급 / 매일경제 헤드라인 언급 / 네이버뉴스 헤드라인 언급 / 한국경제 헤드라인 언급 / 매일경제 기사 언급</t>
+          <t>매일경제 헤드라인 언급 / 한국경제 헤드라인 언급 / 매일경제 기사 언급 / 네이버뉴스 기사 언급 / 매일경제 헤드라인 언급</t>
         </is>
       </c>
       <c r="K18" s="17" t="inlineStr">
@@ -1131,7 +1129,7 @@
     <row r="19" ht="18" customHeight="1">
       <c r="A19" s="15" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B19" s="15" t="n">
@@ -1139,14 +1137,14 @@
       </c>
       <c r="C19" s="16" t="inlineStr">
         <is>
-          <t>인공지능</t>
+          <t>한화오션</t>
         </is>
       </c>
       <c r="D19" s="15" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E19" s="15" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F19" s="15" t="n">
         <v>0</v>
@@ -1154,27 +1152,27 @@
       <c r="G19" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="H19" s="15" t="n">
-        <v/>
-      </c>
-      <c r="I19" s="15" t="n">
-        <v/>
+      <c r="H19" s="19" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="I19" s="18" t="n">
+        <v>-1.04</v>
       </c>
       <c r="J19" s="17" t="inlineStr">
         <is>
-          <t>네이버뉴스 기사 언급 / 매일경제 기사 언급 / 네이버뉴스 기사 언급 / 매일경제 기사 언급 / 매일경제 기사 언급</t>
+          <t>중요공시 1건 / 네이버뉴스 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
         </is>
       </c>
       <c r="K19" s="17" t="inlineStr">
         <is>
-          <t>네이버</t>
+          <t>네이버, 공시</t>
         </is>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
       <c r="A20" s="15" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B20" s="15" t="n">
@@ -1182,7 +1180,7 @@
       </c>
       <c r="C20" s="16" t="inlineStr">
         <is>
-          <t>LG</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="D20" s="15" t="n">
@@ -1198,26 +1196,26 @@
         <v>0</v>
       </c>
       <c r="H20" s="18" t="n">
-        <v>-0.72</v>
+        <v>-14.57</v>
       </c>
       <c r="I20" s="18" t="n">
-        <v>-2.62</v>
+        <v>-25.03</v>
       </c>
       <c r="J20" s="17" t="inlineStr">
         <is>
-          <t>Google 급상승 검색어 등장 (KR) / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급</t>
+          <t>매일경제 기사 언급 / 한국경제 헤드라인 언급 / 매일경제 기사 언급 / 네이버뉴스 기사 언급 / 매일경제 헤드라인 언급</t>
         </is>
       </c>
       <c r="K20" s="17" t="inlineStr">
         <is>
-          <t>Google</t>
+          <t>네이버</t>
         </is>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
       <c r="A21" s="15" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B21" s="15" t="n">
@@ -1225,14 +1223,14 @@
       </c>
       <c r="C21" s="16" t="inlineStr">
         <is>
-          <t>삼성전기</t>
+          <t>전기차</t>
         </is>
       </c>
       <c r="D21" s="15" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E21" s="15" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F21" s="15" t="n">
         <v>0</v>
@@ -1240,27 +1238,27 @@
       <c r="G21" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="H21" s="19" t="n">
-        <v>0.96</v>
-      </c>
-      <c r="I21" s="19" t="n">
-        <v>12.27</v>
+      <c r="H21" s="15" t="n">
+        <v/>
+      </c>
+      <c r="I21" s="15" t="n">
+        <v/>
       </c>
       <c r="J21" s="17" t="inlineStr">
         <is>
-          <t>중요공시 1건 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 기사 언급 / 매일경제 헤드라인 언급</t>
+          <t>한국경제 헤드라인 언급 / 네이버뉴스 헤드라인 언급 / 네이버뉴스 기사 언급 / 한국경제 헤드라인 언급 / 매일경제 헤드라인 언급</t>
         </is>
       </c>
       <c r="K21" s="17" t="inlineStr">
         <is>
-          <t>공시</t>
+          <t>네이버</t>
         </is>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
       <c r="A22" s="15" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B22" s="15" t="n">
@@ -1268,14 +1266,14 @@
       </c>
       <c r="C22" s="16" t="inlineStr">
         <is>
-          <t>바이오</t>
+          <t>인공지능</t>
         </is>
       </c>
       <c r="D22" s="15" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="E22" s="15" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="F22" s="15" t="n">
         <v>0</v>
@@ -1291,7 +1289,7 @@
       </c>
       <c r="J22" s="17" t="inlineStr">
         <is>
-          <t>매일경제 헤드라인 언급 / 네이버뉴스 헤드라인 언급 / 네이버뉴스 헤드라인 언급 / 한국경제 헤드라인 언급 / 네이버뉴스 헤드라인 언급</t>
+          <t>매일경제 기사 언급 / 매일경제 기사 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 기사 언급 / 매일경제 기사 언급</t>
         </is>
       </c>
       <c r="K22" s="17" t="inlineStr">
@@ -1303,7 +1301,7 @@
     <row r="23" ht="18" customHeight="1">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B23" s="15" t="n">
@@ -1311,42 +1309,42 @@
       </c>
       <c r="C23" s="16" t="inlineStr">
         <is>
-          <t>전기차</t>
+          <t>셀트리온</t>
         </is>
       </c>
       <c r="D23" s="15" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="E23" s="15" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="F23" s="15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G23" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="H23" s="15" t="n">
-        <v/>
-      </c>
-      <c r="I23" s="15" t="n">
-        <v/>
+      <c r="H23" s="19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="I23" s="19" t="n">
+        <v>2.02</v>
       </c>
       <c r="J23" s="17" t="inlineStr">
         <is>
-          <t>네이버뉴스 헤드라인 언급 / 매일경제 기사 언급 / 한국경제 헤드라인 언급 / 한국경제 헤드라인 언급 / 매일경제 헤드라인 언급</t>
+          <t>중요공시 2건 / 중요공시 3일 +100% / 한국경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 네이버뉴스 헤드라인 언급</t>
         </is>
       </c>
       <c r="K23" s="17" t="inlineStr">
         <is>
-          <t>네이버</t>
+          <t>네이버, 공시</t>
         </is>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B24" s="15" t="n">
@@ -1354,14 +1352,14 @@
       </c>
       <c r="C24" s="16" t="inlineStr">
         <is>
-          <t>에코프로비엠</t>
+          <t>현대차</t>
         </is>
       </c>
       <c r="D24" s="15" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E24" s="15" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F24" s="15" t="n">
         <v>0</v>
@@ -1370,26 +1368,26 @@
         <v>0</v>
       </c>
       <c r="H24" s="18" t="n">
-        <v>-6.88</v>
+        <v>-1.13</v>
       </c>
       <c r="I24" s="18" t="n">
-        <v>-12.98</v>
+        <v>-4.17</v>
       </c>
       <c r="J24" s="17" t="inlineStr">
         <is>
-          <t>중요공시 3건 / Google 급상승 검색어 등장 (KR) / 매일경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
+          <t>매일경제 기사 언급 / 매일경제 헤드라인 언급 / 한국경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 네이버뉴스 헤드라인 언급</t>
         </is>
       </c>
       <c r="K24" s="17" t="inlineStr">
         <is>
-          <t>Google, 공시</t>
+          <t>네이버</t>
         </is>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
       <c r="A25" s="15" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B25" s="15" t="n">
@@ -1397,40 +1395,42 @@
       </c>
       <c r="C25" s="16" t="inlineStr">
         <is>
-          <t>현대차</t>
+          <t>광진실업</t>
         </is>
       </c>
       <c r="D25" s="15" t="n">
         <v>11</v>
       </c>
       <c r="E25" s="15" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="F25" s="15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G25" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H25" s="18" t="n">
-        <v>-1.52</v>
-      </c>
-      <c r="I25" s="18" t="n">
-        <v>-4.22</v>
+        <v>3</v>
+      </c>
+      <c r="H25" s="19" t="n">
+        <v>30</v>
+      </c>
+      <c r="I25" s="19" t="n">
+        <v>31.71</v>
       </c>
       <c r="J25" s="17" t="inlineStr">
         <is>
-          <t>매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K25" s="17" t="n">
-        <v/>
+          <t>중요공시 5건 / 중요공시 3일 +400% / 중요공시 7일 +400% / 매일경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K25" s="17" t="inlineStr">
+        <is>
+          <t>공시</t>
+        </is>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
       <c r="A26" s="15" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B26" s="15" t="n">
@@ -1438,14 +1438,14 @@
       </c>
       <c r="C26" s="16" t="inlineStr">
         <is>
-          <t>SK스퀘어</t>
+          <t>삼성전기</t>
         </is>
       </c>
       <c r="D26" s="15" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E26" s="15" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F26" s="15" t="n">
         <v>0</v>
@@ -1453,27 +1453,27 @@
       <c r="G26" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="H26" s="19" t="n">
-        <v>3.54</v>
+      <c r="H26" s="18" t="n">
+        <v>-12.65</v>
       </c>
       <c r="I26" s="18" t="n">
-        <v>-2.33</v>
+        <v>-3.56</v>
       </c>
       <c r="J26" s="17" t="inlineStr">
         <is>
-          <t>중요공시 1건 / 네이버뉴스 헤드라인 언급 / 네이버뉴스 헤드라인 언급 / 매일경제 헤드라인 언급</t>
+          <t>중요공시 2건 / 매일경제 헤드라인 언급 / 매일경제 기사 언급 / 한국경제 헤드라인 언급 / 매일경제 기사 언급</t>
         </is>
       </c>
       <c r="K26" s="17" t="inlineStr">
         <is>
-          <t>네이버, 공시</t>
+          <t>공시</t>
         </is>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
       <c r="A27" s="15" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B27" s="15" t="n">
@@ -1481,14 +1481,14 @@
       </c>
       <c r="C27" s="16" t="inlineStr">
         <is>
-          <t>스테이블코인</t>
+          <t>DB</t>
         </is>
       </c>
       <c r="D27" s="15" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E27" s="15" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F27" s="15" t="n">
         <v>0</v>
@@ -1496,25 +1496,27 @@
       <c r="G27" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="H27" s="15" t="n">
-        <v/>
-      </c>
-      <c r="I27" s="15" t="n">
-        <v/>
+      <c r="H27" s="18" t="n">
+        <v>-8.07</v>
+      </c>
+      <c r="I27" s="18" t="n">
+        <v>-11.33</v>
       </c>
       <c r="J27" s="17" t="inlineStr">
         <is>
-          <t>매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 기사 언급 / 매일경제 기사 언급 / 매일경제 기사 언급</t>
-        </is>
-      </c>
-      <c r="K27" s="17" t="n">
-        <v/>
+          <t>한국경제 헤드라인 언급 / 한국경제 헤드라인 언급 / 네이버뉴스 헤드라인 언급 / 매일경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K27" s="17" t="inlineStr">
+        <is>
+          <t>네이버</t>
+        </is>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
       <c r="A28" s="15" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B28" s="15" t="n">
@@ -1522,14 +1524,14 @@
       </c>
       <c r="C28" s="16" t="inlineStr">
         <is>
-          <t>방산</t>
+          <t>삼성증권</t>
         </is>
       </c>
       <c r="D28" s="15" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E28" s="15" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F28" s="15" t="n">
         <v>0</v>
@@ -1537,25 +1539,27 @@
       <c r="G28" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="H28" s="15" t="n">
-        <v/>
-      </c>
-      <c r="I28" s="15" t="n">
-        <v/>
+      <c r="H28" s="18" t="n">
+        <v>-4.26</v>
+      </c>
+      <c r="I28" s="18" t="n">
+        <v>-2.62</v>
       </c>
       <c r="J28" s="17" t="inlineStr">
         <is>
-          <t>한국경제 헤드라인 언급 / 한국경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K28" s="17" t="n">
-        <v/>
+          <t>한국경제 헤드라인 언급 / 한국경제 헤드라인 언급 / 네이버뉴스 헤드라인 언급 / 매일경제 기사 언급</t>
+        </is>
+      </c>
+      <c r="K28" s="17" t="inlineStr">
+        <is>
+          <t>네이버</t>
+        </is>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
       <c r="A29" s="15" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B29" s="15" t="n">
@@ -1563,42 +1567,40 @@
       </c>
       <c r="C29" s="16" t="inlineStr">
         <is>
-          <t>셀트리온</t>
+          <t>클라우드</t>
         </is>
       </c>
       <c r="D29" s="15" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E29" s="15" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F29" s="15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G29" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="H29" s="19" t="n">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="I29" s="19" t="n">
-        <v>1.04</v>
+      <c r="H29" s="15" t="n">
+        <v/>
+      </c>
+      <c r="I29" s="15" t="n">
+        <v/>
       </c>
       <c r="J29" s="17" t="inlineStr">
         <is>
-          <t>중요공시 2건 / 중요공시 3일 +100% / Google 급상승 검색어 등장 (KR)</t>
-        </is>
-      </c>
-      <c r="K29" s="17" t="inlineStr">
-        <is>
-          <t>Google, 공시</t>
-        </is>
+          <t>매일경제 기사 언급 / 매일경제 기사 언급 / 매일경제 헤드라인 언급 / 매일경제 헤드라인 언급 / 매일경제 기사 언급</t>
+        </is>
+      </c>
+      <c r="K29" s="17" t="n">
+        <v/>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
       <c r="A30" s="15" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B30" s="15" t="n">
@@ -1606,171 +1608,167 @@
       </c>
       <c r="C30" s="16" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>제약</t>
         </is>
       </c>
       <c r="D30" s="15" t="n">
+        <v>9</v>
+      </c>
+      <c r="E30" s="15" t="n">
+        <v>9</v>
+      </c>
+      <c r="F30" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" s="15" t="n">
+        <v/>
+      </c>
+      <c r="I30" s="15" t="n">
+        <v/>
+      </c>
+      <c r="J30" s="17" t="inlineStr">
+        <is>
+          <t>매일경제 기사 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 헤드라인 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 기사 언급</t>
+        </is>
+      </c>
+      <c r="K30" s="17" t="inlineStr">
+        <is>
+          <t>네이버</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="18" customHeight="1">
+      <c r="A31" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B31" s="15" t="n">
+        <v>18</v>
+      </c>
+      <c r="C31" s="16" t="inlineStr">
+        <is>
+          <t>카카오</t>
+        </is>
+      </c>
+      <c r="D31" s="15" t="n">
         <v>8</v>
       </c>
-      <c r="E30" s="15" t="n">
+      <c r="E31" s="15" t="n">
         <v>8</v>
       </c>
-      <c r="F30" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G30" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H30" s="19" t="n">
-        <v>10.11</v>
-      </c>
-      <c r="I30" s="19" t="n">
-        <v>10.44</v>
-      </c>
-      <c r="J30" s="17" t="inlineStr">
-        <is>
-          <t>Google 급상승 검색어 등장 (US) / 매일경제 헤드라인 언급</t>
-        </is>
-      </c>
-      <c r="K30" s="17" t="inlineStr">
-        <is>
-          <t>Google</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="18" customHeight="1">
-      <c r="A31" s="20" t="inlineStr">
-        <is>
-          <t>2026-07-02</t>
-        </is>
-      </c>
-      <c r="B31" s="20" t="n">
-        <v>18</v>
-      </c>
-      <c r="C31" s="21" t="inlineStr">
-        <is>
-          <t>모바일어플라이언스</t>
-        </is>
-      </c>
-      <c r="D31" s="20" t="n">
-        <v>6</v>
-      </c>
-      <c r="E31" s="20" t="n">
-        <v>3</v>
-      </c>
-      <c r="F31" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G31" s="20" t="n">
-        <v>3</v>
-      </c>
-      <c r="H31" s="22" t="n">
-        <v>-29.89</v>
-      </c>
-      <c r="I31" s="22" t="n">
-        <v>-15.87</v>
-      </c>
-      <c r="J31" s="23" t="inlineStr">
-        <is>
-          <t>중요공시 3건 / 중요공시 7일 +200%</t>
-        </is>
-      </c>
-      <c r="K31" s="23" t="inlineStr">
+      <c r="F31" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" s="19" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="I31" s="19" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="J31" s="17" t="inlineStr">
+        <is>
+          <t>매일경제 헤드라인 언급 / 한국경제 헤드라인 언급 / 매일경제 기사 언급 / 매일경제 기사 언급</t>
+        </is>
+      </c>
+      <c r="K31" s="17" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="32" ht="18" customHeight="1">
+      <c r="A32" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B32" s="15" t="n">
+        <v>19</v>
+      </c>
+      <c r="C32" s="16" t="inlineStr">
+        <is>
+          <t>기아</t>
+        </is>
+      </c>
+      <c r="D32" s="15" t="n">
+        <v>8</v>
+      </c>
+      <c r="E32" s="15" t="n">
+        <v>8</v>
+      </c>
+      <c r="F32" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" s="19" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="I32" s="19" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="J32" s="17" t="inlineStr">
+        <is>
+          <t>중요공시 1건 / 매일경제 기사 언급 / 매일경제 헤드라인 언급 / 한국경제 헤드라인 언급</t>
+        </is>
+      </c>
+      <c r="K32" s="17" t="inlineStr">
         <is>
           <t>공시</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="18" customHeight="1">
-      <c r="A32" s="20" t="inlineStr">
-        <is>
-          <t>2026-07-02</t>
-        </is>
-      </c>
-      <c r="B32" s="20" t="n">
-        <v>19</v>
-      </c>
-      <c r="C32" s="21" t="inlineStr">
-        <is>
-          <t>스피어</t>
-        </is>
-      </c>
-      <c r="D32" s="20" t="n">
-        <v>6</v>
-      </c>
-      <c r="E32" s="20" t="n">
-        <v>3</v>
-      </c>
-      <c r="F32" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G32" s="20" t="n">
-        <v>3</v>
-      </c>
-      <c r="H32" s="24" t="n">
-        <v>20.13</v>
-      </c>
-      <c r="I32" s="24" t="n">
-        <v>31.07</v>
-      </c>
-      <c r="J32" s="23" t="inlineStr">
-        <is>
-          <t>중요공시 7건 / 중요공시 7일 +250%</t>
-        </is>
-      </c>
-      <c r="K32" s="23" t="inlineStr">
-        <is>
-          <t>공시</t>
-        </is>
-      </c>
-    </row>
     <row r="33" ht="18" customHeight="1">
-      <c r="A33" s="20" t="inlineStr">
-        <is>
-          <t>2026-07-02</t>
-        </is>
-      </c>
-      <c r="B33" s="20" t="n">
+      <c r="A33" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B33" s="15" t="n">
         <v>20</v>
       </c>
-      <c r="C33" s="21" t="inlineStr">
-        <is>
-          <t>파두</t>
-        </is>
-      </c>
-      <c r="D33" s="20" t="n">
-        <v>6</v>
-      </c>
-      <c r="E33" s="20" t="n">
-        <v>3</v>
-      </c>
-      <c r="F33" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G33" s="20" t="n">
-        <v>3</v>
-      </c>
-      <c r="H33" s="22" t="n">
-        <v>-5.6</v>
-      </c>
-      <c r="I33" s="22" t="n">
-        <v>-4.29</v>
-      </c>
-      <c r="J33" s="23" t="inlineStr">
-        <is>
-          <t>중요공시 4건 / 중요공시 7일 +100%</t>
-        </is>
-      </c>
-      <c r="K33" s="23" t="inlineStr">
-        <is>
-          <t>공시</t>
-        </is>
+      <c r="C33" s="16" t="inlineStr">
+        <is>
+          <t>네이버</t>
+        </is>
+      </c>
+      <c r="D33" s="15" t="n">
+        <v>8</v>
+      </c>
+      <c r="E33" s="15" t="n">
+        <v>8</v>
+      </c>
+      <c r="F33" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" s="15" t="n">
+        <v/>
+      </c>
+      <c r="I33" s="15" t="n">
+        <v/>
+      </c>
+      <c r="J33" s="17" t="inlineStr">
+        <is>
+          <t>매일경제 헤드라인 언급 / 한국경제 헤드라인 언급 / 매일경제 기사 언급 / 매일경제 기사 언급</t>
+        </is>
+      </c>
+      <c r="K33" s="17" t="n">
+        <v/>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
       <c r="A34" s="20" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B34" s="20" t="n">
@@ -1778,30 +1776,30 @@
       </c>
       <c r="C34" s="21" t="inlineStr">
         <is>
-          <t>HJ중공업</t>
+          <t>진흥기업</t>
         </is>
       </c>
       <c r="D34" s="20" t="n">
         <v>6</v>
       </c>
       <c r="E34" s="20" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F34" s="20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G34" s="20" t="n">
         <v>3</v>
       </c>
-      <c r="H34" s="24" t="n">
-        <v>0.74</v>
+      <c r="H34" s="22" t="n">
+        <v>29.92</v>
       </c>
       <c r="I34" s="22" t="n">
-        <v>-2.4</v>
+        <v>55.8</v>
       </c>
       <c r="J34" s="23" t="inlineStr">
         <is>
-          <t>중요공시 3건 / 중요공시 7일 +50%</t>
+          <t>중요공시 2건 / 중요공시 3일 +100% / 중요공시 7일 +100%</t>
         </is>
       </c>
       <c r="K34" s="23" t="inlineStr">
@@ -1813,7 +1811,7 @@
     <row r="35" ht="18" customHeight="1">
       <c r="A35" s="20" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B35" s="20" t="n">
@@ -1821,42 +1819,42 @@
       </c>
       <c r="C35" s="21" t="inlineStr">
         <is>
-          <t>제약</t>
+          <t>스피어</t>
         </is>
       </c>
       <c r="D35" s="20" t="n">
         <v>6</v>
       </c>
       <c r="E35" s="20" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F35" s="20" t="n">
         <v>0</v>
       </c>
       <c r="G35" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H35" s="20" t="n">
-        <v/>
-      </c>
-      <c r="I35" s="20" t="n">
-        <v/>
+        <v>3</v>
+      </c>
+      <c r="H35" s="24" t="n">
+        <v>-13.01</v>
+      </c>
+      <c r="I35" s="22" t="n">
+        <v>28.69</v>
       </c>
       <c r="J35" s="23" t="inlineStr">
         <is>
-          <t>매일경제 기사 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 기사 언급 / 네이버뉴스 기사 언급</t>
+          <t>중요공시 7건 / 중요공시 7일 +250%</t>
         </is>
       </c>
       <c r="K35" s="23" t="inlineStr">
         <is>
-          <t>네이버</t>
+          <t>공시</t>
         </is>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
       <c r="A36" s="20" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B36" s="20" t="n">
@@ -1864,42 +1862,42 @@
       </c>
       <c r="C36" s="21" t="inlineStr">
         <is>
-          <t>로봇</t>
+          <t>성호전자</t>
         </is>
       </c>
       <c r="D36" s="20" t="n">
         <v>6</v>
       </c>
       <c r="E36" s="20" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F36" s="20" t="n">
         <v>0</v>
       </c>
       <c r="G36" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H36" s="20" t="n">
-        <v/>
-      </c>
-      <c r="I36" s="20" t="n">
-        <v/>
+        <v>3</v>
+      </c>
+      <c r="H36" s="24" t="n">
+        <v>-28.43</v>
+      </c>
+      <c r="I36" s="24" t="n">
+        <v>-23.83</v>
       </c>
       <c r="J36" s="23" t="inlineStr">
         <is>
-          <t>매일경제 헤드라인 언급 / 매일경제 기사 언급 / 네이버뉴스 헤드라인 언급</t>
+          <t>중요공시 2건 / 중요공시 7일 +100% / 한국경제 헤드라인 언급</t>
         </is>
       </c>
       <c r="K36" s="23" t="inlineStr">
         <is>
-          <t>네이버</t>
+          <t>공시</t>
         </is>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
       <c r="A37" s="20" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B37" s="20" t="n">
@@ -1907,42 +1905,42 @@
       </c>
       <c r="C37" s="21" t="inlineStr">
         <is>
-          <t>클라우드</t>
+          <t>파두</t>
         </is>
       </c>
       <c r="D37" s="20" t="n">
         <v>6</v>
       </c>
       <c r="E37" s="20" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F37" s="20" t="n">
         <v>0</v>
       </c>
       <c r="G37" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H37" s="20" t="n">
-        <v/>
-      </c>
-      <c r="I37" s="20" t="n">
-        <v/>
+        <v>3</v>
+      </c>
+      <c r="H37" s="24" t="n">
+        <v>-7.99</v>
+      </c>
+      <c r="I37" s="24" t="n">
+        <v>-13.14</v>
       </c>
       <c r="J37" s="23" t="inlineStr">
         <is>
-          <t>네이버뉴스 헤드라인 언급 / 한국경제 헤드라인 언급</t>
+          <t>중요공시 3건 / 중요공시 7일 +200%</t>
         </is>
       </c>
       <c r="K37" s="23" t="in